--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.02.20261</t>
-  </si>
-  <si>
-    <t>25.02.20262</t>
-  </si>
-  <si>
-    <t>25.02.20263</t>
-  </si>
-  <si>
-    <t>25.02.20264</t>
-  </si>
-  <si>
-    <t>25.02.20265</t>
-  </si>
-  <si>
-    <t>25.02.20266</t>
-  </si>
-  <si>
-    <t>25.02.20267</t>
-  </si>
-  <si>
-    <t>25.02.20268</t>
-  </si>
-  <si>
-    <t>25.02.20269</t>
-  </si>
-  <si>
-    <t>25.02.202610</t>
-  </si>
-  <si>
-    <t>25.02.202611</t>
-  </si>
-  <si>
-    <t>25.02.202612</t>
-  </si>
-  <si>
-    <t>25.02.202613</t>
-  </si>
-  <si>
-    <t>25.02.202614</t>
-  </si>
-  <si>
-    <t>25.02.202615</t>
-  </si>
-  <si>
-    <t>25.02.202616</t>
-  </si>
-  <si>
-    <t>25.02.202617</t>
-  </si>
-  <si>
-    <t>25.02.202618</t>
-  </si>
-  <si>
-    <t>25.02.202619</t>
-  </si>
-  <si>
-    <t>25.02.202620</t>
-  </si>
-  <si>
-    <t>25.02.202621</t>
-  </si>
-  <si>
-    <t>25.02.202622</t>
-  </si>
-  <si>
-    <t>25.02.202623</t>
-  </si>
-  <si>
-    <t>25.02.202624</t>
-  </si>
-  <si>
-    <t>25.02.202625</t>
-  </si>
-  <si>
-    <t>25.02.202626</t>
-  </si>
-  <si>
-    <t>25.02.202627</t>
-  </si>
-  <si>
-    <t>25.02.202628</t>
-  </si>
-  <si>
-    <t>25.02.202629</t>
-  </si>
-  <si>
-    <t>25.02.202630</t>
-  </si>
-  <si>
-    <t>25.02.202631</t>
-  </si>
-  <si>
-    <t>25.02.202632</t>
-  </si>
-  <si>
-    <t>25.02.202633</t>
-  </si>
-  <si>
-    <t>25.02.202634</t>
-  </si>
-  <si>
-    <t>25.02.202635</t>
-  </si>
-  <si>
-    <t>25.02.202636</t>
-  </si>
-  <si>
-    <t>25.02.202637</t>
-  </si>
-  <si>
-    <t>25.02.202638</t>
-  </si>
-  <si>
-    <t>25.02.202639</t>
-  </si>
-  <si>
-    <t>25.02.202640</t>
-  </si>
-  <si>
-    <t>25.02.202641</t>
-  </si>
-  <si>
-    <t>25.02.202642</t>
-  </si>
-  <si>
-    <t>25.02.202643</t>
-  </si>
-  <si>
-    <t>25.02.202644</t>
-  </si>
-  <si>
-    <t>25.02.202645</t>
-  </si>
-  <si>
-    <t>25.02.202646</t>
-  </si>
-  <si>
-    <t>25.02.202647</t>
-  </si>
-  <si>
-    <t>25.02.202648</t>
-  </si>
-  <si>
-    <t>25.02.202649</t>
-  </si>
-  <si>
-    <t>25.02.202650</t>
-  </si>
-  <si>
-    <t>25.02.202651</t>
-  </si>
-  <si>
-    <t>25.02.202652</t>
-  </si>
-  <si>
-    <t>25.02.202653</t>
-  </si>
-  <si>
-    <t>25.02.202654</t>
-  </si>
-  <si>
-    <t>25.02.202655</t>
-  </si>
-  <si>
-    <t>25.02.202656</t>
-  </si>
-  <si>
-    <t>25.02.202657</t>
-  </si>
-  <si>
-    <t>25.02.202658</t>
-  </si>
-  <si>
-    <t>25.02.202659</t>
-  </si>
-  <si>
-    <t>25.02.202660</t>
-  </si>
-  <si>
-    <t>25.02.202661</t>
-  </si>
-  <si>
-    <t>25.02.202662</t>
-  </si>
-  <si>
-    <t>25.02.202663</t>
-  </si>
-  <si>
-    <t>25.02.202664</t>
-  </si>
-  <si>
-    <t>25.02.202665</t>
-  </si>
-  <si>
-    <t>25.02.202666</t>
-  </si>
-  <si>
-    <t>25.02.202667</t>
-  </si>
-  <si>
-    <t>25.02.202668</t>
-  </si>
-  <si>
-    <t>25.02.202669</t>
-  </si>
-  <si>
-    <t>25.02.202670</t>
-  </si>
-  <si>
-    <t>25.02.202671</t>
-  </si>
-  <si>
-    <t>25.02.202672</t>
-  </si>
-  <si>
-    <t>25.02.202673</t>
-  </si>
-  <si>
-    <t>25.02.202674</t>
-  </si>
-  <si>
-    <t>25.02.202675</t>
-  </si>
-  <si>
-    <t>25.02.202676</t>
-  </si>
-  <si>
-    <t>25.02.202677</t>
-  </si>
-  <si>
-    <t>25.02.202678</t>
-  </si>
-  <si>
-    <t>25.02.202679</t>
-  </si>
-  <si>
-    <t>25.02.202680</t>
-  </si>
-  <si>
-    <t>25.02.202681</t>
-  </si>
-  <si>
-    <t>25.02.202682</t>
-  </si>
-  <si>
-    <t>25.02.202683</t>
-  </si>
-  <si>
-    <t>25.02.202684</t>
-  </si>
-  <si>
-    <t>25.02.202685</t>
-  </si>
-  <si>
-    <t>25.02.202686</t>
-  </si>
-  <si>
-    <t>25.02.202687</t>
-  </si>
-  <si>
-    <t>25.02.202688</t>
-  </si>
-  <si>
-    <t>25.02.202689</t>
-  </si>
-  <si>
-    <t>25.02.202690</t>
-  </si>
-  <si>
-    <t>25.02.202691</t>
-  </si>
-  <si>
-    <t>25.02.202692</t>
-  </si>
-  <si>
-    <t>25.02.202693</t>
-  </si>
-  <si>
-    <t>25.02.202694</t>
-  </si>
-  <si>
-    <t>25.02.202695</t>
-  </si>
-  <si>
-    <t>25.02.202696</t>
-  </si>
-  <si>
-    <t>26.02.20261</t>
-  </si>
-  <si>
-    <t>26.02.20262</t>
-  </si>
-  <si>
-    <t>26.02.20263</t>
-  </si>
-  <si>
-    <t>26.02.20264</t>
-  </si>
-  <si>
-    <t>26.02.20265</t>
-  </si>
-  <si>
-    <t>26.02.20266</t>
-  </si>
-  <si>
-    <t>26.02.20267</t>
-  </si>
-  <si>
-    <t>26.02.20268</t>
-  </si>
-  <si>
-    <t>26.02.20269</t>
-  </si>
-  <si>
-    <t>26.02.202610</t>
-  </si>
-  <si>
-    <t>26.02.202611</t>
-  </si>
-  <si>
-    <t>26.02.202612</t>
-  </si>
-  <si>
-    <t>26.02.202613</t>
-  </si>
-  <si>
-    <t>26.02.202614</t>
-  </si>
-  <si>
-    <t>26.02.202615</t>
-  </si>
-  <si>
-    <t>26.02.202616</t>
-  </si>
-  <si>
-    <t>26.02.202617</t>
-  </si>
-  <si>
-    <t>26.02.202618</t>
-  </si>
-  <si>
-    <t>26.02.202619</t>
-  </si>
-  <si>
-    <t>26.02.202620</t>
-  </si>
-  <si>
-    <t>26.02.202621</t>
-  </si>
-  <si>
-    <t>26.02.202622</t>
-  </si>
-  <si>
-    <t>26.02.202623</t>
-  </si>
-  <si>
-    <t>26.02.202624</t>
-  </si>
-  <si>
-    <t>26.02.202625</t>
-  </si>
-  <si>
-    <t>26.02.202626</t>
-  </si>
-  <si>
-    <t>26.02.202627</t>
-  </si>
-  <si>
-    <t>26.02.202628</t>
-  </si>
-  <si>
-    <t>26.02.202629</t>
-  </si>
-  <si>
-    <t>26.02.202630</t>
-  </si>
-  <si>
-    <t>26.02.202631</t>
-  </si>
-  <si>
-    <t>26.02.202632</t>
-  </si>
-  <si>
-    <t>26.02.202633</t>
-  </si>
-  <si>
-    <t>26.02.202634</t>
-  </si>
-  <si>
-    <t>26.02.202635</t>
-  </si>
-  <si>
-    <t>26.02.202636</t>
-  </si>
-  <si>
-    <t>26.02.202637</t>
-  </si>
-  <si>
-    <t>26.02.202638</t>
-  </si>
-  <si>
-    <t>26.02.202639</t>
-  </si>
-  <si>
-    <t>26.02.202640</t>
-  </si>
-  <si>
-    <t>26.02.202641</t>
-  </si>
-  <si>
-    <t>26.02.202642</t>
-  </si>
-  <si>
-    <t>26.02.202643</t>
-  </si>
-  <si>
-    <t>26.02.202644</t>
-  </si>
-  <si>
-    <t>26.02.202645</t>
-  </si>
-  <si>
-    <t>26.02.202646</t>
-  </si>
-  <si>
-    <t>26.02.202647</t>
-  </si>
-  <si>
-    <t>26.02.202648</t>
-  </si>
-  <si>
-    <t>26.02.202649</t>
-  </si>
-  <si>
-    <t>26.02.202650</t>
-  </si>
-  <si>
-    <t>26.02.202651</t>
-  </si>
-  <si>
-    <t>26.02.202652</t>
-  </si>
-  <si>
-    <t>26.02.202653</t>
-  </si>
-  <si>
-    <t>26.02.202654</t>
-  </si>
-  <si>
-    <t>26.02.202655</t>
-  </si>
-  <si>
-    <t>26.02.202656</t>
-  </si>
-  <si>
-    <t>26.02.202657</t>
-  </si>
-  <si>
-    <t>26.02.202658</t>
-  </si>
-  <si>
-    <t>26.02.202659</t>
-  </si>
-  <si>
-    <t>26.02.202660</t>
-  </si>
-  <si>
-    <t>26.02.202661</t>
-  </si>
-  <si>
-    <t>26.02.202662</t>
-  </si>
-  <si>
-    <t>26.02.202663</t>
-  </si>
-  <si>
-    <t>26.02.202664</t>
-  </si>
-  <si>
-    <t>26.02.202665</t>
-  </si>
-  <si>
-    <t>26.02.202666</t>
-  </si>
-  <si>
-    <t>26.02.202667</t>
-  </si>
-  <si>
-    <t>26.02.202668</t>
-  </si>
-  <si>
-    <t>26.02.202669</t>
-  </si>
-  <si>
-    <t>26.02.202670</t>
-  </si>
-  <si>
-    <t>26.02.202671</t>
-  </si>
-  <si>
-    <t>26.02.202672</t>
-  </si>
-  <si>
-    <t>26.02.202673</t>
-  </si>
-  <si>
-    <t>26.02.202674</t>
-  </si>
-  <si>
-    <t>26.02.202675</t>
-  </si>
-  <si>
-    <t>26.02.202676</t>
-  </si>
-  <si>
-    <t>26.02.202677</t>
-  </si>
-  <si>
-    <t>26.02.202678</t>
-  </si>
-  <si>
-    <t>26.02.202679</t>
-  </si>
-  <si>
-    <t>26.02.202680</t>
-  </si>
-  <si>
-    <t>26.02.202681</t>
-  </si>
-  <si>
-    <t>26.02.202682</t>
-  </si>
-  <si>
-    <t>26.02.202683</t>
-  </si>
-  <si>
-    <t>26.02.202684</t>
-  </si>
-  <si>
-    <t>26.02.202685</t>
-  </si>
-  <si>
-    <t>26.02.202686</t>
-  </si>
-  <si>
-    <t>26.02.202687</t>
-  </si>
-  <si>
-    <t>26.02.202688</t>
-  </si>
-  <si>
-    <t>26.02.202689</t>
-  </si>
-  <si>
-    <t>26.02.202690</t>
-  </si>
-  <si>
-    <t>26.02.202691</t>
-  </si>
-  <si>
-    <t>26.02.202692</t>
-  </si>
-  <si>
-    <t>26.02.202693</t>
-  </si>
-  <si>
-    <t>26.02.202694</t>
-  </si>
-  <si>
-    <t>26.02.202695</t>
-  </si>
-  <si>
-    <t>26.02.202696</t>
+    <t>12.03.20261</t>
+  </si>
+  <si>
+    <t>12.03.20262</t>
+  </si>
+  <si>
+    <t>12.03.20263</t>
+  </si>
+  <si>
+    <t>12.03.20264</t>
+  </si>
+  <si>
+    <t>12.03.20265</t>
+  </si>
+  <si>
+    <t>12.03.20266</t>
+  </si>
+  <si>
+    <t>12.03.20267</t>
+  </si>
+  <si>
+    <t>12.03.20268</t>
+  </si>
+  <si>
+    <t>12.03.20269</t>
+  </si>
+  <si>
+    <t>12.03.202610</t>
+  </si>
+  <si>
+    <t>12.03.202611</t>
+  </si>
+  <si>
+    <t>12.03.202612</t>
+  </si>
+  <si>
+    <t>12.03.202613</t>
+  </si>
+  <si>
+    <t>12.03.202614</t>
+  </si>
+  <si>
+    <t>12.03.202615</t>
+  </si>
+  <si>
+    <t>12.03.202616</t>
+  </si>
+  <si>
+    <t>12.03.202617</t>
+  </si>
+  <si>
+    <t>12.03.202618</t>
+  </si>
+  <si>
+    <t>12.03.202619</t>
+  </si>
+  <si>
+    <t>12.03.202620</t>
+  </si>
+  <si>
+    <t>12.03.202621</t>
+  </si>
+  <si>
+    <t>12.03.202622</t>
+  </si>
+  <si>
+    <t>12.03.202623</t>
+  </si>
+  <si>
+    <t>12.03.202624</t>
+  </si>
+  <si>
+    <t>12.03.202625</t>
+  </si>
+  <si>
+    <t>12.03.202626</t>
+  </si>
+  <si>
+    <t>12.03.202627</t>
+  </si>
+  <si>
+    <t>12.03.202628</t>
+  </si>
+  <si>
+    <t>12.03.202629</t>
+  </si>
+  <si>
+    <t>12.03.202630</t>
+  </si>
+  <si>
+    <t>12.03.202631</t>
+  </si>
+  <si>
+    <t>12.03.202632</t>
+  </si>
+  <si>
+    <t>12.03.202633</t>
+  </si>
+  <si>
+    <t>12.03.202634</t>
+  </si>
+  <si>
+    <t>12.03.202635</t>
+  </si>
+  <si>
+    <t>12.03.202636</t>
+  </si>
+  <si>
+    <t>12.03.202637</t>
+  </si>
+  <si>
+    <t>12.03.202638</t>
+  </si>
+  <si>
+    <t>12.03.202639</t>
+  </si>
+  <si>
+    <t>12.03.202640</t>
+  </si>
+  <si>
+    <t>12.03.202641</t>
+  </si>
+  <si>
+    <t>12.03.202642</t>
+  </si>
+  <si>
+    <t>12.03.202643</t>
+  </si>
+  <si>
+    <t>12.03.202644</t>
+  </si>
+  <si>
+    <t>12.03.202645</t>
+  </si>
+  <si>
+    <t>12.03.202646</t>
+  </si>
+  <si>
+    <t>12.03.202647</t>
+  </si>
+  <si>
+    <t>12.03.202648</t>
+  </si>
+  <si>
+    <t>12.03.202649</t>
+  </si>
+  <si>
+    <t>12.03.202650</t>
+  </si>
+  <si>
+    <t>12.03.202651</t>
+  </si>
+  <si>
+    <t>12.03.202652</t>
+  </si>
+  <si>
+    <t>12.03.202653</t>
+  </si>
+  <si>
+    <t>12.03.202654</t>
+  </si>
+  <si>
+    <t>12.03.202655</t>
+  </si>
+  <si>
+    <t>12.03.202656</t>
+  </si>
+  <si>
+    <t>12.03.202657</t>
+  </si>
+  <si>
+    <t>12.03.202658</t>
+  </si>
+  <si>
+    <t>12.03.202659</t>
+  </si>
+  <si>
+    <t>12.03.202660</t>
+  </si>
+  <si>
+    <t>12.03.202661</t>
+  </si>
+  <si>
+    <t>12.03.202662</t>
+  </si>
+  <si>
+    <t>12.03.202663</t>
+  </si>
+  <si>
+    <t>12.03.202664</t>
+  </si>
+  <si>
+    <t>12.03.202665</t>
+  </si>
+  <si>
+    <t>12.03.202666</t>
+  </si>
+  <si>
+    <t>12.03.202667</t>
+  </si>
+  <si>
+    <t>12.03.202668</t>
+  </si>
+  <si>
+    <t>12.03.202669</t>
+  </si>
+  <si>
+    <t>12.03.202670</t>
+  </si>
+  <si>
+    <t>12.03.202671</t>
+  </si>
+  <si>
+    <t>12.03.202672</t>
+  </si>
+  <si>
+    <t>12.03.202673</t>
+  </si>
+  <si>
+    <t>12.03.202674</t>
+  </si>
+  <si>
+    <t>12.03.202675</t>
+  </si>
+  <si>
+    <t>12.03.202676</t>
+  </si>
+  <si>
+    <t>12.03.202677</t>
+  </si>
+  <si>
+    <t>12.03.202678</t>
+  </si>
+  <si>
+    <t>12.03.202679</t>
+  </si>
+  <si>
+    <t>12.03.202680</t>
+  </si>
+  <si>
+    <t>12.03.202681</t>
+  </si>
+  <si>
+    <t>12.03.202682</t>
+  </si>
+  <si>
+    <t>12.03.202683</t>
+  </si>
+  <si>
+    <t>12.03.202684</t>
+  </si>
+  <si>
+    <t>12.03.202685</t>
+  </si>
+  <si>
+    <t>12.03.202686</t>
+  </si>
+  <si>
+    <t>12.03.202687</t>
+  </si>
+  <si>
+    <t>12.03.202688</t>
+  </si>
+  <si>
+    <t>12.03.202689</t>
+  </si>
+  <si>
+    <t>12.03.202690</t>
+  </si>
+  <si>
+    <t>12.03.202691</t>
+  </si>
+  <si>
+    <t>12.03.202692</t>
+  </si>
+  <si>
+    <t>12.03.202693</t>
+  </si>
+  <si>
+    <t>12.03.202694</t>
+  </si>
+  <si>
+    <t>12.03.202695</t>
+  </si>
+  <si>
+    <t>12.03.202696</t>
+  </si>
+  <si>
+    <t>13.03.20261</t>
+  </si>
+  <si>
+    <t>13.03.20262</t>
+  </si>
+  <si>
+    <t>13.03.20263</t>
+  </si>
+  <si>
+    <t>13.03.20264</t>
+  </si>
+  <si>
+    <t>13.03.20265</t>
+  </si>
+  <si>
+    <t>13.03.20266</t>
+  </si>
+  <si>
+    <t>13.03.20267</t>
+  </si>
+  <si>
+    <t>13.03.20268</t>
+  </si>
+  <si>
+    <t>13.03.20269</t>
+  </si>
+  <si>
+    <t>13.03.202610</t>
+  </si>
+  <si>
+    <t>13.03.202611</t>
+  </si>
+  <si>
+    <t>13.03.202612</t>
+  </si>
+  <si>
+    <t>13.03.202613</t>
+  </si>
+  <si>
+    <t>13.03.202614</t>
+  </si>
+  <si>
+    <t>13.03.202615</t>
+  </si>
+  <si>
+    <t>13.03.202616</t>
+  </si>
+  <si>
+    <t>13.03.202617</t>
+  </si>
+  <si>
+    <t>13.03.202618</t>
+  </si>
+  <si>
+    <t>13.03.202619</t>
+  </si>
+  <si>
+    <t>13.03.202620</t>
+  </si>
+  <si>
+    <t>13.03.202621</t>
+  </si>
+  <si>
+    <t>13.03.202622</t>
+  </si>
+  <si>
+    <t>13.03.202623</t>
+  </si>
+  <si>
+    <t>13.03.202624</t>
+  </si>
+  <si>
+    <t>13.03.202625</t>
+  </si>
+  <si>
+    <t>13.03.202626</t>
+  </si>
+  <si>
+    <t>13.03.202627</t>
+  </si>
+  <si>
+    <t>13.03.202628</t>
+  </si>
+  <si>
+    <t>13.03.202629</t>
+  </si>
+  <si>
+    <t>13.03.202630</t>
+  </si>
+  <si>
+    <t>13.03.202631</t>
+  </si>
+  <si>
+    <t>13.03.202632</t>
+  </si>
+  <si>
+    <t>13.03.202633</t>
+  </si>
+  <si>
+    <t>13.03.202634</t>
+  </si>
+  <si>
+    <t>13.03.202635</t>
+  </si>
+  <si>
+    <t>13.03.202636</t>
+  </si>
+  <si>
+    <t>13.03.202637</t>
+  </si>
+  <si>
+    <t>13.03.202638</t>
+  </si>
+  <si>
+    <t>13.03.202639</t>
+  </si>
+  <si>
+    <t>13.03.202640</t>
+  </si>
+  <si>
+    <t>13.03.202641</t>
+  </si>
+  <si>
+    <t>13.03.202642</t>
+  </si>
+  <si>
+    <t>13.03.202643</t>
+  </si>
+  <si>
+    <t>13.03.202644</t>
+  </si>
+  <si>
+    <t>13.03.202645</t>
+  </si>
+  <si>
+    <t>13.03.202646</t>
+  </si>
+  <si>
+    <t>13.03.202647</t>
+  </si>
+  <si>
+    <t>13.03.202648</t>
+  </si>
+  <si>
+    <t>13.03.202649</t>
+  </si>
+  <si>
+    <t>13.03.202650</t>
+  </si>
+  <si>
+    <t>13.03.202651</t>
+  </si>
+  <si>
+    <t>13.03.202652</t>
+  </si>
+  <si>
+    <t>13.03.202653</t>
+  </si>
+  <si>
+    <t>13.03.202654</t>
+  </si>
+  <si>
+    <t>13.03.202655</t>
+  </si>
+  <si>
+    <t>13.03.202656</t>
+  </si>
+  <si>
+    <t>13.03.202657</t>
+  </si>
+  <si>
+    <t>13.03.202658</t>
+  </si>
+  <si>
+    <t>13.03.202659</t>
+  </si>
+  <si>
+    <t>13.03.202660</t>
+  </si>
+  <si>
+    <t>13.03.202661</t>
+  </si>
+  <si>
+    <t>13.03.202662</t>
+  </si>
+  <si>
+    <t>13.03.202663</t>
+  </si>
+  <si>
+    <t>13.03.202664</t>
+  </si>
+  <si>
+    <t>13.03.202665</t>
+  </si>
+  <si>
+    <t>13.03.202666</t>
+  </si>
+  <si>
+    <t>13.03.202667</t>
+  </si>
+  <si>
+    <t>13.03.202668</t>
+  </si>
+  <si>
+    <t>13.03.202669</t>
+  </si>
+  <si>
+    <t>13.03.202670</t>
+  </si>
+  <si>
+    <t>13.03.202671</t>
+  </si>
+  <si>
+    <t>13.03.202672</t>
+  </si>
+  <si>
+    <t>13.03.202673</t>
+  </si>
+  <si>
+    <t>13.03.202674</t>
+  </si>
+  <si>
+    <t>13.03.202675</t>
+  </si>
+  <si>
+    <t>13.03.202676</t>
+  </si>
+  <si>
+    <t>13.03.202677</t>
+  </si>
+  <si>
+    <t>13.03.202678</t>
+  </si>
+  <si>
+    <t>13.03.202679</t>
+  </si>
+  <si>
+    <t>13.03.202680</t>
+  </si>
+  <si>
+    <t>13.03.202681</t>
+  </si>
+  <si>
+    <t>13.03.202682</t>
+  </si>
+  <si>
+    <t>13.03.202683</t>
+  </si>
+  <si>
+    <t>13.03.202684</t>
+  </si>
+  <si>
+    <t>13.03.202685</t>
+  </si>
+  <si>
+    <t>13.03.202686</t>
+  </si>
+  <si>
+    <t>13.03.202687</t>
+  </si>
+  <si>
+    <t>13.03.202688</t>
+  </si>
+  <si>
+    <t>13.03.202689</t>
+  </si>
+  <si>
+    <t>13.03.202690</t>
+  </si>
+  <si>
+    <t>13.03.202691</t>
+  </si>
+  <si>
+    <t>13.03.202692</t>
+  </si>
+  <si>
+    <t>13.03.202693</t>
+  </si>
+  <si>
+    <t>13.03.202694</t>
+  </si>
+  <si>
+    <t>13.03.202695</t>
+  </si>
+  <si>
+    <t>13.03.202696</t>
   </si>
 </sst>
 </file>
@@ -988,10 +988,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="B2">
-        <v>0.531</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46078.01041666666</v>
+        <v>46093.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46078.02083333334</v>
+        <v>46093.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46078.03125</v>
+        <v>46093.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46078.04166666666</v>
+        <v>46093.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46078.05208333334</v>
+        <v>46093.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46078.0625</v>
+        <v>46093.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46078.07291666666</v>
+        <v>46093.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46078.08333333334</v>
+        <v>46093.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46078.09375</v>
+        <v>46093.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46078.10416666666</v>
+        <v>46093.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46078.11458333334</v>
+        <v>46093.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46078.125</v>
+        <v>46093.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46078.13541666666</v>
+        <v>46093.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46078.14583333334</v>
+        <v>46093.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46078.15625</v>
+        <v>46093.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46078.16666666666</v>
+        <v>46093.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1.237</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46078.17708333334</v>
+        <v>46093.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46078.1875</v>
+        <v>46093.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46078.19791666666</v>
+        <v>46093.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>3.237</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46078.20833333334</v>
+        <v>46093.20833333334</v>
       </c>
       <c r="B22">
-        <v>22.553</v>
+        <v>5.742</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46078.21875</v>
+        <v>46093.21875</v>
       </c>
       <c r="B23">
-        <v>22.593</v>
+        <v>6.439</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46078.22916666666</v>
+        <v>46093.22916666666</v>
       </c>
       <c r="B24">
-        <v>22.625</v>
+        <v>8.803000000000001</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46078.23958333334</v>
+        <v>46093.23958333334</v>
       </c>
       <c r="B25">
-        <v>22.912</v>
+        <v>18.585</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46078.25</v>
+        <v>46093.25</v>
       </c>
       <c r="B26">
-        <v>48.109</v>
+        <v>100.923</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46078.26041666666</v>
+        <v>46093.26041666666</v>
       </c>
       <c r="B27">
-        <v>76.37</v>
+        <v>169.292</v>
       </c>
       <c r="C27">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46078.27083333334</v>
+        <v>46093.27083333334</v>
       </c>
       <c r="B28">
-        <v>124.264</v>
+        <v>260.796</v>
       </c>
       <c r="C28">
-        <v>93</v>
+        <v>223</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46078.28125</v>
+        <v>46093.28125</v>
       </c>
       <c r="B29">
-        <v>185.962</v>
+        <v>376.636</v>
       </c>
       <c r="C29">
-        <v>207</v>
+        <v>321</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46078.29166666666</v>
+        <v>46093.29166666666</v>
       </c>
       <c r="B30">
-        <v>365.145</v>
+        <v>647.819</v>
       </c>
       <c r="C30">
-        <v>334</v>
+        <v>452</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46078.30208333334</v>
+        <v>46093.30208333334</v>
       </c>
       <c r="B31">
-        <v>488.453</v>
+        <v>780.478</v>
       </c>
       <c r="C31">
-        <v>480</v>
+        <v>569</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46078.3125</v>
+        <v>46093.3125</v>
       </c>
       <c r="B32">
-        <v>632.057</v>
+        <v>974.6609999999999</v>
       </c>
       <c r="C32">
-        <v>593</v>
+        <v>679</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46078.32291666666</v>
+        <v>46093.32291666666</v>
       </c>
       <c r="B33">
-        <v>772.99</v>
+        <v>1141.383</v>
       </c>
       <c r="C33">
-        <v>745</v>
+        <v>800</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46078.33333333334</v>
+        <v>46093.33333333334</v>
       </c>
       <c r="B34">
-        <v>1035.591</v>
+        <v>1420.476</v>
       </c>
       <c r="C34">
-        <v>844</v>
+        <v>910</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46078.34375</v>
+        <v>46093.34375</v>
       </c>
       <c r="B35">
-        <v>1174.674</v>
+        <v>1564.533</v>
       </c>
       <c r="C35">
-        <v>971</v>
+        <v>1002</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46078.35416666666</v>
+        <v>46093.35416666666</v>
       </c>
       <c r="B36">
-        <v>1301.23</v>
+        <v>1717.566</v>
       </c>
       <c r="C36">
-        <v>1067</v>
+        <v>1102</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46078.36458333334</v>
+        <v>46093.36458333334</v>
       </c>
       <c r="B37">
-        <v>1413.128</v>
+        <v>1863.588</v>
       </c>
       <c r="C37">
-        <v>1215</v>
+        <v>1196</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46078.375</v>
+        <v>46093.375</v>
       </c>
       <c r="B38">
-        <v>1575.038</v>
+        <v>2077.24</v>
       </c>
       <c r="C38">
-        <v>1281</v>
+        <v>1266</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46078.38541666666</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="B39">
-        <v>1664.336</v>
+        <v>2195.685</v>
       </c>
       <c r="C39">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46078.39583333334</v>
+        <v>46093.39583333334</v>
       </c>
       <c r="B40">
-        <v>1751.98</v>
+        <v>2306.66</v>
       </c>
       <c r="C40">
-        <v>1340</v>
+        <v>1467</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46078.40625</v>
+        <v>46093.40625</v>
       </c>
       <c r="B41">
-        <v>1819.764</v>
+        <v>2432.506</v>
       </c>
       <c r="C41">
-        <v>1372</v>
+        <v>1530</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46078.41666666666</v>
+        <v>46093.41666666666</v>
       </c>
       <c r="B42">
-        <v>1855.982</v>
+        <v>2579.124</v>
       </c>
       <c r="C42">
-        <v>1414</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46078.42708333334</v>
+        <v>46093.42708333334</v>
       </c>
       <c r="B43">
-        <v>1928.207</v>
+        <v>2643.828</v>
       </c>
       <c r="C43">
-        <v>1410</v>
+        <v>1586</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46078.4375</v>
+        <v>46093.4375</v>
       </c>
       <c r="B44">
-        <v>1960.383</v>
+        <v>2717.95</v>
       </c>
       <c r="C44">
-        <v>1418</v>
+        <v>1602</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46078.44791666666</v>
+        <v>46093.44791666666</v>
       </c>
       <c r="B45">
-        <v>1974.061</v>
+        <v>2764.181</v>
       </c>
       <c r="C45">
-        <v>1435</v>
+        <v>1630</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46078.45833333334</v>
+        <v>46093.45833333334</v>
       </c>
       <c r="B46">
-        <v>1980.984</v>
+        <v>2824.336</v>
       </c>
       <c r="C46">
-        <v>1414</v>
+        <v>1692</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46078.46875</v>
+        <v>46093.46875</v>
       </c>
       <c r="B47">
-        <v>1923.497</v>
+        <v>2873.579</v>
       </c>
       <c r="C47">
-        <v>1368</v>
+        <v>1696</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46078.47916666666</v>
+        <v>46093.47916666666</v>
       </c>
       <c r="B48">
-        <v>1888.647</v>
+        <v>2911.049</v>
       </c>
       <c r="C48">
-        <v>1410</v>
+        <v>1737</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46078.48958333334</v>
+        <v>46093.48958333334</v>
       </c>
       <c r="B49">
-        <v>1854.002</v>
+        <v>2932.346</v>
       </c>
       <c r="C49">
-        <v>1357</v>
+        <v>1726</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46078.5</v>
+        <v>46093.5</v>
       </c>
       <c r="B50">
-        <v>1842.946</v>
+        <v>2942.934</v>
       </c>
       <c r="C50">
-        <v>1366</v>
+        <v>1822</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46078.51041666666</v>
+        <v>46093.51041666666</v>
       </c>
       <c r="B51">
-        <v>1807.263</v>
+        <v>2932.829</v>
       </c>
       <c r="C51">
-        <v>1473</v>
+        <v>1899</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46078.52083333334</v>
+        <v>46093.52083333334</v>
       </c>
       <c r="B52">
-        <v>1825.166</v>
+        <v>2918.873</v>
       </c>
       <c r="C52">
-        <v>1348</v>
+        <v>1921</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46078.53125</v>
+        <v>46093.53125</v>
       </c>
       <c r="B53">
-        <v>1804.495</v>
+        <v>2886.386</v>
       </c>
       <c r="C53">
-        <v>1317</v>
+        <v>2043</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46078.54166666666</v>
+        <v>46093.54166666666</v>
       </c>
       <c r="B54">
-        <v>1723.57</v>
+        <v>2845.263</v>
       </c>
       <c r="C54">
-        <v>1200</v>
+        <v>2032</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46078.55208333334</v>
+        <v>46093.55208333334</v>
       </c>
       <c r="B55">
-        <v>1654.833</v>
+        <v>2779.395</v>
       </c>
       <c r="C55">
-        <v>1199</v>
+        <v>2040</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46078.5625</v>
+        <v>46093.5625</v>
       </c>
       <c r="B56">
-        <v>1590.546</v>
+        <v>2710.779</v>
       </c>
       <c r="C56">
-        <v>1146</v>
+        <v>2042</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46078.57291666666</v>
+        <v>46093.57291666666</v>
       </c>
       <c r="B57">
-        <v>1514.078</v>
+        <v>2623.884</v>
       </c>
       <c r="C57">
-        <v>1112</v>
+        <v>1985</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46078.58333333334</v>
+        <v>46093.58333333334</v>
       </c>
       <c r="B58">
-        <v>1363.304</v>
+        <v>2449.677</v>
       </c>
       <c r="C58">
-        <v>1119</v>
+        <v>1959</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46078.59375</v>
+        <v>46093.59375</v>
       </c>
       <c r="B59">
-        <v>1288.569</v>
+        <v>2324.943</v>
       </c>
       <c r="C59">
-        <v>1047</v>
+        <v>1882</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46078.60416666666</v>
+        <v>46093.60416666666</v>
       </c>
       <c r="B60">
-        <v>1168.333</v>
+        <v>2180.72</v>
       </c>
       <c r="C60">
-        <v>928</v>
+        <v>1778</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46078.61458333334</v>
+        <v>46093.61458333334</v>
       </c>
       <c r="B61">
-        <v>1055.061</v>
+        <v>2045.667</v>
       </c>
       <c r="C61">
-        <v>846</v>
+        <v>1626</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46078.625</v>
+        <v>46093.625</v>
       </c>
       <c r="B62">
-        <v>838.198</v>
+        <v>1661.936</v>
       </c>
       <c r="C62">
-        <v>735</v>
+        <v>1449</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46078.63541666666</v>
+        <v>46093.63541666666</v>
       </c>
       <c r="B63">
-        <v>699.478</v>
+        <v>1476.263</v>
       </c>
       <c r="C63">
-        <v>589</v>
+        <v>1249</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46078.64583333334</v>
+        <v>46093.64583333334</v>
       </c>
       <c r="B64">
-        <v>557.439</v>
+        <v>1264.489</v>
       </c>
       <c r="C64">
-        <v>471</v>
+        <v>1060</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46078.65625</v>
+        <v>46093.65625</v>
       </c>
       <c r="B65">
-        <v>428.871</v>
+        <v>1040.516</v>
       </c>
       <c r="C65">
-        <v>346</v>
+        <v>884</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46078.66666666666</v>
+        <v>46093.66666666666</v>
       </c>
       <c r="B66">
-        <v>226.759</v>
+        <v>705.148</v>
       </c>
       <c r="C66">
-        <v>239</v>
+        <v>666</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46078.67708333334</v>
+        <v>46093.67708333334</v>
       </c>
       <c r="B67">
-        <v>150.149</v>
+        <v>526.967</v>
       </c>
       <c r="C67">
-        <v>149</v>
+        <v>493</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46078.6875</v>
+        <v>46093.6875</v>
       </c>
       <c r="B68">
-        <v>85.34399999999999</v>
+        <v>335.376</v>
       </c>
       <c r="C68">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46078.69791666666</v>
+        <v>46093.69791666666</v>
       </c>
       <c r="B69">
-        <v>43.757</v>
+        <v>228.573</v>
       </c>
       <c r="C69">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46078.70833333334</v>
+        <v>46093.70833333334</v>
       </c>
       <c r="B70">
-        <v>4.407</v>
+        <v>78.44199999999999</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46078.71875</v>
+        <v>46093.71875</v>
       </c>
       <c r="B71">
-        <v>4.281</v>
+        <v>55.923</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46078.72916666666</v>
+        <v>46093.72916666666</v>
       </c>
       <c r="B72">
-        <v>4.42</v>
+        <v>47.257</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46078.73958333334</v>
+        <v>46093.73958333334</v>
       </c>
       <c r="B73">
-        <v>4.572</v>
+        <v>33.273</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46078.75</v>
+        <v>46093.75</v>
       </c>
       <c r="B74">
-        <v>4.472</v>
+        <v>6.605</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46078.76041666666</v>
+        <v>46093.76041666666</v>
       </c>
       <c r="B75">
-        <v>4.572</v>
+        <v>6.784</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46078.77083333334</v>
+        <v>46093.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>6.829</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46078.78125</v>
+        <v>46093.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>6.765</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46078.79166666666</v>
+        <v>46093.79166666666</v>
       </c>
       <c r="B78">
-        <v>4.571</v>
+        <v>6.179</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46078.80208333334</v>
+        <v>46093.80208333334</v>
       </c>
       <c r="B79">
-        <v>4.231</v>
+        <v>5.839</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46078.8125</v>
+        <v>46093.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>13.839</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46078.82291666666</v>
+        <v>46093.82291666666</v>
       </c>
       <c r="B81">
-        <v>1.831</v>
+        <v>13.339</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46078.83333333334</v>
+        <v>46093.83333333334</v>
       </c>
       <c r="B82">
-        <v>0.631</v>
+        <v>12.931</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46078.84375</v>
+        <v>46093.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46078.85416666666</v>
+        <v>46093.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>11.331</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46078.86458333334</v>
+        <v>46093.86458333334</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>9.731</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46078.875</v>
+        <v>46093.875</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>8.83</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46078.88541666666</v>
+        <v>46093.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46078.89583333334</v>
+        <v>46093.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46078.90625</v>
+        <v>46093.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46078.91666666666</v>
+        <v>46093.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46078.92708333334</v>
+        <v>46093.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46078.9375</v>
+        <v>46093.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46078.94791666666</v>
+        <v>46093.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46078.95833333334</v>
+        <v>46093.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46078.96875</v>
+        <v>46093.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46078.97916666666</v>
+        <v>46093.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46078.98958333334</v>
+        <v>46093.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>1.302</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B118">
-        <v>0.821</v>
+        <v>9.94</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B119">
-        <v>0.881</v>
+        <v>11.083</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B120">
-        <v>0.998</v>
+        <v>14.794</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B121">
-        <v>1.484</v>
+        <v>33.784</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B122">
-        <v>30.437</v>
+        <v>171.18</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B123">
-        <v>61.975</v>
+        <v>279.165</v>
       </c>
       <c r="C123">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B124">
-        <v>111.379</v>
+        <v>425.858</v>
       </c>
       <c r="C124">
-        <v>73</v>
+        <v>395</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B125">
-        <v>178.261</v>
+        <v>603.082</v>
       </c>
       <c r="C125">
-        <v>159</v>
+        <v>561</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B126">
-        <v>408.492</v>
+        <v>916.121</v>
       </c>
       <c r="C126">
-        <v>273</v>
+        <v>748</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B127">
-        <v>546.2910000000001</v>
+        <v>1126.853</v>
       </c>
       <c r="C127">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B128">
-        <v>705.248</v>
+        <v>1388.136</v>
       </c>
       <c r="C128">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B129">
-        <v>848.6799999999999</v>
+        <v>1632.988</v>
       </c>
       <c r="C129">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B130">
-        <v>1114.356</v>
+        <v>1949.938</v>
       </c>
       <c r="C130">
-        <v>777</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B131">
-        <v>1233.234</v>
+        <v>2145.372</v>
       </c>
       <c r="C131">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B132">
-        <v>1386.799</v>
+        <v>2359.779</v>
       </c>
       <c r="C132">
-        <v>1069</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B133">
-        <v>1525.191</v>
+        <v>2499.129</v>
       </c>
       <c r="C133">
-        <v>1209</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B134">
-        <v>1753.672</v>
+        <v>2656.294</v>
       </c>
       <c r="C134">
-        <v>1346</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B135">
-        <v>1867.273</v>
+        <v>2714.295</v>
       </c>
       <c r="C135">
-        <v>1421</v>
+        <v>0</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B136">
-        <v>1963.695</v>
+        <v>2831.322</v>
       </c>
       <c r="C136">
-        <v>1529</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B137">
-        <v>2053.522</v>
+        <v>2910.087</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B138">
-        <v>2154.198</v>
+        <v>3011.242</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B139">
-        <v>2219.077</v>
+        <v>3034.847</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B140">
-        <v>2274.671</v>
+        <v>3069.557</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B141">
-        <v>2325.954</v>
+        <v>3091.4</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B142">
-        <v>2373.342</v>
+        <v>3105.324</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B143">
-        <v>2394.107</v>
+        <v>3115.746</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B144">
-        <v>2398.982</v>
+        <v>3117.202</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B145">
-        <v>2390.419</v>
+        <v>3112.853</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B146">
-        <v>2371.276</v>
+        <v>3091.786</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B147">
-        <v>2351.192</v>
+        <v>3130.661</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B148">
-        <v>2319.383</v>
+        <v>3098.149</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B149">
-        <v>2271.275</v>
+        <v>3060.284</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B150">
-        <v>2211.691</v>
+        <v>2998.506</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B151">
-        <v>2142.674</v>
+        <v>2930.898</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B152">
-        <v>2045.948</v>
+        <v>2860.665</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B153">
-        <v>1960.052</v>
+        <v>2767.031</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B154">
-        <v>1815.654</v>
+        <v>2603.809</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B155">
-        <v>1688.734</v>
+        <v>2475.991</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B156">
-        <v>1551.178</v>
+        <v>2326.605</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B157">
-        <v>1408.017</v>
+        <v>2141.978</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B158">
-        <v>1072.701</v>
+        <v>1801.954</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B159">
-        <v>974.074</v>
+        <v>1596.062</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B160">
-        <v>793.741</v>
+        <v>1342.913</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B161">
-        <v>628.609</v>
+        <v>1148.427</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B162">
-        <v>353.864</v>
+        <v>775.152</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B163">
-        <v>236.208</v>
+        <v>581.431</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B164">
-        <v>136.496</v>
+        <v>404.898</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B165">
-        <v>66.14</v>
+        <v>270.884</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B166">
-        <v>12.678</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B167">
-        <v>10.714</v>
+        <v>47.98</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B168">
-        <v>9.949</v>
+        <v>34.157</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B169">
-        <v>9.840999999999999</v>
+        <v>24.58</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B170">
-        <v>6.972</v>
+        <v>6.404</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B171">
-        <v>5.114</v>
+        <v>6.564</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B172">
-        <v>5.079</v>
+        <v>6.684</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B173">
-        <v>5.093</v>
+        <v>6.752</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B174">
-        <v>5.071</v>
+        <v>6.134</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B175">
-        <v>4.731</v>
+        <v>5.794</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B177">
-        <v>2.331</v>
+        <v>5.294</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B178">
-        <v>0.531</v>
+        <v>4.891</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>3.291</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>1.691</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.03.20261</t>
-  </si>
-  <si>
-    <t>12.03.20262</t>
-  </si>
-  <si>
-    <t>12.03.20263</t>
-  </si>
-  <si>
-    <t>12.03.20264</t>
-  </si>
-  <si>
-    <t>12.03.20265</t>
-  </si>
-  <si>
-    <t>12.03.20266</t>
-  </si>
-  <si>
-    <t>12.03.20267</t>
-  </si>
-  <si>
-    <t>12.03.20268</t>
-  </si>
-  <si>
-    <t>12.03.20269</t>
-  </si>
-  <si>
-    <t>12.03.202610</t>
-  </si>
-  <si>
-    <t>12.03.202611</t>
-  </si>
-  <si>
-    <t>12.03.202612</t>
-  </si>
-  <si>
-    <t>12.03.202613</t>
-  </si>
-  <si>
-    <t>12.03.202614</t>
-  </si>
-  <si>
-    <t>12.03.202615</t>
-  </si>
-  <si>
-    <t>12.03.202616</t>
-  </si>
-  <si>
-    <t>12.03.202617</t>
-  </si>
-  <si>
-    <t>12.03.202618</t>
-  </si>
-  <si>
-    <t>12.03.202619</t>
-  </si>
-  <si>
-    <t>12.03.202620</t>
-  </si>
-  <si>
-    <t>12.03.202621</t>
-  </si>
-  <si>
-    <t>12.03.202622</t>
-  </si>
-  <si>
-    <t>12.03.202623</t>
-  </si>
-  <si>
-    <t>12.03.202624</t>
-  </si>
-  <si>
-    <t>12.03.202625</t>
-  </si>
-  <si>
-    <t>12.03.202626</t>
-  </si>
-  <si>
-    <t>12.03.202627</t>
-  </si>
-  <si>
-    <t>12.03.202628</t>
-  </si>
-  <si>
-    <t>12.03.202629</t>
-  </si>
-  <si>
-    <t>12.03.202630</t>
-  </si>
-  <si>
-    <t>12.03.202631</t>
-  </si>
-  <si>
-    <t>12.03.202632</t>
-  </si>
-  <si>
-    <t>12.03.202633</t>
-  </si>
-  <si>
-    <t>12.03.202634</t>
-  </si>
-  <si>
-    <t>12.03.202635</t>
-  </si>
-  <si>
-    <t>12.03.202636</t>
-  </si>
-  <si>
-    <t>12.03.202637</t>
-  </si>
-  <si>
-    <t>12.03.202638</t>
-  </si>
-  <si>
-    <t>12.03.202639</t>
-  </si>
-  <si>
-    <t>12.03.202640</t>
-  </si>
-  <si>
-    <t>12.03.202641</t>
-  </si>
-  <si>
-    <t>12.03.202642</t>
-  </si>
-  <si>
-    <t>12.03.202643</t>
-  </si>
-  <si>
-    <t>12.03.202644</t>
-  </si>
-  <si>
-    <t>12.03.202645</t>
-  </si>
-  <si>
-    <t>12.03.202646</t>
-  </si>
-  <si>
-    <t>12.03.202647</t>
-  </si>
-  <si>
-    <t>12.03.202648</t>
-  </si>
-  <si>
-    <t>12.03.202649</t>
-  </si>
-  <si>
-    <t>12.03.202650</t>
-  </si>
-  <si>
-    <t>12.03.202651</t>
-  </si>
-  <si>
-    <t>12.03.202652</t>
-  </si>
-  <si>
-    <t>12.03.202653</t>
-  </si>
-  <si>
-    <t>12.03.202654</t>
-  </si>
-  <si>
-    <t>12.03.202655</t>
-  </si>
-  <si>
-    <t>12.03.202656</t>
-  </si>
-  <si>
-    <t>12.03.202657</t>
-  </si>
-  <si>
-    <t>12.03.202658</t>
-  </si>
-  <si>
-    <t>12.03.202659</t>
-  </si>
-  <si>
-    <t>12.03.202660</t>
-  </si>
-  <si>
-    <t>12.03.202661</t>
-  </si>
-  <si>
-    <t>12.03.202662</t>
-  </si>
-  <si>
-    <t>12.03.202663</t>
-  </si>
-  <si>
-    <t>12.03.202664</t>
-  </si>
-  <si>
-    <t>12.03.202665</t>
-  </si>
-  <si>
-    <t>12.03.202666</t>
-  </si>
-  <si>
-    <t>12.03.202667</t>
-  </si>
-  <si>
-    <t>12.03.202668</t>
-  </si>
-  <si>
-    <t>12.03.202669</t>
-  </si>
-  <si>
-    <t>12.03.202670</t>
-  </si>
-  <si>
-    <t>12.03.202671</t>
-  </si>
-  <si>
-    <t>12.03.202672</t>
-  </si>
-  <si>
-    <t>12.03.202673</t>
-  </si>
-  <si>
-    <t>12.03.202674</t>
-  </si>
-  <si>
-    <t>12.03.202675</t>
-  </si>
-  <si>
-    <t>12.03.202676</t>
-  </si>
-  <si>
-    <t>12.03.202677</t>
-  </si>
-  <si>
-    <t>12.03.202678</t>
-  </si>
-  <si>
-    <t>12.03.202679</t>
-  </si>
-  <si>
-    <t>12.03.202680</t>
-  </si>
-  <si>
-    <t>12.03.202681</t>
-  </si>
-  <si>
-    <t>12.03.202682</t>
-  </si>
-  <si>
-    <t>12.03.202683</t>
-  </si>
-  <si>
-    <t>12.03.202684</t>
-  </si>
-  <si>
-    <t>12.03.202685</t>
-  </si>
-  <si>
-    <t>12.03.202686</t>
-  </si>
-  <si>
-    <t>12.03.202687</t>
-  </si>
-  <si>
-    <t>12.03.202688</t>
-  </si>
-  <si>
-    <t>12.03.202689</t>
-  </si>
-  <si>
-    <t>12.03.202690</t>
-  </si>
-  <si>
-    <t>12.03.202691</t>
-  </si>
-  <si>
-    <t>12.03.202692</t>
-  </si>
-  <si>
-    <t>12.03.202693</t>
-  </si>
-  <si>
-    <t>12.03.202694</t>
-  </si>
-  <si>
-    <t>12.03.202695</t>
-  </si>
-  <si>
-    <t>12.03.202696</t>
-  </si>
-  <si>
-    <t>13.03.20261</t>
-  </si>
-  <si>
-    <t>13.03.20262</t>
-  </si>
-  <si>
-    <t>13.03.20263</t>
-  </si>
-  <si>
-    <t>13.03.20264</t>
-  </si>
-  <si>
-    <t>13.03.20265</t>
-  </si>
-  <si>
-    <t>13.03.20266</t>
-  </si>
-  <si>
-    <t>13.03.20267</t>
-  </si>
-  <si>
-    <t>13.03.20268</t>
-  </si>
-  <si>
-    <t>13.03.20269</t>
-  </si>
-  <si>
-    <t>13.03.202610</t>
-  </si>
-  <si>
-    <t>13.03.202611</t>
-  </si>
-  <si>
-    <t>13.03.202612</t>
-  </si>
-  <si>
-    <t>13.03.202613</t>
-  </si>
-  <si>
-    <t>13.03.202614</t>
-  </si>
-  <si>
-    <t>13.03.202615</t>
-  </si>
-  <si>
-    <t>13.03.202616</t>
-  </si>
-  <si>
-    <t>13.03.202617</t>
-  </si>
-  <si>
-    <t>13.03.202618</t>
-  </si>
-  <si>
-    <t>13.03.202619</t>
-  </si>
-  <si>
-    <t>13.03.202620</t>
-  </si>
-  <si>
-    <t>13.03.202621</t>
-  </si>
-  <si>
-    <t>13.03.202622</t>
-  </si>
-  <si>
-    <t>13.03.202623</t>
-  </si>
-  <si>
-    <t>13.03.202624</t>
-  </si>
-  <si>
-    <t>13.03.202625</t>
-  </si>
-  <si>
-    <t>13.03.202626</t>
-  </si>
-  <si>
-    <t>13.03.202627</t>
-  </si>
-  <si>
-    <t>13.03.202628</t>
-  </si>
-  <si>
-    <t>13.03.202629</t>
-  </si>
-  <si>
-    <t>13.03.202630</t>
-  </si>
-  <si>
-    <t>13.03.202631</t>
-  </si>
-  <si>
-    <t>13.03.202632</t>
-  </si>
-  <si>
-    <t>13.03.202633</t>
-  </si>
-  <si>
-    <t>13.03.202634</t>
-  </si>
-  <si>
-    <t>13.03.202635</t>
-  </si>
-  <si>
-    <t>13.03.202636</t>
-  </si>
-  <si>
-    <t>13.03.202637</t>
-  </si>
-  <si>
-    <t>13.03.202638</t>
-  </si>
-  <si>
-    <t>13.03.202639</t>
-  </si>
-  <si>
-    <t>13.03.202640</t>
-  </si>
-  <si>
-    <t>13.03.202641</t>
-  </si>
-  <si>
-    <t>13.03.202642</t>
-  </si>
-  <si>
-    <t>13.03.202643</t>
-  </si>
-  <si>
-    <t>13.03.202644</t>
-  </si>
-  <si>
-    <t>13.03.202645</t>
-  </si>
-  <si>
-    <t>13.03.202646</t>
-  </si>
-  <si>
-    <t>13.03.202647</t>
-  </si>
-  <si>
-    <t>13.03.202648</t>
-  </si>
-  <si>
-    <t>13.03.202649</t>
-  </si>
-  <si>
-    <t>13.03.202650</t>
-  </si>
-  <si>
-    <t>13.03.202651</t>
-  </si>
-  <si>
-    <t>13.03.202652</t>
-  </si>
-  <si>
-    <t>13.03.202653</t>
-  </si>
-  <si>
-    <t>13.03.202654</t>
-  </si>
-  <si>
-    <t>13.03.202655</t>
-  </si>
-  <si>
-    <t>13.03.202656</t>
-  </si>
-  <si>
-    <t>13.03.202657</t>
-  </si>
-  <si>
-    <t>13.03.202658</t>
-  </si>
-  <si>
-    <t>13.03.202659</t>
-  </si>
-  <si>
-    <t>13.03.202660</t>
-  </si>
-  <si>
-    <t>13.03.202661</t>
-  </si>
-  <si>
-    <t>13.03.202662</t>
-  </si>
-  <si>
-    <t>13.03.202663</t>
-  </si>
-  <si>
-    <t>13.03.202664</t>
-  </si>
-  <si>
-    <t>13.03.202665</t>
-  </si>
-  <si>
-    <t>13.03.202666</t>
-  </si>
-  <si>
-    <t>13.03.202667</t>
-  </si>
-  <si>
-    <t>13.03.202668</t>
-  </si>
-  <si>
-    <t>13.03.202669</t>
-  </si>
-  <si>
-    <t>13.03.202670</t>
-  </si>
-  <si>
-    <t>13.03.202671</t>
-  </si>
-  <si>
-    <t>13.03.202672</t>
-  </si>
-  <si>
-    <t>13.03.202673</t>
-  </si>
-  <si>
-    <t>13.03.202674</t>
-  </si>
-  <si>
-    <t>13.03.202675</t>
-  </si>
-  <si>
-    <t>13.03.202676</t>
-  </si>
-  <si>
-    <t>13.03.202677</t>
-  </si>
-  <si>
-    <t>13.03.202678</t>
-  </si>
-  <si>
-    <t>13.03.202679</t>
-  </si>
-  <si>
-    <t>13.03.202680</t>
-  </si>
-  <si>
-    <t>13.03.202681</t>
-  </si>
-  <si>
-    <t>13.03.202682</t>
-  </si>
-  <si>
-    <t>13.03.202683</t>
-  </si>
-  <si>
-    <t>13.03.202684</t>
-  </si>
-  <si>
-    <t>13.03.202685</t>
-  </si>
-  <si>
-    <t>13.03.202686</t>
-  </si>
-  <si>
-    <t>13.03.202687</t>
-  </si>
-  <si>
-    <t>13.03.202688</t>
-  </si>
-  <si>
-    <t>13.03.202689</t>
-  </si>
-  <si>
-    <t>13.03.202690</t>
-  </si>
-  <si>
-    <t>13.03.202691</t>
-  </si>
-  <si>
-    <t>13.03.202692</t>
-  </si>
-  <si>
-    <t>13.03.202693</t>
-  </si>
-  <si>
-    <t>13.03.202694</t>
-  </si>
-  <si>
-    <t>13.03.202695</t>
-  </si>
-  <si>
-    <t>13.03.202696</t>
+    <t>25.03.20261</t>
+  </si>
+  <si>
+    <t>25.03.20262</t>
+  </si>
+  <si>
+    <t>25.03.20263</t>
+  </si>
+  <si>
+    <t>25.03.20264</t>
+  </si>
+  <si>
+    <t>25.03.20265</t>
+  </si>
+  <si>
+    <t>25.03.20266</t>
+  </si>
+  <si>
+    <t>25.03.20267</t>
+  </si>
+  <si>
+    <t>25.03.20268</t>
+  </si>
+  <si>
+    <t>25.03.20269</t>
+  </si>
+  <si>
+    <t>25.03.202610</t>
+  </si>
+  <si>
+    <t>25.03.202611</t>
+  </si>
+  <si>
+    <t>25.03.202612</t>
+  </si>
+  <si>
+    <t>25.03.202613</t>
+  </si>
+  <si>
+    <t>25.03.202614</t>
+  </si>
+  <si>
+    <t>25.03.202615</t>
+  </si>
+  <si>
+    <t>25.03.202616</t>
+  </si>
+  <si>
+    <t>25.03.202617</t>
+  </si>
+  <si>
+    <t>25.03.202618</t>
+  </si>
+  <si>
+    <t>25.03.202619</t>
+  </si>
+  <si>
+    <t>25.03.202620</t>
+  </si>
+  <si>
+    <t>25.03.202621</t>
+  </si>
+  <si>
+    <t>25.03.202622</t>
+  </si>
+  <si>
+    <t>25.03.202623</t>
+  </si>
+  <si>
+    <t>25.03.202624</t>
+  </si>
+  <si>
+    <t>25.03.202625</t>
+  </si>
+  <si>
+    <t>25.03.202626</t>
+  </si>
+  <si>
+    <t>25.03.202627</t>
+  </si>
+  <si>
+    <t>25.03.202628</t>
+  </si>
+  <si>
+    <t>25.03.202629</t>
+  </si>
+  <si>
+    <t>25.03.202630</t>
+  </si>
+  <si>
+    <t>25.03.202631</t>
+  </si>
+  <si>
+    <t>25.03.202632</t>
+  </si>
+  <si>
+    <t>25.03.202633</t>
+  </si>
+  <si>
+    <t>25.03.202634</t>
+  </si>
+  <si>
+    <t>25.03.202635</t>
+  </si>
+  <si>
+    <t>25.03.202636</t>
+  </si>
+  <si>
+    <t>25.03.202637</t>
+  </si>
+  <si>
+    <t>25.03.202638</t>
+  </si>
+  <si>
+    <t>25.03.202639</t>
+  </si>
+  <si>
+    <t>25.03.202640</t>
+  </si>
+  <si>
+    <t>25.03.202641</t>
+  </si>
+  <si>
+    <t>25.03.202642</t>
+  </si>
+  <si>
+    <t>25.03.202643</t>
+  </si>
+  <si>
+    <t>25.03.202644</t>
+  </si>
+  <si>
+    <t>25.03.202645</t>
+  </si>
+  <si>
+    <t>25.03.202646</t>
+  </si>
+  <si>
+    <t>25.03.202647</t>
+  </si>
+  <si>
+    <t>25.03.202648</t>
+  </si>
+  <si>
+    <t>25.03.202649</t>
+  </si>
+  <si>
+    <t>25.03.202650</t>
+  </si>
+  <si>
+    <t>25.03.202651</t>
+  </si>
+  <si>
+    <t>25.03.202652</t>
+  </si>
+  <si>
+    <t>25.03.202653</t>
+  </si>
+  <si>
+    <t>25.03.202654</t>
+  </si>
+  <si>
+    <t>25.03.202655</t>
+  </si>
+  <si>
+    <t>25.03.202656</t>
+  </si>
+  <si>
+    <t>25.03.202657</t>
+  </si>
+  <si>
+    <t>25.03.202658</t>
+  </si>
+  <si>
+    <t>25.03.202659</t>
+  </si>
+  <si>
+    <t>25.03.202660</t>
+  </si>
+  <si>
+    <t>25.03.202661</t>
+  </si>
+  <si>
+    <t>25.03.202662</t>
+  </si>
+  <si>
+    <t>25.03.202663</t>
+  </si>
+  <si>
+    <t>25.03.202664</t>
+  </si>
+  <si>
+    <t>25.03.202665</t>
+  </si>
+  <si>
+    <t>25.03.202666</t>
+  </si>
+  <si>
+    <t>25.03.202667</t>
+  </si>
+  <si>
+    <t>25.03.202668</t>
+  </si>
+  <si>
+    <t>25.03.202669</t>
+  </si>
+  <si>
+    <t>25.03.202670</t>
+  </si>
+  <si>
+    <t>25.03.202671</t>
+  </si>
+  <si>
+    <t>25.03.202672</t>
+  </si>
+  <si>
+    <t>25.03.202673</t>
+  </si>
+  <si>
+    <t>25.03.202674</t>
+  </si>
+  <si>
+    <t>25.03.202675</t>
+  </si>
+  <si>
+    <t>25.03.202676</t>
+  </si>
+  <si>
+    <t>25.03.202677</t>
+  </si>
+  <si>
+    <t>25.03.202678</t>
+  </si>
+  <si>
+    <t>25.03.202679</t>
+  </si>
+  <si>
+    <t>25.03.202680</t>
+  </si>
+  <si>
+    <t>25.03.202681</t>
+  </si>
+  <si>
+    <t>25.03.202682</t>
+  </si>
+  <si>
+    <t>25.03.202683</t>
+  </si>
+  <si>
+    <t>25.03.202684</t>
+  </si>
+  <si>
+    <t>25.03.202685</t>
+  </si>
+  <si>
+    <t>25.03.202686</t>
+  </si>
+  <si>
+    <t>25.03.202687</t>
+  </si>
+  <si>
+    <t>25.03.202688</t>
+  </si>
+  <si>
+    <t>25.03.202689</t>
+  </si>
+  <si>
+    <t>25.03.202690</t>
+  </si>
+  <si>
+    <t>25.03.202691</t>
+  </si>
+  <si>
+    <t>25.03.202692</t>
+  </si>
+  <si>
+    <t>25.03.202693</t>
+  </si>
+  <si>
+    <t>25.03.202694</t>
+  </si>
+  <si>
+    <t>25.03.202695</t>
+  </si>
+  <si>
+    <t>25.03.202696</t>
+  </si>
+  <si>
+    <t>26.03.20261</t>
+  </si>
+  <si>
+    <t>26.03.20262</t>
+  </si>
+  <si>
+    <t>26.03.20263</t>
+  </si>
+  <si>
+    <t>26.03.20264</t>
+  </si>
+  <si>
+    <t>26.03.20265</t>
+  </si>
+  <si>
+    <t>26.03.20266</t>
+  </si>
+  <si>
+    <t>26.03.20267</t>
+  </si>
+  <si>
+    <t>26.03.20268</t>
+  </si>
+  <si>
+    <t>26.03.20269</t>
+  </si>
+  <si>
+    <t>26.03.202610</t>
+  </si>
+  <si>
+    <t>26.03.202611</t>
+  </si>
+  <si>
+    <t>26.03.202612</t>
+  </si>
+  <si>
+    <t>26.03.202613</t>
+  </si>
+  <si>
+    <t>26.03.202614</t>
+  </si>
+  <si>
+    <t>26.03.202615</t>
+  </si>
+  <si>
+    <t>26.03.202616</t>
+  </si>
+  <si>
+    <t>26.03.202617</t>
+  </si>
+  <si>
+    <t>26.03.202618</t>
+  </si>
+  <si>
+    <t>26.03.202619</t>
+  </si>
+  <si>
+    <t>26.03.202620</t>
+  </si>
+  <si>
+    <t>26.03.202621</t>
+  </si>
+  <si>
+    <t>26.03.202622</t>
+  </si>
+  <si>
+    <t>26.03.202623</t>
+  </si>
+  <si>
+    <t>26.03.202624</t>
+  </si>
+  <si>
+    <t>26.03.202625</t>
+  </si>
+  <si>
+    <t>26.03.202626</t>
+  </si>
+  <si>
+    <t>26.03.202627</t>
+  </si>
+  <si>
+    <t>26.03.202628</t>
+  </si>
+  <si>
+    <t>26.03.202629</t>
+  </si>
+  <si>
+    <t>26.03.202630</t>
+  </si>
+  <si>
+    <t>26.03.202631</t>
+  </si>
+  <si>
+    <t>26.03.202632</t>
+  </si>
+  <si>
+    <t>26.03.202633</t>
+  </si>
+  <si>
+    <t>26.03.202634</t>
+  </si>
+  <si>
+    <t>26.03.202635</t>
+  </si>
+  <si>
+    <t>26.03.202636</t>
+  </si>
+  <si>
+    <t>26.03.202637</t>
+  </si>
+  <si>
+    <t>26.03.202638</t>
+  </si>
+  <si>
+    <t>26.03.202639</t>
+  </si>
+  <si>
+    <t>26.03.202640</t>
+  </si>
+  <si>
+    <t>26.03.202641</t>
+  </si>
+  <si>
+    <t>26.03.202642</t>
+  </si>
+  <si>
+    <t>26.03.202643</t>
+  </si>
+  <si>
+    <t>26.03.202644</t>
+  </si>
+  <si>
+    <t>26.03.202645</t>
+  </si>
+  <si>
+    <t>26.03.202646</t>
+  </si>
+  <si>
+    <t>26.03.202647</t>
+  </si>
+  <si>
+    <t>26.03.202648</t>
+  </si>
+  <si>
+    <t>26.03.202649</t>
+  </si>
+  <si>
+    <t>26.03.202650</t>
+  </si>
+  <si>
+    <t>26.03.202651</t>
+  </si>
+  <si>
+    <t>26.03.202652</t>
+  </si>
+  <si>
+    <t>26.03.202653</t>
+  </si>
+  <si>
+    <t>26.03.202654</t>
+  </si>
+  <si>
+    <t>26.03.202655</t>
+  </si>
+  <si>
+    <t>26.03.202656</t>
+  </si>
+  <si>
+    <t>26.03.202657</t>
+  </si>
+  <si>
+    <t>26.03.202658</t>
+  </si>
+  <si>
+    <t>26.03.202659</t>
+  </si>
+  <si>
+    <t>26.03.202660</t>
+  </si>
+  <si>
+    <t>26.03.202661</t>
+  </si>
+  <si>
+    <t>26.03.202662</t>
+  </si>
+  <si>
+    <t>26.03.202663</t>
+  </si>
+  <si>
+    <t>26.03.202664</t>
+  </si>
+  <si>
+    <t>26.03.202665</t>
+  </si>
+  <si>
+    <t>26.03.202666</t>
+  </si>
+  <si>
+    <t>26.03.202667</t>
+  </si>
+  <si>
+    <t>26.03.202668</t>
+  </si>
+  <si>
+    <t>26.03.202669</t>
+  </si>
+  <si>
+    <t>26.03.202670</t>
+  </si>
+  <si>
+    <t>26.03.202671</t>
+  </si>
+  <si>
+    <t>26.03.202672</t>
+  </si>
+  <si>
+    <t>26.03.202673</t>
+  </si>
+  <si>
+    <t>26.03.202674</t>
+  </si>
+  <si>
+    <t>26.03.202675</t>
+  </si>
+  <si>
+    <t>26.03.202676</t>
+  </si>
+  <si>
+    <t>26.03.202677</t>
+  </si>
+  <si>
+    <t>26.03.202678</t>
+  </si>
+  <si>
+    <t>26.03.202679</t>
+  </si>
+  <si>
+    <t>26.03.202680</t>
+  </si>
+  <si>
+    <t>26.03.202681</t>
+  </si>
+  <si>
+    <t>26.03.202682</t>
+  </si>
+  <si>
+    <t>26.03.202683</t>
+  </si>
+  <si>
+    <t>26.03.202684</t>
+  </si>
+  <si>
+    <t>26.03.202685</t>
+  </si>
+  <si>
+    <t>26.03.202686</t>
+  </si>
+  <si>
+    <t>26.03.202687</t>
+  </si>
+  <si>
+    <t>26.03.202688</t>
+  </si>
+  <si>
+    <t>26.03.202689</t>
+  </si>
+  <si>
+    <t>26.03.202690</t>
+  </si>
+  <si>
+    <t>26.03.202691</t>
+  </si>
+  <si>
+    <t>26.03.202692</t>
+  </si>
+  <si>
+    <t>26.03.202693</t>
+  </si>
+  <si>
+    <t>26.03.202694</t>
+  </si>
+  <si>
+    <t>26.03.202695</t>
+  </si>
+  <si>
+    <t>26.03.202696</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46093.01041666666</v>
+        <v>46106.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46093.02083333334</v>
+        <v>46106.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46093.03125</v>
+        <v>46106.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46093.04166666666</v>
+        <v>46106.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46093.05208333334</v>
+        <v>46106.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46093.0625</v>
+        <v>46106.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46093.07291666666</v>
+        <v>46106.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46093.08333333334</v>
+        <v>46106.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46093.09375</v>
+        <v>46106.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46093.10416666666</v>
+        <v>46106.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46093.11458333334</v>
+        <v>46106.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46093.125</v>
+        <v>46106.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46093.13541666666</v>
+        <v>46106.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46093.14583333334</v>
+        <v>46106.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46093.15625</v>
+        <v>46106.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46093.16666666666</v>
+        <v>46106.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.237</v>
+        <v>0.742</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46093.17708333334</v>
+        <v>46106.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46093.1875</v>
+        <v>46106.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46093.19791666666</v>
+        <v>46106.19791666666</v>
       </c>
       <c r="B21">
-        <v>3.237</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46093.20833333334</v>
+        <v>46106.20833333334</v>
       </c>
       <c r="B22">
-        <v>5.742</v>
+        <v>9.026</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46093.21875</v>
+        <v>46106.21875</v>
       </c>
       <c r="B23">
-        <v>6.439</v>
+        <v>18.367</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46093.22916666666</v>
+        <v>46106.22916666666</v>
       </c>
       <c r="B24">
-        <v>8.803000000000001</v>
+        <v>38.336</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46093.23958333334</v>
+        <v>46106.23958333334</v>
       </c>
       <c r="B25">
-        <v>18.585</v>
+        <v>73.88800000000001</v>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46093.25</v>
+        <v>46106.25</v>
       </c>
       <c r="B26">
-        <v>100.923</v>
+        <v>218.546</v>
       </c>
       <c r="C26">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46093.26041666666</v>
+        <v>46106.26041666666</v>
       </c>
       <c r="B27">
-        <v>169.292</v>
+        <v>319.038</v>
       </c>
       <c r="C27">
-        <v>119</v>
+        <v>228</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46093.27083333334</v>
+        <v>46106.27083333334</v>
       </c>
       <c r="B28">
-        <v>260.796</v>
+        <v>455.994</v>
       </c>
       <c r="C28">
-        <v>223</v>
+        <v>324</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46093.28125</v>
+        <v>46106.28125</v>
       </c>
       <c r="B29">
-        <v>376.636</v>
+        <v>611.636</v>
       </c>
       <c r="C29">
-        <v>321</v>
+        <v>430</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46093.29166666666</v>
+        <v>46106.29166666666</v>
       </c>
       <c r="B30">
-        <v>647.819</v>
+        <v>877.7809999999999</v>
       </c>
       <c r="C30">
-        <v>452</v>
+        <v>596</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46093.30208333334</v>
+        <v>46106.30208333334</v>
       </c>
       <c r="B31">
-        <v>780.478</v>
+        <v>1034.09</v>
       </c>
       <c r="C31">
-        <v>569</v>
+        <v>727</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46093.3125</v>
+        <v>46106.3125</v>
       </c>
       <c r="B32">
-        <v>974.6609999999999</v>
+        <v>1201.771</v>
       </c>
       <c r="C32">
-        <v>679</v>
+        <v>923</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46093.32291666666</v>
+        <v>46106.32291666666</v>
       </c>
       <c r="B33">
-        <v>1141.383</v>
+        <v>1389.241</v>
       </c>
       <c r="C33">
-        <v>800</v>
+        <v>1083</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46093.33333333334</v>
+        <v>46106.33333333334</v>
       </c>
       <c r="B34">
-        <v>1420.476</v>
+        <v>1683.214</v>
       </c>
       <c r="C34">
-        <v>910</v>
+        <v>1247</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46093.34375</v>
+        <v>46106.34375</v>
       </c>
       <c r="B35">
-        <v>1564.533</v>
+        <v>1870.419</v>
       </c>
       <c r="C35">
-        <v>1002</v>
+        <v>1342</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46093.35416666666</v>
+        <v>46106.35416666666</v>
       </c>
       <c r="B36">
-        <v>1717.566</v>
+        <v>2030.304</v>
       </c>
       <c r="C36">
-        <v>1102</v>
+        <v>1453</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46093.36458333334</v>
+        <v>46106.36458333334</v>
       </c>
       <c r="B37">
-        <v>1863.588</v>
+        <v>2190.345</v>
       </c>
       <c r="C37">
-        <v>1196</v>
+        <v>1555</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46093.375</v>
+        <v>46106.375</v>
       </c>
       <c r="B38">
-        <v>2077.24</v>
+        <v>2362.587</v>
       </c>
       <c r="C38">
-        <v>1266</v>
+        <v>1658</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46093.38541666666</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="B39">
-        <v>2195.685</v>
+        <v>2491.896</v>
       </c>
       <c r="C39">
-        <v>1346</v>
+        <v>1772</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46093.39583333334</v>
+        <v>46106.39583333334</v>
       </c>
       <c r="B40">
-        <v>2306.66</v>
+        <v>2596.302</v>
       </c>
       <c r="C40">
-        <v>1467</v>
+        <v>1837</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46093.40625</v>
+        <v>46106.40625</v>
       </c>
       <c r="B41">
-        <v>2432.506</v>
+        <v>2683.092</v>
       </c>
       <c r="C41">
-        <v>1530</v>
+        <v>1870</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46093.41666666666</v>
+        <v>46106.41666666666</v>
       </c>
       <c r="B42">
-        <v>2579.124</v>
+        <v>2725.867</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1866</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46093.42708333334</v>
+        <v>46106.42708333334</v>
       </c>
       <c r="B43">
-        <v>2643.828</v>
+        <v>2789.488</v>
       </c>
       <c r="C43">
-        <v>1586</v>
+        <v>1898</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46093.4375</v>
+        <v>46106.4375</v>
       </c>
       <c r="B44">
-        <v>2717.95</v>
+        <v>2805.932</v>
       </c>
       <c r="C44">
-        <v>1602</v>
+        <v>1958</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46093.44791666666</v>
+        <v>46106.44791666666</v>
       </c>
       <c r="B45">
-        <v>2764.181</v>
+        <v>2790.311</v>
       </c>
       <c r="C45">
-        <v>1630</v>
+        <v>1982</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46093.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="B46">
-        <v>2824.336</v>
+        <v>2649.291</v>
       </c>
       <c r="C46">
-        <v>1692</v>
+        <v>1896</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46093.46875</v>
+        <v>46106.46875</v>
       </c>
       <c r="B47">
-        <v>2873.579</v>
+        <v>2700.025</v>
       </c>
       <c r="C47">
-        <v>1696</v>
+        <v>1898</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46093.47916666666</v>
+        <v>46106.47916666666</v>
       </c>
       <c r="B48">
-        <v>2911.049</v>
+        <v>2635.038</v>
       </c>
       <c r="C48">
-        <v>1737</v>
+        <v>1799</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46093.48958333334</v>
+        <v>46106.48958333334</v>
       </c>
       <c r="B49">
-        <v>2932.346</v>
+        <v>2562.7</v>
       </c>
       <c r="C49">
-        <v>1726</v>
+        <v>1825</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46093.5</v>
+        <v>46106.5</v>
       </c>
       <c r="B50">
-        <v>2942.934</v>
+        <v>2448.756</v>
       </c>
       <c r="C50">
-        <v>1822</v>
+        <v>1830</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46093.51041666666</v>
+        <v>46106.51041666666</v>
       </c>
       <c r="B51">
-        <v>2932.829</v>
+        <v>2375.178</v>
       </c>
       <c r="C51">
-        <v>1899</v>
+        <v>1818</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46093.52083333334</v>
+        <v>46106.52083333334</v>
       </c>
       <c r="B52">
-        <v>2918.873</v>
+        <v>2305.895</v>
       </c>
       <c r="C52">
-        <v>1921</v>
+        <v>1814</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46093.53125</v>
+        <v>46106.53125</v>
       </c>
       <c r="B53">
-        <v>2886.386</v>
+        <v>2219.01</v>
       </c>
       <c r="C53">
-        <v>2043</v>
+        <v>1796</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46093.54166666666</v>
+        <v>46106.54166666666</v>
       </c>
       <c r="B54">
-        <v>2845.263</v>
+        <v>2080.858</v>
       </c>
       <c r="C54">
-        <v>2032</v>
+        <v>1717</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46093.55208333334</v>
+        <v>46106.55208333334</v>
       </c>
       <c r="B55">
-        <v>2779.395</v>
+        <v>1994.21</v>
       </c>
       <c r="C55">
-        <v>2040</v>
+        <v>1579</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46093.5625</v>
+        <v>46106.5625</v>
       </c>
       <c r="B56">
-        <v>2710.779</v>
+        <v>1906.367</v>
       </c>
       <c r="C56">
-        <v>2042</v>
+        <v>1508</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46093.57291666666</v>
+        <v>46106.57291666666</v>
       </c>
       <c r="B57">
-        <v>2623.884</v>
+        <v>1837.724</v>
       </c>
       <c r="C57">
-        <v>1985</v>
+        <v>1443</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46093.58333333334</v>
+        <v>46106.58333333334</v>
       </c>
       <c r="B58">
-        <v>2449.677</v>
+        <v>1639.941</v>
       </c>
       <c r="C58">
-        <v>1959</v>
+        <v>1402</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46093.59375</v>
+        <v>46106.59375</v>
       </c>
       <c r="B59">
-        <v>2324.943</v>
+        <v>1559.565</v>
       </c>
       <c r="C59">
-        <v>1882</v>
+        <v>1273</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46093.60416666666</v>
+        <v>46106.60416666666</v>
       </c>
       <c r="B60">
-        <v>2180.72</v>
+        <v>1446.62</v>
       </c>
       <c r="C60">
-        <v>1778</v>
+        <v>1166</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46093.61458333334</v>
+        <v>46106.61458333334</v>
       </c>
       <c r="B61">
-        <v>2045.667</v>
+        <v>1338.344</v>
       </c>
       <c r="C61">
-        <v>1626</v>
+        <v>1137</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46093.625</v>
+        <v>46106.625</v>
       </c>
       <c r="B62">
-        <v>1661.936</v>
+        <v>1147.508</v>
       </c>
       <c r="C62">
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46093.63541666666</v>
+        <v>46106.63541666666</v>
       </c>
       <c r="B63">
-        <v>1476.263</v>
+        <v>1011.478</v>
       </c>
       <c r="C63">
-        <v>1249</v>
+        <v>951</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46093.64583333334</v>
+        <v>46106.64583333334</v>
       </c>
       <c r="B64">
-        <v>1264.489</v>
+        <v>859.783</v>
       </c>
       <c r="C64">
-        <v>1060</v>
+        <v>814</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46093.65625</v>
+        <v>46106.65625</v>
       </c>
       <c r="B65">
-        <v>1040.516</v>
+        <v>734.6369999999999</v>
       </c>
       <c r="C65">
-        <v>884</v>
+        <v>687</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46093.66666666666</v>
+        <v>46106.66666666666</v>
       </c>
       <c r="B66">
-        <v>705.148</v>
+        <v>582.104</v>
       </c>
       <c r="C66">
-        <v>666</v>
+        <v>527</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46093.67708333334</v>
+        <v>46106.67708333334</v>
       </c>
       <c r="B67">
-        <v>526.967</v>
+        <v>433.079</v>
       </c>
       <c r="C67">
-        <v>493</v>
+        <v>375</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46093.6875</v>
+        <v>46106.6875</v>
       </c>
       <c r="B68">
-        <v>335.376</v>
+        <v>304.722</v>
       </c>
       <c r="C68">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46093.69791666666</v>
+        <v>46106.69791666666</v>
       </c>
       <c r="B69">
-        <v>228.573</v>
+        <v>219.139</v>
       </c>
       <c r="C69">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46093.70833333334</v>
+        <v>46106.70833333334</v>
       </c>
       <c r="B70">
-        <v>78.44199999999999</v>
+        <v>107.239</v>
       </c>
       <c r="C70">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46093.71875</v>
+        <v>46106.71875</v>
       </c>
       <c r="B71">
-        <v>55.923</v>
+        <v>68.38800000000001</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,10 +2178,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46093.72916666666</v>
+        <v>46106.72916666666</v>
       </c>
       <c r="B72">
-        <v>47.257</v>
+        <v>41.502</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46093.73958333334</v>
+        <v>46106.73958333334</v>
       </c>
       <c r="B73">
-        <v>33.273</v>
+        <v>33.546</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46093.75</v>
+        <v>46106.75</v>
       </c>
       <c r="B74">
-        <v>6.605</v>
+        <v>8.352</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46093.76041666666</v>
+        <v>46106.76041666666</v>
       </c>
       <c r="B75">
-        <v>6.784</v>
+        <v>9.406000000000001</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46093.77083333334</v>
+        <v>46106.77083333334</v>
       </c>
       <c r="B76">
-        <v>6.829</v>
+        <v>10.907</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46093.78125</v>
+        <v>46106.78125</v>
       </c>
       <c r="B77">
-        <v>6.765</v>
+        <v>10.161</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46093.79166666666</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B78">
-        <v>6.179</v>
+        <v>7.473</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46093.80208333334</v>
+        <v>46106.80208333334</v>
       </c>
       <c r="B79">
-        <v>5.839</v>
+        <v>0</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46093.8125</v>
+        <v>46106.8125</v>
       </c>
       <c r="B80">
-        <v>13.839</v>
+        <v>5.473</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46093.82291666666</v>
+        <v>46106.82291666666</v>
       </c>
       <c r="B81">
-        <v>13.339</v>
+        <v>6.333</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46093.83333333334</v>
+        <v>46106.83333333334</v>
       </c>
       <c r="B82">
-        <v>12.931</v>
+        <v>5.13</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46093.84375</v>
+        <v>46106.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46093.85416666666</v>
+        <v>46106.85416666666</v>
       </c>
       <c r="B84">
-        <v>11.331</v>
+        <v>0</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46093.86458333334</v>
+        <v>46106.86458333334</v>
       </c>
       <c r="B85">
-        <v>9.731</v>
+        <v>1.23</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46093.875</v>
+        <v>46106.875</v>
       </c>
       <c r="B86">
-        <v>8.83</v>
+        <v>4.73</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46093.88541666666</v>
+        <v>46106.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46093.89583333334</v>
+        <v>46106.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46093.90625</v>
+        <v>46106.90625</v>
       </c>
       <c r="B89">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46093.91666666666</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B90">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46093.92708333334</v>
+        <v>46106.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46093.9375</v>
+        <v>46106.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46093.94791666666</v>
+        <v>46106.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46093.95833333334</v>
+        <v>46106.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46093.96875</v>
+        <v>46106.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46093.97916666666</v>
+        <v>46106.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46093.98958333334</v>
+        <v>46106.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B98">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.302</v>
+        <v>1.235</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>1.241</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>1.259</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>1.281</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B118">
-        <v>9.94</v>
+        <v>12.917</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B119">
-        <v>11.083</v>
+        <v>26.045</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B120">
-        <v>14.794</v>
+        <v>50.104</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B121">
-        <v>33.784</v>
+        <v>90.68899999999999</v>
       </c>
       <c r="C121">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B122">
-        <v>171.18</v>
+        <v>234.643</v>
       </c>
       <c r="C122">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B123">
-        <v>279.165</v>
+        <v>333.959</v>
       </c>
       <c r="C123">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B124">
-        <v>425.858</v>
+        <v>475.517</v>
       </c>
       <c r="C124">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B125">
-        <v>603.082</v>
+        <v>642.0650000000001</v>
       </c>
       <c r="C125">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B126">
-        <v>916.121</v>
+        <v>914.766</v>
       </c>
       <c r="C126">
-        <v>748</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B127">
-        <v>1126.853</v>
+        <v>1083.649</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B128">
-        <v>1388.136</v>
+        <v>1255.247</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B129">
-        <v>1632.988</v>
+        <v>1446.998</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B130">
-        <v>1949.938</v>
+        <v>1708.339</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B131">
-        <v>2145.372</v>
+        <v>1894.187</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3198,10 +3198,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B132">
-        <v>2359.779</v>
+        <v>2052.623</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B133">
-        <v>2499.129</v>
+        <v>2087.385</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B134">
-        <v>2656.294</v>
+        <v>2352.307</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B135">
-        <v>2714.295</v>
+        <v>2472.299</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B136">
-        <v>2831.322</v>
+        <v>2458.286</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B137">
-        <v>2910.087</v>
+        <v>2532.9</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B138">
-        <v>3011.242</v>
+        <v>2619.849</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B139">
-        <v>3034.847</v>
+        <v>2672.445</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B140">
-        <v>3069.557</v>
+        <v>2712.791</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B141">
-        <v>3091.4</v>
+        <v>2730.309</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B142">
-        <v>3105.324</v>
+        <v>2708.633</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B143">
-        <v>3115.746</v>
+        <v>2699.127</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B144">
-        <v>3117.202</v>
+        <v>2675.546</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B145">
-        <v>3112.853</v>
+        <v>2642.549</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B146">
-        <v>3091.786</v>
+        <v>2703.842</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B147">
-        <v>3130.661</v>
+        <v>2674.448</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B148">
-        <v>3098.149</v>
+        <v>2611.995</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B149">
-        <v>3060.284</v>
+        <v>2528.494</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B150">
-        <v>2998.506</v>
+        <v>2364.614</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B151">
-        <v>2930.898</v>
+        <v>2237.629</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B152">
-        <v>2860.665</v>
+        <v>2182.316</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B153">
-        <v>2767.031</v>
+        <v>2072.936</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B154">
-        <v>2603.809</v>
+        <v>1771.793</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B155">
-        <v>2475.991</v>
+        <v>1651.749</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B156">
-        <v>2326.605</v>
+        <v>1525.526</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B157">
-        <v>2141.978</v>
+        <v>1410.909</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B158">
-        <v>1801.954</v>
+        <v>1262.929</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B159">
-        <v>1596.062</v>
+        <v>1093.231</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B160">
-        <v>1342.913</v>
+        <v>926.672</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B161">
-        <v>1148.427</v>
+        <v>775.96</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B162">
-        <v>775.152</v>
+        <v>589.553</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B163">
-        <v>581.431</v>
+        <v>440.248</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B164">
-        <v>404.898</v>
+        <v>306.027</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B165">
-        <v>270.884</v>
+        <v>214.487</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B166">
-        <v>87.09999999999999</v>
+        <v>99.142</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B167">
-        <v>47.98</v>
+        <v>60.792</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B168">
-        <v>34.157</v>
+        <v>39.538</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B169">
-        <v>24.58</v>
+        <v>26.183</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B170">
-        <v>6.404</v>
+        <v>6.761</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B171">
-        <v>6.564</v>
+        <v>6.653</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B172">
-        <v>6.684</v>
+        <v>6.749</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B173">
-        <v>6.752</v>
+        <v>6.785</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B174">
-        <v>6.134</v>
+        <v>6.072</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B175">
-        <v>5.794</v>
+        <v>0</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B177">
-        <v>5.294</v>
+        <v>5.232</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B178">
-        <v>4.891</v>
+        <v>5.13</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B180">
-        <v>3.291</v>
+        <v>0</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B181">
-        <v>1.691</v>
+        <v>2.43</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B182">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="577">
   <si>
     <t>Timestamp</t>
   </si>
@@ -605,6 +605,1146 @@
   </si>
   <si>
     <t>26.03.202696</t>
+  </si>
+  <si>
+    <t>27.03.20261</t>
+  </si>
+  <si>
+    <t>27.03.20262</t>
+  </si>
+  <si>
+    <t>27.03.20263</t>
+  </si>
+  <si>
+    <t>27.03.20264</t>
+  </si>
+  <si>
+    <t>27.03.20265</t>
+  </si>
+  <si>
+    <t>27.03.20266</t>
+  </si>
+  <si>
+    <t>27.03.20267</t>
+  </si>
+  <si>
+    <t>27.03.20268</t>
+  </si>
+  <si>
+    <t>27.03.20269</t>
+  </si>
+  <si>
+    <t>27.03.202610</t>
+  </si>
+  <si>
+    <t>27.03.202611</t>
+  </si>
+  <si>
+    <t>27.03.202612</t>
+  </si>
+  <si>
+    <t>27.03.202613</t>
+  </si>
+  <si>
+    <t>27.03.202614</t>
+  </si>
+  <si>
+    <t>27.03.202615</t>
+  </si>
+  <si>
+    <t>27.03.202616</t>
+  </si>
+  <si>
+    <t>27.03.202617</t>
+  </si>
+  <si>
+    <t>27.03.202618</t>
+  </si>
+  <si>
+    <t>27.03.202619</t>
+  </si>
+  <si>
+    <t>27.03.202620</t>
+  </si>
+  <si>
+    <t>27.03.202621</t>
+  </si>
+  <si>
+    <t>27.03.202622</t>
+  </si>
+  <si>
+    <t>27.03.202623</t>
+  </si>
+  <si>
+    <t>27.03.202624</t>
+  </si>
+  <si>
+    <t>27.03.202625</t>
+  </si>
+  <si>
+    <t>27.03.202626</t>
+  </si>
+  <si>
+    <t>27.03.202627</t>
+  </si>
+  <si>
+    <t>27.03.202628</t>
+  </si>
+  <si>
+    <t>27.03.202629</t>
+  </si>
+  <si>
+    <t>27.03.202630</t>
+  </si>
+  <si>
+    <t>27.03.202631</t>
+  </si>
+  <si>
+    <t>27.03.202632</t>
+  </si>
+  <si>
+    <t>27.03.202633</t>
+  </si>
+  <si>
+    <t>27.03.202634</t>
+  </si>
+  <si>
+    <t>27.03.202635</t>
+  </si>
+  <si>
+    <t>27.03.202636</t>
+  </si>
+  <si>
+    <t>27.03.202637</t>
+  </si>
+  <si>
+    <t>27.03.202638</t>
+  </si>
+  <si>
+    <t>27.03.202639</t>
+  </si>
+  <si>
+    <t>27.03.202640</t>
+  </si>
+  <si>
+    <t>27.03.202641</t>
+  </si>
+  <si>
+    <t>27.03.202642</t>
+  </si>
+  <si>
+    <t>27.03.202643</t>
+  </si>
+  <si>
+    <t>27.03.202644</t>
+  </si>
+  <si>
+    <t>27.03.202645</t>
+  </si>
+  <si>
+    <t>27.03.202646</t>
+  </si>
+  <si>
+    <t>27.03.202647</t>
+  </si>
+  <si>
+    <t>27.03.202648</t>
+  </si>
+  <si>
+    <t>27.03.202649</t>
+  </si>
+  <si>
+    <t>27.03.202650</t>
+  </si>
+  <si>
+    <t>27.03.202651</t>
+  </si>
+  <si>
+    <t>27.03.202652</t>
+  </si>
+  <si>
+    <t>27.03.202653</t>
+  </si>
+  <si>
+    <t>27.03.202654</t>
+  </si>
+  <si>
+    <t>27.03.202655</t>
+  </si>
+  <si>
+    <t>27.03.202656</t>
+  </si>
+  <si>
+    <t>27.03.202657</t>
+  </si>
+  <si>
+    <t>27.03.202658</t>
+  </si>
+  <si>
+    <t>27.03.202659</t>
+  </si>
+  <si>
+    <t>27.03.202660</t>
+  </si>
+  <si>
+    <t>27.03.202661</t>
+  </si>
+  <si>
+    <t>27.03.202662</t>
+  </si>
+  <si>
+    <t>27.03.202663</t>
+  </si>
+  <si>
+    <t>27.03.202664</t>
+  </si>
+  <si>
+    <t>27.03.202665</t>
+  </si>
+  <si>
+    <t>27.03.202666</t>
+  </si>
+  <si>
+    <t>27.03.202667</t>
+  </si>
+  <si>
+    <t>27.03.202668</t>
+  </si>
+  <si>
+    <t>27.03.202669</t>
+  </si>
+  <si>
+    <t>27.03.202670</t>
+  </si>
+  <si>
+    <t>27.03.202671</t>
+  </si>
+  <si>
+    <t>27.03.202672</t>
+  </si>
+  <si>
+    <t>27.03.202673</t>
+  </si>
+  <si>
+    <t>27.03.202674</t>
+  </si>
+  <si>
+    <t>27.03.202675</t>
+  </si>
+  <si>
+    <t>27.03.202676</t>
+  </si>
+  <si>
+    <t>27.03.202677</t>
+  </si>
+  <si>
+    <t>27.03.202678</t>
+  </si>
+  <si>
+    <t>27.03.202679</t>
+  </si>
+  <si>
+    <t>27.03.202680</t>
+  </si>
+  <si>
+    <t>27.03.202681</t>
+  </si>
+  <si>
+    <t>27.03.202682</t>
+  </si>
+  <si>
+    <t>27.03.202683</t>
+  </si>
+  <si>
+    <t>27.03.202684</t>
+  </si>
+  <si>
+    <t>27.03.202685</t>
+  </si>
+  <si>
+    <t>27.03.202686</t>
+  </si>
+  <si>
+    <t>27.03.202687</t>
+  </si>
+  <si>
+    <t>27.03.202688</t>
+  </si>
+  <si>
+    <t>27.03.202689</t>
+  </si>
+  <si>
+    <t>27.03.202690</t>
+  </si>
+  <si>
+    <t>27.03.202691</t>
+  </si>
+  <si>
+    <t>27.03.202692</t>
+  </si>
+  <si>
+    <t>27.03.202693</t>
+  </si>
+  <si>
+    <t>27.03.202694</t>
+  </si>
+  <si>
+    <t>27.03.202695</t>
+  </si>
+  <si>
+    <t>27.03.202696</t>
+  </si>
+  <si>
+    <t>28.03.20261</t>
+  </si>
+  <si>
+    <t>28.03.20262</t>
+  </si>
+  <si>
+    <t>28.03.20263</t>
+  </si>
+  <si>
+    <t>28.03.20264</t>
+  </si>
+  <si>
+    <t>28.03.20265</t>
+  </si>
+  <si>
+    <t>28.03.20266</t>
+  </si>
+  <si>
+    <t>28.03.20267</t>
+  </si>
+  <si>
+    <t>28.03.20268</t>
+  </si>
+  <si>
+    <t>28.03.20269</t>
+  </si>
+  <si>
+    <t>28.03.202610</t>
+  </si>
+  <si>
+    <t>28.03.202611</t>
+  </si>
+  <si>
+    <t>28.03.202612</t>
+  </si>
+  <si>
+    <t>28.03.202613</t>
+  </si>
+  <si>
+    <t>28.03.202614</t>
+  </si>
+  <si>
+    <t>28.03.202615</t>
+  </si>
+  <si>
+    <t>28.03.202616</t>
+  </si>
+  <si>
+    <t>28.03.202617</t>
+  </si>
+  <si>
+    <t>28.03.202618</t>
+  </si>
+  <si>
+    <t>28.03.202619</t>
+  </si>
+  <si>
+    <t>28.03.202620</t>
+  </si>
+  <si>
+    <t>28.03.202621</t>
+  </si>
+  <si>
+    <t>28.03.202622</t>
+  </si>
+  <si>
+    <t>28.03.202623</t>
+  </si>
+  <si>
+    <t>28.03.202624</t>
+  </si>
+  <si>
+    <t>28.03.202625</t>
+  </si>
+  <si>
+    <t>28.03.202626</t>
+  </si>
+  <si>
+    <t>28.03.202627</t>
+  </si>
+  <si>
+    <t>28.03.202628</t>
+  </si>
+  <si>
+    <t>28.03.202629</t>
+  </si>
+  <si>
+    <t>28.03.202630</t>
+  </si>
+  <si>
+    <t>28.03.202631</t>
+  </si>
+  <si>
+    <t>28.03.202632</t>
+  </si>
+  <si>
+    <t>28.03.202633</t>
+  </si>
+  <si>
+    <t>28.03.202634</t>
+  </si>
+  <si>
+    <t>28.03.202635</t>
+  </si>
+  <si>
+    <t>28.03.202636</t>
+  </si>
+  <si>
+    <t>28.03.202637</t>
+  </si>
+  <si>
+    <t>28.03.202638</t>
+  </si>
+  <si>
+    <t>28.03.202639</t>
+  </si>
+  <si>
+    <t>28.03.202640</t>
+  </si>
+  <si>
+    <t>28.03.202641</t>
+  </si>
+  <si>
+    <t>28.03.202642</t>
+  </si>
+  <si>
+    <t>28.03.202643</t>
+  </si>
+  <si>
+    <t>28.03.202644</t>
+  </si>
+  <si>
+    <t>28.03.202645</t>
+  </si>
+  <si>
+    <t>28.03.202646</t>
+  </si>
+  <si>
+    <t>28.03.202647</t>
+  </si>
+  <si>
+    <t>28.03.202648</t>
+  </si>
+  <si>
+    <t>28.03.202649</t>
+  </si>
+  <si>
+    <t>28.03.202650</t>
+  </si>
+  <si>
+    <t>28.03.202651</t>
+  </si>
+  <si>
+    <t>28.03.202652</t>
+  </si>
+  <si>
+    <t>28.03.202653</t>
+  </si>
+  <si>
+    <t>28.03.202654</t>
+  </si>
+  <si>
+    <t>28.03.202655</t>
+  </si>
+  <si>
+    <t>28.03.202656</t>
+  </si>
+  <si>
+    <t>28.03.202657</t>
+  </si>
+  <si>
+    <t>28.03.202658</t>
+  </si>
+  <si>
+    <t>28.03.202659</t>
+  </si>
+  <si>
+    <t>28.03.202660</t>
+  </si>
+  <si>
+    <t>28.03.202661</t>
+  </si>
+  <si>
+    <t>28.03.202662</t>
+  </si>
+  <si>
+    <t>28.03.202663</t>
+  </si>
+  <si>
+    <t>28.03.202664</t>
+  </si>
+  <si>
+    <t>28.03.202665</t>
+  </si>
+  <si>
+    <t>28.03.202666</t>
+  </si>
+  <si>
+    <t>28.03.202667</t>
+  </si>
+  <si>
+    <t>28.03.202668</t>
+  </si>
+  <si>
+    <t>28.03.202669</t>
+  </si>
+  <si>
+    <t>28.03.202670</t>
+  </si>
+  <si>
+    <t>28.03.202671</t>
+  </si>
+  <si>
+    <t>28.03.202672</t>
+  </si>
+  <si>
+    <t>28.03.202673</t>
+  </si>
+  <si>
+    <t>28.03.202674</t>
+  </si>
+  <si>
+    <t>28.03.202675</t>
+  </si>
+  <si>
+    <t>28.03.202676</t>
+  </si>
+  <si>
+    <t>28.03.202677</t>
+  </si>
+  <si>
+    <t>28.03.202678</t>
+  </si>
+  <si>
+    <t>28.03.202679</t>
+  </si>
+  <si>
+    <t>28.03.202680</t>
+  </si>
+  <si>
+    <t>28.03.202681</t>
+  </si>
+  <si>
+    <t>28.03.202682</t>
+  </si>
+  <si>
+    <t>28.03.202683</t>
+  </si>
+  <si>
+    <t>28.03.202684</t>
+  </si>
+  <si>
+    <t>28.03.202685</t>
+  </si>
+  <si>
+    <t>28.03.202686</t>
+  </si>
+  <si>
+    <t>28.03.202687</t>
+  </si>
+  <si>
+    <t>28.03.202688</t>
+  </si>
+  <si>
+    <t>28.03.202689</t>
+  </si>
+  <si>
+    <t>28.03.202690</t>
+  </si>
+  <si>
+    <t>28.03.202691</t>
+  </si>
+  <si>
+    <t>28.03.202692</t>
+  </si>
+  <si>
+    <t>28.03.202693</t>
+  </si>
+  <si>
+    <t>28.03.202694</t>
+  </si>
+  <si>
+    <t>28.03.202695</t>
+  </si>
+  <si>
+    <t>28.03.202696</t>
+  </si>
+  <si>
+    <t>29.03.20261</t>
+  </si>
+  <si>
+    <t>29.03.20262</t>
+  </si>
+  <si>
+    <t>29.03.20263</t>
+  </si>
+  <si>
+    <t>29.03.20264</t>
+  </si>
+  <si>
+    <t>29.03.20265</t>
+  </si>
+  <si>
+    <t>29.03.20266</t>
+  </si>
+  <si>
+    <t>29.03.20267</t>
+  </si>
+  <si>
+    <t>29.03.20268</t>
+  </si>
+  <si>
+    <t>29.03.20269</t>
+  </si>
+  <si>
+    <t>29.03.202610</t>
+  </si>
+  <si>
+    <t>29.03.202611</t>
+  </si>
+  <si>
+    <t>29.03.202612</t>
+  </si>
+  <si>
+    <t>29.03.202613</t>
+  </si>
+  <si>
+    <t>29.03.202614</t>
+  </si>
+  <si>
+    <t>29.03.202615</t>
+  </si>
+  <si>
+    <t>29.03.202616</t>
+  </si>
+  <si>
+    <t>29.03.202617</t>
+  </si>
+  <si>
+    <t>29.03.202618</t>
+  </si>
+  <si>
+    <t>29.03.202619</t>
+  </si>
+  <si>
+    <t>29.03.202620</t>
+  </si>
+  <si>
+    <t>29.03.202621</t>
+  </si>
+  <si>
+    <t>29.03.202622</t>
+  </si>
+  <si>
+    <t>29.03.202623</t>
+  </si>
+  <si>
+    <t>29.03.202624</t>
+  </si>
+  <si>
+    <t>29.03.202625</t>
+  </si>
+  <si>
+    <t>29.03.202626</t>
+  </si>
+  <si>
+    <t>29.03.202627</t>
+  </si>
+  <si>
+    <t>29.03.202628</t>
+  </si>
+  <si>
+    <t>29.03.202629</t>
+  </si>
+  <si>
+    <t>29.03.202630</t>
+  </si>
+  <si>
+    <t>29.03.202631</t>
+  </si>
+  <si>
+    <t>29.03.202632</t>
+  </si>
+  <si>
+    <t>29.03.202633</t>
+  </si>
+  <si>
+    <t>29.03.202634</t>
+  </si>
+  <si>
+    <t>29.03.202635</t>
+  </si>
+  <si>
+    <t>29.03.202636</t>
+  </si>
+  <si>
+    <t>29.03.202637</t>
+  </si>
+  <si>
+    <t>29.03.202638</t>
+  </si>
+  <si>
+    <t>29.03.202639</t>
+  </si>
+  <si>
+    <t>29.03.202640</t>
+  </si>
+  <si>
+    <t>29.03.202641</t>
+  </si>
+  <si>
+    <t>29.03.202642</t>
+  </si>
+  <si>
+    <t>29.03.202643</t>
+  </si>
+  <si>
+    <t>29.03.202644</t>
+  </si>
+  <si>
+    <t>29.03.202645</t>
+  </si>
+  <si>
+    <t>29.03.202646</t>
+  </si>
+  <si>
+    <t>29.03.202647</t>
+  </si>
+  <si>
+    <t>29.03.202648</t>
+  </si>
+  <si>
+    <t>29.03.202649</t>
+  </si>
+  <si>
+    <t>29.03.202650</t>
+  </si>
+  <si>
+    <t>29.03.202651</t>
+  </si>
+  <si>
+    <t>29.03.202652</t>
+  </si>
+  <si>
+    <t>29.03.202653</t>
+  </si>
+  <si>
+    <t>29.03.202654</t>
+  </si>
+  <si>
+    <t>29.03.202655</t>
+  </si>
+  <si>
+    <t>29.03.202656</t>
+  </si>
+  <si>
+    <t>29.03.202657</t>
+  </si>
+  <si>
+    <t>29.03.202658</t>
+  </si>
+  <si>
+    <t>29.03.202659</t>
+  </si>
+  <si>
+    <t>29.03.202660</t>
+  </si>
+  <si>
+    <t>29.03.202661</t>
+  </si>
+  <si>
+    <t>29.03.202662</t>
+  </si>
+  <si>
+    <t>29.03.202663</t>
+  </si>
+  <si>
+    <t>29.03.202664</t>
+  </si>
+  <si>
+    <t>29.03.202665</t>
+  </si>
+  <si>
+    <t>29.03.202666</t>
+  </si>
+  <si>
+    <t>29.03.202667</t>
+  </si>
+  <si>
+    <t>29.03.202668</t>
+  </si>
+  <si>
+    <t>29.03.202669</t>
+  </si>
+  <si>
+    <t>29.03.202670</t>
+  </si>
+  <si>
+    <t>29.03.202671</t>
+  </si>
+  <si>
+    <t>29.03.202672</t>
+  </si>
+  <si>
+    <t>29.03.202673</t>
+  </si>
+  <si>
+    <t>29.03.202674</t>
+  </si>
+  <si>
+    <t>29.03.202675</t>
+  </si>
+  <si>
+    <t>29.03.202676</t>
+  </si>
+  <si>
+    <t>29.03.202677</t>
+  </si>
+  <si>
+    <t>29.03.202678</t>
+  </si>
+  <si>
+    <t>29.03.202679</t>
+  </si>
+  <si>
+    <t>29.03.202680</t>
+  </si>
+  <si>
+    <t>29.03.202681</t>
+  </si>
+  <si>
+    <t>29.03.202682</t>
+  </si>
+  <si>
+    <t>29.03.202683</t>
+  </si>
+  <si>
+    <t>29.03.202684</t>
+  </si>
+  <si>
+    <t>29.03.202685</t>
+  </si>
+  <si>
+    <t>29.03.202686</t>
+  </si>
+  <si>
+    <t>29.03.202687</t>
+  </si>
+  <si>
+    <t>29.03.202688</t>
+  </si>
+  <si>
+    <t>29.03.202689</t>
+  </si>
+  <si>
+    <t>29.03.202690</t>
+  </si>
+  <si>
+    <t>29.03.202691</t>
+  </si>
+  <si>
+    <t>29.03.202692</t>
+  </si>
+  <si>
+    <t>30.03.202693</t>
+  </si>
+  <si>
+    <t>30.03.202694</t>
+  </si>
+  <si>
+    <t>30.03.202695</t>
+  </si>
+  <si>
+    <t>30.03.202696</t>
+  </si>
+  <si>
+    <t>30.03.20261</t>
+  </si>
+  <si>
+    <t>30.03.20262</t>
+  </si>
+  <si>
+    <t>30.03.20263</t>
+  </si>
+  <si>
+    <t>30.03.20264</t>
+  </si>
+  <si>
+    <t>30.03.20265</t>
+  </si>
+  <si>
+    <t>30.03.20266</t>
+  </si>
+  <si>
+    <t>30.03.20267</t>
+  </si>
+  <si>
+    <t>30.03.20268</t>
+  </si>
+  <si>
+    <t>30.03.20269</t>
+  </si>
+  <si>
+    <t>30.03.202610</t>
+  </si>
+  <si>
+    <t>30.03.202611</t>
+  </si>
+  <si>
+    <t>30.03.202612</t>
+  </si>
+  <si>
+    <t>30.03.202613</t>
+  </si>
+  <si>
+    <t>30.03.202614</t>
+  </si>
+  <si>
+    <t>30.03.202615</t>
+  </si>
+  <si>
+    <t>30.03.202616</t>
+  </si>
+  <si>
+    <t>30.03.202617</t>
+  </si>
+  <si>
+    <t>30.03.202618</t>
+  </si>
+  <si>
+    <t>30.03.202619</t>
+  </si>
+  <si>
+    <t>30.03.202620</t>
+  </si>
+  <si>
+    <t>30.03.202621</t>
+  </si>
+  <si>
+    <t>30.03.202622</t>
+  </si>
+  <si>
+    <t>30.03.202623</t>
+  </si>
+  <si>
+    <t>30.03.202624</t>
+  </si>
+  <si>
+    <t>30.03.202625</t>
+  </si>
+  <si>
+    <t>30.03.202626</t>
+  </si>
+  <si>
+    <t>30.03.202627</t>
+  </si>
+  <si>
+    <t>30.03.202628</t>
+  </si>
+  <si>
+    <t>30.03.202629</t>
+  </si>
+  <si>
+    <t>30.03.202630</t>
+  </si>
+  <si>
+    <t>30.03.202631</t>
+  </si>
+  <si>
+    <t>30.03.202632</t>
+  </si>
+  <si>
+    <t>30.03.202633</t>
+  </si>
+  <si>
+    <t>30.03.202634</t>
+  </si>
+  <si>
+    <t>30.03.202635</t>
+  </si>
+  <si>
+    <t>30.03.202636</t>
+  </si>
+  <si>
+    <t>30.03.202637</t>
+  </si>
+  <si>
+    <t>30.03.202638</t>
+  </si>
+  <si>
+    <t>30.03.202639</t>
+  </si>
+  <si>
+    <t>30.03.202640</t>
+  </si>
+  <si>
+    <t>30.03.202641</t>
+  </si>
+  <si>
+    <t>30.03.202642</t>
+  </si>
+  <si>
+    <t>30.03.202643</t>
+  </si>
+  <si>
+    <t>30.03.202644</t>
+  </si>
+  <si>
+    <t>30.03.202645</t>
+  </si>
+  <si>
+    <t>30.03.202646</t>
+  </si>
+  <si>
+    <t>30.03.202647</t>
+  </si>
+  <si>
+    <t>30.03.202648</t>
+  </si>
+  <si>
+    <t>30.03.202649</t>
+  </si>
+  <si>
+    <t>30.03.202650</t>
+  </si>
+  <si>
+    <t>30.03.202651</t>
+  </si>
+  <si>
+    <t>30.03.202652</t>
+  </si>
+  <si>
+    <t>30.03.202653</t>
+  </si>
+  <si>
+    <t>30.03.202654</t>
+  </si>
+  <si>
+    <t>30.03.202655</t>
+  </si>
+  <si>
+    <t>30.03.202656</t>
+  </si>
+  <si>
+    <t>30.03.202657</t>
+  </si>
+  <si>
+    <t>30.03.202658</t>
+  </si>
+  <si>
+    <t>30.03.202659</t>
+  </si>
+  <si>
+    <t>30.03.202660</t>
+  </si>
+  <si>
+    <t>30.03.202661</t>
+  </si>
+  <si>
+    <t>30.03.202662</t>
+  </si>
+  <si>
+    <t>30.03.202663</t>
+  </si>
+  <si>
+    <t>30.03.202664</t>
+  </si>
+  <si>
+    <t>30.03.202665</t>
+  </si>
+  <si>
+    <t>30.03.202666</t>
+  </si>
+  <si>
+    <t>30.03.202667</t>
+  </si>
+  <si>
+    <t>30.03.202668</t>
+  </si>
+  <si>
+    <t>30.03.202669</t>
+  </si>
+  <si>
+    <t>30.03.202670</t>
+  </si>
+  <si>
+    <t>30.03.202671</t>
+  </si>
+  <si>
+    <t>30.03.202672</t>
+  </si>
+  <si>
+    <t>30.03.202673</t>
+  </si>
+  <si>
+    <t>30.03.202674</t>
+  </si>
+  <si>
+    <t>30.03.202675</t>
+  </si>
+  <si>
+    <t>30.03.202676</t>
+  </si>
+  <si>
+    <t>30.03.202677</t>
+  </si>
+  <si>
+    <t>30.03.202678</t>
+  </si>
+  <si>
+    <t>30.03.202679</t>
+  </si>
+  <si>
+    <t>30.03.202680</t>
+  </si>
+  <si>
+    <t>30.03.202681</t>
+  </si>
+  <si>
+    <t>30.03.202682</t>
+  </si>
+  <si>
+    <t>30.03.202683</t>
+  </si>
+  <si>
+    <t>30.03.202684</t>
+  </si>
+  <si>
+    <t>30.03.202685</t>
+  </si>
+  <si>
+    <t>30.03.202686</t>
+  </si>
+  <si>
+    <t>30.03.202687</t>
+  </si>
+  <si>
+    <t>30.03.202688</t>
+  </si>
+  <si>
+    <t>30.03.202689</t>
+  </si>
+  <si>
+    <t>30.03.202690</t>
+  </si>
+  <si>
+    <t>30.03.202691</t>
+  </si>
+  <si>
+    <t>30.03.202692</t>
   </si>
 </sst>
 </file>
@@ -966,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2963,7 +4103,7 @@
         <v>46107.20833333334</v>
       </c>
       <c r="B118">
-        <v>12.917</v>
+        <v>12.798</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2980,10 +4120,10 @@
         <v>46107.21875</v>
       </c>
       <c r="B119">
-        <v>26.045</v>
+        <v>25.401</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2997,10 +4137,10 @@
         <v>46107.22916666666</v>
       </c>
       <c r="B120">
-        <v>50.104</v>
+        <v>49.987</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3014,10 +4154,10 @@
         <v>46107.23958333334</v>
       </c>
       <c r="B121">
-        <v>90.68899999999999</v>
+        <v>91.744</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3031,10 +4171,10 @@
         <v>46107.25</v>
       </c>
       <c r="B122">
-        <v>234.643</v>
+        <v>245.794</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3048,10 +4188,10 @@
         <v>46107.26041666666</v>
       </c>
       <c r="B123">
-        <v>333.959</v>
+        <v>346.97</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3065,10 +4205,10 @@
         <v>46107.27083333334</v>
       </c>
       <c r="B124">
-        <v>475.517</v>
+        <v>497.803</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3082,10 +4222,10 @@
         <v>46107.28125</v>
       </c>
       <c r="B125">
-        <v>642.0650000000001</v>
+        <v>672.865</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3099,10 +4239,10 @@
         <v>46107.29166666666</v>
       </c>
       <c r="B126">
-        <v>914.766</v>
+        <v>950.3869999999999</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3116,10 +4256,10 @@
         <v>46107.30208333334</v>
       </c>
       <c r="B127">
-        <v>1083.649</v>
+        <v>1130.328</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3133,10 +4273,10 @@
         <v>46107.3125</v>
       </c>
       <c r="B128">
-        <v>1255.247</v>
+        <v>1307.034</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3150,10 +4290,10 @@
         <v>46107.32291666666</v>
       </c>
       <c r="B129">
-        <v>1446.998</v>
+        <v>1492.185</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>972</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3167,10 +4307,10 @@
         <v>46107.33333333334</v>
       </c>
       <c r="B130">
-        <v>1708.339</v>
+        <v>1773.934</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>1141</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3184,10 +4324,10 @@
         <v>46107.34375</v>
       </c>
       <c r="B131">
-        <v>1894.187</v>
+        <v>1938.913</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3201,10 +4341,10 @@
         <v>46107.35416666666</v>
       </c>
       <c r="B132">
-        <v>2052.623</v>
+        <v>2093.793</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1420</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3218,10 +4358,10 @@
         <v>46107.36458333334</v>
       </c>
       <c r="B133">
-        <v>2087.385</v>
+        <v>2230.405</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1646</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3235,10 +4375,10 @@
         <v>46107.375</v>
       </c>
       <c r="B134">
-        <v>2352.307</v>
+        <v>2405.962</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1685</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3252,10 +4392,10 @@
         <v>46107.38541666666</v>
       </c>
       <c r="B135">
-        <v>2472.299</v>
+        <v>2526.341</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1730</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3269,10 +4409,10 @@
         <v>46107.39583333334</v>
       </c>
       <c r="B136">
-        <v>2458.286</v>
+        <v>2517.506</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1724</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3286,10 +4426,10 @@
         <v>46107.40625</v>
       </c>
       <c r="B137">
-        <v>2532.9</v>
+        <v>2591.175</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1712</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3303,10 +4443,10 @@
         <v>46107.41666666666</v>
       </c>
       <c r="B138">
-        <v>2619.849</v>
+        <v>2660.418</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1741</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3320,10 +4460,10 @@
         <v>46107.42708333334</v>
       </c>
       <c r="B139">
-        <v>2672.445</v>
+        <v>2712.046</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3337,10 +4477,10 @@
         <v>46107.4375</v>
       </c>
       <c r="B140">
-        <v>2712.791</v>
+        <v>2752.393</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>1845</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3354,10 +4494,10 @@
         <v>46107.44791666666</v>
       </c>
       <c r="B141">
-        <v>2730.309</v>
+        <v>2771.858</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1926</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3371,10 +4511,10 @@
         <v>46107.45833333334</v>
       </c>
       <c r="B142">
-        <v>2708.633</v>
+        <v>2754.7</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1935</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3388,10 +4528,10 @@
         <v>46107.46875</v>
       </c>
       <c r="B143">
-        <v>2699.127</v>
+        <v>2745.106</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1955</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3405,10 +4545,10 @@
         <v>46107.47916666666</v>
       </c>
       <c r="B144">
-        <v>2675.546</v>
+        <v>2725.423</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1971</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3422,10 +4562,10 @@
         <v>46107.48958333334</v>
       </c>
       <c r="B145">
-        <v>2642.549</v>
+        <v>2693.366</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1955</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3439,10 +4579,10 @@
         <v>46107.5</v>
       </c>
       <c r="B146">
-        <v>2703.842</v>
+        <v>2755.37</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1869</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3456,10 +4596,10 @@
         <v>46107.51041666666</v>
       </c>
       <c r="B147">
-        <v>2674.448</v>
+        <v>2720.024</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1860</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3473,10 +4613,10 @@
         <v>46107.52083333334</v>
       </c>
       <c r="B148">
-        <v>2611.995</v>
+        <v>2660.563</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1837</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3490,10 +4630,10 @@
         <v>46107.53125</v>
       </c>
       <c r="B149">
-        <v>2528.494</v>
+        <v>2573.909</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1694</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3507,10 +4647,10 @@
         <v>46107.54166666666</v>
       </c>
       <c r="B150">
-        <v>2364.614</v>
+        <v>2456.957</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>1705</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3524,10 +4664,10 @@
         <v>46107.55208333334</v>
       </c>
       <c r="B151">
-        <v>2237.629</v>
+        <v>2348.874</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>1547</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3541,10 +4681,10 @@
         <v>46107.5625</v>
       </c>
       <c r="B152">
-        <v>2182.316</v>
+        <v>2233.527</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>1567</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3558,10 +4698,10 @@
         <v>46107.57291666666</v>
       </c>
       <c r="B153">
-        <v>2072.936</v>
+        <v>2124.185</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3575,10 +4715,10 @@
         <v>46107.58333333334</v>
       </c>
       <c r="B154">
-        <v>1771.793</v>
+        <v>1833.223</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>1357</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3592,10 +4732,10 @@
         <v>46107.59375</v>
       </c>
       <c r="B155">
-        <v>1651.749</v>
+        <v>1712.955</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>1303</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3609,10 +4749,10 @@
         <v>46107.60416666666</v>
       </c>
       <c r="B156">
-        <v>1525.526</v>
+        <v>1588.262</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>1133</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3626,10 +4766,10 @@
         <v>46107.61458333334</v>
       </c>
       <c r="B157">
-        <v>1410.909</v>
+        <v>1473.647</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3643,10 +4783,10 @@
         <v>46107.625</v>
       </c>
       <c r="B158">
-        <v>1262.929</v>
+        <v>1331.574</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>956</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3660,10 +4800,10 @@
         <v>46107.63541666666</v>
       </c>
       <c r="B159">
-        <v>1093.231</v>
+        <v>1152.784</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3677,10 +4817,10 @@
         <v>46107.64583333334</v>
       </c>
       <c r="B160">
-        <v>926.672</v>
+        <v>973.134</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3694,10 +4834,10 @@
         <v>46107.65625</v>
       </c>
       <c r="B161">
-        <v>775.96</v>
+        <v>819.039</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>633</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3711,10 +4851,10 @@
         <v>46107.66666666666</v>
       </c>
       <c r="B162">
-        <v>589.553</v>
+        <v>612.865</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>498</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3728,10 +4868,10 @@
         <v>46107.67708333334</v>
       </c>
       <c r="B163">
-        <v>440.248</v>
+        <v>458.4</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3745,10 +4885,10 @@
         <v>46107.6875</v>
       </c>
       <c r="B164">
-        <v>306.027</v>
+        <v>319.921</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3762,10 +4902,10 @@
         <v>46107.69791666666</v>
       </c>
       <c r="B165">
-        <v>214.487</v>
+        <v>226.918</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3779,10 +4919,10 @@
         <v>46107.70833333334</v>
       </c>
       <c r="B166">
-        <v>99.142</v>
+        <v>99.301</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3796,10 +4936,10 @@
         <v>46107.71875</v>
       </c>
       <c r="B167">
-        <v>60.792</v>
+        <v>60.774</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3813,7 +4953,7 @@
         <v>46107.72916666666</v>
       </c>
       <c r="B168">
-        <v>39.538</v>
+        <v>39.534</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -4139,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4248,6 +5388,6466 @@
       </c>
       <c r="E193" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46108.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46108.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46108.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46108.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46108.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46108.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46108.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46108.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46108.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46108.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46108.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46108.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46108.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46108.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46108.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46108.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>1.23</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46108.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46108.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46108.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46108.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>4.245</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46108.21875</v>
+      </c>
+      <c r="B215">
+        <v>13.935</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46108.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>29.74</v>
+      </c>
+      <c r="C216">
+        <v>27</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46108.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>57.473</v>
+      </c>
+      <c r="C217">
+        <v>81</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46108.25</v>
+      </c>
+      <c r="B218">
+        <v>134.573</v>
+      </c>
+      <c r="C218">
+        <v>151</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46108.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>196.542</v>
+      </c>
+      <c r="C219">
+        <v>212</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46108.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>273.879</v>
+      </c>
+      <c r="C220">
+        <v>254</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46108.28125</v>
+      </c>
+      <c r="B221">
+        <v>352.289</v>
+      </c>
+      <c r="C221">
+        <v>330</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46108.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>513.803</v>
+      </c>
+      <c r="C222">
+        <v>445</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46108.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>613.798</v>
+      </c>
+      <c r="C223">
+        <v>566</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46108.3125</v>
+      </c>
+      <c r="B224">
+        <v>744.948</v>
+      </c>
+      <c r="C224">
+        <v>693</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46108.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>858.3579999999999</v>
+      </c>
+      <c r="C225">
+        <v>795</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46108.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1042.298</v>
+      </c>
+      <c r="C226">
+        <v>943</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46108.34375</v>
+      </c>
+      <c r="B227">
+        <v>1138.022</v>
+      </c>
+      <c r="C227">
+        <v>984</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46108.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>1227.07</v>
+      </c>
+      <c r="C228">
+        <v>1055</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46108.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>1330.138</v>
+      </c>
+      <c r="C229">
+        <v>1077</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46108.375</v>
+      </c>
+      <c r="B230">
+        <v>1407.816</v>
+      </c>
+      <c r="C230">
+        <v>1184</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46108.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>1490.74</v>
+      </c>
+      <c r="C231">
+        <v>1260</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46108.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>1552.093</v>
+      </c>
+      <c r="C232">
+        <v>1307</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46108.40625</v>
+      </c>
+      <c r="B233">
+        <v>1604.827</v>
+      </c>
+      <c r="C233">
+        <v>1387</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46108.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>1668.429</v>
+      </c>
+      <c r="C234">
+        <v>1466</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46108.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>1693.784</v>
+      </c>
+      <c r="C235">
+        <v>1447</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46108.4375</v>
+      </c>
+      <c r="B236">
+        <v>1717.121</v>
+      </c>
+      <c r="C236">
+        <v>1472</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46108.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>1722.944</v>
+      </c>
+      <c r="C237">
+        <v>1454</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46108.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>1711.893</v>
+      </c>
+      <c r="C238">
+        <v>1483</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46108.46875</v>
+      </c>
+      <c r="B239">
+        <v>1684.744</v>
+      </c>
+      <c r="C239">
+        <v>1480</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46108.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>1653.903</v>
+      </c>
+      <c r="C240">
+        <v>1424</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46108.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>1606.05</v>
+      </c>
+      <c r="C241">
+        <v>1419</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46108.5</v>
+      </c>
+      <c r="B242">
+        <v>1531.342</v>
+      </c>
+      <c r="C242">
+        <v>1343</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46108.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>1469.485</v>
+      </c>
+      <c r="C243">
+        <v>1201</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46108.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>1405.975</v>
+      </c>
+      <c r="C244">
+        <v>1085</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46108.53125</v>
+      </c>
+      <c r="B245">
+        <v>1317.574</v>
+      </c>
+      <c r="C245">
+        <v>1114</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46108.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>1205.299</v>
+      </c>
+      <c r="C246">
+        <v>997</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46108.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1120.259</v>
+      </c>
+      <c r="C247">
+        <v>902</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46108.5625</v>
+      </c>
+      <c r="B248">
+        <v>1038.93</v>
+      </c>
+      <c r="C248">
+        <v>804</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46108.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>983.273</v>
+      </c>
+      <c r="C249">
+        <v>805</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46108.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>873.941</v>
+      </c>
+      <c r="C250">
+        <v>743</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46108.59375</v>
+      </c>
+      <c r="B251">
+        <v>808.05</v>
+      </c>
+      <c r="C251">
+        <v>721</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46108.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>736.365</v>
+      </c>
+      <c r="C252">
+        <v>630</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46108.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>667.9400000000001</v>
+      </c>
+      <c r="C253">
+        <v>549</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46108.625</v>
+      </c>
+      <c r="B254">
+        <v>567.87</v>
+      </c>
+      <c r="C254">
+        <v>514</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46108.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>505.792</v>
+      </c>
+      <c r="C255">
+        <v>422</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46108.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>421.559</v>
+      </c>
+      <c r="C256">
+        <v>315</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46108.65625</v>
+      </c>
+      <c r="B257">
+        <v>354.794</v>
+      </c>
+      <c r="C257">
+        <v>237</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46108.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>255.338</v>
+      </c>
+      <c r="C258">
+        <v>181</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46108.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>197.93</v>
+      </c>
+      <c r="C259">
+        <v>132</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46108.6875</v>
+      </c>
+      <c r="B260">
+        <v>139.428</v>
+      </c>
+      <c r="C260">
+        <v>104</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46108.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>105.144</v>
+      </c>
+      <c r="C261">
+        <v>64</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46108.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>51.167</v>
+      </c>
+      <c r="C262">
+        <v>25</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46108.71875</v>
+      </c>
+      <c r="B263">
+        <v>36.247</v>
+      </c>
+      <c r="C263">
+        <v>8</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46108.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>27.318</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46108.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>19.119</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46108.75</v>
+      </c>
+      <c r="B266">
+        <v>8.593999999999999</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46108.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>8.622</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46108.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>10.63</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46108.78125</v>
+      </c>
+      <c r="B269">
+        <v>10.554</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46108.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>10.07</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46108.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46108.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46108.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>9.23</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46108.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46108.84375</v>
+      </c>
+      <c r="B275">
+        <v>8.73</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46108.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46108.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>3.93</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46108.875</v>
+      </c>
+      <c r="B278">
+        <v>4.73</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46108.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46108.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46108.90625</v>
+      </c>
+      <c r="B281">
+        <v>2.73</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46108.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>4.73</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46108.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0.73</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46108.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46108.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46108.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46108.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46108.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46108.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46109</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46109.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46109.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46109.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46109.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46109.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46109.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46109.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46109.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46109.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46109.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46109.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46109.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46109.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46109.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46109.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46109.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0.732</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46109.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46109.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46109.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46109.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>1.681</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46109.21875</v>
+      </c>
+      <c r="B311">
+        <v>4.856</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46109.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>11.091</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46109.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>20.742</v>
+      </c>
+      <c r="C313">
+        <v>9</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46109.25</v>
+      </c>
+      <c r="B314">
+        <v>40.444</v>
+      </c>
+      <c r="C314">
+        <v>24</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46109.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>61.193</v>
+      </c>
+      <c r="C315">
+        <v>47</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46109.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>81.262</v>
+      </c>
+      <c r="C316">
+        <v>74</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46109.28125</v>
+      </c>
+      <c r="B317">
+        <v>101.645</v>
+      </c>
+      <c r="C317">
+        <v>99</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46109.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>147.319</v>
+      </c>
+      <c r="C318">
+        <v>134</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46109.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>185.251</v>
+      </c>
+      <c r="C319">
+        <v>189</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46109.3125</v>
+      </c>
+      <c r="B320">
+        <v>213.98</v>
+      </c>
+      <c r="C320">
+        <v>208</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46109.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>252.822</v>
+      </c>
+      <c r="C321">
+        <v>239</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46109.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>302.975</v>
+      </c>
+      <c r="C322">
+        <v>267</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46109.34375</v>
+      </c>
+      <c r="B323">
+        <v>329.877</v>
+      </c>
+      <c r="C323">
+        <v>306</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46109.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>361.288</v>
+      </c>
+      <c r="C324">
+        <v>338</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46109.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>403.562</v>
+      </c>
+      <c r="C325">
+        <v>392</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46109.375</v>
+      </c>
+      <c r="B326">
+        <v>430.444</v>
+      </c>
+      <c r="C326">
+        <v>433</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46109.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>456.485</v>
+      </c>
+      <c r="C327">
+        <v>480</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46109.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>482.938</v>
+      </c>
+      <c r="C328">
+        <v>501</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46109.40625</v>
+      </c>
+      <c r="B329">
+        <v>511.73</v>
+      </c>
+      <c r="C329">
+        <v>534</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46109.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>543.046</v>
+      </c>
+      <c r="C330">
+        <v>573</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46109.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>565.048</v>
+      </c>
+      <c r="C331">
+        <v>574</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46109.4375</v>
+      </c>
+      <c r="B332">
+        <v>580.538</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46109.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>600.792</v>
+      </c>
+      <c r="C333">
+        <v>560</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46109.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>615.759</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46109.46875</v>
+      </c>
+      <c r="B335">
+        <v>629.886</v>
+      </c>
+      <c r="C335">
+        <v>582</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46109.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>639.274</v>
+      </c>
+      <c r="C336">
+        <v>620</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46109.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>644.011</v>
+      </c>
+      <c r="C337">
+        <v>624</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46109.5</v>
+      </c>
+      <c r="B338">
+        <v>643.433</v>
+      </c>
+      <c r="C338">
+        <v>619</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46109.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>639.961</v>
+      </c>
+      <c r="C339">
+        <v>552</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46109.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>633.8869999999999</v>
+      </c>
+      <c r="C340">
+        <v>542</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46109.53125</v>
+      </c>
+      <c r="B341">
+        <v>625.876</v>
+      </c>
+      <c r="C341">
+        <v>530</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46109.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>596.919</v>
+      </c>
+      <c r="C342">
+        <v>514</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46109.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>575.602</v>
+      </c>
+      <c r="C343">
+        <v>472</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46109.5625</v>
+      </c>
+      <c r="B344">
+        <v>555.327</v>
+      </c>
+      <c r="C344">
+        <v>398</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46109.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>533.236</v>
+      </c>
+      <c r="C345">
+        <v>396</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46109.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>496.573</v>
+      </c>
+      <c r="C346">
+        <v>368</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46109.59375</v>
+      </c>
+      <c r="B347">
+        <v>471.832</v>
+      </c>
+      <c r="C347">
+        <v>336</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46109.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>442.066</v>
+      </c>
+      <c r="C348">
+        <v>339</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46109.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>408.792</v>
+      </c>
+      <c r="C349">
+        <v>313</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46109.625</v>
+      </c>
+      <c r="B350">
+        <v>355.027</v>
+      </c>
+      <c r="C350">
+        <v>291</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46109.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>317.337</v>
+      </c>
+      <c r="C351">
+        <v>331</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46109.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>276.038</v>
+      </c>
+      <c r="C352">
+        <v>251</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46109.65625</v>
+      </c>
+      <c r="B353">
+        <v>238.32</v>
+      </c>
+      <c r="C353">
+        <v>204</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46109.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>185.029</v>
+      </c>
+      <c r="C354">
+        <v>152</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46109.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>147.38</v>
+      </c>
+      <c r="C355">
+        <v>118</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46109.6875</v>
+      </c>
+      <c r="B356">
+        <v>105.025</v>
+      </c>
+      <c r="C356">
+        <v>92</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46109.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>77.66800000000001</v>
+      </c>
+      <c r="C357">
+        <v>52</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46109.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>39.252</v>
+      </c>
+      <c r="C358">
+        <v>26</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46109.71875</v>
+      </c>
+      <c r="B359">
+        <v>23.792</v>
+      </c>
+      <c r="C359">
+        <v>9</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46109.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>14.404</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46109.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>8.757999999999999</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46109.75</v>
+      </c>
+      <c r="B362">
+        <v>6.141</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46109.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>6.221</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46109.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>6.211</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46109.78125</v>
+      </c>
+      <c r="B365">
+        <v>6.101</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46109.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>5.57</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46109.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46109.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46109.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>4.73</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46109.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>4.63</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46109.84375</v>
+      </c>
+      <c r="B371">
+        <v>4.73</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46109.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46109.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>1.93</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46109.875</v>
+      </c>
+      <c r="B374">
+        <v>0.73</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46109.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46109.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46109.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46109.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46109.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46109.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46109.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46109.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46109.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46109.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46109.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46110</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46110.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46110.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46110.03125</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="2">
+        <v>46110.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+      <c r="E390" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="2">
+        <v>46110.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+      <c r="E391" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="2">
+        <v>46110.0625</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>7</v>
+      </c>
+      <c r="E392" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="2">
+        <v>46110.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="2">
+        <v>46110.125</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394">
+        <v>9</v>
+      </c>
+      <c r="E394" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="2">
+        <v>46110.13541666666</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>10</v>
+      </c>
+      <c r="E395" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="2">
+        <v>46110.14583333334</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>11</v>
+      </c>
+      <c r="E396" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="2">
+        <v>46110.15625</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="2">
+        <v>46110.16666666666</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>13</v>
+      </c>
+      <c r="E398" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="2">
+        <v>46110.17708333334</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>14</v>
+      </c>
+      <c r="E399" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="2">
+        <v>46110.1875</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>15</v>
+      </c>
+      <c r="E400" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="2">
+        <v>46110.19791666666</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>16</v>
+      </c>
+      <c r="E401" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="2">
+        <v>46110.20833333334</v>
+      </c>
+      <c r="B402">
+        <v>1.262</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>17</v>
+      </c>
+      <c r="E402" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="2">
+        <v>46110.21875</v>
+      </c>
+      <c r="B403">
+        <v>2.049</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>18</v>
+      </c>
+      <c r="E403" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="2">
+        <v>46110.22916666666</v>
+      </c>
+      <c r="B404">
+        <v>5.386</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>19</v>
+      </c>
+      <c r="E404" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="2">
+        <v>46110.23958333334</v>
+      </c>
+      <c r="B405">
+        <v>7.621</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>20</v>
+      </c>
+      <c r="E405" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="2">
+        <v>46110.25</v>
+      </c>
+      <c r="B406">
+        <v>15.651</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="2">
+        <v>46110.26041666666</v>
+      </c>
+      <c r="B407">
+        <v>28.417</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+      <c r="D407">
+        <v>22</v>
+      </c>
+      <c r="E407" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="2">
+        <v>46110.27083333334</v>
+      </c>
+      <c r="B408">
+        <v>44.309</v>
+      </c>
+      <c r="C408">
+        <v>3</v>
+      </c>
+      <c r="D408">
+        <v>23</v>
+      </c>
+      <c r="E408" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="2">
+        <v>46110.28125</v>
+      </c>
+      <c r="B409">
+        <v>66.738</v>
+      </c>
+      <c r="C409">
+        <v>16</v>
+      </c>
+      <c r="D409">
+        <v>24</v>
+      </c>
+      <c r="E409" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="2">
+        <v>46110.29166666666</v>
+      </c>
+      <c r="B410">
+        <v>95.70399999999999</v>
+      </c>
+      <c r="C410">
+        <v>36</v>
+      </c>
+      <c r="D410">
+        <v>25</v>
+      </c>
+      <c r="E410" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="2">
+        <v>46110.30208333334</v>
+      </c>
+      <c r="B411">
+        <v>126.661</v>
+      </c>
+      <c r="C411">
+        <v>59</v>
+      </c>
+      <c r="D411">
+        <v>26</v>
+      </c>
+      <c r="E411" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="2">
+        <v>46110.3125</v>
+      </c>
+      <c r="B412">
+        <v>161.61</v>
+      </c>
+      <c r="C412">
+        <v>89</v>
+      </c>
+      <c r="D412">
+        <v>27</v>
+      </c>
+      <c r="E412" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="2">
+        <v>46110.32291666666</v>
+      </c>
+      <c r="B413">
+        <v>197.742</v>
+      </c>
+      <c r="C413">
+        <v>124</v>
+      </c>
+      <c r="D413">
+        <v>28</v>
+      </c>
+      <c r="E413" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="2">
+        <v>46110.33333333334</v>
+      </c>
+      <c r="B414">
+        <v>254.843</v>
+      </c>
+      <c r="C414">
+        <v>164</v>
+      </c>
+      <c r="D414">
+        <v>29</v>
+      </c>
+      <c r="E414" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="2">
+        <v>46110.34375</v>
+      </c>
+      <c r="B415">
+        <v>290.872</v>
+      </c>
+      <c r="C415">
+        <v>197</v>
+      </c>
+      <c r="D415">
+        <v>30</v>
+      </c>
+      <c r="E415" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="2">
+        <v>46110.35416666666</v>
+      </c>
+      <c r="B416">
+        <v>341.411</v>
+      </c>
+      <c r="C416">
+        <v>229</v>
+      </c>
+      <c r="D416">
+        <v>31</v>
+      </c>
+      <c r="E416" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="2">
+        <v>46110.36458333334</v>
+      </c>
+      <c r="B417">
+        <v>370.75</v>
+      </c>
+      <c r="C417">
+        <v>242</v>
+      </c>
+      <c r="D417">
+        <v>32</v>
+      </c>
+      <c r="E417" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="2">
+        <v>46110.375</v>
+      </c>
+      <c r="B418">
+        <v>408.39</v>
+      </c>
+      <c r="C418">
+        <v>284</v>
+      </c>
+      <c r="D418">
+        <v>33</v>
+      </c>
+      <c r="E418" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="2">
+        <v>46110.38541666666</v>
+      </c>
+      <c r="B419">
+        <v>442.679</v>
+      </c>
+      <c r="C419">
+        <v>313</v>
+      </c>
+      <c r="D419">
+        <v>34</v>
+      </c>
+      <c r="E419" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="2">
+        <v>46110.39583333334</v>
+      </c>
+      <c r="B420">
+        <v>470.062</v>
+      </c>
+      <c r="C420">
+        <v>350</v>
+      </c>
+      <c r="D420">
+        <v>35</v>
+      </c>
+      <c r="E420" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="2">
+        <v>46110.40625</v>
+      </c>
+      <c r="B421">
+        <v>498.813</v>
+      </c>
+      <c r="C421">
+        <v>383</v>
+      </c>
+      <c r="D421">
+        <v>36</v>
+      </c>
+      <c r="E421" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="2">
+        <v>46110.41666666666</v>
+      </c>
+      <c r="B422">
+        <v>537.1900000000001</v>
+      </c>
+      <c r="C422">
+        <v>409</v>
+      </c>
+      <c r="D422">
+        <v>37</v>
+      </c>
+      <c r="E422" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="2">
+        <v>46110.42708333334</v>
+      </c>
+      <c r="B423">
+        <v>555.612</v>
+      </c>
+      <c r="C423">
+        <v>435</v>
+      </c>
+      <c r="D423">
+        <v>38</v>
+      </c>
+      <c r="E423" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="2">
+        <v>46110.4375</v>
+      </c>
+      <c r="B424">
+        <v>575.7809999999999</v>
+      </c>
+      <c r="C424">
+        <v>444</v>
+      </c>
+      <c r="D424">
+        <v>39</v>
+      </c>
+      <c r="E424" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="2">
+        <v>46110.44791666666</v>
+      </c>
+      <c r="B425">
+        <v>585.452</v>
+      </c>
+      <c r="C425">
+        <v>467</v>
+      </c>
+      <c r="D425">
+        <v>40</v>
+      </c>
+      <c r="E425" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="2">
+        <v>46110.45833333334</v>
+      </c>
+      <c r="B426">
+        <v>591.917</v>
+      </c>
+      <c r="C426">
+        <v>465</v>
+      </c>
+      <c r="D426">
+        <v>41</v>
+      </c>
+      <c r="E426" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="2">
+        <v>46110.46875</v>
+      </c>
+      <c r="B427">
+        <v>601.768</v>
+      </c>
+      <c r="C427">
+        <v>477</v>
+      </c>
+      <c r="D427">
+        <v>42</v>
+      </c>
+      <c r="E427" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="2">
+        <v>46110.47916666666</v>
+      </c>
+      <c r="B428">
+        <v>606.855</v>
+      </c>
+      <c r="C428">
+        <v>485</v>
+      </c>
+      <c r="D428">
+        <v>43</v>
+      </c>
+      <c r="E428" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="2">
+        <v>46110.48958333334</v>
+      </c>
+      <c r="B429">
+        <v>609.854</v>
+      </c>
+      <c r="C429">
+        <v>525</v>
+      </c>
+      <c r="D429">
+        <v>44</v>
+      </c>
+      <c r="E429" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="2">
+        <v>46110.5</v>
+      </c>
+      <c r="B430">
+        <v>601.46</v>
+      </c>
+      <c r="C430">
+        <v>517</v>
+      </c>
+      <c r="D430">
+        <v>45</v>
+      </c>
+      <c r="E430" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="2">
+        <v>46110.51041666666</v>
+      </c>
+      <c r="B431">
+        <v>597.621</v>
+      </c>
+      <c r="C431">
+        <v>551</v>
+      </c>
+      <c r="D431">
+        <v>46</v>
+      </c>
+      <c r="E431" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="2">
+        <v>46110.52083333334</v>
+      </c>
+      <c r="B432">
+        <v>588.245</v>
+      </c>
+      <c r="C432">
+        <v>530</v>
+      </c>
+      <c r="D432">
+        <v>47</v>
+      </c>
+      <c r="E432" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="2">
+        <v>46110.53125</v>
+      </c>
+      <c r="B433">
+        <v>575.458</v>
+      </c>
+      <c r="C433">
+        <v>545</v>
+      </c>
+      <c r="D433">
+        <v>48</v>
+      </c>
+      <c r="E433" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="2">
+        <v>46110.54166666666</v>
+      </c>
+      <c r="B434">
+        <v>551.9450000000001</v>
+      </c>
+      <c r="C434">
+        <v>524</v>
+      </c>
+      <c r="D434">
+        <v>49</v>
+      </c>
+      <c r="E434" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="2">
+        <v>46110.55208333334</v>
+      </c>
+      <c r="B435">
+        <v>534.653</v>
+      </c>
+      <c r="C435">
+        <v>549</v>
+      </c>
+      <c r="D435">
+        <v>50</v>
+      </c>
+      <c r="E435" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="2">
+        <v>46110.5625</v>
+      </c>
+      <c r="B436">
+        <v>518.71</v>
+      </c>
+      <c r="C436">
+        <v>510</v>
+      </c>
+      <c r="D436">
+        <v>51</v>
+      </c>
+      <c r="E436" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="2">
+        <v>46110.57291666666</v>
+      </c>
+      <c r="B437">
+        <v>504.161</v>
+      </c>
+      <c r="C437">
+        <v>476</v>
+      </c>
+      <c r="D437">
+        <v>52</v>
+      </c>
+      <c r="E437" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="2">
+        <v>46110.58333333334</v>
+      </c>
+      <c r="B438">
+        <v>464.784</v>
+      </c>
+      <c r="C438">
+        <v>416</v>
+      </c>
+      <c r="D438">
+        <v>53</v>
+      </c>
+      <c r="E438" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="2">
+        <v>46110.59375</v>
+      </c>
+      <c r="B439">
+        <v>440.841</v>
+      </c>
+      <c r="C439">
+        <v>369</v>
+      </c>
+      <c r="D439">
+        <v>54</v>
+      </c>
+      <c r="E439" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="2">
+        <v>46110.60416666666</v>
+      </c>
+      <c r="B440">
+        <v>417.199</v>
+      </c>
+      <c r="C440">
+        <v>372</v>
+      </c>
+      <c r="D440">
+        <v>55</v>
+      </c>
+      <c r="E440" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="2">
+        <v>46110.61458333334</v>
+      </c>
+      <c r="B441">
+        <v>389.487</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441">
+        <v>56</v>
+      </c>
+      <c r="E441" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="2">
+        <v>46110.625</v>
+      </c>
+      <c r="B442">
+        <v>351.652</v>
+      </c>
+      <c r="C442">
+        <v>355</v>
+      </c>
+      <c r="D442">
+        <v>57</v>
+      </c>
+      <c r="E442" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="2">
+        <v>46110.63541666666</v>
+      </c>
+      <c r="B443">
+        <v>323.26</v>
+      </c>
+      <c r="C443">
+        <v>345</v>
+      </c>
+      <c r="D443">
+        <v>58</v>
+      </c>
+      <c r="E443" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="2">
+        <v>46110.64583333334</v>
+      </c>
+      <c r="B444">
+        <v>276.337</v>
+      </c>
+      <c r="C444">
+        <v>298</v>
+      </c>
+      <c r="D444">
+        <v>59</v>
+      </c>
+      <c r="E444" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="2">
+        <v>46110.65625</v>
+      </c>
+      <c r="B445">
+        <v>249.444</v>
+      </c>
+      <c r="C445">
+        <v>282</v>
+      </c>
+      <c r="D445">
+        <v>60</v>
+      </c>
+      <c r="E445" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="2">
+        <v>46110.66666666666</v>
+      </c>
+      <c r="B446">
+        <v>200.871</v>
+      </c>
+      <c r="C446">
+        <v>274</v>
+      </c>
+      <c r="D446">
+        <v>61</v>
+      </c>
+      <c r="E446" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="2">
+        <v>46110.67708333334</v>
+      </c>
+      <c r="B447">
+        <v>175.961</v>
+      </c>
+      <c r="C447">
+        <v>235</v>
+      </c>
+      <c r="D447">
+        <v>62</v>
+      </c>
+      <c r="E447" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="2">
+        <v>46110.6875</v>
+      </c>
+      <c r="B448">
+        <v>147.232</v>
+      </c>
+      <c r="C448">
+        <v>199</v>
+      </c>
+      <c r="D448">
+        <v>63</v>
+      </c>
+      <c r="E448" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="2">
+        <v>46110.69791666666</v>
+      </c>
+      <c r="B449">
+        <v>124.155</v>
+      </c>
+      <c r="C449">
+        <v>159</v>
+      </c>
+      <c r="D449">
+        <v>64</v>
+      </c>
+      <c r="E449" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="2">
+        <v>46110.70833333334</v>
+      </c>
+      <c r="B450">
+        <v>81.71599999999999</v>
+      </c>
+      <c r="C450">
+        <v>117</v>
+      </c>
+      <c r="D450">
+        <v>65</v>
+      </c>
+      <c r="E450" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="2">
+        <v>46110.71875</v>
+      </c>
+      <c r="B451">
+        <v>64.04900000000001</v>
+      </c>
+      <c r="C451">
+        <v>84</v>
+      </c>
+      <c r="D451">
+        <v>66</v>
+      </c>
+      <c r="E451" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="2">
+        <v>46110.72916666666</v>
+      </c>
+      <c r="B452">
+        <v>49.442</v>
+      </c>
+      <c r="C452">
+        <v>66</v>
+      </c>
+      <c r="D452">
+        <v>67</v>
+      </c>
+      <c r="E452" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="2">
+        <v>46110.73958333334</v>
+      </c>
+      <c r="B453">
+        <v>35.144</v>
+      </c>
+      <c r="C453">
+        <v>40</v>
+      </c>
+      <c r="D453">
+        <v>68</v>
+      </c>
+      <c r="E453" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="2">
+        <v>46110.75</v>
+      </c>
+      <c r="B454">
+        <v>26.287</v>
+      </c>
+      <c r="C454">
+        <v>15</v>
+      </c>
+      <c r="D454">
+        <v>69</v>
+      </c>
+      <c r="E454" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="2">
+        <v>46110.76041666666</v>
+      </c>
+      <c r="B455">
+        <v>19.459</v>
+      </c>
+      <c r="C455">
+        <v>4</v>
+      </c>
+      <c r="D455">
+        <v>70</v>
+      </c>
+      <c r="E455" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="2">
+        <v>46110.77083333334</v>
+      </c>
+      <c r="B456">
+        <v>12.77</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456">
+        <v>71</v>
+      </c>
+      <c r="E456" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="2">
+        <v>46110.78125</v>
+      </c>
+      <c r="B457">
+        <v>9.708</v>
+      </c>
+      <c r="C457">
+        <v>0</v>
+      </c>
+      <c r="D457">
+        <v>72</v>
+      </c>
+      <c r="E457" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="2">
+        <v>46110.79166666666</v>
+      </c>
+      <c r="B458">
+        <v>6.322</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458">
+        <v>73</v>
+      </c>
+      <c r="E458" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="2">
+        <v>46110.80208333334</v>
+      </c>
+      <c r="B459">
+        <v>5.69</v>
+      </c>
+      <c r="C459">
+        <v>0</v>
+      </c>
+      <c r="D459">
+        <v>74</v>
+      </c>
+      <c r="E459" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="2">
+        <v>46110.8125</v>
+      </c>
+      <c r="B460">
+        <v>5.61</v>
+      </c>
+      <c r="C460">
+        <v>0</v>
+      </c>
+      <c r="D460">
+        <v>75</v>
+      </c>
+      <c r="E460" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="2">
+        <v>46110.82291666666</v>
+      </c>
+      <c r="B461">
+        <v>4.73</v>
+      </c>
+      <c r="C461">
+        <v>0</v>
+      </c>
+      <c r="D461">
+        <v>76</v>
+      </c>
+      <c r="E461" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="2">
+        <v>46110.83333333334</v>
+      </c>
+      <c r="B462">
+        <v>4.63</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462">
+        <v>77</v>
+      </c>
+      <c r="E462" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="2">
+        <v>46110.84375</v>
+      </c>
+      <c r="B463">
+        <v>4.73</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+      <c r="D463">
+        <v>78</v>
+      </c>
+      <c r="E463" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="2">
+        <v>46110.85416666666</v>
+      </c>
+      <c r="B464">
+        <v>0</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464">
+        <v>79</v>
+      </c>
+      <c r="E464" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="2">
+        <v>46110.86458333334</v>
+      </c>
+      <c r="B465">
+        <v>1.93</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+      <c r="D465">
+        <v>80</v>
+      </c>
+      <c r="E465" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="2">
+        <v>46110.875</v>
+      </c>
+      <c r="B466">
+        <v>0.73</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466">
+        <v>81</v>
+      </c>
+      <c r="E466" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="2">
+        <v>46110.88541666666</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+      <c r="D467">
+        <v>82</v>
+      </c>
+      <c r="E467" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="2">
+        <v>46110.89583333334</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+      <c r="D468">
+        <v>83</v>
+      </c>
+      <c r="E468" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="2">
+        <v>46110.90625</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+      <c r="D469">
+        <v>84</v>
+      </c>
+      <c r="E469" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="2">
+        <v>46110.91666666666</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+      <c r="C470">
+        <v>0</v>
+      </c>
+      <c r="D470">
+        <v>85</v>
+      </c>
+      <c r="E470" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="2">
+        <v>46110.92708333334</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471">
+        <v>86</v>
+      </c>
+      <c r="E471" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" s="2">
+        <v>46110.9375</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472">
+        <v>87</v>
+      </c>
+      <c r="E472" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" s="2">
+        <v>46110.94791666666</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473">
+        <v>88</v>
+      </c>
+      <c r="E473" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" s="2">
+        <v>46110.95833333334</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474">
+        <v>89</v>
+      </c>
+      <c r="E474" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" s="2">
+        <v>46110.96875</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
+      </c>
+      <c r="D475">
+        <v>90</v>
+      </c>
+      <c r="E475" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" s="2">
+        <v>46110.97916666666</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+      <c r="D476">
+        <v>91</v>
+      </c>
+      <c r="E476" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" s="2">
+        <v>46110.98958333334</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+      <c r="C477">
+        <v>0</v>
+      </c>
+      <c r="D477">
+        <v>92</v>
+      </c>
+      <c r="E477" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+      <c r="D478">
+        <v>93</v>
+      </c>
+      <c r="E478" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479" s="2">
+        <v>46111.01041666666</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+      <c r="D479">
+        <v>94</v>
+      </c>
+      <c r="E479" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480" s="2">
+        <v>46111.02083333334</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+      <c r="C480">
+        <v>0</v>
+      </c>
+      <c r="D480">
+        <v>95</v>
+      </c>
+      <c r="E480" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481" s="2">
+        <v>46111.03125</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+      <c r="D481">
+        <v>96</v>
+      </c>
+      <c r="E481" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5">
+      <c r="A482" s="2">
+        <v>46111.04166666666</v>
+      </c>
+      <c r="B482">
+        <v>0</v>
+      </c>
+      <c r="C482">
+        <v>0</v>
+      </c>
+      <c r="D482">
+        <v>1</v>
+      </c>
+      <c r="E482" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5">
+      <c r="A483" s="2">
+        <v>46111.05208333334</v>
+      </c>
+      <c r="B483">
+        <v>0</v>
+      </c>
+      <c r="C483">
+        <v>0</v>
+      </c>
+      <c r="D483">
+        <v>2</v>
+      </c>
+      <c r="E483" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5">
+      <c r="A484" s="2">
+        <v>46111.0625</v>
+      </c>
+      <c r="B484">
+        <v>0</v>
+      </c>
+      <c r="C484">
+        <v>0</v>
+      </c>
+      <c r="D484">
+        <v>3</v>
+      </c>
+      <c r="E484" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5">
+      <c r="A485" s="2">
+        <v>46111.07291666666</v>
+      </c>
+      <c r="B485">
+        <v>0</v>
+      </c>
+      <c r="C485">
+        <v>0</v>
+      </c>
+      <c r="D485">
+        <v>4</v>
+      </c>
+      <c r="E485" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5">
+      <c r="A486" s="2">
+        <v>46111.08333333334</v>
+      </c>
+      <c r="B486">
+        <v>0</v>
+      </c>
+      <c r="C486">
+        <v>0</v>
+      </c>
+      <c r="D486">
+        <v>5</v>
+      </c>
+      <c r="E486" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5">
+      <c r="A487" s="2">
+        <v>46111.09375</v>
+      </c>
+      <c r="B487">
+        <v>0</v>
+      </c>
+      <c r="C487">
+        <v>0</v>
+      </c>
+      <c r="D487">
+        <v>6</v>
+      </c>
+      <c r="E487" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5">
+      <c r="A488" s="2">
+        <v>46111.10416666666</v>
+      </c>
+      <c r="B488">
+        <v>0</v>
+      </c>
+      <c r="C488">
+        <v>0</v>
+      </c>
+      <c r="D488">
+        <v>7</v>
+      </c>
+      <c r="E488" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5">
+      <c r="A489" s="2">
+        <v>46111.11458333334</v>
+      </c>
+      <c r="B489">
+        <v>0</v>
+      </c>
+      <c r="C489">
+        <v>0</v>
+      </c>
+      <c r="D489">
+        <v>8</v>
+      </c>
+      <c r="E489" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5">
+      <c r="A490" s="2">
+        <v>46111.125</v>
+      </c>
+      <c r="B490">
+        <v>0</v>
+      </c>
+      <c r="C490">
+        <v>0</v>
+      </c>
+      <c r="D490">
+        <v>9</v>
+      </c>
+      <c r="E490" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5">
+      <c r="A491" s="2">
+        <v>46111.13541666666</v>
+      </c>
+      <c r="B491">
+        <v>0</v>
+      </c>
+      <c r="C491">
+        <v>0</v>
+      </c>
+      <c r="D491">
+        <v>10</v>
+      </c>
+      <c r="E491" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5">
+      <c r="A492" s="2">
+        <v>46111.14583333334</v>
+      </c>
+      <c r="B492">
+        <v>0</v>
+      </c>
+      <c r="C492">
+        <v>0</v>
+      </c>
+      <c r="D492">
+        <v>11</v>
+      </c>
+      <c r="E492" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5">
+      <c r="A493" s="2">
+        <v>46111.15625</v>
+      </c>
+      <c r="B493">
+        <v>0</v>
+      </c>
+      <c r="C493">
+        <v>0</v>
+      </c>
+      <c r="D493">
+        <v>12</v>
+      </c>
+      <c r="E493" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5">
+      <c r="A494" s="2">
+        <v>46111.16666666666</v>
+      </c>
+      <c r="B494">
+        <v>0</v>
+      </c>
+      <c r="C494">
+        <v>0</v>
+      </c>
+      <c r="D494">
+        <v>13</v>
+      </c>
+      <c r="E494" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5">
+      <c r="A495" s="2">
+        <v>46111.17708333334</v>
+      </c>
+      <c r="B495">
+        <v>0</v>
+      </c>
+      <c r="C495">
+        <v>0</v>
+      </c>
+      <c r="D495">
+        <v>14</v>
+      </c>
+      <c r="E495" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5">
+      <c r="A496" s="2">
+        <v>46111.1875</v>
+      </c>
+      <c r="B496">
+        <v>0</v>
+      </c>
+      <c r="C496">
+        <v>0</v>
+      </c>
+      <c r="D496">
+        <v>15</v>
+      </c>
+      <c r="E496" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5">
+      <c r="A497" s="2">
+        <v>46111.19791666666</v>
+      </c>
+      <c r="B497">
+        <v>12.73</v>
+      </c>
+      <c r="C497">
+        <v>0</v>
+      </c>
+      <c r="D497">
+        <v>16</v>
+      </c>
+      <c r="E497" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5">
+      <c r="A498" s="2">
+        <v>46111.20833333334</v>
+      </c>
+      <c r="B498">
+        <v>27.776</v>
+      </c>
+      <c r="C498">
+        <v>0</v>
+      </c>
+      <c r="D498">
+        <v>17</v>
+      </c>
+      <c r="E498" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5">
+      <c r="A499" s="2">
+        <v>46111.21875</v>
+      </c>
+      <c r="B499">
+        <v>24.977</v>
+      </c>
+      <c r="C499">
+        <v>0</v>
+      </c>
+      <c r="D499">
+        <v>18</v>
+      </c>
+      <c r="E499" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5">
+      <c r="A500" s="2">
+        <v>46111.22916666666</v>
+      </c>
+      <c r="B500">
+        <v>25.929</v>
+      </c>
+      <c r="C500">
+        <v>0</v>
+      </c>
+      <c r="D500">
+        <v>19</v>
+      </c>
+      <c r="E500" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5">
+      <c r="A501" s="2">
+        <v>46111.23958333334</v>
+      </c>
+      <c r="B501">
+        <v>23.354</v>
+      </c>
+      <c r="C501">
+        <v>0</v>
+      </c>
+      <c r="D501">
+        <v>20</v>
+      </c>
+      <c r="E501" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5">
+      <c r="A502" s="2">
+        <v>46111.25</v>
+      </c>
+      <c r="B502">
+        <v>11.492</v>
+      </c>
+      <c r="C502">
+        <v>0</v>
+      </c>
+      <c r="D502">
+        <v>21</v>
+      </c>
+      <c r="E502" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5">
+      <c r="A503" s="2">
+        <v>46111.26041666666</v>
+      </c>
+      <c r="B503">
+        <v>19.426</v>
+      </c>
+      <c r="C503">
+        <v>0</v>
+      </c>
+      <c r="D503">
+        <v>22</v>
+      </c>
+      <c r="E503" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5">
+      <c r="A504" s="2">
+        <v>46111.27083333334</v>
+      </c>
+      <c r="B504">
+        <v>36.134</v>
+      </c>
+      <c r="C504">
+        <v>15</v>
+      </c>
+      <c r="D504">
+        <v>23</v>
+      </c>
+      <c r="E504" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5">
+      <c r="A505" s="2">
+        <v>46111.28125</v>
+      </c>
+      <c r="B505">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="C505">
+        <v>38</v>
+      </c>
+      <c r="D505">
+        <v>24</v>
+      </c>
+      <c r="E505" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5">
+      <c r="A506" s="2">
+        <v>46111.29166666666</v>
+      </c>
+      <c r="B506">
+        <v>110.018</v>
+      </c>
+      <c r="C506">
+        <v>76</v>
+      </c>
+      <c r="D506">
+        <v>25</v>
+      </c>
+      <c r="E506" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5">
+      <c r="A507" s="2">
+        <v>46111.30208333334</v>
+      </c>
+      <c r="B507">
+        <v>154.12</v>
+      </c>
+      <c r="C507">
+        <v>0</v>
+      </c>
+      <c r="D507">
+        <v>26</v>
+      </c>
+      <c r="E507" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5">
+      <c r="A508" s="2">
+        <v>46111.3125</v>
+      </c>
+      <c r="B508">
+        <v>197.943</v>
+      </c>
+      <c r="C508">
+        <v>0</v>
+      </c>
+      <c r="D508">
+        <v>27</v>
+      </c>
+      <c r="E508" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5">
+      <c r="A509" s="2">
+        <v>46111.32291666666</v>
+      </c>
+      <c r="B509">
+        <v>256.318</v>
+      </c>
+      <c r="C509">
+        <v>0</v>
+      </c>
+      <c r="D509">
+        <v>28</v>
+      </c>
+      <c r="E509" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5">
+      <c r="A510" s="2">
+        <v>46111.33333333334</v>
+      </c>
+      <c r="B510">
+        <v>333.826</v>
+      </c>
+      <c r="C510">
+        <v>0</v>
+      </c>
+      <c r="D510">
+        <v>29</v>
+      </c>
+      <c r="E510" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5">
+      <c r="A511" s="2">
+        <v>46111.34375</v>
+      </c>
+      <c r="B511">
+        <v>394.462</v>
+      </c>
+      <c r="C511">
+        <v>0</v>
+      </c>
+      <c r="D511">
+        <v>30</v>
+      </c>
+      <c r="E511" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5">
+      <c r="A512" s="2">
+        <v>46111.35416666666</v>
+      </c>
+      <c r="B512">
+        <v>454.56</v>
+      </c>
+      <c r="C512">
+        <v>0</v>
+      </c>
+      <c r="D512">
+        <v>31</v>
+      </c>
+      <c r="E512" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5">
+      <c r="A513" s="2">
+        <v>46111.36458333334</v>
+      </c>
+      <c r="B513">
+        <v>527.205</v>
+      </c>
+      <c r="C513">
+        <v>0</v>
+      </c>
+      <c r="D513">
+        <v>32</v>
+      </c>
+      <c r="E513" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5">
+      <c r="A514" s="2">
+        <v>46111.375</v>
+      </c>
+      <c r="B514">
+        <v>603.612</v>
+      </c>
+      <c r="C514">
+        <v>0</v>
+      </c>
+      <c r="D514">
+        <v>33</v>
+      </c>
+      <c r="E514" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5">
+      <c r="A515" s="2">
+        <v>46111.38541666666</v>
+      </c>
+      <c r="B515">
+        <v>665.804</v>
+      </c>
+      <c r="C515">
+        <v>0</v>
+      </c>
+      <c r="D515">
+        <v>34</v>
+      </c>
+      <c r="E515" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5">
+      <c r="A516" s="2">
+        <v>46111.39583333334</v>
+      </c>
+      <c r="B516">
+        <v>732.481</v>
+      </c>
+      <c r="C516">
+        <v>0</v>
+      </c>
+      <c r="D516">
+        <v>35</v>
+      </c>
+      <c r="E516" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5">
+      <c r="A517" s="2">
+        <v>46111.40625</v>
+      </c>
+      <c r="B517">
+        <v>790.407</v>
+      </c>
+      <c r="C517">
+        <v>0</v>
+      </c>
+      <c r="D517">
+        <v>36</v>
+      </c>
+      <c r="E517" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5">
+      <c r="A518" s="2">
+        <v>46111.41666666666</v>
+      </c>
+      <c r="B518">
+        <v>883.1180000000001</v>
+      </c>
+      <c r="C518">
+        <v>0</v>
+      </c>
+      <c r="D518">
+        <v>37</v>
+      </c>
+      <c r="E518" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5">
+      <c r="A519" s="2">
+        <v>46111.42708333334</v>
+      </c>
+      <c r="B519">
+        <v>928.577</v>
+      </c>
+      <c r="C519">
+        <v>0</v>
+      </c>
+      <c r="D519">
+        <v>38</v>
+      </c>
+      <c r="E519" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5">
+      <c r="A520" s="2">
+        <v>46111.4375</v>
+      </c>
+      <c r="B520">
+        <v>979.9690000000001</v>
+      </c>
+      <c r="C520">
+        <v>0</v>
+      </c>
+      <c r="D520">
+        <v>39</v>
+      </c>
+      <c r="E520" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5">
+      <c r="A521" s="2">
+        <v>46111.44791666666</v>
+      </c>
+      <c r="B521">
+        <v>1019.397</v>
+      </c>
+      <c r="C521">
+        <v>0</v>
+      </c>
+      <c r="D521">
+        <v>40</v>
+      </c>
+      <c r="E521" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5">
+      <c r="A522" s="2">
+        <v>46111.45833333334</v>
+      </c>
+      <c r="B522">
+        <v>1070.75</v>
+      </c>
+      <c r="C522">
+        <v>0</v>
+      </c>
+      <c r="D522">
+        <v>41</v>
+      </c>
+      <c r="E522" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5">
+      <c r="A523" s="2">
+        <v>46111.46875</v>
+      </c>
+      <c r="B523">
+        <v>1093.128</v>
+      </c>
+      <c r="C523">
+        <v>0</v>
+      </c>
+      <c r="D523">
+        <v>42</v>
+      </c>
+      <c r="E523" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5">
+      <c r="A524" s="2">
+        <v>46111.47916666666</v>
+      </c>
+      <c r="B524">
+        <v>1104.583</v>
+      </c>
+      <c r="C524">
+        <v>0</v>
+      </c>
+      <c r="D524">
+        <v>43</v>
+      </c>
+      <c r="E524" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5">
+      <c r="A525" s="2">
+        <v>46111.48958333334</v>
+      </c>
+      <c r="B525">
+        <v>1106.911</v>
+      </c>
+      <c r="C525">
+        <v>0</v>
+      </c>
+      <c r="D525">
+        <v>44</v>
+      </c>
+      <c r="E525" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5">
+      <c r="A526" s="2">
+        <v>46111.5</v>
+      </c>
+      <c r="B526">
+        <v>1110.228</v>
+      </c>
+      <c r="C526">
+        <v>0</v>
+      </c>
+      <c r="D526">
+        <v>45</v>
+      </c>
+      <c r="E526" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5">
+      <c r="A527" s="2">
+        <v>46111.51041666666</v>
+      </c>
+      <c r="B527">
+        <v>1111.745</v>
+      </c>
+      <c r="C527">
+        <v>0</v>
+      </c>
+      <c r="D527">
+        <v>46</v>
+      </c>
+      <c r="E527" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5">
+      <c r="A528" s="2">
+        <v>46111.52083333334</v>
+      </c>
+      <c r="B528">
+        <v>1099.547</v>
+      </c>
+      <c r="C528">
+        <v>0</v>
+      </c>
+      <c r="D528">
+        <v>47</v>
+      </c>
+      <c r="E528" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5">
+      <c r="A529" s="2">
+        <v>46111.53125</v>
+      </c>
+      <c r="B529">
+        <v>1085.046</v>
+      </c>
+      <c r="C529">
+        <v>0</v>
+      </c>
+      <c r="D529">
+        <v>48</v>
+      </c>
+      <c r="E529" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5">
+      <c r="A530" s="2">
+        <v>46111.54166666666</v>
+      </c>
+      <c r="B530">
+        <v>1055.087</v>
+      </c>
+      <c r="C530">
+        <v>0</v>
+      </c>
+      <c r="D530">
+        <v>49</v>
+      </c>
+      <c r="E530" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5">
+      <c r="A531" s="2">
+        <v>46111.55208333334</v>
+      </c>
+      <c r="B531">
+        <v>1031.119</v>
+      </c>
+      <c r="C531">
+        <v>0</v>
+      </c>
+      <c r="D531">
+        <v>50</v>
+      </c>
+      <c r="E531" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5">
+      <c r="A532" s="2">
+        <v>46111.5625</v>
+      </c>
+      <c r="B532">
+        <v>997.823</v>
+      </c>
+      <c r="C532">
+        <v>0</v>
+      </c>
+      <c r="D532">
+        <v>51</v>
+      </c>
+      <c r="E532" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5">
+      <c r="A533" s="2">
+        <v>46111.57291666666</v>
+      </c>
+      <c r="B533">
+        <v>966.778</v>
+      </c>
+      <c r="C533">
+        <v>0</v>
+      </c>
+      <c r="D533">
+        <v>52</v>
+      </c>
+      <c r="E533" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5">
+      <c r="A534" s="2">
+        <v>46111.58333333334</v>
+      </c>
+      <c r="B534">
+        <v>900.793</v>
+      </c>
+      <c r="C534">
+        <v>0</v>
+      </c>
+      <c r="D534">
+        <v>53</v>
+      </c>
+      <c r="E534" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5">
+      <c r="A535" s="2">
+        <v>46111.59375</v>
+      </c>
+      <c r="B535">
+        <v>862.674</v>
+      </c>
+      <c r="C535">
+        <v>0</v>
+      </c>
+      <c r="D535">
+        <v>54</v>
+      </c>
+      <c r="E535" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5">
+      <c r="A536" s="2">
+        <v>46111.60416666666</v>
+      </c>
+      <c r="B536">
+        <v>828.583</v>
+      </c>
+      <c r="C536">
+        <v>0</v>
+      </c>
+      <c r="D536">
+        <v>55</v>
+      </c>
+      <c r="E536" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5">
+      <c r="A537" s="2">
+        <v>46111.61458333334</v>
+      </c>
+      <c r="B537">
+        <v>784.424</v>
+      </c>
+      <c r="C537">
+        <v>0</v>
+      </c>
+      <c r="D537">
+        <v>56</v>
+      </c>
+      <c r="E537" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5">
+      <c r="A538" s="2">
+        <v>46111.625</v>
+      </c>
+      <c r="B538">
+        <v>701.229</v>
+      </c>
+      <c r="C538">
+        <v>0</v>
+      </c>
+      <c r="D538">
+        <v>57</v>
+      </c>
+      <c r="E538" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5">
+      <c r="A539" s="2">
+        <v>46111.63541666666</v>
+      </c>
+      <c r="B539">
+        <v>658.211</v>
+      </c>
+      <c r="C539">
+        <v>0</v>
+      </c>
+      <c r="D539">
+        <v>58</v>
+      </c>
+      <c r="E539" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5">
+      <c r="A540" s="2">
+        <v>46111.64583333334</v>
+      </c>
+      <c r="B540">
+        <v>607.7619999999999</v>
+      </c>
+      <c r="C540">
+        <v>0</v>
+      </c>
+      <c r="D540">
+        <v>59</v>
+      </c>
+      <c r="E540" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5">
+      <c r="A541" s="2">
+        <v>46111.65625</v>
+      </c>
+      <c r="B541">
+        <v>542.862</v>
+      </c>
+      <c r="C541">
+        <v>0</v>
+      </c>
+      <c r="D541">
+        <v>60</v>
+      </c>
+      <c r="E541" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5">
+      <c r="A542" s="2">
+        <v>46111.66666666666</v>
+      </c>
+      <c r="B542">
+        <v>436.213</v>
+      </c>
+      <c r="C542">
+        <v>0</v>
+      </c>
+      <c r="D542">
+        <v>61</v>
+      </c>
+      <c r="E542" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5">
+      <c r="A543" s="2">
+        <v>46111.67708333334</v>
+      </c>
+      <c r="B543">
+        <v>379.773</v>
+      </c>
+      <c r="C543">
+        <v>0</v>
+      </c>
+      <c r="D543">
+        <v>62</v>
+      </c>
+      <c r="E543" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5">
+      <c r="A544" s="2">
+        <v>46111.6875</v>
+      </c>
+      <c r="B544">
+        <v>330.358</v>
+      </c>
+      <c r="C544">
+        <v>0</v>
+      </c>
+      <c r="D544">
+        <v>63</v>
+      </c>
+      <c r="E544" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5">
+      <c r="A545" s="2">
+        <v>46111.69791666666</v>
+      </c>
+      <c r="B545">
+        <v>287.787</v>
+      </c>
+      <c r="C545">
+        <v>0</v>
+      </c>
+      <c r="D545">
+        <v>64</v>
+      </c>
+      <c r="E545" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5">
+      <c r="A546" s="2">
+        <v>46111.70833333334</v>
+      </c>
+      <c r="B546">
+        <v>183.451</v>
+      </c>
+      <c r="C546">
+        <v>0</v>
+      </c>
+      <c r="D546">
+        <v>65</v>
+      </c>
+      <c r="E546" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5">
+      <c r="A547" s="2">
+        <v>46111.71875</v>
+      </c>
+      <c r="B547">
+        <v>149.31</v>
+      </c>
+      <c r="C547">
+        <v>0</v>
+      </c>
+      <c r="D547">
+        <v>66</v>
+      </c>
+      <c r="E547" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5">
+      <c r="A548" s="2">
+        <v>46111.72916666666</v>
+      </c>
+      <c r="B548">
+        <v>116.269</v>
+      </c>
+      <c r="C548">
+        <v>0</v>
+      </c>
+      <c r="D548">
+        <v>67</v>
+      </c>
+      <c r="E548" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5">
+      <c r="A549" s="2">
+        <v>46111.73958333334</v>
+      </c>
+      <c r="B549">
+        <v>87.762</v>
+      </c>
+      <c r="C549">
+        <v>0</v>
+      </c>
+      <c r="D549">
+        <v>68</v>
+      </c>
+      <c r="E549" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5">
+      <c r="A550" s="2">
+        <v>46111.75</v>
+      </c>
+      <c r="B550">
+        <v>48.822</v>
+      </c>
+      <c r="C550">
+        <v>0</v>
+      </c>
+      <c r="D550">
+        <v>69</v>
+      </c>
+      <c r="E550" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5">
+      <c r="A551" s="2">
+        <v>46111.76041666666</v>
+      </c>
+      <c r="B551">
+        <v>33.14</v>
+      </c>
+      <c r="C551">
+        <v>0</v>
+      </c>
+      <c r="D551">
+        <v>70</v>
+      </c>
+      <c r="E551" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5">
+      <c r="A552" s="2">
+        <v>46111.77083333334</v>
+      </c>
+      <c r="B552">
+        <v>22.528</v>
+      </c>
+      <c r="C552">
+        <v>0</v>
+      </c>
+      <c r="D552">
+        <v>71</v>
+      </c>
+      <c r="E552" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5">
+      <c r="A553" s="2">
+        <v>46111.78125</v>
+      </c>
+      <c r="B553">
+        <v>15.797</v>
+      </c>
+      <c r="C553">
+        <v>0</v>
+      </c>
+      <c r="D553">
+        <v>72</v>
+      </c>
+      <c r="E553" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5">
+      <c r="A554" s="2">
+        <v>46111.79166666666</v>
+      </c>
+      <c r="B554">
+        <v>9.641999999999999</v>
+      </c>
+      <c r="C554">
+        <v>0</v>
+      </c>
+      <c r="D554">
+        <v>73</v>
+      </c>
+      <c r="E554" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5">
+      <c r="A555" s="2">
+        <v>46111.80208333334</v>
+      </c>
+      <c r="B555">
+        <v>8.109</v>
+      </c>
+      <c r="C555">
+        <v>0</v>
+      </c>
+      <c r="D555">
+        <v>74</v>
+      </c>
+      <c r="E555" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5">
+      <c r="A556" s="2">
+        <v>46111.8125</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+      <c r="C556">
+        <v>0</v>
+      </c>
+      <c r="D556">
+        <v>75</v>
+      </c>
+      <c r="E556" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5">
+      <c r="A557" s="2">
+        <v>46111.82291666666</v>
+      </c>
+      <c r="B557">
+        <v>7.23</v>
+      </c>
+      <c r="C557">
+        <v>0</v>
+      </c>
+      <c r="D557">
+        <v>76</v>
+      </c>
+      <c r="E557" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5">
+      <c r="A558" s="2">
+        <v>46111.83333333334</v>
+      </c>
+      <c r="B558">
+        <v>6.63</v>
+      </c>
+      <c r="C558">
+        <v>0</v>
+      </c>
+      <c r="D558">
+        <v>77</v>
+      </c>
+      <c r="E558" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5">
+      <c r="A559" s="2">
+        <v>46111.84375</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+      <c r="C559">
+        <v>0</v>
+      </c>
+      <c r="D559">
+        <v>78</v>
+      </c>
+      <c r="E559" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5">
+      <c r="A560" s="2">
+        <v>46111.85416666666</v>
+      </c>
+      <c r="B560">
+        <v>0</v>
+      </c>
+      <c r="C560">
+        <v>0</v>
+      </c>
+      <c r="D560">
+        <v>79</v>
+      </c>
+      <c r="E560" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5">
+      <c r="A561" s="2">
+        <v>46111.86458333334</v>
+      </c>
+      <c r="B561">
+        <v>3.83</v>
+      </c>
+      <c r="C561">
+        <v>0</v>
+      </c>
+      <c r="D561">
+        <v>80</v>
+      </c>
+      <c r="E561" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5">
+      <c r="A562" s="2">
+        <v>46111.875</v>
+      </c>
+      <c r="B562">
+        <v>2.63</v>
+      </c>
+      <c r="C562">
+        <v>0</v>
+      </c>
+      <c r="D562">
+        <v>81</v>
+      </c>
+      <c r="E562" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5">
+      <c r="A563" s="2">
+        <v>46111.88541666666</v>
+      </c>
+      <c r="B563">
+        <v>0</v>
+      </c>
+      <c r="C563">
+        <v>0</v>
+      </c>
+      <c r="D563">
+        <v>82</v>
+      </c>
+      <c r="E563" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5">
+      <c r="A564" s="2">
+        <v>46111.89583333334</v>
+      </c>
+      <c r="B564">
+        <v>0</v>
+      </c>
+      <c r="C564">
+        <v>0</v>
+      </c>
+      <c r="D564">
+        <v>83</v>
+      </c>
+      <c r="E564" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5">
+      <c r="A565" s="2">
+        <v>46111.90625</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+      <c r="C565">
+        <v>0</v>
+      </c>
+      <c r="D565">
+        <v>84</v>
+      </c>
+      <c r="E565" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5">
+      <c r="A566" s="2">
+        <v>46111.91666666666</v>
+      </c>
+      <c r="B566">
+        <v>0</v>
+      </c>
+      <c r="C566">
+        <v>0</v>
+      </c>
+      <c r="D566">
+        <v>85</v>
+      </c>
+      <c r="E566" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5">
+      <c r="A567" s="2">
+        <v>46111.92708333334</v>
+      </c>
+      <c r="B567">
+        <v>0.63</v>
+      </c>
+      <c r="C567">
+        <v>0</v>
+      </c>
+      <c r="D567">
+        <v>86</v>
+      </c>
+      <c r="E567" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5">
+      <c r="A568" s="2">
+        <v>46111.9375</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+      <c r="C568">
+        <v>0</v>
+      </c>
+      <c r="D568">
+        <v>87</v>
+      </c>
+      <c r="E568" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5">
+      <c r="A569" s="2">
+        <v>46111.94791666666</v>
+      </c>
+      <c r="B569">
+        <v>0</v>
+      </c>
+      <c r="C569">
+        <v>0</v>
+      </c>
+      <c r="D569">
+        <v>88</v>
+      </c>
+      <c r="E569" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5">
+      <c r="A570" s="2">
+        <v>46111.95833333334</v>
+      </c>
+      <c r="B570">
+        <v>0</v>
+      </c>
+      <c r="C570">
+        <v>0</v>
+      </c>
+      <c r="D570">
+        <v>89</v>
+      </c>
+      <c r="E570" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5">
+      <c r="A571" s="2">
+        <v>46111.96875</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+      <c r="C571">
+        <v>0</v>
+      </c>
+      <c r="D571">
+        <v>90</v>
+      </c>
+      <c r="E571" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5">
+      <c r="A572" s="2">
+        <v>46111.97916666666</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+      <c r="C572">
+        <v>0</v>
+      </c>
+      <c r="D572">
+        <v>91</v>
+      </c>
+      <c r="E572" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5">
+      <c r="A573" s="2">
+        <v>46111.98958333334</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+      <c r="C573">
+        <v>0</v>
+      </c>
+      <c r="D573">
+        <v>92</v>
+      </c>
+      <c r="E573" t="s">
+        <v>576</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.04.20261</t>
-  </si>
-  <si>
-    <t>09.04.20262</t>
-  </si>
-  <si>
-    <t>09.04.20263</t>
-  </si>
-  <si>
-    <t>09.04.20264</t>
-  </si>
-  <si>
-    <t>09.04.20265</t>
-  </si>
-  <si>
-    <t>09.04.20266</t>
-  </si>
-  <si>
-    <t>09.04.20267</t>
-  </si>
-  <si>
-    <t>09.04.20268</t>
-  </si>
-  <si>
-    <t>09.04.20269</t>
-  </si>
-  <si>
-    <t>09.04.202610</t>
-  </si>
-  <si>
-    <t>09.04.202611</t>
-  </si>
-  <si>
-    <t>09.04.202612</t>
-  </si>
-  <si>
-    <t>09.04.202613</t>
-  </si>
-  <si>
-    <t>09.04.202614</t>
-  </si>
-  <si>
-    <t>09.04.202615</t>
-  </si>
-  <si>
-    <t>09.04.202616</t>
-  </si>
-  <si>
-    <t>09.04.202617</t>
-  </si>
-  <si>
-    <t>09.04.202618</t>
-  </si>
-  <si>
-    <t>09.04.202619</t>
-  </si>
-  <si>
-    <t>09.04.202620</t>
-  </si>
-  <si>
-    <t>09.04.202621</t>
-  </si>
-  <si>
-    <t>09.04.202622</t>
-  </si>
-  <si>
-    <t>09.04.202623</t>
-  </si>
-  <si>
-    <t>09.04.202624</t>
-  </si>
-  <si>
-    <t>09.04.202625</t>
-  </si>
-  <si>
-    <t>09.04.202626</t>
-  </si>
-  <si>
-    <t>09.04.202627</t>
-  </si>
-  <si>
-    <t>09.04.202628</t>
-  </si>
-  <si>
-    <t>09.04.202629</t>
-  </si>
-  <si>
-    <t>09.04.202630</t>
-  </si>
-  <si>
-    <t>09.04.202631</t>
-  </si>
-  <si>
-    <t>09.04.202632</t>
-  </si>
-  <si>
-    <t>09.04.202633</t>
-  </si>
-  <si>
-    <t>09.04.202634</t>
-  </si>
-  <si>
-    <t>09.04.202635</t>
-  </si>
-  <si>
-    <t>09.04.202636</t>
-  </si>
-  <si>
-    <t>09.04.202637</t>
-  </si>
-  <si>
-    <t>09.04.202638</t>
-  </si>
-  <si>
-    <t>09.04.202639</t>
-  </si>
-  <si>
-    <t>09.04.202640</t>
-  </si>
-  <si>
-    <t>09.04.202641</t>
-  </si>
-  <si>
-    <t>09.04.202642</t>
-  </si>
-  <si>
-    <t>09.04.202643</t>
-  </si>
-  <si>
-    <t>09.04.202644</t>
-  </si>
-  <si>
-    <t>09.04.202645</t>
-  </si>
-  <si>
-    <t>09.04.202646</t>
-  </si>
-  <si>
-    <t>09.04.202647</t>
-  </si>
-  <si>
-    <t>09.04.202648</t>
-  </si>
-  <si>
-    <t>09.04.202649</t>
-  </si>
-  <si>
-    <t>09.04.202650</t>
-  </si>
-  <si>
-    <t>09.04.202651</t>
-  </si>
-  <si>
-    <t>09.04.202652</t>
-  </si>
-  <si>
-    <t>09.04.202653</t>
-  </si>
-  <si>
-    <t>09.04.202654</t>
-  </si>
-  <si>
-    <t>09.04.202655</t>
-  </si>
-  <si>
-    <t>09.04.202656</t>
-  </si>
-  <si>
-    <t>09.04.202657</t>
-  </si>
-  <si>
-    <t>09.04.202658</t>
-  </si>
-  <si>
-    <t>09.04.202659</t>
-  </si>
-  <si>
-    <t>09.04.202660</t>
-  </si>
-  <si>
-    <t>09.04.202661</t>
-  </si>
-  <si>
-    <t>09.04.202662</t>
-  </si>
-  <si>
-    <t>09.04.202663</t>
-  </si>
-  <si>
-    <t>09.04.202664</t>
-  </si>
-  <si>
-    <t>09.04.202665</t>
-  </si>
-  <si>
-    <t>09.04.202666</t>
-  </si>
-  <si>
-    <t>09.04.202667</t>
-  </si>
-  <si>
-    <t>09.04.202668</t>
-  </si>
-  <si>
-    <t>09.04.202669</t>
-  </si>
-  <si>
-    <t>09.04.202670</t>
-  </si>
-  <si>
-    <t>09.04.202671</t>
-  </si>
-  <si>
-    <t>09.04.202672</t>
-  </si>
-  <si>
-    <t>09.04.202673</t>
-  </si>
-  <si>
-    <t>09.04.202674</t>
-  </si>
-  <si>
-    <t>09.04.202675</t>
-  </si>
-  <si>
-    <t>09.04.202676</t>
-  </si>
-  <si>
-    <t>09.04.202677</t>
-  </si>
-  <si>
-    <t>09.04.202678</t>
-  </si>
-  <si>
-    <t>09.04.202679</t>
-  </si>
-  <si>
-    <t>09.04.202680</t>
-  </si>
-  <si>
-    <t>09.04.202681</t>
-  </si>
-  <si>
-    <t>09.04.202682</t>
-  </si>
-  <si>
-    <t>09.04.202683</t>
-  </si>
-  <si>
-    <t>09.04.202684</t>
-  </si>
-  <si>
-    <t>09.04.202685</t>
-  </si>
-  <si>
-    <t>09.04.202686</t>
-  </si>
-  <si>
-    <t>09.04.202687</t>
-  </si>
-  <si>
-    <t>09.04.202688</t>
-  </si>
-  <si>
-    <t>09.04.202689</t>
-  </si>
-  <si>
-    <t>09.04.202690</t>
-  </si>
-  <si>
-    <t>09.04.202691</t>
-  </si>
-  <si>
-    <t>09.04.202692</t>
-  </si>
-  <si>
-    <t>09.04.202693</t>
-  </si>
-  <si>
-    <t>09.04.202694</t>
-  </si>
-  <si>
-    <t>09.04.202695</t>
-  </si>
-  <si>
-    <t>09.04.202696</t>
-  </si>
-  <si>
-    <t>10.04.20261</t>
-  </si>
-  <si>
-    <t>10.04.20262</t>
-  </si>
-  <si>
-    <t>10.04.20263</t>
-  </si>
-  <si>
-    <t>10.04.20264</t>
-  </si>
-  <si>
-    <t>10.04.20265</t>
-  </si>
-  <si>
-    <t>10.04.20266</t>
-  </si>
-  <si>
-    <t>10.04.20267</t>
-  </si>
-  <si>
-    <t>10.04.20268</t>
-  </si>
-  <si>
-    <t>10.04.20269</t>
-  </si>
-  <si>
-    <t>10.04.202610</t>
-  </si>
-  <si>
-    <t>10.04.202611</t>
-  </si>
-  <si>
-    <t>10.04.202612</t>
-  </si>
-  <si>
-    <t>10.04.202613</t>
-  </si>
-  <si>
-    <t>10.04.202614</t>
-  </si>
-  <si>
-    <t>10.04.202615</t>
-  </si>
-  <si>
-    <t>10.04.202616</t>
-  </si>
-  <si>
-    <t>10.04.202617</t>
-  </si>
-  <si>
-    <t>10.04.202618</t>
-  </si>
-  <si>
-    <t>10.04.202619</t>
-  </si>
-  <si>
-    <t>10.04.202620</t>
-  </si>
-  <si>
-    <t>10.04.202621</t>
-  </si>
-  <si>
-    <t>10.04.202622</t>
-  </si>
-  <si>
-    <t>10.04.202623</t>
-  </si>
-  <si>
-    <t>10.04.202624</t>
-  </si>
-  <si>
-    <t>10.04.202625</t>
-  </si>
-  <si>
-    <t>10.04.202626</t>
-  </si>
-  <si>
-    <t>10.04.202627</t>
-  </si>
-  <si>
-    <t>10.04.202628</t>
-  </si>
-  <si>
-    <t>10.04.202629</t>
-  </si>
-  <si>
-    <t>10.04.202630</t>
-  </si>
-  <si>
-    <t>10.04.202631</t>
-  </si>
-  <si>
-    <t>10.04.202632</t>
-  </si>
-  <si>
-    <t>10.04.202633</t>
-  </si>
-  <si>
-    <t>10.04.202634</t>
-  </si>
-  <si>
-    <t>10.04.202635</t>
-  </si>
-  <si>
-    <t>10.04.202636</t>
-  </si>
-  <si>
-    <t>10.04.202637</t>
-  </si>
-  <si>
-    <t>10.04.202638</t>
-  </si>
-  <si>
-    <t>10.04.202639</t>
-  </si>
-  <si>
-    <t>10.04.202640</t>
-  </si>
-  <si>
-    <t>10.04.202641</t>
-  </si>
-  <si>
-    <t>10.04.202642</t>
-  </si>
-  <si>
-    <t>10.04.202643</t>
-  </si>
-  <si>
-    <t>10.04.202644</t>
-  </si>
-  <si>
-    <t>10.04.202645</t>
-  </si>
-  <si>
-    <t>10.04.202646</t>
-  </si>
-  <si>
-    <t>10.04.202647</t>
-  </si>
-  <si>
-    <t>10.04.202648</t>
-  </si>
-  <si>
-    <t>10.04.202649</t>
-  </si>
-  <si>
-    <t>10.04.202650</t>
-  </si>
-  <si>
-    <t>10.04.202651</t>
-  </si>
-  <si>
-    <t>10.04.202652</t>
-  </si>
-  <si>
-    <t>10.04.202653</t>
-  </si>
-  <si>
-    <t>10.04.202654</t>
-  </si>
-  <si>
-    <t>10.04.202655</t>
-  </si>
-  <si>
-    <t>10.04.202656</t>
-  </si>
-  <si>
-    <t>10.04.202657</t>
-  </si>
-  <si>
-    <t>10.04.202658</t>
-  </si>
-  <si>
-    <t>10.04.202659</t>
-  </si>
-  <si>
-    <t>10.04.202660</t>
-  </si>
-  <si>
-    <t>10.04.202661</t>
-  </si>
-  <si>
-    <t>10.04.202662</t>
-  </si>
-  <si>
-    <t>10.04.202663</t>
-  </si>
-  <si>
-    <t>10.04.202664</t>
-  </si>
-  <si>
-    <t>10.04.202665</t>
-  </si>
-  <si>
-    <t>10.04.202666</t>
-  </si>
-  <si>
-    <t>10.04.202667</t>
-  </si>
-  <si>
-    <t>10.04.202668</t>
-  </si>
-  <si>
-    <t>10.04.202669</t>
-  </si>
-  <si>
-    <t>10.04.202670</t>
-  </si>
-  <si>
-    <t>10.04.202671</t>
-  </si>
-  <si>
-    <t>10.04.202672</t>
-  </si>
-  <si>
-    <t>10.04.202673</t>
-  </si>
-  <si>
-    <t>10.04.202674</t>
-  </si>
-  <si>
-    <t>10.04.202675</t>
-  </si>
-  <si>
-    <t>10.04.202676</t>
-  </si>
-  <si>
-    <t>10.04.202677</t>
-  </si>
-  <si>
-    <t>10.04.202678</t>
-  </si>
-  <si>
-    <t>10.04.202679</t>
-  </si>
-  <si>
-    <t>10.04.202680</t>
-  </si>
-  <si>
-    <t>10.04.202681</t>
-  </si>
-  <si>
-    <t>10.04.202682</t>
-  </si>
-  <si>
-    <t>10.04.202683</t>
-  </si>
-  <si>
-    <t>10.04.202684</t>
-  </si>
-  <si>
-    <t>10.04.202685</t>
-  </si>
-  <si>
-    <t>10.04.202686</t>
-  </si>
-  <si>
-    <t>10.04.202687</t>
-  </si>
-  <si>
-    <t>10.04.202688</t>
-  </si>
-  <si>
-    <t>10.04.202689</t>
-  </si>
-  <si>
-    <t>10.04.202690</t>
-  </si>
-  <si>
-    <t>10.04.202691</t>
-  </si>
-  <si>
-    <t>10.04.202692</t>
-  </si>
-  <si>
-    <t>10.04.202693</t>
-  </si>
-  <si>
-    <t>10.04.202694</t>
-  </si>
-  <si>
-    <t>10.04.202695</t>
-  </si>
-  <si>
-    <t>10.04.202696</t>
+    <t>16.04.20261</t>
+  </si>
+  <si>
+    <t>16.04.20262</t>
+  </si>
+  <si>
+    <t>16.04.20263</t>
+  </si>
+  <si>
+    <t>16.04.20264</t>
+  </si>
+  <si>
+    <t>16.04.20265</t>
+  </si>
+  <si>
+    <t>16.04.20266</t>
+  </si>
+  <si>
+    <t>16.04.20267</t>
+  </si>
+  <si>
+    <t>16.04.20268</t>
+  </si>
+  <si>
+    <t>16.04.20269</t>
+  </si>
+  <si>
+    <t>16.04.202610</t>
+  </si>
+  <si>
+    <t>16.04.202611</t>
+  </si>
+  <si>
+    <t>16.04.202612</t>
+  </si>
+  <si>
+    <t>16.04.202613</t>
+  </si>
+  <si>
+    <t>16.04.202614</t>
+  </si>
+  <si>
+    <t>16.04.202615</t>
+  </si>
+  <si>
+    <t>16.04.202616</t>
+  </si>
+  <si>
+    <t>16.04.202617</t>
+  </si>
+  <si>
+    <t>16.04.202618</t>
+  </si>
+  <si>
+    <t>16.04.202619</t>
+  </si>
+  <si>
+    <t>16.04.202620</t>
+  </si>
+  <si>
+    <t>16.04.202621</t>
+  </si>
+  <si>
+    <t>16.04.202622</t>
+  </si>
+  <si>
+    <t>16.04.202623</t>
+  </si>
+  <si>
+    <t>16.04.202624</t>
+  </si>
+  <si>
+    <t>16.04.202625</t>
+  </si>
+  <si>
+    <t>16.04.202626</t>
+  </si>
+  <si>
+    <t>16.04.202627</t>
+  </si>
+  <si>
+    <t>16.04.202628</t>
+  </si>
+  <si>
+    <t>16.04.202629</t>
+  </si>
+  <si>
+    <t>16.04.202630</t>
+  </si>
+  <si>
+    <t>16.04.202631</t>
+  </si>
+  <si>
+    <t>16.04.202632</t>
+  </si>
+  <si>
+    <t>16.04.202633</t>
+  </si>
+  <si>
+    <t>16.04.202634</t>
+  </si>
+  <si>
+    <t>16.04.202635</t>
+  </si>
+  <si>
+    <t>16.04.202636</t>
+  </si>
+  <si>
+    <t>16.04.202637</t>
+  </si>
+  <si>
+    <t>16.04.202638</t>
+  </si>
+  <si>
+    <t>16.04.202639</t>
+  </si>
+  <si>
+    <t>16.04.202640</t>
+  </si>
+  <si>
+    <t>16.04.202641</t>
+  </si>
+  <si>
+    <t>16.04.202642</t>
+  </si>
+  <si>
+    <t>16.04.202643</t>
+  </si>
+  <si>
+    <t>16.04.202644</t>
+  </si>
+  <si>
+    <t>16.04.202645</t>
+  </si>
+  <si>
+    <t>16.04.202646</t>
+  </si>
+  <si>
+    <t>16.04.202647</t>
+  </si>
+  <si>
+    <t>16.04.202648</t>
+  </si>
+  <si>
+    <t>16.04.202649</t>
+  </si>
+  <si>
+    <t>16.04.202650</t>
+  </si>
+  <si>
+    <t>16.04.202651</t>
+  </si>
+  <si>
+    <t>16.04.202652</t>
+  </si>
+  <si>
+    <t>16.04.202653</t>
+  </si>
+  <si>
+    <t>16.04.202654</t>
+  </si>
+  <si>
+    <t>16.04.202655</t>
+  </si>
+  <si>
+    <t>16.04.202656</t>
+  </si>
+  <si>
+    <t>16.04.202657</t>
+  </si>
+  <si>
+    <t>16.04.202658</t>
+  </si>
+  <si>
+    <t>16.04.202659</t>
+  </si>
+  <si>
+    <t>16.04.202660</t>
+  </si>
+  <si>
+    <t>16.04.202661</t>
+  </si>
+  <si>
+    <t>16.04.202662</t>
+  </si>
+  <si>
+    <t>16.04.202663</t>
+  </si>
+  <si>
+    <t>16.04.202664</t>
+  </si>
+  <si>
+    <t>16.04.202665</t>
+  </si>
+  <si>
+    <t>16.04.202666</t>
+  </si>
+  <si>
+    <t>16.04.202667</t>
+  </si>
+  <si>
+    <t>16.04.202668</t>
+  </si>
+  <si>
+    <t>16.04.202669</t>
+  </si>
+  <si>
+    <t>16.04.202670</t>
+  </si>
+  <si>
+    <t>16.04.202671</t>
+  </si>
+  <si>
+    <t>16.04.202672</t>
+  </si>
+  <si>
+    <t>16.04.202673</t>
+  </si>
+  <si>
+    <t>16.04.202674</t>
+  </si>
+  <si>
+    <t>16.04.202675</t>
+  </si>
+  <si>
+    <t>16.04.202676</t>
+  </si>
+  <si>
+    <t>16.04.202677</t>
+  </si>
+  <si>
+    <t>16.04.202678</t>
+  </si>
+  <si>
+    <t>16.04.202679</t>
+  </si>
+  <si>
+    <t>16.04.202680</t>
+  </si>
+  <si>
+    <t>16.04.202681</t>
+  </si>
+  <si>
+    <t>16.04.202682</t>
+  </si>
+  <si>
+    <t>16.04.202683</t>
+  </si>
+  <si>
+    <t>16.04.202684</t>
+  </si>
+  <si>
+    <t>16.04.202685</t>
+  </si>
+  <si>
+    <t>16.04.202686</t>
+  </si>
+  <si>
+    <t>16.04.202687</t>
+  </si>
+  <si>
+    <t>16.04.202688</t>
+  </si>
+  <si>
+    <t>16.04.202689</t>
+  </si>
+  <si>
+    <t>16.04.202690</t>
+  </si>
+  <si>
+    <t>16.04.202691</t>
+  </si>
+  <si>
+    <t>16.04.202692</t>
+  </si>
+  <si>
+    <t>16.04.202693</t>
+  </si>
+  <si>
+    <t>16.04.202694</t>
+  </si>
+  <si>
+    <t>16.04.202695</t>
+  </si>
+  <si>
+    <t>16.04.202696</t>
+  </si>
+  <si>
+    <t>17.04.20261</t>
+  </si>
+  <si>
+    <t>17.04.20262</t>
+  </si>
+  <si>
+    <t>17.04.20263</t>
+  </si>
+  <si>
+    <t>17.04.20264</t>
+  </si>
+  <si>
+    <t>17.04.20265</t>
+  </si>
+  <si>
+    <t>17.04.20266</t>
+  </si>
+  <si>
+    <t>17.04.20267</t>
+  </si>
+  <si>
+    <t>17.04.20268</t>
+  </si>
+  <si>
+    <t>17.04.20269</t>
+  </si>
+  <si>
+    <t>17.04.202610</t>
+  </si>
+  <si>
+    <t>17.04.202611</t>
+  </si>
+  <si>
+    <t>17.04.202612</t>
+  </si>
+  <si>
+    <t>17.04.202613</t>
+  </si>
+  <si>
+    <t>17.04.202614</t>
+  </si>
+  <si>
+    <t>17.04.202615</t>
+  </si>
+  <si>
+    <t>17.04.202616</t>
+  </si>
+  <si>
+    <t>17.04.202617</t>
+  </si>
+  <si>
+    <t>17.04.202618</t>
+  </si>
+  <si>
+    <t>17.04.202619</t>
+  </si>
+  <si>
+    <t>17.04.202620</t>
+  </si>
+  <si>
+    <t>17.04.202621</t>
+  </si>
+  <si>
+    <t>17.04.202622</t>
+  </si>
+  <si>
+    <t>17.04.202623</t>
+  </si>
+  <si>
+    <t>17.04.202624</t>
+  </si>
+  <si>
+    <t>17.04.202625</t>
+  </si>
+  <si>
+    <t>17.04.202626</t>
+  </si>
+  <si>
+    <t>17.04.202627</t>
+  </si>
+  <si>
+    <t>17.04.202628</t>
+  </si>
+  <si>
+    <t>17.04.202629</t>
+  </si>
+  <si>
+    <t>17.04.202630</t>
+  </si>
+  <si>
+    <t>17.04.202631</t>
+  </si>
+  <si>
+    <t>17.04.202632</t>
+  </si>
+  <si>
+    <t>17.04.202633</t>
+  </si>
+  <si>
+    <t>17.04.202634</t>
+  </si>
+  <si>
+    <t>17.04.202635</t>
+  </si>
+  <si>
+    <t>17.04.202636</t>
+  </si>
+  <si>
+    <t>17.04.202637</t>
+  </si>
+  <si>
+    <t>17.04.202638</t>
+  </si>
+  <si>
+    <t>17.04.202639</t>
+  </si>
+  <si>
+    <t>17.04.202640</t>
+  </si>
+  <si>
+    <t>17.04.202641</t>
+  </si>
+  <si>
+    <t>17.04.202642</t>
+  </si>
+  <si>
+    <t>17.04.202643</t>
+  </si>
+  <si>
+    <t>17.04.202644</t>
+  </si>
+  <si>
+    <t>17.04.202645</t>
+  </si>
+  <si>
+    <t>17.04.202646</t>
+  </si>
+  <si>
+    <t>17.04.202647</t>
+  </si>
+  <si>
+    <t>17.04.202648</t>
+  </si>
+  <si>
+    <t>17.04.202649</t>
+  </si>
+  <si>
+    <t>17.04.202650</t>
+  </si>
+  <si>
+    <t>17.04.202651</t>
+  </si>
+  <si>
+    <t>17.04.202652</t>
+  </si>
+  <si>
+    <t>17.04.202653</t>
+  </si>
+  <si>
+    <t>17.04.202654</t>
+  </si>
+  <si>
+    <t>17.04.202655</t>
+  </si>
+  <si>
+    <t>17.04.202656</t>
+  </si>
+  <si>
+    <t>17.04.202657</t>
+  </si>
+  <si>
+    <t>17.04.202658</t>
+  </si>
+  <si>
+    <t>17.04.202659</t>
+  </si>
+  <si>
+    <t>17.04.202660</t>
+  </si>
+  <si>
+    <t>17.04.202661</t>
+  </si>
+  <si>
+    <t>17.04.202662</t>
+  </si>
+  <si>
+    <t>17.04.202663</t>
+  </si>
+  <si>
+    <t>17.04.202664</t>
+  </si>
+  <si>
+    <t>17.04.202665</t>
+  </si>
+  <si>
+    <t>17.04.202666</t>
+  </si>
+  <si>
+    <t>17.04.202667</t>
+  </si>
+  <si>
+    <t>17.04.202668</t>
+  </si>
+  <si>
+    <t>17.04.202669</t>
+  </si>
+  <si>
+    <t>17.04.202670</t>
+  </si>
+  <si>
+    <t>17.04.202671</t>
+  </si>
+  <si>
+    <t>17.04.202672</t>
+  </si>
+  <si>
+    <t>17.04.202673</t>
+  </si>
+  <si>
+    <t>17.04.202674</t>
+  </si>
+  <si>
+    <t>17.04.202675</t>
+  </si>
+  <si>
+    <t>17.04.202676</t>
+  </si>
+  <si>
+    <t>17.04.202677</t>
+  </si>
+  <si>
+    <t>17.04.202678</t>
+  </si>
+  <si>
+    <t>17.04.202679</t>
+  </si>
+  <si>
+    <t>17.04.202680</t>
+  </si>
+  <si>
+    <t>17.04.202681</t>
+  </si>
+  <si>
+    <t>17.04.202682</t>
+  </si>
+  <si>
+    <t>17.04.202683</t>
+  </si>
+  <si>
+    <t>17.04.202684</t>
+  </si>
+  <si>
+    <t>17.04.202685</t>
+  </si>
+  <si>
+    <t>17.04.202686</t>
+  </si>
+  <si>
+    <t>17.04.202687</t>
+  </si>
+  <si>
+    <t>17.04.202688</t>
+  </si>
+  <si>
+    <t>17.04.202689</t>
+  </si>
+  <si>
+    <t>17.04.202690</t>
+  </si>
+  <si>
+    <t>17.04.202691</t>
+  </si>
+  <si>
+    <t>17.04.202692</t>
+  </si>
+  <si>
+    <t>17.04.202693</t>
+  </si>
+  <si>
+    <t>17.04.202694</t>
+  </si>
+  <si>
+    <t>17.04.202695</t>
+  </si>
+  <si>
+    <t>17.04.202696</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46121.01041666666</v>
+        <v>46128.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46121.02083333334</v>
+        <v>46128.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46121.03125</v>
+        <v>46128.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46121.04166666666</v>
+        <v>46128.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46121.05208333334</v>
+        <v>46128.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46121.0625</v>
+        <v>46128.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46121.07291666666</v>
+        <v>46128.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46121.08333333334</v>
+        <v>46128.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46121.09375</v>
+        <v>46128.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46121.10416666666</v>
+        <v>46128.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46121.11458333334</v>
+        <v>46128.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46121.125</v>
+        <v>46128.125</v>
       </c>
       <c r="B14">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46121.13541666666</v>
+        <v>46128.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46121.14583333334</v>
+        <v>46128.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46121.15625</v>
+        <v>46128.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46121.16666666666</v>
+        <v>46128.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.75</v>
+        <v>1.231</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46121.17708333334</v>
+        <v>46128.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46121.1875</v>
+        <v>46128.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46121.19791666666</v>
+        <v>46128.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1.235</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46121.20833333334</v>
+        <v>46128.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.005</v>
+        <v>2.386</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46121.21875</v>
+        <v>46128.21875</v>
       </c>
       <c r="B23">
-        <v>2.175</v>
+        <v>2.716</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46121.22916666666</v>
+        <v>46128.22916666666</v>
       </c>
       <c r="B24">
-        <v>2.597</v>
+        <v>4.495</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46121.23958333334</v>
+        <v>46128.23958333334</v>
       </c>
       <c r="B25">
-        <v>16.263</v>
+        <v>25.685</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46121.25</v>
+        <v>46128.25</v>
       </c>
       <c r="B26">
-        <v>68.77500000000001</v>
+        <v>119.682</v>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46121.26041666666</v>
+        <v>46128.26041666666</v>
       </c>
       <c r="B27">
-        <v>111.734</v>
+        <v>190.757</v>
       </c>
       <c r="C27">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46121.27083333334</v>
+        <v>46128.27083333334</v>
       </c>
       <c r="B28">
-        <v>181.027</v>
+        <v>276.02</v>
       </c>
       <c r="C28">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46121.28125</v>
+        <v>46128.28125</v>
       </c>
       <c r="B29">
-        <v>276.391</v>
+        <v>389.506</v>
       </c>
       <c r="C29">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46121.29166666666</v>
+        <v>46128.29166666666</v>
       </c>
       <c r="B30">
-        <v>472.607</v>
+        <v>628.177</v>
       </c>
       <c r="C30">
-        <v>293</v>
+        <v>439</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46121.30208333334</v>
+        <v>46128.30208333334</v>
       </c>
       <c r="B31">
-        <v>628.021</v>
+        <v>801.15</v>
       </c>
       <c r="C31">
-        <v>410</v>
+        <v>559</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46121.3125</v>
+        <v>46128.3125</v>
       </c>
       <c r="B32">
-        <v>799.309</v>
+        <v>1002.586</v>
       </c>
       <c r="C32">
-        <v>581</v>
+        <v>717</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46121.32291666666</v>
+        <v>46128.32291666666</v>
       </c>
       <c r="B33">
-        <v>978.14</v>
+        <v>1237.311</v>
       </c>
       <c r="C33">
-        <v>722</v>
+        <v>896</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46121.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="B34">
-        <v>1224.246</v>
+        <v>1546.126</v>
       </c>
       <c r="C34">
-        <v>860</v>
+        <v>1061</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46121.34375</v>
+        <v>46128.34375</v>
       </c>
       <c r="B35">
-        <v>1406.779</v>
+        <v>1731.142</v>
       </c>
       <c r="C35">
-        <v>1010</v>
+        <v>1247</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46121.35416666666</v>
+        <v>46128.35416666666</v>
       </c>
       <c r="B36">
-        <v>1585.219</v>
+        <v>1927.558</v>
       </c>
       <c r="C36">
-        <v>1151</v>
+        <v>1417</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46121.36458333334</v>
+        <v>46128.36458333334</v>
       </c>
       <c r="B37">
-        <v>1741.858</v>
+        <v>2110.304</v>
       </c>
       <c r="C37">
-        <v>1228</v>
+        <v>1543</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46121.375</v>
+        <v>46128.375</v>
       </c>
       <c r="B38">
-        <v>1879.569</v>
+        <v>2309.127</v>
       </c>
       <c r="C38">
-        <v>1374</v>
+        <v>1648</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46121.38541666666</v>
+        <v>46128.38541666666</v>
       </c>
       <c r="B39">
-        <v>1994.883</v>
+        <v>2434.985</v>
       </c>
       <c r="C39">
-        <v>1442</v>
+        <v>1764</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46121.39583333334</v>
+        <v>46128.39583333334</v>
       </c>
       <c r="B40">
-        <v>2072.353</v>
+        <v>2558.44</v>
       </c>
       <c r="C40">
-        <v>1525</v>
+        <v>1879</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46121.40625</v>
+        <v>46128.40625</v>
       </c>
       <c r="B41">
-        <v>2130.02</v>
+        <v>2658.646</v>
       </c>
       <c r="C41">
-        <v>1585</v>
+        <v>1947</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46121.41666666666</v>
+        <v>46128.41666666666</v>
       </c>
       <c r="B42">
-        <v>2207.042</v>
+        <v>2790.027</v>
       </c>
       <c r="C42">
-        <v>1567</v>
+        <v>1932</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46121.42708333334</v>
+        <v>46128.42708333334</v>
       </c>
       <c r="B43">
-        <v>2251.994</v>
+        <v>2864.062</v>
       </c>
       <c r="C43">
-        <v>1601</v>
+        <v>2074</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46121.4375</v>
+        <v>46128.4375</v>
       </c>
       <c r="B44">
-        <v>2287.753</v>
+        <v>2943.131</v>
       </c>
       <c r="C44">
-        <v>1621</v>
+        <v>2138</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46121.44791666666</v>
+        <v>46128.44791666666</v>
       </c>
       <c r="B45">
-        <v>2279.381</v>
+        <v>2991.569</v>
       </c>
       <c r="C45">
-        <v>1653</v>
+        <v>2062</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46121.45833333334</v>
+        <v>46128.45833333334</v>
       </c>
       <c r="B46">
-        <v>2273.525</v>
+        <v>3028.078</v>
       </c>
       <c r="C46">
-        <v>1544</v>
+        <v>2114</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46121.46875</v>
+        <v>46128.46875</v>
       </c>
       <c r="B47">
-        <v>2089.301</v>
+        <v>3045.385</v>
       </c>
       <c r="C47">
-        <v>1492</v>
+        <v>2151</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46121.47916666666</v>
+        <v>46128.47916666666</v>
       </c>
       <c r="B48">
-        <v>1957.306</v>
+        <v>3051.479</v>
       </c>
       <c r="C48">
-        <v>1331</v>
+        <v>2160</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46121.48958333334</v>
+        <v>46128.48958333334</v>
       </c>
       <c r="B49">
-        <v>1589.664</v>
+        <v>3060.759</v>
       </c>
       <c r="C49">
-        <v>1061</v>
+        <v>2166</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46121.5</v>
+        <v>46128.5</v>
       </c>
       <c r="B50">
-        <v>1515.873</v>
+        <v>3065.378</v>
       </c>
       <c r="C50">
-        <v>920</v>
+        <v>2124</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46121.51041666666</v>
+        <v>46128.51041666666</v>
       </c>
       <c r="B51">
-        <v>1496.578</v>
+        <v>3062.667</v>
       </c>
       <c r="C51">
-        <v>926</v>
+        <v>2197</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46121.52083333334</v>
+        <v>46128.52083333334</v>
       </c>
       <c r="B52">
-        <v>1440.193</v>
+        <v>3048.384</v>
       </c>
       <c r="C52">
-        <v>898</v>
+        <v>2291</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46121.53125</v>
+        <v>46128.53125</v>
       </c>
       <c r="B53">
-        <v>1400.486</v>
+        <v>3032.533</v>
       </c>
       <c r="C53">
-        <v>856</v>
+        <v>2304</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46121.54166666666</v>
+        <v>46128.54166666666</v>
       </c>
       <c r="B54">
-        <v>1345.86</v>
+        <v>2999.467</v>
       </c>
       <c r="C54">
-        <v>875</v>
+        <v>2280</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46121.55208333334</v>
+        <v>46128.55208333334</v>
       </c>
       <c r="B55">
-        <v>1325.265</v>
+        <v>2968.77</v>
       </c>
       <c r="C55">
-        <v>890</v>
+        <v>2240</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46121.5625</v>
+        <v>46128.5625</v>
       </c>
       <c r="B56">
-        <v>1300.209</v>
+        <v>2920.586</v>
       </c>
       <c r="C56">
-        <v>884</v>
+        <v>2189</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46121.57291666666</v>
+        <v>46128.57291666666</v>
       </c>
       <c r="B57">
-        <v>1268.36</v>
+        <v>2869.781</v>
       </c>
       <c r="C57">
-        <v>874</v>
+        <v>2106</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46121.58333333334</v>
+        <v>46128.58333333334</v>
       </c>
       <c r="B58">
-        <v>1299.718</v>
+        <v>2795.06</v>
       </c>
       <c r="C58">
-        <v>768</v>
+        <v>2022</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46121.59375</v>
+        <v>46128.59375</v>
       </c>
       <c r="B59">
-        <v>1367.251</v>
+        <v>2728.474</v>
       </c>
       <c r="C59">
-        <v>933</v>
+        <v>1993</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46121.60416666666</v>
+        <v>46128.60416666666</v>
       </c>
       <c r="B60">
-        <v>1368.027</v>
+        <v>2634.481</v>
       </c>
       <c r="C60">
-        <v>867</v>
+        <v>1979</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46121.61458333334</v>
+        <v>46128.61458333334</v>
       </c>
       <c r="B61">
-        <v>1316.04</v>
+        <v>2546.356</v>
       </c>
       <c r="C61">
-        <v>771</v>
+        <v>1941</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46121.625</v>
+        <v>46128.625</v>
       </c>
       <c r="B62">
-        <v>1271.178</v>
+        <v>2331.08</v>
       </c>
       <c r="C62">
-        <v>729</v>
+        <v>1762</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46121.63541666666</v>
+        <v>46128.63541666666</v>
       </c>
       <c r="B63">
-        <v>1202.543</v>
+        <v>2227.496</v>
       </c>
       <c r="C63">
-        <v>722</v>
+        <v>1678</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46121.64583333334</v>
+        <v>46128.64583333334</v>
       </c>
       <c r="B64">
-        <v>1150.31</v>
+        <v>2099.106</v>
       </c>
       <c r="C64">
-        <v>728</v>
+        <v>1593</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46121.65625</v>
+        <v>46128.65625</v>
       </c>
       <c r="B65">
-        <v>1093.67</v>
+        <v>1958.309</v>
       </c>
       <c r="C65">
-        <v>717</v>
+        <v>1485</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46121.66666666666</v>
+        <v>46128.66666666666</v>
       </c>
       <c r="B66">
-        <v>981.673</v>
+        <v>1733.428</v>
       </c>
       <c r="C66">
-        <v>746</v>
+        <v>1389</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46121.67708333334</v>
+        <v>46128.67708333334</v>
       </c>
       <c r="B67">
-        <v>928.775</v>
+        <v>1594.739</v>
       </c>
       <c r="C67">
-        <v>601</v>
+        <v>1250</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46121.6875</v>
+        <v>46128.6875</v>
       </c>
       <c r="B68">
-        <v>818.729</v>
+        <v>1431.144</v>
       </c>
       <c r="C68">
-        <v>532</v>
+        <v>1112</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46121.69791666666</v>
+        <v>46128.69791666666</v>
       </c>
       <c r="B69">
-        <v>712.9690000000001</v>
+        <v>1237.674</v>
       </c>
       <c r="C69">
-        <v>518</v>
+        <v>954</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46121.70833333334</v>
+        <v>46128.70833333334</v>
       </c>
       <c r="B70">
-        <v>571.841</v>
+        <v>991.203</v>
       </c>
       <c r="C70">
-        <v>447</v>
+        <v>770</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46121.71875</v>
+        <v>46128.71875</v>
       </c>
       <c r="B71">
-        <v>466.314</v>
+        <v>823.246</v>
       </c>
       <c r="C71">
-        <v>363</v>
+        <v>627</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46121.72916666666</v>
+        <v>46128.72916666666</v>
       </c>
       <c r="B72">
-        <v>368.066</v>
+        <v>683.292</v>
       </c>
       <c r="C72">
-        <v>320</v>
+        <v>470</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46121.73958333334</v>
+        <v>46128.73958333334</v>
       </c>
       <c r="B73">
-        <v>284.73</v>
+        <v>517.386</v>
       </c>
       <c r="C73">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46121.75</v>
+        <v>46128.75</v>
       </c>
       <c r="B74">
-        <v>178.499</v>
+        <v>335.581</v>
       </c>
       <c r="C74">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46121.76041666666</v>
+        <v>46128.76041666666</v>
       </c>
       <c r="B75">
-        <v>123.761</v>
+        <v>261.524</v>
       </c>
       <c r="C75">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46121.77083333334</v>
+        <v>46128.77083333334</v>
       </c>
       <c r="B76">
-        <v>75.77500000000001</v>
+        <v>154.062</v>
       </c>
       <c r="C76">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46121.78125</v>
+        <v>46128.78125</v>
       </c>
       <c r="B77">
-        <v>47.243</v>
+        <v>67.40600000000001</v>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46121.79166666666</v>
+        <v>46128.79166666666</v>
       </c>
       <c r="B78">
-        <v>19.099</v>
+        <v>26.862</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46121.80208333334</v>
+        <v>46128.80208333334</v>
       </c>
       <c r="B79">
-        <v>17.945</v>
+        <v>21.877</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46121.8125</v>
+        <v>46128.8125</v>
       </c>
       <c r="B80">
-        <v>16.528</v>
+        <v>15.11</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46121.82291666666</v>
+        <v>46128.82291666666</v>
       </c>
       <c r="B81">
-        <v>14.898</v>
+        <v>13.916</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46121.83333333334</v>
+        <v>46128.83333333334</v>
       </c>
       <c r="B82">
-        <v>13.099</v>
+        <v>12.27</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46121.84375</v>
+        <v>46128.84375</v>
       </c>
       <c r="B83">
-        <v>12.871</v>
+        <v>9.997999999999999</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46121.85416666666</v>
+        <v>46128.85416666666</v>
       </c>
       <c r="B84">
-        <v>9.831</v>
+        <v>4.93</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46121.86458333334</v>
+        <v>46128.86458333334</v>
       </c>
       <c r="B85">
-        <v>8.234999999999999</v>
+        <v>1.342</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46121.875</v>
+        <v>46128.875</v>
       </c>
       <c r="B86">
-        <v>6.73</v>
+        <v>9.23</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46121.88541666666</v>
+        <v>46128.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46121.89583333334</v>
+        <v>46128.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>9.23</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46121.90625</v>
+        <v>46128.90625</v>
       </c>
       <c r="B89">
-        <v>4.73</v>
+        <v>5.23</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46121.91666666666</v>
+        <v>46128.91666666666</v>
       </c>
       <c r="B90">
-        <v>2.73</v>
+        <v>0.73</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46121.92708333334</v>
+        <v>46128.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46121.9375</v>
+        <v>46128.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46121.94791666666</v>
+        <v>46128.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46121.95833333334</v>
+        <v>46128.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46121.96875</v>
+        <v>46128.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46121.97916666666</v>
+        <v>46128.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46121.98958333334</v>
+        <v>46128.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46122.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46122.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46122.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46122.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46122.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46122.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46122.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46122.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46122.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46122.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46122.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46122.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46122.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46122.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46122.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46122.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46122.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46122.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46122.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B117">
-        <v>0.734</v>
+        <v>1.234</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46122.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B118">
-        <v>1.965</v>
+        <v>17.033</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46122.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B119">
-        <v>2.076</v>
+        <v>17.273</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46122.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B120">
-        <v>2.557</v>
+        <v>19.461</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46122.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B121">
-        <v>8.891999999999999</v>
+        <v>38.097</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46122.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B122">
-        <v>59.068</v>
+        <v>182.904</v>
       </c>
       <c r="C122">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46122.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B123">
-        <v>102.414</v>
+        <v>250.008</v>
       </c>
       <c r="C123">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46122.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B124">
-        <v>171.272</v>
+        <v>335.896</v>
       </c>
       <c r="C124">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46122.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B125">
-        <v>265.889</v>
+        <v>451.432</v>
       </c>
       <c r="C125">
-        <v>167</v>
+        <v>304</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46122.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B126">
-        <v>423.955</v>
+        <v>604.9059999999999</v>
       </c>
       <c r="C126">
-        <v>247</v>
+        <v>414</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46122.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B127">
-        <v>553.809</v>
+        <v>742.593</v>
       </c>
       <c r="C127">
-        <v>347</v>
+        <v>503</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46122.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B128">
-        <v>706.648</v>
+        <v>886.485</v>
       </c>
       <c r="C128">
-        <v>459</v>
+        <v>611</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46122.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B129">
-        <v>855.808</v>
+        <v>1070.784</v>
       </c>
       <c r="C129">
-        <v>603</v>
+        <v>733</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46122.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B130">
-        <v>1086.441</v>
+        <v>1296.813</v>
       </c>
       <c r="C130">
-        <v>777</v>
+        <v>876</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46122.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B131">
-        <v>1256.431</v>
+        <v>1445.005</v>
       </c>
       <c r="C131">
-        <v>873</v>
+        <v>994</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46122.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B132">
-        <v>1430.487</v>
+        <v>1581.171</v>
       </c>
       <c r="C132">
-        <v>1012</v>
+        <v>1132</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46122.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B133">
-        <v>1580.584</v>
+        <v>1752.782</v>
       </c>
       <c r="C133">
-        <v>1115</v>
+        <v>1253</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46122.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B134">
-        <v>1747.35</v>
+        <v>1883.887</v>
       </c>
       <c r="C134">
-        <v>1165</v>
+        <v>1334</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46122.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B135">
-        <v>1849.909</v>
+        <v>1989.607</v>
       </c>
       <c r="C135">
-        <v>1234</v>
+        <v>1412</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46122.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B136">
-        <v>1942.85</v>
+        <v>2112.248</v>
       </c>
       <c r="C136">
-        <v>1369</v>
+        <v>1458</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46122.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B137">
-        <v>2019.554</v>
+        <v>2210.066</v>
       </c>
       <c r="C137">
-        <v>1308</v>
+        <v>1518</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46122.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B138">
-        <v>2096.831</v>
+        <v>2321.558</v>
       </c>
       <c r="C138">
-        <v>1311</v>
+        <v>1644</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46122.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B139">
-        <v>2138.464</v>
+        <v>2391.725</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1669</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46122.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B140">
-        <v>2180.436</v>
+        <v>2459.007</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>1657</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3351,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46122.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B141">
-        <v>2230.067</v>
+        <v>2518.555</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46122.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B142">
-        <v>2234.095</v>
+        <v>2585.181</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1789</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3385,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46122.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B143">
-        <v>2236.732</v>
+        <v>2627.89</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1777</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3402,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46122.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B144">
-        <v>2243.452</v>
+        <v>2644.508</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1775</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3419,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46122.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B145">
-        <v>2247.801</v>
+        <v>2661.18</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1859</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46122.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B146">
-        <v>2212.911</v>
+        <v>2639.826</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46122.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B147">
-        <v>2204.962</v>
+        <v>2630.889</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46122.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B148">
-        <v>2195.357</v>
+        <v>2618.456</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46122.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B149">
-        <v>2183.338</v>
+        <v>2594.214</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46122.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B150">
-        <v>2104.919</v>
+        <v>2583.058</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46122.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B151">
-        <v>2091.748</v>
+        <v>2555.154</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46122.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B152">
-        <v>2069.631</v>
+        <v>2529.858</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46122.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B153">
-        <v>2056.802</v>
+        <v>2483.403</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46122.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B154">
-        <v>1974.408</v>
+        <v>2356.923</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46122.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B155">
-        <v>1931.062</v>
+        <v>2311.403</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46122.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B156">
-        <v>1889.842</v>
+        <v>2238.127</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46122.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B157">
-        <v>1838.956</v>
+        <v>2157.699</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46122.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B158">
-        <v>1684.322</v>
+        <v>2018.522</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46122.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B159">
-        <v>1607.776</v>
+        <v>1885.211</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46122.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B160">
-        <v>1503.457</v>
+        <v>1773.584</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46122.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B161">
-        <v>1436.273</v>
+        <v>1657.405</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46122.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B162">
-        <v>1251.752</v>
+        <v>1499.311</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46122.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B163">
-        <v>1107.981</v>
+        <v>1313.297</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46122.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B164">
-        <v>964.922</v>
+        <v>1155.212</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46122.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B165">
-        <v>849.924</v>
+        <v>1020.77</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46122.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B166">
-        <v>649.352</v>
+        <v>797.491</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46122.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B167">
-        <v>533.201</v>
+        <v>669.069</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46122.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B168">
-        <v>384.369</v>
+        <v>533.576</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46122.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B169">
-        <v>291.523</v>
+        <v>415.121</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46122.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B170">
-        <v>171.679</v>
+        <v>309.116</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46122.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B171">
-        <v>114.304</v>
+        <v>227.459</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46122.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B172">
-        <v>69.137</v>
+        <v>163.195</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46122.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B173">
-        <v>38.975</v>
+        <v>82.117</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46122.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B174">
-        <v>14.87</v>
+        <v>23.081</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46122.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B175">
-        <v>12.544</v>
+        <v>16.741</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46122.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B176">
-        <v>9.723000000000001</v>
+        <v>16.788</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46122.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B177">
-        <v>8.815</v>
+        <v>15.907</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46122.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B178">
-        <v>7.199</v>
+        <v>18.206</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46122.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B179">
-        <v>6.888</v>
+        <v>17.906</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46122.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B180">
-        <v>3.835</v>
+        <v>13.031</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46122.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B181">
-        <v>3.231</v>
+        <v>7.473</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46122.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B182">
-        <v>2.73</v>
+        <v>5.73</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46122.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B183">
-        <v>2.23</v>
+        <v>3.43</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46122.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46122.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46122.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B186">
-        <v>1.23</v>
+        <v>2.93</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46122.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B187">
         <v>0.73</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46122.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46122.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46122.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46122.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46122.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46122.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>16.04.20261</t>
-  </si>
-  <si>
-    <t>16.04.20262</t>
-  </si>
-  <si>
-    <t>16.04.20263</t>
-  </si>
-  <si>
-    <t>16.04.20264</t>
-  </si>
-  <si>
-    <t>16.04.20265</t>
-  </si>
-  <si>
-    <t>16.04.20266</t>
-  </si>
-  <si>
-    <t>16.04.20267</t>
-  </si>
-  <si>
-    <t>16.04.20268</t>
-  </si>
-  <si>
-    <t>16.04.20269</t>
-  </si>
-  <si>
-    <t>16.04.202610</t>
-  </si>
-  <si>
-    <t>16.04.202611</t>
-  </si>
-  <si>
-    <t>16.04.202612</t>
-  </si>
-  <si>
-    <t>16.04.202613</t>
-  </si>
-  <si>
-    <t>16.04.202614</t>
-  </si>
-  <si>
-    <t>16.04.202615</t>
-  </si>
-  <si>
-    <t>16.04.202616</t>
-  </si>
-  <si>
-    <t>16.04.202617</t>
-  </si>
-  <si>
-    <t>16.04.202618</t>
-  </si>
-  <si>
-    <t>16.04.202619</t>
-  </si>
-  <si>
-    <t>16.04.202620</t>
-  </si>
-  <si>
-    <t>16.04.202621</t>
-  </si>
-  <si>
-    <t>16.04.202622</t>
-  </si>
-  <si>
-    <t>16.04.202623</t>
-  </si>
-  <si>
-    <t>16.04.202624</t>
-  </si>
-  <si>
-    <t>16.04.202625</t>
-  </si>
-  <si>
-    <t>16.04.202626</t>
-  </si>
-  <si>
-    <t>16.04.202627</t>
-  </si>
-  <si>
-    <t>16.04.202628</t>
-  </si>
-  <si>
-    <t>16.04.202629</t>
-  </si>
-  <si>
-    <t>16.04.202630</t>
-  </si>
-  <si>
-    <t>16.04.202631</t>
-  </si>
-  <si>
-    <t>16.04.202632</t>
-  </si>
-  <si>
-    <t>16.04.202633</t>
-  </si>
-  <si>
-    <t>16.04.202634</t>
-  </si>
-  <si>
-    <t>16.04.202635</t>
-  </si>
-  <si>
-    <t>16.04.202636</t>
-  </si>
-  <si>
-    <t>16.04.202637</t>
-  </si>
-  <si>
-    <t>16.04.202638</t>
-  </si>
-  <si>
-    <t>16.04.202639</t>
-  </si>
-  <si>
-    <t>16.04.202640</t>
-  </si>
-  <si>
-    <t>16.04.202641</t>
-  </si>
-  <si>
-    <t>16.04.202642</t>
-  </si>
-  <si>
-    <t>16.04.202643</t>
-  </si>
-  <si>
-    <t>16.04.202644</t>
-  </si>
-  <si>
-    <t>16.04.202645</t>
-  </si>
-  <si>
-    <t>16.04.202646</t>
-  </si>
-  <si>
-    <t>16.04.202647</t>
-  </si>
-  <si>
-    <t>16.04.202648</t>
-  </si>
-  <si>
-    <t>16.04.202649</t>
-  </si>
-  <si>
-    <t>16.04.202650</t>
-  </si>
-  <si>
-    <t>16.04.202651</t>
-  </si>
-  <si>
-    <t>16.04.202652</t>
-  </si>
-  <si>
-    <t>16.04.202653</t>
-  </si>
-  <si>
-    <t>16.04.202654</t>
-  </si>
-  <si>
-    <t>16.04.202655</t>
-  </si>
-  <si>
-    <t>16.04.202656</t>
-  </si>
-  <si>
-    <t>16.04.202657</t>
-  </si>
-  <si>
-    <t>16.04.202658</t>
-  </si>
-  <si>
-    <t>16.04.202659</t>
-  </si>
-  <si>
-    <t>16.04.202660</t>
-  </si>
-  <si>
-    <t>16.04.202661</t>
-  </si>
-  <si>
-    <t>16.04.202662</t>
-  </si>
-  <si>
-    <t>16.04.202663</t>
-  </si>
-  <si>
-    <t>16.04.202664</t>
-  </si>
-  <si>
-    <t>16.04.202665</t>
-  </si>
-  <si>
-    <t>16.04.202666</t>
-  </si>
-  <si>
-    <t>16.04.202667</t>
-  </si>
-  <si>
-    <t>16.04.202668</t>
-  </si>
-  <si>
-    <t>16.04.202669</t>
-  </si>
-  <si>
-    <t>16.04.202670</t>
-  </si>
-  <si>
-    <t>16.04.202671</t>
-  </si>
-  <si>
-    <t>16.04.202672</t>
-  </si>
-  <si>
-    <t>16.04.202673</t>
-  </si>
-  <si>
-    <t>16.04.202674</t>
-  </si>
-  <si>
-    <t>16.04.202675</t>
-  </si>
-  <si>
-    <t>16.04.202676</t>
-  </si>
-  <si>
-    <t>16.04.202677</t>
-  </si>
-  <si>
-    <t>16.04.202678</t>
-  </si>
-  <si>
-    <t>16.04.202679</t>
-  </si>
-  <si>
-    <t>16.04.202680</t>
-  </si>
-  <si>
-    <t>16.04.202681</t>
-  </si>
-  <si>
-    <t>16.04.202682</t>
-  </si>
-  <si>
-    <t>16.04.202683</t>
-  </si>
-  <si>
-    <t>16.04.202684</t>
-  </si>
-  <si>
-    <t>16.04.202685</t>
-  </si>
-  <si>
-    <t>16.04.202686</t>
-  </si>
-  <si>
-    <t>16.04.202687</t>
-  </si>
-  <si>
-    <t>16.04.202688</t>
-  </si>
-  <si>
-    <t>16.04.202689</t>
-  </si>
-  <si>
-    <t>16.04.202690</t>
-  </si>
-  <si>
-    <t>16.04.202691</t>
-  </si>
-  <si>
-    <t>16.04.202692</t>
-  </si>
-  <si>
-    <t>16.04.202693</t>
-  </si>
-  <si>
-    <t>16.04.202694</t>
-  </si>
-  <si>
-    <t>16.04.202695</t>
-  </si>
-  <si>
-    <t>16.04.202696</t>
-  </si>
-  <si>
     <t>17.04.20261</t>
   </si>
   <si>
@@ -605,6 +317,870 @@
   </si>
   <si>
     <t>17.04.202696</t>
+  </si>
+  <si>
+    <t>18.04.20261</t>
+  </si>
+  <si>
+    <t>18.04.20262</t>
+  </si>
+  <si>
+    <t>18.04.20263</t>
+  </si>
+  <si>
+    <t>18.04.20264</t>
+  </si>
+  <si>
+    <t>18.04.20265</t>
+  </si>
+  <si>
+    <t>18.04.20266</t>
+  </si>
+  <si>
+    <t>18.04.20267</t>
+  </si>
+  <si>
+    <t>18.04.20268</t>
+  </si>
+  <si>
+    <t>18.04.20269</t>
+  </si>
+  <si>
+    <t>18.04.202610</t>
+  </si>
+  <si>
+    <t>18.04.202611</t>
+  </si>
+  <si>
+    <t>18.04.202612</t>
+  </si>
+  <si>
+    <t>18.04.202613</t>
+  </si>
+  <si>
+    <t>18.04.202614</t>
+  </si>
+  <si>
+    <t>18.04.202615</t>
+  </si>
+  <si>
+    <t>18.04.202616</t>
+  </si>
+  <si>
+    <t>18.04.202617</t>
+  </si>
+  <si>
+    <t>18.04.202618</t>
+  </si>
+  <si>
+    <t>18.04.202619</t>
+  </si>
+  <si>
+    <t>18.04.202620</t>
+  </si>
+  <si>
+    <t>18.04.202621</t>
+  </si>
+  <si>
+    <t>18.04.202622</t>
+  </si>
+  <si>
+    <t>18.04.202623</t>
+  </si>
+  <si>
+    <t>18.04.202624</t>
+  </si>
+  <si>
+    <t>18.04.202625</t>
+  </si>
+  <si>
+    <t>18.04.202626</t>
+  </si>
+  <si>
+    <t>18.04.202627</t>
+  </si>
+  <si>
+    <t>18.04.202628</t>
+  </si>
+  <si>
+    <t>18.04.202629</t>
+  </si>
+  <si>
+    <t>18.04.202630</t>
+  </si>
+  <si>
+    <t>18.04.202631</t>
+  </si>
+  <si>
+    <t>18.04.202632</t>
+  </si>
+  <si>
+    <t>18.04.202633</t>
+  </si>
+  <si>
+    <t>18.04.202634</t>
+  </si>
+  <si>
+    <t>18.04.202635</t>
+  </si>
+  <si>
+    <t>18.04.202636</t>
+  </si>
+  <si>
+    <t>18.04.202637</t>
+  </si>
+  <si>
+    <t>18.04.202638</t>
+  </si>
+  <si>
+    <t>18.04.202639</t>
+  </si>
+  <si>
+    <t>18.04.202640</t>
+  </si>
+  <si>
+    <t>18.04.202641</t>
+  </si>
+  <si>
+    <t>18.04.202642</t>
+  </si>
+  <si>
+    <t>18.04.202643</t>
+  </si>
+  <si>
+    <t>18.04.202644</t>
+  </si>
+  <si>
+    <t>18.04.202645</t>
+  </si>
+  <si>
+    <t>18.04.202646</t>
+  </si>
+  <si>
+    <t>18.04.202647</t>
+  </si>
+  <si>
+    <t>18.04.202648</t>
+  </si>
+  <si>
+    <t>18.04.202649</t>
+  </si>
+  <si>
+    <t>18.04.202650</t>
+  </si>
+  <si>
+    <t>18.04.202651</t>
+  </si>
+  <si>
+    <t>18.04.202652</t>
+  </si>
+  <si>
+    <t>18.04.202653</t>
+  </si>
+  <si>
+    <t>18.04.202654</t>
+  </si>
+  <si>
+    <t>18.04.202655</t>
+  </si>
+  <si>
+    <t>18.04.202656</t>
+  </si>
+  <si>
+    <t>18.04.202657</t>
+  </si>
+  <si>
+    <t>18.04.202658</t>
+  </si>
+  <si>
+    <t>18.04.202659</t>
+  </si>
+  <si>
+    <t>18.04.202660</t>
+  </si>
+  <si>
+    <t>18.04.202661</t>
+  </si>
+  <si>
+    <t>18.04.202662</t>
+  </si>
+  <si>
+    <t>18.04.202663</t>
+  </si>
+  <si>
+    <t>18.04.202664</t>
+  </si>
+  <si>
+    <t>18.04.202665</t>
+  </si>
+  <si>
+    <t>18.04.202666</t>
+  </si>
+  <si>
+    <t>18.04.202667</t>
+  </si>
+  <si>
+    <t>18.04.202668</t>
+  </si>
+  <si>
+    <t>18.04.202669</t>
+  </si>
+  <si>
+    <t>18.04.202670</t>
+  </si>
+  <si>
+    <t>18.04.202671</t>
+  </si>
+  <si>
+    <t>18.04.202672</t>
+  </si>
+  <si>
+    <t>18.04.202673</t>
+  </si>
+  <si>
+    <t>18.04.202674</t>
+  </si>
+  <si>
+    <t>18.04.202675</t>
+  </si>
+  <si>
+    <t>18.04.202676</t>
+  </si>
+  <si>
+    <t>18.04.202677</t>
+  </si>
+  <si>
+    <t>18.04.202678</t>
+  </si>
+  <si>
+    <t>18.04.202679</t>
+  </si>
+  <si>
+    <t>18.04.202680</t>
+  </si>
+  <si>
+    <t>18.04.202681</t>
+  </si>
+  <si>
+    <t>18.04.202682</t>
+  </si>
+  <si>
+    <t>18.04.202683</t>
+  </si>
+  <si>
+    <t>18.04.202684</t>
+  </si>
+  <si>
+    <t>18.04.202685</t>
+  </si>
+  <si>
+    <t>18.04.202686</t>
+  </si>
+  <si>
+    <t>18.04.202687</t>
+  </si>
+  <si>
+    <t>18.04.202688</t>
+  </si>
+  <si>
+    <t>18.04.202689</t>
+  </si>
+  <si>
+    <t>18.04.202690</t>
+  </si>
+  <si>
+    <t>18.04.202691</t>
+  </si>
+  <si>
+    <t>18.04.202692</t>
+  </si>
+  <si>
+    <t>18.04.202693</t>
+  </si>
+  <si>
+    <t>18.04.202694</t>
+  </si>
+  <si>
+    <t>18.04.202695</t>
+  </si>
+  <si>
+    <t>18.04.202696</t>
+  </si>
+  <si>
+    <t>19.04.20261</t>
+  </si>
+  <si>
+    <t>19.04.20262</t>
+  </si>
+  <si>
+    <t>19.04.20263</t>
+  </si>
+  <si>
+    <t>19.04.20264</t>
+  </si>
+  <si>
+    <t>19.04.20265</t>
+  </si>
+  <si>
+    <t>19.04.20266</t>
+  </si>
+  <si>
+    <t>19.04.20267</t>
+  </si>
+  <si>
+    <t>19.04.20268</t>
+  </si>
+  <si>
+    <t>19.04.20269</t>
+  </si>
+  <si>
+    <t>19.04.202610</t>
+  </si>
+  <si>
+    <t>19.04.202611</t>
+  </si>
+  <si>
+    <t>19.04.202612</t>
+  </si>
+  <si>
+    <t>19.04.202613</t>
+  </si>
+  <si>
+    <t>19.04.202614</t>
+  </si>
+  <si>
+    <t>19.04.202615</t>
+  </si>
+  <si>
+    <t>19.04.202616</t>
+  </si>
+  <si>
+    <t>19.04.202617</t>
+  </si>
+  <si>
+    <t>19.04.202618</t>
+  </si>
+  <si>
+    <t>19.04.202619</t>
+  </si>
+  <si>
+    <t>19.04.202620</t>
+  </si>
+  <si>
+    <t>19.04.202621</t>
+  </si>
+  <si>
+    <t>19.04.202622</t>
+  </si>
+  <si>
+    <t>19.04.202623</t>
+  </si>
+  <si>
+    <t>19.04.202624</t>
+  </si>
+  <si>
+    <t>19.04.202625</t>
+  </si>
+  <si>
+    <t>19.04.202626</t>
+  </si>
+  <si>
+    <t>19.04.202627</t>
+  </si>
+  <si>
+    <t>19.04.202628</t>
+  </si>
+  <si>
+    <t>19.04.202629</t>
+  </si>
+  <si>
+    <t>19.04.202630</t>
+  </si>
+  <si>
+    <t>19.04.202631</t>
+  </si>
+  <si>
+    <t>19.04.202632</t>
+  </si>
+  <si>
+    <t>19.04.202633</t>
+  </si>
+  <si>
+    <t>19.04.202634</t>
+  </si>
+  <si>
+    <t>19.04.202635</t>
+  </si>
+  <si>
+    <t>19.04.202636</t>
+  </si>
+  <si>
+    <t>19.04.202637</t>
+  </si>
+  <si>
+    <t>19.04.202638</t>
+  </si>
+  <si>
+    <t>19.04.202639</t>
+  </si>
+  <si>
+    <t>19.04.202640</t>
+  </si>
+  <si>
+    <t>19.04.202641</t>
+  </si>
+  <si>
+    <t>19.04.202642</t>
+  </si>
+  <si>
+    <t>19.04.202643</t>
+  </si>
+  <si>
+    <t>19.04.202644</t>
+  </si>
+  <si>
+    <t>19.04.202645</t>
+  </si>
+  <si>
+    <t>19.04.202646</t>
+  </si>
+  <si>
+    <t>19.04.202647</t>
+  </si>
+  <si>
+    <t>19.04.202648</t>
+  </si>
+  <si>
+    <t>19.04.202649</t>
+  </si>
+  <si>
+    <t>19.04.202650</t>
+  </si>
+  <si>
+    <t>19.04.202651</t>
+  </si>
+  <si>
+    <t>19.04.202652</t>
+  </si>
+  <si>
+    <t>19.04.202653</t>
+  </si>
+  <si>
+    <t>19.04.202654</t>
+  </si>
+  <si>
+    <t>19.04.202655</t>
+  </si>
+  <si>
+    <t>19.04.202656</t>
+  </si>
+  <si>
+    <t>19.04.202657</t>
+  </si>
+  <si>
+    <t>19.04.202658</t>
+  </si>
+  <si>
+    <t>19.04.202659</t>
+  </si>
+  <si>
+    <t>19.04.202660</t>
+  </si>
+  <si>
+    <t>19.04.202661</t>
+  </si>
+  <si>
+    <t>19.04.202662</t>
+  </si>
+  <si>
+    <t>19.04.202663</t>
+  </si>
+  <si>
+    <t>19.04.202664</t>
+  </si>
+  <si>
+    <t>19.04.202665</t>
+  </si>
+  <si>
+    <t>19.04.202666</t>
+  </si>
+  <si>
+    <t>19.04.202667</t>
+  </si>
+  <si>
+    <t>19.04.202668</t>
+  </si>
+  <si>
+    <t>19.04.202669</t>
+  </si>
+  <si>
+    <t>19.04.202670</t>
+  </si>
+  <si>
+    <t>19.04.202671</t>
+  </si>
+  <si>
+    <t>19.04.202672</t>
+  </si>
+  <si>
+    <t>19.04.202673</t>
+  </si>
+  <si>
+    <t>19.04.202674</t>
+  </si>
+  <si>
+    <t>19.04.202675</t>
+  </si>
+  <si>
+    <t>19.04.202676</t>
+  </si>
+  <si>
+    <t>19.04.202677</t>
+  </si>
+  <si>
+    <t>19.04.202678</t>
+  </si>
+  <si>
+    <t>19.04.202679</t>
+  </si>
+  <si>
+    <t>19.04.202680</t>
+  </si>
+  <si>
+    <t>19.04.202681</t>
+  </si>
+  <si>
+    <t>19.04.202682</t>
+  </si>
+  <si>
+    <t>19.04.202683</t>
+  </si>
+  <si>
+    <t>19.04.202684</t>
+  </si>
+  <si>
+    <t>19.04.202685</t>
+  </si>
+  <si>
+    <t>19.04.202686</t>
+  </si>
+  <si>
+    <t>19.04.202687</t>
+  </si>
+  <si>
+    <t>19.04.202688</t>
+  </si>
+  <si>
+    <t>19.04.202689</t>
+  </si>
+  <si>
+    <t>19.04.202690</t>
+  </si>
+  <si>
+    <t>19.04.202691</t>
+  </si>
+  <si>
+    <t>19.04.202692</t>
+  </si>
+  <si>
+    <t>19.04.202693</t>
+  </si>
+  <si>
+    <t>19.04.202694</t>
+  </si>
+  <si>
+    <t>19.04.202695</t>
+  </si>
+  <si>
+    <t>19.04.202696</t>
+  </si>
+  <si>
+    <t>20.04.20261</t>
+  </si>
+  <si>
+    <t>20.04.20262</t>
+  </si>
+  <si>
+    <t>20.04.20263</t>
+  </si>
+  <si>
+    <t>20.04.20264</t>
+  </si>
+  <si>
+    <t>20.04.20265</t>
+  </si>
+  <si>
+    <t>20.04.20266</t>
+  </si>
+  <si>
+    <t>20.04.20267</t>
+  </si>
+  <si>
+    <t>20.04.20268</t>
+  </si>
+  <si>
+    <t>20.04.20269</t>
+  </si>
+  <si>
+    <t>20.04.202610</t>
+  </si>
+  <si>
+    <t>20.04.202611</t>
+  </si>
+  <si>
+    <t>20.04.202612</t>
+  </si>
+  <si>
+    <t>20.04.202613</t>
+  </si>
+  <si>
+    <t>20.04.202614</t>
+  </si>
+  <si>
+    <t>20.04.202615</t>
+  </si>
+  <si>
+    <t>20.04.202616</t>
+  </si>
+  <si>
+    <t>20.04.202617</t>
+  </si>
+  <si>
+    <t>20.04.202618</t>
+  </si>
+  <si>
+    <t>20.04.202619</t>
+  </si>
+  <si>
+    <t>20.04.202620</t>
+  </si>
+  <si>
+    <t>20.04.202621</t>
+  </si>
+  <si>
+    <t>20.04.202622</t>
+  </si>
+  <si>
+    <t>20.04.202623</t>
+  </si>
+  <si>
+    <t>20.04.202624</t>
+  </si>
+  <si>
+    <t>20.04.202625</t>
+  </si>
+  <si>
+    <t>20.04.202626</t>
+  </si>
+  <si>
+    <t>20.04.202627</t>
+  </si>
+  <si>
+    <t>20.04.202628</t>
+  </si>
+  <si>
+    <t>20.04.202629</t>
+  </si>
+  <si>
+    <t>20.04.202630</t>
+  </si>
+  <si>
+    <t>20.04.202631</t>
+  </si>
+  <si>
+    <t>20.04.202632</t>
+  </si>
+  <si>
+    <t>20.04.202633</t>
+  </si>
+  <si>
+    <t>20.04.202634</t>
+  </si>
+  <si>
+    <t>20.04.202635</t>
+  </si>
+  <si>
+    <t>20.04.202636</t>
+  </si>
+  <si>
+    <t>20.04.202637</t>
+  </si>
+  <si>
+    <t>20.04.202638</t>
+  </si>
+  <si>
+    <t>20.04.202639</t>
+  </si>
+  <si>
+    <t>20.04.202640</t>
+  </si>
+  <si>
+    <t>20.04.202641</t>
+  </si>
+  <si>
+    <t>20.04.202642</t>
+  </si>
+  <si>
+    <t>20.04.202643</t>
+  </si>
+  <si>
+    <t>20.04.202644</t>
+  </si>
+  <si>
+    <t>20.04.202645</t>
+  </si>
+  <si>
+    <t>20.04.202646</t>
+  </si>
+  <si>
+    <t>20.04.202647</t>
+  </si>
+  <si>
+    <t>20.04.202648</t>
+  </si>
+  <si>
+    <t>20.04.202649</t>
+  </si>
+  <si>
+    <t>20.04.202650</t>
+  </si>
+  <si>
+    <t>20.04.202651</t>
+  </si>
+  <si>
+    <t>20.04.202652</t>
+  </si>
+  <si>
+    <t>20.04.202653</t>
+  </si>
+  <si>
+    <t>20.04.202654</t>
+  </si>
+  <si>
+    <t>20.04.202655</t>
+  </si>
+  <si>
+    <t>20.04.202656</t>
+  </si>
+  <si>
+    <t>20.04.202657</t>
+  </si>
+  <si>
+    <t>20.04.202658</t>
+  </si>
+  <si>
+    <t>20.04.202659</t>
+  </si>
+  <si>
+    <t>20.04.202660</t>
+  </si>
+  <si>
+    <t>20.04.202661</t>
+  </si>
+  <si>
+    <t>20.04.202662</t>
+  </si>
+  <si>
+    <t>20.04.202663</t>
+  </si>
+  <si>
+    <t>20.04.202664</t>
+  </si>
+  <si>
+    <t>20.04.202665</t>
+  </si>
+  <si>
+    <t>20.04.202666</t>
+  </si>
+  <si>
+    <t>20.04.202667</t>
+  </si>
+  <si>
+    <t>20.04.202668</t>
+  </si>
+  <si>
+    <t>20.04.202669</t>
+  </si>
+  <si>
+    <t>20.04.202670</t>
+  </si>
+  <si>
+    <t>20.04.202671</t>
+  </si>
+  <si>
+    <t>20.04.202672</t>
+  </si>
+  <si>
+    <t>20.04.202673</t>
+  </si>
+  <si>
+    <t>20.04.202674</t>
+  </si>
+  <si>
+    <t>20.04.202675</t>
+  </si>
+  <si>
+    <t>20.04.202676</t>
+  </si>
+  <si>
+    <t>20.04.202677</t>
+  </si>
+  <si>
+    <t>20.04.202678</t>
+  </si>
+  <si>
+    <t>20.04.202679</t>
+  </si>
+  <si>
+    <t>20.04.202680</t>
+  </si>
+  <si>
+    <t>20.04.202681</t>
+  </si>
+  <si>
+    <t>20.04.202682</t>
+  </si>
+  <si>
+    <t>20.04.202683</t>
+  </si>
+  <si>
+    <t>20.04.202684</t>
+  </si>
+  <si>
+    <t>20.04.202685</t>
+  </si>
+  <si>
+    <t>20.04.202686</t>
+  </si>
+  <si>
+    <t>20.04.202687</t>
+  </si>
+  <si>
+    <t>20.04.202688</t>
+  </si>
+  <si>
+    <t>20.04.202689</t>
+  </si>
+  <si>
+    <t>20.04.202690</t>
+  </si>
+  <si>
+    <t>20.04.202691</t>
+  </si>
+  <si>
+    <t>20.04.202692</t>
+  </si>
+  <si>
+    <t>20.04.202693</t>
+  </si>
+  <si>
+    <t>20.04.202694</t>
+  </si>
+  <si>
+    <t>20.04.202695</t>
+  </si>
+  <si>
+    <t>20.04.202696</t>
   </si>
 </sst>
 </file>
@@ -966,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -988,7 +1564,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -1005,7 +1581,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46128.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1598,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46128.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1615,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46128.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1632,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46128.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1649,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46128.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1666,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46128.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1683,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46128.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1700,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46128.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1717,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46128.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1734,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46128.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1751,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46128.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,7 +1768,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46128.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1209,7 +1785,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46128.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,7 +1802,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46128.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1243,7 +1819,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46128.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1260,10 +1836,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46128.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.231</v>
+        <v>1.23</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,7 +1853,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46128.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1294,7 +1870,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46128.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1311,10 +1887,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46128.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.235</v>
+        <v>1.234</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,10 +1904,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46128.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.386</v>
+        <v>17.033</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1345,10 +1921,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46128.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B23">
-        <v>2.716</v>
+        <v>17.273</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1362,10 +1938,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46128.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B24">
-        <v>4.495</v>
+        <v>19.461</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1379,13 +1955,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46128.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B25">
-        <v>25.685</v>
+        <v>38.097</v>
       </c>
       <c r="C25">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1972,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46128.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B26">
-        <v>119.682</v>
+        <v>182.904</v>
       </c>
       <c r="C26">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1989,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46128.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B27">
-        <v>190.757</v>
+        <v>250.008</v>
       </c>
       <c r="C27">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +2006,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46128.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B28">
-        <v>276.02</v>
+        <v>335.896</v>
       </c>
       <c r="C28">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +2023,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46128.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B29">
-        <v>389.506</v>
+        <v>451.432</v>
       </c>
       <c r="C29">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +2040,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46128.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B30">
-        <v>628.177</v>
+        <v>604.9059999999999</v>
       </c>
       <c r="C30">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +2057,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46128.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B31">
-        <v>801.15</v>
+        <v>742.593</v>
       </c>
       <c r="C31">
-        <v>559</v>
+        <v>503</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +2074,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46128.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B32">
-        <v>1002.586</v>
+        <v>886.485</v>
       </c>
       <c r="C32">
-        <v>717</v>
+        <v>611</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +2091,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46128.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B33">
-        <v>1237.311</v>
+        <v>1070.784</v>
       </c>
       <c r="C33">
-        <v>896</v>
+        <v>733</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +2108,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46128.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B34">
-        <v>1546.126</v>
+        <v>1296.813</v>
       </c>
       <c r="C34">
-        <v>1061</v>
+        <v>876</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +2125,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46128.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B35">
-        <v>1731.142</v>
+        <v>1445.005</v>
       </c>
       <c r="C35">
-        <v>1247</v>
+        <v>994</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +2142,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46128.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B36">
-        <v>1927.558</v>
+        <v>1581.171</v>
       </c>
       <c r="C36">
-        <v>1417</v>
+        <v>1132</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +2159,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46128.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B37">
-        <v>2110.304</v>
+        <v>1752.782</v>
       </c>
       <c r="C37">
-        <v>1543</v>
+        <v>1253</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +2176,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46128.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B38">
-        <v>2309.127</v>
+        <v>1883.887</v>
       </c>
       <c r="C38">
-        <v>1648</v>
+        <v>1334</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +2193,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46128.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B39">
-        <v>2434.985</v>
+        <v>1989.607</v>
       </c>
       <c r="C39">
-        <v>1764</v>
+        <v>1412</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +2210,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46128.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B40">
-        <v>2558.44</v>
+        <v>2112.248</v>
       </c>
       <c r="C40">
-        <v>1879</v>
+        <v>1458</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +2227,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46128.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B41">
-        <v>2658.646</v>
+        <v>2210.066</v>
       </c>
       <c r="C41">
-        <v>1947</v>
+        <v>1518</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +2244,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46128.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B42">
-        <v>2790.027</v>
+        <v>2321.558</v>
       </c>
       <c r="C42">
-        <v>1932</v>
+        <v>1644</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +2261,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46128.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B43">
-        <v>2864.062</v>
+        <v>2391.725</v>
       </c>
       <c r="C43">
-        <v>2074</v>
+        <v>1669</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +2278,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46128.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B44">
-        <v>2943.131</v>
+        <v>2459.007</v>
       </c>
       <c r="C44">
-        <v>2138</v>
+        <v>1657</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +2295,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46128.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B45">
-        <v>2991.569</v>
+        <v>2518.555</v>
       </c>
       <c r="C45">
-        <v>2062</v>
+        <v>1750</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +2312,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46128.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B46">
-        <v>3028.078</v>
+        <v>2585.181</v>
       </c>
       <c r="C46">
-        <v>2114</v>
+        <v>1789</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +2329,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46128.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B47">
-        <v>3045.385</v>
+        <v>2627.89</v>
       </c>
       <c r="C47">
-        <v>2151</v>
+        <v>1777</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +2346,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46128.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B48">
-        <v>3051.479</v>
+        <v>2644.508</v>
       </c>
       <c r="C48">
-        <v>2160</v>
+        <v>1775</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +2363,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46128.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B49">
-        <v>3060.759</v>
+        <v>2661.18</v>
       </c>
       <c r="C49">
-        <v>2166</v>
+        <v>1859</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +2380,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46128.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B50">
-        <v>3065.378</v>
+        <v>2639.826</v>
       </c>
       <c r="C50">
-        <v>2124</v>
+        <v>1871</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +2397,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46128.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B51">
-        <v>3062.667</v>
+        <v>2630.889</v>
       </c>
       <c r="C51">
-        <v>2197</v>
+        <v>1797</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +2414,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46128.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B52">
-        <v>3048.384</v>
+        <v>2618.456</v>
       </c>
       <c r="C52">
-        <v>2291</v>
+        <v>1753</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +2431,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46128.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B53">
-        <v>3032.533</v>
+        <v>2594.214</v>
       </c>
       <c r="C53">
-        <v>2304</v>
+        <v>1804</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +2448,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46128.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B54">
-        <v>2999.467</v>
+        <v>2583.058</v>
       </c>
       <c r="C54">
-        <v>2280</v>
+        <v>1809</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +2465,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46128.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B55">
-        <v>2968.77</v>
+        <v>2555.154</v>
       </c>
       <c r="C55">
-        <v>2240</v>
+        <v>1873</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +2482,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46128.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B56">
-        <v>2920.586</v>
+        <v>2529.858</v>
       </c>
       <c r="C56">
-        <v>2189</v>
+        <v>1862</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +2499,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46128.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B57">
-        <v>2869.781</v>
+        <v>2483.403</v>
       </c>
       <c r="C57">
-        <v>2106</v>
+        <v>1828</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +2516,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46128.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B58">
-        <v>2795.06</v>
+        <v>2356.923</v>
       </c>
       <c r="C58">
-        <v>2022</v>
+        <v>1760</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +2533,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46128.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B59">
-        <v>2728.474</v>
+        <v>2311.403</v>
       </c>
       <c r="C59">
-        <v>1993</v>
+        <v>1716</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +2550,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46128.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B60">
-        <v>2634.481</v>
+        <v>2238.127</v>
       </c>
       <c r="C60">
-        <v>1979</v>
+        <v>1650</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +2567,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46128.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B61">
-        <v>2546.356</v>
+        <v>2157.699</v>
       </c>
       <c r="C61">
-        <v>1941</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2584,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46128.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B62">
-        <v>2331.08</v>
+        <v>2018.522</v>
       </c>
       <c r="C62">
-        <v>1762</v>
+        <v>1605</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2601,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46128.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B63">
-        <v>2227.496</v>
+        <v>1885.211</v>
       </c>
       <c r="C63">
-        <v>1678</v>
+        <v>1528</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2618,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46128.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B64">
-        <v>2099.106</v>
+        <v>1773.584</v>
       </c>
       <c r="C64">
-        <v>1593</v>
+        <v>1467</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2635,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46128.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B65">
-        <v>1958.309</v>
+        <v>1657.405</v>
       </c>
       <c r="C65">
-        <v>1485</v>
+        <v>1382</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2652,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46128.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B66">
-        <v>1733.428</v>
+        <v>1499.311</v>
       </c>
       <c r="C66">
-        <v>1389</v>
+        <v>1256</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2669,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46128.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B67">
-        <v>1594.739</v>
+        <v>1313.297</v>
       </c>
       <c r="C67">
-        <v>1250</v>
+        <v>1059</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2686,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46128.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B68">
-        <v>1431.144</v>
+        <v>1155.212</v>
       </c>
       <c r="C68">
-        <v>1112</v>
+        <v>926</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2703,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46128.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B69">
-        <v>1237.674</v>
+        <v>1020.77</v>
       </c>
       <c r="C69">
-        <v>954</v>
+        <v>764</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2720,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46128.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B70">
-        <v>991.203</v>
+        <v>797.491</v>
       </c>
       <c r="C70">
-        <v>770</v>
+        <v>569</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2737,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46128.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B71">
-        <v>823.246</v>
+        <v>669.069</v>
       </c>
       <c r="C71">
-        <v>627</v>
+        <v>426</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2754,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46128.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B72">
-        <v>683.292</v>
+        <v>533.576</v>
       </c>
       <c r="C72">
-        <v>470</v>
+        <v>321</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2771,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46128.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B73">
-        <v>517.386</v>
+        <v>415.121</v>
       </c>
       <c r="C73">
-        <v>323</v>
+        <v>246</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2788,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46128.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B74">
-        <v>335.581</v>
+        <v>309.116</v>
       </c>
       <c r="C74">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2805,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46128.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B75">
-        <v>261.524</v>
+        <v>227.459</v>
       </c>
       <c r="C75">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2822,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46128.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B76">
-        <v>154.062</v>
+        <v>163.195</v>
       </c>
       <c r="C76">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2839,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46128.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B77">
-        <v>67.40600000000001</v>
+        <v>82.117</v>
       </c>
       <c r="C77">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,10 +2856,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46128.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B78">
-        <v>26.862</v>
+        <v>23.081</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2297,10 +2873,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46128.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B79">
-        <v>21.877</v>
+        <v>16.741</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2314,10 +2890,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46128.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B80">
-        <v>15.11</v>
+        <v>16.788</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2331,10 +2907,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46128.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B81">
-        <v>13.916</v>
+        <v>15.907</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2924,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46128.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B82">
-        <v>12.27</v>
+        <v>18.206</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2941,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46128.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B83">
-        <v>9.997999999999999</v>
+        <v>17.906</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2958,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46128.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B84">
-        <v>4.93</v>
+        <v>13.031</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2975,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46128.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B85">
-        <v>1.342</v>
+        <v>7.473</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2992,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46128.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B86">
-        <v>9.23</v>
+        <v>5.73</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +3009,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46128.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B87">
-        <v>5.23</v>
+        <v>3.43</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +3026,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46128.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B88">
-        <v>9.23</v>
+        <v>0</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +3043,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46128.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B89">
-        <v>5.23</v>
+        <v>1.23</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +3060,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46128.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.73</v>
+        <v>2.93</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +3077,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46128.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +3094,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46128.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,7 +3111,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46128.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,7 +3128,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46128.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2569,7 +3145,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46128.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +3162,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46128.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +3179,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46128.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +3196,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2637,7 +3213,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46129.01041666666</v>
+        <v>46130.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +3230,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46129.02083333334</v>
+        <v>46130.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +3247,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46129.03125</v>
+        <v>46130.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +3264,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46129.04166666666</v>
+        <v>46130.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +3281,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46129.05208333334</v>
+        <v>46130.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +3298,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46129.0625</v>
+        <v>46130.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +3315,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46129.07291666666</v>
+        <v>46130.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +3332,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46129.08333333334</v>
+        <v>46130.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +3349,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46129.09375</v>
+        <v>46130.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +3366,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46129.10416666666</v>
+        <v>46130.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +3383,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46129.11458333334</v>
+        <v>46130.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,7 +3400,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46129.125</v>
+        <v>46130.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2841,7 +3417,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46129.13541666666</v>
+        <v>46130.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +3434,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46129.14583333334</v>
+        <v>46130.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,7 +3451,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46129.15625</v>
+        <v>46130.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2892,10 +3468,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46129.16666666666</v>
+        <v>46130.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.23</v>
+        <v>0.755</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,7 +3485,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46129.17708333334</v>
+        <v>46130.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2926,7 +3502,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46129.1875</v>
+        <v>46130.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2943,10 +3519,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46129.19791666666</v>
+        <v>46130.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.234</v>
+        <v>0.759</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,10 +3536,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46129.20833333334</v>
+        <v>46130.20833333334</v>
       </c>
       <c r="B118">
-        <v>17.033</v>
+        <v>2.544</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2977,10 +3553,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46129.21875</v>
+        <v>46130.21875</v>
       </c>
       <c r="B119">
-        <v>17.273</v>
+        <v>3.092</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2994,10 +3570,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46129.22916666666</v>
+        <v>46130.22916666666</v>
       </c>
       <c r="B120">
-        <v>19.461</v>
+        <v>6.841</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3011,10 +3587,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46129.23958333334</v>
+        <v>46130.23958333334</v>
       </c>
       <c r="B121">
-        <v>38.097</v>
+        <v>25.488</v>
       </c>
       <c r="C121">
         <v>17</v>
@@ -3028,13 +3604,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46129.25</v>
+        <v>46130.25</v>
       </c>
       <c r="B122">
-        <v>182.904</v>
+        <v>100.685</v>
       </c>
       <c r="C122">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3621,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46129.26041666666</v>
+        <v>46130.26041666666</v>
       </c>
       <c r="B123">
-        <v>250.008</v>
+        <v>166.083</v>
       </c>
       <c r="C123">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3638,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46129.27083333334</v>
+        <v>46130.27083333334</v>
       </c>
       <c r="B124">
-        <v>335.896</v>
+        <v>256.339</v>
       </c>
       <c r="C124">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3655,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46129.28125</v>
+        <v>46130.28125</v>
       </c>
       <c r="B125">
-        <v>451.432</v>
+        <v>367.638</v>
       </c>
       <c r="C125">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3672,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46129.29166666666</v>
+        <v>46130.29166666666</v>
       </c>
       <c r="B126">
-        <v>604.9059999999999</v>
+        <v>569.183</v>
       </c>
       <c r="C126">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3689,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46129.30208333334</v>
+        <v>46130.30208333334</v>
       </c>
       <c r="B127">
-        <v>742.593</v>
+        <v>716.5309999999999</v>
       </c>
       <c r="C127">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3706,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46129.3125</v>
+        <v>46130.3125</v>
       </c>
       <c r="B128">
-        <v>886.485</v>
+        <v>852.505</v>
       </c>
       <c r="C128">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3723,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46129.32291666666</v>
+        <v>46130.32291666666</v>
       </c>
       <c r="B129">
-        <v>1070.784</v>
+        <v>1033.561</v>
       </c>
       <c r="C129">
-        <v>733</v>
+        <v>782</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3740,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46129.33333333334</v>
+        <v>46130.33333333334</v>
       </c>
       <c r="B130">
-        <v>1296.813</v>
+        <v>1222.653</v>
       </c>
       <c r="C130">
-        <v>876</v>
+        <v>941</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3757,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46129.34375</v>
+        <v>46130.34375</v>
       </c>
       <c r="B131">
-        <v>1445.005</v>
+        <v>1358.169</v>
       </c>
       <c r="C131">
-        <v>994</v>
+        <v>1043</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3774,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46129.35416666666</v>
+        <v>46130.35416666666</v>
       </c>
       <c r="B132">
-        <v>1581.171</v>
+        <v>1504.739</v>
       </c>
       <c r="C132">
-        <v>1132</v>
+        <v>1082</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3791,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46129.36458333334</v>
+        <v>46130.36458333334</v>
       </c>
       <c r="B133">
-        <v>1752.782</v>
+        <v>1669.717</v>
       </c>
       <c r="C133">
-        <v>1253</v>
+        <v>1244</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3808,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46129.375</v>
+        <v>46130.375</v>
       </c>
       <c r="B134">
-        <v>1883.887</v>
+        <v>1876.666</v>
       </c>
       <c r="C134">
-        <v>1334</v>
+        <v>1406</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3825,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46129.38541666666</v>
+        <v>46130.38541666666</v>
       </c>
       <c r="B135">
-        <v>1989.607</v>
+        <v>1983.125</v>
       </c>
       <c r="C135">
-        <v>1412</v>
+        <v>1474</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3842,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46129.39583333334</v>
+        <v>46130.39583333334</v>
       </c>
       <c r="B136">
-        <v>2112.248</v>
+        <v>1967.727</v>
       </c>
       <c r="C136">
-        <v>1458</v>
+        <v>1398</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3859,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46129.40625</v>
+        <v>46130.40625</v>
       </c>
       <c r="B137">
-        <v>2210.066</v>
+        <v>2023.812</v>
       </c>
       <c r="C137">
-        <v>1518</v>
+        <v>1306</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3876,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46129.41666666666</v>
+        <v>46130.41666666666</v>
       </c>
       <c r="B138">
-        <v>2321.558</v>
+        <v>2128.612</v>
       </c>
       <c r="C138">
-        <v>1644</v>
+        <v>1319</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3893,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46129.42708333334</v>
+        <v>46130.42708333334</v>
       </c>
       <c r="B139">
-        <v>2391.725</v>
+        <v>2014.458</v>
       </c>
       <c r="C139">
-        <v>1669</v>
+        <v>1227</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3910,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46129.4375</v>
+        <v>46130.4375</v>
       </c>
       <c r="B140">
-        <v>2459.007</v>
+        <v>1604.872</v>
       </c>
       <c r="C140">
-        <v>1657</v>
+        <v>926</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3927,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46129.44791666666</v>
+        <v>46130.44791666666</v>
       </c>
       <c r="B141">
-        <v>2518.555</v>
+        <v>1629.756</v>
       </c>
       <c r="C141">
-        <v>1750</v>
+        <v>898</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3944,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46129.45833333334</v>
+        <v>46130.45833333334</v>
       </c>
       <c r="B142">
-        <v>2585.181</v>
+        <v>1656.506</v>
       </c>
       <c r="C142">
-        <v>1789</v>
+        <v>960</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3961,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46129.46875</v>
+        <v>46130.46875</v>
       </c>
       <c r="B143">
-        <v>2627.89</v>
+        <v>1671.43</v>
       </c>
       <c r="C143">
-        <v>1777</v>
+        <v>994</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3978,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46129.47916666666</v>
+        <v>46130.47916666666</v>
       </c>
       <c r="B144">
-        <v>2644.508</v>
+        <v>1674.984</v>
       </c>
       <c r="C144">
-        <v>1775</v>
+        <v>1013</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3995,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46129.48958333334</v>
+        <v>46130.48958333334</v>
       </c>
       <c r="B145">
-        <v>2661.18</v>
+        <v>1618.397</v>
       </c>
       <c r="C145">
-        <v>1859</v>
+        <v>989</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +4012,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46129.5</v>
+        <v>46130.5</v>
       </c>
       <c r="B146">
-        <v>2639.826</v>
+        <v>1692.519</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1054</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +4029,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46129.51041666666</v>
+        <v>46130.51041666666</v>
       </c>
       <c r="B147">
-        <v>2630.889</v>
+        <v>1676.58</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +4046,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46129.52083333334</v>
+        <v>46130.52083333334</v>
       </c>
       <c r="B148">
-        <v>2618.456</v>
+        <v>1609.363</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>995</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,13 +4063,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46129.53125</v>
+        <v>46130.53125</v>
       </c>
       <c r="B149">
-        <v>2594.214</v>
+        <v>1592.691</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3504,13 +4080,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46129.54166666666</v>
+        <v>46130.54166666666</v>
       </c>
       <c r="B150">
-        <v>2583.058</v>
+        <v>1593.499</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>951</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3521,13 +4097,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46129.55208333334</v>
+        <v>46130.55208333334</v>
       </c>
       <c r="B151">
-        <v>2555.154</v>
+        <v>1572.549</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3538,13 +4114,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46129.5625</v>
+        <v>46130.5625</v>
       </c>
       <c r="B152">
-        <v>2529.858</v>
+        <v>1544.022</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3555,13 +4131,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46129.57291666666</v>
+        <v>46130.57291666666</v>
       </c>
       <c r="B153">
-        <v>2483.403</v>
+        <v>1570.407</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>949</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3572,13 +4148,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46129.58333333334</v>
+        <v>46130.58333333334</v>
       </c>
       <c r="B154">
-        <v>2356.923</v>
+        <v>1537.133</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3589,13 +4165,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46129.59375</v>
+        <v>46130.59375</v>
       </c>
       <c r="B155">
-        <v>2311.403</v>
+        <v>1505.343</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3606,13 +4182,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46129.60416666666</v>
+        <v>46130.60416666666</v>
       </c>
       <c r="B156">
-        <v>2238.127</v>
+        <v>1456.634</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>884</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3623,13 +4199,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46129.61458333334</v>
+        <v>46130.61458333334</v>
       </c>
       <c r="B157">
-        <v>2157.699</v>
+        <v>1434.452</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3640,13 +4216,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46129.625</v>
+        <v>46130.625</v>
       </c>
       <c r="B158">
-        <v>2018.522</v>
+        <v>1294.284</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>854</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3657,13 +4233,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46129.63541666666</v>
+        <v>46130.63541666666</v>
       </c>
       <c r="B159">
-        <v>1885.211</v>
+        <v>1218.893</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3674,13 +4250,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46129.64583333334</v>
+        <v>46130.64583333334</v>
       </c>
       <c r="B160">
-        <v>1773.584</v>
+        <v>1579.72</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3691,13 +4267,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46129.65625</v>
+        <v>46130.65625</v>
       </c>
       <c r="B161">
-        <v>1657.405</v>
+        <v>1528.678</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3708,13 +4284,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46129.66666666666</v>
+        <v>46130.66666666666</v>
       </c>
       <c r="B162">
-        <v>1499.311</v>
+        <v>1395.04</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3725,13 +4301,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46129.67708333334</v>
+        <v>46130.67708333334</v>
       </c>
       <c r="B163">
-        <v>1313.297</v>
+        <v>1242.031</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3742,13 +4318,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46129.6875</v>
+        <v>46130.6875</v>
       </c>
       <c r="B164">
-        <v>1155.212</v>
+        <v>1219.692</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3759,13 +4335,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46129.69791666666</v>
+        <v>46130.69791666666</v>
       </c>
       <c r="B165">
-        <v>1020.77</v>
+        <v>1092.629</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>754</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3776,13 +4352,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46129.70833333334</v>
+        <v>46130.70833333334</v>
       </c>
       <c r="B166">
-        <v>797.491</v>
+        <v>773.4</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3793,13 +4369,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46129.71875</v>
+        <v>46130.71875</v>
       </c>
       <c r="B167">
-        <v>669.069</v>
+        <v>704.458</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3810,13 +4386,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46129.72916666666</v>
+        <v>46130.72916666666</v>
       </c>
       <c r="B168">
-        <v>533.576</v>
+        <v>558.402</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3827,13 +4403,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46129.73958333334</v>
+        <v>46130.73958333334</v>
       </c>
       <c r="B169">
-        <v>415.121</v>
+        <v>428.539</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3844,13 +4420,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46129.75</v>
+        <v>46130.75</v>
       </c>
       <c r="B170">
-        <v>309.116</v>
+        <v>283.454</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3861,13 +4437,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46129.76041666666</v>
+        <v>46130.76041666666</v>
       </c>
       <c r="B171">
-        <v>227.459</v>
+        <v>192.558</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3878,13 +4454,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46129.77083333334</v>
+        <v>46130.77083333334</v>
       </c>
       <c r="B172">
-        <v>163.195</v>
+        <v>120.795</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3895,13 +4471,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46129.78125</v>
+        <v>46130.78125</v>
       </c>
       <c r="B173">
-        <v>82.117</v>
+        <v>72.584</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3912,13 +4488,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46129.79166666666</v>
+        <v>46130.79166666666</v>
       </c>
       <c r="B174">
-        <v>23.081</v>
+        <v>31.463</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3929,10 +4505,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46129.80208333334</v>
+        <v>46130.80208333334</v>
       </c>
       <c r="B175">
-        <v>16.741</v>
+        <v>21.27</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +4522,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46129.8125</v>
+        <v>46130.8125</v>
       </c>
       <c r="B176">
-        <v>16.788</v>
+        <v>13.319</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +4539,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46129.82291666666</v>
+        <v>46130.82291666666</v>
       </c>
       <c r="B177">
-        <v>15.907</v>
+        <v>11.846</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +4556,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46129.83333333334</v>
+        <v>46130.83333333334</v>
       </c>
       <c r="B178">
-        <v>18.206</v>
+        <v>12.228</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +4573,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46129.84375</v>
+        <v>46130.84375</v>
       </c>
       <c r="B179">
-        <v>17.906</v>
+        <v>11.901</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4590,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46129.85416666666</v>
+        <v>46130.85416666666</v>
       </c>
       <c r="B180">
-        <v>13.031</v>
+        <v>9.631</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4607,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46129.86458333334</v>
+        <v>46130.86458333334</v>
       </c>
       <c r="B181">
-        <v>7.473</v>
+        <v>8.231</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4624,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46129.875</v>
+        <v>46130.875</v>
       </c>
       <c r="B182">
-        <v>5.73</v>
+        <v>3.73</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4641,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46129.88541666666</v>
+        <v>46130.88541666666</v>
       </c>
       <c r="B183">
-        <v>3.43</v>
+        <v>1.73</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4658,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46129.89583333334</v>
+        <v>46130.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4675,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46129.90625</v>
+        <v>46130.90625</v>
       </c>
       <c r="B185">
-        <v>1.23</v>
+        <v>2.23</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4692,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46129.91666666666</v>
+        <v>46130.91666666666</v>
       </c>
       <c r="B186">
-        <v>2.93</v>
+        <v>0.73</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4709,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46129.92708333334</v>
+        <v>46130.92708333334</v>
       </c>
       <c r="B187">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,7 +4726,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46129.9375</v>
+        <v>46130.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,7 +4743,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46129.94791666666</v>
+        <v>46130.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4760,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46129.95833333334</v>
+        <v>46130.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4777,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46129.96875</v>
+        <v>46130.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4794,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46129.97916666666</v>
+        <v>46130.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4811,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46129.98958333334</v>
+        <v>46130.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4248,6 +4824,3270 @@
       </c>
       <c r="E193" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46131.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46131.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46131.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46131.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46131.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46131.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46131.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46131.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46131.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46131.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46131.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46131.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46131.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46131.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46131.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46131.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0.74</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46131.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46131.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46131.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0.744</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46131.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>3.082</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46131.21875</v>
+      </c>
+      <c r="B215">
+        <v>3.592</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46131.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>8.183999999999999</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46131.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>28.267</v>
+      </c>
+      <c r="C217">
+        <v>27</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46131.25</v>
+      </c>
+      <c r="B218">
+        <v>105.774</v>
+      </c>
+      <c r="C218">
+        <v>76</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46131.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>180.047</v>
+      </c>
+      <c r="C219">
+        <v>150</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46131.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>279.827</v>
+      </c>
+      <c r="C220">
+        <v>244</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46131.28125</v>
+      </c>
+      <c r="B221">
+        <v>402.222</v>
+      </c>
+      <c r="C221">
+        <v>367</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46131.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>629.7859999999999</v>
+      </c>
+      <c r="C222">
+        <v>507</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46131.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>804.995</v>
+      </c>
+      <c r="C223">
+        <v>653</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46131.3125</v>
+      </c>
+      <c r="B224">
+        <v>980.818</v>
+      </c>
+      <c r="C224">
+        <v>785</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46131.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>1096.611</v>
+      </c>
+      <c r="C225">
+        <v>835</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46131.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1507.946</v>
+      </c>
+      <c r="C226">
+        <v>1044</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46131.34375</v>
+      </c>
+      <c r="B227">
+        <v>1672.609</v>
+      </c>
+      <c r="C227">
+        <v>1200</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46131.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>1841.285</v>
+      </c>
+      <c r="C228">
+        <v>1259</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46131.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>1859.511</v>
+      </c>
+      <c r="C229">
+        <v>1239</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46131.375</v>
+      </c>
+      <c r="B230">
+        <v>2035.002</v>
+      </c>
+      <c r="C230">
+        <v>1279</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46131.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>2123.471</v>
+      </c>
+      <c r="C231">
+        <v>1359</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46131.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>2222.602</v>
+      </c>
+      <c r="C232">
+        <v>1458</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46131.40625</v>
+      </c>
+      <c r="B233">
+        <v>2294.602</v>
+      </c>
+      <c r="C233">
+        <v>1530</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46131.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>2392.603</v>
+      </c>
+      <c r="C234">
+        <v>1614</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46131.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>2388.964</v>
+      </c>
+      <c r="C235">
+        <v>1601</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46131.4375</v>
+      </c>
+      <c r="B236">
+        <v>2357.056</v>
+      </c>
+      <c r="C236">
+        <v>1570</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46131.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>2331.439</v>
+      </c>
+      <c r="C237">
+        <v>1520</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46131.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>2346.641</v>
+      </c>
+      <c r="C238">
+        <v>1494</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46131.46875</v>
+      </c>
+      <c r="B239">
+        <v>2315.686</v>
+      </c>
+      <c r="C239">
+        <v>1374</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46131.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>2359.715</v>
+      </c>
+      <c r="C240">
+        <v>1634</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46131.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>2332.676</v>
+      </c>
+      <c r="C241">
+        <v>1604</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46131.5</v>
+      </c>
+      <c r="B242">
+        <v>2444.919</v>
+      </c>
+      <c r="C242">
+        <v>1680</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46131.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>2415.594</v>
+      </c>
+      <c r="C243">
+        <v>1615</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46131.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>2344.758</v>
+      </c>
+      <c r="C244">
+        <v>1529</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46131.53125</v>
+      </c>
+      <c r="B245">
+        <v>1862.481</v>
+      </c>
+      <c r="C245">
+        <v>1205</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46131.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>2030.195</v>
+      </c>
+      <c r="C246">
+        <v>1180</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46131.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1764.714</v>
+      </c>
+      <c r="C247">
+        <v>1160</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46131.5625</v>
+      </c>
+      <c r="B248">
+        <v>1630.358</v>
+      </c>
+      <c r="C248">
+        <v>1074</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46131.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>1602.733</v>
+      </c>
+      <c r="C249">
+        <v>1050</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46131.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1523.354</v>
+      </c>
+      <c r="C250">
+        <v>1004</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46131.59375</v>
+      </c>
+      <c r="B251">
+        <v>1488.129</v>
+      </c>
+      <c r="C251">
+        <v>982</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46131.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>1435.781</v>
+      </c>
+      <c r="C252">
+        <v>949</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46131.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>1354.528</v>
+      </c>
+      <c r="C253">
+        <v>891</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46131.625</v>
+      </c>
+      <c r="B254">
+        <v>1273.852</v>
+      </c>
+      <c r="C254">
+        <v>851</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46131.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>1217.885</v>
+      </c>
+      <c r="C255">
+        <v>809</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46131.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1138.248</v>
+      </c>
+      <c r="C256">
+        <v>792</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46131.65625</v>
+      </c>
+      <c r="B257">
+        <v>1073.062</v>
+      </c>
+      <c r="C257">
+        <v>733</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46131.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>975.487</v>
+      </c>
+      <c r="C258">
+        <v>670</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46131.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>1195.046</v>
+      </c>
+      <c r="C259">
+        <v>776</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46131.6875</v>
+      </c>
+      <c r="B260">
+        <v>1102.123</v>
+      </c>
+      <c r="C260">
+        <v>869</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46131.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>1009.374</v>
+      </c>
+      <c r="C261">
+        <v>749</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46131.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>777.301</v>
+      </c>
+      <c r="C262">
+        <v>631</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46131.71875</v>
+      </c>
+      <c r="B263">
+        <v>659.4109999999999</v>
+      </c>
+      <c r="C263">
+        <v>509</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46131.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>521.116</v>
+      </c>
+      <c r="C264">
+        <v>392</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46131.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>405.759</v>
+      </c>
+      <c r="C265">
+        <v>288</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46131.75</v>
+      </c>
+      <c r="B266">
+        <v>262.181</v>
+      </c>
+      <c r="C266">
+        <v>204</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46131.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>186.898</v>
+      </c>
+      <c r="C267">
+        <v>139</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46131.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>120.587</v>
+      </c>
+      <c r="C268">
+        <v>72</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46131.78125</v>
+      </c>
+      <c r="B269">
+        <v>74.515</v>
+      </c>
+      <c r="C269">
+        <v>21</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46131.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>33.659</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46131.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>23.334</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46131.8125</v>
+      </c>
+      <c r="B272">
+        <v>14.598</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46131.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>13.237</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46131.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>8.257</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46131.84375</v>
+      </c>
+      <c r="B275">
+        <v>7.901</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46131.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>4.831</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46131.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>4.231</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46131.875</v>
+      </c>
+      <c r="B278">
+        <v>2.73</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46131.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46131.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>2.43</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46131.90625</v>
+      </c>
+      <c r="B281">
+        <v>2.73</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46131.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>1.43</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46131.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0.73</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46131.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46131.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46131.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46131.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46131.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46131.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46132.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46132.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46132.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46132.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46132.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46132.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46132.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46132.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46132.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46132.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46132.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46132.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46132.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46132.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46132.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46132.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0.739</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46132.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46132.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46132.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0.743</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46132.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>3.009</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46132.21875</v>
+      </c>
+      <c r="B311">
+        <v>3.487</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46132.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>11.183</v>
+      </c>
+      <c r="C312">
+        <v>2</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46132.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>33.354</v>
+      </c>
+      <c r="C313">
+        <v>28</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46132.25</v>
+      </c>
+      <c r="B314">
+        <v>111.972</v>
+      </c>
+      <c r="C314">
+        <v>78</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46132.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>179.35</v>
+      </c>
+      <c r="C315">
+        <v>151</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46132.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>268.858</v>
+      </c>
+      <c r="C316">
+        <v>246</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46132.28125</v>
+      </c>
+      <c r="B317">
+        <v>367.523</v>
+      </c>
+      <c r="C317">
+        <v>371</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46132.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>570.6180000000001</v>
+      </c>
+      <c r="C318">
+        <v>497</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46132.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>713.6559999999999</v>
+      </c>
+      <c r="C319">
+        <v>662</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46132.3125</v>
+      </c>
+      <c r="B320">
+        <v>856.2859999999999</v>
+      </c>
+      <c r="C320">
+        <v>792</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46132.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>995.558</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46132.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>1150.666</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46132.34375</v>
+      </c>
+      <c r="B323">
+        <v>1291.061</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46132.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>1375.368</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46132.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>1506.424</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46132.375</v>
+      </c>
+      <c r="B326">
+        <v>1757.842</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46132.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>1841.843</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46132.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>1914.931</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46132.40625</v>
+      </c>
+      <c r="B329">
+        <v>1981.272</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46132.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>2040.893</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46132.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>2083.085</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46132.4375</v>
+      </c>
+      <c r="B332">
+        <v>2105.529</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46132.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>2119.23</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46132.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>2074.496</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46132.46875</v>
+      </c>
+      <c r="B335">
+        <v>2073.417</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46132.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>2048.6</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46132.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>2029.091</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46132.5</v>
+      </c>
+      <c r="B338">
+        <v>1985.504</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46132.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>1949.766</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46132.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>1922.14</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46132.53125</v>
+      </c>
+      <c r="B341">
+        <v>1891.443</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46132.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>1829.366</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46132.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>1791.416</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46132.5625</v>
+      </c>
+      <c r="B344">
+        <v>1741.789</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46132.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>1686.32</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46132.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>1612.789</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46132.59375</v>
+      </c>
+      <c r="B347">
+        <v>1538.57</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46132.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>1465.112</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46132.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>1401.148</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46132.625</v>
+      </c>
+      <c r="B350">
+        <v>1323.499</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46132.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>1224.683</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46132.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>1143.063</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46132.65625</v>
+      </c>
+      <c r="B353">
+        <v>1076.688</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46132.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>967.5700000000001</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46132.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>868.8869999999999</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46132.6875</v>
+      </c>
+      <c r="B356">
+        <v>797.832</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46132.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>716.199</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46132.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>562.972</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46132.71875</v>
+      </c>
+      <c r="B359">
+        <v>483.681</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46132.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>403.225</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46132.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>318.992</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46132.75</v>
+      </c>
+      <c r="B362">
+        <v>234.427</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46132.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>171.537</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46132.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>128.562</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46132.78125</v>
+      </c>
+      <c r="B365">
+        <v>88.681</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46132.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>26.442</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46132.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>18.175</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46132.8125</v>
+      </c>
+      <c r="B368">
+        <v>13.79</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46132.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>11.457</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46132.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>11.214</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46132.84375</v>
+      </c>
+      <c r="B371">
+        <v>10.239</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46132.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>7.169</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46132.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>5.23</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46132.875</v>
+      </c>
+      <c r="B374">
+        <v>0.73</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46132.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>2.03</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46132.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>2.73</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46132.90625</v>
+      </c>
+      <c r="B377">
+        <v>2.03</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46132.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46132.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46132.9375</v>
+      </c>
+      <c r="B380">
+        <v>0.73</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46132.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46132.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46132.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46132.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46132.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.04.20261</t>
-  </si>
-  <si>
-    <t>20.04.20262</t>
-  </si>
-  <si>
-    <t>20.04.20263</t>
-  </si>
-  <si>
-    <t>20.04.20264</t>
-  </si>
-  <si>
-    <t>20.04.20265</t>
-  </si>
-  <si>
-    <t>20.04.20266</t>
-  </si>
-  <si>
-    <t>20.04.20267</t>
-  </si>
-  <si>
-    <t>20.04.20268</t>
-  </si>
-  <si>
-    <t>20.04.20269</t>
-  </si>
-  <si>
-    <t>20.04.202610</t>
-  </si>
-  <si>
-    <t>20.04.202611</t>
-  </si>
-  <si>
-    <t>20.04.202612</t>
-  </si>
-  <si>
-    <t>20.04.202613</t>
-  </si>
-  <si>
-    <t>20.04.202614</t>
-  </si>
-  <si>
-    <t>20.04.202615</t>
-  </si>
-  <si>
-    <t>20.04.202616</t>
-  </si>
-  <si>
-    <t>20.04.202617</t>
-  </si>
-  <si>
-    <t>20.04.202618</t>
-  </si>
-  <si>
-    <t>20.04.202619</t>
-  </si>
-  <si>
-    <t>20.04.202620</t>
-  </si>
-  <si>
-    <t>20.04.202621</t>
-  </si>
-  <si>
-    <t>20.04.202622</t>
-  </si>
-  <si>
-    <t>20.04.202623</t>
-  </si>
-  <si>
-    <t>20.04.202624</t>
-  </si>
-  <si>
-    <t>20.04.202625</t>
-  </si>
-  <si>
-    <t>20.04.202626</t>
-  </si>
-  <si>
-    <t>20.04.202627</t>
-  </si>
-  <si>
-    <t>20.04.202628</t>
-  </si>
-  <si>
-    <t>20.04.202629</t>
-  </si>
-  <si>
-    <t>20.04.202630</t>
-  </si>
-  <si>
-    <t>20.04.202631</t>
-  </si>
-  <si>
-    <t>20.04.202632</t>
-  </si>
-  <si>
-    <t>20.04.202633</t>
-  </si>
-  <si>
-    <t>20.04.202634</t>
-  </si>
-  <si>
-    <t>20.04.202635</t>
-  </si>
-  <si>
-    <t>20.04.202636</t>
-  </si>
-  <si>
-    <t>20.04.202637</t>
-  </si>
-  <si>
-    <t>20.04.202638</t>
-  </si>
-  <si>
-    <t>20.04.202639</t>
-  </si>
-  <si>
-    <t>20.04.202640</t>
-  </si>
-  <si>
-    <t>20.04.202641</t>
-  </si>
-  <si>
-    <t>20.04.202642</t>
-  </si>
-  <si>
-    <t>20.04.202643</t>
-  </si>
-  <si>
-    <t>20.04.202644</t>
-  </si>
-  <si>
-    <t>20.04.202645</t>
-  </si>
-  <si>
-    <t>20.04.202646</t>
-  </si>
-  <si>
-    <t>20.04.202647</t>
-  </si>
-  <si>
-    <t>20.04.202648</t>
-  </si>
-  <si>
-    <t>20.04.202649</t>
-  </si>
-  <si>
-    <t>20.04.202650</t>
-  </si>
-  <si>
-    <t>20.04.202651</t>
-  </si>
-  <si>
-    <t>20.04.202652</t>
-  </si>
-  <si>
-    <t>20.04.202653</t>
-  </si>
-  <si>
-    <t>20.04.202654</t>
-  </si>
-  <si>
-    <t>20.04.202655</t>
-  </si>
-  <si>
-    <t>20.04.202656</t>
-  </si>
-  <si>
-    <t>20.04.202657</t>
-  </si>
-  <si>
-    <t>20.04.202658</t>
-  </si>
-  <si>
-    <t>20.04.202659</t>
-  </si>
-  <si>
-    <t>20.04.202660</t>
-  </si>
-  <si>
-    <t>20.04.202661</t>
-  </si>
-  <si>
-    <t>20.04.202662</t>
-  </si>
-  <si>
-    <t>20.04.202663</t>
-  </si>
-  <si>
-    <t>20.04.202664</t>
-  </si>
-  <si>
-    <t>20.04.202665</t>
-  </si>
-  <si>
-    <t>20.04.202666</t>
-  </si>
-  <si>
-    <t>20.04.202667</t>
-  </si>
-  <si>
-    <t>20.04.202668</t>
-  </si>
-  <si>
-    <t>20.04.202669</t>
-  </si>
-  <si>
-    <t>20.04.202670</t>
-  </si>
-  <si>
-    <t>20.04.202671</t>
-  </si>
-  <si>
-    <t>20.04.202672</t>
-  </si>
-  <si>
-    <t>20.04.202673</t>
-  </si>
-  <si>
-    <t>20.04.202674</t>
-  </si>
-  <si>
-    <t>20.04.202675</t>
-  </si>
-  <si>
-    <t>20.04.202676</t>
-  </si>
-  <si>
-    <t>20.04.202677</t>
-  </si>
-  <si>
-    <t>20.04.202678</t>
-  </si>
-  <si>
-    <t>20.04.202679</t>
-  </si>
-  <si>
-    <t>20.04.202680</t>
-  </si>
-  <si>
-    <t>20.04.202681</t>
-  </si>
-  <si>
-    <t>20.04.202682</t>
-  </si>
-  <si>
-    <t>20.04.202683</t>
-  </si>
-  <si>
-    <t>20.04.202684</t>
-  </si>
-  <si>
-    <t>20.04.202685</t>
-  </si>
-  <si>
-    <t>20.04.202686</t>
-  </si>
-  <si>
-    <t>20.04.202687</t>
-  </si>
-  <si>
-    <t>20.04.202688</t>
-  </si>
-  <si>
-    <t>20.04.202689</t>
-  </si>
-  <si>
-    <t>20.04.202690</t>
-  </si>
-  <si>
-    <t>20.04.202691</t>
-  </si>
-  <si>
-    <t>20.04.202692</t>
-  </si>
-  <si>
-    <t>20.04.202693</t>
-  </si>
-  <si>
-    <t>20.04.202694</t>
-  </si>
-  <si>
-    <t>20.04.202695</t>
-  </si>
-  <si>
-    <t>20.04.202696</t>
-  </si>
-  <si>
     <t>21.04.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>21.04.202696</t>
+  </si>
+  <si>
+    <t>22.04.20261</t>
+  </si>
+  <si>
+    <t>22.04.20262</t>
+  </si>
+  <si>
+    <t>22.04.20263</t>
+  </si>
+  <si>
+    <t>22.04.20264</t>
+  </si>
+  <si>
+    <t>22.04.20265</t>
+  </si>
+  <si>
+    <t>22.04.20266</t>
+  </si>
+  <si>
+    <t>22.04.20267</t>
+  </si>
+  <si>
+    <t>22.04.20268</t>
+  </si>
+  <si>
+    <t>22.04.20269</t>
+  </si>
+  <si>
+    <t>22.04.202610</t>
+  </si>
+  <si>
+    <t>22.04.202611</t>
+  </si>
+  <si>
+    <t>22.04.202612</t>
+  </si>
+  <si>
+    <t>22.04.202613</t>
+  </si>
+  <si>
+    <t>22.04.202614</t>
+  </si>
+  <si>
+    <t>22.04.202615</t>
+  </si>
+  <si>
+    <t>22.04.202616</t>
+  </si>
+  <si>
+    <t>22.04.202617</t>
+  </si>
+  <si>
+    <t>22.04.202618</t>
+  </si>
+  <si>
+    <t>22.04.202619</t>
+  </si>
+  <si>
+    <t>22.04.202620</t>
+  </si>
+  <si>
+    <t>22.04.202621</t>
+  </si>
+  <si>
+    <t>22.04.202622</t>
+  </si>
+  <si>
+    <t>22.04.202623</t>
+  </si>
+  <si>
+    <t>22.04.202624</t>
+  </si>
+  <si>
+    <t>22.04.202625</t>
+  </si>
+  <si>
+    <t>22.04.202626</t>
+  </si>
+  <si>
+    <t>22.04.202627</t>
+  </si>
+  <si>
+    <t>22.04.202628</t>
+  </si>
+  <si>
+    <t>22.04.202629</t>
+  </si>
+  <si>
+    <t>22.04.202630</t>
+  </si>
+  <si>
+    <t>22.04.202631</t>
+  </si>
+  <si>
+    <t>22.04.202632</t>
+  </si>
+  <si>
+    <t>22.04.202633</t>
+  </si>
+  <si>
+    <t>22.04.202634</t>
+  </si>
+  <si>
+    <t>22.04.202635</t>
+  </si>
+  <si>
+    <t>22.04.202636</t>
+  </si>
+  <si>
+    <t>22.04.202637</t>
+  </si>
+  <si>
+    <t>22.04.202638</t>
+  </si>
+  <si>
+    <t>22.04.202639</t>
+  </si>
+  <si>
+    <t>22.04.202640</t>
+  </si>
+  <si>
+    <t>22.04.202641</t>
+  </si>
+  <si>
+    <t>22.04.202642</t>
+  </si>
+  <si>
+    <t>22.04.202643</t>
+  </si>
+  <si>
+    <t>22.04.202644</t>
+  </si>
+  <si>
+    <t>22.04.202645</t>
+  </si>
+  <si>
+    <t>22.04.202646</t>
+  </si>
+  <si>
+    <t>22.04.202647</t>
+  </si>
+  <si>
+    <t>22.04.202648</t>
+  </si>
+  <si>
+    <t>22.04.202649</t>
+  </si>
+  <si>
+    <t>22.04.202650</t>
+  </si>
+  <si>
+    <t>22.04.202651</t>
+  </si>
+  <si>
+    <t>22.04.202652</t>
+  </si>
+  <si>
+    <t>22.04.202653</t>
+  </si>
+  <si>
+    <t>22.04.202654</t>
+  </si>
+  <si>
+    <t>22.04.202655</t>
+  </si>
+  <si>
+    <t>22.04.202656</t>
+  </si>
+  <si>
+    <t>22.04.202657</t>
+  </si>
+  <si>
+    <t>22.04.202658</t>
+  </si>
+  <si>
+    <t>22.04.202659</t>
+  </si>
+  <si>
+    <t>22.04.202660</t>
+  </si>
+  <si>
+    <t>22.04.202661</t>
+  </si>
+  <si>
+    <t>22.04.202662</t>
+  </si>
+  <si>
+    <t>22.04.202663</t>
+  </si>
+  <si>
+    <t>22.04.202664</t>
+  </si>
+  <si>
+    <t>22.04.202665</t>
+  </si>
+  <si>
+    <t>22.04.202666</t>
+  </si>
+  <si>
+    <t>22.04.202667</t>
+  </si>
+  <si>
+    <t>22.04.202668</t>
+  </si>
+  <si>
+    <t>22.04.202669</t>
+  </si>
+  <si>
+    <t>22.04.202670</t>
+  </si>
+  <si>
+    <t>22.04.202671</t>
+  </si>
+  <si>
+    <t>22.04.202672</t>
+  </si>
+  <si>
+    <t>22.04.202673</t>
+  </si>
+  <si>
+    <t>22.04.202674</t>
+  </si>
+  <si>
+    <t>22.04.202675</t>
+  </si>
+  <si>
+    <t>22.04.202676</t>
+  </si>
+  <si>
+    <t>22.04.202677</t>
+  </si>
+  <si>
+    <t>22.04.202678</t>
+  </si>
+  <si>
+    <t>22.04.202679</t>
+  </si>
+  <si>
+    <t>22.04.202680</t>
+  </si>
+  <si>
+    <t>22.04.202681</t>
+  </si>
+  <si>
+    <t>22.04.202682</t>
+  </si>
+  <si>
+    <t>22.04.202683</t>
+  </si>
+  <si>
+    <t>22.04.202684</t>
+  </si>
+  <si>
+    <t>22.04.202685</t>
+  </si>
+  <si>
+    <t>22.04.202686</t>
+  </si>
+  <si>
+    <t>22.04.202687</t>
+  </si>
+  <si>
+    <t>22.04.202688</t>
+  </si>
+  <si>
+    <t>22.04.202689</t>
+  </si>
+  <si>
+    <t>22.04.202690</t>
+  </si>
+  <si>
+    <t>22.04.202691</t>
+  </si>
+  <si>
+    <t>22.04.202692</t>
+  </si>
+  <si>
+    <t>22.04.202693</t>
+  </si>
+  <si>
+    <t>22.04.202694</t>
+  </si>
+  <si>
+    <t>22.04.202695</t>
+  </si>
+  <si>
+    <t>22.04.202696</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.739</v>
+        <v>17.73</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.743</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.009</v>
+        <v>28.603</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
-        <v>3.487</v>
+        <v>28.834</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
-        <v>11.183</v>
+        <v>33.491</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
-        <v>33.354</v>
+        <v>49.824</v>
       </c>
       <c r="C25">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
-        <v>111.972</v>
+        <v>128.33</v>
       </c>
       <c r="C26">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
-        <v>179.35</v>
+        <v>179.384</v>
       </c>
       <c r="C27">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
-        <v>268.858</v>
+        <v>242.578</v>
       </c>
       <c r="C28">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
-        <v>367.523</v>
+        <v>314.328</v>
       </c>
       <c r="C29">
-        <v>371</v>
+        <v>283</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
-        <v>570.6180000000001</v>
+        <v>455.529</v>
       </c>
       <c r="C30">
-        <v>497</v>
+        <v>352</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
-        <v>713.6559999999999</v>
+        <v>550.471</v>
       </c>
       <c r="C31">
-        <v>662</v>
+        <v>425</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
-        <v>856.2859999999999</v>
+        <v>651.323</v>
       </c>
       <c r="C32">
-        <v>792</v>
+        <v>512</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
-        <v>995.558</v>
+        <v>778.053</v>
       </c>
       <c r="C33">
-        <v>851</v>
+        <v>665</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
-        <v>1150.666</v>
+        <v>932.63</v>
       </c>
       <c r="C34">
-        <v>911</v>
+        <v>699</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
-        <v>1291.061</v>
+        <v>1033.448</v>
       </c>
       <c r="C35">
-        <v>1016</v>
+        <v>854</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
-        <v>1375.368</v>
+        <v>1121.84</v>
       </c>
       <c r="C36">
-        <v>1117</v>
+        <v>968</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
-        <v>1506.424</v>
+        <v>1215.914</v>
       </c>
       <c r="C37">
-        <v>1243</v>
+        <v>1019</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
-        <v>1757.842</v>
+        <v>1293.732</v>
       </c>
       <c r="C38">
-        <v>1350</v>
+        <v>1092</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
-        <v>1841.843</v>
+        <v>1362.951</v>
       </c>
       <c r="C39">
-        <v>1454</v>
+        <v>1151</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
-        <v>1914.931</v>
+        <v>1425.539</v>
       </c>
       <c r="C40">
-        <v>1507</v>
+        <v>1164</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
-        <v>1981.272</v>
+        <v>1483.644</v>
       </c>
       <c r="C41">
-        <v>1535</v>
+        <v>1063</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
-        <v>2040.893</v>
+        <v>1552.392</v>
       </c>
       <c r="C42">
-        <v>1627</v>
+        <v>1076</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
-        <v>2083.085</v>
+        <v>1597.645</v>
       </c>
       <c r="C43">
-        <v>1693</v>
+        <v>1166</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
-        <v>2105.529</v>
+        <v>1627.276</v>
       </c>
       <c r="C44">
-        <v>1656</v>
+        <v>1216</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
-        <v>2119.23</v>
+        <v>1656.179</v>
       </c>
       <c r="C45">
-        <v>1663</v>
+        <v>1246</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
-        <v>2074.496</v>
+        <v>1681.697</v>
       </c>
       <c r="C46">
-        <v>1612</v>
+        <v>1269</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
-        <v>2073.417</v>
+        <v>1693.967</v>
       </c>
       <c r="C47">
-        <v>1647</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
-        <v>2048.6</v>
+        <v>1673.647</v>
       </c>
       <c r="C48">
-        <v>1683</v>
+        <v>1262</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
-        <v>2029.091</v>
+        <v>1669.106</v>
       </c>
       <c r="C49">
-        <v>1645</v>
+        <v>1281</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
-        <v>1985.504</v>
+        <v>1661.777</v>
       </c>
       <c r="C50">
-        <v>1584</v>
+        <v>1261</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
-        <v>1949.766</v>
+        <v>1656.133</v>
       </c>
       <c r="C51">
-        <v>1575</v>
+        <v>1297</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
-        <v>1922.14</v>
+        <v>1645.866</v>
       </c>
       <c r="C52">
-        <v>1554</v>
+        <v>1303</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
-        <v>1891.443</v>
+        <v>1634.58</v>
       </c>
       <c r="C53">
-        <v>1513</v>
+        <v>1228</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
-        <v>1829.366</v>
+        <v>1628.633</v>
       </c>
       <c r="C54">
-        <v>1622</v>
+        <v>1183</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
-        <v>1791.416</v>
+        <v>1611.101</v>
       </c>
       <c r="C55">
-        <v>1585</v>
+        <v>1134</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
-        <v>1741.789</v>
+        <v>1588.84</v>
       </c>
       <c r="C56">
-        <v>1592</v>
+        <v>1138</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
-        <v>1686.32</v>
+        <v>1556.13</v>
       </c>
       <c r="C57">
-        <v>1446</v>
+        <v>1115</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
-        <v>1612.789</v>
+        <v>1467.948</v>
       </c>
       <c r="C58">
-        <v>1433</v>
+        <v>1104</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
-        <v>1538.57</v>
+        <v>1419.925</v>
       </c>
       <c r="C59">
-        <v>1343</v>
+        <v>1130</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
-        <v>1465.112</v>
+        <v>1368.665</v>
       </c>
       <c r="C60">
-        <v>1316</v>
+        <v>1070</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
-        <v>1401.148</v>
+        <v>1322.337</v>
       </c>
       <c r="C61">
-        <v>1284</v>
+        <v>950</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
-        <v>1323.499</v>
+        <v>1221.793</v>
       </c>
       <c r="C62">
-        <v>1191</v>
+        <v>939</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
-        <v>1224.683</v>
+        <v>1154.026</v>
       </c>
       <c r="C63">
-        <v>1163</v>
+        <v>978</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
-        <v>1143.063</v>
+        <v>1087.606</v>
       </c>
       <c r="C64">
-        <v>1075</v>
+        <v>935</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
-        <v>1076.688</v>
+        <v>1012.211</v>
       </c>
       <c r="C65">
-        <v>945</v>
+        <v>844</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
-        <v>967.5700000000001</v>
+        <v>895.968</v>
       </c>
       <c r="C66">
-        <v>884</v>
+        <v>828</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
-        <v>868.8869999999999</v>
+        <v>806.313</v>
       </c>
       <c r="C67">
-        <v>771</v>
+        <v>743</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
-        <v>797.832</v>
+        <v>719.8339999999999</v>
       </c>
       <c r="C68">
-        <v>745</v>
+        <v>650</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
-        <v>716.199</v>
+        <v>647.595</v>
       </c>
       <c r="C69">
-        <v>629</v>
+        <v>586</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
-        <v>562.972</v>
+        <v>518.069</v>
       </c>
       <c r="C70">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
-        <v>483.681</v>
+        <v>440.295</v>
       </c>
       <c r="C71">
-        <v>443</v>
+        <v>366</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
-        <v>403.225</v>
+        <v>351.856</v>
       </c>
       <c r="C72">
-        <v>408</v>
+        <v>321</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
-        <v>318.992</v>
+        <v>299.578</v>
       </c>
       <c r="C73">
-        <v>283</v>
+        <v>238</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
-        <v>234.427</v>
+        <v>205.453</v>
       </c>
       <c r="C74">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
-        <v>171.537</v>
+        <v>159.332</v>
       </c>
       <c r="C75">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
-        <v>128.562</v>
+        <v>76.60599999999999</v>
       </c>
       <c r="C76">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
-        <v>88.681</v>
+        <v>50.974</v>
       </c>
       <c r="C77">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
-        <v>26.442</v>
+        <v>22.645</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
-        <v>18.175</v>
+        <v>17.36</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
-        <v>13.79</v>
+        <v>15.969</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
-        <v>11.457</v>
+        <v>13.738</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
-        <v>11.214</v>
+        <v>7.7</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
-        <v>10.239</v>
+        <v>7.412</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
-        <v>7.169</v>
+        <v>4.362</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
-        <v>5.23</v>
+        <v>3.73</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
-        <v>0.73</v>
+        <v>2.73</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46133.01041666666</v>
+        <v>46134.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46133.02083333334</v>
+        <v>46134.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46133.03125</v>
+        <v>46134.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46133.04166666666</v>
+        <v>46134.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46133.05208333334</v>
+        <v>46134.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46133.0625</v>
+        <v>46134.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46133.07291666666</v>
+        <v>46134.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46133.08333333334</v>
+        <v>46134.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46133.09375</v>
+        <v>46134.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46133.10416666666</v>
+        <v>46134.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46133.11458333334</v>
+        <v>46134.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46133.125</v>
+        <v>46134.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46133.13541666666</v>
+        <v>46134.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46133.14583333334</v>
+        <v>46134.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46133.15625</v>
+        <v>46134.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46133.16666666666</v>
+        <v>46134.16666666666</v>
       </c>
       <c r="B114">
-        <v>17.73</v>
+        <v>0.762</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46133.17708333334</v>
+        <v>46134.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46133.1875</v>
+        <v>46134.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46133.19791666666</v>
+        <v>46134.19791666666</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46133.20833333334</v>
+        <v>46134.20833333334</v>
       </c>
       <c r="B118">
-        <v>28.603</v>
+        <v>1.541</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46133.21875</v>
+        <v>46134.21875</v>
       </c>
       <c r="B119">
-        <v>28.834</v>
+        <v>2.215</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46133.22916666666</v>
+        <v>46134.22916666666</v>
       </c>
       <c r="B120">
-        <v>33.491</v>
+        <v>8.882</v>
       </c>
       <c r="C120">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46133.23958333334</v>
+        <v>46134.23958333334</v>
       </c>
       <c r="B121">
-        <v>49.824</v>
+        <v>28.218</v>
       </c>
       <c r="C121">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46133.25</v>
+        <v>46134.25</v>
       </c>
       <c r="B122">
-        <v>128.33</v>
+        <v>93.256</v>
       </c>
       <c r="C122">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46133.26041666666</v>
+        <v>46134.26041666666</v>
       </c>
       <c r="B123">
-        <v>179.384</v>
+        <v>150.627</v>
       </c>
       <c r="C123">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46133.27083333334</v>
+        <v>46134.27083333334</v>
       </c>
       <c r="B124">
-        <v>242.578</v>
+        <v>227.969</v>
       </c>
       <c r="C124">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46133.28125</v>
+        <v>46134.28125</v>
       </c>
       <c r="B125">
-        <v>314.328</v>
+        <v>315.111</v>
       </c>
       <c r="C125">
         <v>283</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46133.29166666666</v>
+        <v>46134.29166666666</v>
       </c>
       <c r="B126">
-        <v>455.529</v>
+        <v>440.148</v>
       </c>
       <c r="C126">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46133.30208333334</v>
+        <v>46134.30208333334</v>
       </c>
       <c r="B127">
-        <v>550.471</v>
+        <v>545.1660000000001</v>
       </c>
       <c r="C127">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46133.3125</v>
+        <v>46134.3125</v>
       </c>
       <c r="B128">
-        <v>651.323</v>
+        <v>666.579</v>
       </c>
       <c r="C128">
-        <v>512</v>
+        <v>568</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46133.32291666666</v>
+        <v>46134.32291666666</v>
       </c>
       <c r="B129">
-        <v>778.053</v>
+        <v>786.561</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46133.33333333334</v>
+        <v>46134.33333333334</v>
       </c>
       <c r="B130">
-        <v>932.63</v>
+        <v>974.1559999999999</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46133.34375</v>
+        <v>46134.34375</v>
       </c>
       <c r="B131">
-        <v>1033.448</v>
+        <v>1087.779</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>893</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46133.35416666666</v>
+        <v>46134.35416666666</v>
       </c>
       <c r="B132">
-        <v>1121.84</v>
+        <v>1221.673</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>943</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46133.36458333334</v>
+        <v>46134.36458333334</v>
       </c>
       <c r="B133">
-        <v>1215.914</v>
+        <v>1327.251</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46133.375</v>
+        <v>46134.375</v>
       </c>
       <c r="B134">
-        <v>1293.732</v>
+        <v>1494.343</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1114</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46133.38541666666</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="B135">
-        <v>1362.951</v>
+        <v>1575.25</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46133.39583333334</v>
+        <v>46134.39583333334</v>
       </c>
       <c r="B136">
-        <v>1425.539</v>
+        <v>1665.605</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1271</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46133.40625</v>
+        <v>46134.40625</v>
       </c>
       <c r="B137">
-        <v>1483.644</v>
+        <v>1740.885</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1357</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46133.41666666666</v>
+        <v>46134.41666666666</v>
       </c>
       <c r="B138">
-        <v>1552.392</v>
+        <v>1806.898</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1435</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46133.42708333334</v>
+        <v>46134.42708333334</v>
       </c>
       <c r="B139">
-        <v>1597.645</v>
+        <v>1857.69</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46133.4375</v>
+        <v>46134.4375</v>
       </c>
       <c r="B140">
-        <v>1627.276</v>
+        <v>1899.746</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46133.44791666666</v>
+        <v>46134.44791666666</v>
       </c>
       <c r="B141">
-        <v>1656.179</v>
+        <v>1927.155</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46133.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="B142">
-        <v>1681.697</v>
+        <v>1933.348</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46133.46875</v>
+        <v>46134.46875</v>
       </c>
       <c r="B143">
-        <v>1693.967</v>
+        <v>1961.971</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46133.47916666666</v>
+        <v>46134.47916666666</v>
       </c>
       <c r="B144">
-        <v>1673.647</v>
+        <v>1974.113</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46133.48958333334</v>
+        <v>46134.48958333334</v>
       </c>
       <c r="B145">
-        <v>1669.106</v>
+        <v>1988.061</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46133.5</v>
+        <v>46134.5</v>
       </c>
       <c r="B146">
-        <v>1661.777</v>
+        <v>1975.282</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46133.51041666666</v>
+        <v>46134.51041666666</v>
       </c>
       <c r="B147">
-        <v>1656.133</v>
+        <v>1974.845</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46133.52083333334</v>
+        <v>46134.52083333334</v>
       </c>
       <c r="B148">
-        <v>1645.866</v>
+        <v>1978.148</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46133.53125</v>
+        <v>46134.53125</v>
       </c>
       <c r="B149">
-        <v>1634.58</v>
+        <v>1979.769</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46133.54166666666</v>
+        <v>46134.54166666666</v>
       </c>
       <c r="B150">
-        <v>1628.633</v>
+        <v>1984.791</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46133.55208333334</v>
+        <v>46134.55208333334</v>
       </c>
       <c r="B151">
-        <v>1611.101</v>
+        <v>1974.093</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46133.5625</v>
+        <v>46134.5625</v>
       </c>
       <c r="B152">
-        <v>1588.84</v>
+        <v>1952.668</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46133.57291666666</v>
+        <v>46134.57291666666</v>
       </c>
       <c r="B153">
-        <v>1556.13</v>
+        <v>1923.582</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46133.58333333334</v>
+        <v>46134.58333333334</v>
       </c>
       <c r="B154">
-        <v>1467.948</v>
+        <v>1857.452</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46133.59375</v>
+        <v>46134.59375</v>
       </c>
       <c r="B155">
-        <v>1419.925</v>
+        <v>1806.277</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46133.60416666666</v>
+        <v>46134.60416666666</v>
       </c>
       <c r="B156">
-        <v>1368.665</v>
+        <v>1745.643</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46133.61458333334</v>
+        <v>46134.61458333334</v>
       </c>
       <c r="B157">
-        <v>1322.337</v>
+        <v>1690.303</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46133.625</v>
+        <v>46134.625</v>
       </c>
       <c r="B158">
-        <v>1221.793</v>
+        <v>1586.116</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46133.63541666666</v>
+        <v>46134.63541666666</v>
       </c>
       <c r="B159">
-        <v>1154.026</v>
+        <v>1489.582</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46133.64583333334</v>
+        <v>46134.64583333334</v>
       </c>
       <c r="B160">
-        <v>1087.606</v>
+        <v>1402.071</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46133.65625</v>
+        <v>46134.65625</v>
       </c>
       <c r="B161">
-        <v>1012.211</v>
+        <v>1320.467</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46133.66666666666</v>
+        <v>46134.66666666666</v>
       </c>
       <c r="B162">
-        <v>895.968</v>
+        <v>1185.261</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46133.67708333334</v>
+        <v>46134.67708333334</v>
       </c>
       <c r="B163">
-        <v>806.313</v>
+        <v>1049.354</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46133.6875</v>
+        <v>46134.6875</v>
       </c>
       <c r="B164">
-        <v>719.8339999999999</v>
+        <v>946.377</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46133.69791666666</v>
+        <v>46134.69791666666</v>
       </c>
       <c r="B165">
-        <v>647.595</v>
+        <v>839.8819999999999</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46133.70833333334</v>
+        <v>46134.70833333334</v>
       </c>
       <c r="B166">
-        <v>518.069</v>
+        <v>664.437</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46133.71875</v>
+        <v>46134.71875</v>
       </c>
       <c r="B167">
-        <v>440.295</v>
+        <v>570.655</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46133.72916666666</v>
+        <v>46134.72916666666</v>
       </c>
       <c r="B168">
-        <v>351.856</v>
+        <v>474.545</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46133.73958333334</v>
+        <v>46134.73958333334</v>
       </c>
       <c r="B169">
-        <v>299.578</v>
+        <v>372.27</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46133.75</v>
+        <v>46134.75</v>
       </c>
       <c r="B170">
-        <v>205.453</v>
+        <v>244.617</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46133.76041666666</v>
+        <v>46134.76041666666</v>
       </c>
       <c r="B171">
-        <v>159.332</v>
+        <v>176.072</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46133.77083333334</v>
+        <v>46134.77083333334</v>
       </c>
       <c r="B172">
-        <v>76.60599999999999</v>
+        <v>116.026</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46133.78125</v>
+        <v>46134.78125</v>
       </c>
       <c r="B173">
-        <v>50.974</v>
+        <v>73.11199999999999</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46133.79166666666</v>
+        <v>46134.79166666666</v>
       </c>
       <c r="B174">
-        <v>22.645</v>
+        <v>28.518</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46133.80208333334</v>
+        <v>46134.80208333334</v>
       </c>
       <c r="B175">
-        <v>17.36</v>
+        <v>19.378</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46133.8125</v>
+        <v>46134.8125</v>
       </c>
       <c r="B176">
-        <v>15.969</v>
+        <v>14.253</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46133.82291666666</v>
+        <v>46134.82291666666</v>
       </c>
       <c r="B177">
-        <v>13.738</v>
+        <v>9.646000000000001</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46133.83333333334</v>
+        <v>46134.83333333334</v>
       </c>
       <c r="B178">
-        <v>7.7</v>
+        <v>7.229</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46133.84375</v>
+        <v>46134.84375</v>
       </c>
       <c r="B179">
-        <v>7.412</v>
+        <v>6.929</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46133.85416666666</v>
+        <v>46134.85416666666</v>
       </c>
       <c r="B180">
-        <v>4.362</v>
+        <v>3.859</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46133.86458333334</v>
+        <v>46134.86458333334</v>
       </c>
       <c r="B181">
-        <v>3.73</v>
+        <v>3.259</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46133.875</v>
+        <v>46134.875</v>
       </c>
       <c r="B182">
         <v>2.73</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46133.88541666666</v>
+        <v>46134.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46133.89583333334</v>
+        <v>46134.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46133.90625</v>
+        <v>46134.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46133.91666666666</v>
+        <v>46134.91666666666</v>
       </c>
       <c r="B186">
         <v>1.43</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46133.92708333334</v>
+        <v>46134.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46133.9375</v>
+        <v>46134.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46133.94791666666</v>
+        <v>46134.94791666666</v>
       </c>
       <c r="B189">
         <v>0.73</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46133.95833333334</v>
+        <v>46134.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46133.96875</v>
+        <v>46134.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46133.97916666666</v>
+        <v>46134.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46133.98958333334</v>
+        <v>46134.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,580 +31,1156 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.04.20261</t>
-  </si>
-  <si>
-    <t>21.04.20262</t>
-  </si>
-  <si>
-    <t>21.04.20263</t>
-  </si>
-  <si>
-    <t>21.04.20264</t>
-  </si>
-  <si>
-    <t>21.04.20265</t>
-  </si>
-  <si>
-    <t>21.04.20266</t>
-  </si>
-  <si>
-    <t>21.04.20267</t>
-  </si>
-  <si>
-    <t>21.04.20268</t>
-  </si>
-  <si>
-    <t>21.04.20269</t>
-  </si>
-  <si>
-    <t>21.04.202610</t>
-  </si>
-  <si>
-    <t>21.04.202611</t>
-  </si>
-  <si>
-    <t>21.04.202612</t>
-  </si>
-  <si>
-    <t>21.04.202613</t>
-  </si>
-  <si>
-    <t>21.04.202614</t>
-  </si>
-  <si>
-    <t>21.04.202615</t>
-  </si>
-  <si>
-    <t>21.04.202616</t>
-  </si>
-  <si>
-    <t>21.04.202617</t>
-  </si>
-  <si>
-    <t>21.04.202618</t>
-  </si>
-  <si>
-    <t>21.04.202619</t>
-  </si>
-  <si>
-    <t>21.04.202620</t>
-  </si>
-  <si>
-    <t>21.04.202621</t>
-  </si>
-  <si>
-    <t>21.04.202622</t>
-  </si>
-  <si>
-    <t>21.04.202623</t>
-  </si>
-  <si>
-    <t>21.04.202624</t>
-  </si>
-  <si>
-    <t>21.04.202625</t>
-  </si>
-  <si>
-    <t>21.04.202626</t>
-  </si>
-  <si>
-    <t>21.04.202627</t>
-  </si>
-  <si>
-    <t>21.04.202628</t>
-  </si>
-  <si>
-    <t>21.04.202629</t>
-  </si>
-  <si>
-    <t>21.04.202630</t>
-  </si>
-  <si>
-    <t>21.04.202631</t>
-  </si>
-  <si>
-    <t>21.04.202632</t>
-  </si>
-  <si>
-    <t>21.04.202633</t>
-  </si>
-  <si>
-    <t>21.04.202634</t>
-  </si>
-  <si>
-    <t>21.04.202635</t>
-  </si>
-  <si>
-    <t>21.04.202636</t>
-  </si>
-  <si>
-    <t>21.04.202637</t>
-  </si>
-  <si>
-    <t>21.04.202638</t>
-  </si>
-  <si>
-    <t>21.04.202639</t>
-  </si>
-  <si>
-    <t>21.04.202640</t>
-  </si>
-  <si>
-    <t>21.04.202641</t>
-  </si>
-  <si>
-    <t>21.04.202642</t>
-  </si>
-  <si>
-    <t>21.04.202643</t>
-  </si>
-  <si>
-    <t>21.04.202644</t>
-  </si>
-  <si>
-    <t>21.04.202645</t>
-  </si>
-  <si>
-    <t>21.04.202646</t>
-  </si>
-  <si>
-    <t>21.04.202647</t>
-  </si>
-  <si>
-    <t>21.04.202648</t>
-  </si>
-  <si>
-    <t>21.04.202649</t>
-  </si>
-  <si>
-    <t>21.04.202650</t>
-  </si>
-  <si>
-    <t>21.04.202651</t>
-  </si>
-  <si>
-    <t>21.04.202652</t>
-  </si>
-  <si>
-    <t>21.04.202653</t>
-  </si>
-  <si>
-    <t>21.04.202654</t>
-  </si>
-  <si>
-    <t>21.04.202655</t>
-  </si>
-  <si>
-    <t>21.04.202656</t>
-  </si>
-  <si>
-    <t>21.04.202657</t>
-  </si>
-  <si>
-    <t>21.04.202658</t>
-  </si>
-  <si>
-    <t>21.04.202659</t>
-  </si>
-  <si>
-    <t>21.04.202660</t>
-  </si>
-  <si>
-    <t>21.04.202661</t>
-  </si>
-  <si>
-    <t>21.04.202662</t>
-  </si>
-  <si>
-    <t>21.04.202663</t>
-  </si>
-  <si>
-    <t>21.04.202664</t>
-  </si>
-  <si>
-    <t>21.04.202665</t>
-  </si>
-  <si>
-    <t>21.04.202666</t>
-  </si>
-  <si>
-    <t>21.04.202667</t>
-  </si>
-  <si>
-    <t>21.04.202668</t>
-  </si>
-  <si>
-    <t>21.04.202669</t>
-  </si>
-  <si>
-    <t>21.04.202670</t>
-  </si>
-  <si>
-    <t>21.04.202671</t>
-  </si>
-  <si>
-    <t>21.04.202672</t>
-  </si>
-  <si>
-    <t>21.04.202673</t>
-  </si>
-  <si>
-    <t>21.04.202674</t>
-  </si>
-  <si>
-    <t>21.04.202675</t>
-  </si>
-  <si>
-    <t>21.04.202676</t>
-  </si>
-  <si>
-    <t>21.04.202677</t>
-  </si>
-  <si>
-    <t>21.04.202678</t>
-  </si>
-  <si>
-    <t>21.04.202679</t>
-  </si>
-  <si>
-    <t>21.04.202680</t>
-  </si>
-  <si>
-    <t>21.04.202681</t>
-  </si>
-  <si>
-    <t>21.04.202682</t>
-  </si>
-  <si>
-    <t>21.04.202683</t>
-  </si>
-  <si>
-    <t>21.04.202684</t>
-  </si>
-  <si>
-    <t>21.04.202685</t>
-  </si>
-  <si>
-    <t>21.04.202686</t>
-  </si>
-  <si>
-    <t>21.04.202687</t>
-  </si>
-  <si>
-    <t>21.04.202688</t>
-  </si>
-  <si>
-    <t>21.04.202689</t>
-  </si>
-  <si>
-    <t>21.04.202690</t>
-  </si>
-  <si>
-    <t>21.04.202691</t>
-  </si>
-  <si>
-    <t>21.04.202692</t>
-  </si>
-  <si>
-    <t>21.04.202693</t>
-  </si>
-  <si>
-    <t>21.04.202694</t>
-  </si>
-  <si>
-    <t>21.04.202695</t>
-  </si>
-  <si>
-    <t>21.04.202696</t>
-  </si>
-  <si>
-    <t>22.04.20261</t>
-  </si>
-  <si>
-    <t>22.04.20262</t>
-  </si>
-  <si>
-    <t>22.04.20263</t>
-  </si>
-  <si>
-    <t>22.04.20264</t>
-  </si>
-  <si>
-    <t>22.04.20265</t>
-  </si>
-  <si>
-    <t>22.04.20266</t>
-  </si>
-  <si>
-    <t>22.04.20267</t>
-  </si>
-  <si>
-    <t>22.04.20268</t>
-  </si>
-  <si>
-    <t>22.04.20269</t>
-  </si>
-  <si>
-    <t>22.04.202610</t>
-  </si>
-  <si>
-    <t>22.04.202611</t>
-  </si>
-  <si>
-    <t>22.04.202612</t>
-  </si>
-  <si>
-    <t>22.04.202613</t>
-  </si>
-  <si>
-    <t>22.04.202614</t>
-  </si>
-  <si>
-    <t>22.04.202615</t>
-  </si>
-  <si>
-    <t>22.04.202616</t>
-  </si>
-  <si>
-    <t>22.04.202617</t>
-  </si>
-  <si>
-    <t>22.04.202618</t>
-  </si>
-  <si>
-    <t>22.04.202619</t>
-  </si>
-  <si>
-    <t>22.04.202620</t>
-  </si>
-  <si>
-    <t>22.04.202621</t>
-  </si>
-  <si>
-    <t>22.04.202622</t>
-  </si>
-  <si>
-    <t>22.04.202623</t>
-  </si>
-  <si>
-    <t>22.04.202624</t>
-  </si>
-  <si>
-    <t>22.04.202625</t>
-  </si>
-  <si>
-    <t>22.04.202626</t>
-  </si>
-  <si>
-    <t>22.04.202627</t>
-  </si>
-  <si>
-    <t>22.04.202628</t>
-  </si>
-  <si>
-    <t>22.04.202629</t>
-  </si>
-  <si>
-    <t>22.04.202630</t>
-  </si>
-  <si>
-    <t>22.04.202631</t>
-  </si>
-  <si>
-    <t>22.04.202632</t>
-  </si>
-  <si>
-    <t>22.04.202633</t>
-  </si>
-  <si>
-    <t>22.04.202634</t>
-  </si>
-  <si>
-    <t>22.04.202635</t>
-  </si>
-  <si>
-    <t>22.04.202636</t>
-  </si>
-  <si>
-    <t>22.04.202637</t>
-  </si>
-  <si>
-    <t>22.04.202638</t>
-  </si>
-  <si>
-    <t>22.04.202639</t>
-  </si>
-  <si>
-    <t>22.04.202640</t>
-  </si>
-  <si>
-    <t>22.04.202641</t>
-  </si>
-  <si>
-    <t>22.04.202642</t>
-  </si>
-  <si>
-    <t>22.04.202643</t>
-  </si>
-  <si>
-    <t>22.04.202644</t>
-  </si>
-  <si>
-    <t>22.04.202645</t>
-  </si>
-  <si>
-    <t>22.04.202646</t>
-  </si>
-  <si>
-    <t>22.04.202647</t>
-  </si>
-  <si>
-    <t>22.04.202648</t>
-  </si>
-  <si>
-    <t>22.04.202649</t>
-  </si>
-  <si>
-    <t>22.04.202650</t>
-  </si>
-  <si>
-    <t>22.04.202651</t>
-  </si>
-  <si>
-    <t>22.04.202652</t>
-  </si>
-  <si>
-    <t>22.04.202653</t>
-  </si>
-  <si>
-    <t>22.04.202654</t>
-  </si>
-  <si>
-    <t>22.04.202655</t>
-  </si>
-  <si>
-    <t>22.04.202656</t>
-  </si>
-  <si>
-    <t>22.04.202657</t>
-  </si>
-  <si>
-    <t>22.04.202658</t>
-  </si>
-  <si>
-    <t>22.04.202659</t>
-  </si>
-  <si>
-    <t>22.04.202660</t>
-  </si>
-  <si>
-    <t>22.04.202661</t>
-  </si>
-  <si>
-    <t>22.04.202662</t>
-  </si>
-  <si>
-    <t>22.04.202663</t>
-  </si>
-  <si>
-    <t>22.04.202664</t>
-  </si>
-  <si>
-    <t>22.04.202665</t>
-  </si>
-  <si>
-    <t>22.04.202666</t>
-  </si>
-  <si>
-    <t>22.04.202667</t>
-  </si>
-  <si>
-    <t>22.04.202668</t>
-  </si>
-  <si>
-    <t>22.04.202669</t>
-  </si>
-  <si>
-    <t>22.04.202670</t>
-  </si>
-  <si>
-    <t>22.04.202671</t>
-  </si>
-  <si>
-    <t>22.04.202672</t>
-  </si>
-  <si>
-    <t>22.04.202673</t>
-  </si>
-  <si>
-    <t>22.04.202674</t>
-  </si>
-  <si>
-    <t>22.04.202675</t>
-  </si>
-  <si>
-    <t>22.04.202676</t>
-  </si>
-  <si>
-    <t>22.04.202677</t>
-  </si>
-  <si>
-    <t>22.04.202678</t>
-  </si>
-  <si>
-    <t>22.04.202679</t>
-  </si>
-  <si>
-    <t>22.04.202680</t>
-  </si>
-  <si>
-    <t>22.04.202681</t>
-  </si>
-  <si>
-    <t>22.04.202682</t>
-  </si>
-  <si>
-    <t>22.04.202683</t>
-  </si>
-  <si>
-    <t>22.04.202684</t>
-  </si>
-  <si>
-    <t>22.04.202685</t>
-  </si>
-  <si>
-    <t>22.04.202686</t>
-  </si>
-  <si>
-    <t>22.04.202687</t>
-  </si>
-  <si>
-    <t>22.04.202688</t>
-  </si>
-  <si>
-    <t>22.04.202689</t>
-  </si>
-  <si>
-    <t>22.04.202690</t>
-  </si>
-  <si>
-    <t>22.04.202691</t>
-  </si>
-  <si>
-    <t>22.04.202692</t>
-  </si>
-  <si>
-    <t>22.04.202693</t>
-  </si>
-  <si>
-    <t>22.04.202694</t>
-  </si>
-  <si>
-    <t>22.04.202695</t>
-  </si>
-  <si>
-    <t>22.04.202696</t>
+    <t>24.04.20261</t>
+  </si>
+  <si>
+    <t>24.04.20262</t>
+  </si>
+  <si>
+    <t>24.04.20263</t>
+  </si>
+  <si>
+    <t>24.04.20264</t>
+  </si>
+  <si>
+    <t>24.04.20265</t>
+  </si>
+  <si>
+    <t>24.04.20266</t>
+  </si>
+  <si>
+    <t>24.04.20267</t>
+  </si>
+  <si>
+    <t>24.04.20268</t>
+  </si>
+  <si>
+    <t>24.04.20269</t>
+  </si>
+  <si>
+    <t>24.04.202610</t>
+  </si>
+  <si>
+    <t>24.04.202611</t>
+  </si>
+  <si>
+    <t>24.04.202612</t>
+  </si>
+  <si>
+    <t>24.04.202613</t>
+  </si>
+  <si>
+    <t>24.04.202614</t>
+  </si>
+  <si>
+    <t>24.04.202615</t>
+  </si>
+  <si>
+    <t>24.04.202616</t>
+  </si>
+  <si>
+    <t>24.04.202617</t>
+  </si>
+  <si>
+    <t>24.04.202618</t>
+  </si>
+  <si>
+    <t>24.04.202619</t>
+  </si>
+  <si>
+    <t>24.04.202620</t>
+  </si>
+  <si>
+    <t>24.04.202621</t>
+  </si>
+  <si>
+    <t>24.04.202622</t>
+  </si>
+  <si>
+    <t>24.04.202623</t>
+  </si>
+  <si>
+    <t>24.04.202624</t>
+  </si>
+  <si>
+    <t>24.04.202625</t>
+  </si>
+  <si>
+    <t>24.04.202626</t>
+  </si>
+  <si>
+    <t>24.04.202627</t>
+  </si>
+  <si>
+    <t>24.04.202628</t>
+  </si>
+  <si>
+    <t>24.04.202629</t>
+  </si>
+  <si>
+    <t>24.04.202630</t>
+  </si>
+  <si>
+    <t>24.04.202631</t>
+  </si>
+  <si>
+    <t>24.04.202632</t>
+  </si>
+  <si>
+    <t>24.04.202633</t>
+  </si>
+  <si>
+    <t>24.04.202634</t>
+  </si>
+  <si>
+    <t>24.04.202635</t>
+  </si>
+  <si>
+    <t>24.04.202636</t>
+  </si>
+  <si>
+    <t>24.04.202637</t>
+  </si>
+  <si>
+    <t>24.04.202638</t>
+  </si>
+  <si>
+    <t>24.04.202639</t>
+  </si>
+  <si>
+    <t>24.04.202640</t>
+  </si>
+  <si>
+    <t>24.04.202641</t>
+  </si>
+  <si>
+    <t>24.04.202642</t>
+  </si>
+  <si>
+    <t>24.04.202643</t>
+  </si>
+  <si>
+    <t>24.04.202644</t>
+  </si>
+  <si>
+    <t>24.04.202645</t>
+  </si>
+  <si>
+    <t>24.04.202646</t>
+  </si>
+  <si>
+    <t>24.04.202647</t>
+  </si>
+  <si>
+    <t>24.04.202648</t>
+  </si>
+  <si>
+    <t>24.04.202649</t>
+  </si>
+  <si>
+    <t>24.04.202650</t>
+  </si>
+  <si>
+    <t>24.04.202651</t>
+  </si>
+  <si>
+    <t>24.04.202652</t>
+  </si>
+  <si>
+    <t>24.04.202653</t>
+  </si>
+  <si>
+    <t>24.04.202654</t>
+  </si>
+  <si>
+    <t>24.04.202655</t>
+  </si>
+  <si>
+    <t>24.04.202656</t>
+  </si>
+  <si>
+    <t>24.04.202657</t>
+  </si>
+  <si>
+    <t>24.04.202658</t>
+  </si>
+  <si>
+    <t>24.04.202659</t>
+  </si>
+  <si>
+    <t>24.04.202660</t>
+  </si>
+  <si>
+    <t>24.04.202661</t>
+  </si>
+  <si>
+    <t>24.04.202662</t>
+  </si>
+  <si>
+    <t>24.04.202663</t>
+  </si>
+  <si>
+    <t>24.04.202664</t>
+  </si>
+  <si>
+    <t>24.04.202665</t>
+  </si>
+  <si>
+    <t>24.04.202666</t>
+  </si>
+  <si>
+    <t>24.04.202667</t>
+  </si>
+  <si>
+    <t>24.04.202668</t>
+  </si>
+  <si>
+    <t>24.04.202669</t>
+  </si>
+  <si>
+    <t>24.04.202670</t>
+  </si>
+  <si>
+    <t>24.04.202671</t>
+  </si>
+  <si>
+    <t>24.04.202672</t>
+  </si>
+  <si>
+    <t>24.04.202673</t>
+  </si>
+  <si>
+    <t>24.04.202674</t>
+  </si>
+  <si>
+    <t>24.04.202675</t>
+  </si>
+  <si>
+    <t>24.04.202676</t>
+  </si>
+  <si>
+    <t>24.04.202677</t>
+  </si>
+  <si>
+    <t>24.04.202678</t>
+  </si>
+  <si>
+    <t>24.04.202679</t>
+  </si>
+  <si>
+    <t>24.04.202680</t>
+  </si>
+  <si>
+    <t>24.04.202681</t>
+  </si>
+  <si>
+    <t>24.04.202682</t>
+  </si>
+  <si>
+    <t>24.04.202683</t>
+  </si>
+  <si>
+    <t>24.04.202684</t>
+  </si>
+  <si>
+    <t>24.04.202685</t>
+  </si>
+  <si>
+    <t>24.04.202686</t>
+  </si>
+  <si>
+    <t>24.04.202687</t>
+  </si>
+  <si>
+    <t>24.04.202688</t>
+  </si>
+  <si>
+    <t>24.04.202689</t>
+  </si>
+  <si>
+    <t>24.04.202690</t>
+  </si>
+  <si>
+    <t>24.04.202691</t>
+  </si>
+  <si>
+    <t>24.04.202692</t>
+  </si>
+  <si>
+    <t>24.04.202693</t>
+  </si>
+  <si>
+    <t>24.04.202694</t>
+  </si>
+  <si>
+    <t>24.04.202695</t>
+  </si>
+  <si>
+    <t>24.04.202696</t>
+  </si>
+  <si>
+    <t>25.04.20261</t>
+  </si>
+  <si>
+    <t>25.04.20262</t>
+  </si>
+  <si>
+    <t>25.04.20263</t>
+  </si>
+  <si>
+    <t>25.04.20264</t>
+  </si>
+  <si>
+    <t>25.04.20265</t>
+  </si>
+  <si>
+    <t>25.04.20266</t>
+  </si>
+  <si>
+    <t>25.04.20267</t>
+  </si>
+  <si>
+    <t>25.04.20268</t>
+  </si>
+  <si>
+    <t>25.04.20269</t>
+  </si>
+  <si>
+    <t>25.04.202610</t>
+  </si>
+  <si>
+    <t>25.04.202611</t>
+  </si>
+  <si>
+    <t>25.04.202612</t>
+  </si>
+  <si>
+    <t>25.04.202613</t>
+  </si>
+  <si>
+    <t>25.04.202614</t>
+  </si>
+  <si>
+    <t>25.04.202615</t>
+  </si>
+  <si>
+    <t>25.04.202616</t>
+  </si>
+  <si>
+    <t>25.04.202617</t>
+  </si>
+  <si>
+    <t>25.04.202618</t>
+  </si>
+  <si>
+    <t>25.04.202619</t>
+  </si>
+  <si>
+    <t>25.04.202620</t>
+  </si>
+  <si>
+    <t>25.04.202621</t>
+  </si>
+  <si>
+    <t>25.04.202622</t>
+  </si>
+  <si>
+    <t>25.04.202623</t>
+  </si>
+  <si>
+    <t>25.04.202624</t>
+  </si>
+  <si>
+    <t>25.04.202625</t>
+  </si>
+  <si>
+    <t>25.04.202626</t>
+  </si>
+  <si>
+    <t>25.04.202627</t>
+  </si>
+  <si>
+    <t>25.04.202628</t>
+  </si>
+  <si>
+    <t>25.04.202629</t>
+  </si>
+  <si>
+    <t>25.04.202630</t>
+  </si>
+  <si>
+    <t>25.04.202631</t>
+  </si>
+  <si>
+    <t>25.04.202632</t>
+  </si>
+  <si>
+    <t>25.04.202633</t>
+  </si>
+  <si>
+    <t>25.04.202634</t>
+  </si>
+  <si>
+    <t>25.04.202635</t>
+  </si>
+  <si>
+    <t>25.04.202636</t>
+  </si>
+  <si>
+    <t>25.04.202637</t>
+  </si>
+  <si>
+    <t>25.04.202638</t>
+  </si>
+  <si>
+    <t>25.04.202639</t>
+  </si>
+  <si>
+    <t>25.04.202640</t>
+  </si>
+  <si>
+    <t>25.04.202641</t>
+  </si>
+  <si>
+    <t>25.04.202642</t>
+  </si>
+  <si>
+    <t>25.04.202643</t>
+  </si>
+  <si>
+    <t>25.04.202644</t>
+  </si>
+  <si>
+    <t>25.04.202645</t>
+  </si>
+  <si>
+    <t>25.04.202646</t>
+  </si>
+  <si>
+    <t>25.04.202647</t>
+  </si>
+  <si>
+    <t>25.04.202648</t>
+  </si>
+  <si>
+    <t>25.04.202649</t>
+  </si>
+  <si>
+    <t>25.04.202650</t>
+  </si>
+  <si>
+    <t>25.04.202651</t>
+  </si>
+  <si>
+    <t>25.04.202652</t>
+  </si>
+  <si>
+    <t>25.04.202653</t>
+  </si>
+  <si>
+    <t>25.04.202654</t>
+  </si>
+  <si>
+    <t>25.04.202655</t>
+  </si>
+  <si>
+    <t>25.04.202656</t>
+  </si>
+  <si>
+    <t>25.04.202657</t>
+  </si>
+  <si>
+    <t>25.04.202658</t>
+  </si>
+  <si>
+    <t>25.04.202659</t>
+  </si>
+  <si>
+    <t>25.04.202660</t>
+  </si>
+  <si>
+    <t>25.04.202661</t>
+  </si>
+  <si>
+    <t>25.04.202662</t>
+  </si>
+  <si>
+    <t>25.04.202663</t>
+  </si>
+  <si>
+    <t>25.04.202664</t>
+  </si>
+  <si>
+    <t>25.04.202665</t>
+  </si>
+  <si>
+    <t>25.04.202666</t>
+  </si>
+  <si>
+    <t>25.04.202667</t>
+  </si>
+  <si>
+    <t>25.04.202668</t>
+  </si>
+  <si>
+    <t>25.04.202669</t>
+  </si>
+  <si>
+    <t>25.04.202670</t>
+  </si>
+  <si>
+    <t>25.04.202671</t>
+  </si>
+  <si>
+    <t>25.04.202672</t>
+  </si>
+  <si>
+    <t>25.04.202673</t>
+  </si>
+  <si>
+    <t>25.04.202674</t>
+  </si>
+  <si>
+    <t>25.04.202675</t>
+  </si>
+  <si>
+    <t>25.04.202676</t>
+  </si>
+  <si>
+    <t>25.04.202677</t>
+  </si>
+  <si>
+    <t>25.04.202678</t>
+  </si>
+  <si>
+    <t>25.04.202679</t>
+  </si>
+  <si>
+    <t>25.04.202680</t>
+  </si>
+  <si>
+    <t>25.04.202681</t>
+  </si>
+  <si>
+    <t>25.04.202682</t>
+  </si>
+  <si>
+    <t>25.04.202683</t>
+  </si>
+  <si>
+    <t>25.04.202684</t>
+  </si>
+  <si>
+    <t>25.04.202685</t>
+  </si>
+  <si>
+    <t>25.04.202686</t>
+  </si>
+  <si>
+    <t>25.04.202687</t>
+  </si>
+  <si>
+    <t>25.04.202688</t>
+  </si>
+  <si>
+    <t>25.04.202689</t>
+  </si>
+  <si>
+    <t>25.04.202690</t>
+  </si>
+  <si>
+    <t>25.04.202691</t>
+  </si>
+  <si>
+    <t>25.04.202692</t>
+  </si>
+  <si>
+    <t>25.04.202693</t>
+  </si>
+  <si>
+    <t>25.04.202694</t>
+  </si>
+  <si>
+    <t>25.04.202695</t>
+  </si>
+  <si>
+    <t>25.04.202696</t>
+  </si>
+  <si>
+    <t>26.04.20261</t>
+  </si>
+  <si>
+    <t>26.04.20262</t>
+  </si>
+  <si>
+    <t>26.04.20263</t>
+  </si>
+  <si>
+    <t>26.04.20264</t>
+  </si>
+  <si>
+    <t>26.04.20265</t>
+  </si>
+  <si>
+    <t>26.04.20266</t>
+  </si>
+  <si>
+    <t>26.04.20267</t>
+  </si>
+  <si>
+    <t>26.04.20268</t>
+  </si>
+  <si>
+    <t>26.04.20269</t>
+  </si>
+  <si>
+    <t>26.04.202610</t>
+  </si>
+  <si>
+    <t>26.04.202611</t>
+  </si>
+  <si>
+    <t>26.04.202612</t>
+  </si>
+  <si>
+    <t>26.04.202613</t>
+  </si>
+  <si>
+    <t>26.04.202614</t>
+  </si>
+  <si>
+    <t>26.04.202615</t>
+  </si>
+  <si>
+    <t>26.04.202616</t>
+  </si>
+  <si>
+    <t>26.04.202617</t>
+  </si>
+  <si>
+    <t>26.04.202618</t>
+  </si>
+  <si>
+    <t>26.04.202619</t>
+  </si>
+  <si>
+    <t>26.04.202620</t>
+  </si>
+  <si>
+    <t>26.04.202621</t>
+  </si>
+  <si>
+    <t>26.04.202622</t>
+  </si>
+  <si>
+    <t>26.04.202623</t>
+  </si>
+  <si>
+    <t>26.04.202624</t>
+  </si>
+  <si>
+    <t>26.04.202625</t>
+  </si>
+  <si>
+    <t>26.04.202626</t>
+  </si>
+  <si>
+    <t>26.04.202627</t>
+  </si>
+  <si>
+    <t>26.04.202628</t>
+  </si>
+  <si>
+    <t>26.04.202629</t>
+  </si>
+  <si>
+    <t>26.04.202630</t>
+  </si>
+  <si>
+    <t>26.04.202631</t>
+  </si>
+  <si>
+    <t>26.04.202632</t>
+  </si>
+  <si>
+    <t>26.04.202633</t>
+  </si>
+  <si>
+    <t>26.04.202634</t>
+  </si>
+  <si>
+    <t>26.04.202635</t>
+  </si>
+  <si>
+    <t>26.04.202636</t>
+  </si>
+  <si>
+    <t>26.04.202637</t>
+  </si>
+  <si>
+    <t>26.04.202638</t>
+  </si>
+  <si>
+    <t>26.04.202639</t>
+  </si>
+  <si>
+    <t>26.04.202640</t>
+  </si>
+  <si>
+    <t>26.04.202641</t>
+  </si>
+  <si>
+    <t>26.04.202642</t>
+  </si>
+  <si>
+    <t>26.04.202643</t>
+  </si>
+  <si>
+    <t>26.04.202644</t>
+  </si>
+  <si>
+    <t>26.04.202645</t>
+  </si>
+  <si>
+    <t>26.04.202646</t>
+  </si>
+  <si>
+    <t>26.04.202647</t>
+  </si>
+  <si>
+    <t>26.04.202648</t>
+  </si>
+  <si>
+    <t>26.04.202649</t>
+  </si>
+  <si>
+    <t>26.04.202650</t>
+  </si>
+  <si>
+    <t>26.04.202651</t>
+  </si>
+  <si>
+    <t>26.04.202652</t>
+  </si>
+  <si>
+    <t>26.04.202653</t>
+  </si>
+  <si>
+    <t>26.04.202654</t>
+  </si>
+  <si>
+    <t>26.04.202655</t>
+  </si>
+  <si>
+    <t>26.04.202656</t>
+  </si>
+  <si>
+    <t>26.04.202657</t>
+  </si>
+  <si>
+    <t>26.04.202658</t>
+  </si>
+  <si>
+    <t>26.04.202659</t>
+  </si>
+  <si>
+    <t>26.04.202660</t>
+  </si>
+  <si>
+    <t>26.04.202661</t>
+  </si>
+  <si>
+    <t>26.04.202662</t>
+  </si>
+  <si>
+    <t>26.04.202663</t>
+  </si>
+  <si>
+    <t>26.04.202664</t>
+  </si>
+  <si>
+    <t>26.04.202665</t>
+  </si>
+  <si>
+    <t>26.04.202666</t>
+  </si>
+  <si>
+    <t>26.04.202667</t>
+  </si>
+  <si>
+    <t>26.04.202668</t>
+  </si>
+  <si>
+    <t>26.04.202669</t>
+  </si>
+  <si>
+    <t>26.04.202670</t>
+  </si>
+  <si>
+    <t>26.04.202671</t>
+  </si>
+  <si>
+    <t>26.04.202672</t>
+  </si>
+  <si>
+    <t>26.04.202673</t>
+  </si>
+  <si>
+    <t>26.04.202674</t>
+  </si>
+  <si>
+    <t>26.04.202675</t>
+  </si>
+  <si>
+    <t>26.04.202676</t>
+  </si>
+  <si>
+    <t>26.04.202677</t>
+  </si>
+  <si>
+    <t>26.04.202678</t>
+  </si>
+  <si>
+    <t>26.04.202679</t>
+  </si>
+  <si>
+    <t>26.04.202680</t>
+  </si>
+  <si>
+    <t>26.04.202681</t>
+  </si>
+  <si>
+    <t>26.04.202682</t>
+  </si>
+  <si>
+    <t>26.04.202683</t>
+  </si>
+  <si>
+    <t>26.04.202684</t>
+  </si>
+  <si>
+    <t>26.04.202685</t>
+  </si>
+  <si>
+    <t>26.04.202686</t>
+  </si>
+  <si>
+    <t>26.04.202687</t>
+  </si>
+  <si>
+    <t>26.04.202688</t>
+  </si>
+  <si>
+    <t>26.04.202689</t>
+  </si>
+  <si>
+    <t>26.04.202690</t>
+  </si>
+  <si>
+    <t>26.04.202691</t>
+  </si>
+  <si>
+    <t>26.04.202692</t>
+  </si>
+  <si>
+    <t>26.04.202693</t>
+  </si>
+  <si>
+    <t>26.04.202694</t>
+  </si>
+  <si>
+    <t>26.04.202695</t>
+  </si>
+  <si>
+    <t>26.04.202696</t>
+  </si>
+  <si>
+    <t>27.04.20261</t>
+  </si>
+  <si>
+    <t>27.04.20262</t>
+  </si>
+  <si>
+    <t>27.04.20263</t>
+  </si>
+  <si>
+    <t>27.04.20264</t>
+  </si>
+  <si>
+    <t>27.04.20265</t>
+  </si>
+  <si>
+    <t>27.04.20266</t>
+  </si>
+  <si>
+    <t>27.04.20267</t>
+  </si>
+  <si>
+    <t>27.04.20268</t>
+  </si>
+  <si>
+    <t>27.04.20269</t>
+  </si>
+  <si>
+    <t>27.04.202610</t>
+  </si>
+  <si>
+    <t>27.04.202611</t>
+  </si>
+  <si>
+    <t>27.04.202612</t>
+  </si>
+  <si>
+    <t>27.04.202613</t>
+  </si>
+  <si>
+    <t>27.04.202614</t>
+  </si>
+  <si>
+    <t>27.04.202615</t>
+  </si>
+  <si>
+    <t>27.04.202616</t>
+  </si>
+  <si>
+    <t>27.04.202617</t>
+  </si>
+  <si>
+    <t>27.04.202618</t>
+  </si>
+  <si>
+    <t>27.04.202619</t>
+  </si>
+  <si>
+    <t>27.04.202620</t>
+  </si>
+  <si>
+    <t>27.04.202621</t>
+  </si>
+  <si>
+    <t>27.04.202622</t>
+  </si>
+  <si>
+    <t>27.04.202623</t>
+  </si>
+  <si>
+    <t>27.04.202624</t>
+  </si>
+  <si>
+    <t>27.04.202625</t>
+  </si>
+  <si>
+    <t>27.04.202626</t>
+  </si>
+  <si>
+    <t>27.04.202627</t>
+  </si>
+  <si>
+    <t>27.04.202628</t>
+  </si>
+  <si>
+    <t>27.04.202629</t>
+  </si>
+  <si>
+    <t>27.04.202630</t>
+  </si>
+  <si>
+    <t>27.04.202631</t>
+  </si>
+  <si>
+    <t>27.04.202632</t>
+  </si>
+  <si>
+    <t>27.04.202633</t>
+  </si>
+  <si>
+    <t>27.04.202634</t>
+  </si>
+  <si>
+    <t>27.04.202635</t>
+  </si>
+  <si>
+    <t>27.04.202636</t>
+  </si>
+  <si>
+    <t>27.04.202637</t>
+  </si>
+  <si>
+    <t>27.04.202638</t>
+  </si>
+  <si>
+    <t>27.04.202639</t>
+  </si>
+  <si>
+    <t>27.04.202640</t>
+  </si>
+  <si>
+    <t>27.04.202641</t>
+  </si>
+  <si>
+    <t>27.04.202642</t>
+  </si>
+  <si>
+    <t>27.04.202643</t>
+  </si>
+  <si>
+    <t>27.04.202644</t>
+  </si>
+  <si>
+    <t>27.04.202645</t>
+  </si>
+  <si>
+    <t>27.04.202646</t>
+  </si>
+  <si>
+    <t>27.04.202647</t>
+  </si>
+  <si>
+    <t>27.04.202648</t>
+  </si>
+  <si>
+    <t>27.04.202649</t>
+  </si>
+  <si>
+    <t>27.04.202650</t>
+  </si>
+  <si>
+    <t>27.04.202651</t>
+  </si>
+  <si>
+    <t>27.04.202652</t>
+  </si>
+  <si>
+    <t>27.04.202653</t>
+  </si>
+  <si>
+    <t>27.04.202654</t>
+  </si>
+  <si>
+    <t>27.04.202655</t>
+  </si>
+  <si>
+    <t>27.04.202656</t>
+  </si>
+  <si>
+    <t>27.04.202657</t>
+  </si>
+  <si>
+    <t>27.04.202658</t>
+  </si>
+  <si>
+    <t>27.04.202659</t>
+  </si>
+  <si>
+    <t>27.04.202660</t>
+  </si>
+  <si>
+    <t>27.04.202661</t>
+  </si>
+  <si>
+    <t>27.04.202662</t>
+  </si>
+  <si>
+    <t>27.04.202663</t>
+  </si>
+  <si>
+    <t>27.04.202664</t>
+  </si>
+  <si>
+    <t>27.04.202665</t>
+  </si>
+  <si>
+    <t>27.04.202666</t>
+  </si>
+  <si>
+    <t>27.04.202667</t>
+  </si>
+  <si>
+    <t>27.04.202668</t>
+  </si>
+  <si>
+    <t>27.04.202669</t>
+  </si>
+  <si>
+    <t>27.04.202670</t>
+  </si>
+  <si>
+    <t>27.04.202671</t>
+  </si>
+  <si>
+    <t>27.04.202672</t>
+  </si>
+  <si>
+    <t>27.04.202673</t>
+  </si>
+  <si>
+    <t>27.04.202674</t>
+  </si>
+  <si>
+    <t>27.04.202675</t>
+  </si>
+  <si>
+    <t>27.04.202676</t>
+  </si>
+  <si>
+    <t>27.04.202677</t>
+  </si>
+  <si>
+    <t>27.04.202678</t>
+  </si>
+  <si>
+    <t>27.04.202679</t>
+  </si>
+  <si>
+    <t>27.04.202680</t>
+  </si>
+  <si>
+    <t>27.04.202681</t>
+  </si>
+  <si>
+    <t>27.04.202682</t>
+  </si>
+  <si>
+    <t>27.04.202683</t>
+  </si>
+  <si>
+    <t>27.04.202684</t>
+  </si>
+  <si>
+    <t>27.04.202685</t>
+  </si>
+  <si>
+    <t>27.04.202686</t>
+  </si>
+  <si>
+    <t>27.04.202687</t>
+  </si>
+  <si>
+    <t>27.04.202688</t>
+  </si>
+  <si>
+    <t>27.04.202689</t>
+  </si>
+  <si>
+    <t>27.04.202690</t>
+  </si>
+  <si>
+    <t>27.04.202691</t>
+  </si>
+  <si>
+    <t>27.04.202692</t>
+  </si>
+  <si>
+    <t>27.04.202693</t>
+  </si>
+  <si>
+    <t>27.04.202694</t>
+  </si>
+  <si>
+    <t>27.04.202695</t>
+  </si>
+  <si>
+    <t>27.04.202696</t>
   </si>
 </sst>
 </file>
@@ -966,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -988,10 +1564,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B2">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1005,7 +1581,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46133.01041666666</v>
+        <v>46136.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1598,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46133.02083333334</v>
+        <v>46136.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1615,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46133.03125</v>
+        <v>46136.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1632,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46133.04166666666</v>
+        <v>46136.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1649,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46133.05208333334</v>
+        <v>46136.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1666,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46133.0625</v>
+        <v>46136.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1683,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46133.07291666666</v>
+        <v>46136.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1700,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46133.08333333334</v>
+        <v>46136.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1717,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46133.09375</v>
+        <v>46136.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1734,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46133.10416666666</v>
+        <v>46136.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1751,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46133.11458333334</v>
+        <v>46136.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,10 +1768,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46133.125</v>
+        <v>46136.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.905</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,7 +1785,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46133.13541666666</v>
+        <v>46136.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,7 +1802,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46133.14583333334</v>
+        <v>46136.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1243,7 +1819,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46133.15625</v>
+        <v>46136.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1260,10 +1836,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46133.16666666666</v>
+        <v>46136.16666666666</v>
       </c>
       <c r="B18">
-        <v>17.73</v>
+        <v>26.886</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,7 +1853,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46133.17708333334</v>
+        <v>46136.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1294,7 +1870,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46133.1875</v>
+        <v>46136.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1311,10 +1887,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46133.19791666666</v>
+        <v>46136.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>26.89</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,10 +1904,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46133.20833333334</v>
+        <v>46136.20833333334</v>
       </c>
       <c r="B22">
-        <v>28.603</v>
+        <v>35.035</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1345,10 +1921,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46133.21875</v>
+        <v>46136.21875</v>
       </c>
       <c r="B23">
-        <v>28.834</v>
+        <v>37.694</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1362,13 +1938,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46133.22916666666</v>
+        <v>46136.22916666666</v>
       </c>
       <c r="B24">
-        <v>33.491</v>
+        <v>56.723</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1955,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46133.23958333334</v>
+        <v>46136.23958333334</v>
       </c>
       <c r="B25">
-        <v>49.824</v>
+        <v>94.11</v>
       </c>
       <c r="C25">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1972,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46133.25</v>
+        <v>46136.25</v>
       </c>
       <c r="B26">
-        <v>128.33</v>
+        <v>278.339</v>
       </c>
       <c r="C26">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1989,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46133.26041666666</v>
+        <v>46136.26041666666</v>
       </c>
       <c r="B27">
-        <v>179.384</v>
+        <v>383.425</v>
       </c>
       <c r="C27">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +2006,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46133.27083333334</v>
+        <v>46136.27083333334</v>
       </c>
       <c r="B28">
-        <v>242.578</v>
+        <v>518.035</v>
       </c>
       <c r="C28">
-        <v>200</v>
+        <v>372</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +2023,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46133.28125</v>
+        <v>46136.28125</v>
       </c>
       <c r="B29">
-        <v>314.328</v>
+        <v>690.628</v>
       </c>
       <c r="C29">
-        <v>283</v>
+        <v>532</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +2040,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46133.29166666666</v>
+        <v>46136.29166666666</v>
       </c>
       <c r="B30">
-        <v>455.529</v>
+        <v>960.205</v>
       </c>
       <c r="C30">
-        <v>352</v>
+        <v>737</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +2057,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46133.30208333334</v>
+        <v>46136.30208333334</v>
       </c>
       <c r="B31">
-        <v>550.471</v>
+        <v>1155.521</v>
       </c>
       <c r="C31">
-        <v>425</v>
+        <v>937</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +2074,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46133.3125</v>
+        <v>46136.3125</v>
       </c>
       <c r="B32">
-        <v>651.323</v>
+        <v>1363.506</v>
       </c>
       <c r="C32">
-        <v>512</v>
+        <v>1126</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +2091,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46133.32291666666</v>
+        <v>46136.32291666666</v>
       </c>
       <c r="B33">
-        <v>778.053</v>
+        <v>1591.723</v>
       </c>
       <c r="C33">
-        <v>665</v>
+        <v>1307</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +2108,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46133.33333333334</v>
+        <v>46136.33333333334</v>
       </c>
       <c r="B34">
-        <v>932.63</v>
+        <v>1876.48</v>
       </c>
       <c r="C34">
-        <v>699</v>
+        <v>1514</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +2125,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46133.34375</v>
+        <v>46136.34375</v>
       </c>
       <c r="B35">
-        <v>1033.448</v>
+        <v>2048.707</v>
       </c>
       <c r="C35">
-        <v>854</v>
+        <v>1664</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +2142,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46133.35416666666</v>
+        <v>46136.35416666666</v>
       </c>
       <c r="B36">
-        <v>1121.84</v>
+        <v>2235.378</v>
       </c>
       <c r="C36">
-        <v>968</v>
+        <v>1736</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +2159,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46133.36458333334</v>
+        <v>46136.36458333334</v>
       </c>
       <c r="B37">
-        <v>1215.914</v>
+        <v>2420.08</v>
       </c>
       <c r="C37">
-        <v>1019</v>
+        <v>1838</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +2176,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46133.375</v>
+        <v>46136.375</v>
       </c>
       <c r="B38">
-        <v>1293.732</v>
+        <v>2638.573</v>
       </c>
       <c r="C38">
-        <v>1092</v>
+        <v>1960</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +2193,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46133.38541666666</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="B39">
-        <v>1362.951</v>
+        <v>2756.284</v>
       </c>
       <c r="C39">
-        <v>1151</v>
+        <v>2021</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +2210,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46133.39583333334</v>
+        <v>46136.39583333334</v>
       </c>
       <c r="B40">
-        <v>1425.539</v>
+        <v>2820.767</v>
       </c>
       <c r="C40">
-        <v>1164</v>
+        <v>2115</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +2227,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46133.40625</v>
+        <v>46136.40625</v>
       </c>
       <c r="B41">
-        <v>1483.644</v>
+        <v>2897.648</v>
       </c>
       <c r="C41">
-        <v>1063</v>
+        <v>2165</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +2244,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46133.41666666666</v>
+        <v>46136.41666666666</v>
       </c>
       <c r="B42">
-        <v>1552.392</v>
+        <v>2987.317</v>
       </c>
       <c r="C42">
-        <v>1076</v>
+        <v>2222</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +2261,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46133.42708333334</v>
+        <v>46136.42708333334</v>
       </c>
       <c r="B43">
-        <v>1597.645</v>
+        <v>3035.402</v>
       </c>
       <c r="C43">
-        <v>1166</v>
+        <v>2213</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +2278,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46133.4375</v>
+        <v>46136.4375</v>
       </c>
       <c r="B44">
-        <v>1627.276</v>
+        <v>3054.293</v>
       </c>
       <c r="C44">
-        <v>1216</v>
+        <v>2243</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +2295,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46133.44791666666</v>
+        <v>46136.44791666666</v>
       </c>
       <c r="B45">
-        <v>1656.179</v>
+        <v>2811.29</v>
       </c>
       <c r="C45">
-        <v>1246</v>
+        <v>2072</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +2312,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46133.45833333334</v>
+        <v>46136.45833333334</v>
       </c>
       <c r="B46">
-        <v>1681.697</v>
+        <v>2875.33</v>
       </c>
       <c r="C46">
-        <v>1269</v>
+        <v>2055</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +2329,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46133.46875</v>
+        <v>46136.46875</v>
       </c>
       <c r="B47">
-        <v>1693.967</v>
+        <v>2224.113</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +2346,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46133.47916666666</v>
+        <v>46136.47916666666</v>
       </c>
       <c r="B48">
-        <v>1673.647</v>
+        <v>2205.991</v>
       </c>
       <c r="C48">
-        <v>1262</v>
+        <v>1446</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +2363,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46133.48958333334</v>
+        <v>46136.48958333334</v>
       </c>
       <c r="B49">
-        <v>1669.106</v>
+        <v>2199.954</v>
       </c>
       <c r="C49">
-        <v>1281</v>
+        <v>1463</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +2380,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46133.5</v>
+        <v>46136.5</v>
       </c>
       <c r="B50">
-        <v>1661.777</v>
+        <v>2072.116</v>
       </c>
       <c r="C50">
-        <v>1261</v>
+        <v>1419</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +2397,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46133.51041666666</v>
+        <v>46136.51041666666</v>
       </c>
       <c r="B51">
-        <v>1656.133</v>
+        <v>1988.862</v>
       </c>
       <c r="C51">
-        <v>1297</v>
+        <v>1402</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +2414,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46133.52083333334</v>
+        <v>46136.52083333334</v>
       </c>
       <c r="B52">
-        <v>1645.866</v>
+        <v>1958.887</v>
       </c>
       <c r="C52">
-        <v>1303</v>
+        <v>1401</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +2431,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46133.53125</v>
+        <v>46136.53125</v>
       </c>
       <c r="B53">
-        <v>1634.58</v>
+        <v>1886.634</v>
       </c>
       <c r="C53">
-        <v>1228</v>
+        <v>1312</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +2448,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46133.54166666666</v>
+        <v>46136.54166666666</v>
       </c>
       <c r="B54">
-        <v>1628.633</v>
+        <v>1853.956</v>
       </c>
       <c r="C54">
-        <v>1183</v>
+        <v>1261</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +2465,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46133.55208333334</v>
+        <v>46136.55208333334</v>
       </c>
       <c r="B55">
-        <v>1611.101</v>
+        <v>1823.589</v>
       </c>
       <c r="C55">
-        <v>1134</v>
+        <v>1249</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +2482,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46133.5625</v>
+        <v>46136.5625</v>
       </c>
       <c r="B56">
-        <v>1588.84</v>
+        <v>1785.42</v>
       </c>
       <c r="C56">
-        <v>1138</v>
+        <v>1241</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +2499,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46133.57291666666</v>
+        <v>46136.57291666666</v>
       </c>
       <c r="B57">
-        <v>1556.13</v>
+        <v>1757.522</v>
       </c>
       <c r="C57">
-        <v>1115</v>
+        <v>1245</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +2516,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46133.58333333334</v>
+        <v>46136.58333333334</v>
       </c>
       <c r="B58">
-        <v>1467.948</v>
+        <v>1692.607</v>
       </c>
       <c r="C58">
-        <v>1104</v>
+        <v>1121</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +2533,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46133.59375</v>
+        <v>46136.59375</v>
       </c>
       <c r="B59">
-        <v>1419.925</v>
+        <v>1639.658</v>
       </c>
       <c r="C59">
-        <v>1130</v>
+        <v>1088</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,10 +2550,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46133.60416666666</v>
+        <v>46136.60416666666</v>
       </c>
       <c r="B60">
-        <v>1368.665</v>
+        <v>1595.69</v>
       </c>
       <c r="C60">
         <v>1070</v>
@@ -1991,13 +2567,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46133.61458333334</v>
+        <v>46136.61458333334</v>
       </c>
       <c r="B61">
-        <v>1322.337</v>
+        <v>1522.133</v>
       </c>
       <c r="C61">
-        <v>950</v>
+        <v>1067</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2584,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46133.625</v>
+        <v>46136.625</v>
       </c>
       <c r="B62">
-        <v>1221.793</v>
+        <v>1419.683</v>
       </c>
       <c r="C62">
-        <v>939</v>
+        <v>990</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2601,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46133.63541666666</v>
+        <v>46136.63541666666</v>
       </c>
       <c r="B63">
-        <v>1154.026</v>
+        <v>1332.477</v>
       </c>
       <c r="C63">
-        <v>978</v>
+        <v>937</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2618,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46133.64583333334</v>
+        <v>46136.64583333334</v>
       </c>
       <c r="B64">
-        <v>1087.606</v>
+        <v>1271.364</v>
       </c>
       <c r="C64">
-        <v>935</v>
+        <v>879</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2635,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46133.65625</v>
+        <v>46136.65625</v>
       </c>
       <c r="B65">
-        <v>1012.211</v>
+        <v>1222.827</v>
       </c>
       <c r="C65">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2652,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46133.66666666666</v>
+        <v>46136.66666666666</v>
       </c>
       <c r="B66">
-        <v>895.968</v>
+        <v>1128.664</v>
       </c>
       <c r="C66">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2669,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46133.67708333334</v>
+        <v>46136.67708333334</v>
       </c>
       <c r="B67">
-        <v>806.313</v>
+        <v>1058.196</v>
       </c>
       <c r="C67">
-        <v>743</v>
+        <v>783</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2686,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46133.6875</v>
+        <v>46136.6875</v>
       </c>
       <c r="B68">
-        <v>719.8339999999999</v>
+        <v>1259.631</v>
       </c>
       <c r="C68">
-        <v>650</v>
+        <v>980</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2703,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46133.69791666666</v>
+        <v>46136.69791666666</v>
       </c>
       <c r="B69">
-        <v>647.595</v>
+        <v>1132.627</v>
       </c>
       <c r="C69">
-        <v>586</v>
+        <v>882</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2720,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46133.70833333334</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="B70">
-        <v>518.069</v>
+        <v>911.146</v>
       </c>
       <c r="C70">
-        <v>492</v>
+        <v>800</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2737,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46133.71875</v>
+        <v>46136.71875</v>
       </c>
       <c r="B71">
-        <v>440.295</v>
+        <v>850.621</v>
       </c>
       <c r="C71">
-        <v>366</v>
+        <v>715</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2754,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46133.72916666666</v>
+        <v>46136.72916666666</v>
       </c>
       <c r="B72">
-        <v>351.856</v>
+        <v>704.78</v>
       </c>
       <c r="C72">
-        <v>321</v>
+        <v>610</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2771,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46133.73958333334</v>
+        <v>46136.73958333334</v>
       </c>
       <c r="B73">
-        <v>299.578</v>
+        <v>566.678</v>
       </c>
       <c r="C73">
-        <v>238</v>
+        <v>474</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2788,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46133.75</v>
+        <v>46136.75</v>
       </c>
       <c r="B74">
-        <v>205.453</v>
+        <v>429.497</v>
       </c>
       <c r="C74">
-        <v>170</v>
+        <v>345</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2805,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46133.76041666666</v>
+        <v>46136.76041666666</v>
       </c>
       <c r="B75">
-        <v>159.332</v>
+        <v>322.668</v>
       </c>
       <c r="C75">
-        <v>101</v>
+        <v>216</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2822,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46133.77083333334</v>
+        <v>46136.77083333334</v>
       </c>
       <c r="B76">
-        <v>76.60599999999999</v>
+        <v>239.634</v>
       </c>
       <c r="C76">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2839,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46133.78125</v>
+        <v>46136.78125</v>
       </c>
       <c r="B77">
-        <v>50.974</v>
+        <v>179.256</v>
       </c>
       <c r="C77">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2856,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46133.79166666666</v>
+        <v>46136.79166666666</v>
       </c>
       <c r="B78">
-        <v>22.645</v>
+        <v>44.502</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2873,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46133.80208333334</v>
+        <v>46136.80208333334</v>
       </c>
       <c r="B79">
-        <v>17.36</v>
+        <v>24.568</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,10 +2890,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46133.8125</v>
+        <v>46136.8125</v>
       </c>
       <c r="B80">
-        <v>15.969</v>
+        <v>19.597</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2331,10 +2907,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46133.82291666666</v>
+        <v>46136.82291666666</v>
       </c>
       <c r="B81">
-        <v>13.738</v>
+        <v>10.257</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2924,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46133.83333333334</v>
+        <v>46136.83333333334</v>
       </c>
       <c r="B82">
-        <v>7.7</v>
+        <v>11.004</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2941,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46133.84375</v>
+        <v>46136.84375</v>
       </c>
       <c r="B83">
-        <v>7.412</v>
+        <v>10.511</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2958,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46133.85416666666</v>
+        <v>46136.85416666666</v>
       </c>
       <c r="B84">
-        <v>4.362</v>
+        <v>7.431</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2975,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46133.86458333334</v>
+        <v>46136.86458333334</v>
       </c>
       <c r="B85">
-        <v>3.73</v>
+        <v>6.535</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2992,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46133.875</v>
+        <v>46136.875</v>
       </c>
       <c r="B86">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,7 +3009,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46133.88541666666</v>
+        <v>46136.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2450,10 +3026,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46133.89583333334</v>
+        <v>46136.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +3043,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46133.90625</v>
+        <v>46136.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +3060,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46133.91666666666</v>
+        <v>46136.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.43</v>
+        <v>0.83</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +3077,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46133.92708333334</v>
+        <v>46136.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,10 +3094,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46133.9375</v>
+        <v>46136.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2535,10 +3111,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46133.94791666666</v>
+        <v>46136.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2552,7 +3128,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46133.95833333334</v>
+        <v>46136.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2569,7 +3145,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46133.96875</v>
+        <v>46136.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +3162,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46133.97916666666</v>
+        <v>46136.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +3179,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46133.98958333334</v>
+        <v>46136.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +3196,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2637,7 +3213,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46134.01041666666</v>
+        <v>46137.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +3230,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46134.02083333334</v>
+        <v>46137.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +3247,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46134.03125</v>
+        <v>46137.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +3264,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46134.04166666666</v>
+        <v>46137.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +3281,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46134.05208333334</v>
+        <v>46137.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +3298,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46134.0625</v>
+        <v>46137.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +3315,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46134.07291666666</v>
+        <v>46137.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +3332,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46134.08333333334</v>
+        <v>46137.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +3349,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46134.09375</v>
+        <v>46137.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +3366,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46134.10416666666</v>
+        <v>46137.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +3383,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46134.11458333334</v>
+        <v>46137.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,7 +3400,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46134.125</v>
+        <v>46137.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2841,7 +3417,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46134.13541666666</v>
+        <v>46137.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +3434,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46134.14583333334</v>
+        <v>46137.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,7 +3451,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46134.15625</v>
+        <v>46137.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2892,10 +3468,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46134.16666666666</v>
+        <v>46137.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,7 +3485,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46134.17708333334</v>
+        <v>46137.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2926,7 +3502,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46134.1875</v>
+        <v>46137.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2943,10 +3519,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46134.19791666666</v>
+        <v>46137.19791666666</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>0.834</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,10 +3536,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46134.20833333334</v>
+        <v>46137.20833333334</v>
       </c>
       <c r="B118">
-        <v>1.541</v>
+        <v>3.011</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2977,10 +3553,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46134.21875</v>
+        <v>46137.21875</v>
       </c>
       <c r="B119">
-        <v>2.215</v>
+        <v>7.148</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2994,13 +3570,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46134.22916666666</v>
+        <v>46137.22916666666</v>
       </c>
       <c r="B120">
-        <v>8.882</v>
+        <v>26.298</v>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3587,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46134.23958333334</v>
+        <v>46137.23958333334</v>
       </c>
       <c r="B121">
-        <v>28.218</v>
+        <v>65.54300000000001</v>
       </c>
       <c r="C121">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3604,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46134.25</v>
+        <v>46137.25</v>
       </c>
       <c r="B122">
-        <v>93.256</v>
+        <v>178.861</v>
       </c>
       <c r="C122">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3621,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46134.26041666666</v>
+        <v>46137.26041666666</v>
       </c>
       <c r="B123">
-        <v>150.627</v>
+        <v>269.699</v>
       </c>
       <c r="C123">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3638,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46134.27083333334</v>
+        <v>46137.27083333334</v>
       </c>
       <c r="B124">
-        <v>227.969</v>
+        <v>390.655</v>
       </c>
       <c r="C124">
-        <v>196</v>
+        <v>284</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3655,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46134.28125</v>
+        <v>46137.28125</v>
       </c>
       <c r="B125">
-        <v>315.111</v>
+        <v>533.663</v>
       </c>
       <c r="C125">
-        <v>283</v>
+        <v>405</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3672,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46134.29166666666</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="B126">
-        <v>440.148</v>
+        <v>803.0359999999999</v>
       </c>
       <c r="C126">
-        <v>395</v>
+        <v>542</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3689,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46134.30208333334</v>
+        <v>46137.30208333334</v>
       </c>
       <c r="B127">
-        <v>545.1660000000001</v>
+        <v>962.372</v>
       </c>
       <c r="C127">
-        <v>462</v>
+        <v>651</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3706,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46134.3125</v>
+        <v>46137.3125</v>
       </c>
       <c r="B128">
-        <v>666.579</v>
+        <v>1148.865</v>
       </c>
       <c r="C128">
-        <v>568</v>
+        <v>750</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3723,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46134.32291666666</v>
+        <v>46137.32291666666</v>
       </c>
       <c r="B129">
-        <v>786.561</v>
+        <v>1338.995</v>
       </c>
       <c r="C129">
-        <v>663</v>
+        <v>878</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3740,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46134.33333333334</v>
+        <v>46137.33333333334</v>
       </c>
       <c r="B130">
-        <v>974.1559999999999</v>
+        <v>1612.074</v>
       </c>
       <c r="C130">
-        <v>840</v>
+        <v>1039</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3757,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46134.34375</v>
+        <v>46137.34375</v>
       </c>
       <c r="B131">
-        <v>1087.779</v>
+        <v>1792.904</v>
       </c>
       <c r="C131">
-        <v>893</v>
+        <v>1196</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3774,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46134.35416666666</v>
+        <v>46137.35416666666</v>
       </c>
       <c r="B132">
-        <v>1221.673</v>
+        <v>1979.459</v>
       </c>
       <c r="C132">
-        <v>943</v>
+        <v>1270</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3791,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46134.36458333334</v>
+        <v>46137.36458333334</v>
       </c>
       <c r="B133">
-        <v>1327.251</v>
+        <v>2116.849</v>
       </c>
       <c r="C133">
-        <v>1035</v>
+        <v>1351</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3808,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46134.375</v>
+        <v>46137.375</v>
       </c>
       <c r="B134">
-        <v>1494.343</v>
+        <v>2368.475</v>
       </c>
       <c r="C134">
-        <v>1114</v>
+        <v>1469</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3825,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46134.38541666666</v>
+        <v>46137.38541666666</v>
       </c>
       <c r="B135">
-        <v>1575.25</v>
+        <v>2464.221</v>
       </c>
       <c r="C135">
-        <v>1163</v>
+        <v>1567</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3842,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46134.39583333334</v>
+        <v>46137.39583333334</v>
       </c>
       <c r="B136">
-        <v>1665.605</v>
+        <v>2388.721</v>
       </c>
       <c r="C136">
-        <v>1271</v>
+        <v>1429</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3859,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46134.40625</v>
+        <v>46137.40625</v>
       </c>
       <c r="B137">
-        <v>1740.885</v>
+        <v>1926.158</v>
       </c>
       <c r="C137">
-        <v>1357</v>
+        <v>1124</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3876,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46134.41666666666</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="B138">
-        <v>1806.898</v>
+        <v>2004.03</v>
       </c>
       <c r="C138">
-        <v>1435</v>
+        <v>1087</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3893,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46134.42708333334</v>
+        <v>46137.42708333334</v>
       </c>
       <c r="B139">
-        <v>1857.69</v>
+        <v>1954.679</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3910,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46134.4375</v>
+        <v>46137.4375</v>
       </c>
       <c r="B140">
-        <v>1899.746</v>
+        <v>1922.484</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>1101</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3927,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46134.44791666666</v>
+        <v>46137.44791666666</v>
       </c>
       <c r="B141">
-        <v>1927.155</v>
+        <v>1930.686</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1135</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3944,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46134.45833333334</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="B142">
-        <v>1933.348</v>
+        <v>1957.9</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3961,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46134.46875</v>
+        <v>46137.46875</v>
       </c>
       <c r="B143">
-        <v>1961.971</v>
+        <v>1875.363</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1135</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3978,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46134.47916666666</v>
+        <v>46137.47916666666</v>
       </c>
       <c r="B144">
-        <v>1974.113</v>
+        <v>1823.578</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1120</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3995,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46134.48958333334</v>
+        <v>46137.48958333334</v>
       </c>
       <c r="B145">
-        <v>1988.061</v>
+        <v>1815.525</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +4012,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46134.5</v>
+        <v>46137.5</v>
       </c>
       <c r="B146">
-        <v>1975.282</v>
+        <v>1786.97</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1084</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +4029,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46134.51041666666</v>
+        <v>46137.51041666666</v>
       </c>
       <c r="B147">
-        <v>1974.845</v>
+        <v>1775.824</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1058</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +4046,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46134.52083333334</v>
+        <v>46137.52083333334</v>
       </c>
       <c r="B148">
-        <v>1978.148</v>
+        <v>1760.072</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,10 +4063,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46134.53125</v>
+        <v>46137.53125</v>
       </c>
       <c r="B149">
-        <v>1979.769</v>
+        <v>1729.993</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,13 +4080,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46134.54166666666</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="B150">
-        <v>1984.791</v>
+        <v>1686.1</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>1017</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3521,13 +4097,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46134.55208333334</v>
+        <v>46137.55208333334</v>
       </c>
       <c r="B151">
-        <v>1974.093</v>
+        <v>1651.819</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3538,13 +4114,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46134.5625</v>
+        <v>46137.5625</v>
       </c>
       <c r="B152">
-        <v>1952.668</v>
+        <v>1612.9</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>897</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3555,13 +4131,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46134.57291666666</v>
+        <v>46137.57291666666</v>
       </c>
       <c r="B153">
-        <v>1923.582</v>
+        <v>1571.354</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>902</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3572,13 +4148,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46134.58333333334</v>
+        <v>46137.58333333334</v>
       </c>
       <c r="B154">
-        <v>1857.452</v>
+        <v>1498.557</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3589,13 +4165,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46134.59375</v>
+        <v>46137.59375</v>
       </c>
       <c r="B155">
-        <v>1806.277</v>
+        <v>1453.068</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3606,13 +4182,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46134.60416666666</v>
+        <v>46137.60416666666</v>
       </c>
       <c r="B156">
-        <v>1745.643</v>
+        <v>1405.482</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>819</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3623,13 +4199,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46134.61458333334</v>
+        <v>46137.61458333334</v>
       </c>
       <c r="B157">
-        <v>1690.303</v>
+        <v>1355.021</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>831</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3640,13 +4216,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46134.625</v>
+        <v>46137.625</v>
       </c>
       <c r="B158">
-        <v>1586.116</v>
+        <v>1225.11</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3657,13 +4233,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46134.63541666666</v>
+        <v>46137.63541666666</v>
       </c>
       <c r="B159">
-        <v>1489.582</v>
+        <v>1170.727</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3674,13 +4250,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46134.64583333334</v>
+        <v>46137.64583333334</v>
       </c>
       <c r="B160">
-        <v>1402.071</v>
+        <v>1110.645</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3691,13 +4267,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46134.65625</v>
+        <v>46137.65625</v>
       </c>
       <c r="B161">
-        <v>1320.467</v>
+        <v>1042.737</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>789</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3708,13 +4284,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46134.66666666666</v>
+        <v>46137.66666666666</v>
       </c>
       <c r="B162">
-        <v>1185.261</v>
+        <v>904.4059999999999</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3725,13 +4301,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46134.67708333334</v>
+        <v>46137.67708333334</v>
       </c>
       <c r="B163">
-        <v>1049.354</v>
+        <v>842.765</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>724</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3742,13 +4318,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46134.6875</v>
+        <v>46137.6875</v>
       </c>
       <c r="B164">
-        <v>946.377</v>
+        <v>824.728</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3759,13 +4335,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46134.69791666666</v>
+        <v>46137.69791666666</v>
       </c>
       <c r="B165">
-        <v>839.8819999999999</v>
+        <v>786.439</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3776,13 +4352,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46134.70833333334</v>
+        <v>46137.70833333334</v>
       </c>
       <c r="B166">
-        <v>664.437</v>
+        <v>580.946</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3793,13 +4369,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46134.71875</v>
+        <v>46137.71875</v>
       </c>
       <c r="B167">
-        <v>570.655</v>
+        <v>712.024</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3810,13 +4386,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46134.72916666666</v>
+        <v>46137.72916666666</v>
       </c>
       <c r="B168">
-        <v>474.545</v>
+        <v>633.103</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3827,13 +4403,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46134.73958333334</v>
+        <v>46137.73958333334</v>
       </c>
       <c r="B169">
-        <v>372.27</v>
+        <v>511.202</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3844,13 +4420,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46134.75</v>
+        <v>46137.75</v>
       </c>
       <c r="B170">
-        <v>244.617</v>
+        <v>332.602</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3861,13 +4437,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46134.76041666666</v>
+        <v>46137.76041666666</v>
       </c>
       <c r="B171">
-        <v>176.072</v>
+        <v>238.106</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3878,13 +4454,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46134.77083333334</v>
+        <v>46137.77083333334</v>
       </c>
       <c r="B172">
-        <v>116.026</v>
+        <v>160.298</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3895,13 +4471,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46134.78125</v>
+        <v>46137.78125</v>
       </c>
       <c r="B173">
-        <v>73.11199999999999</v>
+        <v>98.447</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3912,13 +4488,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46134.79166666666</v>
+        <v>46137.79166666666</v>
       </c>
       <c r="B174">
-        <v>28.518</v>
+        <v>42.501</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3929,13 +4505,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46134.80208333334</v>
+        <v>46137.80208333334</v>
       </c>
       <c r="B175">
-        <v>19.378</v>
+        <v>24.909</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3946,10 +4522,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46134.8125</v>
+        <v>46137.8125</v>
       </c>
       <c r="B176">
-        <v>14.253</v>
+        <v>18.566</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +4539,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46134.82291666666</v>
+        <v>46137.82291666666</v>
       </c>
       <c r="B177">
-        <v>9.646000000000001</v>
+        <v>10.76</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +4556,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46134.83333333334</v>
+        <v>46137.83333333334</v>
       </c>
       <c r="B178">
-        <v>7.229</v>
+        <v>11.827</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +4573,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46134.84375</v>
+        <v>46137.84375</v>
       </c>
       <c r="B179">
-        <v>6.929</v>
+        <v>10.643</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4590,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46134.85416666666</v>
+        <v>46137.85416666666</v>
       </c>
       <c r="B180">
-        <v>3.859</v>
+        <v>9.766</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4607,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46134.86458333334</v>
+        <v>46137.86458333334</v>
       </c>
       <c r="B181">
-        <v>3.259</v>
+        <v>9.968999999999999</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4624,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46134.875</v>
+        <v>46137.875</v>
       </c>
       <c r="B182">
-        <v>2.73</v>
+        <v>4.43</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4641,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46134.88541666666</v>
+        <v>46137.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4658,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46134.89583333334</v>
+        <v>46137.89583333334</v>
       </c>
       <c r="B184">
-        <v>2.43</v>
+        <v>1.43</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4675,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46134.90625</v>
+        <v>46137.90625</v>
       </c>
       <c r="B185">
-        <v>2.03</v>
+        <v>0.83</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4692,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46134.91666666666</v>
+        <v>46137.91666666666</v>
       </c>
       <c r="B186">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4709,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46134.92708333334</v>
+        <v>46137.92708333334</v>
       </c>
       <c r="B187">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4726,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46134.9375</v>
+        <v>46137.9375</v>
       </c>
       <c r="B188">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4743,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46134.94791666666</v>
+        <v>46137.94791666666</v>
       </c>
       <c r="B189">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4760,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46134.95833333334</v>
+        <v>46137.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4777,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46134.96875</v>
+        <v>46137.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4794,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46134.97916666666</v>
+        <v>46137.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4811,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46134.98958333334</v>
+        <v>46137.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4248,6 +4824,3270 @@
       </c>
       <c r="E193" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46138</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46138.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46138.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46138.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46138.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46138.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46138.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46138.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46138.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46138.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46138.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46138.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46138.125</v>
+      </c>
+      <c r="B206">
+        <v>0.832</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46138.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46138.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46138.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46138.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0.83</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46138.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46138.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46138.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0.834</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46138.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>3.607</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46138.21875</v>
+      </c>
+      <c r="B215">
+        <v>9.614000000000001</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46138.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>38.794</v>
+      </c>
+      <c r="C216">
+        <v>17</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46138.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>79.307</v>
+      </c>
+      <c r="C217">
+        <v>51</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46138.25</v>
+      </c>
+      <c r="B218">
+        <v>256.217</v>
+      </c>
+      <c r="C218">
+        <v>109</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46138.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>355.357</v>
+      </c>
+      <c r="C219">
+        <v>194</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46138.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>483.693</v>
+      </c>
+      <c r="C220">
+        <v>307</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46138.28125</v>
+      </c>
+      <c r="B221">
+        <v>632.851</v>
+      </c>
+      <c r="C221">
+        <v>448</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46138.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>902.101</v>
+      </c>
+      <c r="C222">
+        <v>575</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46138.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>1081.861</v>
+      </c>
+      <c r="C223">
+        <v>691</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46138.3125</v>
+      </c>
+      <c r="B224">
+        <v>1280.656</v>
+      </c>
+      <c r="C224">
+        <v>808</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46138.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>1406.769</v>
+      </c>
+      <c r="C225">
+        <v>893</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46138.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1664.818</v>
+      </c>
+      <c r="C226">
+        <v>1005</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46138.34375</v>
+      </c>
+      <c r="B227">
+        <v>1803.542</v>
+      </c>
+      <c r="C227">
+        <v>1109</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46138.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>1783.188</v>
+      </c>
+      <c r="C228">
+        <v>1100</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46138.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>1541.454</v>
+      </c>
+      <c r="C229">
+        <v>967</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46138.375</v>
+      </c>
+      <c r="B230">
+        <v>1739.004</v>
+      </c>
+      <c r="C230">
+        <v>1038</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46138.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>1787.955</v>
+      </c>
+      <c r="C231">
+        <v>1088</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46138.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>1767.207</v>
+      </c>
+      <c r="C232">
+        <v>970</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46138.40625</v>
+      </c>
+      <c r="B233">
+        <v>1821.541</v>
+      </c>
+      <c r="C233">
+        <v>944</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46138.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>1896.042</v>
+      </c>
+      <c r="C234">
+        <v>997</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46138.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>1908.499</v>
+      </c>
+      <c r="C235">
+        <v>1049</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46138.4375</v>
+      </c>
+      <c r="B236">
+        <v>1884.037</v>
+      </c>
+      <c r="C236">
+        <v>1006</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46138.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>1861.985</v>
+      </c>
+      <c r="C237">
+        <v>1016</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46138.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>1824.923</v>
+      </c>
+      <c r="C238">
+        <v>934</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46138.46875</v>
+      </c>
+      <c r="B239">
+        <v>1846.084</v>
+      </c>
+      <c r="C239">
+        <v>929</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46138.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>1846.75</v>
+      </c>
+      <c r="C240">
+        <v>925</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46138.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>1797.777</v>
+      </c>
+      <c r="C241">
+        <v>921</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46138.5</v>
+      </c>
+      <c r="B242">
+        <v>1780.678</v>
+      </c>
+      <c r="C242">
+        <v>919</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46138.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>1774.255</v>
+      </c>
+      <c r="C243">
+        <v>884</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46138.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>1757.544</v>
+      </c>
+      <c r="C244">
+        <v>886</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46138.53125</v>
+      </c>
+      <c r="B245">
+        <v>1714.716</v>
+      </c>
+      <c r="C245">
+        <v>871</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46138.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>1564.988</v>
+      </c>
+      <c r="C246">
+        <v>864</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46138.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1553.653</v>
+      </c>
+      <c r="C247">
+        <v>857</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46138.5625</v>
+      </c>
+      <c r="B248">
+        <v>1594.291</v>
+      </c>
+      <c r="C248">
+        <v>848</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46138.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>1630.215</v>
+      </c>
+      <c r="C249">
+        <v>844</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46138.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1581.439</v>
+      </c>
+      <c r="C250">
+        <v>819</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46138.59375</v>
+      </c>
+      <c r="B251">
+        <v>1543.238</v>
+      </c>
+      <c r="C251">
+        <v>787</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46138.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>1504.808</v>
+      </c>
+      <c r="C252">
+        <v>776</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46138.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>1401.523</v>
+      </c>
+      <c r="C253">
+        <v>778</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46138.625</v>
+      </c>
+      <c r="B254">
+        <v>1374.31</v>
+      </c>
+      <c r="C254">
+        <v>717</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46138.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>1315.098</v>
+      </c>
+      <c r="C255">
+        <v>703</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46138.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1291.292</v>
+      </c>
+      <c r="C256">
+        <v>669</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46138.65625</v>
+      </c>
+      <c r="B257">
+        <v>1221.107</v>
+      </c>
+      <c r="C257">
+        <v>652</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46138.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1085.499</v>
+      </c>
+      <c r="C258">
+        <v>648</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46138.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>968.99</v>
+      </c>
+      <c r="C259">
+        <v>571</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46138.6875</v>
+      </c>
+      <c r="B260">
+        <v>928.4160000000001</v>
+      </c>
+      <c r="C260">
+        <v>548</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46138.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>884.345</v>
+      </c>
+      <c r="C261">
+        <v>501</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46138.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>685.832</v>
+      </c>
+      <c r="C262">
+        <v>441</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46138.71875</v>
+      </c>
+      <c r="B263">
+        <v>607.64</v>
+      </c>
+      <c r="C263">
+        <v>364</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46138.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>719.41</v>
+      </c>
+      <c r="C264">
+        <v>435</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46138.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>602.23</v>
+      </c>
+      <c r="C265">
+        <v>381</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46138.75</v>
+      </c>
+      <c r="B266">
+        <v>408.703</v>
+      </c>
+      <c r="C266">
+        <v>244</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46138.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>303.098</v>
+      </c>
+      <c r="C267">
+        <v>154</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46138.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>175.086</v>
+      </c>
+      <c r="C268">
+        <v>93</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46138.78125</v>
+      </c>
+      <c r="B269">
+        <v>112.354</v>
+      </c>
+      <c r="C269">
+        <v>47</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46138.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>48.407</v>
+      </c>
+      <c r="C270">
+        <v>10</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46138.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>31.325</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46138.8125</v>
+      </c>
+      <c r="B272">
+        <v>22.739</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46138.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>12.027</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46138.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>6.122</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46138.84375</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46138.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>5.755</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46138.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>4.955</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46138.875</v>
+      </c>
+      <c r="B278">
+        <v>4.43</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46138.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>4.13</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46138.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>1.43</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46138.90625</v>
+      </c>
+      <c r="B281">
+        <v>0.83</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46138.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46138.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46138.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46138.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46138.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46138.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46138.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46138.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0.93</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46139.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46139.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46139.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46139.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46139.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46139.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46139.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46139.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46139.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46139.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46139.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46139.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46139.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46139.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46139.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>19.93</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46139.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46139.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46139.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>19.934</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46139.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>35.506</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46139.21875</v>
+      </c>
+      <c r="B311">
+        <v>46.3</v>
+      </c>
+      <c r="C311">
+        <v>2</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46139.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>75.43000000000001</v>
+      </c>
+      <c r="C312">
+        <v>30</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46139.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>119.29</v>
+      </c>
+      <c r="C313">
+        <v>76</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46139.25</v>
+      </c>
+      <c r="B314">
+        <v>262.357</v>
+      </c>
+      <c r="C314">
+        <v>150</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46139.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>375.294</v>
+      </c>
+      <c r="C315">
+        <v>263</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46139.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>506.715</v>
+      </c>
+      <c r="C316">
+        <v>406</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46139.28125</v>
+      </c>
+      <c r="B317">
+        <v>667.468</v>
+      </c>
+      <c r="C317">
+        <v>602</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46139.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>950.105</v>
+      </c>
+      <c r="C318">
+        <v>787</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46139.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>1145.909</v>
+      </c>
+      <c r="C319">
+        <v>952</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46139.3125</v>
+      </c>
+      <c r="B320">
+        <v>1323.232</v>
+      </c>
+      <c r="C320">
+        <v>1137</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46139.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>1555.51</v>
+      </c>
+      <c r="C321">
+        <v>1297</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46139.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>1867.862</v>
+      </c>
+      <c r="C322">
+        <v>1442</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46139.34375</v>
+      </c>
+      <c r="B323">
+        <v>2040.571</v>
+      </c>
+      <c r="C323">
+        <v>1566</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46139.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>2214.938</v>
+      </c>
+      <c r="C324">
+        <v>1667</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46139.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>2381.693</v>
+      </c>
+      <c r="C325">
+        <v>1812</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46139.375</v>
+      </c>
+      <c r="B326">
+        <v>2607.496</v>
+      </c>
+      <c r="C326">
+        <v>1898</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46139.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>2714.983</v>
+      </c>
+      <c r="C327">
+        <v>2062</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46139.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>2835.379</v>
+      </c>
+      <c r="C328">
+        <v>2154</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46139.40625</v>
+      </c>
+      <c r="B329">
+        <v>2941.058</v>
+      </c>
+      <c r="C329">
+        <v>2170</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46139.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>3045.231</v>
+      </c>
+      <c r="C330">
+        <v>2267</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46139.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>3118.065</v>
+      </c>
+      <c r="C331">
+        <v>2248</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46139.4375</v>
+      </c>
+      <c r="B332">
+        <v>3169.995</v>
+      </c>
+      <c r="C332">
+        <v>2279</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46139.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>3184.391</v>
+      </c>
+      <c r="C333">
+        <v>2310</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46139.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>3246.584</v>
+      </c>
+      <c r="C334">
+        <v>2256</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46139.46875</v>
+      </c>
+      <c r="B335">
+        <v>3033.751</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46139.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>2478.727</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46139.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>2473.377</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46139.5</v>
+      </c>
+      <c r="B338">
+        <v>2472.51</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46139.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>2468.958</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46139.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>2458.091</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46139.53125</v>
+      </c>
+      <c r="B341">
+        <v>2436.669</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46139.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>2360.532</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46139.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>2338.583</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46139.5625</v>
+      </c>
+      <c r="B344">
+        <v>2288.484</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46139.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>2246.35</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46139.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>2280.126</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46139.59375</v>
+      </c>
+      <c r="B347">
+        <v>2252.695</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46139.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>2198.795</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46139.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>2150.394</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46139.625</v>
+      </c>
+      <c r="B350">
+        <v>2006.685</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46139.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>1926.59</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46139.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>2316.525</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46139.65625</v>
+      </c>
+      <c r="B353">
+        <v>2343.831</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46139.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>2114.306</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46139.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>1931.936</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46139.6875</v>
+      </c>
+      <c r="B356">
+        <v>1728.814</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46139.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>1510.767</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46139.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>1213.31</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46139.71875</v>
+      </c>
+      <c r="B359">
+        <v>1025.504</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46139.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>851.218</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46139.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>673.534</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46139.75</v>
+      </c>
+      <c r="B362">
+        <v>412.423</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46139.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>288.463</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46139.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>189.298</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46139.78125</v>
+      </c>
+      <c r="B365">
+        <v>118.653</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46139.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>49.565</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46139.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>26.854</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46139.8125</v>
+      </c>
+      <c r="B368">
+        <v>19.498</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46139.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>11.777</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46139.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>15.123</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46139.84375</v>
+      </c>
+      <c r="B371">
+        <v>15.124</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46139.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>13.759</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46139.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>6.267</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46139.875</v>
+      </c>
+      <c r="B374">
+        <v>12.33</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46139.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>10.03</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46139.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>9.33</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46139.90625</v>
+      </c>
+      <c r="B377">
+        <v>4.03</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46139.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>2.03</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46139.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0.73</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46139.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46139.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46139.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46139.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46139.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46139.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,1156 +31,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>24.04.20261</t>
-  </si>
-  <si>
-    <t>24.04.20262</t>
-  </si>
-  <si>
-    <t>24.04.20263</t>
-  </si>
-  <si>
-    <t>24.04.20264</t>
-  </si>
-  <si>
-    <t>24.04.20265</t>
-  </si>
-  <si>
-    <t>24.04.20266</t>
-  </si>
-  <si>
-    <t>24.04.20267</t>
-  </si>
-  <si>
-    <t>24.04.20268</t>
-  </si>
-  <si>
-    <t>24.04.20269</t>
-  </si>
-  <si>
-    <t>24.04.202610</t>
-  </si>
-  <si>
-    <t>24.04.202611</t>
-  </si>
-  <si>
-    <t>24.04.202612</t>
-  </si>
-  <si>
-    <t>24.04.202613</t>
-  </si>
-  <si>
-    <t>24.04.202614</t>
-  </si>
-  <si>
-    <t>24.04.202615</t>
-  </si>
-  <si>
-    <t>24.04.202616</t>
-  </si>
-  <si>
-    <t>24.04.202617</t>
-  </si>
-  <si>
-    <t>24.04.202618</t>
-  </si>
-  <si>
-    <t>24.04.202619</t>
-  </si>
-  <si>
-    <t>24.04.202620</t>
-  </si>
-  <si>
-    <t>24.04.202621</t>
-  </si>
-  <si>
-    <t>24.04.202622</t>
-  </si>
-  <si>
-    <t>24.04.202623</t>
-  </si>
-  <si>
-    <t>24.04.202624</t>
-  </si>
-  <si>
-    <t>24.04.202625</t>
-  </si>
-  <si>
-    <t>24.04.202626</t>
-  </si>
-  <si>
-    <t>24.04.202627</t>
-  </si>
-  <si>
-    <t>24.04.202628</t>
-  </si>
-  <si>
-    <t>24.04.202629</t>
-  </si>
-  <si>
-    <t>24.04.202630</t>
-  </si>
-  <si>
-    <t>24.04.202631</t>
-  </si>
-  <si>
-    <t>24.04.202632</t>
-  </si>
-  <si>
-    <t>24.04.202633</t>
-  </si>
-  <si>
-    <t>24.04.202634</t>
-  </si>
-  <si>
-    <t>24.04.202635</t>
-  </si>
-  <si>
-    <t>24.04.202636</t>
-  </si>
-  <si>
-    <t>24.04.202637</t>
-  </si>
-  <si>
-    <t>24.04.202638</t>
-  </si>
-  <si>
-    <t>24.04.202639</t>
-  </si>
-  <si>
-    <t>24.04.202640</t>
-  </si>
-  <si>
-    <t>24.04.202641</t>
-  </si>
-  <si>
-    <t>24.04.202642</t>
-  </si>
-  <si>
-    <t>24.04.202643</t>
-  </si>
-  <si>
-    <t>24.04.202644</t>
-  </si>
-  <si>
-    <t>24.04.202645</t>
-  </si>
-  <si>
-    <t>24.04.202646</t>
-  </si>
-  <si>
-    <t>24.04.202647</t>
-  </si>
-  <si>
-    <t>24.04.202648</t>
-  </si>
-  <si>
-    <t>24.04.202649</t>
-  </si>
-  <si>
-    <t>24.04.202650</t>
-  </si>
-  <si>
-    <t>24.04.202651</t>
-  </si>
-  <si>
-    <t>24.04.202652</t>
-  </si>
-  <si>
-    <t>24.04.202653</t>
-  </si>
-  <si>
-    <t>24.04.202654</t>
-  </si>
-  <si>
-    <t>24.04.202655</t>
-  </si>
-  <si>
-    <t>24.04.202656</t>
-  </si>
-  <si>
-    <t>24.04.202657</t>
-  </si>
-  <si>
-    <t>24.04.202658</t>
-  </si>
-  <si>
-    <t>24.04.202659</t>
-  </si>
-  <si>
-    <t>24.04.202660</t>
-  </si>
-  <si>
-    <t>24.04.202661</t>
-  </si>
-  <si>
-    <t>24.04.202662</t>
-  </si>
-  <si>
-    <t>24.04.202663</t>
-  </si>
-  <si>
-    <t>24.04.202664</t>
-  </si>
-  <si>
-    <t>24.04.202665</t>
-  </si>
-  <si>
-    <t>24.04.202666</t>
-  </si>
-  <si>
-    <t>24.04.202667</t>
-  </si>
-  <si>
-    <t>24.04.202668</t>
-  </si>
-  <si>
-    <t>24.04.202669</t>
-  </si>
-  <si>
-    <t>24.04.202670</t>
-  </si>
-  <si>
-    <t>24.04.202671</t>
-  </si>
-  <si>
-    <t>24.04.202672</t>
-  </si>
-  <si>
-    <t>24.04.202673</t>
-  </si>
-  <si>
-    <t>24.04.202674</t>
-  </si>
-  <si>
-    <t>24.04.202675</t>
-  </si>
-  <si>
-    <t>24.04.202676</t>
-  </si>
-  <si>
-    <t>24.04.202677</t>
-  </si>
-  <si>
-    <t>24.04.202678</t>
-  </si>
-  <si>
-    <t>24.04.202679</t>
-  </si>
-  <si>
-    <t>24.04.202680</t>
-  </si>
-  <si>
-    <t>24.04.202681</t>
-  </si>
-  <si>
-    <t>24.04.202682</t>
-  </si>
-  <si>
-    <t>24.04.202683</t>
-  </si>
-  <si>
-    <t>24.04.202684</t>
-  </si>
-  <si>
-    <t>24.04.202685</t>
-  </si>
-  <si>
-    <t>24.04.202686</t>
-  </si>
-  <si>
-    <t>24.04.202687</t>
-  </si>
-  <si>
-    <t>24.04.202688</t>
-  </si>
-  <si>
-    <t>24.04.202689</t>
-  </si>
-  <si>
-    <t>24.04.202690</t>
-  </si>
-  <si>
-    <t>24.04.202691</t>
-  </si>
-  <si>
-    <t>24.04.202692</t>
-  </si>
-  <si>
-    <t>24.04.202693</t>
-  </si>
-  <si>
-    <t>24.04.202694</t>
-  </si>
-  <si>
-    <t>24.04.202695</t>
-  </si>
-  <si>
-    <t>24.04.202696</t>
-  </si>
-  <si>
-    <t>25.04.20261</t>
-  </si>
-  <si>
-    <t>25.04.20262</t>
-  </si>
-  <si>
-    <t>25.04.20263</t>
-  </si>
-  <si>
-    <t>25.04.20264</t>
-  </si>
-  <si>
-    <t>25.04.20265</t>
-  </si>
-  <si>
-    <t>25.04.20266</t>
-  </si>
-  <si>
-    <t>25.04.20267</t>
-  </si>
-  <si>
-    <t>25.04.20268</t>
-  </si>
-  <si>
-    <t>25.04.20269</t>
-  </si>
-  <si>
-    <t>25.04.202610</t>
-  </si>
-  <si>
-    <t>25.04.202611</t>
-  </si>
-  <si>
-    <t>25.04.202612</t>
-  </si>
-  <si>
-    <t>25.04.202613</t>
-  </si>
-  <si>
-    <t>25.04.202614</t>
-  </si>
-  <si>
-    <t>25.04.202615</t>
-  </si>
-  <si>
-    <t>25.04.202616</t>
-  </si>
-  <si>
-    <t>25.04.202617</t>
-  </si>
-  <si>
-    <t>25.04.202618</t>
-  </si>
-  <si>
-    <t>25.04.202619</t>
-  </si>
-  <si>
-    <t>25.04.202620</t>
-  </si>
-  <si>
-    <t>25.04.202621</t>
-  </si>
-  <si>
-    <t>25.04.202622</t>
-  </si>
-  <si>
-    <t>25.04.202623</t>
-  </si>
-  <si>
-    <t>25.04.202624</t>
-  </si>
-  <si>
-    <t>25.04.202625</t>
-  </si>
-  <si>
-    <t>25.04.202626</t>
-  </si>
-  <si>
-    <t>25.04.202627</t>
-  </si>
-  <si>
-    <t>25.04.202628</t>
-  </si>
-  <si>
-    <t>25.04.202629</t>
-  </si>
-  <si>
-    <t>25.04.202630</t>
-  </si>
-  <si>
-    <t>25.04.202631</t>
-  </si>
-  <si>
-    <t>25.04.202632</t>
-  </si>
-  <si>
-    <t>25.04.202633</t>
-  </si>
-  <si>
-    <t>25.04.202634</t>
-  </si>
-  <si>
-    <t>25.04.202635</t>
-  </si>
-  <si>
-    <t>25.04.202636</t>
-  </si>
-  <si>
-    <t>25.04.202637</t>
-  </si>
-  <si>
-    <t>25.04.202638</t>
-  </si>
-  <si>
-    <t>25.04.202639</t>
-  </si>
-  <si>
-    <t>25.04.202640</t>
-  </si>
-  <si>
-    <t>25.04.202641</t>
-  </si>
-  <si>
-    <t>25.04.202642</t>
-  </si>
-  <si>
-    <t>25.04.202643</t>
-  </si>
-  <si>
-    <t>25.04.202644</t>
-  </si>
-  <si>
-    <t>25.04.202645</t>
-  </si>
-  <si>
-    <t>25.04.202646</t>
-  </si>
-  <si>
-    <t>25.04.202647</t>
-  </si>
-  <si>
-    <t>25.04.202648</t>
-  </si>
-  <si>
-    <t>25.04.202649</t>
-  </si>
-  <si>
-    <t>25.04.202650</t>
-  </si>
-  <si>
-    <t>25.04.202651</t>
-  </si>
-  <si>
-    <t>25.04.202652</t>
-  </si>
-  <si>
-    <t>25.04.202653</t>
-  </si>
-  <si>
-    <t>25.04.202654</t>
-  </si>
-  <si>
-    <t>25.04.202655</t>
-  </si>
-  <si>
-    <t>25.04.202656</t>
-  </si>
-  <si>
-    <t>25.04.202657</t>
-  </si>
-  <si>
-    <t>25.04.202658</t>
-  </si>
-  <si>
-    <t>25.04.202659</t>
-  </si>
-  <si>
-    <t>25.04.202660</t>
-  </si>
-  <si>
-    <t>25.04.202661</t>
-  </si>
-  <si>
-    <t>25.04.202662</t>
-  </si>
-  <si>
-    <t>25.04.202663</t>
-  </si>
-  <si>
-    <t>25.04.202664</t>
-  </si>
-  <si>
-    <t>25.04.202665</t>
-  </si>
-  <si>
-    <t>25.04.202666</t>
-  </si>
-  <si>
-    <t>25.04.202667</t>
-  </si>
-  <si>
-    <t>25.04.202668</t>
-  </si>
-  <si>
-    <t>25.04.202669</t>
-  </si>
-  <si>
-    <t>25.04.202670</t>
-  </si>
-  <si>
-    <t>25.04.202671</t>
-  </si>
-  <si>
-    <t>25.04.202672</t>
-  </si>
-  <si>
-    <t>25.04.202673</t>
-  </si>
-  <si>
-    <t>25.04.202674</t>
-  </si>
-  <si>
-    <t>25.04.202675</t>
-  </si>
-  <si>
-    <t>25.04.202676</t>
-  </si>
-  <si>
-    <t>25.04.202677</t>
-  </si>
-  <si>
-    <t>25.04.202678</t>
-  </si>
-  <si>
-    <t>25.04.202679</t>
-  </si>
-  <si>
-    <t>25.04.202680</t>
-  </si>
-  <si>
-    <t>25.04.202681</t>
-  </si>
-  <si>
-    <t>25.04.202682</t>
-  </si>
-  <si>
-    <t>25.04.202683</t>
-  </si>
-  <si>
-    <t>25.04.202684</t>
-  </si>
-  <si>
-    <t>25.04.202685</t>
-  </si>
-  <si>
-    <t>25.04.202686</t>
-  </si>
-  <si>
-    <t>25.04.202687</t>
-  </si>
-  <si>
-    <t>25.04.202688</t>
-  </si>
-  <si>
-    <t>25.04.202689</t>
-  </si>
-  <si>
-    <t>25.04.202690</t>
-  </si>
-  <si>
-    <t>25.04.202691</t>
-  </si>
-  <si>
-    <t>25.04.202692</t>
-  </si>
-  <si>
-    <t>25.04.202693</t>
-  </si>
-  <si>
-    <t>25.04.202694</t>
-  </si>
-  <si>
-    <t>25.04.202695</t>
-  </si>
-  <si>
-    <t>25.04.202696</t>
-  </si>
-  <si>
-    <t>26.04.20261</t>
-  </si>
-  <si>
-    <t>26.04.20262</t>
-  </si>
-  <si>
-    <t>26.04.20263</t>
-  </si>
-  <si>
-    <t>26.04.20264</t>
-  </si>
-  <si>
-    <t>26.04.20265</t>
-  </si>
-  <si>
-    <t>26.04.20266</t>
-  </si>
-  <si>
-    <t>26.04.20267</t>
-  </si>
-  <si>
-    <t>26.04.20268</t>
-  </si>
-  <si>
-    <t>26.04.20269</t>
-  </si>
-  <si>
-    <t>26.04.202610</t>
-  </si>
-  <si>
-    <t>26.04.202611</t>
-  </si>
-  <si>
-    <t>26.04.202612</t>
-  </si>
-  <si>
-    <t>26.04.202613</t>
-  </si>
-  <si>
-    <t>26.04.202614</t>
-  </si>
-  <si>
-    <t>26.04.202615</t>
-  </si>
-  <si>
-    <t>26.04.202616</t>
-  </si>
-  <si>
-    <t>26.04.202617</t>
-  </si>
-  <si>
-    <t>26.04.202618</t>
-  </si>
-  <si>
-    <t>26.04.202619</t>
-  </si>
-  <si>
-    <t>26.04.202620</t>
-  </si>
-  <si>
-    <t>26.04.202621</t>
-  </si>
-  <si>
-    <t>26.04.202622</t>
-  </si>
-  <si>
-    <t>26.04.202623</t>
-  </si>
-  <si>
-    <t>26.04.202624</t>
-  </si>
-  <si>
-    <t>26.04.202625</t>
-  </si>
-  <si>
-    <t>26.04.202626</t>
-  </si>
-  <si>
-    <t>26.04.202627</t>
-  </si>
-  <si>
-    <t>26.04.202628</t>
-  </si>
-  <si>
-    <t>26.04.202629</t>
-  </si>
-  <si>
-    <t>26.04.202630</t>
-  </si>
-  <si>
-    <t>26.04.202631</t>
-  </si>
-  <si>
-    <t>26.04.202632</t>
-  </si>
-  <si>
-    <t>26.04.202633</t>
-  </si>
-  <si>
-    <t>26.04.202634</t>
-  </si>
-  <si>
-    <t>26.04.202635</t>
-  </si>
-  <si>
-    <t>26.04.202636</t>
-  </si>
-  <si>
-    <t>26.04.202637</t>
-  </si>
-  <si>
-    <t>26.04.202638</t>
-  </si>
-  <si>
-    <t>26.04.202639</t>
-  </si>
-  <si>
-    <t>26.04.202640</t>
-  </si>
-  <si>
-    <t>26.04.202641</t>
-  </si>
-  <si>
-    <t>26.04.202642</t>
-  </si>
-  <si>
-    <t>26.04.202643</t>
-  </si>
-  <si>
-    <t>26.04.202644</t>
-  </si>
-  <si>
-    <t>26.04.202645</t>
-  </si>
-  <si>
-    <t>26.04.202646</t>
-  </si>
-  <si>
-    <t>26.04.202647</t>
-  </si>
-  <si>
-    <t>26.04.202648</t>
-  </si>
-  <si>
-    <t>26.04.202649</t>
-  </si>
-  <si>
-    <t>26.04.202650</t>
-  </si>
-  <si>
-    <t>26.04.202651</t>
-  </si>
-  <si>
-    <t>26.04.202652</t>
-  </si>
-  <si>
-    <t>26.04.202653</t>
-  </si>
-  <si>
-    <t>26.04.202654</t>
-  </si>
-  <si>
-    <t>26.04.202655</t>
-  </si>
-  <si>
-    <t>26.04.202656</t>
-  </si>
-  <si>
-    <t>26.04.202657</t>
-  </si>
-  <si>
-    <t>26.04.202658</t>
-  </si>
-  <si>
-    <t>26.04.202659</t>
-  </si>
-  <si>
-    <t>26.04.202660</t>
-  </si>
-  <si>
-    <t>26.04.202661</t>
-  </si>
-  <si>
-    <t>26.04.202662</t>
-  </si>
-  <si>
-    <t>26.04.202663</t>
-  </si>
-  <si>
-    <t>26.04.202664</t>
-  </si>
-  <si>
-    <t>26.04.202665</t>
-  </si>
-  <si>
-    <t>26.04.202666</t>
-  </si>
-  <si>
-    <t>26.04.202667</t>
-  </si>
-  <si>
-    <t>26.04.202668</t>
-  </si>
-  <si>
-    <t>26.04.202669</t>
-  </si>
-  <si>
-    <t>26.04.202670</t>
-  </si>
-  <si>
-    <t>26.04.202671</t>
-  </si>
-  <si>
-    <t>26.04.202672</t>
-  </si>
-  <si>
-    <t>26.04.202673</t>
-  </si>
-  <si>
-    <t>26.04.202674</t>
-  </si>
-  <si>
-    <t>26.04.202675</t>
-  </si>
-  <si>
-    <t>26.04.202676</t>
-  </si>
-  <si>
-    <t>26.04.202677</t>
-  </si>
-  <si>
-    <t>26.04.202678</t>
-  </si>
-  <si>
-    <t>26.04.202679</t>
-  </si>
-  <si>
-    <t>26.04.202680</t>
-  </si>
-  <si>
-    <t>26.04.202681</t>
-  </si>
-  <si>
-    <t>26.04.202682</t>
-  </si>
-  <si>
-    <t>26.04.202683</t>
-  </si>
-  <si>
-    <t>26.04.202684</t>
-  </si>
-  <si>
-    <t>26.04.202685</t>
-  </si>
-  <si>
-    <t>26.04.202686</t>
-  </si>
-  <si>
-    <t>26.04.202687</t>
-  </si>
-  <si>
-    <t>26.04.202688</t>
-  </si>
-  <si>
-    <t>26.04.202689</t>
-  </si>
-  <si>
-    <t>26.04.202690</t>
-  </si>
-  <si>
-    <t>26.04.202691</t>
-  </si>
-  <si>
-    <t>26.04.202692</t>
-  </si>
-  <si>
-    <t>26.04.202693</t>
-  </si>
-  <si>
-    <t>26.04.202694</t>
-  </si>
-  <si>
-    <t>26.04.202695</t>
-  </si>
-  <si>
-    <t>26.04.202696</t>
-  </si>
-  <si>
-    <t>27.04.20261</t>
-  </si>
-  <si>
-    <t>27.04.20262</t>
-  </si>
-  <si>
-    <t>27.04.20263</t>
-  </si>
-  <si>
-    <t>27.04.20264</t>
-  </si>
-  <si>
-    <t>27.04.20265</t>
-  </si>
-  <si>
-    <t>27.04.20266</t>
-  </si>
-  <si>
-    <t>27.04.20267</t>
-  </si>
-  <si>
-    <t>27.04.20268</t>
-  </si>
-  <si>
-    <t>27.04.20269</t>
-  </si>
-  <si>
-    <t>27.04.202610</t>
-  </si>
-  <si>
-    <t>27.04.202611</t>
-  </si>
-  <si>
-    <t>27.04.202612</t>
-  </si>
-  <si>
-    <t>27.04.202613</t>
-  </si>
-  <si>
-    <t>27.04.202614</t>
-  </si>
-  <si>
-    <t>27.04.202615</t>
-  </si>
-  <si>
-    <t>27.04.202616</t>
-  </si>
-  <si>
-    <t>27.04.202617</t>
-  </si>
-  <si>
-    <t>27.04.202618</t>
-  </si>
-  <si>
-    <t>27.04.202619</t>
-  </si>
-  <si>
-    <t>27.04.202620</t>
-  </si>
-  <si>
-    <t>27.04.202621</t>
-  </si>
-  <si>
-    <t>27.04.202622</t>
-  </si>
-  <si>
-    <t>27.04.202623</t>
-  </si>
-  <si>
-    <t>27.04.202624</t>
-  </si>
-  <si>
-    <t>27.04.202625</t>
-  </si>
-  <si>
-    <t>27.04.202626</t>
-  </si>
-  <si>
-    <t>27.04.202627</t>
-  </si>
-  <si>
-    <t>27.04.202628</t>
-  </si>
-  <si>
-    <t>27.04.202629</t>
-  </si>
-  <si>
-    <t>27.04.202630</t>
-  </si>
-  <si>
-    <t>27.04.202631</t>
-  </si>
-  <si>
-    <t>27.04.202632</t>
-  </si>
-  <si>
-    <t>27.04.202633</t>
-  </si>
-  <si>
-    <t>27.04.202634</t>
-  </si>
-  <si>
-    <t>27.04.202635</t>
-  </si>
-  <si>
-    <t>27.04.202636</t>
-  </si>
-  <si>
-    <t>27.04.202637</t>
-  </si>
-  <si>
-    <t>27.04.202638</t>
-  </si>
-  <si>
-    <t>27.04.202639</t>
-  </si>
-  <si>
-    <t>27.04.202640</t>
-  </si>
-  <si>
-    <t>27.04.202641</t>
-  </si>
-  <si>
-    <t>27.04.202642</t>
-  </si>
-  <si>
-    <t>27.04.202643</t>
-  </si>
-  <si>
-    <t>27.04.202644</t>
-  </si>
-  <si>
-    <t>27.04.202645</t>
-  </si>
-  <si>
-    <t>27.04.202646</t>
-  </si>
-  <si>
-    <t>27.04.202647</t>
-  </si>
-  <si>
-    <t>27.04.202648</t>
-  </si>
-  <si>
-    <t>27.04.202649</t>
-  </si>
-  <si>
-    <t>27.04.202650</t>
-  </si>
-  <si>
-    <t>27.04.202651</t>
-  </si>
-  <si>
-    <t>27.04.202652</t>
-  </si>
-  <si>
-    <t>27.04.202653</t>
-  </si>
-  <si>
-    <t>27.04.202654</t>
-  </si>
-  <si>
-    <t>27.04.202655</t>
-  </si>
-  <si>
-    <t>27.04.202656</t>
-  </si>
-  <si>
-    <t>27.04.202657</t>
-  </si>
-  <si>
-    <t>27.04.202658</t>
-  </si>
-  <si>
-    <t>27.04.202659</t>
-  </si>
-  <si>
-    <t>27.04.202660</t>
-  </si>
-  <si>
-    <t>27.04.202661</t>
-  </si>
-  <si>
-    <t>27.04.202662</t>
-  </si>
-  <si>
-    <t>27.04.202663</t>
-  </si>
-  <si>
-    <t>27.04.202664</t>
-  </si>
-  <si>
-    <t>27.04.202665</t>
-  </si>
-  <si>
-    <t>27.04.202666</t>
-  </si>
-  <si>
-    <t>27.04.202667</t>
-  </si>
-  <si>
-    <t>27.04.202668</t>
-  </si>
-  <si>
-    <t>27.04.202669</t>
-  </si>
-  <si>
-    <t>27.04.202670</t>
-  </si>
-  <si>
-    <t>27.04.202671</t>
-  </si>
-  <si>
-    <t>27.04.202672</t>
-  </si>
-  <si>
-    <t>27.04.202673</t>
-  </si>
-  <si>
-    <t>27.04.202674</t>
-  </si>
-  <si>
-    <t>27.04.202675</t>
-  </si>
-  <si>
-    <t>27.04.202676</t>
-  </si>
-  <si>
-    <t>27.04.202677</t>
-  </si>
-  <si>
-    <t>27.04.202678</t>
-  </si>
-  <si>
-    <t>27.04.202679</t>
-  </si>
-  <si>
-    <t>27.04.202680</t>
-  </si>
-  <si>
-    <t>27.04.202681</t>
-  </si>
-  <si>
-    <t>27.04.202682</t>
-  </si>
-  <si>
-    <t>27.04.202683</t>
-  </si>
-  <si>
-    <t>27.04.202684</t>
-  </si>
-  <si>
-    <t>27.04.202685</t>
-  </si>
-  <si>
-    <t>27.04.202686</t>
-  </si>
-  <si>
-    <t>27.04.202687</t>
-  </si>
-  <si>
-    <t>27.04.202688</t>
-  </si>
-  <si>
-    <t>27.04.202689</t>
-  </si>
-  <si>
-    <t>27.04.202690</t>
-  </si>
-  <si>
-    <t>27.04.202691</t>
-  </si>
-  <si>
-    <t>27.04.202692</t>
-  </si>
-  <si>
-    <t>27.04.202693</t>
-  </si>
-  <si>
-    <t>27.04.202694</t>
-  </si>
-  <si>
-    <t>27.04.202695</t>
-  </si>
-  <si>
-    <t>27.04.202696</t>
+    <t>28.04.20261</t>
+  </si>
+  <si>
+    <t>28.04.20262</t>
+  </si>
+  <si>
+    <t>28.04.20263</t>
+  </si>
+  <si>
+    <t>28.04.20264</t>
+  </si>
+  <si>
+    <t>28.04.20265</t>
+  </si>
+  <si>
+    <t>28.04.20266</t>
+  </si>
+  <si>
+    <t>28.04.20267</t>
+  </si>
+  <si>
+    <t>28.04.20268</t>
+  </si>
+  <si>
+    <t>28.04.20269</t>
+  </si>
+  <si>
+    <t>28.04.202610</t>
+  </si>
+  <si>
+    <t>28.04.202611</t>
+  </si>
+  <si>
+    <t>28.04.202612</t>
+  </si>
+  <si>
+    <t>28.04.202613</t>
+  </si>
+  <si>
+    <t>28.04.202614</t>
+  </si>
+  <si>
+    <t>28.04.202615</t>
+  </si>
+  <si>
+    <t>28.04.202616</t>
+  </si>
+  <si>
+    <t>28.04.202617</t>
+  </si>
+  <si>
+    <t>28.04.202618</t>
+  </si>
+  <si>
+    <t>28.04.202619</t>
+  </si>
+  <si>
+    <t>28.04.202620</t>
+  </si>
+  <si>
+    <t>28.04.202621</t>
+  </si>
+  <si>
+    <t>28.04.202622</t>
+  </si>
+  <si>
+    <t>28.04.202623</t>
+  </si>
+  <si>
+    <t>28.04.202624</t>
+  </si>
+  <si>
+    <t>28.04.202625</t>
+  </si>
+  <si>
+    <t>28.04.202626</t>
+  </si>
+  <si>
+    <t>28.04.202627</t>
+  </si>
+  <si>
+    <t>28.04.202628</t>
+  </si>
+  <si>
+    <t>28.04.202629</t>
+  </si>
+  <si>
+    <t>28.04.202630</t>
+  </si>
+  <si>
+    <t>28.04.202631</t>
+  </si>
+  <si>
+    <t>28.04.202632</t>
+  </si>
+  <si>
+    <t>28.04.202633</t>
+  </si>
+  <si>
+    <t>28.04.202634</t>
+  </si>
+  <si>
+    <t>28.04.202635</t>
+  </si>
+  <si>
+    <t>28.04.202636</t>
+  </si>
+  <si>
+    <t>28.04.202637</t>
+  </si>
+  <si>
+    <t>28.04.202638</t>
+  </si>
+  <si>
+    <t>28.04.202639</t>
+  </si>
+  <si>
+    <t>28.04.202640</t>
+  </si>
+  <si>
+    <t>28.04.202641</t>
+  </si>
+  <si>
+    <t>28.04.202642</t>
+  </si>
+  <si>
+    <t>28.04.202643</t>
+  </si>
+  <si>
+    <t>28.04.202644</t>
+  </si>
+  <si>
+    <t>28.04.202645</t>
+  </si>
+  <si>
+    <t>28.04.202646</t>
+  </si>
+  <si>
+    <t>28.04.202647</t>
+  </si>
+  <si>
+    <t>28.04.202648</t>
+  </si>
+  <si>
+    <t>28.04.202649</t>
+  </si>
+  <si>
+    <t>28.04.202650</t>
+  </si>
+  <si>
+    <t>28.04.202651</t>
+  </si>
+  <si>
+    <t>28.04.202652</t>
+  </si>
+  <si>
+    <t>28.04.202653</t>
+  </si>
+  <si>
+    <t>28.04.202654</t>
+  </si>
+  <si>
+    <t>28.04.202655</t>
+  </si>
+  <si>
+    <t>28.04.202656</t>
+  </si>
+  <si>
+    <t>28.04.202657</t>
+  </si>
+  <si>
+    <t>28.04.202658</t>
+  </si>
+  <si>
+    <t>28.04.202659</t>
+  </si>
+  <si>
+    <t>28.04.202660</t>
+  </si>
+  <si>
+    <t>28.04.202661</t>
+  </si>
+  <si>
+    <t>28.04.202662</t>
+  </si>
+  <si>
+    <t>28.04.202663</t>
+  </si>
+  <si>
+    <t>28.04.202664</t>
+  </si>
+  <si>
+    <t>28.04.202665</t>
+  </si>
+  <si>
+    <t>28.04.202666</t>
+  </si>
+  <si>
+    <t>28.04.202667</t>
+  </si>
+  <si>
+    <t>28.04.202668</t>
+  </si>
+  <si>
+    <t>28.04.202669</t>
+  </si>
+  <si>
+    <t>28.04.202670</t>
+  </si>
+  <si>
+    <t>28.04.202671</t>
+  </si>
+  <si>
+    <t>28.04.202672</t>
+  </si>
+  <si>
+    <t>28.04.202673</t>
+  </si>
+  <si>
+    <t>28.04.202674</t>
+  </si>
+  <si>
+    <t>28.04.202675</t>
+  </si>
+  <si>
+    <t>28.04.202676</t>
+  </si>
+  <si>
+    <t>28.04.202677</t>
+  </si>
+  <si>
+    <t>28.04.202678</t>
+  </si>
+  <si>
+    <t>28.04.202679</t>
+  </si>
+  <si>
+    <t>28.04.202680</t>
+  </si>
+  <si>
+    <t>28.04.202681</t>
+  </si>
+  <si>
+    <t>28.04.202682</t>
+  </si>
+  <si>
+    <t>28.04.202683</t>
+  </si>
+  <si>
+    <t>28.04.202684</t>
+  </si>
+  <si>
+    <t>28.04.202685</t>
+  </si>
+  <si>
+    <t>28.04.202686</t>
+  </si>
+  <si>
+    <t>28.04.202687</t>
+  </si>
+  <si>
+    <t>28.04.202688</t>
+  </si>
+  <si>
+    <t>28.04.202689</t>
+  </si>
+  <si>
+    <t>28.04.202690</t>
+  </si>
+  <si>
+    <t>28.04.202691</t>
+  </si>
+  <si>
+    <t>28.04.202692</t>
+  </si>
+  <si>
+    <t>28.04.202693</t>
+  </si>
+  <si>
+    <t>28.04.202694</t>
+  </si>
+  <si>
+    <t>28.04.202695</t>
+  </si>
+  <si>
+    <t>28.04.202696</t>
+  </si>
+  <si>
+    <t>29.04.20261</t>
+  </si>
+  <si>
+    <t>29.04.20262</t>
+  </si>
+  <si>
+    <t>29.04.20263</t>
+  </si>
+  <si>
+    <t>29.04.20264</t>
+  </si>
+  <si>
+    <t>29.04.20265</t>
+  </si>
+  <si>
+    <t>29.04.20266</t>
+  </si>
+  <si>
+    <t>29.04.20267</t>
+  </si>
+  <si>
+    <t>29.04.20268</t>
+  </si>
+  <si>
+    <t>29.04.20269</t>
+  </si>
+  <si>
+    <t>29.04.202610</t>
+  </si>
+  <si>
+    <t>29.04.202611</t>
+  </si>
+  <si>
+    <t>29.04.202612</t>
+  </si>
+  <si>
+    <t>29.04.202613</t>
+  </si>
+  <si>
+    <t>29.04.202614</t>
+  </si>
+  <si>
+    <t>29.04.202615</t>
+  </si>
+  <si>
+    <t>29.04.202616</t>
+  </si>
+  <si>
+    <t>29.04.202617</t>
+  </si>
+  <si>
+    <t>29.04.202618</t>
+  </si>
+  <si>
+    <t>29.04.202619</t>
+  </si>
+  <si>
+    <t>29.04.202620</t>
+  </si>
+  <si>
+    <t>29.04.202621</t>
+  </si>
+  <si>
+    <t>29.04.202622</t>
+  </si>
+  <si>
+    <t>29.04.202623</t>
+  </si>
+  <si>
+    <t>29.04.202624</t>
+  </si>
+  <si>
+    <t>29.04.202625</t>
+  </si>
+  <si>
+    <t>29.04.202626</t>
+  </si>
+  <si>
+    <t>29.04.202627</t>
+  </si>
+  <si>
+    <t>29.04.202628</t>
+  </si>
+  <si>
+    <t>29.04.202629</t>
+  </si>
+  <si>
+    <t>29.04.202630</t>
+  </si>
+  <si>
+    <t>29.04.202631</t>
+  </si>
+  <si>
+    <t>29.04.202632</t>
+  </si>
+  <si>
+    <t>29.04.202633</t>
+  </si>
+  <si>
+    <t>29.04.202634</t>
+  </si>
+  <si>
+    <t>29.04.202635</t>
+  </si>
+  <si>
+    <t>29.04.202636</t>
+  </si>
+  <si>
+    <t>29.04.202637</t>
+  </si>
+  <si>
+    <t>29.04.202638</t>
+  </si>
+  <si>
+    <t>29.04.202639</t>
+  </si>
+  <si>
+    <t>29.04.202640</t>
+  </si>
+  <si>
+    <t>29.04.202641</t>
+  </si>
+  <si>
+    <t>29.04.202642</t>
+  </si>
+  <si>
+    <t>29.04.202643</t>
+  </si>
+  <si>
+    <t>29.04.202644</t>
+  </si>
+  <si>
+    <t>29.04.202645</t>
+  </si>
+  <si>
+    <t>29.04.202646</t>
+  </si>
+  <si>
+    <t>29.04.202647</t>
+  </si>
+  <si>
+    <t>29.04.202648</t>
+  </si>
+  <si>
+    <t>29.04.202649</t>
+  </si>
+  <si>
+    <t>29.04.202650</t>
+  </si>
+  <si>
+    <t>29.04.202651</t>
+  </si>
+  <si>
+    <t>29.04.202652</t>
+  </si>
+  <si>
+    <t>29.04.202653</t>
+  </si>
+  <si>
+    <t>29.04.202654</t>
+  </si>
+  <si>
+    <t>29.04.202655</t>
+  </si>
+  <si>
+    <t>29.04.202656</t>
+  </si>
+  <si>
+    <t>29.04.202657</t>
+  </si>
+  <si>
+    <t>29.04.202658</t>
+  </si>
+  <si>
+    <t>29.04.202659</t>
+  </si>
+  <si>
+    <t>29.04.202660</t>
+  </si>
+  <si>
+    <t>29.04.202661</t>
+  </si>
+  <si>
+    <t>29.04.202662</t>
+  </si>
+  <si>
+    <t>29.04.202663</t>
+  </si>
+  <si>
+    <t>29.04.202664</t>
+  </si>
+  <si>
+    <t>29.04.202665</t>
+  </si>
+  <si>
+    <t>29.04.202666</t>
+  </si>
+  <si>
+    <t>29.04.202667</t>
+  </si>
+  <si>
+    <t>29.04.202668</t>
+  </si>
+  <si>
+    <t>29.04.202669</t>
+  </si>
+  <si>
+    <t>29.04.202670</t>
+  </si>
+  <si>
+    <t>29.04.202671</t>
+  </si>
+  <si>
+    <t>29.04.202672</t>
+  </si>
+  <si>
+    <t>29.04.202673</t>
+  </si>
+  <si>
+    <t>29.04.202674</t>
+  </si>
+  <si>
+    <t>29.04.202675</t>
+  </si>
+  <si>
+    <t>29.04.202676</t>
+  </si>
+  <si>
+    <t>29.04.202677</t>
+  </si>
+  <si>
+    <t>29.04.202678</t>
+  </si>
+  <si>
+    <t>29.04.202679</t>
+  </si>
+  <si>
+    <t>29.04.202680</t>
+  </si>
+  <si>
+    <t>29.04.202681</t>
+  </si>
+  <si>
+    <t>29.04.202682</t>
+  </si>
+  <si>
+    <t>29.04.202683</t>
+  </si>
+  <si>
+    <t>29.04.202684</t>
+  </si>
+  <si>
+    <t>29.04.202685</t>
+  </si>
+  <si>
+    <t>29.04.202686</t>
+  </si>
+  <si>
+    <t>29.04.202687</t>
+  </si>
+  <si>
+    <t>29.04.202688</t>
+  </si>
+  <si>
+    <t>29.04.202689</t>
+  </si>
+  <si>
+    <t>29.04.202690</t>
+  </si>
+  <si>
+    <t>29.04.202691</t>
+  </si>
+  <si>
+    <t>29.04.202692</t>
+  </si>
+  <si>
+    <t>29.04.202693</t>
+  </si>
+  <si>
+    <t>29.04.202694</t>
+  </si>
+  <si>
+    <t>29.04.202695</t>
+  </si>
+  <si>
+    <t>29.04.202696</t>
+  </si>
+  <si>
+    <t>30.04.20261</t>
+  </si>
+  <si>
+    <t>30.04.20262</t>
+  </si>
+  <si>
+    <t>30.04.20263</t>
+  </si>
+  <si>
+    <t>30.04.20264</t>
+  </si>
+  <si>
+    <t>30.04.20265</t>
+  </si>
+  <si>
+    <t>30.04.20266</t>
+  </si>
+  <si>
+    <t>30.04.20267</t>
+  </si>
+  <si>
+    <t>30.04.20268</t>
+  </si>
+  <si>
+    <t>30.04.20269</t>
+  </si>
+  <si>
+    <t>30.04.202610</t>
+  </si>
+  <si>
+    <t>30.04.202611</t>
+  </si>
+  <si>
+    <t>30.04.202612</t>
+  </si>
+  <si>
+    <t>30.04.202613</t>
+  </si>
+  <si>
+    <t>30.04.202614</t>
+  </si>
+  <si>
+    <t>30.04.202615</t>
+  </si>
+  <si>
+    <t>30.04.202616</t>
+  </si>
+  <si>
+    <t>30.04.202617</t>
+  </si>
+  <si>
+    <t>30.04.202618</t>
+  </si>
+  <si>
+    <t>30.04.202619</t>
+  </si>
+  <si>
+    <t>30.04.202620</t>
+  </si>
+  <si>
+    <t>30.04.202621</t>
+  </si>
+  <si>
+    <t>30.04.202622</t>
+  </si>
+  <si>
+    <t>30.04.202623</t>
+  </si>
+  <si>
+    <t>30.04.202624</t>
+  </si>
+  <si>
+    <t>30.04.202625</t>
+  </si>
+  <si>
+    <t>30.04.202626</t>
+  </si>
+  <si>
+    <t>30.04.202627</t>
+  </si>
+  <si>
+    <t>30.04.202628</t>
+  </si>
+  <si>
+    <t>30.04.202629</t>
+  </si>
+  <si>
+    <t>30.04.202630</t>
+  </si>
+  <si>
+    <t>30.04.202631</t>
+  </si>
+  <si>
+    <t>30.04.202632</t>
+  </si>
+  <si>
+    <t>30.04.202633</t>
+  </si>
+  <si>
+    <t>30.04.202634</t>
+  </si>
+  <si>
+    <t>30.04.202635</t>
+  </si>
+  <si>
+    <t>30.04.202636</t>
+  </si>
+  <si>
+    <t>30.04.202637</t>
+  </si>
+  <si>
+    <t>30.04.202638</t>
+  </si>
+  <si>
+    <t>30.04.202639</t>
+  </si>
+  <si>
+    <t>30.04.202640</t>
+  </si>
+  <si>
+    <t>30.04.202641</t>
+  </si>
+  <si>
+    <t>30.04.202642</t>
+  </si>
+  <si>
+    <t>30.04.202643</t>
+  </si>
+  <si>
+    <t>30.04.202644</t>
+  </si>
+  <si>
+    <t>30.04.202645</t>
+  </si>
+  <si>
+    <t>30.04.202646</t>
+  </si>
+  <si>
+    <t>30.04.202647</t>
+  </si>
+  <si>
+    <t>30.04.202648</t>
+  </si>
+  <si>
+    <t>30.04.202649</t>
+  </si>
+  <si>
+    <t>30.04.202650</t>
+  </si>
+  <si>
+    <t>30.04.202651</t>
+  </si>
+  <si>
+    <t>30.04.202652</t>
+  </si>
+  <si>
+    <t>30.04.202653</t>
+  </si>
+  <si>
+    <t>30.04.202654</t>
+  </si>
+  <si>
+    <t>30.04.202655</t>
+  </si>
+  <si>
+    <t>30.04.202656</t>
+  </si>
+  <si>
+    <t>30.04.202657</t>
+  </si>
+  <si>
+    <t>30.04.202658</t>
+  </si>
+  <si>
+    <t>30.04.202659</t>
+  </si>
+  <si>
+    <t>30.04.202660</t>
+  </si>
+  <si>
+    <t>30.04.202661</t>
+  </si>
+  <si>
+    <t>30.04.202662</t>
+  </si>
+  <si>
+    <t>30.04.202663</t>
+  </si>
+  <si>
+    <t>30.04.202664</t>
+  </si>
+  <si>
+    <t>30.04.202665</t>
+  </si>
+  <si>
+    <t>30.04.202666</t>
+  </si>
+  <si>
+    <t>30.04.202667</t>
+  </si>
+  <si>
+    <t>30.04.202668</t>
+  </si>
+  <si>
+    <t>30.04.202669</t>
+  </si>
+  <si>
+    <t>30.04.202670</t>
+  </si>
+  <si>
+    <t>30.04.202671</t>
+  </si>
+  <si>
+    <t>30.04.202672</t>
+  </si>
+  <si>
+    <t>30.04.202673</t>
+  </si>
+  <si>
+    <t>30.04.202674</t>
+  </si>
+  <si>
+    <t>30.04.202675</t>
+  </si>
+  <si>
+    <t>30.04.202676</t>
+  </si>
+  <si>
+    <t>30.04.202677</t>
+  </si>
+  <si>
+    <t>30.04.202678</t>
+  </si>
+  <si>
+    <t>30.04.202679</t>
+  </si>
+  <si>
+    <t>30.04.202680</t>
+  </si>
+  <si>
+    <t>30.04.202681</t>
+  </si>
+  <si>
+    <t>30.04.202682</t>
+  </si>
+  <si>
+    <t>30.04.202683</t>
+  </si>
+  <si>
+    <t>30.04.202684</t>
+  </si>
+  <si>
+    <t>30.04.202685</t>
+  </si>
+  <si>
+    <t>30.04.202686</t>
+  </si>
+  <si>
+    <t>30.04.202687</t>
+  </si>
+  <si>
+    <t>30.04.202688</t>
+  </si>
+  <si>
+    <t>30.04.202689</t>
+  </si>
+  <si>
+    <t>30.04.202690</t>
+  </si>
+  <si>
+    <t>30.04.202691</t>
+  </si>
+  <si>
+    <t>30.04.202692</t>
+  </si>
+  <si>
+    <t>30.04.202693</t>
+  </si>
+  <si>
+    <t>30.04.202694</t>
+  </si>
+  <si>
+    <t>30.04.202695</t>
+  </si>
+  <si>
+    <t>30.04.202696</t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E385"/>
+  <dimension ref="A1:E289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1564,10 +1276,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B2">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1581,7 +1293,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46136.01041666666</v>
+        <v>46140.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1598,7 +1310,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46136.02083333334</v>
+        <v>46140.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1615,10 +1327,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46136.03125</v>
+        <v>46140.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1632,7 +1344,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46136.04166666666</v>
+        <v>46140.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1649,7 +1361,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46136.05208333334</v>
+        <v>46140.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1666,7 +1378,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46136.0625</v>
+        <v>46140.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1683,7 +1395,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46136.07291666666</v>
+        <v>46140.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1700,7 +1412,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46136.08333333334</v>
+        <v>46140.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1717,7 +1429,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46136.09375</v>
+        <v>46140.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1734,7 +1446,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46136.10416666666</v>
+        <v>46140.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1751,7 +1463,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46136.11458333334</v>
+        <v>46140.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1768,10 +1480,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46136.125</v>
+        <v>46140.125</v>
       </c>
       <c r="B14">
-        <v>0.905</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1785,7 +1497,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46136.13541666666</v>
+        <v>46140.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1802,7 +1514,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46136.14583333334</v>
+        <v>46140.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1819,7 +1531,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46136.15625</v>
+        <v>46140.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1836,10 +1548,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46136.16666666666</v>
+        <v>46140.16666666666</v>
       </c>
       <c r="B18">
-        <v>26.886</v>
+        <v>22.01</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1853,7 +1565,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46136.17708333334</v>
+        <v>46140.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1870,7 +1582,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46136.1875</v>
+        <v>46140.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1887,10 +1599,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46136.19791666666</v>
+        <v>46140.19791666666</v>
       </c>
       <c r="B21">
-        <v>26.89</v>
+        <v>22.034</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1904,10 +1616,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46136.20833333334</v>
+        <v>46140.20833333334</v>
       </c>
       <c r="B22">
-        <v>35.035</v>
+        <v>75.251</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1921,13 +1633,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46136.21875</v>
+        <v>46140.21875</v>
       </c>
       <c r="B23">
-        <v>37.694</v>
+        <v>80.616</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1938,13 +1650,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46136.22916666666</v>
+        <v>46140.22916666666</v>
       </c>
       <c r="B24">
-        <v>56.723</v>
+        <v>110.354</v>
       </c>
       <c r="C24">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1955,13 +1667,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46136.23958333334</v>
+        <v>46140.23958333334</v>
       </c>
       <c r="B25">
-        <v>94.11</v>
+        <v>147.313</v>
       </c>
       <c r="C25">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1972,13 +1684,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46136.25</v>
+        <v>46140.25</v>
       </c>
       <c r="B26">
-        <v>278.339</v>
+        <v>315.602</v>
       </c>
       <c r="C26">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1989,13 +1701,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46136.26041666666</v>
+        <v>46140.26041666666</v>
       </c>
       <c r="B27">
-        <v>383.425</v>
+        <v>419.067</v>
       </c>
       <c r="C27">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -2006,13 +1718,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46136.27083333334</v>
+        <v>46140.27083333334</v>
       </c>
       <c r="B28">
-        <v>518.035</v>
+        <v>548.071</v>
       </c>
       <c r="C28">
-        <v>372</v>
+        <v>418</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -2023,13 +1735,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46136.28125</v>
+        <v>46140.28125</v>
       </c>
       <c r="B29">
-        <v>690.628</v>
+        <v>703.403</v>
       </c>
       <c r="C29">
-        <v>532</v>
+        <v>564</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -2040,13 +1752,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46136.29166666666</v>
+        <v>46140.29166666666</v>
       </c>
       <c r="B30">
-        <v>960.205</v>
+        <v>1020.552</v>
       </c>
       <c r="C30">
-        <v>737</v>
+        <v>786</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -2057,13 +1769,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46136.30208333334</v>
+        <v>46140.30208333334</v>
       </c>
       <c r="B31">
-        <v>1155.521</v>
+        <v>1203.034</v>
       </c>
       <c r="C31">
-        <v>937</v>
+        <v>956</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -2074,13 +1786,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46136.3125</v>
+        <v>46140.3125</v>
       </c>
       <c r="B32">
-        <v>1363.506</v>
+        <v>1409.283</v>
       </c>
       <c r="C32">
-        <v>1126</v>
+        <v>1136</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -2091,13 +1803,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46136.32291666666</v>
+        <v>46140.32291666666</v>
       </c>
       <c r="B33">
-        <v>1591.723</v>
+        <v>1630.29</v>
       </c>
       <c r="C33">
-        <v>1307</v>
+        <v>1339</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -2108,13 +1820,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46136.33333333334</v>
+        <v>46140.33333333334</v>
       </c>
       <c r="B34">
-        <v>1876.48</v>
+        <v>1949.604</v>
       </c>
       <c r="C34">
-        <v>1514</v>
+        <v>1471</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -2125,13 +1837,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46136.34375</v>
+        <v>46140.34375</v>
       </c>
       <c r="B35">
-        <v>2048.707</v>
+        <v>2141.299</v>
       </c>
       <c r="C35">
-        <v>1664</v>
+        <v>1644</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -2142,13 +1854,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46136.35416666666</v>
+        <v>46140.35416666666</v>
       </c>
       <c r="B36">
-        <v>2235.378</v>
+        <v>2324.015</v>
       </c>
       <c r="C36">
-        <v>1736</v>
+        <v>1746</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -2159,13 +1871,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46136.36458333334</v>
+        <v>46140.36458333334</v>
       </c>
       <c r="B37">
-        <v>2420.08</v>
+        <v>2500.263</v>
       </c>
       <c r="C37">
-        <v>1838</v>
+        <v>1851</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -2176,13 +1888,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46136.375</v>
+        <v>46140.375</v>
       </c>
       <c r="B38">
-        <v>2638.573</v>
+        <v>2713.739</v>
       </c>
       <c r="C38">
-        <v>1960</v>
+        <v>1950</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -2193,13 +1905,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46136.38541666666</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="B39">
-        <v>2756.284</v>
+        <v>2829.575</v>
       </c>
       <c r="C39">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -2210,13 +1922,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46136.39583333334</v>
+        <v>46140.39583333334</v>
       </c>
       <c r="B40">
-        <v>2820.767</v>
+        <v>2927.652</v>
       </c>
       <c r="C40">
-        <v>2115</v>
+        <v>2140</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -2227,13 +1939,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46136.40625</v>
+        <v>46140.40625</v>
       </c>
       <c r="B41">
-        <v>2897.648</v>
+        <v>3023.953</v>
       </c>
       <c r="C41">
-        <v>2165</v>
+        <v>2218</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -2244,13 +1956,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46136.41666666666</v>
+        <v>46140.41666666666</v>
       </c>
       <c r="B42">
-        <v>2987.317</v>
+        <v>3119.685</v>
       </c>
       <c r="C42">
-        <v>2222</v>
+        <v>2286</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -2261,13 +1973,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46136.42708333334</v>
+        <v>46140.42708333334</v>
       </c>
       <c r="B43">
-        <v>3035.402</v>
+        <v>3192.844</v>
       </c>
       <c r="C43">
-        <v>2213</v>
+        <v>2329</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -2278,13 +1990,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46136.4375</v>
+        <v>46140.4375</v>
       </c>
       <c r="B44">
-        <v>3054.293</v>
+        <v>3231.801</v>
       </c>
       <c r="C44">
-        <v>2243</v>
+        <v>2308</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -2295,13 +2007,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46136.44791666666</v>
+        <v>46140.44791666666</v>
       </c>
       <c r="B45">
-        <v>2811.29</v>
+        <v>3105.175</v>
       </c>
       <c r="C45">
-        <v>2072</v>
+        <v>2261</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -2312,13 +2024,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46136.45833333334</v>
+        <v>46140.45833333334</v>
       </c>
       <c r="B46">
-        <v>2875.33</v>
+        <v>3066.433</v>
       </c>
       <c r="C46">
-        <v>2055</v>
+        <v>2178</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2329,13 +2041,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46136.46875</v>
+        <v>46140.46875</v>
       </c>
       <c r="B47">
-        <v>2224.113</v>
+        <v>3085.051</v>
       </c>
       <c r="C47">
-        <v>1535</v>
+        <v>2133</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2346,13 +2058,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46136.47916666666</v>
+        <v>46140.47916666666</v>
       </c>
       <c r="B48">
-        <v>2205.991</v>
+        <v>3100.987</v>
       </c>
       <c r="C48">
-        <v>1446</v>
+        <v>2139</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2363,13 +2075,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46136.48958333334</v>
+        <v>46140.48958333334</v>
       </c>
       <c r="B49">
-        <v>2199.954</v>
+        <v>3098.989</v>
       </c>
       <c r="C49">
-        <v>1463</v>
+        <v>2159</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2380,13 +2092,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46136.5</v>
+        <v>46140.5</v>
       </c>
       <c r="B50">
-        <v>2072.116</v>
+        <v>3082.926</v>
       </c>
       <c r="C50">
-        <v>1419</v>
+        <v>2211</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2397,13 +2109,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46136.51041666666</v>
+        <v>46140.51041666666</v>
       </c>
       <c r="B51">
-        <v>1988.862</v>
+        <v>3071.039</v>
       </c>
       <c r="C51">
-        <v>1402</v>
+        <v>2188</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2414,13 +2126,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46136.52083333334</v>
+        <v>46140.52083333334</v>
       </c>
       <c r="B52">
-        <v>1958.887</v>
+        <v>3048.628</v>
       </c>
       <c r="C52">
-        <v>1401</v>
+        <v>2127</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2431,13 +2143,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46136.53125</v>
+        <v>46140.53125</v>
       </c>
       <c r="B53">
-        <v>1886.634</v>
+        <v>3024.525</v>
       </c>
       <c r="C53">
-        <v>1312</v>
+        <v>2101</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2448,13 +2160,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46136.54166666666</v>
+        <v>46140.54166666666</v>
       </c>
       <c r="B54">
-        <v>1853.956</v>
+        <v>2917.154</v>
       </c>
       <c r="C54">
-        <v>1261</v>
+        <v>2097</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2465,13 +2177,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46136.55208333334</v>
+        <v>46140.55208333334</v>
       </c>
       <c r="B55">
-        <v>1823.589</v>
+        <v>2853.964</v>
       </c>
       <c r="C55">
-        <v>1249</v>
+        <v>2009</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2482,13 +2194,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46136.5625</v>
+        <v>46140.5625</v>
       </c>
       <c r="B56">
-        <v>1785.42</v>
+        <v>2713.949</v>
       </c>
       <c r="C56">
-        <v>1241</v>
+        <v>1972</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2499,13 +2211,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46136.57291666666</v>
+        <v>46140.57291666666</v>
       </c>
       <c r="B57">
-        <v>1757.522</v>
+        <v>2705.297</v>
       </c>
       <c r="C57">
-        <v>1245</v>
+        <v>1875</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2516,13 +2228,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46136.58333333334</v>
+        <v>46140.58333333334</v>
       </c>
       <c r="B58">
-        <v>1692.607</v>
+        <v>2686.374</v>
       </c>
       <c r="C58">
-        <v>1121</v>
+        <v>1938</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2533,13 +2245,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46136.59375</v>
+        <v>46140.59375</v>
       </c>
       <c r="B59">
-        <v>1639.658</v>
+        <v>2608.302</v>
       </c>
       <c r="C59">
-        <v>1088</v>
+        <v>1899</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2550,13 +2262,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46136.60416666666</v>
+        <v>46140.60416666666</v>
       </c>
       <c r="B60">
-        <v>1595.69</v>
+        <v>2518.48</v>
       </c>
       <c r="C60">
-        <v>1070</v>
+        <v>1877</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2567,13 +2279,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46136.61458333334</v>
+        <v>46140.61458333334</v>
       </c>
       <c r="B61">
-        <v>1522.133</v>
+        <v>2427.629</v>
       </c>
       <c r="C61">
-        <v>1067</v>
+        <v>1803</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2584,13 +2296,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46136.625</v>
+        <v>46140.625</v>
       </c>
       <c r="B62">
-        <v>1419.683</v>
+        <v>2299.592</v>
       </c>
       <c r="C62">
-        <v>990</v>
+        <v>1787</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2601,13 +2313,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46136.63541666666</v>
+        <v>46140.63541666666</v>
       </c>
       <c r="B63">
-        <v>1332.477</v>
+        <v>2185.593</v>
       </c>
       <c r="C63">
-        <v>937</v>
+        <v>1730</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2618,13 +2330,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46136.64583333334</v>
+        <v>46140.64583333334</v>
       </c>
       <c r="B64">
-        <v>1271.364</v>
+        <v>2088.134</v>
       </c>
       <c r="C64">
-        <v>879</v>
+        <v>1606</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2635,13 +2347,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46136.65625</v>
+        <v>46140.65625</v>
       </c>
       <c r="B65">
-        <v>1222.827</v>
+        <v>1969.843</v>
       </c>
       <c r="C65">
-        <v>865</v>
+        <v>1589</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2652,13 +2364,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46136.66666666666</v>
+        <v>46140.66666666666</v>
       </c>
       <c r="B66">
-        <v>1128.664</v>
+        <v>1789.688</v>
       </c>
       <c r="C66">
-        <v>827</v>
+        <v>1411</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2669,13 +2381,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46136.67708333334</v>
+        <v>46140.67708333334</v>
       </c>
       <c r="B67">
-        <v>1058.196</v>
+        <v>1634.848</v>
       </c>
       <c r="C67">
-        <v>783</v>
+        <v>1258</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2686,13 +2398,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46136.6875</v>
+        <v>46140.6875</v>
       </c>
       <c r="B68">
-        <v>1259.631</v>
+        <v>1600.075</v>
       </c>
       <c r="C68">
-        <v>980</v>
+        <v>1238</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2703,13 +2415,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46136.69791666666</v>
+        <v>46140.69791666666</v>
       </c>
       <c r="B69">
-        <v>1132.627</v>
+        <v>1416.817</v>
       </c>
       <c r="C69">
-        <v>882</v>
+        <v>1164</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2720,13 +2432,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46136.70833333334</v>
+        <v>46140.70833333334</v>
       </c>
       <c r="B70">
-        <v>911.146</v>
+        <v>1144.559</v>
       </c>
       <c r="C70">
-        <v>800</v>
+        <v>964</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2737,13 +2449,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46136.71875</v>
+        <v>46140.71875</v>
       </c>
       <c r="B71">
-        <v>850.621</v>
+        <v>974.2569999999999</v>
       </c>
       <c r="C71">
-        <v>715</v>
+        <v>807</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2754,13 +2466,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46136.72916666666</v>
+        <v>46140.72916666666</v>
       </c>
       <c r="B72">
-        <v>704.78</v>
+        <v>823.393</v>
       </c>
       <c r="C72">
-        <v>610</v>
+        <v>632</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2771,13 +2483,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46136.73958333334</v>
+        <v>46140.73958333334</v>
       </c>
       <c r="B73">
-        <v>566.678</v>
+        <v>678.311</v>
       </c>
       <c r="C73">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2788,13 +2500,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46136.75</v>
+        <v>46140.75</v>
       </c>
       <c r="B74">
-        <v>429.497</v>
+        <v>495.367</v>
       </c>
       <c r="C74">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2805,13 +2517,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46136.76041666666</v>
+        <v>46140.76041666666</v>
       </c>
       <c r="B75">
-        <v>322.668</v>
+        <v>381.48</v>
       </c>
       <c r="C75">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2822,13 +2534,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46136.77083333334</v>
+        <v>46140.77083333334</v>
       </c>
       <c r="B76">
-        <v>239.634</v>
+        <v>201.744</v>
       </c>
       <c r="C76">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2839,13 +2551,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46136.78125</v>
+        <v>46140.78125</v>
       </c>
       <c r="B77">
-        <v>179.256</v>
+        <v>139.57</v>
       </c>
       <c r="C77">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2856,13 +2568,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46136.79166666666</v>
+        <v>46140.79166666666</v>
       </c>
       <c r="B78">
-        <v>44.502</v>
+        <v>65.65600000000001</v>
       </c>
       <c r="C78">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2873,13 +2585,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46136.80208333334</v>
+        <v>46140.80208333334</v>
       </c>
       <c r="B79">
-        <v>24.568</v>
+        <v>41.446</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2890,10 +2602,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46136.8125</v>
+        <v>46140.8125</v>
       </c>
       <c r="B80">
-        <v>19.597</v>
+        <v>34.688</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2907,10 +2619,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46136.82291666666</v>
+        <v>46140.82291666666</v>
       </c>
       <c r="B81">
-        <v>10.257</v>
+        <v>26.504</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2924,10 +2636,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46136.83333333334</v>
+        <v>46140.83333333334</v>
       </c>
       <c r="B82">
-        <v>11.004</v>
+        <v>15.737</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2941,10 +2653,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46136.84375</v>
+        <v>46140.84375</v>
       </c>
       <c r="B83">
-        <v>10.511</v>
+        <v>14.033</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2958,10 +2670,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46136.85416666666</v>
+        <v>46140.85416666666</v>
       </c>
       <c r="B84">
-        <v>7.431</v>
+        <v>11.737</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2975,10 +2687,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46136.86458333334</v>
+        <v>46140.86458333334</v>
       </c>
       <c r="B85">
-        <v>6.535</v>
+        <v>10.128</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2992,10 +2704,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46136.875</v>
+        <v>46140.875</v>
       </c>
       <c r="B86">
-        <v>2.83</v>
+        <v>4.599</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3009,10 +2721,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46136.88541666666</v>
+        <v>46140.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3026,10 +2738,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46136.89583333334</v>
+        <v>46140.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.53</v>
+        <v>2.13</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3043,10 +2755,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46136.90625</v>
+        <v>46140.90625</v>
       </c>
       <c r="B89">
-        <v>2.53</v>
+        <v>0.83</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -3060,10 +2772,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46136.91666666666</v>
+        <v>46140.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.83</v>
+        <v>1.53</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3077,10 +2789,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46136.92708333334</v>
+        <v>46140.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.53</v>
+        <v>0.83</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3094,10 +2806,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46136.9375</v>
+        <v>46140.9375</v>
       </c>
       <c r="B92">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -3111,7 +2823,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46136.94791666666</v>
+        <v>46140.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -3128,10 +2840,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46136.95833333334</v>
+        <v>46140.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -3145,7 +2857,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46136.96875</v>
+        <v>46140.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -3162,7 +2874,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46136.97916666666</v>
+        <v>46140.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -3179,7 +2891,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46136.98958333334</v>
+        <v>46140.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -3196,7 +2908,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -3213,7 +2925,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46137.01041666666</v>
+        <v>46141.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -3230,13 +2942,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46137.02083333334</v>
+        <v>46141.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -3247,7 +2959,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46137.03125</v>
+        <v>46141.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3264,13 +2976,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46137.04166666666</v>
+        <v>46141.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -3281,7 +2993,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46137.05208333334</v>
+        <v>46141.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3298,7 +3010,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46137.0625</v>
+        <v>46141.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3315,7 +3027,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46137.07291666666</v>
+        <v>46141.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3332,13 +3044,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46137.08333333334</v>
+        <v>46141.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -3349,7 +3061,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46137.09375</v>
+        <v>46141.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3366,7 +3078,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46137.10416666666</v>
+        <v>46141.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3383,13 +3095,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46137.11458333334</v>
+        <v>46141.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -3400,13 +3112,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46137.125</v>
+        <v>46141.125</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -3417,7 +3129,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46137.13541666666</v>
+        <v>46141.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3434,13 +3146,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46137.14583333334</v>
+        <v>46141.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -3451,13 +3163,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46137.15625</v>
+        <v>46141.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -3468,13 +3180,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46137.16666666666</v>
+        <v>46141.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -3485,13 +3197,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46137.17708333334</v>
+        <v>46141.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -3502,13 +3214,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46137.1875</v>
+        <v>46141.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -3519,13 +3231,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46137.19791666666</v>
+        <v>46141.19791666666</v>
       </c>
       <c r="B117">
-        <v>0.834</v>
+        <v>0.756</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3536,10 +3248,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46137.20833333334</v>
+        <v>46141.20833333334</v>
       </c>
       <c r="B118">
-        <v>3.011</v>
+        <v>11.045</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -3553,13 +3265,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46137.21875</v>
+        <v>46141.21875</v>
       </c>
       <c r="B119">
-        <v>7.148</v>
+        <v>15.682</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3570,13 +3282,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46137.22916666666</v>
+        <v>46141.22916666666</v>
       </c>
       <c r="B120">
-        <v>26.298</v>
+        <v>32.722</v>
       </c>
       <c r="C120">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3587,13 +3299,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46137.23958333334</v>
+        <v>46141.23958333334</v>
       </c>
       <c r="B121">
-        <v>65.54300000000001</v>
+        <v>61.025</v>
       </c>
       <c r="C121">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3604,13 +3316,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46137.25</v>
+        <v>46141.25</v>
       </c>
       <c r="B122">
-        <v>178.861</v>
+        <v>130.402</v>
       </c>
       <c r="C122">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3621,13 +3333,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46137.26041666666</v>
+        <v>46141.26041666666</v>
       </c>
       <c r="B123">
-        <v>269.699</v>
+        <v>193.994</v>
       </c>
       <c r="C123">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3638,13 +3350,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46137.27083333334</v>
+        <v>46141.27083333334</v>
       </c>
       <c r="B124">
-        <v>390.655</v>
+        <v>267.392</v>
       </c>
       <c r="C124">
-        <v>284</v>
+        <v>345</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3655,13 +3367,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46137.28125</v>
+        <v>46141.28125</v>
       </c>
       <c r="B125">
-        <v>533.663</v>
+        <v>353.411</v>
       </c>
       <c r="C125">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3672,13 +3384,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46137.29166666666</v>
+        <v>46141.29166666666</v>
       </c>
       <c r="B126">
-        <v>803.0359999999999</v>
+        <v>524.915</v>
       </c>
       <c r="C126">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3689,13 +3401,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46137.30208333334</v>
+        <v>46141.30208333334</v>
       </c>
       <c r="B127">
-        <v>962.372</v>
+        <v>632.053</v>
       </c>
       <c r="C127">
-        <v>651</v>
+        <v>603</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3706,13 +3418,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46137.3125</v>
+        <v>46141.3125</v>
       </c>
       <c r="B128">
-        <v>1148.865</v>
+        <v>743.644</v>
       </c>
       <c r="C128">
-        <v>750</v>
+        <v>715</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3723,13 +3435,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46137.32291666666</v>
+        <v>46141.32291666666</v>
       </c>
       <c r="B129">
-        <v>1338.995</v>
+        <v>848.614</v>
       </c>
       <c r="C129">
-        <v>878</v>
+        <v>821</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3740,13 +3452,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46137.33333333334</v>
+        <v>46141.33333333334</v>
       </c>
       <c r="B130">
-        <v>1612.074</v>
+        <v>1068.76</v>
       </c>
       <c r="C130">
-        <v>1039</v>
+        <v>866</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3757,13 +3469,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46137.34375</v>
+        <v>46141.34375</v>
       </c>
       <c r="B131">
-        <v>1792.904</v>
+        <v>1164.273</v>
       </c>
       <c r="C131">
-        <v>1196</v>
+        <v>923</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3774,13 +3486,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46137.35416666666</v>
+        <v>46141.35416666666</v>
       </c>
       <c r="B132">
-        <v>1979.459</v>
+        <v>1269.225</v>
       </c>
       <c r="C132">
-        <v>1270</v>
+        <v>1038</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3791,13 +3503,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46137.36458333334</v>
+        <v>46141.36458333334</v>
       </c>
       <c r="B133">
-        <v>2116.849</v>
+        <v>1367.32</v>
       </c>
       <c r="C133">
-        <v>1351</v>
+        <v>1149</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3808,13 +3520,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46137.375</v>
+        <v>46141.375</v>
       </c>
       <c r="B134">
-        <v>2368.475</v>
+        <v>1442.394</v>
       </c>
       <c r="C134">
-        <v>1469</v>
+        <v>1317</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3825,13 +3537,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46137.38541666666</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="B135">
-        <v>2464.221</v>
+        <v>1497.739</v>
       </c>
       <c r="C135">
-        <v>1567</v>
+        <v>1447</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3842,13 +3554,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46137.39583333334</v>
+        <v>46141.39583333334</v>
       </c>
       <c r="B136">
-        <v>2388.721</v>
+        <v>1557.444</v>
       </c>
       <c r="C136">
-        <v>1429</v>
+        <v>1422</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3859,13 +3571,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46137.40625</v>
+        <v>46141.40625</v>
       </c>
       <c r="B137">
-        <v>1926.158</v>
+        <v>1619.98</v>
       </c>
       <c r="C137">
-        <v>1124</v>
+        <v>1488</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3876,13 +3588,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46137.41666666666</v>
+        <v>46141.41666666666</v>
       </c>
       <c r="B138">
-        <v>2004.03</v>
+        <v>1654.938</v>
       </c>
       <c r="C138">
-        <v>1087</v>
+        <v>1459</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3893,13 +3605,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46137.42708333334</v>
+        <v>46141.42708333334</v>
       </c>
       <c r="B139">
-        <v>1954.679</v>
+        <v>1704.475</v>
       </c>
       <c r="C139">
-        <v>1086</v>
+        <v>1550</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3910,13 +3622,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46137.4375</v>
+        <v>46141.4375</v>
       </c>
       <c r="B140">
-        <v>1922.484</v>
+        <v>1748.388</v>
       </c>
       <c r="C140">
-        <v>1101</v>
+        <v>1498</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3927,13 +3639,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46137.44791666666</v>
+        <v>46141.44791666666</v>
       </c>
       <c r="B141">
-        <v>1930.686</v>
+        <v>1771.856</v>
       </c>
       <c r="C141">
-        <v>1135</v>
+        <v>1552</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3944,13 +3656,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46137.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="B142">
-        <v>1957.9</v>
+        <v>1789.33</v>
       </c>
       <c r="C142">
-        <v>1140</v>
+        <v>1645</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3961,13 +3673,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46137.46875</v>
+        <v>46141.46875</v>
       </c>
       <c r="B143">
-        <v>1875.363</v>
+        <v>1807.038</v>
       </c>
       <c r="C143">
-        <v>1135</v>
+        <v>1693</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3978,13 +3690,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46137.47916666666</v>
+        <v>46141.47916666666</v>
       </c>
       <c r="B144">
-        <v>1823.578</v>
+        <v>1815.013</v>
       </c>
       <c r="C144">
-        <v>1120</v>
+        <v>1720</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3995,13 +3707,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46137.48958333334</v>
+        <v>46141.48958333334</v>
       </c>
       <c r="B145">
-        <v>1815.525</v>
+        <v>1810.938</v>
       </c>
       <c r="C145">
-        <v>1015</v>
+        <v>1744</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -4012,13 +3724,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46137.5</v>
+        <v>46141.5</v>
       </c>
       <c r="B146">
-        <v>1786.97</v>
+        <v>1814.622</v>
       </c>
       <c r="C146">
-        <v>1084</v>
+        <v>1675</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -4029,13 +3741,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46137.51041666666</v>
+        <v>46141.51041666666</v>
       </c>
       <c r="B147">
-        <v>1775.824</v>
+        <v>1802.46</v>
       </c>
       <c r="C147">
-        <v>1058</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -4046,13 +3758,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46137.52083333334</v>
+        <v>46141.52083333334</v>
       </c>
       <c r="B148">
-        <v>1760.072</v>
+        <v>1782.527</v>
       </c>
       <c r="C148">
-        <v>1041</v>
+        <v>1689</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -4063,13 +3775,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46137.53125</v>
+        <v>46141.53125</v>
       </c>
       <c r="B149">
-        <v>1729.993</v>
+        <v>1762.23</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1577</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -4080,13 +3792,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46137.54166666666</v>
+        <v>46141.54166666666</v>
       </c>
       <c r="B150">
-        <v>1686.1</v>
+        <v>1699.862</v>
       </c>
       <c r="C150">
-        <v>1017</v>
+        <v>1556</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -4097,13 +3809,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46137.55208333334</v>
+        <v>46141.55208333334</v>
       </c>
       <c r="B151">
-        <v>1651.819</v>
+        <v>1655.654</v>
       </c>
       <c r="C151">
-        <v>927</v>
+        <v>1560</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -4114,13 +3826,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46137.5625</v>
+        <v>46141.5625</v>
       </c>
       <c r="B152">
-        <v>1612.9</v>
+        <v>1604.698</v>
       </c>
       <c r="C152">
-        <v>897</v>
+        <v>1529</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -4131,13 +3843,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46137.57291666666</v>
+        <v>46141.57291666666</v>
       </c>
       <c r="B153">
-        <v>1571.354</v>
+        <v>1565.791</v>
       </c>
       <c r="C153">
-        <v>902</v>
+        <v>1416</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -4148,13 +3860,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46137.58333333334</v>
+        <v>46141.58333333334</v>
       </c>
       <c r="B154">
-        <v>1498.557</v>
+        <v>1500.185</v>
       </c>
       <c r="C154">
-        <v>871</v>
+        <v>1424</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -4165,13 +3877,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46137.59375</v>
+        <v>46141.59375</v>
       </c>
       <c r="B155">
-        <v>1453.068</v>
+        <v>1446.701</v>
       </c>
       <c r="C155">
-        <v>847</v>
+        <v>1410</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -4182,13 +3894,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46137.60416666666</v>
+        <v>46141.60416666666</v>
       </c>
       <c r="B156">
-        <v>1405.482</v>
+        <v>1400.633</v>
       </c>
       <c r="C156">
-        <v>819</v>
+        <v>1363</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -4199,13 +3911,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46137.61458333334</v>
+        <v>46141.61458333334</v>
       </c>
       <c r="B157">
-        <v>1355.021</v>
+        <v>1345.089</v>
       </c>
       <c r="C157">
-        <v>831</v>
+        <v>1294</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -4216,13 +3928,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46137.625</v>
+        <v>46141.625</v>
       </c>
       <c r="B158">
-        <v>1225.11</v>
+        <v>1256.175</v>
       </c>
       <c r="C158">
-        <v>850</v>
+        <v>1238</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -4233,13 +3945,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46137.63541666666</v>
+        <v>46141.63541666666</v>
       </c>
       <c r="B159">
-        <v>1170.727</v>
+        <v>1188.51</v>
       </c>
       <c r="C159">
-        <v>825</v>
+        <v>1122</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -4250,13 +3962,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46137.64583333334</v>
+        <v>46141.64583333334</v>
       </c>
       <c r="B160">
-        <v>1110.645</v>
+        <v>1116.756</v>
       </c>
       <c r="C160">
-        <v>823</v>
+        <v>1036</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -4267,13 +3979,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46137.65625</v>
+        <v>46141.65625</v>
       </c>
       <c r="B161">
-        <v>1042.737</v>
+        <v>1052.12</v>
       </c>
       <c r="C161">
-        <v>789</v>
+        <v>971</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -4284,13 +3996,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46137.66666666666</v>
+        <v>46141.66666666666</v>
       </c>
       <c r="B162">
-        <v>904.4059999999999</v>
+        <v>968.23</v>
       </c>
       <c r="C162">
-        <v>757</v>
+        <v>907</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -4301,13 +4013,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46137.67708333334</v>
+        <v>46141.67708333334</v>
       </c>
       <c r="B163">
-        <v>842.765</v>
+        <v>867.434</v>
       </c>
       <c r="C163">
-        <v>724</v>
+        <v>809</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -4318,13 +4030,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46137.6875</v>
+        <v>46141.6875</v>
       </c>
       <c r="B164">
-        <v>824.728</v>
+        <v>781.586</v>
       </c>
       <c r="C164">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -4335,13 +4047,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46137.69791666666</v>
+        <v>46141.69791666666</v>
       </c>
       <c r="B165">
-        <v>786.439</v>
+        <v>700.439</v>
       </c>
       <c r="C165">
-        <v>658</v>
+        <v>692</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -4352,13 +4064,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46137.70833333334</v>
+        <v>46141.70833333334</v>
       </c>
       <c r="B166">
-        <v>580.946</v>
+        <v>550.974</v>
       </c>
       <c r="C166">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -4369,13 +4081,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46137.71875</v>
+        <v>46141.71875</v>
       </c>
       <c r="B167">
-        <v>712.024</v>
+        <v>470.199</v>
       </c>
       <c r="C167">
-        <v>574</v>
+        <v>493</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -4386,13 +4098,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46137.72916666666</v>
+        <v>46141.72916666666</v>
       </c>
       <c r="B168">
-        <v>633.103</v>
+        <v>394.149</v>
       </c>
       <c r="C168">
-        <v>514</v>
+        <v>400</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -4403,13 +4115,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46137.73958333334</v>
+        <v>46141.73958333334</v>
       </c>
       <c r="B169">
-        <v>511.202</v>
+        <v>318.213</v>
       </c>
       <c r="C169">
-        <v>420</v>
+        <v>313</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -4420,13 +4132,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46137.75</v>
+        <v>46141.75</v>
       </c>
       <c r="B170">
-        <v>332.602</v>
+        <v>205.633</v>
       </c>
       <c r="C170">
-        <v>303</v>
+        <v>244</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -4437,13 +4149,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46137.76041666666</v>
+        <v>46141.76041666666</v>
       </c>
       <c r="B171">
-        <v>238.106</v>
+        <v>156.412</v>
       </c>
       <c r="C171">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -4454,13 +4166,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46137.77083333334</v>
+        <v>46141.77083333334</v>
       </c>
       <c r="B172">
-        <v>160.298</v>
+        <v>108.522</v>
       </c>
       <c r="C172">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4471,13 +4183,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46137.78125</v>
+        <v>46141.78125</v>
       </c>
       <c r="B173">
-        <v>98.447</v>
+        <v>81.214</v>
       </c>
       <c r="C173">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4488,13 +4200,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46137.79166666666</v>
+        <v>46141.79166666666</v>
       </c>
       <c r="B174">
-        <v>42.501</v>
+        <v>38.395</v>
       </c>
       <c r="C174">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -4505,13 +4217,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46137.80208333334</v>
+        <v>46141.80208333334</v>
       </c>
       <c r="B175">
-        <v>24.909</v>
+        <v>32.6</v>
       </c>
       <c r="C175">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -4522,10 +4234,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46137.8125</v>
+        <v>46141.8125</v>
       </c>
       <c r="B176">
-        <v>18.566</v>
+        <v>24.63</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -4539,10 +4251,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46137.82291666666</v>
+        <v>46141.82291666666</v>
       </c>
       <c r="B177">
-        <v>10.76</v>
+        <v>20.472</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -4556,10 +4268,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46137.83333333334</v>
+        <v>46141.83333333334</v>
       </c>
       <c r="B178">
-        <v>11.827</v>
+        <v>15.203</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -4573,10 +4285,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46137.84375</v>
+        <v>46141.84375</v>
       </c>
       <c r="B179">
-        <v>10.643</v>
+        <v>0</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4590,10 +4302,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46137.85416666666</v>
+        <v>46141.85416666666</v>
       </c>
       <c r="B180">
-        <v>9.766</v>
+        <v>14.861</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4607,10 +4319,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46137.86458333334</v>
+        <v>46141.86458333334</v>
       </c>
       <c r="B181">
-        <v>9.968999999999999</v>
+        <v>11.733</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4624,10 +4336,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46137.875</v>
+        <v>46141.875</v>
       </c>
       <c r="B182">
-        <v>4.43</v>
+        <v>13.33</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4641,10 +4353,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46137.88541666666</v>
+        <v>46141.88541666666</v>
       </c>
       <c r="B183">
-        <v>4.13</v>
+        <v>10.73</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4658,10 +4370,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46137.89583333334</v>
+        <v>46141.89583333334</v>
       </c>
       <c r="B184">
-        <v>1.43</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4675,10 +4387,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46137.90625</v>
+        <v>46141.90625</v>
       </c>
       <c r="B185">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4692,7 +4404,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46137.91666666666</v>
+        <v>46141.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4709,7 +4421,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46137.92708333334</v>
+        <v>46141.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4726,7 +4438,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46137.9375</v>
+        <v>46141.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4743,7 +4455,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46137.94791666666</v>
+        <v>46141.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4760,7 +4472,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46137.95833333334</v>
+        <v>46141.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4777,7 +4489,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46137.96875</v>
+        <v>46141.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4506,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46137.97916666666</v>
+        <v>46141.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4811,7 +4523,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46137.98958333334</v>
+        <v>46141.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4828,7 +4540,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4845,7 +4557,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46138.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -4862,7 +4574,7 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46138.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -4879,7 +4591,7 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46138.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -4896,7 +4608,7 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46138.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -4913,7 +4625,7 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46138.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -4930,7 +4642,7 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46138.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -4947,7 +4659,7 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46138.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B201">
         <v>0</v>
@@ -4964,7 +4676,7 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46138.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B202">
         <v>0</v>
@@ -4981,7 +4693,7 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46138.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B203">
         <v>0</v>
@@ -4998,7 +4710,7 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46138.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B204">
         <v>0</v>
@@ -5015,7 +4727,7 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46138.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B205">
         <v>0</v>
@@ -5032,10 +4744,10 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46138.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B206">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -5049,7 +4761,7 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46138.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B207">
         <v>0</v>
@@ -5066,7 +4778,7 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46138.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B208">
         <v>0</v>
@@ -5083,7 +4795,7 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46138.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B209">
         <v>0</v>
@@ -5100,10 +4812,10 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46138.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B210">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -5117,7 +4829,7 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46138.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B211">
         <v>0</v>
@@ -5134,10 +4846,10 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46138.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B212">
-        <v>0</v>
+        <v>0.747</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -5151,10 +4863,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46138.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B213">
-        <v>0.834</v>
+        <v>0.779</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -5168,10 +4880,10 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46138.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B214">
-        <v>3.607</v>
+        <v>1.371</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -5185,10 +4897,10 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46138.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B215">
-        <v>9.614000000000001</v>
+        <v>4.827</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -5202,13 +4914,13 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46138.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B216">
-        <v>38.794</v>
+        <v>14.981</v>
       </c>
       <c r="C216">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -5219,13 +4931,13 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46138.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B217">
-        <v>79.307</v>
+        <v>31.343</v>
       </c>
       <c r="C217">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D217">
         <v>24</v>
@@ -5236,13 +4948,13 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46138.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B218">
-        <v>256.217</v>
+        <v>110.775</v>
       </c>
       <c r="C218">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="D218">
         <v>25</v>
@@ -5253,13 +4965,13 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46138.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B219">
-        <v>355.357</v>
+        <v>156.833</v>
       </c>
       <c r="C219">
-        <v>194</v>
+        <v>67</v>
       </c>
       <c r="D219">
         <v>26</v>
@@ -5270,13 +4982,13 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46138.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B220">
-        <v>483.693</v>
+        <v>202.328</v>
       </c>
       <c r="C220">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="D220">
         <v>27</v>
@@ -5287,13 +4999,13 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46138.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B221">
-        <v>632.851</v>
+        <v>260.181</v>
       </c>
       <c r="C221">
-        <v>448</v>
+        <v>136</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -5304,13 +5016,13 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46138.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B222">
-        <v>902.101</v>
+        <v>351.994</v>
       </c>
       <c r="C222">
-        <v>575</v>
+        <v>178</v>
       </c>
       <c r="D222">
         <v>29</v>
@@ -5321,13 +5033,13 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46138.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B223">
-        <v>1081.861</v>
+        <v>420.295</v>
       </c>
       <c r="C223">
-        <v>691</v>
+        <v>234</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -5338,13 +5050,13 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46138.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B224">
-        <v>1280.656</v>
+        <v>499.001</v>
       </c>
       <c r="C224">
-        <v>808</v>
+        <v>303</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -5355,13 +5067,13 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46138.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B225">
-        <v>1406.769</v>
+        <v>571.061</v>
       </c>
       <c r="C225">
-        <v>893</v>
+        <v>369</v>
       </c>
       <c r="D225">
         <v>32</v>
@@ -5372,13 +5084,13 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46138.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B226">
-        <v>1664.818</v>
+        <v>669.073</v>
       </c>
       <c r="C226">
-        <v>1005</v>
+        <v>430</v>
       </c>
       <c r="D226">
         <v>33</v>
@@ -5389,13 +5101,13 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46138.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B227">
-        <v>1803.542</v>
+        <v>728.499</v>
       </c>
       <c r="C227">
-        <v>1109</v>
+        <v>515</v>
       </c>
       <c r="D227">
         <v>34</v>
@@ -5406,13 +5118,13 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46138.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B228">
-        <v>1783.188</v>
+        <v>812.227</v>
       </c>
       <c r="C228">
-        <v>1100</v>
+        <v>568</v>
       </c>
       <c r="D228">
         <v>35</v>
@@ -5423,13 +5135,13 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46138.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B229">
-        <v>1541.454</v>
+        <v>890.375</v>
       </c>
       <c r="C229">
-        <v>967</v>
+        <v>641</v>
       </c>
       <c r="D229">
         <v>36</v>
@@ -5440,13 +5152,13 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46138.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B230">
-        <v>1739.004</v>
+        <v>991.02</v>
       </c>
       <c r="C230">
-        <v>1038</v>
+        <v>732</v>
       </c>
       <c r="D230">
         <v>37</v>
@@ -5457,13 +5169,13 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46138.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B231">
-        <v>1787.955</v>
+        <v>1060.596</v>
       </c>
       <c r="C231">
-        <v>1088</v>
+        <v>801</v>
       </c>
       <c r="D231">
         <v>38</v>
@@ -5474,13 +5186,13 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46138.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B232">
-        <v>1767.207</v>
+        <v>1126.624</v>
       </c>
       <c r="C232">
-        <v>970</v>
+        <v>818</v>
       </c>
       <c r="D232">
         <v>39</v>
@@ -5491,13 +5203,13 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46138.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B233">
-        <v>1821.541</v>
+        <v>1139.684</v>
       </c>
       <c r="C233">
-        <v>944</v>
+        <v>789</v>
       </c>
       <c r="D233">
         <v>40</v>
@@ -5508,13 +5220,13 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46138.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B234">
-        <v>1896.042</v>
+        <v>1265.215</v>
       </c>
       <c r="C234">
-        <v>997</v>
+        <v>858</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5525,13 +5237,13 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46138.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B235">
-        <v>1908.499</v>
+        <v>1273.377</v>
       </c>
       <c r="C235">
-        <v>1049</v>
+        <v>841</v>
       </c>
       <c r="D235">
         <v>42</v>
@@ -5542,13 +5254,13 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46138.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B236">
-        <v>1884.037</v>
+        <v>1329.612</v>
       </c>
       <c r="C236">
-        <v>1006</v>
+        <v>853</v>
       </c>
       <c r="D236">
         <v>43</v>
@@ -5559,13 +5271,13 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46138.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B237">
-        <v>1861.985</v>
+        <v>1373.685</v>
       </c>
       <c r="C237">
-        <v>1016</v>
+        <v>950</v>
       </c>
       <c r="D237">
         <v>44</v>
@@ -5576,13 +5288,13 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46138.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B238">
-        <v>1824.923</v>
+        <v>1410.317</v>
       </c>
       <c r="C238">
-        <v>934</v>
+        <v>987</v>
       </c>
       <c r="D238">
         <v>45</v>
@@ -5593,13 +5305,13 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46138.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B239">
-        <v>1846.084</v>
+        <v>1433.672</v>
       </c>
       <c r="C239">
-        <v>929</v>
+        <v>0</v>
       </c>
       <c r="D239">
         <v>46</v>
@@ -5610,13 +5322,13 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46138.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B240">
-        <v>1846.75</v>
+        <v>1454.381</v>
       </c>
       <c r="C240">
-        <v>925</v>
+        <v>0</v>
       </c>
       <c r="D240">
         <v>47</v>
@@ -5627,13 +5339,13 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46138.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B241">
-        <v>1797.777</v>
+        <v>1472.87</v>
       </c>
       <c r="C241">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="D241">
         <v>48</v>
@@ -5644,13 +5356,13 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46138.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B242">
-        <v>1780.678</v>
+        <v>1513.705</v>
       </c>
       <c r="C242">
-        <v>919</v>
+        <v>0</v>
       </c>
       <c r="D242">
         <v>49</v>
@@ -5661,13 +5373,13 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46138.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B243">
-        <v>1774.255</v>
+        <v>1526.324</v>
       </c>
       <c r="C243">
-        <v>884</v>
+        <v>0</v>
       </c>
       <c r="D243">
         <v>50</v>
@@ -5678,13 +5390,13 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46138.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B244">
-        <v>1757.544</v>
+        <v>1490.692</v>
       </c>
       <c r="C244">
-        <v>886</v>
+        <v>0</v>
       </c>
       <c r="D244">
         <v>51</v>
@@ -5695,13 +5407,13 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46138.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B245">
-        <v>1714.716</v>
+        <v>1496.842</v>
       </c>
       <c r="C245">
-        <v>871</v>
+        <v>0</v>
       </c>
       <c r="D245">
         <v>52</v>
@@ -5712,13 +5424,13 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46138.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B246">
-        <v>1564.988</v>
+        <v>1527.108</v>
       </c>
       <c r="C246">
-        <v>864</v>
+        <v>0</v>
       </c>
       <c r="D246">
         <v>53</v>
@@ -5729,13 +5441,13 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46138.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B247">
-        <v>1553.653</v>
+        <v>1526.442</v>
       </c>
       <c r="C247">
-        <v>857</v>
+        <v>0</v>
       </c>
       <c r="D247">
         <v>54</v>
@@ -5746,13 +5458,13 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46138.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B248">
-        <v>1594.291</v>
+        <v>1510.656</v>
       </c>
       <c r="C248">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="D248">
         <v>55</v>
@@ -5763,13 +5475,13 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46138.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B249">
-        <v>1630.215</v>
+        <v>1524.884</v>
       </c>
       <c r="C249">
-        <v>844</v>
+        <v>0</v>
       </c>
       <c r="D249">
         <v>56</v>
@@ -5780,13 +5492,13 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46138.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B250">
-        <v>1581.439</v>
+        <v>1477.674</v>
       </c>
       <c r="C250">
-        <v>819</v>
+        <v>0</v>
       </c>
       <c r="D250">
         <v>57</v>
@@ -5797,13 +5509,13 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46138.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B251">
-        <v>1543.238</v>
+        <v>1469.93</v>
       </c>
       <c r="C251">
-        <v>787</v>
+        <v>0</v>
       </c>
       <c r="D251">
         <v>58</v>
@@ -5814,13 +5526,13 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46138.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B252">
-        <v>1504.808</v>
+        <v>1491.82</v>
       </c>
       <c r="C252">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="D252">
         <v>59</v>
@@ -5831,13 +5543,13 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46138.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B253">
-        <v>1401.523</v>
+        <v>1408.701</v>
       </c>
       <c r="C253">
-        <v>778</v>
+        <v>0</v>
       </c>
       <c r="D253">
         <v>60</v>
@@ -5848,13 +5560,13 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46138.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B254">
-        <v>1374.31</v>
+        <v>1339.777</v>
       </c>
       <c r="C254">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="D254">
         <v>61</v>
@@ -5865,13 +5577,13 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46138.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B255">
-        <v>1315.098</v>
+        <v>1303.075</v>
       </c>
       <c r="C255">
-        <v>703</v>
+        <v>0</v>
       </c>
       <c r="D255">
         <v>62</v>
@@ -5882,13 +5594,13 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46138.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B256">
-        <v>1291.292</v>
+        <v>1260.499</v>
       </c>
       <c r="C256">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="D256">
         <v>63</v>
@@ -5899,13 +5611,13 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46138.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B257">
-        <v>1221.107</v>
+        <v>1220.323</v>
       </c>
       <c r="C257">
-        <v>652</v>
+        <v>0</v>
       </c>
       <c r="D257">
         <v>64</v>
@@ -5916,13 +5628,13 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46138.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B258">
-        <v>1085.499</v>
+        <v>1092.93</v>
       </c>
       <c r="C258">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="D258">
         <v>65</v>
@@ -5933,13 +5645,13 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46138.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B259">
-        <v>968.99</v>
+        <v>1030.117</v>
       </c>
       <c r="C259">
-        <v>571</v>
+        <v>0</v>
       </c>
       <c r="D259">
         <v>66</v>
@@ -5950,13 +5662,13 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46138.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B260">
-        <v>928.4160000000001</v>
+        <v>953.944</v>
       </c>
       <c r="C260">
-        <v>548</v>
+        <v>0</v>
       </c>
       <c r="D260">
         <v>67</v>
@@ -5967,13 +5679,13 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46138.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B261">
-        <v>884.345</v>
+        <v>869.2809999999999</v>
       </c>
       <c r="C261">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="D261">
         <v>68</v>
@@ -5984,13 +5696,13 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46138.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B262">
-        <v>685.832</v>
+        <v>708.288</v>
       </c>
       <c r="C262">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="D262">
         <v>69</v>
@@ -6001,13 +5713,13 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46138.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B263">
-        <v>607.64</v>
+        <v>624.579</v>
       </c>
       <c r="C263">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="D263">
         <v>70</v>
@@ -6018,13 +5730,13 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46138.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B264">
-        <v>719.41</v>
+        <v>538.212</v>
       </c>
       <c r="C264">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="D264">
         <v>71</v>
@@ -6035,13 +5747,13 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46138.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B265">
-        <v>602.23</v>
+        <v>458.013</v>
       </c>
       <c r="C265">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="D265">
         <v>72</v>
@@ -6052,13 +5764,13 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46138.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B266">
-        <v>408.703</v>
+        <v>328.63</v>
       </c>
       <c r="C266">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="D266">
         <v>73</v>
@@ -6069,13 +5781,13 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46138.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B267">
-        <v>303.098</v>
+        <v>261.095</v>
       </c>
       <c r="C267">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="D267">
         <v>74</v>
@@ -6086,13 +5798,13 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46138.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B268">
-        <v>175.086</v>
+        <v>164.975</v>
       </c>
       <c r="C268">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D268">
         <v>75</v>
@@ -6103,13 +5815,13 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46138.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B269">
-        <v>112.354</v>
+        <v>97.503</v>
       </c>
       <c r="C269">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="D269">
         <v>76</v>
@@ -6120,13 +5832,13 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46138.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B270">
-        <v>48.407</v>
+        <v>42.661</v>
       </c>
       <c r="C270">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D270">
         <v>77</v>
@@ -6137,10 +5849,10 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46138.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B271">
-        <v>31.325</v>
+        <v>34.753</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -6154,10 +5866,10 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46138.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B272">
-        <v>22.739</v>
+        <v>24.809</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -6171,10 +5883,10 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46138.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B273">
-        <v>12.027</v>
+        <v>19.274</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -6188,10 +5900,10 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46138.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B274">
-        <v>6.122</v>
+        <v>15.778</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -6205,10 +5917,10 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46138.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B275">
-        <v>0</v>
+        <v>15.667</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -6222,10 +5934,10 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46138.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B276">
-        <v>5.755</v>
+        <v>15.271</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -6239,10 +5951,10 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46138.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B277">
-        <v>4.955</v>
+        <v>13.081</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -6256,10 +5968,10 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46138.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B278">
-        <v>4.43</v>
+        <v>13.33</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -6273,10 +5985,10 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46138.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B279">
-        <v>4.13</v>
+        <v>13.03</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -6290,10 +6002,10 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46138.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B280">
-        <v>1.43</v>
+        <v>10.33</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -6307,10 +6019,10 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46138.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B281">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -6324,7 +6036,7 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46138.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -6341,7 +6053,7 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46138.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -6358,7 +6070,7 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46138.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -6375,7 +6087,7 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46138.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -6392,7 +6104,7 @@
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="2">
-        <v>46138.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -6409,7 +6121,7 @@
     </row>
     <row r="287" spans="1:5">
       <c r="A287" s="2">
-        <v>46138.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -6426,7 +6138,7 @@
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="2">
-        <v>46138.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -6443,10 +6155,10 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" s="2">
-        <v>46138.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B289">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -6456,1638 +6168,6 @@
       </c>
       <c r="E289" t="s">
         <v>292</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5">
-      <c r="A290" s="2">
-        <v>46139</v>
-      </c>
-      <c r="B290">
-        <v>0</v>
-      </c>
-      <c r="C290">
-        <v>0</v>
-      </c>
-      <c r="D290">
-        <v>1</v>
-      </c>
-      <c r="E290" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5">
-      <c r="A291" s="2">
-        <v>46139.01041666666</v>
-      </c>
-      <c r="B291">
-        <v>0</v>
-      </c>
-      <c r="C291">
-        <v>0</v>
-      </c>
-      <c r="D291">
-        <v>2</v>
-      </c>
-      <c r="E291" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5">
-      <c r="A292" s="2">
-        <v>46139.02083333334</v>
-      </c>
-      <c r="B292">
-        <v>0</v>
-      </c>
-      <c r="C292">
-        <v>0</v>
-      </c>
-      <c r="D292">
-        <v>3</v>
-      </c>
-      <c r="E292" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5">
-      <c r="A293" s="2">
-        <v>46139.03125</v>
-      </c>
-      <c r="B293">
-        <v>0</v>
-      </c>
-      <c r="C293">
-        <v>0</v>
-      </c>
-      <c r="D293">
-        <v>4</v>
-      </c>
-      <c r="E293" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5">
-      <c r="A294" s="2">
-        <v>46139.04166666666</v>
-      </c>
-      <c r="B294">
-        <v>0</v>
-      </c>
-      <c r="C294">
-        <v>0</v>
-      </c>
-      <c r="D294">
-        <v>5</v>
-      </c>
-      <c r="E294" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5">
-      <c r="A295" s="2">
-        <v>46139.05208333334</v>
-      </c>
-      <c r="B295">
-        <v>0</v>
-      </c>
-      <c r="C295">
-        <v>0</v>
-      </c>
-      <c r="D295">
-        <v>6</v>
-      </c>
-      <c r="E295" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5">
-      <c r="A296" s="2">
-        <v>46139.0625</v>
-      </c>
-      <c r="B296">
-        <v>0</v>
-      </c>
-      <c r="C296">
-        <v>0</v>
-      </c>
-      <c r="D296">
-        <v>7</v>
-      </c>
-      <c r="E296" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5">
-      <c r="A297" s="2">
-        <v>46139.07291666666</v>
-      </c>
-      <c r="B297">
-        <v>0</v>
-      </c>
-      <c r="C297">
-        <v>0</v>
-      </c>
-      <c r="D297">
-        <v>8</v>
-      </c>
-      <c r="E297" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5">
-      <c r="A298" s="2">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="B298">
-        <v>0</v>
-      </c>
-      <c r="C298">
-        <v>0</v>
-      </c>
-      <c r="D298">
-        <v>9</v>
-      </c>
-      <c r="E298" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5">
-      <c r="A299" s="2">
-        <v>46139.09375</v>
-      </c>
-      <c r="B299">
-        <v>0</v>
-      </c>
-      <c r="C299">
-        <v>0</v>
-      </c>
-      <c r="D299">
-        <v>10</v>
-      </c>
-      <c r="E299" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5">
-      <c r="A300" s="2">
-        <v>46139.10416666666</v>
-      </c>
-      <c r="B300">
-        <v>0</v>
-      </c>
-      <c r="C300">
-        <v>0</v>
-      </c>
-      <c r="D300">
-        <v>11</v>
-      </c>
-      <c r="E300" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5">
-      <c r="A301" s="2">
-        <v>46139.11458333334</v>
-      </c>
-      <c r="B301">
-        <v>0</v>
-      </c>
-      <c r="C301">
-        <v>0</v>
-      </c>
-      <c r="D301">
-        <v>12</v>
-      </c>
-      <c r="E301" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5">
-      <c r="A302" s="2">
-        <v>46139.125</v>
-      </c>
-      <c r="B302">
-        <v>0</v>
-      </c>
-      <c r="C302">
-        <v>0</v>
-      </c>
-      <c r="D302">
-        <v>13</v>
-      </c>
-      <c r="E302" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5">
-      <c r="A303" s="2">
-        <v>46139.13541666666</v>
-      </c>
-      <c r="B303">
-        <v>0</v>
-      </c>
-      <c r="C303">
-        <v>0</v>
-      </c>
-      <c r="D303">
-        <v>14</v>
-      </c>
-      <c r="E303" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5">
-      <c r="A304" s="2">
-        <v>46139.14583333334</v>
-      </c>
-      <c r="B304">
-        <v>0</v>
-      </c>
-      <c r="C304">
-        <v>0</v>
-      </c>
-      <c r="D304">
-        <v>15</v>
-      </c>
-      <c r="E304" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5">
-      <c r="A305" s="2">
-        <v>46139.15625</v>
-      </c>
-      <c r="B305">
-        <v>0</v>
-      </c>
-      <c r="C305">
-        <v>0</v>
-      </c>
-      <c r="D305">
-        <v>16</v>
-      </c>
-      <c r="E305" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5">
-      <c r="A306" s="2">
-        <v>46139.16666666666</v>
-      </c>
-      <c r="B306">
-        <v>19.93</v>
-      </c>
-      <c r="C306">
-        <v>0</v>
-      </c>
-      <c r="D306">
-        <v>17</v>
-      </c>
-      <c r="E306" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5">
-      <c r="A307" s="2">
-        <v>46139.17708333334</v>
-      </c>
-      <c r="B307">
-        <v>0</v>
-      </c>
-      <c r="C307">
-        <v>0</v>
-      </c>
-      <c r="D307">
-        <v>18</v>
-      </c>
-      <c r="E307" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5">
-      <c r="A308" s="2">
-        <v>46139.1875</v>
-      </c>
-      <c r="B308">
-        <v>0</v>
-      </c>
-      <c r="C308">
-        <v>0</v>
-      </c>
-      <c r="D308">
-        <v>19</v>
-      </c>
-      <c r="E308" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5">
-      <c r="A309" s="2">
-        <v>46139.19791666666</v>
-      </c>
-      <c r="B309">
-        <v>19.934</v>
-      </c>
-      <c r="C309">
-        <v>0</v>
-      </c>
-      <c r="D309">
-        <v>20</v>
-      </c>
-      <c r="E309" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5">
-      <c r="A310" s="2">
-        <v>46139.20833333334</v>
-      </c>
-      <c r="B310">
-        <v>35.506</v>
-      </c>
-      <c r="C310">
-        <v>0</v>
-      </c>
-      <c r="D310">
-        <v>21</v>
-      </c>
-      <c r="E310" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5">
-      <c r="A311" s="2">
-        <v>46139.21875</v>
-      </c>
-      <c r="B311">
-        <v>46.3</v>
-      </c>
-      <c r="C311">
-        <v>2</v>
-      </c>
-      <c r="D311">
-        <v>22</v>
-      </c>
-      <c r="E311" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5">
-      <c r="A312" s="2">
-        <v>46139.22916666666</v>
-      </c>
-      <c r="B312">
-        <v>75.43000000000001</v>
-      </c>
-      <c r="C312">
-        <v>30</v>
-      </c>
-      <c r="D312">
-        <v>23</v>
-      </c>
-      <c r="E312" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5">
-      <c r="A313" s="2">
-        <v>46139.23958333334</v>
-      </c>
-      <c r="B313">
-        <v>119.29</v>
-      </c>
-      <c r="C313">
-        <v>76</v>
-      </c>
-      <c r="D313">
-        <v>24</v>
-      </c>
-      <c r="E313" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5">
-      <c r="A314" s="2">
-        <v>46139.25</v>
-      </c>
-      <c r="B314">
-        <v>262.357</v>
-      </c>
-      <c r="C314">
-        <v>150</v>
-      </c>
-      <c r="D314">
-        <v>25</v>
-      </c>
-      <c r="E314" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5">
-      <c r="A315" s="2">
-        <v>46139.26041666666</v>
-      </c>
-      <c r="B315">
-        <v>375.294</v>
-      </c>
-      <c r="C315">
-        <v>263</v>
-      </c>
-      <c r="D315">
-        <v>26</v>
-      </c>
-      <c r="E315" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5">
-      <c r="A316" s="2">
-        <v>46139.27083333334</v>
-      </c>
-      <c r="B316">
-        <v>506.715</v>
-      </c>
-      <c r="C316">
-        <v>406</v>
-      </c>
-      <c r="D316">
-        <v>27</v>
-      </c>
-      <c r="E316" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5">
-      <c r="A317" s="2">
-        <v>46139.28125</v>
-      </c>
-      <c r="B317">
-        <v>667.468</v>
-      </c>
-      <c r="C317">
-        <v>602</v>
-      </c>
-      <c r="D317">
-        <v>28</v>
-      </c>
-      <c r="E317" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5">
-      <c r="A318" s="2">
-        <v>46139.29166666666</v>
-      </c>
-      <c r="B318">
-        <v>950.105</v>
-      </c>
-      <c r="C318">
-        <v>787</v>
-      </c>
-      <c r="D318">
-        <v>29</v>
-      </c>
-      <c r="E318" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5">
-      <c r="A319" s="2">
-        <v>46139.30208333334</v>
-      </c>
-      <c r="B319">
-        <v>1145.909</v>
-      </c>
-      <c r="C319">
-        <v>952</v>
-      </c>
-      <c r="D319">
-        <v>30</v>
-      </c>
-      <c r="E319" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5">
-      <c r="A320" s="2">
-        <v>46139.3125</v>
-      </c>
-      <c r="B320">
-        <v>1323.232</v>
-      </c>
-      <c r="C320">
-        <v>1137</v>
-      </c>
-      <c r="D320">
-        <v>31</v>
-      </c>
-      <c r="E320" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5">
-      <c r="A321" s="2">
-        <v>46139.32291666666</v>
-      </c>
-      <c r="B321">
-        <v>1555.51</v>
-      </c>
-      <c r="C321">
-        <v>1297</v>
-      </c>
-      <c r="D321">
-        <v>32</v>
-      </c>
-      <c r="E321" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5">
-      <c r="A322" s="2">
-        <v>46139.33333333334</v>
-      </c>
-      <c r="B322">
-        <v>1867.862</v>
-      </c>
-      <c r="C322">
-        <v>1442</v>
-      </c>
-      <c r="D322">
-        <v>33</v>
-      </c>
-      <c r="E322" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5">
-      <c r="A323" s="2">
-        <v>46139.34375</v>
-      </c>
-      <c r="B323">
-        <v>2040.571</v>
-      </c>
-      <c r="C323">
-        <v>1566</v>
-      </c>
-      <c r="D323">
-        <v>34</v>
-      </c>
-      <c r="E323" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5">
-      <c r="A324" s="2">
-        <v>46139.35416666666</v>
-      </c>
-      <c r="B324">
-        <v>2214.938</v>
-      </c>
-      <c r="C324">
-        <v>1667</v>
-      </c>
-      <c r="D324">
-        <v>35</v>
-      </c>
-      <c r="E324" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5">
-      <c r="A325" s="2">
-        <v>46139.36458333334</v>
-      </c>
-      <c r="B325">
-        <v>2381.693</v>
-      </c>
-      <c r="C325">
-        <v>1812</v>
-      </c>
-      <c r="D325">
-        <v>36</v>
-      </c>
-      <c r="E325" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5">
-      <c r="A326" s="2">
-        <v>46139.375</v>
-      </c>
-      <c r="B326">
-        <v>2607.496</v>
-      </c>
-      <c r="C326">
-        <v>1898</v>
-      </c>
-      <c r="D326">
-        <v>37</v>
-      </c>
-      <c r="E326" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5">
-      <c r="A327" s="2">
-        <v>46139.38541666666</v>
-      </c>
-      <c r="B327">
-        <v>2714.983</v>
-      </c>
-      <c r="C327">
-        <v>2062</v>
-      </c>
-      <c r="D327">
-        <v>38</v>
-      </c>
-      <c r="E327" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5">
-      <c r="A328" s="2">
-        <v>46139.39583333334</v>
-      </c>
-      <c r="B328">
-        <v>2835.379</v>
-      </c>
-      <c r="C328">
-        <v>2154</v>
-      </c>
-      <c r="D328">
-        <v>39</v>
-      </c>
-      <c r="E328" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5">
-      <c r="A329" s="2">
-        <v>46139.40625</v>
-      </c>
-      <c r="B329">
-        <v>2941.058</v>
-      </c>
-      <c r="C329">
-        <v>2170</v>
-      </c>
-      <c r="D329">
-        <v>40</v>
-      </c>
-      <c r="E329" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5">
-      <c r="A330" s="2">
-        <v>46139.41666666666</v>
-      </c>
-      <c r="B330">
-        <v>3045.231</v>
-      </c>
-      <c r="C330">
-        <v>2267</v>
-      </c>
-      <c r="D330">
-        <v>41</v>
-      </c>
-      <c r="E330" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5">
-      <c r="A331" s="2">
-        <v>46139.42708333334</v>
-      </c>
-      <c r="B331">
-        <v>3118.065</v>
-      </c>
-      <c r="C331">
-        <v>2248</v>
-      </c>
-      <c r="D331">
-        <v>42</v>
-      </c>
-      <c r="E331" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5">
-      <c r="A332" s="2">
-        <v>46139.4375</v>
-      </c>
-      <c r="B332">
-        <v>3169.995</v>
-      </c>
-      <c r="C332">
-        <v>2279</v>
-      </c>
-      <c r="D332">
-        <v>43</v>
-      </c>
-      <c r="E332" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5">
-      <c r="A333" s="2">
-        <v>46139.44791666666</v>
-      </c>
-      <c r="B333">
-        <v>3184.391</v>
-      </c>
-      <c r="C333">
-        <v>2310</v>
-      </c>
-      <c r="D333">
-        <v>44</v>
-      </c>
-      <c r="E333" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5">
-      <c r="A334" s="2">
-        <v>46139.45833333334</v>
-      </c>
-      <c r="B334">
-        <v>3246.584</v>
-      </c>
-      <c r="C334">
-        <v>2256</v>
-      </c>
-      <c r="D334">
-        <v>45</v>
-      </c>
-      <c r="E334" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5">
-      <c r="A335" s="2">
-        <v>46139.46875</v>
-      </c>
-      <c r="B335">
-        <v>3033.751</v>
-      </c>
-      <c r="C335">
-        <v>0</v>
-      </c>
-      <c r="D335">
-        <v>46</v>
-      </c>
-      <c r="E335" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5">
-      <c r="A336" s="2">
-        <v>46139.47916666666</v>
-      </c>
-      <c r="B336">
-        <v>2478.727</v>
-      </c>
-      <c r="C336">
-        <v>0</v>
-      </c>
-      <c r="D336">
-        <v>47</v>
-      </c>
-      <c r="E336" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5">
-      <c r="A337" s="2">
-        <v>46139.48958333334</v>
-      </c>
-      <c r="B337">
-        <v>2473.377</v>
-      </c>
-      <c r="C337">
-        <v>0</v>
-      </c>
-      <c r="D337">
-        <v>48</v>
-      </c>
-      <c r="E337" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5">
-      <c r="A338" s="2">
-        <v>46139.5</v>
-      </c>
-      <c r="B338">
-        <v>2472.51</v>
-      </c>
-      <c r="C338">
-        <v>0</v>
-      </c>
-      <c r="D338">
-        <v>49</v>
-      </c>
-      <c r="E338" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5">
-      <c r="A339" s="2">
-        <v>46139.51041666666</v>
-      </c>
-      <c r="B339">
-        <v>2468.958</v>
-      </c>
-      <c r="C339">
-        <v>0</v>
-      </c>
-      <c r="D339">
-        <v>50</v>
-      </c>
-      <c r="E339" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5">
-      <c r="A340" s="2">
-        <v>46139.52083333334</v>
-      </c>
-      <c r="B340">
-        <v>2458.091</v>
-      </c>
-      <c r="C340">
-        <v>0</v>
-      </c>
-      <c r="D340">
-        <v>51</v>
-      </c>
-      <c r="E340" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5">
-      <c r="A341" s="2">
-        <v>46139.53125</v>
-      </c>
-      <c r="B341">
-        <v>2436.669</v>
-      </c>
-      <c r="C341">
-        <v>0</v>
-      </c>
-      <c r="D341">
-        <v>52</v>
-      </c>
-      <c r="E341" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5">
-      <c r="A342" s="2">
-        <v>46139.54166666666</v>
-      </c>
-      <c r="B342">
-        <v>2360.532</v>
-      </c>
-      <c r="C342">
-        <v>0</v>
-      </c>
-      <c r="D342">
-        <v>53</v>
-      </c>
-      <c r="E342" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5">
-      <c r="A343" s="2">
-        <v>46139.55208333334</v>
-      </c>
-      <c r="B343">
-        <v>2338.583</v>
-      </c>
-      <c r="C343">
-        <v>0</v>
-      </c>
-      <c r="D343">
-        <v>54</v>
-      </c>
-      <c r="E343" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5">
-      <c r="A344" s="2">
-        <v>46139.5625</v>
-      </c>
-      <c r="B344">
-        <v>2288.484</v>
-      </c>
-      <c r="C344">
-        <v>0</v>
-      </c>
-      <c r="D344">
-        <v>55</v>
-      </c>
-      <c r="E344" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5">
-      <c r="A345" s="2">
-        <v>46139.57291666666</v>
-      </c>
-      <c r="B345">
-        <v>2246.35</v>
-      </c>
-      <c r="C345">
-        <v>0</v>
-      </c>
-      <c r="D345">
-        <v>56</v>
-      </c>
-      <c r="E345" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5">
-      <c r="A346" s="2">
-        <v>46139.58333333334</v>
-      </c>
-      <c r="B346">
-        <v>2280.126</v>
-      </c>
-      <c r="C346">
-        <v>0</v>
-      </c>
-      <c r="D346">
-        <v>57</v>
-      </c>
-      <c r="E346" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5">
-      <c r="A347" s="2">
-        <v>46139.59375</v>
-      </c>
-      <c r="B347">
-        <v>2252.695</v>
-      </c>
-      <c r="C347">
-        <v>0</v>
-      </c>
-      <c r="D347">
-        <v>58</v>
-      </c>
-      <c r="E347" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5">
-      <c r="A348" s="2">
-        <v>46139.60416666666</v>
-      </c>
-      <c r="B348">
-        <v>2198.795</v>
-      </c>
-      <c r="C348">
-        <v>0</v>
-      </c>
-      <c r="D348">
-        <v>59</v>
-      </c>
-      <c r="E348" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5">
-      <c r="A349" s="2">
-        <v>46139.61458333334</v>
-      </c>
-      <c r="B349">
-        <v>2150.394</v>
-      </c>
-      <c r="C349">
-        <v>0</v>
-      </c>
-      <c r="D349">
-        <v>60</v>
-      </c>
-      <c r="E349" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5">
-      <c r="A350" s="2">
-        <v>46139.625</v>
-      </c>
-      <c r="B350">
-        <v>2006.685</v>
-      </c>
-      <c r="C350">
-        <v>0</v>
-      </c>
-      <c r="D350">
-        <v>61</v>
-      </c>
-      <c r="E350" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5">
-      <c r="A351" s="2">
-        <v>46139.63541666666</v>
-      </c>
-      <c r="B351">
-        <v>1926.59</v>
-      </c>
-      <c r="C351">
-        <v>0</v>
-      </c>
-      <c r="D351">
-        <v>62</v>
-      </c>
-      <c r="E351" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="352" spans="1:5">
-      <c r="A352" s="2">
-        <v>46139.64583333334</v>
-      </c>
-      <c r="B352">
-        <v>2316.525</v>
-      </c>
-      <c r="C352">
-        <v>0</v>
-      </c>
-      <c r="D352">
-        <v>63</v>
-      </c>
-      <c r="E352" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5">
-      <c r="A353" s="2">
-        <v>46139.65625</v>
-      </c>
-      <c r="B353">
-        <v>2343.831</v>
-      </c>
-      <c r="C353">
-        <v>0</v>
-      </c>
-      <c r="D353">
-        <v>64</v>
-      </c>
-      <c r="E353" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5">
-      <c r="A354" s="2">
-        <v>46139.66666666666</v>
-      </c>
-      <c r="B354">
-        <v>2114.306</v>
-      </c>
-      <c r="C354">
-        <v>0</v>
-      </c>
-      <c r="D354">
-        <v>65</v>
-      </c>
-      <c r="E354" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5">
-      <c r="A355" s="2">
-        <v>46139.67708333334</v>
-      </c>
-      <c r="B355">
-        <v>1931.936</v>
-      </c>
-      <c r="C355">
-        <v>0</v>
-      </c>
-      <c r="D355">
-        <v>66</v>
-      </c>
-      <c r="E355" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5">
-      <c r="A356" s="2">
-        <v>46139.6875</v>
-      </c>
-      <c r="B356">
-        <v>1728.814</v>
-      </c>
-      <c r="C356">
-        <v>0</v>
-      </c>
-      <c r="D356">
-        <v>67</v>
-      </c>
-      <c r="E356" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5">
-      <c r="A357" s="2">
-        <v>46139.69791666666</v>
-      </c>
-      <c r="B357">
-        <v>1510.767</v>
-      </c>
-      <c r="C357">
-        <v>0</v>
-      </c>
-      <c r="D357">
-        <v>68</v>
-      </c>
-      <c r="E357" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5">
-      <c r="A358" s="2">
-        <v>46139.70833333334</v>
-      </c>
-      <c r="B358">
-        <v>1213.31</v>
-      </c>
-      <c r="C358">
-        <v>0</v>
-      </c>
-      <c r="D358">
-        <v>69</v>
-      </c>
-      <c r="E358" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5">
-      <c r="A359" s="2">
-        <v>46139.71875</v>
-      </c>
-      <c r="B359">
-        <v>1025.504</v>
-      </c>
-      <c r="C359">
-        <v>0</v>
-      </c>
-      <c r="D359">
-        <v>70</v>
-      </c>
-      <c r="E359" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5">
-      <c r="A360" s="2">
-        <v>46139.72916666666</v>
-      </c>
-      <c r="B360">
-        <v>851.218</v>
-      </c>
-      <c r="C360">
-        <v>0</v>
-      </c>
-      <c r="D360">
-        <v>71</v>
-      </c>
-      <c r="E360" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5">
-      <c r="A361" s="2">
-        <v>46139.73958333334</v>
-      </c>
-      <c r="B361">
-        <v>673.534</v>
-      </c>
-      <c r="C361">
-        <v>0</v>
-      </c>
-      <c r="D361">
-        <v>72</v>
-      </c>
-      <c r="E361" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5">
-      <c r="A362" s="2">
-        <v>46139.75</v>
-      </c>
-      <c r="B362">
-        <v>412.423</v>
-      </c>
-      <c r="C362">
-        <v>0</v>
-      </c>
-      <c r="D362">
-        <v>73</v>
-      </c>
-      <c r="E362" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5">
-      <c r="A363" s="2">
-        <v>46139.76041666666</v>
-      </c>
-      <c r="B363">
-        <v>288.463</v>
-      </c>
-      <c r="C363">
-        <v>0</v>
-      </c>
-      <c r="D363">
-        <v>74</v>
-      </c>
-      <c r="E363" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5">
-      <c r="A364" s="2">
-        <v>46139.77083333334</v>
-      </c>
-      <c r="B364">
-        <v>189.298</v>
-      </c>
-      <c r="C364">
-        <v>0</v>
-      </c>
-      <c r="D364">
-        <v>75</v>
-      </c>
-      <c r="E364" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5">
-      <c r="A365" s="2">
-        <v>46139.78125</v>
-      </c>
-      <c r="B365">
-        <v>118.653</v>
-      </c>
-      <c r="C365">
-        <v>0</v>
-      </c>
-      <c r="D365">
-        <v>76</v>
-      </c>
-      <c r="E365" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5">
-      <c r="A366" s="2">
-        <v>46139.79166666666</v>
-      </c>
-      <c r="B366">
-        <v>49.565</v>
-      </c>
-      <c r="C366">
-        <v>0</v>
-      </c>
-      <c r="D366">
-        <v>77</v>
-      </c>
-      <c r="E366" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5">
-      <c r="A367" s="2">
-        <v>46139.80208333334</v>
-      </c>
-      <c r="B367">
-        <v>26.854</v>
-      </c>
-      <c r="C367">
-        <v>0</v>
-      </c>
-      <c r="D367">
-        <v>78</v>
-      </c>
-      <c r="E367" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5">
-      <c r="A368" s="2">
-        <v>46139.8125</v>
-      </c>
-      <c r="B368">
-        <v>19.498</v>
-      </c>
-      <c r="C368">
-        <v>0</v>
-      </c>
-      <c r="D368">
-        <v>79</v>
-      </c>
-      <c r="E368" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5">
-      <c r="A369" s="2">
-        <v>46139.82291666666</v>
-      </c>
-      <c r="B369">
-        <v>11.777</v>
-      </c>
-      <c r="C369">
-        <v>0</v>
-      </c>
-      <c r="D369">
-        <v>80</v>
-      </c>
-      <c r="E369" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5">
-      <c r="A370" s="2">
-        <v>46139.83333333334</v>
-      </c>
-      <c r="B370">
-        <v>15.123</v>
-      </c>
-      <c r="C370">
-        <v>0</v>
-      </c>
-      <c r="D370">
-        <v>81</v>
-      </c>
-      <c r="E370" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5">
-      <c r="A371" s="2">
-        <v>46139.84375</v>
-      </c>
-      <c r="B371">
-        <v>15.124</v>
-      </c>
-      <c r="C371">
-        <v>0</v>
-      </c>
-      <c r="D371">
-        <v>82</v>
-      </c>
-      <c r="E371" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5">
-      <c r="A372" s="2">
-        <v>46139.85416666666</v>
-      </c>
-      <c r="B372">
-        <v>13.759</v>
-      </c>
-      <c r="C372">
-        <v>0</v>
-      </c>
-      <c r="D372">
-        <v>83</v>
-      </c>
-      <c r="E372" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="373" spans="1:5">
-      <c r="A373" s="2">
-        <v>46139.86458333334</v>
-      </c>
-      <c r="B373">
-        <v>6.267</v>
-      </c>
-      <c r="C373">
-        <v>0</v>
-      </c>
-      <c r="D373">
-        <v>84</v>
-      </c>
-      <c r="E373" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="374" spans="1:5">
-      <c r="A374" s="2">
-        <v>46139.875</v>
-      </c>
-      <c r="B374">
-        <v>12.33</v>
-      </c>
-      <c r="C374">
-        <v>0</v>
-      </c>
-      <c r="D374">
-        <v>85</v>
-      </c>
-      <c r="E374" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="375" spans="1:5">
-      <c r="A375" s="2">
-        <v>46139.88541666666</v>
-      </c>
-      <c r="B375">
-        <v>10.03</v>
-      </c>
-      <c r="C375">
-        <v>0</v>
-      </c>
-      <c r="D375">
-        <v>86</v>
-      </c>
-      <c r="E375" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5">
-      <c r="A376" s="2">
-        <v>46139.89583333334</v>
-      </c>
-      <c r="B376">
-        <v>9.33</v>
-      </c>
-      <c r="C376">
-        <v>0</v>
-      </c>
-      <c r="D376">
-        <v>87</v>
-      </c>
-      <c r="E376" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5">
-      <c r="A377" s="2">
-        <v>46139.90625</v>
-      </c>
-      <c r="B377">
-        <v>4.03</v>
-      </c>
-      <c r="C377">
-        <v>0</v>
-      </c>
-      <c r="D377">
-        <v>88</v>
-      </c>
-      <c r="E377" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5">
-      <c r="A378" s="2">
-        <v>46139.91666666666</v>
-      </c>
-      <c r="B378">
-        <v>2.03</v>
-      </c>
-      <c r="C378">
-        <v>0</v>
-      </c>
-      <c r="D378">
-        <v>89</v>
-      </c>
-      <c r="E378" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5">
-      <c r="A379" s="2">
-        <v>46139.92708333334</v>
-      </c>
-      <c r="B379">
-        <v>0.73</v>
-      </c>
-      <c r="C379">
-        <v>0</v>
-      </c>
-      <c r="D379">
-        <v>90</v>
-      </c>
-      <c r="E379" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5">
-      <c r="A380" s="2">
-        <v>46139.9375</v>
-      </c>
-      <c r="B380">
-        <v>0</v>
-      </c>
-      <c r="C380">
-        <v>0</v>
-      </c>
-      <c r="D380">
-        <v>91</v>
-      </c>
-      <c r="E380" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5">
-      <c r="A381" s="2">
-        <v>46139.94791666666</v>
-      </c>
-      <c r="B381">
-        <v>0</v>
-      </c>
-      <c r="C381">
-        <v>0</v>
-      </c>
-      <c r="D381">
-        <v>92</v>
-      </c>
-      <c r="E381" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5">
-      <c r="A382" s="2">
-        <v>46139.95833333334</v>
-      </c>
-      <c r="B382">
-        <v>0</v>
-      </c>
-      <c r="C382">
-        <v>0</v>
-      </c>
-      <c r="D382">
-        <v>93</v>
-      </c>
-      <c r="E382" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5">
-      <c r="A383" s="2">
-        <v>46139.96875</v>
-      </c>
-      <c r="B383">
-        <v>0</v>
-      </c>
-      <c r="C383">
-        <v>0</v>
-      </c>
-      <c r="D383">
-        <v>94</v>
-      </c>
-      <c r="E383" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="384" spans="1:5">
-      <c r="A384" s="2">
-        <v>46139.97916666666</v>
-      </c>
-      <c r="B384">
-        <v>0</v>
-      </c>
-      <c r="C384">
-        <v>0</v>
-      </c>
-      <c r="D384">
-        <v>95</v>
-      </c>
-      <c r="E384" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5">
-      <c r="A385" s="2">
-        <v>46139.98958333334</v>
-      </c>
-      <c r="B385">
-        <v>0</v>
-      </c>
-      <c r="C385">
-        <v>0</v>
-      </c>
-      <c r="D385">
-        <v>96</v>
-      </c>
-      <c r="E385" t="s">
-        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,582 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.04.20261</t>
-  </si>
-  <si>
-    <t>28.04.20262</t>
-  </si>
-  <si>
-    <t>28.04.20263</t>
-  </si>
-  <si>
-    <t>28.04.20264</t>
-  </si>
-  <si>
-    <t>28.04.20265</t>
-  </si>
-  <si>
-    <t>28.04.20266</t>
-  </si>
-  <si>
-    <t>28.04.20267</t>
-  </si>
-  <si>
-    <t>28.04.20268</t>
-  </si>
-  <si>
-    <t>28.04.20269</t>
-  </si>
-  <si>
-    <t>28.04.202610</t>
-  </si>
-  <si>
-    <t>28.04.202611</t>
-  </si>
-  <si>
-    <t>28.04.202612</t>
-  </si>
-  <si>
-    <t>28.04.202613</t>
-  </si>
-  <si>
-    <t>28.04.202614</t>
-  </si>
-  <si>
-    <t>28.04.202615</t>
-  </si>
-  <si>
-    <t>28.04.202616</t>
-  </si>
-  <si>
-    <t>28.04.202617</t>
-  </si>
-  <si>
-    <t>28.04.202618</t>
-  </si>
-  <si>
-    <t>28.04.202619</t>
-  </si>
-  <si>
-    <t>28.04.202620</t>
-  </si>
-  <si>
-    <t>28.04.202621</t>
-  </si>
-  <si>
-    <t>28.04.202622</t>
-  </si>
-  <si>
-    <t>28.04.202623</t>
-  </si>
-  <si>
-    <t>28.04.202624</t>
-  </si>
-  <si>
-    <t>28.04.202625</t>
-  </si>
-  <si>
-    <t>28.04.202626</t>
-  </si>
-  <si>
-    <t>28.04.202627</t>
-  </si>
-  <si>
-    <t>28.04.202628</t>
-  </si>
-  <si>
-    <t>28.04.202629</t>
-  </si>
-  <si>
-    <t>28.04.202630</t>
-  </si>
-  <si>
-    <t>28.04.202631</t>
-  </si>
-  <si>
-    <t>28.04.202632</t>
-  </si>
-  <si>
-    <t>28.04.202633</t>
-  </si>
-  <si>
-    <t>28.04.202634</t>
-  </si>
-  <si>
-    <t>28.04.202635</t>
-  </si>
-  <si>
-    <t>28.04.202636</t>
-  </si>
-  <si>
-    <t>28.04.202637</t>
-  </si>
-  <si>
-    <t>28.04.202638</t>
-  </si>
-  <si>
-    <t>28.04.202639</t>
-  </si>
-  <si>
-    <t>28.04.202640</t>
-  </si>
-  <si>
-    <t>28.04.202641</t>
-  </si>
-  <si>
-    <t>28.04.202642</t>
-  </si>
-  <si>
-    <t>28.04.202643</t>
-  </si>
-  <si>
-    <t>28.04.202644</t>
-  </si>
-  <si>
-    <t>28.04.202645</t>
-  </si>
-  <si>
-    <t>28.04.202646</t>
-  </si>
-  <si>
-    <t>28.04.202647</t>
-  </si>
-  <si>
-    <t>28.04.202648</t>
-  </si>
-  <si>
-    <t>28.04.202649</t>
-  </si>
-  <si>
-    <t>28.04.202650</t>
-  </si>
-  <si>
-    <t>28.04.202651</t>
-  </si>
-  <si>
-    <t>28.04.202652</t>
-  </si>
-  <si>
-    <t>28.04.202653</t>
-  </si>
-  <si>
-    <t>28.04.202654</t>
-  </si>
-  <si>
-    <t>28.04.202655</t>
-  </si>
-  <si>
-    <t>28.04.202656</t>
-  </si>
-  <si>
-    <t>28.04.202657</t>
-  </si>
-  <si>
-    <t>28.04.202658</t>
-  </si>
-  <si>
-    <t>28.04.202659</t>
-  </si>
-  <si>
-    <t>28.04.202660</t>
-  </si>
-  <si>
-    <t>28.04.202661</t>
-  </si>
-  <si>
-    <t>28.04.202662</t>
-  </si>
-  <si>
-    <t>28.04.202663</t>
-  </si>
-  <si>
-    <t>28.04.202664</t>
-  </si>
-  <si>
-    <t>28.04.202665</t>
-  </si>
-  <si>
-    <t>28.04.202666</t>
-  </si>
-  <si>
-    <t>28.04.202667</t>
-  </si>
-  <si>
-    <t>28.04.202668</t>
-  </si>
-  <si>
-    <t>28.04.202669</t>
-  </si>
-  <si>
-    <t>28.04.202670</t>
-  </si>
-  <si>
-    <t>28.04.202671</t>
-  </si>
-  <si>
-    <t>28.04.202672</t>
-  </si>
-  <si>
-    <t>28.04.202673</t>
-  </si>
-  <si>
-    <t>28.04.202674</t>
-  </si>
-  <si>
-    <t>28.04.202675</t>
-  </si>
-  <si>
-    <t>28.04.202676</t>
-  </si>
-  <si>
-    <t>28.04.202677</t>
-  </si>
-  <si>
-    <t>28.04.202678</t>
-  </si>
-  <si>
-    <t>28.04.202679</t>
-  </si>
-  <si>
-    <t>28.04.202680</t>
-  </si>
-  <si>
-    <t>28.04.202681</t>
-  </si>
-  <si>
-    <t>28.04.202682</t>
-  </si>
-  <si>
-    <t>28.04.202683</t>
-  </si>
-  <si>
-    <t>28.04.202684</t>
-  </si>
-  <si>
-    <t>28.04.202685</t>
-  </si>
-  <si>
-    <t>28.04.202686</t>
-  </si>
-  <si>
-    <t>28.04.202687</t>
-  </si>
-  <si>
-    <t>28.04.202688</t>
-  </si>
-  <si>
-    <t>28.04.202689</t>
-  </si>
-  <si>
-    <t>28.04.202690</t>
-  </si>
-  <si>
-    <t>28.04.202691</t>
-  </si>
-  <si>
-    <t>28.04.202692</t>
-  </si>
-  <si>
-    <t>28.04.202693</t>
-  </si>
-  <si>
-    <t>28.04.202694</t>
-  </si>
-  <si>
-    <t>28.04.202695</t>
-  </si>
-  <si>
-    <t>28.04.202696</t>
-  </si>
-  <si>
-    <t>29.04.20261</t>
-  </si>
-  <si>
-    <t>29.04.20262</t>
-  </si>
-  <si>
-    <t>29.04.20263</t>
-  </si>
-  <si>
-    <t>29.04.20264</t>
-  </si>
-  <si>
-    <t>29.04.20265</t>
-  </si>
-  <si>
-    <t>29.04.20266</t>
-  </si>
-  <si>
-    <t>29.04.20267</t>
-  </si>
-  <si>
-    <t>29.04.20268</t>
-  </si>
-  <si>
-    <t>29.04.20269</t>
-  </si>
-  <si>
-    <t>29.04.202610</t>
-  </si>
-  <si>
-    <t>29.04.202611</t>
-  </si>
-  <si>
-    <t>29.04.202612</t>
-  </si>
-  <si>
-    <t>29.04.202613</t>
-  </si>
-  <si>
-    <t>29.04.202614</t>
-  </si>
-  <si>
-    <t>29.04.202615</t>
-  </si>
-  <si>
-    <t>29.04.202616</t>
-  </si>
-  <si>
-    <t>29.04.202617</t>
-  </si>
-  <si>
-    <t>29.04.202618</t>
-  </si>
-  <si>
-    <t>29.04.202619</t>
-  </si>
-  <si>
-    <t>29.04.202620</t>
-  </si>
-  <si>
-    <t>29.04.202621</t>
-  </si>
-  <si>
-    <t>29.04.202622</t>
-  </si>
-  <si>
-    <t>29.04.202623</t>
-  </si>
-  <si>
-    <t>29.04.202624</t>
-  </si>
-  <si>
-    <t>29.04.202625</t>
-  </si>
-  <si>
-    <t>29.04.202626</t>
-  </si>
-  <si>
-    <t>29.04.202627</t>
-  </si>
-  <si>
-    <t>29.04.202628</t>
-  </si>
-  <si>
-    <t>29.04.202629</t>
-  </si>
-  <si>
-    <t>29.04.202630</t>
-  </si>
-  <si>
-    <t>29.04.202631</t>
-  </si>
-  <si>
-    <t>29.04.202632</t>
-  </si>
-  <si>
-    <t>29.04.202633</t>
-  </si>
-  <si>
-    <t>29.04.202634</t>
-  </si>
-  <si>
-    <t>29.04.202635</t>
-  </si>
-  <si>
-    <t>29.04.202636</t>
-  </si>
-  <si>
-    <t>29.04.202637</t>
-  </si>
-  <si>
-    <t>29.04.202638</t>
-  </si>
-  <si>
-    <t>29.04.202639</t>
-  </si>
-  <si>
-    <t>29.04.202640</t>
-  </si>
-  <si>
-    <t>29.04.202641</t>
-  </si>
-  <si>
-    <t>29.04.202642</t>
-  </si>
-  <si>
-    <t>29.04.202643</t>
-  </si>
-  <si>
-    <t>29.04.202644</t>
-  </si>
-  <si>
-    <t>29.04.202645</t>
-  </si>
-  <si>
-    <t>29.04.202646</t>
-  </si>
-  <si>
-    <t>29.04.202647</t>
-  </si>
-  <si>
-    <t>29.04.202648</t>
-  </si>
-  <si>
-    <t>29.04.202649</t>
-  </si>
-  <si>
-    <t>29.04.202650</t>
-  </si>
-  <si>
-    <t>29.04.202651</t>
-  </si>
-  <si>
-    <t>29.04.202652</t>
-  </si>
-  <si>
-    <t>29.04.202653</t>
-  </si>
-  <si>
-    <t>29.04.202654</t>
-  </si>
-  <si>
-    <t>29.04.202655</t>
-  </si>
-  <si>
-    <t>29.04.202656</t>
-  </si>
-  <si>
-    <t>29.04.202657</t>
-  </si>
-  <si>
-    <t>29.04.202658</t>
-  </si>
-  <si>
-    <t>29.04.202659</t>
-  </si>
-  <si>
-    <t>29.04.202660</t>
-  </si>
-  <si>
-    <t>29.04.202661</t>
-  </si>
-  <si>
-    <t>29.04.202662</t>
-  </si>
-  <si>
-    <t>29.04.202663</t>
-  </si>
-  <si>
-    <t>29.04.202664</t>
-  </si>
-  <si>
-    <t>29.04.202665</t>
-  </si>
-  <si>
-    <t>29.04.202666</t>
-  </si>
-  <si>
-    <t>29.04.202667</t>
-  </si>
-  <si>
-    <t>29.04.202668</t>
-  </si>
-  <si>
-    <t>29.04.202669</t>
-  </si>
-  <si>
-    <t>29.04.202670</t>
-  </si>
-  <si>
-    <t>29.04.202671</t>
-  </si>
-  <si>
-    <t>29.04.202672</t>
-  </si>
-  <si>
-    <t>29.04.202673</t>
-  </si>
-  <si>
-    <t>29.04.202674</t>
-  </si>
-  <si>
-    <t>29.04.202675</t>
-  </si>
-  <si>
-    <t>29.04.202676</t>
-  </si>
-  <si>
-    <t>29.04.202677</t>
-  </si>
-  <si>
-    <t>29.04.202678</t>
-  </si>
-  <si>
-    <t>29.04.202679</t>
-  </si>
-  <si>
-    <t>29.04.202680</t>
-  </si>
-  <si>
-    <t>29.04.202681</t>
-  </si>
-  <si>
-    <t>29.04.202682</t>
-  </si>
-  <si>
-    <t>29.04.202683</t>
-  </si>
-  <si>
-    <t>29.04.202684</t>
-  </si>
-  <si>
-    <t>29.04.202685</t>
-  </si>
-  <si>
-    <t>29.04.202686</t>
-  </si>
-  <si>
-    <t>29.04.202687</t>
-  </si>
-  <si>
-    <t>29.04.202688</t>
-  </si>
-  <si>
-    <t>29.04.202689</t>
-  </si>
-  <si>
-    <t>29.04.202690</t>
-  </si>
-  <si>
-    <t>29.04.202691</t>
-  </si>
-  <si>
-    <t>29.04.202692</t>
-  </si>
-  <si>
-    <t>29.04.202693</t>
-  </si>
-  <si>
-    <t>29.04.202694</t>
-  </si>
-  <si>
-    <t>29.04.202695</t>
-  </si>
-  <si>
-    <t>29.04.202696</t>
-  </si>
-  <si>
     <t>30.04.20261</t>
   </si>
   <si>
@@ -893,6 +317,1158 @@
   </si>
   <si>
     <t>30.04.202696</t>
+  </si>
+  <si>
+    <t>01.05.20261</t>
+  </si>
+  <si>
+    <t>01.05.20262</t>
+  </si>
+  <si>
+    <t>01.05.20263</t>
+  </si>
+  <si>
+    <t>01.05.20264</t>
+  </si>
+  <si>
+    <t>01.05.20265</t>
+  </si>
+  <si>
+    <t>01.05.20266</t>
+  </si>
+  <si>
+    <t>01.05.20267</t>
+  </si>
+  <si>
+    <t>01.05.20268</t>
+  </si>
+  <si>
+    <t>01.05.20269</t>
+  </si>
+  <si>
+    <t>01.05.202610</t>
+  </si>
+  <si>
+    <t>01.05.202611</t>
+  </si>
+  <si>
+    <t>01.05.202612</t>
+  </si>
+  <si>
+    <t>01.05.202613</t>
+  </si>
+  <si>
+    <t>01.05.202614</t>
+  </si>
+  <si>
+    <t>01.05.202615</t>
+  </si>
+  <si>
+    <t>01.05.202616</t>
+  </si>
+  <si>
+    <t>01.05.202617</t>
+  </si>
+  <si>
+    <t>01.05.202618</t>
+  </si>
+  <si>
+    <t>01.05.202619</t>
+  </si>
+  <si>
+    <t>01.05.202620</t>
+  </si>
+  <si>
+    <t>01.05.202621</t>
+  </si>
+  <si>
+    <t>01.05.202622</t>
+  </si>
+  <si>
+    <t>01.05.202623</t>
+  </si>
+  <si>
+    <t>01.05.202624</t>
+  </si>
+  <si>
+    <t>01.05.202625</t>
+  </si>
+  <si>
+    <t>01.05.202626</t>
+  </si>
+  <si>
+    <t>01.05.202627</t>
+  </si>
+  <si>
+    <t>01.05.202628</t>
+  </si>
+  <si>
+    <t>01.05.202629</t>
+  </si>
+  <si>
+    <t>01.05.202630</t>
+  </si>
+  <si>
+    <t>01.05.202631</t>
+  </si>
+  <si>
+    <t>01.05.202632</t>
+  </si>
+  <si>
+    <t>01.05.202633</t>
+  </si>
+  <si>
+    <t>01.05.202634</t>
+  </si>
+  <si>
+    <t>01.05.202635</t>
+  </si>
+  <si>
+    <t>01.05.202636</t>
+  </si>
+  <si>
+    <t>01.05.202637</t>
+  </si>
+  <si>
+    <t>01.05.202638</t>
+  </si>
+  <si>
+    <t>01.05.202639</t>
+  </si>
+  <si>
+    <t>01.05.202640</t>
+  </si>
+  <si>
+    <t>01.05.202641</t>
+  </si>
+  <si>
+    <t>01.05.202642</t>
+  </si>
+  <si>
+    <t>01.05.202643</t>
+  </si>
+  <si>
+    <t>01.05.202644</t>
+  </si>
+  <si>
+    <t>01.05.202645</t>
+  </si>
+  <si>
+    <t>01.05.202646</t>
+  </si>
+  <si>
+    <t>01.05.202647</t>
+  </si>
+  <si>
+    <t>01.05.202648</t>
+  </si>
+  <si>
+    <t>01.05.202649</t>
+  </si>
+  <si>
+    <t>01.05.202650</t>
+  </si>
+  <si>
+    <t>01.05.202651</t>
+  </si>
+  <si>
+    <t>01.05.202652</t>
+  </si>
+  <si>
+    <t>01.05.202653</t>
+  </si>
+  <si>
+    <t>01.05.202654</t>
+  </si>
+  <si>
+    <t>01.05.202655</t>
+  </si>
+  <si>
+    <t>01.05.202656</t>
+  </si>
+  <si>
+    <t>01.05.202657</t>
+  </si>
+  <si>
+    <t>01.05.202658</t>
+  </si>
+  <si>
+    <t>01.05.202659</t>
+  </si>
+  <si>
+    <t>01.05.202660</t>
+  </si>
+  <si>
+    <t>01.05.202661</t>
+  </si>
+  <si>
+    <t>01.05.202662</t>
+  </si>
+  <si>
+    <t>01.05.202663</t>
+  </si>
+  <si>
+    <t>01.05.202664</t>
+  </si>
+  <si>
+    <t>01.05.202665</t>
+  </si>
+  <si>
+    <t>01.05.202666</t>
+  </si>
+  <si>
+    <t>01.05.202667</t>
+  </si>
+  <si>
+    <t>01.05.202668</t>
+  </si>
+  <si>
+    <t>01.05.202669</t>
+  </si>
+  <si>
+    <t>01.05.202670</t>
+  </si>
+  <si>
+    <t>01.05.202671</t>
+  </si>
+  <si>
+    <t>01.05.202672</t>
+  </si>
+  <si>
+    <t>01.05.202673</t>
+  </si>
+  <si>
+    <t>01.05.202674</t>
+  </si>
+  <si>
+    <t>01.05.202675</t>
+  </si>
+  <si>
+    <t>01.05.202676</t>
+  </si>
+  <si>
+    <t>01.05.202677</t>
+  </si>
+  <si>
+    <t>01.05.202678</t>
+  </si>
+  <si>
+    <t>01.05.202679</t>
+  </si>
+  <si>
+    <t>01.05.202680</t>
+  </si>
+  <si>
+    <t>01.05.202681</t>
+  </si>
+  <si>
+    <t>01.05.202682</t>
+  </si>
+  <si>
+    <t>01.05.202683</t>
+  </si>
+  <si>
+    <t>01.05.202684</t>
+  </si>
+  <si>
+    <t>01.05.202685</t>
+  </si>
+  <si>
+    <t>01.05.202686</t>
+  </si>
+  <si>
+    <t>01.05.202687</t>
+  </si>
+  <si>
+    <t>01.05.202688</t>
+  </si>
+  <si>
+    <t>01.05.202689</t>
+  </si>
+  <si>
+    <t>01.05.202690</t>
+  </si>
+  <si>
+    <t>01.05.202691</t>
+  </si>
+  <si>
+    <t>01.05.202692</t>
+  </si>
+  <si>
+    <t>01.05.202693</t>
+  </si>
+  <si>
+    <t>01.05.202694</t>
+  </si>
+  <si>
+    <t>01.05.202695</t>
+  </si>
+  <si>
+    <t>01.05.202696</t>
+  </si>
+  <si>
+    <t>02.05.20261</t>
+  </si>
+  <si>
+    <t>02.05.20262</t>
+  </si>
+  <si>
+    <t>02.05.20263</t>
+  </si>
+  <si>
+    <t>02.05.20264</t>
+  </si>
+  <si>
+    <t>02.05.20265</t>
+  </si>
+  <si>
+    <t>02.05.20266</t>
+  </si>
+  <si>
+    <t>02.05.20267</t>
+  </si>
+  <si>
+    <t>02.05.20268</t>
+  </si>
+  <si>
+    <t>02.05.20269</t>
+  </si>
+  <si>
+    <t>02.05.202610</t>
+  </si>
+  <si>
+    <t>02.05.202611</t>
+  </si>
+  <si>
+    <t>02.05.202612</t>
+  </si>
+  <si>
+    <t>02.05.202613</t>
+  </si>
+  <si>
+    <t>02.05.202614</t>
+  </si>
+  <si>
+    <t>02.05.202615</t>
+  </si>
+  <si>
+    <t>02.05.202616</t>
+  </si>
+  <si>
+    <t>02.05.202617</t>
+  </si>
+  <si>
+    <t>02.05.202618</t>
+  </si>
+  <si>
+    <t>02.05.202619</t>
+  </si>
+  <si>
+    <t>02.05.202620</t>
+  </si>
+  <si>
+    <t>02.05.202621</t>
+  </si>
+  <si>
+    <t>02.05.202622</t>
+  </si>
+  <si>
+    <t>02.05.202623</t>
+  </si>
+  <si>
+    <t>02.05.202624</t>
+  </si>
+  <si>
+    <t>02.05.202625</t>
+  </si>
+  <si>
+    <t>02.05.202626</t>
+  </si>
+  <si>
+    <t>02.05.202627</t>
+  </si>
+  <si>
+    <t>02.05.202628</t>
+  </si>
+  <si>
+    <t>02.05.202629</t>
+  </si>
+  <si>
+    <t>02.05.202630</t>
+  </si>
+  <si>
+    <t>02.05.202631</t>
+  </si>
+  <si>
+    <t>02.05.202632</t>
+  </si>
+  <si>
+    <t>02.05.202633</t>
+  </si>
+  <si>
+    <t>02.05.202634</t>
+  </si>
+  <si>
+    <t>02.05.202635</t>
+  </si>
+  <si>
+    <t>02.05.202636</t>
+  </si>
+  <si>
+    <t>02.05.202637</t>
+  </si>
+  <si>
+    <t>02.05.202638</t>
+  </si>
+  <si>
+    <t>02.05.202639</t>
+  </si>
+  <si>
+    <t>02.05.202640</t>
+  </si>
+  <si>
+    <t>02.05.202641</t>
+  </si>
+  <si>
+    <t>02.05.202642</t>
+  </si>
+  <si>
+    <t>02.05.202643</t>
+  </si>
+  <si>
+    <t>02.05.202644</t>
+  </si>
+  <si>
+    <t>02.05.202645</t>
+  </si>
+  <si>
+    <t>02.05.202646</t>
+  </si>
+  <si>
+    <t>02.05.202647</t>
+  </si>
+  <si>
+    <t>02.05.202648</t>
+  </si>
+  <si>
+    <t>02.05.202649</t>
+  </si>
+  <si>
+    <t>02.05.202650</t>
+  </si>
+  <si>
+    <t>02.05.202651</t>
+  </si>
+  <si>
+    <t>02.05.202652</t>
+  </si>
+  <si>
+    <t>02.05.202653</t>
+  </si>
+  <si>
+    <t>02.05.202654</t>
+  </si>
+  <si>
+    <t>02.05.202655</t>
+  </si>
+  <si>
+    <t>02.05.202656</t>
+  </si>
+  <si>
+    <t>02.05.202657</t>
+  </si>
+  <si>
+    <t>02.05.202658</t>
+  </si>
+  <si>
+    <t>02.05.202659</t>
+  </si>
+  <si>
+    <t>02.05.202660</t>
+  </si>
+  <si>
+    <t>02.05.202661</t>
+  </si>
+  <si>
+    <t>02.05.202662</t>
+  </si>
+  <si>
+    <t>02.05.202663</t>
+  </si>
+  <si>
+    <t>02.05.202664</t>
+  </si>
+  <si>
+    <t>02.05.202665</t>
+  </si>
+  <si>
+    <t>02.05.202666</t>
+  </si>
+  <si>
+    <t>02.05.202667</t>
+  </si>
+  <si>
+    <t>02.05.202668</t>
+  </si>
+  <si>
+    <t>02.05.202669</t>
+  </si>
+  <si>
+    <t>02.05.202670</t>
+  </si>
+  <si>
+    <t>02.05.202671</t>
+  </si>
+  <si>
+    <t>02.05.202672</t>
+  </si>
+  <si>
+    <t>02.05.202673</t>
+  </si>
+  <si>
+    <t>02.05.202674</t>
+  </si>
+  <si>
+    <t>02.05.202675</t>
+  </si>
+  <si>
+    <t>02.05.202676</t>
+  </si>
+  <si>
+    <t>02.05.202677</t>
+  </si>
+  <si>
+    <t>02.05.202678</t>
+  </si>
+  <si>
+    <t>02.05.202679</t>
+  </si>
+  <si>
+    <t>02.05.202680</t>
+  </si>
+  <si>
+    <t>02.05.202681</t>
+  </si>
+  <si>
+    <t>02.05.202682</t>
+  </si>
+  <si>
+    <t>02.05.202683</t>
+  </si>
+  <si>
+    <t>02.05.202684</t>
+  </si>
+  <si>
+    <t>02.05.202685</t>
+  </si>
+  <si>
+    <t>02.05.202686</t>
+  </si>
+  <si>
+    <t>02.05.202687</t>
+  </si>
+  <si>
+    <t>02.05.202688</t>
+  </si>
+  <si>
+    <t>02.05.202689</t>
+  </si>
+  <si>
+    <t>02.05.202690</t>
+  </si>
+  <si>
+    <t>02.05.202691</t>
+  </si>
+  <si>
+    <t>02.05.202692</t>
+  </si>
+  <si>
+    <t>02.05.202693</t>
+  </si>
+  <si>
+    <t>02.05.202694</t>
+  </si>
+  <si>
+    <t>02.05.202695</t>
+  </si>
+  <si>
+    <t>02.05.202696</t>
+  </si>
+  <si>
+    <t>03.05.20261</t>
+  </si>
+  <si>
+    <t>03.05.20262</t>
+  </si>
+  <si>
+    <t>03.05.20263</t>
+  </si>
+  <si>
+    <t>03.05.20264</t>
+  </si>
+  <si>
+    <t>03.05.20265</t>
+  </si>
+  <si>
+    <t>03.05.20266</t>
+  </si>
+  <si>
+    <t>03.05.20267</t>
+  </si>
+  <si>
+    <t>03.05.20268</t>
+  </si>
+  <si>
+    <t>03.05.20269</t>
+  </si>
+  <si>
+    <t>03.05.202610</t>
+  </si>
+  <si>
+    <t>03.05.202611</t>
+  </si>
+  <si>
+    <t>03.05.202612</t>
+  </si>
+  <si>
+    <t>03.05.202613</t>
+  </si>
+  <si>
+    <t>03.05.202614</t>
+  </si>
+  <si>
+    <t>03.05.202615</t>
+  </si>
+  <si>
+    <t>03.05.202616</t>
+  </si>
+  <si>
+    <t>03.05.202617</t>
+  </si>
+  <si>
+    <t>03.05.202618</t>
+  </si>
+  <si>
+    <t>03.05.202619</t>
+  </si>
+  <si>
+    <t>03.05.202620</t>
+  </si>
+  <si>
+    <t>03.05.202621</t>
+  </si>
+  <si>
+    <t>03.05.202622</t>
+  </si>
+  <si>
+    <t>03.05.202623</t>
+  </si>
+  <si>
+    <t>03.05.202624</t>
+  </si>
+  <si>
+    <t>03.05.202625</t>
+  </si>
+  <si>
+    <t>03.05.202626</t>
+  </si>
+  <si>
+    <t>03.05.202627</t>
+  </si>
+  <si>
+    <t>03.05.202628</t>
+  </si>
+  <si>
+    <t>03.05.202629</t>
+  </si>
+  <si>
+    <t>03.05.202630</t>
+  </si>
+  <si>
+    <t>03.05.202631</t>
+  </si>
+  <si>
+    <t>03.05.202632</t>
+  </si>
+  <si>
+    <t>03.05.202633</t>
+  </si>
+  <si>
+    <t>03.05.202634</t>
+  </si>
+  <si>
+    <t>03.05.202635</t>
+  </si>
+  <si>
+    <t>03.05.202636</t>
+  </si>
+  <si>
+    <t>03.05.202637</t>
+  </si>
+  <si>
+    <t>03.05.202638</t>
+  </si>
+  <si>
+    <t>03.05.202639</t>
+  </si>
+  <si>
+    <t>03.05.202640</t>
+  </si>
+  <si>
+    <t>03.05.202641</t>
+  </si>
+  <si>
+    <t>03.05.202642</t>
+  </si>
+  <si>
+    <t>03.05.202643</t>
+  </si>
+  <si>
+    <t>03.05.202644</t>
+  </si>
+  <si>
+    <t>03.05.202645</t>
+  </si>
+  <si>
+    <t>03.05.202646</t>
+  </si>
+  <si>
+    <t>03.05.202647</t>
+  </si>
+  <si>
+    <t>03.05.202648</t>
+  </si>
+  <si>
+    <t>03.05.202649</t>
+  </si>
+  <si>
+    <t>03.05.202650</t>
+  </si>
+  <si>
+    <t>03.05.202651</t>
+  </si>
+  <si>
+    <t>03.05.202652</t>
+  </si>
+  <si>
+    <t>03.05.202653</t>
+  </si>
+  <si>
+    <t>03.05.202654</t>
+  </si>
+  <si>
+    <t>03.05.202655</t>
+  </si>
+  <si>
+    <t>03.05.202656</t>
+  </si>
+  <si>
+    <t>03.05.202657</t>
+  </si>
+  <si>
+    <t>03.05.202658</t>
+  </si>
+  <si>
+    <t>03.05.202659</t>
+  </si>
+  <si>
+    <t>03.05.202660</t>
+  </si>
+  <si>
+    <t>03.05.202661</t>
+  </si>
+  <si>
+    <t>03.05.202662</t>
+  </si>
+  <si>
+    <t>03.05.202663</t>
+  </si>
+  <si>
+    <t>03.05.202664</t>
+  </si>
+  <si>
+    <t>03.05.202665</t>
+  </si>
+  <si>
+    <t>03.05.202666</t>
+  </si>
+  <si>
+    <t>03.05.202667</t>
+  </si>
+  <si>
+    <t>03.05.202668</t>
+  </si>
+  <si>
+    <t>03.05.202669</t>
+  </si>
+  <si>
+    <t>03.05.202670</t>
+  </si>
+  <si>
+    <t>03.05.202671</t>
+  </si>
+  <si>
+    <t>03.05.202672</t>
+  </si>
+  <si>
+    <t>03.05.202673</t>
+  </si>
+  <si>
+    <t>03.05.202674</t>
+  </si>
+  <si>
+    <t>03.05.202675</t>
+  </si>
+  <si>
+    <t>03.05.202676</t>
+  </si>
+  <si>
+    <t>03.05.202677</t>
+  </si>
+  <si>
+    <t>03.05.202678</t>
+  </si>
+  <si>
+    <t>03.05.202679</t>
+  </si>
+  <si>
+    <t>03.05.202680</t>
+  </si>
+  <si>
+    <t>03.05.202681</t>
+  </si>
+  <si>
+    <t>03.05.202682</t>
+  </si>
+  <si>
+    <t>03.05.202683</t>
+  </si>
+  <si>
+    <t>03.05.202684</t>
+  </si>
+  <si>
+    <t>03.05.202685</t>
+  </si>
+  <si>
+    <t>03.05.202686</t>
+  </si>
+  <si>
+    <t>03.05.202687</t>
+  </si>
+  <si>
+    <t>03.05.202688</t>
+  </si>
+  <si>
+    <t>03.05.202689</t>
+  </si>
+  <si>
+    <t>03.05.202690</t>
+  </si>
+  <si>
+    <t>03.05.202691</t>
+  </si>
+  <si>
+    <t>03.05.202692</t>
+  </si>
+  <si>
+    <t>03.05.202693</t>
+  </si>
+  <si>
+    <t>03.05.202694</t>
+  </si>
+  <si>
+    <t>03.05.202695</t>
+  </si>
+  <si>
+    <t>03.05.202696</t>
+  </si>
+  <si>
+    <t>04.05.20261</t>
+  </si>
+  <si>
+    <t>04.05.20262</t>
+  </si>
+  <si>
+    <t>04.05.20263</t>
+  </si>
+  <si>
+    <t>04.05.20264</t>
+  </si>
+  <si>
+    <t>04.05.20265</t>
+  </si>
+  <si>
+    <t>04.05.20266</t>
+  </si>
+  <si>
+    <t>04.05.20267</t>
+  </si>
+  <si>
+    <t>04.05.20268</t>
+  </si>
+  <si>
+    <t>04.05.20269</t>
+  </si>
+  <si>
+    <t>04.05.202610</t>
+  </si>
+  <si>
+    <t>04.05.202611</t>
+  </si>
+  <si>
+    <t>04.05.202612</t>
+  </si>
+  <si>
+    <t>04.05.202613</t>
+  </si>
+  <si>
+    <t>04.05.202614</t>
+  </si>
+  <si>
+    <t>04.05.202615</t>
+  </si>
+  <si>
+    <t>04.05.202616</t>
+  </si>
+  <si>
+    <t>04.05.202617</t>
+  </si>
+  <si>
+    <t>04.05.202618</t>
+  </si>
+  <si>
+    <t>04.05.202619</t>
+  </si>
+  <si>
+    <t>04.05.202620</t>
+  </si>
+  <si>
+    <t>04.05.202621</t>
+  </si>
+  <si>
+    <t>04.05.202622</t>
+  </si>
+  <si>
+    <t>04.05.202623</t>
+  </si>
+  <si>
+    <t>04.05.202624</t>
+  </si>
+  <si>
+    <t>04.05.202625</t>
+  </si>
+  <si>
+    <t>04.05.202626</t>
+  </si>
+  <si>
+    <t>04.05.202627</t>
+  </si>
+  <si>
+    <t>04.05.202628</t>
+  </si>
+  <si>
+    <t>04.05.202629</t>
+  </si>
+  <si>
+    <t>04.05.202630</t>
+  </si>
+  <si>
+    <t>04.05.202631</t>
+  </si>
+  <si>
+    <t>04.05.202632</t>
+  </si>
+  <si>
+    <t>04.05.202633</t>
+  </si>
+  <si>
+    <t>04.05.202634</t>
+  </si>
+  <si>
+    <t>04.05.202635</t>
+  </si>
+  <si>
+    <t>04.05.202636</t>
+  </si>
+  <si>
+    <t>04.05.202637</t>
+  </si>
+  <si>
+    <t>04.05.202638</t>
+  </si>
+  <si>
+    <t>04.05.202639</t>
+  </si>
+  <si>
+    <t>04.05.202640</t>
+  </si>
+  <si>
+    <t>04.05.202641</t>
+  </si>
+  <si>
+    <t>04.05.202642</t>
+  </si>
+  <si>
+    <t>04.05.202643</t>
+  </si>
+  <si>
+    <t>04.05.202644</t>
+  </si>
+  <si>
+    <t>04.05.202645</t>
+  </si>
+  <si>
+    <t>04.05.202646</t>
+  </si>
+  <si>
+    <t>04.05.202647</t>
+  </si>
+  <si>
+    <t>04.05.202648</t>
+  </si>
+  <si>
+    <t>04.05.202649</t>
+  </si>
+  <si>
+    <t>04.05.202650</t>
+  </si>
+  <si>
+    <t>04.05.202651</t>
+  </si>
+  <si>
+    <t>04.05.202652</t>
+  </si>
+  <si>
+    <t>04.05.202653</t>
+  </si>
+  <si>
+    <t>04.05.202654</t>
+  </si>
+  <si>
+    <t>04.05.202655</t>
+  </si>
+  <si>
+    <t>04.05.202656</t>
+  </si>
+  <si>
+    <t>04.05.202657</t>
+  </si>
+  <si>
+    <t>04.05.202658</t>
+  </si>
+  <si>
+    <t>04.05.202659</t>
+  </si>
+  <si>
+    <t>04.05.202660</t>
+  </si>
+  <si>
+    <t>04.05.202661</t>
+  </si>
+  <si>
+    <t>04.05.202662</t>
+  </si>
+  <si>
+    <t>04.05.202663</t>
+  </si>
+  <si>
+    <t>04.05.202664</t>
+  </si>
+  <si>
+    <t>04.05.202665</t>
+  </si>
+  <si>
+    <t>04.05.202666</t>
+  </si>
+  <si>
+    <t>04.05.202667</t>
+  </si>
+  <si>
+    <t>04.05.202668</t>
+  </si>
+  <si>
+    <t>04.05.202669</t>
+  </si>
+  <si>
+    <t>04.05.202670</t>
+  </si>
+  <si>
+    <t>04.05.202671</t>
+  </si>
+  <si>
+    <t>04.05.202672</t>
+  </si>
+  <si>
+    <t>04.05.202673</t>
+  </si>
+  <si>
+    <t>04.05.202674</t>
+  </si>
+  <si>
+    <t>04.05.202675</t>
+  </si>
+  <si>
+    <t>04.05.202676</t>
+  </si>
+  <si>
+    <t>04.05.202677</t>
+  </si>
+  <si>
+    <t>04.05.202678</t>
+  </si>
+  <si>
+    <t>04.05.202679</t>
+  </si>
+  <si>
+    <t>04.05.202680</t>
+  </si>
+  <si>
+    <t>04.05.202681</t>
+  </si>
+  <si>
+    <t>04.05.202682</t>
+  </si>
+  <si>
+    <t>04.05.202683</t>
+  </si>
+  <si>
+    <t>04.05.202684</t>
+  </si>
+  <si>
+    <t>04.05.202685</t>
+  </si>
+  <si>
+    <t>04.05.202686</t>
+  </si>
+  <si>
+    <t>04.05.202687</t>
+  </si>
+  <si>
+    <t>04.05.202688</t>
+  </si>
+  <si>
+    <t>04.05.202689</t>
+  </si>
+  <si>
+    <t>04.05.202690</t>
+  </si>
+  <si>
+    <t>04.05.202691</t>
+  </si>
+  <si>
+    <t>04.05.202692</t>
+  </si>
+  <si>
+    <t>04.05.202693</t>
+  </si>
+  <si>
+    <t>04.05.202694</t>
+  </si>
+  <si>
+    <t>04.05.202695</t>
+  </si>
+  <si>
+    <t>04.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E289"/>
+  <dimension ref="A1:E481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1276,7 +1852,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -1293,7 +1869,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46140.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1310,7 +1886,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46140.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1327,10 +1903,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46140.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B5">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1344,7 +1920,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46140.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1361,7 +1937,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46140.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1378,7 +1954,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46140.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1395,7 +1971,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46140.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1412,7 +1988,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46140.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1429,7 +2005,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46140.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1446,7 +2022,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46140.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1463,7 +2039,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46140.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1480,7 +2056,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46140.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1497,7 +2073,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46140.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1514,7 +2090,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46140.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1531,7 +2107,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46140.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1548,10 +2124,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46140.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B18">
-        <v>22.01</v>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1565,7 +2141,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46140.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1582,10 +2158,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46140.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>0.747</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1599,10 +2175,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46140.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B21">
-        <v>22.034</v>
+        <v>0.779</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1616,10 +2192,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46140.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B22">
-        <v>75.251</v>
+        <v>1.371</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1633,13 +2209,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46140.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B23">
-        <v>80.616</v>
+        <v>4.827</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1650,13 +2226,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46140.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B24">
-        <v>110.354</v>
+        <v>14.981</v>
       </c>
       <c r="C24">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1667,13 +2243,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46140.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B25">
-        <v>147.313</v>
+        <v>31.343</v>
       </c>
       <c r="C25">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1684,13 +2260,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46140.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B26">
-        <v>315.602</v>
+        <v>110.775</v>
       </c>
       <c r="C26">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1701,13 +2277,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46140.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B27">
-        <v>419.067</v>
+        <v>156.833</v>
       </c>
       <c r="C27">
-        <v>282</v>
+        <v>67</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1718,13 +2294,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46140.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B28">
-        <v>548.071</v>
+        <v>202.328</v>
       </c>
       <c r="C28">
-        <v>418</v>
+        <v>97</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1735,13 +2311,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46140.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B29">
-        <v>703.403</v>
+        <v>260.181</v>
       </c>
       <c r="C29">
-        <v>564</v>
+        <v>136</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1752,13 +2328,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46140.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B30">
-        <v>1020.552</v>
+        <v>351.994</v>
       </c>
       <c r="C30">
-        <v>786</v>
+        <v>178</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1769,13 +2345,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46140.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B31">
-        <v>1203.034</v>
+        <v>420.295</v>
       </c>
       <c r="C31">
-        <v>956</v>
+        <v>234</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1786,13 +2362,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46140.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B32">
-        <v>1409.283</v>
+        <v>499.001</v>
       </c>
       <c r="C32">
-        <v>1136</v>
+        <v>303</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1803,13 +2379,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46140.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B33">
-        <v>1630.29</v>
+        <v>571.061</v>
       </c>
       <c r="C33">
-        <v>1339</v>
+        <v>369</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1820,13 +2396,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46140.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B34">
-        <v>1949.604</v>
+        <v>669.073</v>
       </c>
       <c r="C34">
-        <v>1471</v>
+        <v>430</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1837,13 +2413,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46140.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B35">
-        <v>2141.299</v>
+        <v>728.499</v>
       </c>
       <c r="C35">
-        <v>1644</v>
+        <v>515</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1854,13 +2430,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46140.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B36">
-        <v>2324.015</v>
+        <v>812.227</v>
       </c>
       <c r="C36">
-        <v>1746</v>
+        <v>568</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1871,13 +2447,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46140.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B37">
-        <v>2500.263</v>
+        <v>890.375</v>
       </c>
       <c r="C37">
-        <v>1851</v>
+        <v>641</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1888,13 +2464,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46140.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B38">
-        <v>2713.739</v>
+        <v>991.02</v>
       </c>
       <c r="C38">
-        <v>1950</v>
+        <v>732</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1905,13 +2481,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46140.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B39">
-        <v>2829.575</v>
+        <v>1060.596</v>
       </c>
       <c r="C39">
-        <v>2012</v>
+        <v>801</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1922,13 +2498,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46140.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B40">
-        <v>2927.652</v>
+        <v>1126.624</v>
       </c>
       <c r="C40">
-        <v>2140</v>
+        <v>818</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1939,13 +2515,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46140.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B41">
-        <v>3023.953</v>
+        <v>1139.684</v>
       </c>
       <c r="C41">
-        <v>2218</v>
+        <v>789</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1956,13 +2532,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46140.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B42">
-        <v>3119.685</v>
+        <v>1265.215</v>
       </c>
       <c r="C42">
-        <v>2286</v>
+        <v>858</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1973,13 +2549,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46140.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B43">
-        <v>3192.844</v>
+        <v>1273.377</v>
       </c>
       <c r="C43">
-        <v>2329</v>
+        <v>841</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1990,13 +2566,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46140.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B44">
-        <v>3231.801</v>
+        <v>1329.612</v>
       </c>
       <c r="C44">
-        <v>2308</v>
+        <v>853</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -2007,13 +2583,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46140.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B45">
-        <v>3105.175</v>
+        <v>1373.685</v>
       </c>
       <c r="C45">
-        <v>2261</v>
+        <v>950</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -2024,13 +2600,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46140.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B46">
-        <v>3066.433</v>
+        <v>1410.317</v>
       </c>
       <c r="C46">
-        <v>2178</v>
+        <v>987</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2041,13 +2617,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46140.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B47">
-        <v>3085.051</v>
+        <v>1433.672</v>
       </c>
       <c r="C47">
-        <v>2133</v>
+        <v>1056</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2058,13 +2634,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46140.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B48">
-        <v>3100.987</v>
+        <v>1454.381</v>
       </c>
       <c r="C48">
-        <v>2139</v>
+        <v>1047</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2075,13 +2651,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46140.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B49">
-        <v>3098.989</v>
+        <v>1472.87</v>
       </c>
       <c r="C49">
-        <v>2159</v>
+        <v>1049</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2092,13 +2668,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46140.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B50">
-        <v>3082.926</v>
+        <v>1513.705</v>
       </c>
       <c r="C50">
-        <v>2211</v>
+        <v>1050</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2109,13 +2685,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46140.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B51">
-        <v>3071.039</v>
+        <v>1526.324</v>
       </c>
       <c r="C51">
-        <v>2188</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2126,13 +2702,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46140.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B52">
-        <v>3048.628</v>
+        <v>1490.692</v>
       </c>
       <c r="C52">
-        <v>2127</v>
+        <v>1046</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2143,13 +2719,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46140.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B53">
-        <v>3024.525</v>
+        <v>1496.842</v>
       </c>
       <c r="C53">
-        <v>2101</v>
+        <v>1043</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2160,13 +2736,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46140.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B54">
-        <v>2917.154</v>
+        <v>1527.108</v>
       </c>
       <c r="C54">
-        <v>2097</v>
+        <v>991</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2177,13 +2753,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46140.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B55">
-        <v>2853.964</v>
+        <v>1526.442</v>
       </c>
       <c r="C55">
-        <v>2009</v>
+        <v>993</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2194,13 +2770,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46140.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B56">
-        <v>2713.949</v>
+        <v>1510.656</v>
       </c>
       <c r="C56">
-        <v>1972</v>
+        <v>995</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2211,13 +2787,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46140.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B57">
-        <v>2705.297</v>
+        <v>1524.884</v>
       </c>
       <c r="C57">
-        <v>1875</v>
+        <v>918</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2228,13 +2804,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46140.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B58">
-        <v>2686.374</v>
+        <v>1477.674</v>
       </c>
       <c r="C58">
-        <v>1938</v>
+        <v>908</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2245,13 +2821,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46140.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B59">
-        <v>2608.302</v>
+        <v>1469.93</v>
       </c>
       <c r="C59">
-        <v>1899</v>
+        <v>958</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2262,13 +2838,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46140.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B60">
-        <v>2518.48</v>
+        <v>1491.82</v>
       </c>
       <c r="C60">
-        <v>1877</v>
+        <v>950</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2279,13 +2855,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46140.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B61">
-        <v>2427.629</v>
+        <v>1408.701</v>
       </c>
       <c r="C61">
-        <v>1803</v>
+        <v>893</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2296,13 +2872,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46140.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B62">
-        <v>2299.592</v>
+        <v>1339.777</v>
       </c>
       <c r="C62">
-        <v>1787</v>
+        <v>849</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2313,13 +2889,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46140.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B63">
-        <v>2185.593</v>
+        <v>1303.075</v>
       </c>
       <c r="C63">
-        <v>1730</v>
+        <v>762</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2330,13 +2906,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46140.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B64">
-        <v>2088.134</v>
+        <v>1260.499</v>
       </c>
       <c r="C64">
-        <v>1606</v>
+        <v>738</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2347,13 +2923,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46140.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B65">
-        <v>1969.843</v>
+        <v>1220.323</v>
       </c>
       <c r="C65">
-        <v>1589</v>
+        <v>730</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2364,13 +2940,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46140.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B66">
-        <v>1789.688</v>
+        <v>1092.93</v>
       </c>
       <c r="C66">
-        <v>1411</v>
+        <v>631</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2381,13 +2957,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46140.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B67">
-        <v>1634.848</v>
+        <v>1030.117</v>
       </c>
       <c r="C67">
-        <v>1258</v>
+        <v>629</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2398,13 +2974,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46140.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B68">
-        <v>1600.075</v>
+        <v>953.944</v>
       </c>
       <c r="C68">
-        <v>1238</v>
+        <v>582</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2415,13 +2991,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46140.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B69">
-        <v>1416.817</v>
+        <v>869.2809999999999</v>
       </c>
       <c r="C69">
-        <v>1164</v>
+        <v>526</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2432,13 +3008,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46140.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B70">
-        <v>1144.559</v>
+        <v>708.288</v>
       </c>
       <c r="C70">
-        <v>964</v>
+        <v>488</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2449,13 +3025,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46140.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B71">
-        <v>974.2569999999999</v>
+        <v>624.579</v>
       </c>
       <c r="C71">
-        <v>807</v>
+        <v>432</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2466,13 +3042,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46140.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B72">
-        <v>823.393</v>
+        <v>538.212</v>
       </c>
       <c r="C72">
-        <v>632</v>
+        <v>404</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2483,13 +3059,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46140.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B73">
-        <v>678.311</v>
+        <v>458.013</v>
       </c>
       <c r="C73">
-        <v>478</v>
+        <v>313</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2500,13 +3076,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46140.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B74">
-        <v>495.367</v>
+        <v>328.63</v>
       </c>
       <c r="C74">
-        <v>341</v>
+        <v>214</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2517,13 +3093,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46140.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B75">
-        <v>381.48</v>
+        <v>261.095</v>
       </c>
       <c r="C75">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2534,13 +3110,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46140.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B76">
-        <v>201.744</v>
+        <v>164.975</v>
       </c>
       <c r="C76">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2551,13 +3127,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46140.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B77">
-        <v>139.57</v>
+        <v>97.503</v>
       </c>
       <c r="C77">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2568,13 +3144,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46140.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B78">
-        <v>65.65600000000001</v>
+        <v>42.661</v>
       </c>
       <c r="C78">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2585,10 +3161,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46140.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B79">
-        <v>41.446</v>
+        <v>34.753</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2602,10 +3178,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46140.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B80">
-        <v>34.688</v>
+        <v>24.809</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2619,10 +3195,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46140.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B81">
-        <v>26.504</v>
+        <v>19.274</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2636,10 +3212,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46140.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B82">
-        <v>15.737</v>
+        <v>15.778</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2653,10 +3229,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46140.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B83">
-        <v>14.033</v>
+        <v>15.667</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2670,10 +3246,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46140.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B84">
-        <v>11.737</v>
+        <v>15.271</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2687,10 +3263,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46140.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B85">
-        <v>10.128</v>
+        <v>13.081</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2704,10 +3280,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46140.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B86">
-        <v>4.599</v>
+        <v>13.33</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2721,10 +3297,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46140.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B87">
-        <v>4.15</v>
+        <v>13.03</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2738,10 +3314,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46140.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B88">
-        <v>2.13</v>
+        <v>10.33</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2755,10 +3331,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46140.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B89">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2772,10 +3348,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46140.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2789,10 +3365,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46140.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2806,7 +3382,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46140.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2823,7 +3399,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46140.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2840,10 +3416,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46140.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2857,7 +3433,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46140.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2874,7 +3450,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46140.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2891,7 +3467,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46140.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2908,7 +3484,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2925,7 +3501,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46141.01041666666</v>
+        <v>46143.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2942,13 +3518,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46141.02083333334</v>
+        <v>46143.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2959,7 +3535,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46141.03125</v>
+        <v>46143.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2976,13 +3552,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46141.04166666666</v>
+        <v>46143.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2993,7 +3569,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46141.05208333334</v>
+        <v>46143.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3010,7 +3586,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46141.0625</v>
+        <v>46143.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3027,7 +3603,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46141.07291666666</v>
+        <v>46143.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3044,13 +3620,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46141.08333333334</v>
+        <v>46143.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -3061,7 +3637,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46141.09375</v>
+        <v>46143.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3078,7 +3654,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46141.10416666666</v>
+        <v>46143.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3095,13 +3671,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46141.11458333334</v>
+        <v>46143.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -3112,13 +3688,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46141.125</v>
+        <v>46143.125</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -3129,7 +3705,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46141.13541666666</v>
+        <v>46143.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3146,13 +3722,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46141.14583333334</v>
+        <v>46143.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -3163,13 +3739,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46141.15625</v>
+        <v>46143.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -3180,13 +3756,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46141.16666666666</v>
+        <v>46143.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
       </c>
       <c r="C114">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -3197,13 +3773,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46141.17708333334</v>
+        <v>46143.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>0.734</v>
       </c>
       <c r="C115">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -3214,13 +3790,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46141.1875</v>
+        <v>46143.1875</v>
       </c>
       <c r="B116">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -3231,13 +3807,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46141.19791666666</v>
+        <v>46143.19791666666</v>
       </c>
       <c r="B117">
-        <v>0.756</v>
+        <v>0.862</v>
       </c>
       <c r="C117">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3248,10 +3824,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46141.20833333334</v>
+        <v>46143.20833333334</v>
       </c>
       <c r="B118">
-        <v>11.045</v>
+        <v>4.54</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -3265,13 +3841,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46141.21875</v>
+        <v>46143.21875</v>
       </c>
       <c r="B119">
-        <v>15.682</v>
+        <v>17.905</v>
       </c>
       <c r="C119">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3282,13 +3858,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46141.22916666666</v>
+        <v>46143.22916666666</v>
       </c>
       <c r="B120">
-        <v>32.722</v>
+        <v>46.876</v>
       </c>
       <c r="C120">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3299,13 +3875,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46141.23958333334</v>
+        <v>46143.23958333334</v>
       </c>
       <c r="B121">
-        <v>61.025</v>
+        <v>96.372</v>
       </c>
       <c r="C121">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3316,13 +3892,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46141.25</v>
+        <v>46143.25</v>
       </c>
       <c r="B122">
-        <v>130.402</v>
+        <v>203.955</v>
       </c>
       <c r="C122">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3333,13 +3909,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46141.26041666666</v>
+        <v>46143.26041666666</v>
       </c>
       <c r="B123">
-        <v>193.994</v>
+        <v>302.544</v>
       </c>
       <c r="C123">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3350,13 +3926,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46141.27083333334</v>
+        <v>46143.27083333334</v>
       </c>
       <c r="B124">
-        <v>267.392</v>
+        <v>412.13</v>
       </c>
       <c r="C124">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3367,13 +3943,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46141.28125</v>
+        <v>46143.28125</v>
       </c>
       <c r="B125">
-        <v>353.411</v>
+        <v>546.081</v>
       </c>
       <c r="C125">
-        <v>419</v>
+        <v>477</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3384,13 +3960,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46141.29166666666</v>
+        <v>46143.29166666666</v>
       </c>
       <c r="B126">
-        <v>524.915</v>
+        <v>789.169</v>
       </c>
       <c r="C126">
-        <v>529</v>
+        <v>634</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3401,13 +3977,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46141.30208333334</v>
+        <v>46143.30208333334</v>
       </c>
       <c r="B127">
-        <v>632.053</v>
+        <v>942.745</v>
       </c>
       <c r="C127">
-        <v>603</v>
+        <v>741</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3418,13 +3994,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46141.3125</v>
+        <v>46143.3125</v>
       </c>
       <c r="B128">
-        <v>743.644</v>
+        <v>1104.558</v>
       </c>
       <c r="C128">
-        <v>715</v>
+        <v>855</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3435,13 +4011,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46141.32291666666</v>
+        <v>46143.32291666666</v>
       </c>
       <c r="B129">
-        <v>848.614</v>
+        <v>1283.628</v>
       </c>
       <c r="C129">
-        <v>821</v>
+        <v>955</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3452,13 +4028,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46141.33333333334</v>
+        <v>46143.33333333334</v>
       </c>
       <c r="B130">
-        <v>1068.76</v>
+        <v>1532.529</v>
       </c>
       <c r="C130">
-        <v>866</v>
+        <v>1031</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3469,13 +4045,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46141.34375</v>
+        <v>46143.34375</v>
       </c>
       <c r="B131">
-        <v>1164.273</v>
+        <v>1689.474</v>
       </c>
       <c r="C131">
-        <v>923</v>
+        <v>1138</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3486,13 +4062,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46141.35416666666</v>
+        <v>46143.35416666666</v>
       </c>
       <c r="B132">
-        <v>1269.225</v>
+        <v>1835.025</v>
       </c>
       <c r="C132">
-        <v>1038</v>
+        <v>1204</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3503,13 +4079,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46141.36458333334</v>
+        <v>46143.36458333334</v>
       </c>
       <c r="B133">
-        <v>1367.32</v>
+        <v>1862.928</v>
       </c>
       <c r="C133">
-        <v>1149</v>
+        <v>1210</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3520,13 +4096,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46141.375</v>
+        <v>46143.375</v>
       </c>
       <c r="B134">
-        <v>1442.394</v>
+        <v>2091.137</v>
       </c>
       <c r="C134">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3537,13 +4113,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46141.38541666666</v>
+        <v>46143.38541666666</v>
       </c>
       <c r="B135">
-        <v>1497.739</v>
+        <v>1980.99</v>
       </c>
       <c r="C135">
-        <v>1447</v>
+        <v>1214</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3554,13 +4130,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46141.39583333334</v>
+        <v>46143.39583333334</v>
       </c>
       <c r="B136">
-        <v>1557.444</v>
+        <v>1988.629</v>
       </c>
       <c r="C136">
-        <v>1422</v>
+        <v>1311</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3571,13 +4147,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46141.40625</v>
+        <v>46143.40625</v>
       </c>
       <c r="B137">
-        <v>1619.98</v>
+        <v>1787.635</v>
       </c>
       <c r="C137">
-        <v>1488</v>
+        <v>1172</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3588,13 +4164,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46141.41666666666</v>
+        <v>46143.41666666666</v>
       </c>
       <c r="B138">
-        <v>1654.938</v>
+        <v>2203.442</v>
       </c>
       <c r="C138">
-        <v>1459</v>
+        <v>1302</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3605,13 +4181,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46141.42708333334</v>
+        <v>46143.42708333334</v>
       </c>
       <c r="B139">
-        <v>1704.475</v>
+        <v>2193.927</v>
       </c>
       <c r="C139">
-        <v>1550</v>
+        <v>1320</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3622,13 +4198,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46141.4375</v>
+        <v>46143.4375</v>
       </c>
       <c r="B140">
-        <v>1748.388</v>
+        <v>2218.57</v>
       </c>
       <c r="C140">
-        <v>1498</v>
+        <v>1422</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3639,13 +4215,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46141.44791666666</v>
+        <v>46143.44791666666</v>
       </c>
       <c r="B141">
-        <v>1771.856</v>
+        <v>2209.897</v>
       </c>
       <c r="C141">
-        <v>1552</v>
+        <v>1411</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3656,13 +4232,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46141.45833333334</v>
+        <v>46143.45833333334</v>
       </c>
       <c r="B142">
-        <v>1789.33</v>
+        <v>2222.338</v>
       </c>
       <c r="C142">
-        <v>1645</v>
+        <v>1463</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3673,13 +4249,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46141.46875</v>
+        <v>46143.46875</v>
       </c>
       <c r="B143">
-        <v>1807.038</v>
+        <v>2204.626</v>
       </c>
       <c r="C143">
-        <v>1693</v>
+        <v>1416</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3690,13 +4266,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46141.47916666666</v>
+        <v>46143.47916666666</v>
       </c>
       <c r="B144">
-        <v>1815.013</v>
+        <v>2150.091</v>
       </c>
       <c r="C144">
-        <v>1720</v>
+        <v>1417</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3707,13 +4283,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46141.48958333334</v>
+        <v>46143.48958333334</v>
       </c>
       <c r="B145">
-        <v>1810.938</v>
+        <v>2170.115</v>
       </c>
       <c r="C145">
-        <v>1744</v>
+        <v>1372</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3724,13 +4300,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46141.5</v>
+        <v>46143.5</v>
       </c>
       <c r="B146">
-        <v>1814.622</v>
+        <v>2136.194</v>
       </c>
       <c r="C146">
-        <v>1675</v>
+        <v>1416</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3741,13 +4317,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46141.51041666666</v>
+        <v>46143.51041666666</v>
       </c>
       <c r="B147">
-        <v>1802.46</v>
+        <v>2114.172</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1432</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3758,13 +4334,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46141.52083333334</v>
+        <v>46143.52083333334</v>
       </c>
       <c r="B148">
-        <v>1782.527</v>
+        <v>2081.242</v>
       </c>
       <c r="C148">
-        <v>1689</v>
+        <v>1483</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3775,13 +4351,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46141.53125</v>
+        <v>46143.53125</v>
       </c>
       <c r="B149">
-        <v>1762.23</v>
+        <v>2057.888</v>
       </c>
       <c r="C149">
-        <v>1577</v>
+        <v>1475</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3792,13 +4368,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46141.54166666666</v>
+        <v>46143.54166666666</v>
       </c>
       <c r="B150">
-        <v>1699.862</v>
+        <v>2012.549</v>
       </c>
       <c r="C150">
-        <v>1556</v>
+        <v>1401</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3809,13 +4385,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46141.55208333334</v>
+        <v>46143.55208333334</v>
       </c>
       <c r="B151">
-        <v>1655.654</v>
+        <v>1990.287</v>
       </c>
       <c r="C151">
-        <v>1560</v>
+        <v>1335</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3826,13 +4402,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46141.5625</v>
+        <v>46143.5625</v>
       </c>
       <c r="B152">
-        <v>1604.698</v>
+        <v>1963.92</v>
       </c>
       <c r="C152">
-        <v>1529</v>
+        <v>1325</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3843,13 +4419,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46141.57291666666</v>
+        <v>46143.57291666666</v>
       </c>
       <c r="B153">
-        <v>1565.791</v>
+        <v>1914.925</v>
       </c>
       <c r="C153">
-        <v>1416</v>
+        <v>1362</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3860,13 +4436,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46141.58333333334</v>
+        <v>46143.58333333334</v>
       </c>
       <c r="B154">
-        <v>1500.185</v>
+        <v>1849.432</v>
       </c>
       <c r="C154">
-        <v>1424</v>
+        <v>1266</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3877,13 +4453,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46141.59375</v>
+        <v>46143.59375</v>
       </c>
       <c r="B155">
-        <v>1446.701</v>
+        <v>1799.223</v>
       </c>
       <c r="C155">
-        <v>1410</v>
+        <v>1243</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3894,13 +4470,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46141.60416666666</v>
+        <v>46143.60416666666</v>
       </c>
       <c r="B156">
-        <v>1400.633</v>
+        <v>1428.317</v>
       </c>
       <c r="C156">
-        <v>1363</v>
+        <v>1075</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3911,13 +4487,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46141.61458333334</v>
+        <v>46143.61458333334</v>
       </c>
       <c r="B157">
-        <v>1345.089</v>
+        <v>1604.197</v>
       </c>
       <c r="C157">
-        <v>1294</v>
+        <v>1140</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3928,13 +4504,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46141.625</v>
+        <v>46143.625</v>
       </c>
       <c r="B158">
-        <v>1256.175</v>
+        <v>1279.08</v>
       </c>
       <c r="C158">
-        <v>1238</v>
+        <v>1010</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3945,13 +4521,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46141.63541666666</v>
+        <v>46143.63541666666</v>
       </c>
       <c r="B159">
-        <v>1188.51</v>
+        <v>1407.74</v>
       </c>
       <c r="C159">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3962,13 +4538,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46141.64583333334</v>
+        <v>46143.64583333334</v>
       </c>
       <c r="B160">
-        <v>1116.756</v>
+        <v>1368.923</v>
       </c>
       <c r="C160">
-        <v>1036</v>
+        <v>1209</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3979,13 +4555,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46141.65625</v>
+        <v>46143.65625</v>
       </c>
       <c r="B161">
-        <v>1052.12</v>
+        <v>1315.003</v>
       </c>
       <c r="C161">
-        <v>971</v>
+        <v>1022</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3996,13 +4572,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46141.66666666666</v>
+        <v>46143.66666666666</v>
       </c>
       <c r="B162">
-        <v>968.23</v>
+        <v>1165.721</v>
       </c>
       <c r="C162">
-        <v>907</v>
+        <v>964</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -4013,13 +4589,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46141.67708333334</v>
+        <v>46143.67708333334</v>
       </c>
       <c r="B163">
-        <v>867.434</v>
+        <v>1060.201</v>
       </c>
       <c r="C163">
-        <v>809</v>
+        <v>879</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -4030,13 +4606,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46141.6875</v>
+        <v>46143.6875</v>
       </c>
       <c r="B164">
-        <v>781.586</v>
+        <v>955.874</v>
       </c>
       <c r="C164">
-        <v>745</v>
+        <v>818</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -4047,13 +4623,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46141.69791666666</v>
+        <v>46143.69791666666</v>
       </c>
       <c r="B165">
-        <v>700.439</v>
+        <v>860.125</v>
       </c>
       <c r="C165">
-        <v>692</v>
+        <v>707</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -4064,13 +4640,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46141.70833333334</v>
+        <v>46143.70833333334</v>
       </c>
       <c r="B166">
-        <v>550.974</v>
+        <v>693.876</v>
       </c>
       <c r="C166">
-        <v>591</v>
+        <v>704</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -4081,13 +4657,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46141.71875</v>
+        <v>46143.71875</v>
       </c>
       <c r="B167">
-        <v>470.199</v>
+        <v>611.462</v>
       </c>
       <c r="C167">
-        <v>493</v>
+        <v>602</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -4098,13 +4674,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46141.72916666666</v>
+        <v>46143.72916666666</v>
       </c>
       <c r="B168">
-        <v>394.149</v>
+        <v>505.263</v>
       </c>
       <c r="C168">
-        <v>400</v>
+        <v>467</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -4115,13 +4691,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46141.73958333334</v>
+        <v>46143.73958333334</v>
       </c>
       <c r="B169">
-        <v>318.213</v>
+        <v>403.089</v>
       </c>
       <c r="C169">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -4132,13 +4708,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46141.75</v>
+        <v>46143.75</v>
       </c>
       <c r="B170">
-        <v>205.633</v>
+        <v>269.139</v>
       </c>
       <c r="C170">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -4149,13 +4725,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46141.76041666666</v>
+        <v>46143.76041666666</v>
       </c>
       <c r="B171">
-        <v>156.412</v>
+        <v>195.27</v>
       </c>
       <c r="C171">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -4166,13 +4742,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46141.77083333334</v>
+        <v>46143.77083333334</v>
       </c>
       <c r="B172">
-        <v>108.522</v>
+        <v>132.125</v>
       </c>
       <c r="C172">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4183,13 +4759,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46141.78125</v>
+        <v>46143.78125</v>
       </c>
       <c r="B173">
-        <v>81.214</v>
+        <v>85.82599999999999</v>
       </c>
       <c r="C173">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4200,10 +4776,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46141.79166666666</v>
+        <v>46143.79166666666</v>
       </c>
       <c r="B174">
-        <v>38.395</v>
+        <v>42.26</v>
       </c>
       <c r="C174">
         <v>13</v>
@@ -4217,10 +4793,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46141.80208333334</v>
+        <v>46143.80208333334</v>
       </c>
       <c r="B175">
-        <v>32.6</v>
+        <v>25.52</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -4234,10 +4810,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46141.8125</v>
+        <v>46143.8125</v>
       </c>
       <c r="B176">
-        <v>24.63</v>
+        <v>18.154</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -4251,10 +4827,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46141.82291666666</v>
+        <v>46143.82291666666</v>
       </c>
       <c r="B177">
-        <v>20.472</v>
+        <v>14.561</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -4268,10 +4844,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46141.83333333334</v>
+        <v>46143.83333333334</v>
       </c>
       <c r="B178">
-        <v>15.203</v>
+        <v>8.529</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -4285,10 +4861,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46141.84375</v>
+        <v>46143.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>8.791</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4302,10 +4878,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46141.85416666666</v>
+        <v>46143.85416666666</v>
       </c>
       <c r="B180">
-        <v>14.861</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4319,10 +4895,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46141.86458333334</v>
+        <v>46143.86458333334</v>
       </c>
       <c r="B181">
-        <v>11.733</v>
+        <v>7.06</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4336,10 +4912,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46141.875</v>
+        <v>46143.875</v>
       </c>
       <c r="B182">
-        <v>13.33</v>
+        <v>12.83</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4353,10 +4929,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46141.88541666666</v>
+        <v>46143.88541666666</v>
       </c>
       <c r="B183">
-        <v>10.73</v>
+        <v>12.53</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4370,10 +4946,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46141.89583333334</v>
+        <v>46143.89583333334</v>
       </c>
       <c r="B184">
-        <v>8.029999999999999</v>
+        <v>2.83</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4387,7 +4963,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46141.90625</v>
+        <v>46143.90625</v>
       </c>
       <c r="B185">
         <v>0.73</v>
@@ -4404,10 +4980,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46141.91666666666</v>
+        <v>46143.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4421,7 +4997,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46141.92708333334</v>
+        <v>46143.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4438,10 +5014,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46141.9375</v>
+        <v>46143.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4455,10 +5031,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46141.94791666666</v>
+        <v>46143.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4472,10 +5048,10 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46141.95833333334</v>
+        <v>46143.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -4489,7 +5065,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46141.96875</v>
+        <v>46143.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4506,7 +5082,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46141.97916666666</v>
+        <v>46143.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4523,7 +5099,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46141.98958333334</v>
+        <v>46143.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4540,7 +5116,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4557,7 +5133,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46142.01041666666</v>
+        <v>46144.01041666666</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -4574,7 +5150,7 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46142.02083333334</v>
+        <v>46144.02083333334</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -4591,7 +5167,7 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46142.03125</v>
+        <v>46144.03125</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -4608,7 +5184,7 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46142.04166666666</v>
+        <v>46144.04166666666</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -4625,7 +5201,7 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46142.05208333334</v>
+        <v>46144.05208333334</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -4642,7 +5218,7 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46142.0625</v>
+        <v>46144.0625</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -4659,7 +5235,7 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46142.07291666666</v>
+        <v>46144.07291666666</v>
       </c>
       <c r="B201">
         <v>0</v>
@@ -4676,7 +5252,7 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46142.08333333334</v>
+        <v>46144.08333333334</v>
       </c>
       <c r="B202">
         <v>0</v>
@@ -4693,7 +5269,7 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46142.09375</v>
+        <v>46144.09375</v>
       </c>
       <c r="B203">
         <v>0</v>
@@ -4710,7 +5286,7 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46142.10416666666</v>
+        <v>46144.10416666666</v>
       </c>
       <c r="B204">
         <v>0</v>
@@ -4727,7 +5303,7 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46142.11458333334</v>
+        <v>46144.11458333334</v>
       </c>
       <c r="B205">
         <v>0</v>
@@ -4744,10 +5320,10 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46142.125</v>
+        <v>46144.125</v>
       </c>
       <c r="B206">
-        <v>0</v>
+        <v>0.731</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -4761,7 +5337,7 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46142.13541666666</v>
+        <v>46144.13541666666</v>
       </c>
       <c r="B207">
         <v>0</v>
@@ -4778,7 +5354,7 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46142.14583333334</v>
+        <v>46144.14583333334</v>
       </c>
       <c r="B208">
         <v>0</v>
@@ -4795,7 +5371,7 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46142.15625</v>
+        <v>46144.15625</v>
       </c>
       <c r="B209">
         <v>0</v>
@@ -4812,10 +5388,10 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46142.16666666666</v>
+        <v>46144.16666666666</v>
       </c>
       <c r="B210">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -4829,7 +5405,7 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46142.17708333334</v>
+        <v>46144.17708333334</v>
       </c>
       <c r="B211">
         <v>0</v>
@@ -4846,10 +5422,10 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46142.1875</v>
+        <v>46144.1875</v>
       </c>
       <c r="B212">
-        <v>0.747</v>
+        <v>0.793</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -4863,10 +5439,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46142.19791666666</v>
+        <v>46144.19791666666</v>
       </c>
       <c r="B213">
-        <v>0.779</v>
+        <v>0.822</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -4880,10 +5456,10 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46142.20833333334</v>
+        <v>46144.20833333334</v>
       </c>
       <c r="B214">
-        <v>1.371</v>
+        <v>3.935</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -4897,10 +5473,10 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46142.21875</v>
+        <v>46144.21875</v>
       </c>
       <c r="B215">
-        <v>4.827</v>
+        <v>11.173</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -4914,13 +5490,13 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46142.22916666666</v>
+        <v>46144.22916666666</v>
       </c>
       <c r="B216">
-        <v>14.981</v>
+        <v>34.073</v>
       </c>
       <c r="C216">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -4931,13 +5507,13 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46142.23958333334</v>
+        <v>46144.23958333334</v>
       </c>
       <c r="B217">
-        <v>31.343</v>
+        <v>69.407</v>
       </c>
       <c r="C217">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D217">
         <v>24</v>
@@ -4948,13 +5524,13 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46142.25</v>
+        <v>46144.25</v>
       </c>
       <c r="B218">
-        <v>110.775</v>
+        <v>154.82</v>
       </c>
       <c r="C218">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D218">
         <v>25</v>
@@ -4965,13 +5541,13 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46142.26041666666</v>
+        <v>46144.26041666666</v>
       </c>
       <c r="B219">
-        <v>156.833</v>
+        <v>228.398</v>
       </c>
       <c r="C219">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="D219">
         <v>26</v>
@@ -4982,13 +5558,13 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46142.27083333334</v>
+        <v>46144.27083333334</v>
       </c>
       <c r="B220">
-        <v>202.328</v>
+        <v>313.84</v>
       </c>
       <c r="C220">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="D220">
         <v>27</v>
@@ -4999,13 +5575,13 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46142.28125</v>
+        <v>46144.28125</v>
       </c>
       <c r="B221">
-        <v>260.181</v>
+        <v>423.371</v>
       </c>
       <c r="C221">
-        <v>136</v>
+        <v>259</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -5016,13 +5592,13 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46142.29166666666</v>
+        <v>46144.29166666666</v>
       </c>
       <c r="B222">
-        <v>351.994</v>
+        <v>623.402</v>
       </c>
       <c r="C222">
-        <v>178</v>
+        <v>325</v>
       </c>
       <c r="D222">
         <v>29</v>
@@ -5033,13 +5609,13 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46142.30208333334</v>
+        <v>46144.30208333334</v>
       </c>
       <c r="B223">
-        <v>420.295</v>
+        <v>757.16</v>
       </c>
       <c r="C223">
-        <v>234</v>
+        <v>435</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -5050,13 +5626,13 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46142.3125</v>
+        <v>46144.3125</v>
       </c>
       <c r="B224">
-        <v>499.001</v>
+        <v>899.293</v>
       </c>
       <c r="C224">
-        <v>303</v>
+        <v>510</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -5067,13 +5643,13 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46142.32291666666</v>
+        <v>46144.32291666666</v>
       </c>
       <c r="B225">
-        <v>571.061</v>
+        <v>1024.155</v>
       </c>
       <c r="C225">
-        <v>369</v>
+        <v>562</v>
       </c>
       <c r="D225">
         <v>32</v>
@@ -5084,13 +5660,13 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46142.33333333334</v>
+        <v>46144.33333333334</v>
       </c>
       <c r="B226">
-        <v>669.073</v>
+        <v>1212.674</v>
       </c>
       <c r="C226">
-        <v>430</v>
+        <v>672</v>
       </c>
       <c r="D226">
         <v>33</v>
@@ -5101,13 +5677,13 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46142.34375</v>
+        <v>46144.34375</v>
       </c>
       <c r="B227">
-        <v>728.499</v>
+        <v>1345.179</v>
       </c>
       <c r="C227">
-        <v>515</v>
+        <v>718</v>
       </c>
       <c r="D227">
         <v>34</v>
@@ -5118,13 +5694,13 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46142.35416666666</v>
+        <v>46144.35416666666</v>
       </c>
       <c r="B228">
-        <v>812.227</v>
+        <v>1481.78</v>
       </c>
       <c r="C228">
-        <v>568</v>
+        <v>810</v>
       </c>
       <c r="D228">
         <v>35</v>
@@ -5135,13 +5711,13 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46142.36458333334</v>
+        <v>46144.36458333334</v>
       </c>
       <c r="B229">
-        <v>890.375</v>
+        <v>1618.508</v>
       </c>
       <c r="C229">
-        <v>641</v>
+        <v>883</v>
       </c>
       <c r="D229">
         <v>36</v>
@@ -5152,13 +5728,13 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46142.375</v>
+        <v>46144.375</v>
       </c>
       <c r="B230">
-        <v>991.02</v>
+        <v>1749.89</v>
       </c>
       <c r="C230">
-        <v>732</v>
+        <v>1017</v>
       </c>
       <c r="D230">
         <v>37</v>
@@ -5169,13 +5745,13 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46142.38541666666</v>
+        <v>46144.38541666666</v>
       </c>
       <c r="B231">
-        <v>1060.596</v>
+        <v>1713.07</v>
       </c>
       <c r="C231">
-        <v>801</v>
+        <v>1054</v>
       </c>
       <c r="D231">
         <v>38</v>
@@ -5186,13 +5762,13 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46142.39583333334</v>
+        <v>46144.39583333334</v>
       </c>
       <c r="B232">
-        <v>1126.624</v>
+        <v>1674.664</v>
       </c>
       <c r="C232">
-        <v>818</v>
+        <v>1015</v>
       </c>
       <c r="D232">
         <v>39</v>
@@ -5203,13 +5779,13 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46142.40625</v>
+        <v>46144.40625</v>
       </c>
       <c r="B233">
-        <v>1139.684</v>
+        <v>1715.445</v>
       </c>
       <c r="C233">
-        <v>789</v>
+        <v>966</v>
       </c>
       <c r="D233">
         <v>40</v>
@@ -5220,13 +5796,13 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46142.41666666666</v>
+        <v>46144.41666666666</v>
       </c>
       <c r="B234">
-        <v>1265.215</v>
+        <v>1872.893</v>
       </c>
       <c r="C234">
-        <v>858</v>
+        <v>1041</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5237,13 +5813,13 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46142.42708333334</v>
+        <v>46144.42708333334</v>
       </c>
       <c r="B235">
-        <v>1273.377</v>
+        <v>1947.745</v>
       </c>
       <c r="C235">
-        <v>841</v>
+        <v>1095</v>
       </c>
       <c r="D235">
         <v>42</v>
@@ -5254,13 +5830,13 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46142.4375</v>
+        <v>46144.4375</v>
       </c>
       <c r="B236">
-        <v>1329.612</v>
+        <v>1997.978</v>
       </c>
       <c r="C236">
-        <v>853</v>
+        <v>1106</v>
       </c>
       <c r="D236">
         <v>43</v>
@@ -5271,13 +5847,13 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46142.44791666666</v>
+        <v>46144.44791666666</v>
       </c>
       <c r="B237">
-        <v>1373.685</v>
+        <v>2012.959</v>
       </c>
       <c r="C237">
-        <v>950</v>
+        <v>1115</v>
       </c>
       <c r="D237">
         <v>44</v>
@@ -5288,13 +5864,13 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46142.45833333334</v>
+        <v>46144.45833333334</v>
       </c>
       <c r="B238">
-        <v>1410.317</v>
+        <v>1919.062</v>
       </c>
       <c r="C238">
-        <v>987</v>
+        <v>1126</v>
       </c>
       <c r="D238">
         <v>45</v>
@@ -5305,13 +5881,13 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46142.46875</v>
+        <v>46144.46875</v>
       </c>
       <c r="B239">
-        <v>1433.672</v>
+        <v>1934.088</v>
       </c>
       <c r="C239">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="D239">
         <v>46</v>
@@ -5322,13 +5898,13 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46142.47916666666</v>
+        <v>46144.47916666666</v>
       </c>
       <c r="B240">
-        <v>1454.381</v>
+        <v>2031.55</v>
       </c>
       <c r="C240">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="D240">
         <v>47</v>
@@ -5339,13 +5915,13 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46142.48958333334</v>
+        <v>46144.48958333334</v>
       </c>
       <c r="B241">
-        <v>1472.87</v>
+        <v>2069.865</v>
       </c>
       <c r="C241">
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="D241">
         <v>48</v>
@@ -5356,13 +5932,13 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46142.5</v>
+        <v>46144.5</v>
       </c>
       <c r="B242">
-        <v>1513.705</v>
+        <v>2052.548</v>
       </c>
       <c r="C242">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="D242">
         <v>49</v>
@@ -5373,13 +5949,13 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46142.51041666666</v>
+        <v>46144.51041666666</v>
       </c>
       <c r="B243">
-        <v>1526.324</v>
+        <v>2052.827</v>
       </c>
       <c r="C243">
-        <v>0</v>
+        <v>1266</v>
       </c>
       <c r="D243">
         <v>50</v>
@@ -5390,13 +5966,13 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46142.52083333334</v>
+        <v>46144.52083333334</v>
       </c>
       <c r="B244">
-        <v>1490.692</v>
+        <v>2002.185</v>
       </c>
       <c r="C244">
-        <v>0</v>
+        <v>1267</v>
       </c>
       <c r="D244">
         <v>51</v>
@@ -5407,13 +5983,13 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46142.53125</v>
+        <v>46144.53125</v>
       </c>
       <c r="B245">
-        <v>1496.842</v>
+        <v>1995.143</v>
       </c>
       <c r="C245">
-        <v>0</v>
+        <v>1190</v>
       </c>
       <c r="D245">
         <v>52</v>
@@ -5424,13 +6000,13 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46142.54166666666</v>
+        <v>46144.54166666666</v>
       </c>
       <c r="B246">
-        <v>1527.108</v>
+        <v>1886.665</v>
       </c>
       <c r="C246">
-        <v>0</v>
+        <v>1175</v>
       </c>
       <c r="D246">
         <v>53</v>
@@ -5441,13 +6017,13 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46142.55208333334</v>
+        <v>46144.55208333334</v>
       </c>
       <c r="B247">
-        <v>1526.442</v>
+        <v>1919.085</v>
       </c>
       <c r="C247">
-        <v>0</v>
+        <v>1282</v>
       </c>
       <c r="D247">
         <v>54</v>
@@ -5458,13 +6034,13 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46142.5625</v>
+        <v>46144.5625</v>
       </c>
       <c r="B248">
-        <v>1510.656</v>
+        <v>1890.314</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>1169</v>
       </c>
       <c r="D248">
         <v>55</v>
@@ -5475,13 +6051,13 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46142.57291666666</v>
+        <v>46144.57291666666</v>
       </c>
       <c r="B249">
-        <v>1524.884</v>
+        <v>1838.758</v>
       </c>
       <c r="C249">
-        <v>0</v>
+        <v>1159</v>
       </c>
       <c r="D249">
         <v>56</v>
@@ -5492,13 +6068,13 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46142.58333333334</v>
+        <v>46144.58333333334</v>
       </c>
       <c r="B250">
-        <v>1477.674</v>
+        <v>1787.12</v>
       </c>
       <c r="C250">
-        <v>0</v>
+        <v>1109</v>
       </c>
       <c r="D250">
         <v>57</v>
@@ -5509,13 +6085,13 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46142.59375</v>
+        <v>46144.59375</v>
       </c>
       <c r="B251">
-        <v>1469.93</v>
+        <v>1757.412</v>
       </c>
       <c r="C251">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="D251">
         <v>58</v>
@@ -5526,13 +6102,13 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46142.60416666666</v>
+        <v>46144.60416666666</v>
       </c>
       <c r="B252">
-        <v>1491.82</v>
+        <v>1728.569</v>
       </c>
       <c r="C252">
-        <v>0</v>
+        <v>1026</v>
       </c>
       <c r="D252">
         <v>59</v>
@@ -5543,13 +6119,13 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46142.61458333334</v>
+        <v>46144.61458333334</v>
       </c>
       <c r="B253">
-        <v>1408.701</v>
+        <v>1653.387</v>
       </c>
       <c r="C253">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="D253">
         <v>60</v>
@@ -5560,13 +6136,13 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46142.625</v>
+        <v>46144.625</v>
       </c>
       <c r="B254">
-        <v>1339.777</v>
+        <v>1566.309</v>
       </c>
       <c r="C254">
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="D254">
         <v>61</v>
@@ -5577,13 +6153,13 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46142.63541666666</v>
+        <v>46144.63541666666</v>
       </c>
       <c r="B255">
-        <v>1303.075</v>
+        <v>1510.662</v>
       </c>
       <c r="C255">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="D255">
         <v>62</v>
@@ -5594,13 +6170,13 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46142.64583333334</v>
+        <v>46144.64583333334</v>
       </c>
       <c r="B256">
-        <v>1260.499</v>
+        <v>1433.807</v>
       </c>
       <c r="C256">
-        <v>0</v>
+        <v>788</v>
       </c>
       <c r="D256">
         <v>63</v>
@@ -5611,13 +6187,13 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46142.65625</v>
+        <v>46144.65625</v>
       </c>
       <c r="B257">
-        <v>1220.323</v>
+        <v>1377.819</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="D257">
         <v>64</v>
@@ -5628,13 +6204,13 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46142.66666666666</v>
+        <v>46144.66666666666</v>
       </c>
       <c r="B258">
-        <v>1092.93</v>
+        <v>1265.402</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="D258">
         <v>65</v>
@@ -5645,13 +6221,13 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46142.67708333334</v>
+        <v>46144.67708333334</v>
       </c>
       <c r="B259">
-        <v>1030.117</v>
+        <v>1147.099</v>
       </c>
       <c r="C259">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="D259">
         <v>66</v>
@@ -5662,13 +6238,13 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46142.6875</v>
+        <v>46144.6875</v>
       </c>
       <c r="B260">
-        <v>953.944</v>
+        <v>1035.753</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="D260">
         <v>67</v>
@@ -5679,13 +6255,13 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46142.69791666666</v>
+        <v>46144.69791666666</v>
       </c>
       <c r="B261">
-        <v>869.2809999999999</v>
+        <v>944.189</v>
       </c>
       <c r="C261">
-        <v>0</v>
+        <v>573</v>
       </c>
       <c r="D261">
         <v>68</v>
@@ -5696,13 +6272,13 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46142.70833333334</v>
+        <v>46144.70833333334</v>
       </c>
       <c r="B262">
-        <v>708.288</v>
+        <v>758.4450000000001</v>
       </c>
       <c r="C262">
-        <v>0</v>
+        <v>535</v>
       </c>
       <c r="D262">
         <v>69</v>
@@ -5713,13 +6289,13 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46142.71875</v>
+        <v>46144.71875</v>
       </c>
       <c r="B263">
-        <v>624.579</v>
+        <v>661.998</v>
       </c>
       <c r="C263">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="D263">
         <v>70</v>
@@ -5730,13 +6306,13 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46142.72916666666</v>
+        <v>46144.72916666666</v>
       </c>
       <c r="B264">
-        <v>538.212</v>
+        <v>544.571</v>
       </c>
       <c r="C264">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="D264">
         <v>71</v>
@@ -5747,13 +6323,13 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46142.73958333334</v>
+        <v>46144.73958333334</v>
       </c>
       <c r="B265">
-        <v>458.013</v>
+        <v>427.692</v>
       </c>
       <c r="C265">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="D265">
         <v>72</v>
@@ -5764,13 +6340,13 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46142.75</v>
+        <v>46144.75</v>
       </c>
       <c r="B266">
-        <v>328.63</v>
+        <v>297.152</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="D266">
         <v>73</v>
@@ -5781,13 +6357,13 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46142.76041666666</v>
+        <v>46144.76041666666</v>
       </c>
       <c r="B267">
-        <v>261.095</v>
+        <v>217.11</v>
       </c>
       <c r="C267">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="D267">
         <v>74</v>
@@ -5798,13 +6374,13 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46142.77083333334</v>
+        <v>46144.77083333334</v>
       </c>
       <c r="B268">
-        <v>164.975</v>
+        <v>151.201</v>
       </c>
       <c r="C268">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="D268">
         <v>75</v>
@@ -5815,13 +6391,13 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46142.78125</v>
+        <v>46144.78125</v>
       </c>
       <c r="B269">
-        <v>97.503</v>
+        <v>101.963</v>
       </c>
       <c r="C269">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D269">
         <v>76</v>
@@ -5832,13 +6408,13 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46142.79166666666</v>
+        <v>46144.79166666666</v>
       </c>
       <c r="B270">
-        <v>42.661</v>
+        <v>45.944</v>
       </c>
       <c r="C270">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D270">
         <v>77</v>
@@ -5849,10 +6425,10 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46142.80208333334</v>
+        <v>46144.80208333334</v>
       </c>
       <c r="B271">
-        <v>34.753</v>
+        <v>26.931</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -5866,10 +6442,10 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46142.8125</v>
+        <v>46144.8125</v>
       </c>
       <c r="B272">
-        <v>24.809</v>
+        <v>18.237</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -5883,10 +6459,10 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46142.82291666666</v>
+        <v>46144.82291666666</v>
       </c>
       <c r="B273">
-        <v>19.274</v>
+        <v>14.414</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -5900,10 +6476,10 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46142.83333333334</v>
+        <v>46144.83333333334</v>
       </c>
       <c r="B274">
-        <v>15.778</v>
+        <v>7.856</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -5917,10 +6493,10 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46142.84375</v>
+        <v>46144.84375</v>
       </c>
       <c r="B275">
-        <v>15.667</v>
+        <v>7.656</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -5934,10 +6510,10 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46142.85416666666</v>
+        <v>46144.85416666666</v>
       </c>
       <c r="B276">
-        <v>15.271</v>
+        <v>7.208</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -5951,10 +6527,10 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46142.86458333334</v>
+        <v>46144.86458333334</v>
       </c>
       <c r="B277">
-        <v>13.081</v>
+        <v>6.199</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -5968,10 +6544,10 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46142.875</v>
+        <v>46144.875</v>
       </c>
       <c r="B278">
-        <v>13.33</v>
+        <v>6.83</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -5985,10 +6561,10 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46142.88541666666</v>
+        <v>46144.88541666666</v>
       </c>
       <c r="B279">
-        <v>13.03</v>
+        <v>5.23</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -6002,10 +6578,10 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46142.89583333334</v>
+        <v>46144.89583333334</v>
       </c>
       <c r="B280">
-        <v>10.33</v>
+        <v>1.83</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -6019,10 +6595,10 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46142.90625</v>
+        <v>46144.90625</v>
       </c>
       <c r="B281">
-        <v>0.73</v>
+        <v>1.23</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -6036,10 +6612,10 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46142.91666666666</v>
+        <v>46144.91666666666</v>
       </c>
       <c r="B282">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -6053,10 +6629,10 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46142.92708333334</v>
+        <v>46144.92708333334</v>
       </c>
       <c r="B283">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -6070,7 +6646,7 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46142.9375</v>
+        <v>46144.9375</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -6087,7 +6663,7 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46142.94791666666</v>
+        <v>46144.94791666666</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -6104,7 +6680,7 @@
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="2">
-        <v>46142.95833333334</v>
+        <v>46144.95833333334</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -6121,7 +6697,7 @@
     </row>
     <row r="287" spans="1:5">
       <c r="A287" s="2">
-        <v>46142.96875</v>
+        <v>46144.96875</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -6138,7 +6714,7 @@
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="2">
-        <v>46142.97916666666</v>
+        <v>46144.97916666666</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -6155,7 +6731,7 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" s="2">
-        <v>46142.98958333334</v>
+        <v>46144.98958333334</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -6168,6 +6744,3270 @@
       </c>
       <c r="E289" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46145</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46145.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46145.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46145.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46145.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46145.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46145.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46145.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46145.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46145.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46145.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46145.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46145.125</v>
+      </c>
+      <c r="B302">
+        <v>0.764</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46145.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46145.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46145.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46145.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0.73</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46145.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46145.1875</v>
+      </c>
+      <c r="B308">
+        <v>0.774</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46145.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0.862</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46145.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>7.626</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46145.21875</v>
+      </c>
+      <c r="B311">
+        <v>28.042</v>
+      </c>
+      <c r="C311">
+        <v>8</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46145.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>59.575</v>
+      </c>
+      <c r="C312">
+        <v>39</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46145.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>106.701</v>
+      </c>
+      <c r="C313">
+        <v>84</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46145.25</v>
+      </c>
+      <c r="B314">
+        <v>238.675</v>
+      </c>
+      <c r="C314">
+        <v>151</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46145.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>343.573</v>
+      </c>
+      <c r="C315">
+        <v>251</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46145.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>475.222</v>
+      </c>
+      <c r="C316">
+        <v>359</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46145.28125</v>
+      </c>
+      <c r="B317">
+        <v>626.938</v>
+      </c>
+      <c r="C317">
+        <v>491</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46145.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>911.151</v>
+      </c>
+      <c r="C318">
+        <v>635</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46145.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>1108.254</v>
+      </c>
+      <c r="C319">
+        <v>800</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46145.3125</v>
+      </c>
+      <c r="B320">
+        <v>1307.466</v>
+      </c>
+      <c r="C320">
+        <v>950</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46145.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>1499.418</v>
+      </c>
+      <c r="C321">
+        <v>1084</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46145.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>1780.118</v>
+      </c>
+      <c r="C322">
+        <v>1182</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46145.34375</v>
+      </c>
+      <c r="B323">
+        <v>1932.647</v>
+      </c>
+      <c r="C323">
+        <v>1261</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46145.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>2072.425</v>
+      </c>
+      <c r="C324">
+        <v>1352</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46145.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>2230.059</v>
+      </c>
+      <c r="C325">
+        <v>1368</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46145.375</v>
+      </c>
+      <c r="B326">
+        <v>2412.75</v>
+      </c>
+      <c r="C326">
+        <v>1443</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46145.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>2494.118</v>
+      </c>
+      <c r="C327">
+        <v>1500</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46145.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>2557.357</v>
+      </c>
+      <c r="C328">
+        <v>1542</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46145.40625</v>
+      </c>
+      <c r="B329">
+        <v>2484.001</v>
+      </c>
+      <c r="C329">
+        <v>1504</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46145.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>2517.873</v>
+      </c>
+      <c r="C330">
+        <v>1484</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46145.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>2539.142</v>
+      </c>
+      <c r="C331">
+        <v>1594</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46145.4375</v>
+      </c>
+      <c r="B332">
+        <v>2539.241</v>
+      </c>
+      <c r="C332">
+        <v>1601</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46145.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>1987.58</v>
+      </c>
+      <c r="C333">
+        <v>1339</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46145.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>2483.323</v>
+      </c>
+      <c r="C334">
+        <v>1460</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46145.46875</v>
+      </c>
+      <c r="B335">
+        <v>1928.273</v>
+      </c>
+      <c r="C335">
+        <v>1288</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46145.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>1880.764</v>
+      </c>
+      <c r="C336">
+        <v>1214</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46145.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>1874.983</v>
+      </c>
+      <c r="C337">
+        <v>1199</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46145.5</v>
+      </c>
+      <c r="B338">
+        <v>1777.44</v>
+      </c>
+      <c r="C338">
+        <v>1163</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46145.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>1765.252</v>
+      </c>
+      <c r="C339">
+        <v>1113</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46145.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>1754.383</v>
+      </c>
+      <c r="C340">
+        <v>988</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46145.53125</v>
+      </c>
+      <c r="B341">
+        <v>1743.758</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46145.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>1701.043</v>
+      </c>
+      <c r="C342">
+        <v>1031</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46145.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>1681.363</v>
+      </c>
+      <c r="C343">
+        <v>933</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46145.5625</v>
+      </c>
+      <c r="B344">
+        <v>1659.411</v>
+      </c>
+      <c r="C344">
+        <v>939</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46145.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>1638.876</v>
+      </c>
+      <c r="C345">
+        <v>958</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46145.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>1607.158</v>
+      </c>
+      <c r="C346">
+        <v>922</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46145.59375</v>
+      </c>
+      <c r="B347">
+        <v>1581.139</v>
+      </c>
+      <c r="C347">
+        <v>892</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46145.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>1549.662</v>
+      </c>
+      <c r="C348">
+        <v>915</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46145.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>1496.616</v>
+      </c>
+      <c r="C349">
+        <v>901</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46145.625</v>
+      </c>
+      <c r="B350">
+        <v>1399.426</v>
+      </c>
+      <c r="C350">
+        <v>854</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46145.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>1401.226</v>
+      </c>
+      <c r="C351">
+        <v>861</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46145.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>1389.552</v>
+      </c>
+      <c r="C352">
+        <v>870</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46145.65625</v>
+      </c>
+      <c r="B353">
+        <v>1321.983</v>
+      </c>
+      <c r="C353">
+        <v>871</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46145.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>1535.169</v>
+      </c>
+      <c r="C354">
+        <v>1082</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46145.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>1478.384</v>
+      </c>
+      <c r="C355">
+        <v>1098</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46145.6875</v>
+      </c>
+      <c r="B356">
+        <v>1471.511</v>
+      </c>
+      <c r="C356">
+        <v>1156</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46145.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>1327.887</v>
+      </c>
+      <c r="C357">
+        <v>1033</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46145.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>1092.83</v>
+      </c>
+      <c r="C358">
+        <v>864</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46145.71875</v>
+      </c>
+      <c r="B359">
+        <v>946.752</v>
+      </c>
+      <c r="C359">
+        <v>708</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46145.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>789.3099999999999</v>
+      </c>
+      <c r="C360">
+        <v>595</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46145.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>629.091</v>
+      </c>
+      <c r="C361">
+        <v>466</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46145.75</v>
+      </c>
+      <c r="B362">
+        <v>412.104</v>
+      </c>
+      <c r="C362">
+        <v>322</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46145.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>304.801</v>
+      </c>
+      <c r="C363">
+        <v>209</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46145.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>214.833</v>
+      </c>
+      <c r="C364">
+        <v>119</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46145.78125</v>
+      </c>
+      <c r="B365">
+        <v>140.043</v>
+      </c>
+      <c r="C365">
+        <v>73</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46145.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>68.01600000000001</v>
+      </c>
+      <c r="C366">
+        <v>29</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46145.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>39.23</v>
+      </c>
+      <c r="C367">
+        <v>2</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46145.8125</v>
+      </c>
+      <c r="B368">
+        <v>23.986</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46145.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>17.656</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46145.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>6.012</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46145.84375</v>
+      </c>
+      <c r="B371">
+        <v>6.341</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46145.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>5.618</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46145.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>5.124</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46145.875</v>
+      </c>
+      <c r="B374">
+        <v>6.23</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46145.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>4.73</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46145.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>1.83</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46145.90625</v>
+      </c>
+      <c r="B377">
+        <v>1.23</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46145.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0.93</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46145.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46145.9375</v>
+      </c>
+      <c r="B380">
+        <v>0.73</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46145.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0.93</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46145.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>1.63</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46145.96875</v>
+      </c>
+      <c r="B383">
+        <v>0.73</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46145.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46145.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46146.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46146.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46146.03125</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="2">
+        <v>46146.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+      <c r="E390" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="2">
+        <v>46146.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+      <c r="E391" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="2">
+        <v>46146.0625</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>7</v>
+      </c>
+      <c r="E392" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="2">
+        <v>46146.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="2">
+        <v>46146.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394">
+        <v>9</v>
+      </c>
+      <c r="E394" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="2">
+        <v>46146.09375</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>10</v>
+      </c>
+      <c r="E395" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="2">
+        <v>46146.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>11</v>
+      </c>
+      <c r="E396" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="2">
+        <v>46146.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="2">
+        <v>46146.125</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>13</v>
+      </c>
+      <c r="E398" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="2">
+        <v>46146.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>14</v>
+      </c>
+      <c r="E399" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="2">
+        <v>46146.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>15</v>
+      </c>
+      <c r="E400" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="2">
+        <v>46146.15625</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>16</v>
+      </c>
+      <c r="E401" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="2">
+        <v>46146.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>17</v>
+      </c>
+      <c r="E402" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="2">
+        <v>46146.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>0.734</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>18</v>
+      </c>
+      <c r="E403" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="2">
+        <v>46146.1875</v>
+      </c>
+      <c r="B404">
+        <v>0.75</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>19</v>
+      </c>
+      <c r="E404" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="2">
+        <v>46146.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>0.858</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>20</v>
+      </c>
+      <c r="E405" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="2">
+        <v>46146.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>9.291</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="2">
+        <v>46146.21875</v>
+      </c>
+      <c r="B407">
+        <v>29.988</v>
+      </c>
+      <c r="C407">
+        <v>8</v>
+      </c>
+      <c r="D407">
+        <v>22</v>
+      </c>
+      <c r="E407" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="2">
+        <v>46146.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>66.587</v>
+      </c>
+      <c r="C408">
+        <v>46</v>
+      </c>
+      <c r="D408">
+        <v>23</v>
+      </c>
+      <c r="E408" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="2">
+        <v>46146.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>122.135</v>
+      </c>
+      <c r="C409">
+        <v>93</v>
+      </c>
+      <c r="D409">
+        <v>24</v>
+      </c>
+      <c r="E409" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="2">
+        <v>46146.25</v>
+      </c>
+      <c r="B410">
+        <v>272.025</v>
+      </c>
+      <c r="C410">
+        <v>188</v>
+      </c>
+      <c r="D410">
+        <v>25</v>
+      </c>
+      <c r="E410" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="2">
+        <v>46146.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>385.676</v>
+      </c>
+      <c r="C411">
+        <v>312</v>
+      </c>
+      <c r="D411">
+        <v>26</v>
+      </c>
+      <c r="E411" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="2">
+        <v>46146.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>530.325</v>
+      </c>
+      <c r="C412">
+        <v>459</v>
+      </c>
+      <c r="D412">
+        <v>27</v>
+      </c>
+      <c r="E412" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="2">
+        <v>46146.28125</v>
+      </c>
+      <c r="B413">
+        <v>689.722</v>
+      </c>
+      <c r="C413">
+        <v>595</v>
+      </c>
+      <c r="D413">
+        <v>28</v>
+      </c>
+      <c r="E413" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="2">
+        <v>46146.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>1010.931</v>
+      </c>
+      <c r="C414">
+        <v>824</v>
+      </c>
+      <c r="D414">
+        <v>29</v>
+      </c>
+      <c r="E414" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="2">
+        <v>46146.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>1216.692</v>
+      </c>
+      <c r="C415">
+        <v>1011</v>
+      </c>
+      <c r="D415">
+        <v>30</v>
+      </c>
+      <c r="E415" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="2">
+        <v>46146.3125</v>
+      </c>
+      <c r="B416">
+        <v>1425.09</v>
+      </c>
+      <c r="C416">
+        <v>1168</v>
+      </c>
+      <c r="D416">
+        <v>31</v>
+      </c>
+      <c r="E416" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="2">
+        <v>46146.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>1629.423</v>
+      </c>
+      <c r="C417">
+        <v>1322</v>
+      </c>
+      <c r="D417">
+        <v>32</v>
+      </c>
+      <c r="E417" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="2">
+        <v>46146.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>1919.713</v>
+      </c>
+      <c r="C418">
+        <v>0</v>
+      </c>
+      <c r="D418">
+        <v>33</v>
+      </c>
+      <c r="E418" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="2">
+        <v>46146.34375</v>
+      </c>
+      <c r="B419">
+        <v>2087.411</v>
+      </c>
+      <c r="C419">
+        <v>0</v>
+      </c>
+      <c r="D419">
+        <v>34</v>
+      </c>
+      <c r="E419" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="2">
+        <v>46146.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>2251.52</v>
+      </c>
+      <c r="C420">
+        <v>0</v>
+      </c>
+      <c r="D420">
+        <v>35</v>
+      </c>
+      <c r="E420" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="2">
+        <v>46146.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>2420.034</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+      <c r="D421">
+        <v>36</v>
+      </c>
+      <c r="E421" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="2">
+        <v>46146.375</v>
+      </c>
+      <c r="B422">
+        <v>2654.675</v>
+      </c>
+      <c r="C422">
+        <v>0</v>
+      </c>
+      <c r="D422">
+        <v>37</v>
+      </c>
+      <c r="E422" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="2">
+        <v>46146.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>2762.627</v>
+      </c>
+      <c r="C423">
+        <v>0</v>
+      </c>
+      <c r="D423">
+        <v>38</v>
+      </c>
+      <c r="E423" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="2">
+        <v>46146.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>2865.315</v>
+      </c>
+      <c r="C424">
+        <v>0</v>
+      </c>
+      <c r="D424">
+        <v>39</v>
+      </c>
+      <c r="E424" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="2">
+        <v>46146.40625</v>
+      </c>
+      <c r="B425">
+        <v>2973.998</v>
+      </c>
+      <c r="C425">
+        <v>0</v>
+      </c>
+      <c r="D425">
+        <v>40</v>
+      </c>
+      <c r="E425" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="2">
+        <v>46146.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>3077.142</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
+      </c>
+      <c r="D426">
+        <v>41</v>
+      </c>
+      <c r="E426" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="2">
+        <v>46146.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>3119.52</v>
+      </c>
+      <c r="C427">
+        <v>0</v>
+      </c>
+      <c r="D427">
+        <v>42</v>
+      </c>
+      <c r="E427" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="2">
+        <v>46146.4375</v>
+      </c>
+      <c r="B428">
+        <v>3180.368</v>
+      </c>
+      <c r="C428">
+        <v>0</v>
+      </c>
+      <c r="D428">
+        <v>43</v>
+      </c>
+      <c r="E428" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="2">
+        <v>46146.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>3216.749</v>
+      </c>
+      <c r="C429">
+        <v>0</v>
+      </c>
+      <c r="D429">
+        <v>44</v>
+      </c>
+      <c r="E429" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="2">
+        <v>46146.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>3259.84</v>
+      </c>
+      <c r="C430">
+        <v>0</v>
+      </c>
+      <c r="D430">
+        <v>45</v>
+      </c>
+      <c r="E430" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="2">
+        <v>46146.46875</v>
+      </c>
+      <c r="B431">
+        <v>3268.287</v>
+      </c>
+      <c r="C431">
+        <v>0</v>
+      </c>
+      <c r="D431">
+        <v>46</v>
+      </c>
+      <c r="E431" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="2">
+        <v>46146.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>3272.062</v>
+      </c>
+      <c r="C432">
+        <v>0</v>
+      </c>
+      <c r="D432">
+        <v>47</v>
+      </c>
+      <c r="E432" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="2">
+        <v>46146.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>3274.887</v>
+      </c>
+      <c r="C433">
+        <v>0</v>
+      </c>
+      <c r="D433">
+        <v>48</v>
+      </c>
+      <c r="E433" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="2">
+        <v>46146.5</v>
+      </c>
+      <c r="B434">
+        <v>3246.864</v>
+      </c>
+      <c r="C434">
+        <v>0</v>
+      </c>
+      <c r="D434">
+        <v>49</v>
+      </c>
+      <c r="E434" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="2">
+        <v>46146.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>3245.619</v>
+      </c>
+      <c r="C435">
+        <v>0</v>
+      </c>
+      <c r="D435">
+        <v>50</v>
+      </c>
+      <c r="E435" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="2">
+        <v>46146.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>3237.547</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+      <c r="D436">
+        <v>51</v>
+      </c>
+      <c r="E436" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="2">
+        <v>46146.53125</v>
+      </c>
+      <c r="B437">
+        <v>3205.253</v>
+      </c>
+      <c r="C437">
+        <v>0</v>
+      </c>
+      <c r="D437">
+        <v>52</v>
+      </c>
+      <c r="E437" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="2">
+        <v>46146.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>3173.283</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
+      </c>
+      <c r="D438">
+        <v>53</v>
+      </c>
+      <c r="E438" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="2">
+        <v>46146.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>3144.111</v>
+      </c>
+      <c r="C439">
+        <v>0</v>
+      </c>
+      <c r="D439">
+        <v>54</v>
+      </c>
+      <c r="E439" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="2">
+        <v>46146.5625</v>
+      </c>
+      <c r="B440">
+        <v>3084.477</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+      <c r="D440">
+        <v>55</v>
+      </c>
+      <c r="E440" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="2">
+        <v>46146.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>3026.885</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441">
+        <v>56</v>
+      </c>
+      <c r="E441" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="2">
+        <v>46146.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>2939.365</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442">
+        <v>57</v>
+      </c>
+      <c r="E442" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="2">
+        <v>46146.59375</v>
+      </c>
+      <c r="B443">
+        <v>2875.776</v>
+      </c>
+      <c r="C443">
+        <v>0</v>
+      </c>
+      <c r="D443">
+        <v>58</v>
+      </c>
+      <c r="E443" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="2">
+        <v>46146.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>2802.301</v>
+      </c>
+      <c r="C444">
+        <v>0</v>
+      </c>
+      <c r="D444">
+        <v>59</v>
+      </c>
+      <c r="E444" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="2">
+        <v>46146.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>2712.252</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+      <c r="D445">
+        <v>60</v>
+      </c>
+      <c r="E445" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="2">
+        <v>46146.625</v>
+      </c>
+      <c r="B446">
+        <v>2526.421</v>
+      </c>
+      <c r="C446">
+        <v>0</v>
+      </c>
+      <c r="D446">
+        <v>61</v>
+      </c>
+      <c r="E446" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="2">
+        <v>46146.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>2428.749</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
+      </c>
+      <c r="D447">
+        <v>62</v>
+      </c>
+      <c r="E447" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="2">
+        <v>46146.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>2311.716</v>
+      </c>
+      <c r="C448">
+        <v>0</v>
+      </c>
+      <c r="D448">
+        <v>63</v>
+      </c>
+      <c r="E448" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="2">
+        <v>46146.65625</v>
+      </c>
+      <c r="B449">
+        <v>2194.733</v>
+      </c>
+      <c r="C449">
+        <v>0</v>
+      </c>
+      <c r="D449">
+        <v>64</v>
+      </c>
+      <c r="E449" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="2">
+        <v>46146.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>1977.387</v>
+      </c>
+      <c r="C450">
+        <v>0</v>
+      </c>
+      <c r="D450">
+        <v>65</v>
+      </c>
+      <c r="E450" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="2">
+        <v>46146.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>1805.638</v>
+      </c>
+      <c r="C451">
+        <v>0</v>
+      </c>
+      <c r="D451">
+        <v>66</v>
+      </c>
+      <c r="E451" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="2">
+        <v>46146.6875</v>
+      </c>
+      <c r="B452">
+        <v>1618.514</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+      <c r="D452">
+        <v>67</v>
+      </c>
+      <c r="E452" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="2">
+        <v>46146.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>1451.726</v>
+      </c>
+      <c r="C453">
+        <v>0</v>
+      </c>
+      <c r="D453">
+        <v>68</v>
+      </c>
+      <c r="E453" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="2">
+        <v>46146.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>1198.796</v>
+      </c>
+      <c r="C454">
+        <v>0</v>
+      </c>
+      <c r="D454">
+        <v>69</v>
+      </c>
+      <c r="E454" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="2">
+        <v>46146.71875</v>
+      </c>
+      <c r="B455">
+        <v>1017.102</v>
+      </c>
+      <c r="C455">
+        <v>0</v>
+      </c>
+      <c r="D455">
+        <v>70</v>
+      </c>
+      <c r="E455" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="2">
+        <v>46146.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>843.522</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456">
+        <v>71</v>
+      </c>
+      <c r="E456" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="2">
+        <v>46146.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>696.808</v>
+      </c>
+      <c r="C457">
+        <v>0</v>
+      </c>
+      <c r="D457">
+        <v>72</v>
+      </c>
+      <c r="E457" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="2">
+        <v>46146.75</v>
+      </c>
+      <c r="B458">
+        <v>476.63</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458">
+        <v>73</v>
+      </c>
+      <c r="E458" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="2">
+        <v>46146.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>356.905</v>
+      </c>
+      <c r="C459">
+        <v>0</v>
+      </c>
+      <c r="D459">
+        <v>74</v>
+      </c>
+      <c r="E459" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="2">
+        <v>46146.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>257.285</v>
+      </c>
+      <c r="C460">
+        <v>0</v>
+      </c>
+      <c r="D460">
+        <v>75</v>
+      </c>
+      <c r="E460" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="2">
+        <v>46146.78125</v>
+      </c>
+      <c r="B461">
+        <v>177.694</v>
+      </c>
+      <c r="C461">
+        <v>0</v>
+      </c>
+      <c r="D461">
+        <v>76</v>
+      </c>
+      <c r="E461" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="2">
+        <v>46146.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>88.974</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462">
+        <v>77</v>
+      </c>
+      <c r="E462" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="2">
+        <v>46146.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>53.093</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+      <c r="D463">
+        <v>78</v>
+      </c>
+      <c r="E463" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="2">
+        <v>46146.8125</v>
+      </c>
+      <c r="B464">
+        <v>35.613</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464">
+        <v>79</v>
+      </c>
+      <c r="E464" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="2">
+        <v>46146.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>28.517</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+      <c r="D465">
+        <v>80</v>
+      </c>
+      <c r="E465" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="2">
+        <v>46146.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>18.807</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466">
+        <v>81</v>
+      </c>
+      <c r="E466" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="2">
+        <v>46146.84375</v>
+      </c>
+      <c r="B467">
+        <v>18.782</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+      <c r="D467">
+        <v>82</v>
+      </c>
+      <c r="E467" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="2">
+        <v>46146.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>18.404</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+      <c r="D468">
+        <v>83</v>
+      </c>
+      <c r="E468" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="2">
+        <v>46146.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>18.103</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+      <c r="D469">
+        <v>84</v>
+      </c>
+      <c r="E469" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="2">
+        <v>46146.875</v>
+      </c>
+      <c r="B470">
+        <v>13.83</v>
+      </c>
+      <c r="C470">
+        <v>0</v>
+      </c>
+      <c r="D470">
+        <v>85</v>
+      </c>
+      <c r="E470" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="2">
+        <v>46146.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>13.53</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471">
+        <v>86</v>
+      </c>
+      <c r="E471" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" s="2">
+        <v>46146.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>10.83</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472">
+        <v>87</v>
+      </c>
+      <c r="E472" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" s="2">
+        <v>46146.90625</v>
+      </c>
+      <c r="B473">
+        <v>10.23</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473">
+        <v>88</v>
+      </c>
+      <c r="E473" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" s="2">
+        <v>46146.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>9.73</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474">
+        <v>89</v>
+      </c>
+      <c r="E474" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" s="2">
+        <v>46146.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>2.73</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
+      </c>
+      <c r="D475">
+        <v>90</v>
+      </c>
+      <c r="E475" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" s="2">
+        <v>46146.9375</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+      <c r="D476">
+        <v>91</v>
+      </c>
+      <c r="E476" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" s="2">
+        <v>46146.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+      <c r="C477">
+        <v>0</v>
+      </c>
+      <c r="D477">
+        <v>92</v>
+      </c>
+      <c r="E477" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478" s="2">
+        <v>46146.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+      <c r="D478">
+        <v>93</v>
+      </c>
+      <c r="E478" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479" s="2">
+        <v>46146.96875</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+      <c r="D479">
+        <v>94</v>
+      </c>
+      <c r="E479" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480" s="2">
+        <v>46146.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+      <c r="C480">
+        <v>0</v>
+      </c>
+      <c r="D480">
+        <v>95</v>
+      </c>
+      <c r="E480" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481" s="2">
+        <v>46146.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+      <c r="D481">
+        <v>96</v>
+      </c>
+      <c r="E481" t="s">
+        <v>484</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>05.05.20261</t>
-  </si>
-  <si>
-    <t>05.05.20262</t>
-  </si>
-  <si>
-    <t>05.05.20263</t>
-  </si>
-  <si>
-    <t>05.05.20264</t>
-  </si>
-  <si>
-    <t>05.05.20265</t>
-  </si>
-  <si>
-    <t>05.05.20266</t>
-  </si>
-  <si>
-    <t>05.05.20267</t>
-  </si>
-  <si>
-    <t>05.05.20268</t>
-  </si>
-  <si>
-    <t>05.05.20269</t>
-  </si>
-  <si>
-    <t>05.05.202610</t>
-  </si>
-  <si>
-    <t>05.05.202611</t>
-  </si>
-  <si>
-    <t>05.05.202612</t>
-  </si>
-  <si>
-    <t>05.05.202613</t>
-  </si>
-  <si>
-    <t>05.05.202614</t>
-  </si>
-  <si>
-    <t>05.05.202615</t>
-  </si>
-  <si>
-    <t>05.05.202616</t>
-  </si>
-  <si>
-    <t>05.05.202617</t>
-  </si>
-  <si>
-    <t>05.05.202618</t>
-  </si>
-  <si>
-    <t>05.05.202619</t>
-  </si>
-  <si>
-    <t>05.05.202620</t>
-  </si>
-  <si>
-    <t>05.05.202621</t>
-  </si>
-  <si>
-    <t>05.05.202622</t>
-  </si>
-  <si>
-    <t>05.05.202623</t>
-  </si>
-  <si>
-    <t>05.05.202624</t>
-  </si>
-  <si>
-    <t>05.05.202625</t>
-  </si>
-  <si>
-    <t>05.05.202626</t>
-  </si>
-  <si>
-    <t>05.05.202627</t>
-  </si>
-  <si>
-    <t>05.05.202628</t>
-  </si>
-  <si>
-    <t>05.05.202629</t>
-  </si>
-  <si>
-    <t>05.05.202630</t>
-  </si>
-  <si>
-    <t>05.05.202631</t>
-  </si>
-  <si>
-    <t>05.05.202632</t>
-  </si>
-  <si>
-    <t>05.05.202633</t>
-  </si>
-  <si>
-    <t>05.05.202634</t>
-  </si>
-  <si>
-    <t>05.05.202635</t>
-  </si>
-  <si>
-    <t>05.05.202636</t>
-  </si>
-  <si>
-    <t>05.05.202637</t>
-  </si>
-  <si>
-    <t>05.05.202638</t>
-  </si>
-  <si>
-    <t>05.05.202639</t>
-  </si>
-  <si>
-    <t>05.05.202640</t>
-  </si>
-  <si>
-    <t>05.05.202641</t>
-  </si>
-  <si>
-    <t>05.05.202642</t>
-  </si>
-  <si>
-    <t>05.05.202643</t>
-  </si>
-  <si>
-    <t>05.05.202644</t>
-  </si>
-  <si>
-    <t>05.05.202645</t>
-  </si>
-  <si>
-    <t>05.05.202646</t>
-  </si>
-  <si>
-    <t>05.05.202647</t>
-  </si>
-  <si>
-    <t>05.05.202648</t>
-  </si>
-  <si>
-    <t>05.05.202649</t>
-  </si>
-  <si>
-    <t>05.05.202650</t>
-  </si>
-  <si>
-    <t>05.05.202651</t>
-  </si>
-  <si>
-    <t>05.05.202652</t>
-  </si>
-  <si>
-    <t>05.05.202653</t>
-  </si>
-  <si>
-    <t>05.05.202654</t>
-  </si>
-  <si>
-    <t>05.05.202655</t>
-  </si>
-  <si>
-    <t>05.05.202656</t>
-  </si>
-  <si>
-    <t>05.05.202657</t>
-  </si>
-  <si>
-    <t>05.05.202658</t>
-  </si>
-  <si>
-    <t>05.05.202659</t>
-  </si>
-  <si>
-    <t>05.05.202660</t>
-  </si>
-  <si>
-    <t>05.05.202661</t>
-  </si>
-  <si>
-    <t>05.05.202662</t>
-  </si>
-  <si>
-    <t>05.05.202663</t>
-  </si>
-  <si>
-    <t>05.05.202664</t>
-  </si>
-  <si>
-    <t>05.05.202665</t>
-  </si>
-  <si>
-    <t>05.05.202666</t>
-  </si>
-  <si>
-    <t>05.05.202667</t>
-  </si>
-  <si>
-    <t>05.05.202668</t>
-  </si>
-  <si>
-    <t>05.05.202669</t>
-  </si>
-  <si>
-    <t>05.05.202670</t>
-  </si>
-  <si>
-    <t>05.05.202671</t>
-  </si>
-  <si>
-    <t>05.05.202672</t>
-  </si>
-  <si>
-    <t>05.05.202673</t>
-  </si>
-  <si>
-    <t>05.05.202674</t>
-  </si>
-  <si>
-    <t>05.05.202675</t>
-  </si>
-  <si>
-    <t>05.05.202676</t>
-  </si>
-  <si>
-    <t>05.05.202677</t>
-  </si>
-  <si>
-    <t>05.05.202678</t>
-  </si>
-  <si>
-    <t>05.05.202679</t>
-  </si>
-  <si>
-    <t>05.05.202680</t>
-  </si>
-  <si>
-    <t>05.05.202681</t>
-  </si>
-  <si>
-    <t>05.05.202682</t>
-  </si>
-  <si>
-    <t>05.05.202683</t>
-  </si>
-  <si>
-    <t>05.05.202684</t>
-  </si>
-  <si>
-    <t>05.05.202685</t>
-  </si>
-  <si>
-    <t>05.05.202686</t>
-  </si>
-  <si>
-    <t>05.05.202687</t>
-  </si>
-  <si>
-    <t>05.05.202688</t>
-  </si>
-  <si>
-    <t>05.05.202689</t>
-  </si>
-  <si>
-    <t>05.05.202690</t>
-  </si>
-  <si>
-    <t>05.05.202691</t>
-  </si>
-  <si>
-    <t>05.05.202692</t>
-  </si>
-  <si>
-    <t>05.05.202693</t>
-  </si>
-  <si>
-    <t>05.05.202694</t>
-  </si>
-  <si>
-    <t>05.05.202695</t>
-  </si>
-  <si>
-    <t>05.05.202696</t>
-  </si>
-  <si>
-    <t>06.05.20261</t>
-  </si>
-  <si>
-    <t>06.05.20262</t>
-  </si>
-  <si>
-    <t>06.05.20263</t>
-  </si>
-  <si>
-    <t>06.05.20264</t>
-  </si>
-  <si>
-    <t>06.05.20265</t>
-  </si>
-  <si>
-    <t>06.05.20266</t>
-  </si>
-  <si>
-    <t>06.05.20267</t>
-  </si>
-  <si>
-    <t>06.05.20268</t>
-  </si>
-  <si>
-    <t>06.05.20269</t>
-  </si>
-  <si>
-    <t>06.05.202610</t>
-  </si>
-  <si>
-    <t>06.05.202611</t>
-  </si>
-  <si>
-    <t>06.05.202612</t>
-  </si>
-  <si>
-    <t>06.05.202613</t>
-  </si>
-  <si>
-    <t>06.05.202614</t>
-  </si>
-  <si>
-    <t>06.05.202615</t>
-  </si>
-  <si>
-    <t>06.05.202616</t>
-  </si>
-  <si>
-    <t>06.05.202617</t>
-  </si>
-  <si>
-    <t>06.05.202618</t>
-  </si>
-  <si>
-    <t>06.05.202619</t>
-  </si>
-  <si>
-    <t>06.05.202620</t>
-  </si>
-  <si>
-    <t>06.05.202621</t>
-  </si>
-  <si>
-    <t>06.05.202622</t>
-  </si>
-  <si>
-    <t>06.05.202623</t>
-  </si>
-  <si>
-    <t>06.05.202624</t>
-  </si>
-  <si>
-    <t>06.05.202625</t>
-  </si>
-  <si>
-    <t>06.05.202626</t>
-  </si>
-  <si>
-    <t>06.05.202627</t>
-  </si>
-  <si>
-    <t>06.05.202628</t>
-  </si>
-  <si>
-    <t>06.05.202629</t>
-  </si>
-  <si>
-    <t>06.05.202630</t>
-  </si>
-  <si>
-    <t>06.05.202631</t>
-  </si>
-  <si>
-    <t>06.05.202632</t>
-  </si>
-  <si>
-    <t>06.05.202633</t>
-  </si>
-  <si>
-    <t>06.05.202634</t>
-  </si>
-  <si>
-    <t>06.05.202635</t>
-  </si>
-  <si>
-    <t>06.05.202636</t>
-  </si>
-  <si>
-    <t>06.05.202637</t>
-  </si>
-  <si>
-    <t>06.05.202638</t>
-  </si>
-  <si>
-    <t>06.05.202639</t>
-  </si>
-  <si>
-    <t>06.05.202640</t>
-  </si>
-  <si>
-    <t>06.05.202641</t>
-  </si>
-  <si>
-    <t>06.05.202642</t>
-  </si>
-  <si>
-    <t>06.05.202643</t>
-  </si>
-  <si>
-    <t>06.05.202644</t>
-  </si>
-  <si>
-    <t>06.05.202645</t>
-  </si>
-  <si>
-    <t>06.05.202646</t>
-  </si>
-  <si>
-    <t>06.05.202647</t>
-  </si>
-  <si>
-    <t>06.05.202648</t>
-  </si>
-  <si>
-    <t>06.05.202649</t>
-  </si>
-  <si>
-    <t>06.05.202650</t>
-  </si>
-  <si>
-    <t>06.05.202651</t>
-  </si>
-  <si>
-    <t>06.05.202652</t>
-  </si>
-  <si>
-    <t>06.05.202653</t>
-  </si>
-  <si>
-    <t>06.05.202654</t>
-  </si>
-  <si>
-    <t>06.05.202655</t>
-  </si>
-  <si>
-    <t>06.05.202656</t>
-  </si>
-  <si>
-    <t>06.05.202657</t>
-  </si>
-  <si>
-    <t>06.05.202658</t>
-  </si>
-  <si>
-    <t>06.05.202659</t>
-  </si>
-  <si>
-    <t>06.05.202660</t>
-  </si>
-  <si>
-    <t>06.05.202661</t>
-  </si>
-  <si>
-    <t>06.05.202662</t>
-  </si>
-  <si>
-    <t>06.05.202663</t>
-  </si>
-  <si>
-    <t>06.05.202664</t>
-  </si>
-  <si>
-    <t>06.05.202665</t>
-  </si>
-  <si>
-    <t>06.05.202666</t>
-  </si>
-  <si>
-    <t>06.05.202667</t>
-  </si>
-  <si>
-    <t>06.05.202668</t>
-  </si>
-  <si>
-    <t>06.05.202669</t>
-  </si>
-  <si>
-    <t>06.05.202670</t>
-  </si>
-  <si>
-    <t>06.05.202671</t>
-  </si>
-  <si>
-    <t>06.05.202672</t>
-  </si>
-  <si>
-    <t>06.05.202673</t>
-  </si>
-  <si>
-    <t>06.05.202674</t>
-  </si>
-  <si>
-    <t>06.05.202675</t>
-  </si>
-  <si>
-    <t>06.05.202676</t>
-  </si>
-  <si>
-    <t>06.05.202677</t>
-  </si>
-  <si>
-    <t>06.05.202678</t>
-  </si>
-  <si>
-    <t>06.05.202679</t>
-  </si>
-  <si>
-    <t>06.05.202680</t>
-  </si>
-  <si>
-    <t>06.05.202681</t>
-  </si>
-  <si>
-    <t>06.05.202682</t>
-  </si>
-  <si>
-    <t>06.05.202683</t>
-  </si>
-  <si>
-    <t>06.05.202684</t>
-  </si>
-  <si>
-    <t>06.05.202685</t>
-  </si>
-  <si>
-    <t>06.05.202686</t>
-  </si>
-  <si>
-    <t>06.05.202687</t>
-  </si>
-  <si>
-    <t>06.05.202688</t>
-  </si>
-  <si>
-    <t>06.05.202689</t>
-  </si>
-  <si>
-    <t>06.05.202690</t>
-  </si>
-  <si>
-    <t>06.05.202691</t>
-  </si>
-  <si>
-    <t>06.05.202692</t>
-  </si>
-  <si>
-    <t>06.05.202693</t>
-  </si>
-  <si>
-    <t>06.05.202694</t>
-  </si>
-  <si>
-    <t>06.05.202695</t>
-  </si>
-  <si>
-    <t>06.05.202696</t>
+    <t>07.05.20261</t>
+  </si>
+  <si>
+    <t>07.05.20262</t>
+  </si>
+  <si>
+    <t>07.05.20263</t>
+  </si>
+  <si>
+    <t>07.05.20264</t>
+  </si>
+  <si>
+    <t>07.05.20265</t>
+  </si>
+  <si>
+    <t>07.05.20266</t>
+  </si>
+  <si>
+    <t>07.05.20267</t>
+  </si>
+  <si>
+    <t>07.05.20268</t>
+  </si>
+  <si>
+    <t>07.05.20269</t>
+  </si>
+  <si>
+    <t>07.05.202610</t>
+  </si>
+  <si>
+    <t>07.05.202611</t>
+  </si>
+  <si>
+    <t>07.05.202612</t>
+  </si>
+  <si>
+    <t>07.05.202613</t>
+  </si>
+  <si>
+    <t>07.05.202614</t>
+  </si>
+  <si>
+    <t>07.05.202615</t>
+  </si>
+  <si>
+    <t>07.05.202616</t>
+  </si>
+  <si>
+    <t>07.05.202617</t>
+  </si>
+  <si>
+    <t>07.05.202618</t>
+  </si>
+  <si>
+    <t>07.05.202619</t>
+  </si>
+  <si>
+    <t>07.05.202620</t>
+  </si>
+  <si>
+    <t>07.05.202621</t>
+  </si>
+  <si>
+    <t>07.05.202622</t>
+  </si>
+  <si>
+    <t>07.05.202623</t>
+  </si>
+  <si>
+    <t>07.05.202624</t>
+  </si>
+  <si>
+    <t>07.05.202625</t>
+  </si>
+  <si>
+    <t>07.05.202626</t>
+  </si>
+  <si>
+    <t>07.05.202627</t>
+  </si>
+  <si>
+    <t>07.05.202628</t>
+  </si>
+  <si>
+    <t>07.05.202629</t>
+  </si>
+  <si>
+    <t>07.05.202630</t>
+  </si>
+  <si>
+    <t>07.05.202631</t>
+  </si>
+  <si>
+    <t>07.05.202632</t>
+  </si>
+  <si>
+    <t>07.05.202633</t>
+  </si>
+  <si>
+    <t>07.05.202634</t>
+  </si>
+  <si>
+    <t>07.05.202635</t>
+  </si>
+  <si>
+    <t>07.05.202636</t>
+  </si>
+  <si>
+    <t>07.05.202637</t>
+  </si>
+  <si>
+    <t>07.05.202638</t>
+  </si>
+  <si>
+    <t>07.05.202639</t>
+  </si>
+  <si>
+    <t>07.05.202640</t>
+  </si>
+  <si>
+    <t>07.05.202641</t>
+  </si>
+  <si>
+    <t>07.05.202642</t>
+  </si>
+  <si>
+    <t>07.05.202643</t>
+  </si>
+  <si>
+    <t>07.05.202644</t>
+  </si>
+  <si>
+    <t>07.05.202645</t>
+  </si>
+  <si>
+    <t>07.05.202646</t>
+  </si>
+  <si>
+    <t>07.05.202647</t>
+  </si>
+  <si>
+    <t>07.05.202648</t>
+  </si>
+  <si>
+    <t>07.05.202649</t>
+  </si>
+  <si>
+    <t>07.05.202650</t>
+  </si>
+  <si>
+    <t>07.05.202651</t>
+  </si>
+  <si>
+    <t>07.05.202652</t>
+  </si>
+  <si>
+    <t>07.05.202653</t>
+  </si>
+  <si>
+    <t>07.05.202654</t>
+  </si>
+  <si>
+    <t>07.05.202655</t>
+  </si>
+  <si>
+    <t>07.05.202656</t>
+  </si>
+  <si>
+    <t>07.05.202657</t>
+  </si>
+  <si>
+    <t>07.05.202658</t>
+  </si>
+  <si>
+    <t>07.05.202659</t>
+  </si>
+  <si>
+    <t>07.05.202660</t>
+  </si>
+  <si>
+    <t>07.05.202661</t>
+  </si>
+  <si>
+    <t>07.05.202662</t>
+  </si>
+  <si>
+    <t>07.05.202663</t>
+  </si>
+  <si>
+    <t>07.05.202664</t>
+  </si>
+  <si>
+    <t>07.05.202665</t>
+  </si>
+  <si>
+    <t>07.05.202666</t>
+  </si>
+  <si>
+    <t>07.05.202667</t>
+  </si>
+  <si>
+    <t>07.05.202668</t>
+  </si>
+  <si>
+    <t>07.05.202669</t>
+  </si>
+  <si>
+    <t>07.05.202670</t>
+  </si>
+  <si>
+    <t>07.05.202671</t>
+  </si>
+  <si>
+    <t>07.05.202672</t>
+  </si>
+  <si>
+    <t>07.05.202673</t>
+  </si>
+  <si>
+    <t>07.05.202674</t>
+  </si>
+  <si>
+    <t>07.05.202675</t>
+  </si>
+  <si>
+    <t>07.05.202676</t>
+  </si>
+  <si>
+    <t>07.05.202677</t>
+  </si>
+  <si>
+    <t>07.05.202678</t>
+  </si>
+  <si>
+    <t>07.05.202679</t>
+  </si>
+  <si>
+    <t>07.05.202680</t>
+  </si>
+  <si>
+    <t>07.05.202681</t>
+  </si>
+  <si>
+    <t>07.05.202682</t>
+  </si>
+  <si>
+    <t>07.05.202683</t>
+  </si>
+  <si>
+    <t>07.05.202684</t>
+  </si>
+  <si>
+    <t>07.05.202685</t>
+  </si>
+  <si>
+    <t>07.05.202686</t>
+  </si>
+  <si>
+    <t>07.05.202687</t>
+  </si>
+  <si>
+    <t>07.05.202688</t>
+  </si>
+  <si>
+    <t>07.05.202689</t>
+  </si>
+  <si>
+    <t>07.05.202690</t>
+  </si>
+  <si>
+    <t>07.05.202691</t>
+  </si>
+  <si>
+    <t>07.05.202692</t>
+  </si>
+  <si>
+    <t>07.05.202693</t>
+  </si>
+  <si>
+    <t>07.05.202694</t>
+  </si>
+  <si>
+    <t>07.05.202695</t>
+  </si>
+  <si>
+    <t>07.05.202696</t>
+  </si>
+  <si>
+    <t>08.05.20261</t>
+  </si>
+  <si>
+    <t>08.05.20262</t>
+  </si>
+  <si>
+    <t>08.05.20263</t>
+  </si>
+  <si>
+    <t>08.05.20264</t>
+  </si>
+  <si>
+    <t>08.05.20265</t>
+  </si>
+  <si>
+    <t>08.05.20266</t>
+  </si>
+  <si>
+    <t>08.05.20267</t>
+  </si>
+  <si>
+    <t>08.05.20268</t>
+  </si>
+  <si>
+    <t>08.05.20269</t>
+  </si>
+  <si>
+    <t>08.05.202610</t>
+  </si>
+  <si>
+    <t>08.05.202611</t>
+  </si>
+  <si>
+    <t>08.05.202612</t>
+  </si>
+  <si>
+    <t>08.05.202613</t>
+  </si>
+  <si>
+    <t>08.05.202614</t>
+  </si>
+  <si>
+    <t>08.05.202615</t>
+  </si>
+  <si>
+    <t>08.05.202616</t>
+  </si>
+  <si>
+    <t>08.05.202617</t>
+  </si>
+  <si>
+    <t>08.05.202618</t>
+  </si>
+  <si>
+    <t>08.05.202619</t>
+  </si>
+  <si>
+    <t>08.05.202620</t>
+  </si>
+  <si>
+    <t>08.05.202621</t>
+  </si>
+  <si>
+    <t>08.05.202622</t>
+  </si>
+  <si>
+    <t>08.05.202623</t>
+  </si>
+  <si>
+    <t>08.05.202624</t>
+  </si>
+  <si>
+    <t>08.05.202625</t>
+  </si>
+  <si>
+    <t>08.05.202626</t>
+  </si>
+  <si>
+    <t>08.05.202627</t>
+  </si>
+  <si>
+    <t>08.05.202628</t>
+  </si>
+  <si>
+    <t>08.05.202629</t>
+  </si>
+  <si>
+    <t>08.05.202630</t>
+  </si>
+  <si>
+    <t>08.05.202631</t>
+  </si>
+  <si>
+    <t>08.05.202632</t>
+  </si>
+  <si>
+    <t>08.05.202633</t>
+  </si>
+  <si>
+    <t>08.05.202634</t>
+  </si>
+  <si>
+    <t>08.05.202635</t>
+  </si>
+  <si>
+    <t>08.05.202636</t>
+  </si>
+  <si>
+    <t>08.05.202637</t>
+  </si>
+  <si>
+    <t>08.05.202638</t>
+  </si>
+  <si>
+    <t>08.05.202639</t>
+  </si>
+  <si>
+    <t>08.05.202640</t>
+  </si>
+  <si>
+    <t>08.05.202641</t>
+  </si>
+  <si>
+    <t>08.05.202642</t>
+  </si>
+  <si>
+    <t>08.05.202643</t>
+  </si>
+  <si>
+    <t>08.05.202644</t>
+  </si>
+  <si>
+    <t>08.05.202645</t>
+  </si>
+  <si>
+    <t>08.05.202646</t>
+  </si>
+  <si>
+    <t>08.05.202647</t>
+  </si>
+  <si>
+    <t>08.05.202648</t>
+  </si>
+  <si>
+    <t>08.05.202649</t>
+  </si>
+  <si>
+    <t>08.05.202650</t>
+  </si>
+  <si>
+    <t>08.05.202651</t>
+  </si>
+  <si>
+    <t>08.05.202652</t>
+  </si>
+  <si>
+    <t>08.05.202653</t>
+  </si>
+  <si>
+    <t>08.05.202654</t>
+  </si>
+  <si>
+    <t>08.05.202655</t>
+  </si>
+  <si>
+    <t>08.05.202656</t>
+  </si>
+  <si>
+    <t>08.05.202657</t>
+  </si>
+  <si>
+    <t>08.05.202658</t>
+  </si>
+  <si>
+    <t>08.05.202659</t>
+  </si>
+  <si>
+    <t>08.05.202660</t>
+  </si>
+  <si>
+    <t>08.05.202661</t>
+  </si>
+  <si>
+    <t>08.05.202662</t>
+  </si>
+  <si>
+    <t>08.05.202663</t>
+  </si>
+  <si>
+    <t>08.05.202664</t>
+  </si>
+  <si>
+    <t>08.05.202665</t>
+  </si>
+  <si>
+    <t>08.05.202666</t>
+  </si>
+  <si>
+    <t>08.05.202667</t>
+  </si>
+  <si>
+    <t>08.05.202668</t>
+  </si>
+  <si>
+    <t>08.05.202669</t>
+  </si>
+  <si>
+    <t>08.05.202670</t>
+  </si>
+  <si>
+    <t>08.05.202671</t>
+  </si>
+  <si>
+    <t>08.05.202672</t>
+  </si>
+  <si>
+    <t>08.05.202673</t>
+  </si>
+  <si>
+    <t>08.05.202674</t>
+  </si>
+  <si>
+    <t>08.05.202675</t>
+  </si>
+  <si>
+    <t>08.05.202676</t>
+  </si>
+  <si>
+    <t>08.05.202677</t>
+  </si>
+  <si>
+    <t>08.05.202678</t>
+  </si>
+  <si>
+    <t>08.05.202679</t>
+  </si>
+  <si>
+    <t>08.05.202680</t>
+  </si>
+  <si>
+    <t>08.05.202681</t>
+  </si>
+  <si>
+    <t>08.05.202682</t>
+  </si>
+  <si>
+    <t>08.05.202683</t>
+  </si>
+  <si>
+    <t>08.05.202684</t>
+  </si>
+  <si>
+    <t>08.05.202685</t>
+  </si>
+  <si>
+    <t>08.05.202686</t>
+  </si>
+  <si>
+    <t>08.05.202687</t>
+  </si>
+  <si>
+    <t>08.05.202688</t>
+  </si>
+  <si>
+    <t>08.05.202689</t>
+  </si>
+  <si>
+    <t>08.05.202690</t>
+  </si>
+  <si>
+    <t>08.05.202691</t>
+  </si>
+  <si>
+    <t>08.05.202692</t>
+  </si>
+  <si>
+    <t>08.05.202693</t>
+  </si>
+  <si>
+    <t>08.05.202694</t>
+  </si>
+  <si>
+    <t>08.05.202695</t>
+  </si>
+  <si>
+    <t>08.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46147.01041666666</v>
+        <v>46149.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46147.02083333334</v>
+        <v>46149.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46147.03125</v>
+        <v>46149.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46147.04166666666</v>
+        <v>46149.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46147.05208333334</v>
+        <v>46149.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46147.0625</v>
+        <v>46149.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46147.07291666666</v>
+        <v>46149.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46147.08333333334</v>
+        <v>46149.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46147.09375</v>
+        <v>46149.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46147.10416666666</v>
+        <v>46149.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46147.11458333334</v>
+        <v>46149.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46147.125</v>
+        <v>46149.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46147.13541666666</v>
+        <v>46149.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46147.14583333334</v>
+        <v>46149.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46147.15625</v>
+        <v>46149.15625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46147.16666666666</v>
+        <v>46149.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46147.17708333334</v>
+        <v>46149.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.734</v>
+        <v>0.834</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46147.1875</v>
+        <v>46149.1875</v>
       </c>
       <c r="B20">
-        <v>0.8129999999999999</v>
+        <v>0.874</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46147.19791666666</v>
+        <v>46149.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.87</v>
+        <v>1.5</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46147.20833333334</v>
+        <v>46149.20833333334</v>
       </c>
       <c r="B22">
-        <v>13.329</v>
+        <v>12.517</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46147.21875</v>
+        <v>46149.21875</v>
       </c>
       <c r="B23">
-        <v>38.023</v>
+        <v>40.139</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46147.22916666666</v>
+        <v>46149.22916666666</v>
       </c>
       <c r="B24">
-        <v>84.23099999999999</v>
+        <v>79.848</v>
       </c>
       <c r="C24">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46147.23958333334</v>
+        <v>46149.23958333334</v>
       </c>
       <c r="B25">
-        <v>149.334</v>
+        <v>139.467</v>
       </c>
       <c r="C25">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46147.25</v>
+        <v>46149.25</v>
       </c>
       <c r="B26">
-        <v>289.15</v>
+        <v>279.49</v>
       </c>
       <c r="C26">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46147.26041666666</v>
+        <v>46149.26041666666</v>
       </c>
       <c r="B27">
-        <v>428.008</v>
+        <v>384.303</v>
       </c>
       <c r="C27">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46147.27083333334</v>
+        <v>46149.27083333334</v>
       </c>
       <c r="B28">
-        <v>584.426</v>
+        <v>528.051</v>
       </c>
       <c r="C28">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46147.28125</v>
+        <v>46149.28125</v>
       </c>
       <c r="B29">
-        <v>766.715</v>
+        <v>685.346</v>
       </c>
       <c r="C29">
-        <v>617</v>
+        <v>590</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46147.29166666666</v>
+        <v>46149.29166666666</v>
       </c>
       <c r="B30">
-        <v>1119.353</v>
+        <v>917.466</v>
       </c>
       <c r="C30">
-        <v>796</v>
+        <v>668</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46147.30208333334</v>
+        <v>46149.30208333334</v>
       </c>
       <c r="B31">
-        <v>1332.944</v>
+        <v>1097.754</v>
       </c>
       <c r="C31">
-        <v>985</v>
+        <v>825</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46147.3125</v>
+        <v>46149.3125</v>
       </c>
       <c r="B32">
-        <v>1572.67</v>
+        <v>1301.922</v>
       </c>
       <c r="C32">
-        <v>1201</v>
+        <v>968</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46147.32291666666</v>
+        <v>46149.32291666666</v>
       </c>
       <c r="B33">
-        <v>1813.201</v>
+        <v>1470.915</v>
       </c>
       <c r="C33">
-        <v>1354</v>
+        <v>1123</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46147.33333333334</v>
+        <v>46149.33333333334</v>
       </c>
       <c r="B34">
-        <v>2094</v>
+        <v>1736.635</v>
       </c>
       <c r="C34">
-        <v>1529</v>
+        <v>1254</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46147.34375</v>
+        <v>46149.34375</v>
       </c>
       <c r="B35">
-        <v>2285.466</v>
+        <v>1886.013</v>
       </c>
       <c r="C35">
-        <v>1647</v>
+        <v>1359</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46147.35416666666</v>
+        <v>46149.35416666666</v>
       </c>
       <c r="B36">
-        <v>2461.065</v>
+        <v>2025.409</v>
       </c>
       <c r="C36">
-        <v>1761</v>
+        <v>1424</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46147.36458333334</v>
+        <v>46149.36458333334</v>
       </c>
       <c r="B37">
-        <v>2643.871</v>
+        <v>2184.932</v>
       </c>
       <c r="C37">
-        <v>1883</v>
+        <v>1462</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46147.375</v>
+        <v>46149.375</v>
       </c>
       <c r="B38">
-        <v>2826.256</v>
+        <v>2311.835</v>
       </c>
       <c r="C38">
-        <v>1966</v>
+        <v>1490</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46147.38541666666</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="B39">
-        <v>2933.205</v>
+        <v>2414.147</v>
       </c>
       <c r="C39">
-        <v>2061</v>
+        <v>1542</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46147.39583333334</v>
+        <v>46149.39583333334</v>
       </c>
       <c r="B40">
-        <v>3014.191</v>
+        <v>2497.264</v>
       </c>
       <c r="C40">
-        <v>2124</v>
+        <v>1535</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46147.40625</v>
+        <v>46149.40625</v>
       </c>
       <c r="B41">
-        <v>3092.189</v>
+        <v>2578.43</v>
       </c>
       <c r="C41">
-        <v>2184</v>
+        <v>1576</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46147.41666666666</v>
+        <v>46149.41666666666</v>
       </c>
       <c r="B42">
-        <v>3203.237</v>
+        <v>2639.63</v>
       </c>
       <c r="C42">
-        <v>2232</v>
+        <v>1581</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46147.42708333334</v>
+        <v>46149.42708333334</v>
       </c>
       <c r="B43">
-        <v>3254.293</v>
+        <v>2688.046</v>
       </c>
       <c r="C43">
-        <v>2286</v>
+        <v>1662</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46147.4375</v>
+        <v>46149.4375</v>
       </c>
       <c r="B44">
-        <v>3300.811</v>
+        <v>2732.552</v>
       </c>
       <c r="C44">
-        <v>2337</v>
+        <v>1697</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46147.44791666666</v>
+        <v>46149.44791666666</v>
       </c>
       <c r="B45">
-        <v>3338.075</v>
+        <v>2761.378</v>
       </c>
       <c r="C45">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46147.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="B46">
-        <v>3380.988</v>
+        <v>2780.084</v>
       </c>
       <c r="C46">
-        <v>2381</v>
+        <v>1690</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46147.46875</v>
+        <v>46149.46875</v>
       </c>
       <c r="B47">
-        <v>3397.848</v>
+        <v>2783.548</v>
       </c>
       <c r="C47">
-        <v>2416</v>
+        <v>1749</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46147.47916666666</v>
+        <v>46149.47916666666</v>
       </c>
       <c r="B48">
-        <v>3410.704</v>
+        <v>2782.327</v>
       </c>
       <c r="C48">
-        <v>2431</v>
+        <v>1761</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46147.48958333334</v>
+        <v>46149.48958333334</v>
       </c>
       <c r="B49">
-        <v>3418.379</v>
+        <v>2772.081</v>
       </c>
       <c r="C49">
-        <v>2449</v>
+        <v>1776</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46147.5</v>
+        <v>46149.5</v>
       </c>
       <c r="B50">
-        <v>3398.884</v>
+        <v>2756.762</v>
       </c>
       <c r="C50">
-        <v>2344</v>
+        <v>1728</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46147.51041666666</v>
+        <v>46149.51041666666</v>
       </c>
       <c r="B51">
-        <v>3389.048</v>
+        <v>2740.852</v>
       </c>
       <c r="C51">
-        <v>2270</v>
+        <v>1720</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46147.52083333334</v>
+        <v>46149.52083333334</v>
       </c>
       <c r="B52">
-        <v>3378.685</v>
+        <v>2718.671</v>
       </c>
       <c r="C52">
-        <v>2248</v>
+        <v>1661</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46147.53125</v>
+        <v>46149.53125</v>
       </c>
       <c r="B53">
-        <v>3356.292</v>
+        <v>2691.493</v>
       </c>
       <c r="C53">
-        <v>2237</v>
+        <v>1680</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46147.54166666666</v>
+        <v>46149.54166666666</v>
       </c>
       <c r="B54">
-        <v>3342.289</v>
+        <v>2650.773</v>
       </c>
       <c r="C54">
-        <v>2228</v>
+        <v>1641</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46147.55208333334</v>
+        <v>46149.55208333334</v>
       </c>
       <c r="B55">
-        <v>3315.268</v>
+        <v>2600.583</v>
       </c>
       <c r="C55">
-        <v>2207</v>
+        <v>1618</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46147.5625</v>
+        <v>46149.5625</v>
       </c>
       <c r="B56">
-        <v>3288.024</v>
+        <v>2550.548</v>
       </c>
       <c r="C56">
-        <v>2179</v>
+        <v>1548</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46147.57291666666</v>
+        <v>46149.57291666666</v>
       </c>
       <c r="B57">
-        <v>3242.998</v>
+        <v>2483.976</v>
       </c>
       <c r="C57">
-        <v>2159</v>
+        <v>1546</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46147.58333333334</v>
+        <v>46149.58333333334</v>
       </c>
       <c r="B58">
-        <v>3153.391</v>
+        <v>2365.77</v>
       </c>
       <c r="C58">
-        <v>2190</v>
+        <v>1466</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46147.59375</v>
+        <v>46149.59375</v>
       </c>
       <c r="B59">
-        <v>3099.903</v>
+        <v>2289.439</v>
       </c>
       <c r="C59">
-        <v>2199</v>
+        <v>1390</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46147.60416666666</v>
+        <v>46149.60416666666</v>
       </c>
       <c r="B60">
-        <v>3030.485</v>
+        <v>2197.202</v>
       </c>
       <c r="C60">
-        <v>2203</v>
+        <v>1381</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46147.61458333334</v>
+        <v>46149.61458333334</v>
       </c>
       <c r="B61">
-        <v>2959.981</v>
+        <v>2109.276</v>
       </c>
       <c r="C61">
-        <v>2143</v>
+        <v>1282</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46147.625</v>
+        <v>46149.625</v>
       </c>
       <c r="B62">
-        <v>2810.994</v>
+        <v>1950.187</v>
       </c>
       <c r="C62">
-        <v>2118</v>
+        <v>1172</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46147.63541666666</v>
+        <v>46149.63541666666</v>
       </c>
       <c r="B63">
-        <v>2716.362</v>
+        <v>1810.548</v>
       </c>
       <c r="C63">
-        <v>1984</v>
+        <v>1052</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46147.64583333334</v>
+        <v>46149.64583333334</v>
       </c>
       <c r="B64">
-        <v>2606.537</v>
+        <v>1701.821</v>
       </c>
       <c r="C64">
-        <v>1892</v>
+        <v>989</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46147.65625</v>
+        <v>46149.65625</v>
       </c>
       <c r="B65">
-        <v>2471.708</v>
+        <v>1572.192</v>
       </c>
       <c r="C65">
-        <v>1809</v>
+        <v>923</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46147.66666666666</v>
+        <v>46149.66666666666</v>
       </c>
       <c r="B66">
-        <v>2257.446</v>
+        <v>1384.776</v>
       </c>
       <c r="C66">
-        <v>1668</v>
+        <v>842</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46147.67708333334</v>
+        <v>46149.67708333334</v>
       </c>
       <c r="B67">
-        <v>2087.019</v>
+        <v>1228.815</v>
       </c>
       <c r="C67">
-        <v>1537</v>
+        <v>713</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46147.6875</v>
+        <v>46149.6875</v>
       </c>
       <c r="B68">
-        <v>1882.072</v>
+        <v>1072.049</v>
       </c>
       <c r="C68">
-        <v>1427</v>
+        <v>692</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46147.69791666666</v>
+        <v>46149.69791666666</v>
       </c>
       <c r="B69">
-        <v>1686.514</v>
+        <v>942.89</v>
       </c>
       <c r="C69">
-        <v>1273</v>
+        <v>603</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46147.70833333334</v>
+        <v>46149.70833333334</v>
       </c>
       <c r="B70">
-        <v>1385.01</v>
+        <v>732.215</v>
       </c>
       <c r="C70">
-        <v>1096</v>
+        <v>494</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46147.71875</v>
+        <v>46149.71875</v>
       </c>
       <c r="B71">
-        <v>1181.743</v>
+        <v>614.915</v>
       </c>
       <c r="C71">
-        <v>910</v>
+        <v>446</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46147.72916666666</v>
+        <v>46149.72916666666</v>
       </c>
       <c r="B72">
-        <v>995.646</v>
+        <v>507.925</v>
       </c>
       <c r="C72">
-        <v>750</v>
+        <v>365</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46147.73958333334</v>
+        <v>46149.73958333334</v>
       </c>
       <c r="B73">
-        <v>810.045</v>
+        <v>411.758</v>
       </c>
       <c r="C73">
-        <v>593</v>
+        <v>284</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46147.75</v>
+        <v>46149.75</v>
       </c>
       <c r="B74">
-        <v>533.694</v>
+        <v>267.075</v>
       </c>
       <c r="C74">
-        <v>426</v>
+        <v>206</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46147.76041666666</v>
+        <v>46149.76041666666</v>
       </c>
       <c r="B75">
-        <v>398.423</v>
+        <v>199.127</v>
       </c>
       <c r="C75">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46147.77083333334</v>
+        <v>46149.77083333334</v>
       </c>
       <c r="B76">
-        <v>284.943</v>
+        <v>139.032</v>
       </c>
       <c r="C76">
-        <v>176</v>
+        <v>117</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46147.78125</v>
+        <v>46149.78125</v>
       </c>
       <c r="B77">
-        <v>197.111</v>
+        <v>94.863</v>
       </c>
       <c r="C77">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46147.79166666666</v>
+        <v>46149.79166666666</v>
       </c>
       <c r="B78">
-        <v>94.581</v>
+        <v>49.03</v>
       </c>
       <c r="C78">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46147.80208333334</v>
+        <v>46149.80208333334</v>
       </c>
       <c r="B79">
-        <v>55.015</v>
+        <v>31.998</v>
       </c>
       <c r="C79">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46147.8125</v>
+        <v>46149.8125</v>
       </c>
       <c r="B80">
-        <v>34.609</v>
+        <v>24.535</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46147.82291666666</v>
+        <v>46149.82291666666</v>
       </c>
       <c r="B81">
-        <v>24.824</v>
+        <v>21.962</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46147.83333333334</v>
+        <v>46149.83333333334</v>
       </c>
       <c r="B82">
-        <v>15.003</v>
+        <v>15.595</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46147.84375</v>
+        <v>46149.84375</v>
       </c>
       <c r="B83">
-        <v>14.985</v>
+        <v>15.582</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46147.85416666666</v>
+        <v>46149.85416666666</v>
       </c>
       <c r="B84">
-        <v>14.212</v>
+        <v>15.199</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46147.86458333334</v>
+        <v>46149.86458333334</v>
       </c>
       <c r="B85">
-        <v>13.906</v>
+        <v>14.409</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46147.875</v>
+        <v>46149.875</v>
       </c>
       <c r="B86">
         <v>13.83</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46147.88541666666</v>
+        <v>46149.88541666666</v>
       </c>
       <c r="B87">
         <v>12.43</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46147.89583333334</v>
+        <v>46149.89583333334</v>
       </c>
       <c r="B88">
-        <v>5.83</v>
+        <v>9.33</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46147.90625</v>
+        <v>46149.90625</v>
       </c>
       <c r="B89">
-        <v>3.23</v>
+        <v>5.23</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46147.91666666666</v>
+        <v>46149.91666666666</v>
       </c>
       <c r="B90">
-        <v>4.73</v>
+        <v>8.23</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46147.92708333334</v>
+        <v>46149.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46147.9375</v>
+        <v>46149.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46147.94791666666</v>
+        <v>46149.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46147.95833333334</v>
+        <v>46149.95833333334</v>
       </c>
       <c r="B94">
-        <v>11.73</v>
+        <v>0</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46147.96875</v>
+        <v>46149.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46147.97916666666</v>
+        <v>46149.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46147.98958333334</v>
+        <v>46149.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B98">
-        <v>9.33</v>
+        <v>0</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B102">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B106">
-        <v>9.33</v>
+        <v>0</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B110">
-        <v>11.33</v>
+        <v>0</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B114">
-        <v>9.43</v>
+        <v>0.747</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B115">
-        <v>9.433999999999999</v>
+        <v>0</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B116">
-        <v>9.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B117">
-        <v>9.564</v>
+        <v>0.765</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B118">
-        <v>17.859</v>
+        <v>7.836</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B119">
-        <v>40.187</v>
+        <v>23.399</v>
       </c>
       <c r="C119">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B120">
-        <v>86.34099999999999</v>
+        <v>44.872</v>
       </c>
       <c r="C120">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B121">
-        <v>142.053</v>
+        <v>82.52800000000001</v>
       </c>
       <c r="C121">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B122">
-        <v>298.176</v>
+        <v>182.53</v>
       </c>
       <c r="C122">
-        <v>211</v>
+        <v>148</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B123">
-        <v>412.621</v>
+        <v>260.941</v>
       </c>
       <c r="C123">
-        <v>334</v>
+        <v>236</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B124">
-        <v>563.849</v>
+        <v>350.957</v>
       </c>
       <c r="C124">
-        <v>469</v>
+        <v>342</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B125">
-        <v>716.951</v>
+        <v>459.745</v>
       </c>
       <c r="C125">
-        <v>629</v>
+        <v>426</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B126">
-        <v>1045.779</v>
+        <v>671.236</v>
       </c>
       <c r="C126">
-        <v>786</v>
+        <v>538</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B127">
-        <v>1247.103</v>
+        <v>812.037</v>
       </c>
       <c r="C127">
-        <v>992</v>
+        <v>664</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B128">
-        <v>1466.356</v>
+        <v>952.691</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B129">
-        <v>1672.517</v>
+        <v>1099.473</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B130">
-        <v>1977.038</v>
+        <v>1313.734</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B131">
-        <v>2147.711</v>
+        <v>1454.803</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3198,10 +3198,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B132">
-        <v>2307.389</v>
+        <v>1602.397</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B133">
-        <v>2439.037</v>
+        <v>1762.478</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B134">
-        <v>2597.87</v>
+        <v>1925.71</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B135">
-        <v>2689.22</v>
+        <v>2054.807</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B136">
-        <v>2771.206</v>
+        <v>2173.325</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B137">
-        <v>2862.88</v>
+        <v>2257.083</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B138">
-        <v>2932.442</v>
+        <v>2353.174</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B139">
-        <v>2991.369</v>
+        <v>2394.062</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B140">
-        <v>3048.477</v>
+        <v>2450.131</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B141">
-        <v>3084.556</v>
+        <v>2479.615</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B142">
-        <v>3110.801</v>
+        <v>2531.677</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B143">
-        <v>3133.226</v>
+        <v>2529.619</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B144">
-        <v>3142.733</v>
+        <v>2518.672</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B145">
-        <v>3148.762</v>
+        <v>2517.84</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B146">
-        <v>3141.521</v>
+        <v>2498.208</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B147">
-        <v>3138.468</v>
+        <v>2464.772</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B148">
-        <v>3120.047</v>
+        <v>2439.185</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B149">
-        <v>3102.939</v>
+        <v>2403.381</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B150">
-        <v>3103.028</v>
+        <v>2311.66</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B151">
-        <v>3084.669</v>
+        <v>2285.54</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B152">
-        <v>3051.048</v>
+        <v>2265.596</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B153">
-        <v>3003.98</v>
+        <v>2226.446</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B154">
-        <v>2842.978</v>
+        <v>2132.179</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B155">
-        <v>2783.427</v>
+        <v>2066.237</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B156">
-        <v>2705.454</v>
+        <v>1985.086</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B157">
-        <v>2627.448</v>
+        <v>1913.283</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B158">
-        <v>2480.337</v>
+        <v>1768.834</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B159">
-        <v>2364.535</v>
+        <v>1677.21</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B160">
-        <v>2244.705</v>
+        <v>1567.743</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B161">
-        <v>2144.716</v>
+        <v>1468.29</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B162">
-        <v>1952.849</v>
+        <v>1323.284</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B163">
-        <v>1781.381</v>
+        <v>1189.654</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B164">
-        <v>1610.177</v>
+        <v>1052.596</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B165">
-        <v>1422.144</v>
+        <v>939.599</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B166">
-        <v>1138.642</v>
+        <v>761.752</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B167">
-        <v>992.4160000000001</v>
+        <v>642.043</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B168">
-        <v>834.0890000000001</v>
+        <v>536.2430000000001</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B169">
-        <v>676.159</v>
+        <v>440.37</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B170">
-        <v>467.954</v>
+        <v>307.407</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B171">
-        <v>349.457</v>
+        <v>231.467</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B172">
-        <v>255.784</v>
+        <v>159.121</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B173">
-        <v>174</v>
+        <v>115.64</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B174">
-        <v>88.84699999999999</v>
+        <v>60.973</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B175">
-        <v>51.731</v>
+        <v>43.659</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B176">
-        <v>33.838</v>
+        <v>32.729</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B177">
-        <v>27.17</v>
+        <v>26.329</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B178">
-        <v>15.994</v>
+        <v>19.912</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B179">
-        <v>15.612</v>
+        <v>19.686</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B180">
-        <v>14.792</v>
+        <v>19.206</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B181">
-        <v>13.399</v>
+        <v>18.414</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B182">
-        <v>13.43</v>
+        <v>15.83</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B183">
-        <v>10.33</v>
+        <v>13.53</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B184">
-        <v>5.43</v>
+        <v>9.73</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B185">
-        <v>2.83</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B186">
-        <v>6.53</v>
+        <v>8.23</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B187">
-        <v>0.33</v>
+        <v>2.73</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B188">
-        <v>0.83</v>
+        <v>9.23</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.05.20261</t>
-  </si>
-  <si>
-    <t>07.05.20262</t>
-  </si>
-  <si>
-    <t>07.05.20263</t>
-  </si>
-  <si>
-    <t>07.05.20264</t>
-  </si>
-  <si>
-    <t>07.05.20265</t>
-  </si>
-  <si>
-    <t>07.05.20266</t>
-  </si>
-  <si>
-    <t>07.05.20267</t>
-  </si>
-  <si>
-    <t>07.05.20268</t>
-  </si>
-  <si>
-    <t>07.05.20269</t>
-  </si>
-  <si>
-    <t>07.05.202610</t>
-  </si>
-  <si>
-    <t>07.05.202611</t>
-  </si>
-  <si>
-    <t>07.05.202612</t>
-  </si>
-  <si>
-    <t>07.05.202613</t>
-  </si>
-  <si>
-    <t>07.05.202614</t>
-  </si>
-  <si>
-    <t>07.05.202615</t>
-  </si>
-  <si>
-    <t>07.05.202616</t>
-  </si>
-  <si>
-    <t>07.05.202617</t>
-  </si>
-  <si>
-    <t>07.05.202618</t>
-  </si>
-  <si>
-    <t>07.05.202619</t>
-  </si>
-  <si>
-    <t>07.05.202620</t>
-  </si>
-  <si>
-    <t>07.05.202621</t>
-  </si>
-  <si>
-    <t>07.05.202622</t>
-  </si>
-  <si>
-    <t>07.05.202623</t>
-  </si>
-  <si>
-    <t>07.05.202624</t>
-  </si>
-  <si>
-    <t>07.05.202625</t>
-  </si>
-  <si>
-    <t>07.05.202626</t>
-  </si>
-  <si>
-    <t>07.05.202627</t>
-  </si>
-  <si>
-    <t>07.05.202628</t>
-  </si>
-  <si>
-    <t>07.05.202629</t>
-  </si>
-  <si>
-    <t>07.05.202630</t>
-  </si>
-  <si>
-    <t>07.05.202631</t>
-  </si>
-  <si>
-    <t>07.05.202632</t>
-  </si>
-  <si>
-    <t>07.05.202633</t>
-  </si>
-  <si>
-    <t>07.05.202634</t>
-  </si>
-  <si>
-    <t>07.05.202635</t>
-  </si>
-  <si>
-    <t>07.05.202636</t>
-  </si>
-  <si>
-    <t>07.05.202637</t>
-  </si>
-  <si>
-    <t>07.05.202638</t>
-  </si>
-  <si>
-    <t>07.05.202639</t>
-  </si>
-  <si>
-    <t>07.05.202640</t>
-  </si>
-  <si>
-    <t>07.05.202641</t>
-  </si>
-  <si>
-    <t>07.05.202642</t>
-  </si>
-  <si>
-    <t>07.05.202643</t>
-  </si>
-  <si>
-    <t>07.05.202644</t>
-  </si>
-  <si>
-    <t>07.05.202645</t>
-  </si>
-  <si>
-    <t>07.05.202646</t>
-  </si>
-  <si>
-    <t>07.05.202647</t>
-  </si>
-  <si>
-    <t>07.05.202648</t>
-  </si>
-  <si>
-    <t>07.05.202649</t>
-  </si>
-  <si>
-    <t>07.05.202650</t>
-  </si>
-  <si>
-    <t>07.05.202651</t>
-  </si>
-  <si>
-    <t>07.05.202652</t>
-  </si>
-  <si>
-    <t>07.05.202653</t>
-  </si>
-  <si>
-    <t>07.05.202654</t>
-  </si>
-  <si>
-    <t>07.05.202655</t>
-  </si>
-  <si>
-    <t>07.05.202656</t>
-  </si>
-  <si>
-    <t>07.05.202657</t>
-  </si>
-  <si>
-    <t>07.05.202658</t>
-  </si>
-  <si>
-    <t>07.05.202659</t>
-  </si>
-  <si>
-    <t>07.05.202660</t>
-  </si>
-  <si>
-    <t>07.05.202661</t>
-  </si>
-  <si>
-    <t>07.05.202662</t>
-  </si>
-  <si>
-    <t>07.05.202663</t>
-  </si>
-  <si>
-    <t>07.05.202664</t>
-  </si>
-  <si>
-    <t>07.05.202665</t>
-  </si>
-  <si>
-    <t>07.05.202666</t>
-  </si>
-  <si>
-    <t>07.05.202667</t>
-  </si>
-  <si>
-    <t>07.05.202668</t>
-  </si>
-  <si>
-    <t>07.05.202669</t>
-  </si>
-  <si>
-    <t>07.05.202670</t>
-  </si>
-  <si>
-    <t>07.05.202671</t>
-  </si>
-  <si>
-    <t>07.05.202672</t>
-  </si>
-  <si>
-    <t>07.05.202673</t>
-  </si>
-  <si>
-    <t>07.05.202674</t>
-  </si>
-  <si>
-    <t>07.05.202675</t>
-  </si>
-  <si>
-    <t>07.05.202676</t>
-  </si>
-  <si>
-    <t>07.05.202677</t>
-  </si>
-  <si>
-    <t>07.05.202678</t>
-  </si>
-  <si>
-    <t>07.05.202679</t>
-  </si>
-  <si>
-    <t>07.05.202680</t>
-  </si>
-  <si>
-    <t>07.05.202681</t>
-  </si>
-  <si>
-    <t>07.05.202682</t>
-  </si>
-  <si>
-    <t>07.05.202683</t>
-  </si>
-  <si>
-    <t>07.05.202684</t>
-  </si>
-  <si>
-    <t>07.05.202685</t>
-  </si>
-  <si>
-    <t>07.05.202686</t>
-  </si>
-  <si>
-    <t>07.05.202687</t>
-  </si>
-  <si>
-    <t>07.05.202688</t>
-  </si>
-  <si>
-    <t>07.05.202689</t>
-  </si>
-  <si>
-    <t>07.05.202690</t>
-  </si>
-  <si>
-    <t>07.05.202691</t>
-  </si>
-  <si>
-    <t>07.05.202692</t>
-  </si>
-  <si>
-    <t>07.05.202693</t>
-  </si>
-  <si>
-    <t>07.05.202694</t>
-  </si>
-  <si>
-    <t>07.05.202695</t>
-  </si>
-  <si>
-    <t>07.05.202696</t>
-  </si>
-  <si>
-    <t>08.05.20261</t>
-  </si>
-  <si>
-    <t>08.05.20262</t>
-  </si>
-  <si>
-    <t>08.05.20263</t>
-  </si>
-  <si>
-    <t>08.05.20264</t>
-  </si>
-  <si>
-    <t>08.05.20265</t>
-  </si>
-  <si>
-    <t>08.05.20266</t>
-  </si>
-  <si>
-    <t>08.05.20267</t>
-  </si>
-  <si>
-    <t>08.05.20268</t>
-  </si>
-  <si>
-    <t>08.05.20269</t>
-  </si>
-  <si>
-    <t>08.05.202610</t>
-  </si>
-  <si>
-    <t>08.05.202611</t>
-  </si>
-  <si>
-    <t>08.05.202612</t>
-  </si>
-  <si>
-    <t>08.05.202613</t>
-  </si>
-  <si>
-    <t>08.05.202614</t>
-  </si>
-  <si>
-    <t>08.05.202615</t>
-  </si>
-  <si>
-    <t>08.05.202616</t>
-  </si>
-  <si>
-    <t>08.05.202617</t>
-  </si>
-  <si>
-    <t>08.05.202618</t>
-  </si>
-  <si>
-    <t>08.05.202619</t>
-  </si>
-  <si>
-    <t>08.05.202620</t>
-  </si>
-  <si>
-    <t>08.05.202621</t>
-  </si>
-  <si>
-    <t>08.05.202622</t>
-  </si>
-  <si>
-    <t>08.05.202623</t>
-  </si>
-  <si>
-    <t>08.05.202624</t>
-  </si>
-  <si>
-    <t>08.05.202625</t>
-  </si>
-  <si>
-    <t>08.05.202626</t>
-  </si>
-  <si>
-    <t>08.05.202627</t>
-  </si>
-  <si>
-    <t>08.05.202628</t>
-  </si>
-  <si>
-    <t>08.05.202629</t>
-  </si>
-  <si>
-    <t>08.05.202630</t>
-  </si>
-  <si>
-    <t>08.05.202631</t>
-  </si>
-  <si>
-    <t>08.05.202632</t>
-  </si>
-  <si>
-    <t>08.05.202633</t>
-  </si>
-  <si>
-    <t>08.05.202634</t>
-  </si>
-  <si>
-    <t>08.05.202635</t>
-  </si>
-  <si>
-    <t>08.05.202636</t>
-  </si>
-  <si>
-    <t>08.05.202637</t>
-  </si>
-  <si>
-    <t>08.05.202638</t>
-  </si>
-  <si>
-    <t>08.05.202639</t>
-  </si>
-  <si>
-    <t>08.05.202640</t>
-  </si>
-  <si>
-    <t>08.05.202641</t>
-  </si>
-  <si>
-    <t>08.05.202642</t>
-  </si>
-  <si>
-    <t>08.05.202643</t>
-  </si>
-  <si>
-    <t>08.05.202644</t>
-  </si>
-  <si>
-    <t>08.05.202645</t>
-  </si>
-  <si>
-    <t>08.05.202646</t>
-  </si>
-  <si>
-    <t>08.05.202647</t>
-  </si>
-  <si>
-    <t>08.05.202648</t>
-  </si>
-  <si>
-    <t>08.05.202649</t>
-  </si>
-  <si>
-    <t>08.05.202650</t>
-  </si>
-  <si>
-    <t>08.05.202651</t>
-  </si>
-  <si>
-    <t>08.05.202652</t>
-  </si>
-  <si>
-    <t>08.05.202653</t>
-  </si>
-  <si>
-    <t>08.05.202654</t>
-  </si>
-  <si>
-    <t>08.05.202655</t>
-  </si>
-  <si>
-    <t>08.05.202656</t>
-  </si>
-  <si>
-    <t>08.05.202657</t>
-  </si>
-  <si>
-    <t>08.05.202658</t>
-  </si>
-  <si>
-    <t>08.05.202659</t>
-  </si>
-  <si>
-    <t>08.05.202660</t>
-  </si>
-  <si>
-    <t>08.05.202661</t>
-  </si>
-  <si>
-    <t>08.05.202662</t>
-  </si>
-  <si>
-    <t>08.05.202663</t>
-  </si>
-  <si>
-    <t>08.05.202664</t>
-  </si>
-  <si>
-    <t>08.05.202665</t>
-  </si>
-  <si>
-    <t>08.05.202666</t>
-  </si>
-  <si>
-    <t>08.05.202667</t>
-  </si>
-  <si>
-    <t>08.05.202668</t>
-  </si>
-  <si>
-    <t>08.05.202669</t>
-  </si>
-  <si>
-    <t>08.05.202670</t>
-  </si>
-  <si>
-    <t>08.05.202671</t>
-  </si>
-  <si>
-    <t>08.05.202672</t>
-  </si>
-  <si>
-    <t>08.05.202673</t>
-  </si>
-  <si>
-    <t>08.05.202674</t>
-  </si>
-  <si>
-    <t>08.05.202675</t>
-  </si>
-  <si>
-    <t>08.05.202676</t>
-  </si>
-  <si>
-    <t>08.05.202677</t>
-  </si>
-  <si>
-    <t>08.05.202678</t>
-  </si>
-  <si>
-    <t>08.05.202679</t>
-  </si>
-  <si>
-    <t>08.05.202680</t>
-  </si>
-  <si>
-    <t>08.05.202681</t>
-  </si>
-  <si>
-    <t>08.05.202682</t>
-  </si>
-  <si>
-    <t>08.05.202683</t>
-  </si>
-  <si>
-    <t>08.05.202684</t>
-  </si>
-  <si>
-    <t>08.05.202685</t>
-  </si>
-  <si>
-    <t>08.05.202686</t>
-  </si>
-  <si>
-    <t>08.05.202687</t>
-  </si>
-  <si>
-    <t>08.05.202688</t>
-  </si>
-  <si>
-    <t>08.05.202689</t>
-  </si>
-  <si>
-    <t>08.05.202690</t>
-  </si>
-  <si>
-    <t>08.05.202691</t>
-  </si>
-  <si>
-    <t>08.05.202692</t>
-  </si>
-  <si>
-    <t>08.05.202693</t>
-  </si>
-  <si>
-    <t>08.05.202694</t>
-  </si>
-  <si>
-    <t>08.05.202695</t>
-  </si>
-  <si>
-    <t>08.05.202696</t>
+    <t>11.05.20261</t>
+  </si>
+  <si>
+    <t>11.05.20262</t>
+  </si>
+  <si>
+    <t>11.05.20263</t>
+  </si>
+  <si>
+    <t>11.05.20264</t>
+  </si>
+  <si>
+    <t>11.05.20265</t>
+  </si>
+  <si>
+    <t>11.05.20266</t>
+  </si>
+  <si>
+    <t>11.05.20267</t>
+  </si>
+  <si>
+    <t>11.05.20268</t>
+  </si>
+  <si>
+    <t>11.05.20269</t>
+  </si>
+  <si>
+    <t>11.05.202610</t>
+  </si>
+  <si>
+    <t>11.05.202611</t>
+  </si>
+  <si>
+    <t>11.05.202612</t>
+  </si>
+  <si>
+    <t>11.05.202613</t>
+  </si>
+  <si>
+    <t>11.05.202614</t>
+  </si>
+  <si>
+    <t>11.05.202615</t>
+  </si>
+  <si>
+    <t>11.05.202616</t>
+  </si>
+  <si>
+    <t>11.05.202617</t>
+  </si>
+  <si>
+    <t>11.05.202618</t>
+  </si>
+  <si>
+    <t>11.05.202619</t>
+  </si>
+  <si>
+    <t>11.05.202620</t>
+  </si>
+  <si>
+    <t>11.05.202621</t>
+  </si>
+  <si>
+    <t>11.05.202622</t>
+  </si>
+  <si>
+    <t>11.05.202623</t>
+  </si>
+  <si>
+    <t>11.05.202624</t>
+  </si>
+  <si>
+    <t>11.05.202625</t>
+  </si>
+  <si>
+    <t>11.05.202626</t>
+  </si>
+  <si>
+    <t>11.05.202627</t>
+  </si>
+  <si>
+    <t>11.05.202628</t>
+  </si>
+  <si>
+    <t>11.05.202629</t>
+  </si>
+  <si>
+    <t>11.05.202630</t>
+  </si>
+  <si>
+    <t>11.05.202631</t>
+  </si>
+  <si>
+    <t>11.05.202632</t>
+  </si>
+  <si>
+    <t>11.05.202633</t>
+  </si>
+  <si>
+    <t>11.05.202634</t>
+  </si>
+  <si>
+    <t>11.05.202635</t>
+  </si>
+  <si>
+    <t>11.05.202636</t>
+  </si>
+  <si>
+    <t>11.05.202637</t>
+  </si>
+  <si>
+    <t>11.05.202638</t>
+  </si>
+  <si>
+    <t>11.05.202639</t>
+  </si>
+  <si>
+    <t>11.05.202640</t>
+  </si>
+  <si>
+    <t>11.05.202641</t>
+  </si>
+  <si>
+    <t>11.05.202642</t>
+  </si>
+  <si>
+    <t>11.05.202643</t>
+  </si>
+  <si>
+    <t>11.05.202644</t>
+  </si>
+  <si>
+    <t>11.05.202645</t>
+  </si>
+  <si>
+    <t>11.05.202646</t>
+  </si>
+  <si>
+    <t>11.05.202647</t>
+  </si>
+  <si>
+    <t>11.05.202648</t>
+  </si>
+  <si>
+    <t>11.05.202649</t>
+  </si>
+  <si>
+    <t>11.05.202650</t>
+  </si>
+  <si>
+    <t>11.05.202651</t>
+  </si>
+  <si>
+    <t>11.05.202652</t>
+  </si>
+  <si>
+    <t>11.05.202653</t>
+  </si>
+  <si>
+    <t>11.05.202654</t>
+  </si>
+  <si>
+    <t>11.05.202655</t>
+  </si>
+  <si>
+    <t>11.05.202656</t>
+  </si>
+  <si>
+    <t>11.05.202657</t>
+  </si>
+  <si>
+    <t>11.05.202658</t>
+  </si>
+  <si>
+    <t>11.05.202659</t>
+  </si>
+  <si>
+    <t>11.05.202660</t>
+  </si>
+  <si>
+    <t>11.05.202661</t>
+  </si>
+  <si>
+    <t>11.05.202662</t>
+  </si>
+  <si>
+    <t>11.05.202663</t>
+  </si>
+  <si>
+    <t>11.05.202664</t>
+  </si>
+  <si>
+    <t>11.05.202665</t>
+  </si>
+  <si>
+    <t>11.05.202666</t>
+  </si>
+  <si>
+    <t>11.05.202667</t>
+  </si>
+  <si>
+    <t>11.05.202668</t>
+  </si>
+  <si>
+    <t>11.05.202669</t>
+  </si>
+  <si>
+    <t>11.05.202670</t>
+  </si>
+  <si>
+    <t>11.05.202671</t>
+  </si>
+  <si>
+    <t>11.05.202672</t>
+  </si>
+  <si>
+    <t>11.05.202673</t>
+  </si>
+  <si>
+    <t>11.05.202674</t>
+  </si>
+  <si>
+    <t>11.05.202675</t>
+  </si>
+  <si>
+    <t>11.05.202676</t>
+  </si>
+  <si>
+    <t>11.05.202677</t>
+  </si>
+  <si>
+    <t>11.05.202678</t>
+  </si>
+  <si>
+    <t>11.05.202679</t>
+  </si>
+  <si>
+    <t>11.05.202680</t>
+  </si>
+  <si>
+    <t>11.05.202681</t>
+  </si>
+  <si>
+    <t>11.05.202682</t>
+  </si>
+  <si>
+    <t>11.05.202683</t>
+  </si>
+  <si>
+    <t>11.05.202684</t>
+  </si>
+  <si>
+    <t>11.05.202685</t>
+  </si>
+  <si>
+    <t>11.05.202686</t>
+  </si>
+  <si>
+    <t>11.05.202687</t>
+  </si>
+  <si>
+    <t>11.05.202688</t>
+  </si>
+  <si>
+    <t>11.05.202689</t>
+  </si>
+  <si>
+    <t>11.05.202690</t>
+  </si>
+  <si>
+    <t>11.05.202691</t>
+  </si>
+  <si>
+    <t>11.05.202692</t>
+  </si>
+  <si>
+    <t>11.05.202693</t>
+  </si>
+  <si>
+    <t>11.05.202694</t>
+  </si>
+  <si>
+    <t>11.05.202695</t>
+  </si>
+  <si>
+    <t>11.05.202696</t>
+  </si>
+  <si>
+    <t>12.05.20261</t>
+  </si>
+  <si>
+    <t>12.05.20262</t>
+  </si>
+  <si>
+    <t>12.05.20263</t>
+  </si>
+  <si>
+    <t>12.05.20264</t>
+  </si>
+  <si>
+    <t>12.05.20265</t>
+  </si>
+  <si>
+    <t>12.05.20266</t>
+  </si>
+  <si>
+    <t>12.05.20267</t>
+  </si>
+  <si>
+    <t>12.05.20268</t>
+  </si>
+  <si>
+    <t>12.05.20269</t>
+  </si>
+  <si>
+    <t>12.05.202610</t>
+  </si>
+  <si>
+    <t>12.05.202611</t>
+  </si>
+  <si>
+    <t>12.05.202612</t>
+  </si>
+  <si>
+    <t>12.05.202613</t>
+  </si>
+  <si>
+    <t>12.05.202614</t>
+  </si>
+  <si>
+    <t>12.05.202615</t>
+  </si>
+  <si>
+    <t>12.05.202616</t>
+  </si>
+  <si>
+    <t>12.05.202617</t>
+  </si>
+  <si>
+    <t>12.05.202618</t>
+  </si>
+  <si>
+    <t>12.05.202619</t>
+  </si>
+  <si>
+    <t>12.05.202620</t>
+  </si>
+  <si>
+    <t>12.05.202621</t>
+  </si>
+  <si>
+    <t>12.05.202622</t>
+  </si>
+  <si>
+    <t>12.05.202623</t>
+  </si>
+  <si>
+    <t>12.05.202624</t>
+  </si>
+  <si>
+    <t>12.05.202625</t>
+  </si>
+  <si>
+    <t>12.05.202626</t>
+  </si>
+  <si>
+    <t>12.05.202627</t>
+  </si>
+  <si>
+    <t>12.05.202628</t>
+  </si>
+  <si>
+    <t>12.05.202629</t>
+  </si>
+  <si>
+    <t>12.05.202630</t>
+  </si>
+  <si>
+    <t>12.05.202631</t>
+  </si>
+  <si>
+    <t>12.05.202632</t>
+  </si>
+  <si>
+    <t>12.05.202633</t>
+  </si>
+  <si>
+    <t>12.05.202634</t>
+  </si>
+  <si>
+    <t>12.05.202635</t>
+  </si>
+  <si>
+    <t>12.05.202636</t>
+  </si>
+  <si>
+    <t>12.05.202637</t>
+  </si>
+  <si>
+    <t>12.05.202638</t>
+  </si>
+  <si>
+    <t>12.05.202639</t>
+  </si>
+  <si>
+    <t>12.05.202640</t>
+  </si>
+  <si>
+    <t>12.05.202641</t>
+  </si>
+  <si>
+    <t>12.05.202642</t>
+  </si>
+  <si>
+    <t>12.05.202643</t>
+  </si>
+  <si>
+    <t>12.05.202644</t>
+  </si>
+  <si>
+    <t>12.05.202645</t>
+  </si>
+  <si>
+    <t>12.05.202646</t>
+  </si>
+  <si>
+    <t>12.05.202647</t>
+  </si>
+  <si>
+    <t>12.05.202648</t>
+  </si>
+  <si>
+    <t>12.05.202649</t>
+  </si>
+  <si>
+    <t>12.05.202650</t>
+  </si>
+  <si>
+    <t>12.05.202651</t>
+  </si>
+  <si>
+    <t>12.05.202652</t>
+  </si>
+  <si>
+    <t>12.05.202653</t>
+  </si>
+  <si>
+    <t>12.05.202654</t>
+  </si>
+  <si>
+    <t>12.05.202655</t>
+  </si>
+  <si>
+    <t>12.05.202656</t>
+  </si>
+  <si>
+    <t>12.05.202657</t>
+  </si>
+  <si>
+    <t>12.05.202658</t>
+  </si>
+  <si>
+    <t>12.05.202659</t>
+  </si>
+  <si>
+    <t>12.05.202660</t>
+  </si>
+  <si>
+    <t>12.05.202661</t>
+  </si>
+  <si>
+    <t>12.05.202662</t>
+  </si>
+  <si>
+    <t>12.05.202663</t>
+  </si>
+  <si>
+    <t>12.05.202664</t>
+  </si>
+  <si>
+    <t>12.05.202665</t>
+  </si>
+  <si>
+    <t>12.05.202666</t>
+  </si>
+  <si>
+    <t>12.05.202667</t>
+  </si>
+  <si>
+    <t>12.05.202668</t>
+  </si>
+  <si>
+    <t>12.05.202669</t>
+  </si>
+  <si>
+    <t>12.05.202670</t>
+  </si>
+  <si>
+    <t>12.05.202671</t>
+  </si>
+  <si>
+    <t>12.05.202672</t>
+  </si>
+  <si>
+    <t>12.05.202673</t>
+  </si>
+  <si>
+    <t>12.05.202674</t>
+  </si>
+  <si>
+    <t>12.05.202675</t>
+  </si>
+  <si>
+    <t>12.05.202676</t>
+  </si>
+  <si>
+    <t>12.05.202677</t>
+  </si>
+  <si>
+    <t>12.05.202678</t>
+  </si>
+  <si>
+    <t>12.05.202679</t>
+  </si>
+  <si>
+    <t>12.05.202680</t>
+  </si>
+  <si>
+    <t>12.05.202681</t>
+  </si>
+  <si>
+    <t>12.05.202682</t>
+  </si>
+  <si>
+    <t>12.05.202683</t>
+  </si>
+  <si>
+    <t>12.05.202684</t>
+  </si>
+  <si>
+    <t>12.05.202685</t>
+  </si>
+  <si>
+    <t>12.05.202686</t>
+  </si>
+  <si>
+    <t>12.05.202687</t>
+  </si>
+  <si>
+    <t>12.05.202688</t>
+  </si>
+  <si>
+    <t>12.05.202689</t>
+  </si>
+  <si>
+    <t>12.05.202690</t>
+  </si>
+  <si>
+    <t>12.05.202691</t>
+  </si>
+  <si>
+    <t>12.05.202692</t>
+  </si>
+  <si>
+    <t>12.05.202693</t>
+  </si>
+  <si>
+    <t>12.05.202694</t>
+  </si>
+  <si>
+    <t>12.05.202695</t>
+  </si>
+  <si>
+    <t>12.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46149.01041666666</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46149.02083333334</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46149.03125</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46149.04166666666</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46149.05208333334</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46149.0625</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46149.07291666666</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46149.08333333334</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46149.09375</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46149.10416666666</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46149.11458333334</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>0.731</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46149.125</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46149.13541666666</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>0.734</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46149.14583333334</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.736</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46149.15625</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>0.741</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46149.16666666666</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.83</v>
+        <v>0.745</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46149.17708333334</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.834</v>
+        <v>0.753</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46149.1875</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>0.874</v>
+        <v>2.148</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46149.19791666666</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.5</v>
+        <v>2.316</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46149.20833333334</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>12.517</v>
+        <v>14.138</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46149.21875</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>40.139</v>
+        <v>41.918</v>
       </c>
       <c r="C23">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46149.22916666666</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>79.848</v>
+        <v>79.958</v>
       </c>
       <c r="C24">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46149.23958333334</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>139.467</v>
+        <v>132.078</v>
       </c>
       <c r="C25">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46149.25</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>279.49</v>
+        <v>257.486</v>
       </c>
       <c r="C26">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46149.26041666666</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>384.303</v>
+        <v>350.136</v>
       </c>
       <c r="C27">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46149.27083333334</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>528.051</v>
+        <v>477.18</v>
       </c>
       <c r="C28">
-        <v>422</v>
+        <v>470</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46149.28125</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>685.346</v>
+        <v>610.441</v>
       </c>
       <c r="C29">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46149.29166666666</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>917.466</v>
+        <v>830.992</v>
       </c>
       <c r="C30">
-        <v>668</v>
+        <v>750</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46149.30208333334</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>1097.754</v>
+        <v>993.547</v>
       </c>
       <c r="C31">
-        <v>825</v>
+        <v>917</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46149.3125</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>1301.922</v>
+        <v>1178.372</v>
       </c>
       <c r="C32">
-        <v>968</v>
+        <v>1029</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46149.32291666666</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>1470.915</v>
+        <v>1348.584</v>
       </c>
       <c r="C33">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46149.33333333334</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>1736.635</v>
+        <v>1591.667</v>
       </c>
       <c r="C34">
-        <v>1254</v>
+        <v>1269</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46149.34375</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>1886.013</v>
+        <v>1723.146</v>
       </c>
       <c r="C35">
-        <v>1359</v>
+        <v>1381</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46149.35416666666</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>2025.409</v>
+        <v>1864.455</v>
       </c>
       <c r="C36">
-        <v>1424</v>
+        <v>1472</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46149.36458333334</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>2184.932</v>
+        <v>1997.349</v>
       </c>
       <c r="C37">
-        <v>1462</v>
+        <v>1532</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46149.375</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>2311.835</v>
+        <v>2118.68</v>
       </c>
       <c r="C38">
-        <v>1490</v>
+        <v>1582</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46149.38541666666</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>2414.147</v>
+        <v>2213.983</v>
       </c>
       <c r="C39">
-        <v>1542</v>
+        <v>1684</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46149.39583333334</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>2497.264</v>
+        <v>2313.794</v>
       </c>
       <c r="C40">
-        <v>1535</v>
+        <v>1822</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46149.40625</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>2578.43</v>
+        <v>2376.261</v>
       </c>
       <c r="C41">
-        <v>1576</v>
+        <v>1819</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46149.41666666666</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>2639.63</v>
+        <v>2469.051</v>
       </c>
       <c r="C42">
-        <v>1581</v>
+        <v>1830</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46149.42708333334</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>2688.046</v>
+        <v>2539.22</v>
       </c>
       <c r="C43">
-        <v>1662</v>
+        <v>1869</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46149.4375</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>2732.552</v>
+        <v>2572.596</v>
       </c>
       <c r="C44">
-        <v>1697</v>
+        <v>1858</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46149.44791666666</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>2761.378</v>
+        <v>2605.104</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1922</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46149.45833333334</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>2780.084</v>
+        <v>2591.548</v>
       </c>
       <c r="C46">
-        <v>1690</v>
+        <v>1894</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46149.46875</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>2783.548</v>
+        <v>2600.667</v>
       </c>
       <c r="C47">
-        <v>1749</v>
+        <v>1955</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46149.47916666666</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>2782.327</v>
+        <v>2594.493</v>
       </c>
       <c r="C48">
-        <v>1761</v>
+        <v>1993</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46149.48958333334</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>2772.081</v>
+        <v>2594.586</v>
       </c>
       <c r="C49">
-        <v>1776</v>
+        <v>1967</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46149.5</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>2756.762</v>
+        <v>2574.984</v>
       </c>
       <c r="C50">
-        <v>1728</v>
+        <v>1965</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46149.51041666666</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>2740.852</v>
+        <v>2576.57</v>
       </c>
       <c r="C51">
-        <v>1720</v>
+        <v>1992</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46149.52083333334</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>2718.671</v>
+        <v>2559.326</v>
       </c>
       <c r="C52">
-        <v>1661</v>
+        <v>1998</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46149.53125</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>2691.493</v>
+        <v>2542.745</v>
       </c>
       <c r="C53">
-        <v>1680</v>
+        <v>2009</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46149.54166666666</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>2650.773</v>
+        <v>2521.463</v>
       </c>
       <c r="C54">
-        <v>1641</v>
+        <v>1887</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46149.55208333334</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
-        <v>2600.583</v>
+        <v>2481.81</v>
       </c>
       <c r="C55">
-        <v>1618</v>
+        <v>1773</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46149.5625</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>2550.548</v>
+        <v>2406.429</v>
       </c>
       <c r="C56">
-        <v>1548</v>
+        <v>1721</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46149.57291666666</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>2483.976</v>
+        <v>2347.573</v>
       </c>
       <c r="C57">
-        <v>1546</v>
+        <v>1687</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46149.58333333334</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>2365.77</v>
+        <v>2234.389</v>
       </c>
       <c r="C58">
-        <v>1466</v>
+        <v>1619</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46149.59375</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>2289.439</v>
+        <v>2171.006</v>
       </c>
       <c r="C59">
-        <v>1390</v>
+        <v>1599</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46149.60416666666</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>2197.202</v>
+        <v>2088.722</v>
       </c>
       <c r="C60">
-        <v>1381</v>
+        <v>1500</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46149.61458333334</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>2109.276</v>
+        <v>2007.198</v>
       </c>
       <c r="C61">
-        <v>1282</v>
+        <v>1480</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46149.625</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>1950.187</v>
+        <v>1844.394</v>
       </c>
       <c r="C62">
-        <v>1172</v>
+        <v>1433</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46149.63541666666</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>1810.548</v>
+        <v>1754.045</v>
       </c>
       <c r="C63">
-        <v>1052</v>
+        <v>1405</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46149.64583333334</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>1701.821</v>
+        <v>1651.034</v>
       </c>
       <c r="C64">
-        <v>989</v>
+        <v>1361</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46149.65625</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>1572.192</v>
+        <v>1544.429</v>
       </c>
       <c r="C65">
-        <v>923</v>
+        <v>1242</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46149.66666666666</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>1384.776</v>
+        <v>1350.744</v>
       </c>
       <c r="C66">
-        <v>842</v>
+        <v>1159</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46149.67708333334</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>1228.815</v>
+        <v>1213.75</v>
       </c>
       <c r="C67">
-        <v>713</v>
+        <v>1083</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46149.6875</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>1072.049</v>
+        <v>1089.063</v>
       </c>
       <c r="C68">
-        <v>692</v>
+        <v>997</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46149.69791666666</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>942.89</v>
+        <v>974.899</v>
       </c>
       <c r="C69">
-        <v>603</v>
+        <v>944</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46149.70833333334</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>732.215</v>
+        <v>777.285</v>
       </c>
       <c r="C70">
-        <v>494</v>
+        <v>879</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46149.71875</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>614.915</v>
+        <v>656.016</v>
       </c>
       <c r="C71">
-        <v>446</v>
+        <v>715</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46149.72916666666</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>507.925</v>
+        <v>549.751</v>
       </c>
       <c r="C72">
-        <v>365</v>
+        <v>572</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46149.73958333334</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>411.758</v>
+        <v>455.219</v>
       </c>
       <c r="C73">
-        <v>284</v>
+        <v>456</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46149.75</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>267.075</v>
+        <v>317.748</v>
       </c>
       <c r="C74">
-        <v>206</v>
+        <v>342</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46149.76041666666</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>199.127</v>
+        <v>240.797</v>
       </c>
       <c r="C75">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46149.77083333334</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>139.032</v>
+        <v>176.789</v>
       </c>
       <c r="C76">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46149.78125</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>94.863</v>
+        <v>118.751</v>
       </c>
       <c r="C77">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46149.79166666666</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>49.03</v>
+        <v>66.57599999999999</v>
       </c>
       <c r="C78">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46149.80208333334</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>31.998</v>
+        <v>41.416</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46149.8125</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>24.535</v>
+        <v>28.329</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46149.82291666666</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>21.962</v>
+        <v>21.537</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46149.83333333334</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
-        <v>15.595</v>
+        <v>12.464</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46149.84375</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>15.582</v>
+        <v>15.273</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46149.85416666666</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>15.199</v>
+        <v>17.504</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46149.86458333334</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>14.409</v>
+        <v>12.01</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46149.875</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>13.83</v>
+        <v>5.13</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46149.88541666666</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>12.43</v>
+        <v>4.73</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46149.89583333334</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>9.33</v>
+        <v>1.63</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46149.90625</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>5.23</v>
+        <v>1.23</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46149.91666666666</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>8.23</v>
+        <v>0.73</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46149.92708333334</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46149.9375</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46149.94791666666</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46149.95833333334</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46149.96875</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46149.97916666666</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46149.98958333334</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46150.01041666666</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46150.02083333334</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46150.04166666666</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46150.05208333334</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46150.07291666666</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46150.08333333334</v>
+        <v>46154.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46150.09375</v>
+        <v>46154.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46150.10416666666</v>
+        <v>46154.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46150.11458333334</v>
+        <v>46154.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46150.125</v>
+        <v>46154.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46150.13541666666</v>
+        <v>46154.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46150.14583333334</v>
+        <v>46154.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46150.15625</v>
+        <v>46154.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46150.16666666666</v>
+        <v>46154.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.747</v>
+        <v>1.262</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46150.17708333334</v>
+        <v>46154.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46150.1875</v>
+        <v>46154.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>1.274</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46150.19791666666</v>
+        <v>46154.19791666666</v>
       </c>
       <c r="B117">
-        <v>0.765</v>
+        <v>1.368</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46150.20833333334</v>
+        <v>46154.20833333334</v>
       </c>
       <c r="B118">
-        <v>7.836</v>
+        <v>18.055</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46150.21875</v>
+        <v>46154.21875</v>
       </c>
       <c r="B119">
-        <v>23.399</v>
+        <v>38.648</v>
       </c>
       <c r="C119">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46150.22916666666</v>
+        <v>46154.22916666666</v>
       </c>
       <c r="B120">
-        <v>44.872</v>
+        <v>76.488</v>
       </c>
       <c r="C120">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46150.23958333334</v>
+        <v>46154.23958333334</v>
       </c>
       <c r="B121">
-        <v>82.52800000000001</v>
+        <v>124.529</v>
       </c>
       <c r="C121">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46150.25</v>
+        <v>46154.25</v>
       </c>
       <c r="B122">
-        <v>182.53</v>
+        <v>248.558</v>
       </c>
       <c r="C122">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46150.26041666666</v>
+        <v>46154.26041666666</v>
       </c>
       <c r="B123">
-        <v>260.941</v>
+        <v>331.922</v>
       </c>
       <c r="C123">
-        <v>236</v>
+        <v>291</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46150.27083333334</v>
+        <v>46154.27083333334</v>
       </c>
       <c r="B124">
-        <v>350.957</v>
+        <v>439.529</v>
       </c>
       <c r="C124">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46150.28125</v>
+        <v>46154.28125</v>
       </c>
       <c r="B125">
-        <v>459.745</v>
+        <v>557.573</v>
       </c>
       <c r="C125">
-        <v>426</v>
+        <v>515</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46150.29166666666</v>
+        <v>46154.29166666666</v>
       </c>
       <c r="B126">
-        <v>671.236</v>
+        <v>746.322</v>
       </c>
       <c r="C126">
-        <v>538</v>
+        <v>632</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46150.30208333334</v>
+        <v>46154.30208333334</v>
       </c>
       <c r="B127">
-        <v>812.037</v>
+        <v>859.687</v>
       </c>
       <c r="C127">
-        <v>664</v>
+        <v>735</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46150.3125</v>
+        <v>46154.3125</v>
       </c>
       <c r="B128">
-        <v>952.691</v>
+        <v>993.826</v>
       </c>
       <c r="C128">
-        <v>822</v>
+        <v>797</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46150.32291666666</v>
+        <v>46154.32291666666</v>
       </c>
       <c r="B129">
-        <v>1099.473</v>
+        <v>1132.311</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>908</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46150.33333333334</v>
+        <v>46154.33333333334</v>
       </c>
       <c r="B130">
-        <v>1313.734</v>
+        <v>1356.846</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>939</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46150.34375</v>
+        <v>46154.34375</v>
       </c>
       <c r="B131">
-        <v>1454.803</v>
+        <v>1489.237</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>974</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46150.35416666666</v>
+        <v>46154.35416666666</v>
       </c>
       <c r="B132">
-        <v>1602.397</v>
+        <v>1605.087</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1068</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46150.36458333334</v>
+        <v>46154.36458333334</v>
       </c>
       <c r="B133">
-        <v>1762.478</v>
+        <v>1725.646</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1134</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46150.375</v>
+        <v>46154.375</v>
       </c>
       <c r="B134">
-        <v>1925.71</v>
+        <v>1885.775</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46150.38541666666</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="B135">
-        <v>2054.807</v>
+        <v>1951.338</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46150.39583333334</v>
+        <v>46154.39583333334</v>
       </c>
       <c r="B136">
-        <v>2173.325</v>
+        <v>2023.587</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1239</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46150.40625</v>
+        <v>46154.40625</v>
       </c>
       <c r="B137">
-        <v>2257.083</v>
+        <v>2084.086</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1244</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46150.41666666666</v>
+        <v>46154.41666666666</v>
       </c>
       <c r="B138">
-        <v>2353.174</v>
+        <v>2166.236</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1413</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46150.42708333334</v>
+        <v>46154.42708333334</v>
       </c>
       <c r="B139">
-        <v>2394.062</v>
+        <v>2203.75</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1496</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46150.4375</v>
+        <v>46154.4375</v>
       </c>
       <c r="B140">
-        <v>2450.131</v>
+        <v>2236.966</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46150.44791666666</v>
+        <v>46154.44791666666</v>
       </c>
       <c r="B141">
-        <v>2479.615</v>
+        <v>2259.759</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46150.45833333334</v>
+        <v>46154.45833333334</v>
       </c>
       <c r="B142">
-        <v>2531.677</v>
+        <v>2256.857</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46150.46875</v>
+        <v>46154.46875</v>
       </c>
       <c r="B143">
-        <v>2529.619</v>
+        <v>2228.659</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46150.47916666666</v>
+        <v>46154.47916666666</v>
       </c>
       <c r="B144">
-        <v>2518.672</v>
+        <v>2223.257</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46150.48958333334</v>
+        <v>46154.48958333334</v>
       </c>
       <c r="B145">
-        <v>2517.84</v>
+        <v>2217.456</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46150.5</v>
+        <v>46154.5</v>
       </c>
       <c r="B146">
-        <v>2498.208</v>
+        <v>2221.933</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46150.51041666666</v>
+        <v>46154.51041666666</v>
       </c>
       <c r="B147">
-        <v>2464.772</v>
+        <v>2219.432</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46150.52083333334</v>
+        <v>46154.52083333334</v>
       </c>
       <c r="B148">
-        <v>2439.185</v>
+        <v>2196.833</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46150.53125</v>
+        <v>46154.53125</v>
       </c>
       <c r="B149">
-        <v>2403.381</v>
+        <v>2186.323</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46150.54166666666</v>
+        <v>46154.54166666666</v>
       </c>
       <c r="B150">
-        <v>2311.66</v>
+        <v>2132.365</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46150.55208333334</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="B151">
-        <v>2285.54</v>
+        <v>2117.549</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46150.5625</v>
+        <v>46154.5625</v>
       </c>
       <c r="B152">
-        <v>2265.596</v>
+        <v>2096.992</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46150.57291666666</v>
+        <v>46154.57291666666</v>
       </c>
       <c r="B153">
-        <v>2226.446</v>
+        <v>2069.96</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46150.58333333334</v>
+        <v>46154.58333333334</v>
       </c>
       <c r="B154">
-        <v>2132.179</v>
+        <v>1991.711</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46150.59375</v>
+        <v>46154.59375</v>
       </c>
       <c r="B155">
-        <v>2066.237</v>
+        <v>1918.93</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46150.60416666666</v>
+        <v>46154.60416666666</v>
       </c>
       <c r="B156">
-        <v>1985.086</v>
+        <v>1845.74</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46150.61458333334</v>
+        <v>46154.61458333334</v>
       </c>
       <c r="B157">
-        <v>1913.283</v>
+        <v>1796.869</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46150.625</v>
+        <v>46154.625</v>
       </c>
       <c r="B158">
-        <v>1768.834</v>
+        <v>1696.079</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46150.63541666666</v>
+        <v>46154.63541666666</v>
       </c>
       <c r="B159">
-        <v>1677.21</v>
+        <v>1621.274</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46150.64583333334</v>
+        <v>46154.64583333334</v>
       </c>
       <c r="B160">
-        <v>1567.743</v>
+        <v>1552.654</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46150.65625</v>
+        <v>46154.65625</v>
       </c>
       <c r="B161">
-        <v>1468.29</v>
+        <v>1476.607</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46150.66666666666</v>
+        <v>46154.66666666666</v>
       </c>
       <c r="B162">
-        <v>1323.284</v>
+        <v>1305.415</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46150.67708333334</v>
+        <v>46154.67708333334</v>
       </c>
       <c r="B163">
-        <v>1189.654</v>
+        <v>1214.059</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46150.6875</v>
+        <v>46154.6875</v>
       </c>
       <c r="B164">
-        <v>1052.596</v>
+        <v>1104.717</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46150.69791666666</v>
+        <v>46154.69791666666</v>
       </c>
       <c r="B165">
-        <v>939.599</v>
+        <v>998.577</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46150.70833333334</v>
+        <v>46154.70833333334</v>
       </c>
       <c r="B166">
-        <v>761.752</v>
+        <v>831.554</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46150.71875</v>
+        <v>46154.71875</v>
       </c>
       <c r="B167">
-        <v>642.043</v>
+        <v>725.431</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46150.72916666666</v>
+        <v>46154.72916666666</v>
       </c>
       <c r="B168">
-        <v>536.2430000000001</v>
+        <v>619.076</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46150.73958333334</v>
+        <v>46154.73958333334</v>
       </c>
       <c r="B169">
-        <v>440.37</v>
+        <v>515.04</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46150.75</v>
+        <v>46154.75</v>
       </c>
       <c r="B170">
-        <v>307.407</v>
+        <v>363.742</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46150.76041666666</v>
+        <v>46154.76041666666</v>
       </c>
       <c r="B171">
-        <v>231.467</v>
+        <v>290.164</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46150.77083333334</v>
+        <v>46154.77083333334</v>
       </c>
       <c r="B172">
-        <v>159.121</v>
+        <v>206.819</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46150.78125</v>
+        <v>46154.78125</v>
       </c>
       <c r="B173">
-        <v>115.64</v>
+        <v>143.142</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46150.79166666666</v>
+        <v>46154.79166666666</v>
       </c>
       <c r="B174">
-        <v>60.973</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46150.80208333334</v>
+        <v>46154.80208333334</v>
       </c>
       <c r="B175">
-        <v>43.659</v>
+        <v>50.586</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46150.8125</v>
+        <v>46154.8125</v>
       </c>
       <c r="B176">
-        <v>32.729</v>
+        <v>36.483</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46150.82291666666</v>
+        <v>46154.82291666666</v>
       </c>
       <c r="B177">
-        <v>26.329</v>
+        <v>34.395</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46150.83333333334</v>
+        <v>46154.83333333334</v>
       </c>
       <c r="B178">
-        <v>19.912</v>
+        <v>19.039</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46150.84375</v>
+        <v>46154.84375</v>
       </c>
       <c r="B179">
-        <v>19.686</v>
+        <v>15.581</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46150.85416666666</v>
+        <v>46154.85416666666</v>
       </c>
       <c r="B180">
-        <v>19.206</v>
+        <v>15.226</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46150.86458333334</v>
+        <v>46154.86458333334</v>
       </c>
       <c r="B181">
-        <v>18.414</v>
+        <v>12.029</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46150.875</v>
+        <v>46154.875</v>
       </c>
       <c r="B182">
-        <v>15.83</v>
+        <v>14.13</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46150.88541666666</v>
+        <v>46154.88541666666</v>
       </c>
       <c r="B183">
-        <v>13.53</v>
+        <v>4.73</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46150.89583333334</v>
+        <v>46154.89583333334</v>
       </c>
       <c r="B184">
-        <v>9.73</v>
+        <v>1.63</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46150.90625</v>
+        <v>46154.90625</v>
       </c>
       <c r="B185">
-        <v>9.130000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46150.91666666666</v>
+        <v>46154.91666666666</v>
       </c>
       <c r="B186">
-        <v>8.23</v>
+        <v>4.43</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46150.92708333334</v>
+        <v>46154.92708333334</v>
       </c>
       <c r="B187">
-        <v>2.73</v>
+        <v>0.73</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46150.9375</v>
+        <v>46154.9375</v>
       </c>
       <c r="B188">
-        <v>9.23</v>
+        <v>0</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46150.94791666666</v>
+        <v>46154.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46150.95833333334</v>
+        <v>46154.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46150.96875</v>
+        <v>46154.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46150.97916666666</v>
+        <v>46154.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46150.98958333334</v>
+        <v>46154.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.05.20261</t>
-  </si>
-  <si>
-    <t>11.05.20262</t>
-  </si>
-  <si>
-    <t>11.05.20263</t>
-  </si>
-  <si>
-    <t>11.05.20264</t>
-  </si>
-  <si>
-    <t>11.05.20265</t>
-  </si>
-  <si>
-    <t>11.05.20266</t>
-  </si>
-  <si>
-    <t>11.05.20267</t>
-  </si>
-  <si>
-    <t>11.05.20268</t>
-  </si>
-  <si>
-    <t>11.05.20269</t>
-  </si>
-  <si>
-    <t>11.05.202610</t>
-  </si>
-  <si>
-    <t>11.05.202611</t>
-  </si>
-  <si>
-    <t>11.05.202612</t>
-  </si>
-  <si>
-    <t>11.05.202613</t>
-  </si>
-  <si>
-    <t>11.05.202614</t>
-  </si>
-  <si>
-    <t>11.05.202615</t>
-  </si>
-  <si>
-    <t>11.05.202616</t>
-  </si>
-  <si>
-    <t>11.05.202617</t>
-  </si>
-  <si>
-    <t>11.05.202618</t>
-  </si>
-  <si>
-    <t>11.05.202619</t>
-  </si>
-  <si>
-    <t>11.05.202620</t>
-  </si>
-  <si>
-    <t>11.05.202621</t>
-  </si>
-  <si>
-    <t>11.05.202622</t>
-  </si>
-  <si>
-    <t>11.05.202623</t>
-  </si>
-  <si>
-    <t>11.05.202624</t>
-  </si>
-  <si>
-    <t>11.05.202625</t>
-  </si>
-  <si>
-    <t>11.05.202626</t>
-  </si>
-  <si>
-    <t>11.05.202627</t>
-  </si>
-  <si>
-    <t>11.05.202628</t>
-  </si>
-  <si>
-    <t>11.05.202629</t>
-  </si>
-  <si>
-    <t>11.05.202630</t>
-  </si>
-  <si>
-    <t>11.05.202631</t>
-  </si>
-  <si>
-    <t>11.05.202632</t>
-  </si>
-  <si>
-    <t>11.05.202633</t>
-  </si>
-  <si>
-    <t>11.05.202634</t>
-  </si>
-  <si>
-    <t>11.05.202635</t>
-  </si>
-  <si>
-    <t>11.05.202636</t>
-  </si>
-  <si>
-    <t>11.05.202637</t>
-  </si>
-  <si>
-    <t>11.05.202638</t>
-  </si>
-  <si>
-    <t>11.05.202639</t>
-  </si>
-  <si>
-    <t>11.05.202640</t>
-  </si>
-  <si>
-    <t>11.05.202641</t>
-  </si>
-  <si>
-    <t>11.05.202642</t>
-  </si>
-  <si>
-    <t>11.05.202643</t>
-  </si>
-  <si>
-    <t>11.05.202644</t>
-  </si>
-  <si>
-    <t>11.05.202645</t>
-  </si>
-  <si>
-    <t>11.05.202646</t>
-  </si>
-  <si>
-    <t>11.05.202647</t>
-  </si>
-  <si>
-    <t>11.05.202648</t>
-  </si>
-  <si>
-    <t>11.05.202649</t>
-  </si>
-  <si>
-    <t>11.05.202650</t>
-  </si>
-  <si>
-    <t>11.05.202651</t>
-  </si>
-  <si>
-    <t>11.05.202652</t>
-  </si>
-  <si>
-    <t>11.05.202653</t>
-  </si>
-  <si>
-    <t>11.05.202654</t>
-  </si>
-  <si>
-    <t>11.05.202655</t>
-  </si>
-  <si>
-    <t>11.05.202656</t>
-  </si>
-  <si>
-    <t>11.05.202657</t>
-  </si>
-  <si>
-    <t>11.05.202658</t>
-  </si>
-  <si>
-    <t>11.05.202659</t>
-  </si>
-  <si>
-    <t>11.05.202660</t>
-  </si>
-  <si>
-    <t>11.05.202661</t>
-  </si>
-  <si>
-    <t>11.05.202662</t>
-  </si>
-  <si>
-    <t>11.05.202663</t>
-  </si>
-  <si>
-    <t>11.05.202664</t>
-  </si>
-  <si>
-    <t>11.05.202665</t>
-  </si>
-  <si>
-    <t>11.05.202666</t>
-  </si>
-  <si>
-    <t>11.05.202667</t>
-  </si>
-  <si>
-    <t>11.05.202668</t>
-  </si>
-  <si>
-    <t>11.05.202669</t>
-  </si>
-  <si>
-    <t>11.05.202670</t>
-  </si>
-  <si>
-    <t>11.05.202671</t>
-  </si>
-  <si>
-    <t>11.05.202672</t>
-  </si>
-  <si>
-    <t>11.05.202673</t>
-  </si>
-  <si>
-    <t>11.05.202674</t>
-  </si>
-  <si>
-    <t>11.05.202675</t>
-  </si>
-  <si>
-    <t>11.05.202676</t>
-  </si>
-  <si>
-    <t>11.05.202677</t>
-  </si>
-  <si>
-    <t>11.05.202678</t>
-  </si>
-  <si>
-    <t>11.05.202679</t>
-  </si>
-  <si>
-    <t>11.05.202680</t>
-  </si>
-  <si>
-    <t>11.05.202681</t>
-  </si>
-  <si>
-    <t>11.05.202682</t>
-  </si>
-  <si>
-    <t>11.05.202683</t>
-  </si>
-  <si>
-    <t>11.05.202684</t>
-  </si>
-  <si>
-    <t>11.05.202685</t>
-  </si>
-  <si>
-    <t>11.05.202686</t>
-  </si>
-  <si>
-    <t>11.05.202687</t>
-  </si>
-  <si>
-    <t>11.05.202688</t>
-  </si>
-  <si>
-    <t>11.05.202689</t>
-  </si>
-  <si>
-    <t>11.05.202690</t>
-  </si>
-  <si>
-    <t>11.05.202691</t>
-  </si>
-  <si>
-    <t>11.05.202692</t>
-  </si>
-  <si>
-    <t>11.05.202693</t>
-  </si>
-  <si>
-    <t>11.05.202694</t>
-  </si>
-  <si>
-    <t>11.05.202695</t>
-  </si>
-  <si>
-    <t>11.05.202696</t>
-  </si>
-  <si>
-    <t>12.05.20261</t>
-  </si>
-  <si>
-    <t>12.05.20262</t>
-  </si>
-  <si>
-    <t>12.05.20263</t>
-  </si>
-  <si>
-    <t>12.05.20264</t>
-  </si>
-  <si>
-    <t>12.05.20265</t>
-  </si>
-  <si>
-    <t>12.05.20266</t>
-  </si>
-  <si>
-    <t>12.05.20267</t>
-  </si>
-  <si>
-    <t>12.05.20268</t>
-  </si>
-  <si>
-    <t>12.05.20269</t>
-  </si>
-  <si>
-    <t>12.05.202610</t>
-  </si>
-  <si>
-    <t>12.05.202611</t>
-  </si>
-  <si>
-    <t>12.05.202612</t>
-  </si>
-  <si>
-    <t>12.05.202613</t>
-  </si>
-  <si>
-    <t>12.05.202614</t>
-  </si>
-  <si>
-    <t>12.05.202615</t>
-  </si>
-  <si>
-    <t>12.05.202616</t>
-  </si>
-  <si>
-    <t>12.05.202617</t>
-  </si>
-  <si>
-    <t>12.05.202618</t>
-  </si>
-  <si>
-    <t>12.05.202619</t>
-  </si>
-  <si>
-    <t>12.05.202620</t>
-  </si>
-  <si>
-    <t>12.05.202621</t>
-  </si>
-  <si>
-    <t>12.05.202622</t>
-  </si>
-  <si>
-    <t>12.05.202623</t>
-  </si>
-  <si>
-    <t>12.05.202624</t>
-  </si>
-  <si>
-    <t>12.05.202625</t>
-  </si>
-  <si>
-    <t>12.05.202626</t>
-  </si>
-  <si>
-    <t>12.05.202627</t>
-  </si>
-  <si>
-    <t>12.05.202628</t>
-  </si>
-  <si>
-    <t>12.05.202629</t>
-  </si>
-  <si>
-    <t>12.05.202630</t>
-  </si>
-  <si>
-    <t>12.05.202631</t>
-  </si>
-  <si>
-    <t>12.05.202632</t>
-  </si>
-  <si>
-    <t>12.05.202633</t>
-  </si>
-  <si>
-    <t>12.05.202634</t>
-  </si>
-  <si>
-    <t>12.05.202635</t>
-  </si>
-  <si>
-    <t>12.05.202636</t>
-  </si>
-  <si>
-    <t>12.05.202637</t>
-  </si>
-  <si>
-    <t>12.05.202638</t>
-  </si>
-  <si>
-    <t>12.05.202639</t>
-  </si>
-  <si>
-    <t>12.05.202640</t>
-  </si>
-  <si>
-    <t>12.05.202641</t>
-  </si>
-  <si>
-    <t>12.05.202642</t>
-  </si>
-  <si>
-    <t>12.05.202643</t>
-  </si>
-  <si>
-    <t>12.05.202644</t>
-  </si>
-  <si>
-    <t>12.05.202645</t>
-  </si>
-  <si>
-    <t>12.05.202646</t>
-  </si>
-  <si>
-    <t>12.05.202647</t>
-  </si>
-  <si>
-    <t>12.05.202648</t>
-  </si>
-  <si>
-    <t>12.05.202649</t>
-  </si>
-  <si>
-    <t>12.05.202650</t>
-  </si>
-  <si>
-    <t>12.05.202651</t>
-  </si>
-  <si>
-    <t>12.05.202652</t>
-  </si>
-  <si>
-    <t>12.05.202653</t>
-  </si>
-  <si>
-    <t>12.05.202654</t>
-  </si>
-  <si>
-    <t>12.05.202655</t>
-  </si>
-  <si>
-    <t>12.05.202656</t>
-  </si>
-  <si>
-    <t>12.05.202657</t>
-  </si>
-  <si>
-    <t>12.05.202658</t>
-  </si>
-  <si>
-    <t>12.05.202659</t>
-  </si>
-  <si>
-    <t>12.05.202660</t>
-  </si>
-  <si>
-    <t>12.05.202661</t>
-  </si>
-  <si>
-    <t>12.05.202662</t>
-  </si>
-  <si>
-    <t>12.05.202663</t>
-  </si>
-  <si>
-    <t>12.05.202664</t>
-  </si>
-  <si>
-    <t>12.05.202665</t>
-  </si>
-  <si>
-    <t>12.05.202666</t>
-  </si>
-  <si>
-    <t>12.05.202667</t>
-  </si>
-  <si>
-    <t>12.05.202668</t>
-  </si>
-  <si>
-    <t>12.05.202669</t>
-  </si>
-  <si>
-    <t>12.05.202670</t>
-  </si>
-  <si>
-    <t>12.05.202671</t>
-  </si>
-  <si>
-    <t>12.05.202672</t>
-  </si>
-  <si>
-    <t>12.05.202673</t>
-  </si>
-  <si>
-    <t>12.05.202674</t>
-  </si>
-  <si>
-    <t>12.05.202675</t>
-  </si>
-  <si>
-    <t>12.05.202676</t>
-  </si>
-  <si>
-    <t>12.05.202677</t>
-  </si>
-  <si>
-    <t>12.05.202678</t>
-  </si>
-  <si>
-    <t>12.05.202679</t>
-  </si>
-  <si>
-    <t>12.05.202680</t>
-  </si>
-  <si>
-    <t>12.05.202681</t>
-  </si>
-  <si>
-    <t>12.05.202682</t>
-  </si>
-  <si>
-    <t>12.05.202683</t>
-  </si>
-  <si>
-    <t>12.05.202684</t>
-  </si>
-  <si>
-    <t>12.05.202685</t>
-  </si>
-  <si>
-    <t>12.05.202686</t>
-  </si>
-  <si>
-    <t>12.05.202687</t>
-  </si>
-  <si>
-    <t>12.05.202688</t>
-  </si>
-  <si>
-    <t>12.05.202689</t>
-  </si>
-  <si>
-    <t>12.05.202690</t>
-  </si>
-  <si>
-    <t>12.05.202691</t>
-  </si>
-  <si>
-    <t>12.05.202692</t>
-  </si>
-  <si>
-    <t>12.05.202693</t>
-  </si>
-  <si>
-    <t>12.05.202694</t>
-  </si>
-  <si>
-    <t>12.05.202695</t>
-  </si>
-  <si>
-    <t>12.05.202696</t>
+    <t>13.05.20261</t>
+  </si>
+  <si>
+    <t>13.05.20262</t>
+  </si>
+  <si>
+    <t>13.05.20263</t>
+  </si>
+  <si>
+    <t>13.05.20264</t>
+  </si>
+  <si>
+    <t>13.05.20265</t>
+  </si>
+  <si>
+    <t>13.05.20266</t>
+  </si>
+  <si>
+    <t>13.05.20267</t>
+  </si>
+  <si>
+    <t>13.05.20268</t>
+  </si>
+  <si>
+    <t>13.05.20269</t>
+  </si>
+  <si>
+    <t>13.05.202610</t>
+  </si>
+  <si>
+    <t>13.05.202611</t>
+  </si>
+  <si>
+    <t>13.05.202612</t>
+  </si>
+  <si>
+    <t>13.05.202613</t>
+  </si>
+  <si>
+    <t>13.05.202614</t>
+  </si>
+  <si>
+    <t>13.05.202615</t>
+  </si>
+  <si>
+    <t>13.05.202616</t>
+  </si>
+  <si>
+    <t>13.05.202617</t>
+  </si>
+  <si>
+    <t>13.05.202618</t>
+  </si>
+  <si>
+    <t>13.05.202619</t>
+  </si>
+  <si>
+    <t>13.05.202620</t>
+  </si>
+  <si>
+    <t>13.05.202621</t>
+  </si>
+  <si>
+    <t>13.05.202622</t>
+  </si>
+  <si>
+    <t>13.05.202623</t>
+  </si>
+  <si>
+    <t>13.05.202624</t>
+  </si>
+  <si>
+    <t>13.05.202625</t>
+  </si>
+  <si>
+    <t>13.05.202626</t>
+  </si>
+  <si>
+    <t>13.05.202627</t>
+  </si>
+  <si>
+    <t>13.05.202628</t>
+  </si>
+  <si>
+    <t>13.05.202629</t>
+  </si>
+  <si>
+    <t>13.05.202630</t>
+  </si>
+  <si>
+    <t>13.05.202631</t>
+  </si>
+  <si>
+    <t>13.05.202632</t>
+  </si>
+  <si>
+    <t>13.05.202633</t>
+  </si>
+  <si>
+    <t>13.05.202634</t>
+  </si>
+  <si>
+    <t>13.05.202635</t>
+  </si>
+  <si>
+    <t>13.05.202636</t>
+  </si>
+  <si>
+    <t>13.05.202637</t>
+  </si>
+  <si>
+    <t>13.05.202638</t>
+  </si>
+  <si>
+    <t>13.05.202639</t>
+  </si>
+  <si>
+    <t>13.05.202640</t>
+  </si>
+  <si>
+    <t>13.05.202641</t>
+  </si>
+  <si>
+    <t>13.05.202642</t>
+  </si>
+  <si>
+    <t>13.05.202643</t>
+  </si>
+  <si>
+    <t>13.05.202644</t>
+  </si>
+  <si>
+    <t>13.05.202645</t>
+  </si>
+  <si>
+    <t>13.05.202646</t>
+  </si>
+  <si>
+    <t>13.05.202647</t>
+  </si>
+  <si>
+    <t>13.05.202648</t>
+  </si>
+  <si>
+    <t>13.05.202649</t>
+  </si>
+  <si>
+    <t>13.05.202650</t>
+  </si>
+  <si>
+    <t>13.05.202651</t>
+  </si>
+  <si>
+    <t>13.05.202652</t>
+  </si>
+  <si>
+    <t>13.05.202653</t>
+  </si>
+  <si>
+    <t>13.05.202654</t>
+  </si>
+  <si>
+    <t>13.05.202655</t>
+  </si>
+  <si>
+    <t>13.05.202656</t>
+  </si>
+  <si>
+    <t>13.05.202657</t>
+  </si>
+  <si>
+    <t>13.05.202658</t>
+  </si>
+  <si>
+    <t>13.05.202659</t>
+  </si>
+  <si>
+    <t>13.05.202660</t>
+  </si>
+  <si>
+    <t>13.05.202661</t>
+  </si>
+  <si>
+    <t>13.05.202662</t>
+  </si>
+  <si>
+    <t>13.05.202663</t>
+  </si>
+  <si>
+    <t>13.05.202664</t>
+  </si>
+  <si>
+    <t>13.05.202665</t>
+  </si>
+  <si>
+    <t>13.05.202666</t>
+  </si>
+  <si>
+    <t>13.05.202667</t>
+  </si>
+  <si>
+    <t>13.05.202668</t>
+  </si>
+  <si>
+    <t>13.05.202669</t>
+  </si>
+  <si>
+    <t>13.05.202670</t>
+  </si>
+  <si>
+    <t>13.05.202671</t>
+  </si>
+  <si>
+    <t>13.05.202672</t>
+  </si>
+  <si>
+    <t>13.05.202673</t>
+  </si>
+  <si>
+    <t>13.05.202674</t>
+  </si>
+  <si>
+    <t>13.05.202675</t>
+  </si>
+  <si>
+    <t>13.05.202676</t>
+  </si>
+  <si>
+    <t>13.05.202677</t>
+  </si>
+  <si>
+    <t>13.05.202678</t>
+  </si>
+  <si>
+    <t>13.05.202679</t>
+  </si>
+  <si>
+    <t>13.05.202680</t>
+  </si>
+  <si>
+    <t>13.05.202681</t>
+  </si>
+  <si>
+    <t>13.05.202682</t>
+  </si>
+  <si>
+    <t>13.05.202683</t>
+  </si>
+  <si>
+    <t>13.05.202684</t>
+  </si>
+  <si>
+    <t>13.05.202685</t>
+  </si>
+  <si>
+    <t>13.05.202686</t>
+  </si>
+  <si>
+    <t>13.05.202687</t>
+  </si>
+  <si>
+    <t>13.05.202688</t>
+  </si>
+  <si>
+    <t>13.05.202689</t>
+  </si>
+  <si>
+    <t>13.05.202690</t>
+  </si>
+  <si>
+    <t>13.05.202691</t>
+  </si>
+  <si>
+    <t>13.05.202692</t>
+  </si>
+  <si>
+    <t>13.05.202693</t>
+  </si>
+  <si>
+    <t>13.05.202694</t>
+  </si>
+  <si>
+    <t>13.05.202695</t>
+  </si>
+  <si>
+    <t>13.05.202696</t>
+  </si>
+  <si>
+    <t>14.05.20261</t>
+  </si>
+  <si>
+    <t>14.05.20262</t>
+  </si>
+  <si>
+    <t>14.05.20263</t>
+  </si>
+  <si>
+    <t>14.05.20264</t>
+  </si>
+  <si>
+    <t>14.05.20265</t>
+  </si>
+  <si>
+    <t>14.05.20266</t>
+  </si>
+  <si>
+    <t>14.05.20267</t>
+  </si>
+  <si>
+    <t>14.05.20268</t>
+  </si>
+  <si>
+    <t>14.05.20269</t>
+  </si>
+  <si>
+    <t>14.05.202610</t>
+  </si>
+  <si>
+    <t>14.05.202611</t>
+  </si>
+  <si>
+    <t>14.05.202612</t>
+  </si>
+  <si>
+    <t>14.05.202613</t>
+  </si>
+  <si>
+    <t>14.05.202614</t>
+  </si>
+  <si>
+    <t>14.05.202615</t>
+  </si>
+  <si>
+    <t>14.05.202616</t>
+  </si>
+  <si>
+    <t>14.05.202617</t>
+  </si>
+  <si>
+    <t>14.05.202618</t>
+  </si>
+  <si>
+    <t>14.05.202619</t>
+  </si>
+  <si>
+    <t>14.05.202620</t>
+  </si>
+  <si>
+    <t>14.05.202621</t>
+  </si>
+  <si>
+    <t>14.05.202622</t>
+  </si>
+  <si>
+    <t>14.05.202623</t>
+  </si>
+  <si>
+    <t>14.05.202624</t>
+  </si>
+  <si>
+    <t>14.05.202625</t>
+  </si>
+  <si>
+    <t>14.05.202626</t>
+  </si>
+  <si>
+    <t>14.05.202627</t>
+  </si>
+  <si>
+    <t>14.05.202628</t>
+  </si>
+  <si>
+    <t>14.05.202629</t>
+  </si>
+  <si>
+    <t>14.05.202630</t>
+  </si>
+  <si>
+    <t>14.05.202631</t>
+  </si>
+  <si>
+    <t>14.05.202632</t>
+  </si>
+  <si>
+    <t>14.05.202633</t>
+  </si>
+  <si>
+    <t>14.05.202634</t>
+  </si>
+  <si>
+    <t>14.05.202635</t>
+  </si>
+  <si>
+    <t>14.05.202636</t>
+  </si>
+  <si>
+    <t>14.05.202637</t>
+  </si>
+  <si>
+    <t>14.05.202638</t>
+  </si>
+  <si>
+    <t>14.05.202639</t>
+  </si>
+  <si>
+    <t>14.05.202640</t>
+  </si>
+  <si>
+    <t>14.05.202641</t>
+  </si>
+  <si>
+    <t>14.05.202642</t>
+  </si>
+  <si>
+    <t>14.05.202643</t>
+  </si>
+  <si>
+    <t>14.05.202644</t>
+  </si>
+  <si>
+    <t>14.05.202645</t>
+  </si>
+  <si>
+    <t>14.05.202646</t>
+  </si>
+  <si>
+    <t>14.05.202647</t>
+  </si>
+  <si>
+    <t>14.05.202648</t>
+  </si>
+  <si>
+    <t>14.05.202649</t>
+  </si>
+  <si>
+    <t>14.05.202650</t>
+  </si>
+  <si>
+    <t>14.05.202651</t>
+  </si>
+  <si>
+    <t>14.05.202652</t>
+  </si>
+  <si>
+    <t>14.05.202653</t>
+  </si>
+  <si>
+    <t>14.05.202654</t>
+  </si>
+  <si>
+    <t>14.05.202655</t>
+  </si>
+  <si>
+    <t>14.05.202656</t>
+  </si>
+  <si>
+    <t>14.05.202657</t>
+  </si>
+  <si>
+    <t>14.05.202658</t>
+  </si>
+  <si>
+    <t>14.05.202659</t>
+  </si>
+  <si>
+    <t>14.05.202660</t>
+  </si>
+  <si>
+    <t>14.05.202661</t>
+  </si>
+  <si>
+    <t>14.05.202662</t>
+  </si>
+  <si>
+    <t>14.05.202663</t>
+  </si>
+  <si>
+    <t>14.05.202664</t>
+  </si>
+  <si>
+    <t>14.05.202665</t>
+  </si>
+  <si>
+    <t>14.05.202666</t>
+  </si>
+  <si>
+    <t>14.05.202667</t>
+  </si>
+  <si>
+    <t>14.05.202668</t>
+  </si>
+  <si>
+    <t>14.05.202669</t>
+  </si>
+  <si>
+    <t>14.05.202670</t>
+  </si>
+  <si>
+    <t>14.05.202671</t>
+  </si>
+  <si>
+    <t>14.05.202672</t>
+  </si>
+  <si>
+    <t>14.05.202673</t>
+  </si>
+  <si>
+    <t>14.05.202674</t>
+  </si>
+  <si>
+    <t>14.05.202675</t>
+  </si>
+  <si>
+    <t>14.05.202676</t>
+  </si>
+  <si>
+    <t>14.05.202677</t>
+  </si>
+  <si>
+    <t>14.05.202678</t>
+  </si>
+  <si>
+    <t>14.05.202679</t>
+  </si>
+  <si>
+    <t>14.05.202680</t>
+  </si>
+  <si>
+    <t>14.05.202681</t>
+  </si>
+  <si>
+    <t>14.05.202682</t>
+  </si>
+  <si>
+    <t>14.05.202683</t>
+  </si>
+  <si>
+    <t>14.05.202684</t>
+  </si>
+  <si>
+    <t>14.05.202685</t>
+  </si>
+  <si>
+    <t>14.05.202686</t>
+  </si>
+  <si>
+    <t>14.05.202687</t>
+  </si>
+  <si>
+    <t>14.05.202688</t>
+  </si>
+  <si>
+    <t>14.05.202689</t>
+  </si>
+  <si>
+    <t>14.05.202690</t>
+  </si>
+  <si>
+    <t>14.05.202691</t>
+  </si>
+  <si>
+    <t>14.05.202692</t>
+  </si>
+  <si>
+    <t>14.05.202693</t>
+  </si>
+  <si>
+    <t>14.05.202694</t>
+  </si>
+  <si>
+    <t>14.05.202695</t>
+  </si>
+  <si>
+    <t>14.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.731</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>0.733</v>
+        <v>0.731</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.734</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.736</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>0.741</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.745</v>
+        <v>0.858</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.753</v>
+        <v>0</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>2.148</v>
+        <v>0.866</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>2.316</v>
+        <v>1.197</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>14.138</v>
+        <v>8.992000000000001</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>41.918</v>
+        <v>23.671</v>
       </c>
       <c r="C23">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>79.958</v>
+        <v>51.042</v>
       </c>
       <c r="C24">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>132.078</v>
+        <v>87.053</v>
       </c>
       <c r="C25">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>257.486</v>
+        <v>175.454</v>
       </c>
       <c r="C26">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>350.136</v>
+        <v>246.227</v>
       </c>
       <c r="C27">
-        <v>337</v>
+        <v>211</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>477.18</v>
+        <v>332.908</v>
       </c>
       <c r="C28">
-        <v>470</v>
+        <v>297</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>610.441</v>
+        <v>430.616</v>
       </c>
       <c r="C29">
-        <v>613</v>
+        <v>364</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>830.992</v>
+        <v>607.95</v>
       </c>
       <c r="C30">
-        <v>750</v>
+        <v>448</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>993.547</v>
+        <v>728.011</v>
       </c>
       <c r="C31">
-        <v>917</v>
+        <v>522</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>1178.372</v>
+        <v>842.097</v>
       </c>
       <c r="C32">
-        <v>1029</v>
+        <v>649</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>1348.584</v>
+        <v>970.712</v>
       </c>
       <c r="C33">
-        <v>1117</v>
+        <v>781</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>1591.667</v>
+        <v>1190.038</v>
       </c>
       <c r="C34">
-        <v>1269</v>
+        <v>859</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>1723.146</v>
+        <v>1283.802</v>
       </c>
       <c r="C35">
-        <v>1381</v>
+        <v>926</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>1864.455</v>
+        <v>1364.253</v>
       </c>
       <c r="C36">
-        <v>1472</v>
+        <v>1002</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>1997.349</v>
+        <v>1467.24</v>
       </c>
       <c r="C37">
-        <v>1532</v>
+        <v>1048</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>2118.68</v>
+        <v>1590.903</v>
       </c>
       <c r="C38">
-        <v>1582</v>
+        <v>1074</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>2213.983</v>
+        <v>1671.316</v>
       </c>
       <c r="C39">
-        <v>1684</v>
+        <v>1153</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>2313.794</v>
+        <v>1756.409</v>
       </c>
       <c r="C40">
-        <v>1822</v>
+        <v>1145</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>2376.261</v>
+        <v>1822.275</v>
       </c>
       <c r="C41">
-        <v>1819</v>
+        <v>1176</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>2469.051</v>
+        <v>1880.194</v>
       </c>
       <c r="C42">
-        <v>1830</v>
+        <v>1254</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>2539.22</v>
+        <v>1920.662</v>
       </c>
       <c r="C43">
-        <v>1869</v>
+        <v>1285</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>2572.596</v>
+        <v>1953.418</v>
       </c>
       <c r="C44">
-        <v>1858</v>
+        <v>1334</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>2605.104</v>
+        <v>1971.188</v>
       </c>
       <c r="C45">
-        <v>1922</v>
+        <v>1359</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>2591.548</v>
+        <v>2006.828</v>
       </c>
       <c r="C46">
-        <v>1894</v>
+        <v>1398</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>2600.667</v>
+        <v>2012.832</v>
       </c>
       <c r="C47">
-        <v>1955</v>
+        <v>1452</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>2594.493</v>
+        <v>2006.327</v>
       </c>
       <c r="C48">
-        <v>1993</v>
+        <v>1446</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>2594.586</v>
+        <v>1999.472</v>
       </c>
       <c r="C49">
-        <v>1967</v>
+        <v>1391</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>2574.984</v>
+        <v>1993.451</v>
       </c>
       <c r="C50">
-        <v>1965</v>
+        <v>1369</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>2576.57</v>
+        <v>1984.661</v>
       </c>
       <c r="C51">
-        <v>1992</v>
+        <v>1390</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>2559.326</v>
+        <v>1968.759</v>
       </c>
       <c r="C52">
-        <v>1998</v>
+        <v>1393</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>2542.745</v>
+        <v>1946.723</v>
       </c>
       <c r="C53">
-        <v>2009</v>
+        <v>1355</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>2521.463</v>
+        <v>1927.459</v>
       </c>
       <c r="C54">
-        <v>1887</v>
+        <v>1380</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>2481.81</v>
+        <v>1901.482</v>
       </c>
       <c r="C55">
-        <v>1773</v>
+        <v>1440</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>2406.429</v>
+        <v>1875.397</v>
       </c>
       <c r="C56">
-        <v>1721</v>
+        <v>1392</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>2347.573</v>
+        <v>1853.791</v>
       </c>
       <c r="C57">
-        <v>1687</v>
+        <v>1375</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>2234.389</v>
+        <v>1775.26</v>
       </c>
       <c r="C58">
-        <v>1619</v>
+        <v>1353</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>2171.006</v>
+        <v>1731.699</v>
       </c>
       <c r="C59">
-        <v>1599</v>
+        <v>1347</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>2088.722</v>
+        <v>1690.071</v>
       </c>
       <c r="C60">
-        <v>1500</v>
+        <v>1257</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>2007.198</v>
+        <v>1641.266</v>
       </c>
       <c r="C61">
-        <v>1480</v>
+        <v>1360</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>1844.394</v>
+        <v>1515.51</v>
       </c>
       <c r="C62">
-        <v>1433</v>
+        <v>1245</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>1754.045</v>
+        <v>1417.401</v>
       </c>
       <c r="C63">
-        <v>1405</v>
+        <v>1187</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>1651.034</v>
+        <v>1347.891</v>
       </c>
       <c r="C64">
-        <v>1361</v>
+        <v>1151</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>1544.429</v>
+        <v>1272.081</v>
       </c>
       <c r="C65">
-        <v>1242</v>
+        <v>1028</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>1350.744</v>
+        <v>1130.07</v>
       </c>
       <c r="C66">
-        <v>1159</v>
+        <v>934</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>1213.75</v>
+        <v>1025.422</v>
       </c>
       <c r="C67">
-        <v>1083</v>
+        <v>933</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>1089.063</v>
+        <v>937.413</v>
       </c>
       <c r="C68">
-        <v>997</v>
+        <v>854</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>974.899</v>
+        <v>849.402</v>
       </c>
       <c r="C69">
-        <v>944</v>
+        <v>752</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>777.285</v>
+        <v>691.467</v>
       </c>
       <c r="C70">
-        <v>879</v>
+        <v>650</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>656.016</v>
+        <v>601.09</v>
       </c>
       <c r="C71">
-        <v>715</v>
+        <v>562</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>549.751</v>
+        <v>512.218</v>
       </c>
       <c r="C72">
-        <v>572</v>
+        <v>480</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>455.219</v>
+        <v>425.365</v>
       </c>
       <c r="C73">
-        <v>456</v>
+        <v>394</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>317.748</v>
+        <v>291.106</v>
       </c>
       <c r="C74">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>240.797</v>
+        <v>225.692</v>
       </c>
       <c r="C75">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>176.789</v>
+        <v>166.081</v>
       </c>
       <c r="C76">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>118.751</v>
+        <v>117.307</v>
       </c>
       <c r="C77">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>66.57599999999999</v>
+        <v>67.206</v>
       </c>
       <c r="C78">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>41.416</v>
+        <v>43.034</v>
       </c>
       <c r="C79">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>28.329</v>
+        <v>30.422</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>21.537</v>
+        <v>22.478</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>12.464</v>
+        <v>22.49</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>15.273</v>
+        <v>20.587</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>17.504</v>
+        <v>20.212</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>12.01</v>
+        <v>21.204</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>5.13</v>
+        <v>20.13</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
-        <v>4.73</v>
+        <v>13.23</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.63</v>
+        <v>5.83</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>1.23</v>
+        <v>0.73</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.73</v>
+        <v>5.43</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>0.736</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>0.738</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.262</v>
+        <v>1.256</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.297</v>
+        <v>1.26</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B116">
-        <v>1.274</v>
+        <v>1.299</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.368</v>
+        <v>1.478</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B118">
-        <v>18.055</v>
+        <v>31.249</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B119">
-        <v>38.648</v>
+        <v>63.136</v>
       </c>
       <c r="C119">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B120">
-        <v>76.488</v>
+        <v>112.48</v>
       </c>
       <c r="C120">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B121">
-        <v>124.529</v>
+        <v>175.338</v>
       </c>
       <c r="C121">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B122">
-        <v>248.558</v>
+        <v>311.355</v>
       </c>
       <c r="C122">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B123">
-        <v>331.922</v>
+        <v>417.942</v>
       </c>
       <c r="C123">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B124">
-        <v>439.529</v>
+        <v>540.324</v>
       </c>
       <c r="C124">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B125">
-        <v>557.573</v>
+        <v>679.886</v>
       </c>
       <c r="C125">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B126">
-        <v>746.322</v>
+        <v>994.159</v>
       </c>
       <c r="C126">
-        <v>632</v>
+        <v>601</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B127">
-        <v>859.687</v>
+        <v>1176.464</v>
       </c>
       <c r="C127">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B128">
-        <v>993.826</v>
+        <v>1354.459</v>
       </c>
       <c r="C128">
-        <v>797</v>
+        <v>897</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B129">
-        <v>1132.311</v>
+        <v>1541.154</v>
       </c>
       <c r="C129">
-        <v>908</v>
+        <v>1063</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B130">
-        <v>1356.846</v>
+        <v>1779.083</v>
       </c>
       <c r="C130">
-        <v>939</v>
+        <v>1256</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B131">
-        <v>1489.237</v>
+        <v>1950.896</v>
       </c>
       <c r="C131">
-        <v>974</v>
+        <v>1430</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B132">
-        <v>1605.087</v>
+        <v>2119.794</v>
       </c>
       <c r="C132">
-        <v>1068</v>
+        <v>1520</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B133">
-        <v>1725.646</v>
+        <v>2287.632</v>
       </c>
       <c r="C133">
-        <v>1134</v>
+        <v>1607</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B134">
-        <v>1885.775</v>
+        <v>2447.624</v>
       </c>
       <c r="C134">
-        <v>1168</v>
+        <v>1706</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B135">
-        <v>1951.338</v>
+        <v>2560.062</v>
       </c>
       <c r="C135">
-        <v>1163</v>
+        <v>1782</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B136">
-        <v>2023.587</v>
+        <v>2659.149</v>
       </c>
       <c r="C136">
-        <v>1239</v>
+        <v>1848</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B137">
-        <v>2084.086</v>
+        <v>2744.978</v>
       </c>
       <c r="C137">
-        <v>1244</v>
+        <v>1937</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B138">
-        <v>2166.236</v>
+        <v>2793.637</v>
       </c>
       <c r="C138">
-        <v>1413</v>
+        <v>1946</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B139">
-        <v>2203.75</v>
+        <v>2830.731</v>
       </c>
       <c r="C139">
-        <v>1496</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B140">
-        <v>2236.966</v>
+        <v>2855.859</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B141">
-        <v>2259.759</v>
+        <v>2883.404</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B142">
-        <v>2256.857</v>
+        <v>2912.033</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B143">
-        <v>2228.659</v>
+        <v>2907.561</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B144">
-        <v>2223.257</v>
+        <v>2890.374</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B145">
-        <v>2217.456</v>
+        <v>2876.851</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B146">
-        <v>2221.933</v>
+        <v>2864.175</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B147">
-        <v>2219.432</v>
+        <v>2836.133</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B148">
-        <v>2196.833</v>
+        <v>2807.157</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B149">
-        <v>2186.323</v>
+        <v>2791.156</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B150">
-        <v>2132.365</v>
+        <v>2748.554</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B151">
-        <v>2117.549</v>
+        <v>2725.286</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B152">
-        <v>2096.992</v>
+        <v>2682.541</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B153">
-        <v>2069.96</v>
+        <v>2662.042</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B154">
-        <v>1991.711</v>
+        <v>2597.353</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B155">
-        <v>1918.93</v>
+        <v>2552.622</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B156">
-        <v>1845.74</v>
+        <v>2505.776</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B157">
-        <v>1796.869</v>
+        <v>2457.893</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B158">
-        <v>1696.079</v>
+        <v>2352.909</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B159">
-        <v>1621.274</v>
+        <v>2270.755</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B160">
-        <v>1552.654</v>
+        <v>2177.285</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B161">
-        <v>1476.607</v>
+        <v>2095.707</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B162">
-        <v>1305.415</v>
+        <v>1937.55</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B163">
-        <v>1214.059</v>
+        <v>1789.268</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B164">
-        <v>1104.717</v>
+        <v>1647.55</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B165">
-        <v>998.577</v>
+        <v>1494.335</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B166">
-        <v>831.554</v>
+        <v>1259.164</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B167">
-        <v>725.431</v>
+        <v>1104.201</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B168">
-        <v>619.076</v>
+        <v>954.193</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B169">
-        <v>515.04</v>
+        <v>800.663</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B170">
-        <v>363.742</v>
+        <v>580.751</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B171">
-        <v>290.164</v>
+        <v>449.897</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B172">
-        <v>206.819</v>
+        <v>341.923</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B173">
-        <v>143.142</v>
+        <v>253.339</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B174">
-        <v>79.73999999999999</v>
+        <v>114.921</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B175">
-        <v>50.586</v>
+        <v>78.324</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B176">
-        <v>36.483</v>
+        <v>48.262</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B177">
-        <v>34.395</v>
+        <v>34.226</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B178">
-        <v>19.039</v>
+        <v>22.968</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B179">
-        <v>15.581</v>
+        <v>20.243</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B180">
-        <v>15.226</v>
+        <v>20.244</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B181">
-        <v>12.029</v>
+        <v>19.694</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B182">
         <v>14.13</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B183">
-        <v>4.73</v>
+        <v>13.73</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B184">
-        <v>1.63</v>
+        <v>5.33</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B185">
-        <v>10.23</v>
+        <v>4.93</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B186">
-        <v>4.43</v>
+        <v>2.03</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B187">
         <v>0.73</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.05.20261</t>
-  </si>
-  <si>
-    <t>13.05.20262</t>
-  </si>
-  <si>
-    <t>13.05.20263</t>
-  </si>
-  <si>
-    <t>13.05.20264</t>
-  </si>
-  <si>
-    <t>13.05.20265</t>
-  </si>
-  <si>
-    <t>13.05.20266</t>
-  </si>
-  <si>
-    <t>13.05.20267</t>
-  </si>
-  <si>
-    <t>13.05.20268</t>
-  </si>
-  <si>
-    <t>13.05.20269</t>
-  </si>
-  <si>
-    <t>13.05.202610</t>
-  </si>
-  <si>
-    <t>13.05.202611</t>
-  </si>
-  <si>
-    <t>13.05.202612</t>
-  </si>
-  <si>
-    <t>13.05.202613</t>
-  </si>
-  <si>
-    <t>13.05.202614</t>
-  </si>
-  <si>
-    <t>13.05.202615</t>
-  </si>
-  <si>
-    <t>13.05.202616</t>
-  </si>
-  <si>
-    <t>13.05.202617</t>
-  </si>
-  <si>
-    <t>13.05.202618</t>
-  </si>
-  <si>
-    <t>13.05.202619</t>
-  </si>
-  <si>
-    <t>13.05.202620</t>
-  </si>
-  <si>
-    <t>13.05.202621</t>
-  </si>
-  <si>
-    <t>13.05.202622</t>
-  </si>
-  <si>
-    <t>13.05.202623</t>
-  </si>
-  <si>
-    <t>13.05.202624</t>
-  </si>
-  <si>
-    <t>13.05.202625</t>
-  </si>
-  <si>
-    <t>13.05.202626</t>
-  </si>
-  <si>
-    <t>13.05.202627</t>
-  </si>
-  <si>
-    <t>13.05.202628</t>
-  </si>
-  <si>
-    <t>13.05.202629</t>
-  </si>
-  <si>
-    <t>13.05.202630</t>
-  </si>
-  <si>
-    <t>13.05.202631</t>
-  </si>
-  <si>
-    <t>13.05.202632</t>
-  </si>
-  <si>
-    <t>13.05.202633</t>
-  </si>
-  <si>
-    <t>13.05.202634</t>
-  </si>
-  <si>
-    <t>13.05.202635</t>
-  </si>
-  <si>
-    <t>13.05.202636</t>
-  </si>
-  <si>
-    <t>13.05.202637</t>
-  </si>
-  <si>
-    <t>13.05.202638</t>
-  </si>
-  <si>
-    <t>13.05.202639</t>
-  </si>
-  <si>
-    <t>13.05.202640</t>
-  </si>
-  <si>
-    <t>13.05.202641</t>
-  </si>
-  <si>
-    <t>13.05.202642</t>
-  </si>
-  <si>
-    <t>13.05.202643</t>
-  </si>
-  <si>
-    <t>13.05.202644</t>
-  </si>
-  <si>
-    <t>13.05.202645</t>
-  </si>
-  <si>
-    <t>13.05.202646</t>
-  </si>
-  <si>
-    <t>13.05.202647</t>
-  </si>
-  <si>
-    <t>13.05.202648</t>
-  </si>
-  <si>
-    <t>13.05.202649</t>
-  </si>
-  <si>
-    <t>13.05.202650</t>
-  </si>
-  <si>
-    <t>13.05.202651</t>
-  </si>
-  <si>
-    <t>13.05.202652</t>
-  </si>
-  <si>
-    <t>13.05.202653</t>
-  </si>
-  <si>
-    <t>13.05.202654</t>
-  </si>
-  <si>
-    <t>13.05.202655</t>
-  </si>
-  <si>
-    <t>13.05.202656</t>
-  </si>
-  <si>
-    <t>13.05.202657</t>
-  </si>
-  <si>
-    <t>13.05.202658</t>
-  </si>
-  <si>
-    <t>13.05.202659</t>
-  </si>
-  <si>
-    <t>13.05.202660</t>
-  </si>
-  <si>
-    <t>13.05.202661</t>
-  </si>
-  <si>
-    <t>13.05.202662</t>
-  </si>
-  <si>
-    <t>13.05.202663</t>
-  </si>
-  <si>
-    <t>13.05.202664</t>
-  </si>
-  <si>
-    <t>13.05.202665</t>
-  </si>
-  <si>
-    <t>13.05.202666</t>
-  </si>
-  <si>
-    <t>13.05.202667</t>
-  </si>
-  <si>
-    <t>13.05.202668</t>
-  </si>
-  <si>
-    <t>13.05.202669</t>
-  </si>
-  <si>
-    <t>13.05.202670</t>
-  </si>
-  <si>
-    <t>13.05.202671</t>
-  </si>
-  <si>
-    <t>13.05.202672</t>
-  </si>
-  <si>
-    <t>13.05.202673</t>
-  </si>
-  <si>
-    <t>13.05.202674</t>
-  </si>
-  <si>
-    <t>13.05.202675</t>
-  </si>
-  <si>
-    <t>13.05.202676</t>
-  </si>
-  <si>
-    <t>13.05.202677</t>
-  </si>
-  <si>
-    <t>13.05.202678</t>
-  </si>
-  <si>
-    <t>13.05.202679</t>
-  </si>
-  <si>
-    <t>13.05.202680</t>
-  </si>
-  <si>
-    <t>13.05.202681</t>
-  </si>
-  <si>
-    <t>13.05.202682</t>
-  </si>
-  <si>
-    <t>13.05.202683</t>
-  </si>
-  <si>
-    <t>13.05.202684</t>
-  </si>
-  <si>
-    <t>13.05.202685</t>
-  </si>
-  <si>
-    <t>13.05.202686</t>
-  </si>
-  <si>
-    <t>13.05.202687</t>
-  </si>
-  <si>
-    <t>13.05.202688</t>
-  </si>
-  <si>
-    <t>13.05.202689</t>
-  </si>
-  <si>
-    <t>13.05.202690</t>
-  </si>
-  <si>
-    <t>13.05.202691</t>
-  </si>
-  <si>
-    <t>13.05.202692</t>
-  </si>
-  <si>
-    <t>13.05.202693</t>
-  </si>
-  <si>
-    <t>13.05.202694</t>
-  </si>
-  <si>
-    <t>13.05.202695</t>
-  </si>
-  <si>
-    <t>13.05.202696</t>
-  </si>
-  <si>
     <t>14.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>14.05.202696</t>
+  </si>
+  <si>
+    <t>15.05.20261</t>
+  </si>
+  <si>
+    <t>15.05.20262</t>
+  </si>
+  <si>
+    <t>15.05.20263</t>
+  </si>
+  <si>
+    <t>15.05.20264</t>
+  </si>
+  <si>
+    <t>15.05.20265</t>
+  </si>
+  <si>
+    <t>15.05.20266</t>
+  </si>
+  <si>
+    <t>15.05.20267</t>
+  </si>
+  <si>
+    <t>15.05.20268</t>
+  </si>
+  <si>
+    <t>15.05.20269</t>
+  </si>
+  <si>
+    <t>15.05.202610</t>
+  </si>
+  <si>
+    <t>15.05.202611</t>
+  </si>
+  <si>
+    <t>15.05.202612</t>
+  </si>
+  <si>
+    <t>15.05.202613</t>
+  </si>
+  <si>
+    <t>15.05.202614</t>
+  </si>
+  <si>
+    <t>15.05.202615</t>
+  </si>
+  <si>
+    <t>15.05.202616</t>
+  </si>
+  <si>
+    <t>15.05.202617</t>
+  </si>
+  <si>
+    <t>15.05.202618</t>
+  </si>
+  <si>
+    <t>15.05.202619</t>
+  </si>
+  <si>
+    <t>15.05.202620</t>
+  </si>
+  <si>
+    <t>15.05.202621</t>
+  </si>
+  <si>
+    <t>15.05.202622</t>
+  </si>
+  <si>
+    <t>15.05.202623</t>
+  </si>
+  <si>
+    <t>15.05.202624</t>
+  </si>
+  <si>
+    <t>15.05.202625</t>
+  </si>
+  <si>
+    <t>15.05.202626</t>
+  </si>
+  <si>
+    <t>15.05.202627</t>
+  </si>
+  <si>
+    <t>15.05.202628</t>
+  </si>
+  <si>
+    <t>15.05.202629</t>
+  </si>
+  <si>
+    <t>15.05.202630</t>
+  </si>
+  <si>
+    <t>15.05.202631</t>
+  </si>
+  <si>
+    <t>15.05.202632</t>
+  </si>
+  <si>
+    <t>15.05.202633</t>
+  </si>
+  <si>
+    <t>15.05.202634</t>
+  </si>
+  <si>
+    <t>15.05.202635</t>
+  </si>
+  <si>
+    <t>15.05.202636</t>
+  </si>
+  <si>
+    <t>15.05.202637</t>
+  </si>
+  <si>
+    <t>15.05.202638</t>
+  </si>
+  <si>
+    <t>15.05.202639</t>
+  </si>
+  <si>
+    <t>15.05.202640</t>
+  </si>
+  <si>
+    <t>15.05.202641</t>
+  </si>
+  <si>
+    <t>15.05.202642</t>
+  </si>
+  <si>
+    <t>15.05.202643</t>
+  </si>
+  <si>
+    <t>15.05.202644</t>
+  </si>
+  <si>
+    <t>15.05.202645</t>
+  </si>
+  <si>
+    <t>15.05.202646</t>
+  </si>
+  <si>
+    <t>15.05.202647</t>
+  </si>
+  <si>
+    <t>15.05.202648</t>
+  </si>
+  <si>
+    <t>15.05.202649</t>
+  </si>
+  <si>
+    <t>15.05.202650</t>
+  </si>
+  <si>
+    <t>15.05.202651</t>
+  </si>
+  <si>
+    <t>15.05.202652</t>
+  </si>
+  <si>
+    <t>15.05.202653</t>
+  </si>
+  <si>
+    <t>15.05.202654</t>
+  </si>
+  <si>
+    <t>15.05.202655</t>
+  </si>
+  <si>
+    <t>15.05.202656</t>
+  </si>
+  <si>
+    <t>15.05.202657</t>
+  </si>
+  <si>
+    <t>15.05.202658</t>
+  </si>
+  <si>
+    <t>15.05.202659</t>
+  </si>
+  <si>
+    <t>15.05.202660</t>
+  </si>
+  <si>
+    <t>15.05.202661</t>
+  </si>
+  <si>
+    <t>15.05.202662</t>
+  </si>
+  <si>
+    <t>15.05.202663</t>
+  </si>
+  <si>
+    <t>15.05.202664</t>
+  </si>
+  <si>
+    <t>15.05.202665</t>
+  </si>
+  <si>
+    <t>15.05.202666</t>
+  </si>
+  <si>
+    <t>15.05.202667</t>
+  </si>
+  <si>
+    <t>15.05.202668</t>
+  </si>
+  <si>
+    <t>15.05.202669</t>
+  </si>
+  <si>
+    <t>15.05.202670</t>
+  </si>
+  <si>
+    <t>15.05.202671</t>
+  </si>
+  <si>
+    <t>15.05.202672</t>
+  </si>
+  <si>
+    <t>15.05.202673</t>
+  </si>
+  <si>
+    <t>15.05.202674</t>
+  </si>
+  <si>
+    <t>15.05.202675</t>
+  </si>
+  <si>
+    <t>15.05.202676</t>
+  </si>
+  <si>
+    <t>15.05.202677</t>
+  </si>
+  <si>
+    <t>15.05.202678</t>
+  </si>
+  <si>
+    <t>15.05.202679</t>
+  </si>
+  <si>
+    <t>15.05.202680</t>
+  </si>
+  <si>
+    <t>15.05.202681</t>
+  </si>
+  <si>
+    <t>15.05.202682</t>
+  </si>
+  <si>
+    <t>15.05.202683</t>
+  </si>
+  <si>
+    <t>15.05.202684</t>
+  </si>
+  <si>
+    <t>15.05.202685</t>
+  </si>
+  <si>
+    <t>15.05.202686</t>
+  </si>
+  <si>
+    <t>15.05.202687</t>
+  </si>
+  <si>
+    <t>15.05.202688</t>
+  </si>
+  <si>
+    <t>15.05.202689</t>
+  </si>
+  <si>
+    <t>15.05.202690</t>
+  </si>
+  <si>
+    <t>15.05.202691</t>
+  </si>
+  <si>
+    <t>15.05.202692</t>
+  </si>
+  <si>
+    <t>15.05.202693</t>
+  </si>
+  <si>
+    <t>15.05.202694</t>
+  </si>
+  <si>
+    <t>15.05.202695</t>
+  </si>
+  <si>
+    <t>15.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B2">
         <v>0.73</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B14">
-        <v>0.731</v>
+        <v>0.736</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>0.738</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.858</v>
+        <v>1.256</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B20">
-        <v>0.866</v>
+        <v>1.299</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.197</v>
+        <v>1.478</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B22">
-        <v>8.992000000000001</v>
+        <v>31.249</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B23">
-        <v>23.671</v>
+        <v>63.136</v>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B24">
-        <v>51.042</v>
+        <v>112.48</v>
       </c>
       <c r="C24">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B25">
-        <v>87.053</v>
+        <v>175.338</v>
       </c>
       <c r="C25">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B26">
-        <v>175.454</v>
+        <v>311.355</v>
       </c>
       <c r="C26">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B27">
-        <v>246.227</v>
+        <v>417.942</v>
       </c>
       <c r="C27">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B28">
-        <v>332.908</v>
+        <v>540.324</v>
       </c>
       <c r="C28">
-        <v>297</v>
+        <v>374</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B29">
-        <v>430.616</v>
+        <v>679.886</v>
       </c>
       <c r="C29">
-        <v>364</v>
+        <v>484</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B30">
-        <v>607.95</v>
+        <v>994.159</v>
       </c>
       <c r="C30">
-        <v>448</v>
+        <v>601</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B31">
-        <v>728.011</v>
+        <v>1176.464</v>
       </c>
       <c r="C31">
-        <v>522</v>
+        <v>746</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B32">
-        <v>842.097</v>
+        <v>1354.459</v>
       </c>
       <c r="C32">
-        <v>649</v>
+        <v>897</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B33">
-        <v>970.712</v>
+        <v>1541.154</v>
       </c>
       <c r="C33">
-        <v>781</v>
+        <v>1063</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B34">
-        <v>1190.038</v>
+        <v>1779.083</v>
       </c>
       <c r="C34">
-        <v>859</v>
+        <v>1256</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B35">
-        <v>1283.802</v>
+        <v>1950.896</v>
       </c>
       <c r="C35">
-        <v>926</v>
+        <v>1430</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B36">
-        <v>1364.253</v>
+        <v>2119.794</v>
       </c>
       <c r="C36">
-        <v>1002</v>
+        <v>1520</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B37">
-        <v>1467.24</v>
+        <v>2287.632</v>
       </c>
       <c r="C37">
-        <v>1048</v>
+        <v>1607</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B38">
-        <v>1590.903</v>
+        <v>2447.624</v>
       </c>
       <c r="C38">
-        <v>1074</v>
+        <v>1706</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B39">
-        <v>1671.316</v>
+        <v>2560.062</v>
       </c>
       <c r="C39">
-        <v>1153</v>
+        <v>1782</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B40">
-        <v>1756.409</v>
+        <v>2659.149</v>
       </c>
       <c r="C40">
-        <v>1145</v>
+        <v>1848</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B41">
-        <v>1822.275</v>
+        <v>2744.978</v>
       </c>
       <c r="C41">
-        <v>1176</v>
+        <v>1937</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B42">
-        <v>1880.194</v>
+        <v>2793.637</v>
       </c>
       <c r="C42">
-        <v>1254</v>
+        <v>1946</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B43">
-        <v>1920.662</v>
+        <v>2830.731</v>
       </c>
       <c r="C43">
-        <v>1285</v>
+        <v>2021</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B44">
-        <v>1953.418</v>
+        <v>2855.859</v>
       </c>
       <c r="C44">
-        <v>1334</v>
+        <v>1997</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B45">
-        <v>1971.188</v>
+        <v>2883.404</v>
       </c>
       <c r="C45">
-        <v>1359</v>
+        <v>2066</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B46">
-        <v>2006.828</v>
+        <v>2912.033</v>
       </c>
       <c r="C46">
-        <v>1398</v>
+        <v>1992</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B47">
-        <v>2012.832</v>
+        <v>2907.561</v>
       </c>
       <c r="C47">
-        <v>1452</v>
+        <v>1996</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B48">
-        <v>2006.327</v>
+        <v>2890.374</v>
       </c>
       <c r="C48">
-        <v>1446</v>
+        <v>2031</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B49">
-        <v>1999.472</v>
+        <v>2876.851</v>
       </c>
       <c r="C49">
-        <v>1391</v>
+        <v>1938</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B50">
-        <v>1993.451</v>
+        <v>2864.175</v>
       </c>
       <c r="C50">
-        <v>1369</v>
+        <v>2005</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B51">
-        <v>1984.661</v>
+        <v>2836.133</v>
       </c>
       <c r="C51">
-        <v>1390</v>
+        <v>2087</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B52">
-        <v>1968.759</v>
+        <v>2807.157</v>
       </c>
       <c r="C52">
-        <v>1393</v>
+        <v>1996</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B53">
-        <v>1946.723</v>
+        <v>2791.156</v>
       </c>
       <c r="C53">
-        <v>1355</v>
+        <v>1914</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B54">
-        <v>1927.459</v>
+        <v>2748.554</v>
       </c>
       <c r="C54">
-        <v>1380</v>
+        <v>1960</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46155.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B55">
-        <v>1901.482</v>
+        <v>2725.286</v>
       </c>
       <c r="C55">
-        <v>1440</v>
+        <v>1942</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46155.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B56">
-        <v>1875.397</v>
+        <v>2682.541</v>
       </c>
       <c r="C56">
-        <v>1392</v>
+        <v>1802</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46155.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B57">
-        <v>1853.791</v>
+        <v>2662.042</v>
       </c>
       <c r="C57">
-        <v>1375</v>
+        <v>1850</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46155.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B58">
-        <v>1775.26</v>
+        <v>2597.353</v>
       </c>
       <c r="C58">
-        <v>1353</v>
+        <v>1842</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46155.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B59">
-        <v>1731.699</v>
+        <v>2552.622</v>
       </c>
       <c r="C59">
-        <v>1347</v>
+        <v>1758</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46155.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B60">
-        <v>1690.071</v>
+        <v>2505.776</v>
       </c>
       <c r="C60">
-        <v>1257</v>
+        <v>1714</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46155.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B61">
-        <v>1641.266</v>
+        <v>2457.893</v>
       </c>
       <c r="C61">
-        <v>1360</v>
+        <v>1834</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46155.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B62">
-        <v>1515.51</v>
+        <v>2352.909</v>
       </c>
       <c r="C62">
-        <v>1245</v>
+        <v>1715</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46155.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B63">
-        <v>1417.401</v>
+        <v>2270.755</v>
       </c>
       <c r="C63">
-        <v>1187</v>
+        <v>1671</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46155.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B64">
-        <v>1347.891</v>
+        <v>2177.285</v>
       </c>
       <c r="C64">
-        <v>1151</v>
+        <v>1565</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46155.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B65">
-        <v>1272.081</v>
+        <v>2095.707</v>
       </c>
       <c r="C65">
-        <v>1028</v>
+        <v>1591</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46155.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B66">
-        <v>1130.07</v>
+        <v>1937.55</v>
       </c>
       <c r="C66">
-        <v>934</v>
+        <v>1538</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46155.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B67">
-        <v>1025.422</v>
+        <v>1789.268</v>
       </c>
       <c r="C67">
-        <v>933</v>
+        <v>1535</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46155.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B68">
-        <v>937.413</v>
+        <v>1647.55</v>
       </c>
       <c r="C68">
-        <v>854</v>
+        <v>1489</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46155.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B69">
-        <v>849.402</v>
+        <v>1494.335</v>
       </c>
       <c r="C69">
-        <v>752</v>
+        <v>1339</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46155.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B70">
-        <v>691.467</v>
+        <v>1259.164</v>
       </c>
       <c r="C70">
-        <v>650</v>
+        <v>1142</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46155.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B71">
-        <v>601.09</v>
+        <v>1104.201</v>
       </c>
       <c r="C71">
-        <v>562</v>
+        <v>980</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46155.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B72">
-        <v>512.218</v>
+        <v>954.193</v>
       </c>
       <c r="C72">
-        <v>480</v>
+        <v>828</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46155.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B73">
-        <v>425.365</v>
+        <v>800.663</v>
       </c>
       <c r="C73">
-        <v>394</v>
+        <v>685</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46155.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B74">
-        <v>291.106</v>
+        <v>580.751</v>
       </c>
       <c r="C74">
-        <v>308</v>
+        <v>541</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46155.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B75">
-        <v>225.692</v>
+        <v>449.897</v>
       </c>
       <c r="C75">
-        <v>234</v>
+        <v>378</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46155.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B76">
-        <v>166.081</v>
+        <v>341.923</v>
       </c>
       <c r="C76">
-        <v>160</v>
+        <v>251</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46155.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B77">
-        <v>117.307</v>
+        <v>253.339</v>
       </c>
       <c r="C77">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46155.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B78">
-        <v>67.206</v>
+        <v>114.921</v>
       </c>
       <c r="C78">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46155.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B79">
-        <v>43.034</v>
+        <v>78.324</v>
       </c>
       <c r="C79">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46155.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B80">
-        <v>30.422</v>
+        <v>48.262</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46155.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B81">
-        <v>22.478</v>
+        <v>34.226</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46155.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B82">
-        <v>22.49</v>
+        <v>22.968</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46155.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B83">
-        <v>20.587</v>
+        <v>20.243</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46155.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B84">
-        <v>20.212</v>
+        <v>20.244</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46155.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B85">
-        <v>21.204</v>
+        <v>19.694</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46155.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B86">
-        <v>20.13</v>
+        <v>14.13</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46155.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B87">
-        <v>13.23</v>
+        <v>13.73</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46155.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B88">
-        <v>5.83</v>
+        <v>5.33</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46155.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B89">
-        <v>0.73</v>
+        <v>4.93</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46155.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B90">
-        <v>5.43</v>
+        <v>2.03</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46155.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B91">
         <v>0.73</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46155.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46155.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46155.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46155.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46155.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46155.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46156.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46156.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46156.03125</v>
+        <v>46157.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46156.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46156.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46156.0625</v>
+        <v>46157.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46156.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46156.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46156.09375</v>
+        <v>46157.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46156.10416666666</v>
+        <v>46157.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46156.11458333334</v>
+        <v>46157.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46156.125</v>
+        <v>46157.125</v>
       </c>
       <c r="B110">
-        <v>0.736</v>
+        <v>0</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46156.13541666666</v>
+        <v>46157.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46156.14583333334</v>
+        <v>46157.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46156.15625</v>
+        <v>46157.15625</v>
       </c>
       <c r="B113">
-        <v>0.738</v>
+        <v>0.734</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46156.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.256</v>
+        <v>0.878</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46156.17708333334</v>
+        <v>46157.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.26</v>
+        <v>0.927</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46156.1875</v>
+        <v>46157.1875</v>
       </c>
       <c r="B116">
-        <v>1.299</v>
+        <v>0.976</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46156.19791666666</v>
+        <v>46157.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.478</v>
+        <v>5.052</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46156.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B118">
-        <v>31.249</v>
+        <v>36.279</v>
       </c>
       <c r="C118">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46156.21875</v>
+        <v>46157.21875</v>
       </c>
       <c r="B119">
-        <v>63.136</v>
+        <v>82.262</v>
       </c>
       <c r="C119">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46156.22916666666</v>
+        <v>46157.22916666666</v>
       </c>
       <c r="B120">
-        <v>112.48</v>
+        <v>138.808</v>
       </c>
       <c r="C120">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46156.23958333334</v>
+        <v>46157.23958333334</v>
       </c>
       <c r="B121">
-        <v>175.338</v>
+        <v>212.603</v>
       </c>
       <c r="C121">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46156.25</v>
+        <v>46157.25</v>
       </c>
       <c r="B122">
-        <v>311.355</v>
+        <v>379.599</v>
       </c>
       <c r="C122">
-        <v>200</v>
+        <v>283</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46156.26041666666</v>
+        <v>46157.26041666666</v>
       </c>
       <c r="B123">
-        <v>417.942</v>
+        <v>504.787</v>
       </c>
       <c r="C123">
-        <v>287</v>
+        <v>415</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46156.27083333334</v>
+        <v>46157.27083333334</v>
       </c>
       <c r="B124">
-        <v>540.324</v>
+        <v>644.135</v>
       </c>
       <c r="C124">
-        <v>374</v>
+        <v>575</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46156.28125</v>
+        <v>46157.28125</v>
       </c>
       <c r="B125">
-        <v>679.886</v>
+        <v>806.033</v>
       </c>
       <c r="C125">
-        <v>484</v>
+        <v>701</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46156.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B126">
-        <v>994.159</v>
+        <v>1109.797</v>
       </c>
       <c r="C126">
-        <v>601</v>
+        <v>818</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46156.30208333334</v>
+        <v>46157.30208333334</v>
       </c>
       <c r="B127">
-        <v>1176.464</v>
+        <v>1277.655</v>
       </c>
       <c r="C127">
-        <v>746</v>
+        <v>980</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46156.3125</v>
+        <v>46157.3125</v>
       </c>
       <c r="B128">
-        <v>1354.459</v>
+        <v>1468.783</v>
       </c>
       <c r="C128">
-        <v>897</v>
+        <v>1113</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46156.32291666666</v>
+        <v>46157.32291666666</v>
       </c>
       <c r="B129">
-        <v>1541.154</v>
+        <v>1653.145</v>
       </c>
       <c r="C129">
-        <v>1063</v>
+        <v>1269</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46156.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B130">
-        <v>1779.083</v>
+        <v>1956.7</v>
       </c>
       <c r="C130">
-        <v>1256</v>
+        <v>1398</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46156.34375</v>
+        <v>46157.34375</v>
       </c>
       <c r="B131">
-        <v>1950.896</v>
+        <v>2145.474</v>
       </c>
       <c r="C131">
-        <v>1430</v>
+        <v>1487</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46156.35416666666</v>
+        <v>46157.35416666666</v>
       </c>
       <c r="B132">
-        <v>2119.794</v>
+        <v>2289.582</v>
       </c>
       <c r="C132">
-        <v>1520</v>
+        <v>1599</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46156.36458333334</v>
+        <v>46157.36458333334</v>
       </c>
       <c r="B133">
-        <v>2287.632</v>
+        <v>2428.781</v>
       </c>
       <c r="C133">
-        <v>1607</v>
+        <v>1662</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46156.375</v>
+        <v>46157.375</v>
       </c>
       <c r="B134">
-        <v>2447.624</v>
+        <v>2594.897</v>
       </c>
       <c r="C134">
-        <v>1706</v>
+        <v>1675</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46156.38541666666</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="B135">
-        <v>2560.062</v>
+        <v>2708.788</v>
       </c>
       <c r="C135">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46156.39583333334</v>
+        <v>46157.39583333334</v>
       </c>
       <c r="B136">
-        <v>2659.149</v>
+        <v>2797.196</v>
       </c>
       <c r="C136">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46156.40625</v>
+        <v>46157.40625</v>
       </c>
       <c r="B137">
-        <v>2744.978</v>
+        <v>2867.144</v>
       </c>
       <c r="C137">
-        <v>1937</v>
+        <v>1880</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46156.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B138">
-        <v>2793.637</v>
+        <v>2943.748</v>
       </c>
       <c r="C138">
-        <v>1946</v>
+        <v>1951</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46156.42708333334</v>
+        <v>46157.42708333334</v>
       </c>
       <c r="B139">
-        <v>2830.731</v>
+        <v>2988.933</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>2046</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46156.4375</v>
+        <v>46157.4375</v>
       </c>
       <c r="B140">
-        <v>2855.859</v>
+        <v>3029.447</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>2098</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46156.44791666666</v>
+        <v>46157.44791666666</v>
       </c>
       <c r="B141">
-        <v>2883.404</v>
+        <v>3069.867</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46156.45833333334</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B142">
-        <v>2912.033</v>
+        <v>3090.446</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46156.46875</v>
+        <v>46157.46875</v>
       </c>
       <c r="B143">
-        <v>2907.561</v>
+        <v>3111.366</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46156.47916666666</v>
+        <v>46157.47916666666</v>
       </c>
       <c r="B144">
-        <v>2890.374</v>
+        <v>3122.059</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46156.48958333334</v>
+        <v>46157.48958333334</v>
       </c>
       <c r="B145">
-        <v>2876.851</v>
+        <v>3132.406</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46156.5</v>
+        <v>46157.5</v>
       </c>
       <c r="B146">
-        <v>2864.175</v>
+        <v>3142.348</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46156.51041666666</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B147">
-        <v>2836.133</v>
+        <v>3139.707</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46156.52083333334</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="B148">
-        <v>2807.157</v>
+        <v>3128.819</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46156.53125</v>
+        <v>46157.53125</v>
       </c>
       <c r="B149">
-        <v>2791.156</v>
+        <v>3109.836</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46156.54166666666</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B150">
-        <v>2748.554</v>
+        <v>3088.24</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46156.55208333334</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="B151">
-        <v>2725.286</v>
+        <v>3066.478</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46156.5625</v>
+        <v>46157.5625</v>
       </c>
       <c r="B152">
-        <v>2682.541</v>
+        <v>3043.64</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46156.57291666666</v>
+        <v>46157.57291666666</v>
       </c>
       <c r="B153">
-        <v>2662.042</v>
+        <v>3004.512</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46156.58333333334</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="B154">
-        <v>2597.353</v>
+        <v>2912.009</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46156.59375</v>
+        <v>46157.59375</v>
       </c>
       <c r="B155">
-        <v>2552.622</v>
+        <v>2853.481</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46156.60416666666</v>
+        <v>46157.60416666666</v>
       </c>
       <c r="B156">
-        <v>2505.776</v>
+        <v>2787.17</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46156.61458333334</v>
+        <v>46157.61458333334</v>
       </c>
       <c r="B157">
-        <v>2457.893</v>
+        <v>2717.089</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46156.625</v>
+        <v>46157.625</v>
       </c>
       <c r="B158">
-        <v>2352.909</v>
+        <v>2551.421</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46156.63541666666</v>
+        <v>46157.63541666666</v>
       </c>
       <c r="B159">
-        <v>2270.755</v>
+        <v>2439.653</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46156.64583333334</v>
+        <v>46157.64583333334</v>
       </c>
       <c r="B160">
-        <v>2177.285</v>
+        <v>2324.575</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46156.65625</v>
+        <v>46157.65625</v>
       </c>
       <c r="B161">
-        <v>2095.707</v>
+        <v>2205.711</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46156.66666666666</v>
+        <v>46157.66666666666</v>
       </c>
       <c r="B162">
-        <v>1937.55</v>
+        <v>2004.104</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46156.67708333334</v>
+        <v>46157.67708333334</v>
       </c>
       <c r="B163">
-        <v>1789.268</v>
+        <v>1834.878</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46156.6875</v>
+        <v>46157.6875</v>
       </c>
       <c r="B164">
-        <v>1647.55</v>
+        <v>1633.28</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46156.69791666666</v>
+        <v>46157.69791666666</v>
       </c>
       <c r="B165">
-        <v>1494.335</v>
+        <v>1458.084</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46156.70833333334</v>
+        <v>46157.70833333334</v>
       </c>
       <c r="B166">
-        <v>1259.164</v>
+        <v>1197.831</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46156.71875</v>
+        <v>46157.71875</v>
       </c>
       <c r="B167">
-        <v>1104.201</v>
+        <v>1029.954</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46156.72916666666</v>
+        <v>46157.72916666666</v>
       </c>
       <c r="B168">
-        <v>954.193</v>
+        <v>877.853</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46156.73958333334</v>
+        <v>46157.73958333334</v>
       </c>
       <c r="B169">
-        <v>800.663</v>
+        <v>719.61</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46156.75</v>
+        <v>46157.75</v>
       </c>
       <c r="B170">
-        <v>580.751</v>
+        <v>509.731</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46156.76041666666</v>
+        <v>46157.76041666666</v>
       </c>
       <c r="B171">
-        <v>449.897</v>
+        <v>394.705</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46156.77083333334</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B172">
-        <v>341.923</v>
+        <v>294.964</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46156.78125</v>
+        <v>46157.78125</v>
       </c>
       <c r="B173">
-        <v>253.339</v>
+        <v>193.141</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46156.79166666666</v>
+        <v>46157.79166666666</v>
       </c>
       <c r="B174">
-        <v>114.921</v>
+        <v>108.401</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46156.80208333334</v>
+        <v>46157.80208333334</v>
       </c>
       <c r="B175">
-        <v>78.324</v>
+        <v>63.305</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46156.8125</v>
+        <v>46157.8125</v>
       </c>
       <c r="B176">
-        <v>48.262</v>
+        <v>37.809</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46156.82291666666</v>
+        <v>46157.82291666666</v>
       </c>
       <c r="B177">
-        <v>34.226</v>
+        <v>20.356</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46156.83333333334</v>
+        <v>46157.83333333334</v>
       </c>
       <c r="B178">
-        <v>22.968</v>
+        <v>13.128</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46156.84375</v>
+        <v>46157.84375</v>
       </c>
       <c r="B179">
-        <v>20.243</v>
+        <v>21.717</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46156.85416666666</v>
+        <v>46157.85416666666</v>
       </c>
       <c r="B180">
-        <v>20.244</v>
+        <v>10.706</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46156.86458333334</v>
+        <v>46157.86458333334</v>
       </c>
       <c r="B181">
-        <v>19.694</v>
+        <v>10.197</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46156.875</v>
+        <v>46157.875</v>
       </c>
       <c r="B182">
-        <v>14.13</v>
+        <v>4.63</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46156.88541666666</v>
+        <v>46157.88541666666</v>
       </c>
       <c r="B183">
-        <v>13.73</v>
+        <v>4.23</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46156.89583333334</v>
+        <v>46157.89583333334</v>
       </c>
       <c r="B184">
-        <v>5.33</v>
+        <v>1.13</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46156.90625</v>
+        <v>46157.90625</v>
       </c>
       <c r="B185">
-        <v>4.93</v>
+        <v>0.73</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46156.91666666666</v>
+        <v>46157.91666666666</v>
       </c>
       <c r="B186">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46156.92708333334</v>
+        <v>46157.92708333334</v>
       </c>
       <c r="B187">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46156.9375</v>
+        <v>46157.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46156.94791666666</v>
+        <v>46157.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46156.95833333334</v>
+        <v>46157.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46156.96875</v>
+        <v>46157.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46156.97916666666</v>
+        <v>46157.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46156.98958333334</v>
+        <v>46157.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>14.05.20261</t>
-  </si>
-  <si>
-    <t>14.05.20262</t>
-  </si>
-  <si>
-    <t>14.05.20263</t>
-  </si>
-  <si>
-    <t>14.05.20264</t>
-  </si>
-  <si>
-    <t>14.05.20265</t>
-  </si>
-  <si>
-    <t>14.05.20266</t>
-  </si>
-  <si>
-    <t>14.05.20267</t>
-  </si>
-  <si>
-    <t>14.05.20268</t>
-  </si>
-  <si>
-    <t>14.05.20269</t>
-  </si>
-  <si>
-    <t>14.05.202610</t>
-  </si>
-  <si>
-    <t>14.05.202611</t>
-  </si>
-  <si>
-    <t>14.05.202612</t>
-  </si>
-  <si>
-    <t>14.05.202613</t>
-  </si>
-  <si>
-    <t>14.05.202614</t>
-  </si>
-  <si>
-    <t>14.05.202615</t>
-  </si>
-  <si>
-    <t>14.05.202616</t>
-  </si>
-  <si>
-    <t>14.05.202617</t>
-  </si>
-  <si>
-    <t>14.05.202618</t>
-  </si>
-  <si>
-    <t>14.05.202619</t>
-  </si>
-  <si>
-    <t>14.05.202620</t>
-  </si>
-  <si>
-    <t>14.05.202621</t>
-  </si>
-  <si>
-    <t>14.05.202622</t>
-  </si>
-  <si>
-    <t>14.05.202623</t>
-  </si>
-  <si>
-    <t>14.05.202624</t>
-  </si>
-  <si>
-    <t>14.05.202625</t>
-  </si>
-  <si>
-    <t>14.05.202626</t>
-  </si>
-  <si>
-    <t>14.05.202627</t>
-  </si>
-  <si>
-    <t>14.05.202628</t>
-  </si>
-  <si>
-    <t>14.05.202629</t>
-  </si>
-  <si>
-    <t>14.05.202630</t>
-  </si>
-  <si>
-    <t>14.05.202631</t>
-  </si>
-  <si>
-    <t>14.05.202632</t>
-  </si>
-  <si>
-    <t>14.05.202633</t>
-  </si>
-  <si>
-    <t>14.05.202634</t>
-  </si>
-  <si>
-    <t>14.05.202635</t>
-  </si>
-  <si>
-    <t>14.05.202636</t>
-  </si>
-  <si>
-    <t>14.05.202637</t>
-  </si>
-  <si>
-    <t>14.05.202638</t>
-  </si>
-  <si>
-    <t>14.05.202639</t>
-  </si>
-  <si>
-    <t>14.05.202640</t>
-  </si>
-  <si>
-    <t>14.05.202641</t>
-  </si>
-  <si>
-    <t>14.05.202642</t>
-  </si>
-  <si>
-    <t>14.05.202643</t>
-  </si>
-  <si>
-    <t>14.05.202644</t>
-  </si>
-  <si>
-    <t>14.05.202645</t>
-  </si>
-  <si>
-    <t>14.05.202646</t>
-  </si>
-  <si>
-    <t>14.05.202647</t>
-  </si>
-  <si>
-    <t>14.05.202648</t>
-  </si>
-  <si>
-    <t>14.05.202649</t>
-  </si>
-  <si>
-    <t>14.05.202650</t>
-  </si>
-  <si>
-    <t>14.05.202651</t>
-  </si>
-  <si>
-    <t>14.05.202652</t>
-  </si>
-  <si>
-    <t>14.05.202653</t>
-  </si>
-  <si>
-    <t>14.05.202654</t>
-  </si>
-  <si>
-    <t>14.05.202655</t>
-  </si>
-  <si>
-    <t>14.05.202656</t>
-  </si>
-  <si>
-    <t>14.05.202657</t>
-  </si>
-  <si>
-    <t>14.05.202658</t>
-  </si>
-  <si>
-    <t>14.05.202659</t>
-  </si>
-  <si>
-    <t>14.05.202660</t>
-  </si>
-  <si>
-    <t>14.05.202661</t>
-  </si>
-  <si>
-    <t>14.05.202662</t>
-  </si>
-  <si>
-    <t>14.05.202663</t>
-  </si>
-  <si>
-    <t>14.05.202664</t>
-  </si>
-  <si>
-    <t>14.05.202665</t>
-  </si>
-  <si>
-    <t>14.05.202666</t>
-  </si>
-  <si>
-    <t>14.05.202667</t>
-  </si>
-  <si>
-    <t>14.05.202668</t>
-  </si>
-  <si>
-    <t>14.05.202669</t>
-  </si>
-  <si>
-    <t>14.05.202670</t>
-  </si>
-  <si>
-    <t>14.05.202671</t>
-  </si>
-  <si>
-    <t>14.05.202672</t>
-  </si>
-  <si>
-    <t>14.05.202673</t>
-  </si>
-  <si>
-    <t>14.05.202674</t>
-  </si>
-  <si>
-    <t>14.05.202675</t>
-  </si>
-  <si>
-    <t>14.05.202676</t>
-  </si>
-  <si>
-    <t>14.05.202677</t>
-  </si>
-  <si>
-    <t>14.05.202678</t>
-  </si>
-  <si>
-    <t>14.05.202679</t>
-  </si>
-  <si>
-    <t>14.05.202680</t>
-  </si>
-  <si>
-    <t>14.05.202681</t>
-  </si>
-  <si>
-    <t>14.05.202682</t>
-  </si>
-  <si>
-    <t>14.05.202683</t>
-  </si>
-  <si>
-    <t>14.05.202684</t>
-  </si>
-  <si>
-    <t>14.05.202685</t>
-  </si>
-  <si>
-    <t>14.05.202686</t>
-  </si>
-  <si>
-    <t>14.05.202687</t>
-  </si>
-  <si>
-    <t>14.05.202688</t>
-  </si>
-  <si>
-    <t>14.05.202689</t>
-  </si>
-  <si>
-    <t>14.05.202690</t>
-  </si>
-  <si>
-    <t>14.05.202691</t>
-  </si>
-  <si>
-    <t>14.05.202692</t>
-  </si>
-  <si>
-    <t>14.05.202693</t>
-  </si>
-  <si>
-    <t>14.05.202694</t>
-  </si>
-  <si>
-    <t>14.05.202695</t>
-  </si>
-  <si>
-    <t>14.05.202696</t>
-  </si>
-  <si>
-    <t>15.05.20261</t>
-  </si>
-  <si>
-    <t>15.05.20262</t>
-  </si>
-  <si>
-    <t>15.05.20263</t>
-  </si>
-  <si>
-    <t>15.05.20264</t>
-  </si>
-  <si>
-    <t>15.05.20265</t>
-  </si>
-  <si>
-    <t>15.05.20266</t>
-  </si>
-  <si>
-    <t>15.05.20267</t>
-  </si>
-  <si>
-    <t>15.05.20268</t>
-  </si>
-  <si>
-    <t>15.05.20269</t>
-  </si>
-  <si>
-    <t>15.05.202610</t>
-  </si>
-  <si>
-    <t>15.05.202611</t>
-  </si>
-  <si>
-    <t>15.05.202612</t>
-  </si>
-  <si>
-    <t>15.05.202613</t>
-  </si>
-  <si>
-    <t>15.05.202614</t>
-  </si>
-  <si>
-    <t>15.05.202615</t>
-  </si>
-  <si>
-    <t>15.05.202616</t>
-  </si>
-  <si>
-    <t>15.05.202617</t>
-  </si>
-  <si>
-    <t>15.05.202618</t>
-  </si>
-  <si>
-    <t>15.05.202619</t>
-  </si>
-  <si>
-    <t>15.05.202620</t>
-  </si>
-  <si>
-    <t>15.05.202621</t>
-  </si>
-  <si>
-    <t>15.05.202622</t>
-  </si>
-  <si>
-    <t>15.05.202623</t>
-  </si>
-  <si>
-    <t>15.05.202624</t>
-  </si>
-  <si>
-    <t>15.05.202625</t>
-  </si>
-  <si>
-    <t>15.05.202626</t>
-  </si>
-  <si>
-    <t>15.05.202627</t>
-  </si>
-  <si>
-    <t>15.05.202628</t>
-  </si>
-  <si>
-    <t>15.05.202629</t>
-  </si>
-  <si>
-    <t>15.05.202630</t>
-  </si>
-  <si>
-    <t>15.05.202631</t>
-  </si>
-  <si>
-    <t>15.05.202632</t>
-  </si>
-  <si>
-    <t>15.05.202633</t>
-  </si>
-  <si>
-    <t>15.05.202634</t>
-  </si>
-  <si>
-    <t>15.05.202635</t>
-  </si>
-  <si>
-    <t>15.05.202636</t>
-  </si>
-  <si>
-    <t>15.05.202637</t>
-  </si>
-  <si>
-    <t>15.05.202638</t>
-  </si>
-  <si>
-    <t>15.05.202639</t>
-  </si>
-  <si>
-    <t>15.05.202640</t>
-  </si>
-  <si>
-    <t>15.05.202641</t>
-  </si>
-  <si>
-    <t>15.05.202642</t>
-  </si>
-  <si>
-    <t>15.05.202643</t>
-  </si>
-  <si>
-    <t>15.05.202644</t>
-  </si>
-  <si>
-    <t>15.05.202645</t>
-  </si>
-  <si>
-    <t>15.05.202646</t>
-  </si>
-  <si>
-    <t>15.05.202647</t>
-  </si>
-  <si>
-    <t>15.05.202648</t>
-  </si>
-  <si>
-    <t>15.05.202649</t>
-  </si>
-  <si>
-    <t>15.05.202650</t>
-  </si>
-  <si>
-    <t>15.05.202651</t>
-  </si>
-  <si>
-    <t>15.05.202652</t>
-  </si>
-  <si>
-    <t>15.05.202653</t>
-  </si>
-  <si>
-    <t>15.05.202654</t>
-  </si>
-  <si>
-    <t>15.05.202655</t>
-  </si>
-  <si>
-    <t>15.05.202656</t>
-  </si>
-  <si>
-    <t>15.05.202657</t>
-  </si>
-  <si>
-    <t>15.05.202658</t>
-  </si>
-  <si>
-    <t>15.05.202659</t>
-  </si>
-  <si>
-    <t>15.05.202660</t>
-  </si>
-  <si>
-    <t>15.05.202661</t>
-  </si>
-  <si>
-    <t>15.05.202662</t>
-  </si>
-  <si>
-    <t>15.05.202663</t>
-  </si>
-  <si>
-    <t>15.05.202664</t>
-  </si>
-  <si>
-    <t>15.05.202665</t>
-  </si>
-  <si>
-    <t>15.05.202666</t>
-  </si>
-  <si>
-    <t>15.05.202667</t>
-  </si>
-  <si>
-    <t>15.05.202668</t>
-  </si>
-  <si>
-    <t>15.05.202669</t>
-  </si>
-  <si>
-    <t>15.05.202670</t>
-  </si>
-  <si>
-    <t>15.05.202671</t>
-  </si>
-  <si>
-    <t>15.05.202672</t>
-  </si>
-  <si>
-    <t>15.05.202673</t>
-  </si>
-  <si>
-    <t>15.05.202674</t>
-  </si>
-  <si>
-    <t>15.05.202675</t>
-  </si>
-  <si>
-    <t>15.05.202676</t>
-  </si>
-  <si>
-    <t>15.05.202677</t>
-  </si>
-  <si>
-    <t>15.05.202678</t>
-  </si>
-  <si>
-    <t>15.05.202679</t>
-  </si>
-  <si>
-    <t>15.05.202680</t>
-  </si>
-  <si>
-    <t>15.05.202681</t>
-  </si>
-  <si>
-    <t>15.05.202682</t>
-  </si>
-  <si>
-    <t>15.05.202683</t>
-  </si>
-  <si>
-    <t>15.05.202684</t>
-  </si>
-  <si>
-    <t>15.05.202685</t>
-  </si>
-  <si>
-    <t>15.05.202686</t>
-  </si>
-  <si>
-    <t>15.05.202687</t>
-  </si>
-  <si>
-    <t>15.05.202688</t>
-  </si>
-  <si>
-    <t>15.05.202689</t>
-  </si>
-  <si>
-    <t>15.05.202690</t>
-  </si>
-  <si>
-    <t>15.05.202691</t>
-  </si>
-  <si>
-    <t>15.05.202692</t>
-  </si>
-  <si>
-    <t>15.05.202693</t>
-  </si>
-  <si>
-    <t>15.05.202694</t>
-  </si>
-  <si>
-    <t>15.05.202695</t>
-  </si>
-  <si>
-    <t>15.05.202696</t>
+    <t>20.05.20261</t>
+  </si>
+  <si>
+    <t>20.05.20262</t>
+  </si>
+  <si>
+    <t>20.05.20263</t>
+  </si>
+  <si>
+    <t>20.05.20264</t>
+  </si>
+  <si>
+    <t>20.05.20265</t>
+  </si>
+  <si>
+    <t>20.05.20266</t>
+  </si>
+  <si>
+    <t>20.05.20267</t>
+  </si>
+  <si>
+    <t>20.05.20268</t>
+  </si>
+  <si>
+    <t>20.05.20269</t>
+  </si>
+  <si>
+    <t>20.05.202610</t>
+  </si>
+  <si>
+    <t>20.05.202611</t>
+  </si>
+  <si>
+    <t>20.05.202612</t>
+  </si>
+  <si>
+    <t>20.05.202613</t>
+  </si>
+  <si>
+    <t>20.05.202614</t>
+  </si>
+  <si>
+    <t>20.05.202615</t>
+  </si>
+  <si>
+    <t>20.05.202616</t>
+  </si>
+  <si>
+    <t>20.05.202617</t>
+  </si>
+  <si>
+    <t>20.05.202618</t>
+  </si>
+  <si>
+    <t>20.05.202619</t>
+  </si>
+  <si>
+    <t>20.05.202620</t>
+  </si>
+  <si>
+    <t>20.05.202621</t>
+  </si>
+  <si>
+    <t>20.05.202622</t>
+  </si>
+  <si>
+    <t>20.05.202623</t>
+  </si>
+  <si>
+    <t>20.05.202624</t>
+  </si>
+  <si>
+    <t>20.05.202625</t>
+  </si>
+  <si>
+    <t>20.05.202626</t>
+  </si>
+  <si>
+    <t>20.05.202627</t>
+  </si>
+  <si>
+    <t>20.05.202628</t>
+  </si>
+  <si>
+    <t>20.05.202629</t>
+  </si>
+  <si>
+    <t>20.05.202630</t>
+  </si>
+  <si>
+    <t>20.05.202631</t>
+  </si>
+  <si>
+    <t>20.05.202632</t>
+  </si>
+  <si>
+    <t>20.05.202633</t>
+  </si>
+  <si>
+    <t>20.05.202634</t>
+  </si>
+  <si>
+    <t>20.05.202635</t>
+  </si>
+  <si>
+    <t>20.05.202636</t>
+  </si>
+  <si>
+    <t>20.05.202637</t>
+  </si>
+  <si>
+    <t>20.05.202638</t>
+  </si>
+  <si>
+    <t>20.05.202639</t>
+  </si>
+  <si>
+    <t>20.05.202640</t>
+  </si>
+  <si>
+    <t>20.05.202641</t>
+  </si>
+  <si>
+    <t>20.05.202642</t>
+  </si>
+  <si>
+    <t>20.05.202643</t>
+  </si>
+  <si>
+    <t>20.05.202644</t>
+  </si>
+  <si>
+    <t>20.05.202645</t>
+  </si>
+  <si>
+    <t>20.05.202646</t>
+  </si>
+  <si>
+    <t>20.05.202647</t>
+  </si>
+  <si>
+    <t>20.05.202648</t>
+  </si>
+  <si>
+    <t>20.05.202649</t>
+  </si>
+  <si>
+    <t>20.05.202650</t>
+  </si>
+  <si>
+    <t>20.05.202651</t>
+  </si>
+  <si>
+    <t>20.05.202652</t>
+  </si>
+  <si>
+    <t>20.05.202653</t>
+  </si>
+  <si>
+    <t>20.05.202654</t>
+  </si>
+  <si>
+    <t>20.05.202655</t>
+  </si>
+  <si>
+    <t>20.05.202656</t>
+  </si>
+  <si>
+    <t>20.05.202657</t>
+  </si>
+  <si>
+    <t>20.05.202658</t>
+  </si>
+  <si>
+    <t>20.05.202659</t>
+  </si>
+  <si>
+    <t>20.05.202660</t>
+  </si>
+  <si>
+    <t>20.05.202661</t>
+  </si>
+  <si>
+    <t>20.05.202662</t>
+  </si>
+  <si>
+    <t>20.05.202663</t>
+  </si>
+  <si>
+    <t>20.05.202664</t>
+  </si>
+  <si>
+    <t>20.05.202665</t>
+  </si>
+  <si>
+    <t>20.05.202666</t>
+  </si>
+  <si>
+    <t>20.05.202667</t>
+  </si>
+  <si>
+    <t>20.05.202668</t>
+  </si>
+  <si>
+    <t>20.05.202669</t>
+  </si>
+  <si>
+    <t>20.05.202670</t>
+  </si>
+  <si>
+    <t>20.05.202671</t>
+  </si>
+  <si>
+    <t>20.05.202672</t>
+  </si>
+  <si>
+    <t>20.05.202673</t>
+  </si>
+  <si>
+    <t>20.05.202674</t>
+  </si>
+  <si>
+    <t>20.05.202675</t>
+  </si>
+  <si>
+    <t>20.05.202676</t>
+  </si>
+  <si>
+    <t>20.05.202677</t>
+  </si>
+  <si>
+    <t>20.05.202678</t>
+  </si>
+  <si>
+    <t>20.05.202679</t>
+  </si>
+  <si>
+    <t>20.05.202680</t>
+  </si>
+  <si>
+    <t>20.05.202681</t>
+  </si>
+  <si>
+    <t>20.05.202682</t>
+  </si>
+  <si>
+    <t>20.05.202683</t>
+  </si>
+  <si>
+    <t>20.05.202684</t>
+  </si>
+  <si>
+    <t>20.05.202685</t>
+  </si>
+  <si>
+    <t>20.05.202686</t>
+  </si>
+  <si>
+    <t>20.05.202687</t>
+  </si>
+  <si>
+    <t>20.05.202688</t>
+  </si>
+  <si>
+    <t>20.05.202689</t>
+  </si>
+  <si>
+    <t>20.05.202690</t>
+  </si>
+  <si>
+    <t>20.05.202691</t>
+  </si>
+  <si>
+    <t>20.05.202692</t>
+  </si>
+  <si>
+    <t>20.05.202693</t>
+  </si>
+  <si>
+    <t>20.05.202694</t>
+  </si>
+  <si>
+    <t>20.05.202695</t>
+  </si>
+  <si>
+    <t>20.05.202696</t>
+  </si>
+  <si>
+    <t>21.05.20261</t>
+  </si>
+  <si>
+    <t>21.05.20262</t>
+  </si>
+  <si>
+    <t>21.05.20263</t>
+  </si>
+  <si>
+    <t>21.05.20264</t>
+  </si>
+  <si>
+    <t>21.05.20265</t>
+  </si>
+  <si>
+    <t>21.05.20266</t>
+  </si>
+  <si>
+    <t>21.05.20267</t>
+  </si>
+  <si>
+    <t>21.05.20268</t>
+  </si>
+  <si>
+    <t>21.05.20269</t>
+  </si>
+  <si>
+    <t>21.05.202610</t>
+  </si>
+  <si>
+    <t>21.05.202611</t>
+  </si>
+  <si>
+    <t>21.05.202612</t>
+  </si>
+  <si>
+    <t>21.05.202613</t>
+  </si>
+  <si>
+    <t>21.05.202614</t>
+  </si>
+  <si>
+    <t>21.05.202615</t>
+  </si>
+  <si>
+    <t>21.05.202616</t>
+  </si>
+  <si>
+    <t>21.05.202617</t>
+  </si>
+  <si>
+    <t>21.05.202618</t>
+  </si>
+  <si>
+    <t>21.05.202619</t>
+  </si>
+  <si>
+    <t>21.05.202620</t>
+  </si>
+  <si>
+    <t>21.05.202621</t>
+  </si>
+  <si>
+    <t>21.05.202622</t>
+  </si>
+  <si>
+    <t>21.05.202623</t>
+  </si>
+  <si>
+    <t>21.05.202624</t>
+  </si>
+  <si>
+    <t>21.05.202625</t>
+  </si>
+  <si>
+    <t>21.05.202626</t>
+  </si>
+  <si>
+    <t>21.05.202627</t>
+  </si>
+  <si>
+    <t>21.05.202628</t>
+  </si>
+  <si>
+    <t>21.05.202629</t>
+  </si>
+  <si>
+    <t>21.05.202630</t>
+  </si>
+  <si>
+    <t>21.05.202631</t>
+  </si>
+  <si>
+    <t>21.05.202632</t>
+  </si>
+  <si>
+    <t>21.05.202633</t>
+  </si>
+  <si>
+    <t>21.05.202634</t>
+  </si>
+  <si>
+    <t>21.05.202635</t>
+  </si>
+  <si>
+    <t>21.05.202636</t>
+  </si>
+  <si>
+    <t>21.05.202637</t>
+  </si>
+  <si>
+    <t>21.05.202638</t>
+  </si>
+  <si>
+    <t>21.05.202639</t>
+  </si>
+  <si>
+    <t>21.05.202640</t>
+  </si>
+  <si>
+    <t>21.05.202641</t>
+  </si>
+  <si>
+    <t>21.05.202642</t>
+  </si>
+  <si>
+    <t>21.05.202643</t>
+  </si>
+  <si>
+    <t>21.05.202644</t>
+  </si>
+  <si>
+    <t>21.05.202645</t>
+  </si>
+  <si>
+    <t>21.05.202646</t>
+  </si>
+  <si>
+    <t>21.05.202647</t>
+  </si>
+  <si>
+    <t>21.05.202648</t>
+  </si>
+  <si>
+    <t>21.05.202649</t>
+  </si>
+  <si>
+    <t>21.05.202650</t>
+  </si>
+  <si>
+    <t>21.05.202651</t>
+  </si>
+  <si>
+    <t>21.05.202652</t>
+  </si>
+  <si>
+    <t>21.05.202653</t>
+  </si>
+  <si>
+    <t>21.05.202654</t>
+  </si>
+  <si>
+    <t>21.05.202655</t>
+  </si>
+  <si>
+    <t>21.05.202656</t>
+  </si>
+  <si>
+    <t>21.05.202657</t>
+  </si>
+  <si>
+    <t>21.05.202658</t>
+  </si>
+  <si>
+    <t>21.05.202659</t>
+  </si>
+  <si>
+    <t>21.05.202660</t>
+  </si>
+  <si>
+    <t>21.05.202661</t>
+  </si>
+  <si>
+    <t>21.05.202662</t>
+  </si>
+  <si>
+    <t>21.05.202663</t>
+  </si>
+  <si>
+    <t>21.05.202664</t>
+  </si>
+  <si>
+    <t>21.05.202665</t>
+  </si>
+  <si>
+    <t>21.05.202666</t>
+  </si>
+  <si>
+    <t>21.05.202667</t>
+  </si>
+  <si>
+    <t>21.05.202668</t>
+  </si>
+  <si>
+    <t>21.05.202669</t>
+  </si>
+  <si>
+    <t>21.05.202670</t>
+  </si>
+  <si>
+    <t>21.05.202671</t>
+  </si>
+  <si>
+    <t>21.05.202672</t>
+  </si>
+  <si>
+    <t>21.05.202673</t>
+  </si>
+  <si>
+    <t>21.05.202674</t>
+  </si>
+  <si>
+    <t>21.05.202675</t>
+  </si>
+  <si>
+    <t>21.05.202676</t>
+  </si>
+  <si>
+    <t>21.05.202677</t>
+  </si>
+  <si>
+    <t>21.05.202678</t>
+  </si>
+  <si>
+    <t>21.05.202679</t>
+  </si>
+  <si>
+    <t>21.05.202680</t>
+  </si>
+  <si>
+    <t>21.05.202681</t>
+  </si>
+  <si>
+    <t>21.05.202682</t>
+  </si>
+  <si>
+    <t>21.05.202683</t>
+  </si>
+  <si>
+    <t>21.05.202684</t>
+  </si>
+  <si>
+    <t>21.05.202685</t>
+  </si>
+  <si>
+    <t>21.05.202686</t>
+  </si>
+  <si>
+    <t>21.05.202687</t>
+  </si>
+  <si>
+    <t>21.05.202688</t>
+  </si>
+  <si>
+    <t>21.05.202689</t>
+  </si>
+  <si>
+    <t>21.05.202690</t>
+  </si>
+  <si>
+    <t>21.05.202691</t>
+  </si>
+  <si>
+    <t>21.05.202692</t>
+  </si>
+  <si>
+    <t>21.05.202693</t>
+  </si>
+  <si>
+    <t>21.05.202694</t>
+  </si>
+  <si>
+    <t>21.05.202695</t>
+  </si>
+  <si>
+    <t>21.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,10 +988,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B2">
-        <v>0.73</v>
+        <v>7.27</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46156.01041666666</v>
+        <v>46162.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46156.02083333334</v>
+        <v>46162.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46156.03125</v>
+        <v>46162.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46156.04166666666</v>
+        <v>46162.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46156.05208333334</v>
+        <v>46162.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46156.0625</v>
+        <v>46162.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46156.07291666666</v>
+        <v>46162.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46156.08333333334</v>
+        <v>46162.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46156.09375</v>
+        <v>46162.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46156.10416666666</v>
+        <v>46162.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46156.11458333334</v>
+        <v>46162.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46156.125</v>
+        <v>46162.125</v>
       </c>
       <c r="B14">
-        <v>0.736</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46156.13541666666</v>
+        <v>46162.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46156.14583333334</v>
+        <v>46162.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46156.15625</v>
+        <v>46162.15625</v>
       </c>
       <c r="B17">
-        <v>0.738</v>
+        <v>0.781</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46156.16666666666</v>
+        <v>46162.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.256</v>
+        <v>1.911</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46156.17708333334</v>
+        <v>46162.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.26</v>
+        <v>3.389</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46156.1875</v>
+        <v>46162.1875</v>
       </c>
       <c r="B20">
-        <v>1.299</v>
+        <v>4.434</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46156.19791666666</v>
+        <v>46162.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.478</v>
+        <v>8.507999999999999</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46156.20833333334</v>
+        <v>46162.20833333334</v>
       </c>
       <c r="B22">
-        <v>31.249</v>
+        <v>59.802</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46156.21875</v>
+        <v>46162.21875</v>
       </c>
       <c r="B23">
-        <v>63.136</v>
+        <v>91.84099999999999</v>
       </c>
       <c r="C23">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46156.22916666666</v>
+        <v>46162.22916666666</v>
       </c>
       <c r="B24">
-        <v>112.48</v>
+        <v>139.043</v>
       </c>
       <c r="C24">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46156.23958333334</v>
+        <v>46162.23958333334</v>
       </c>
       <c r="B25">
-        <v>175.338</v>
+        <v>191.907</v>
       </c>
       <c r="C25">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46156.25</v>
+        <v>46162.25</v>
       </c>
       <c r="B26">
-        <v>311.355</v>
+        <v>354.39</v>
       </c>
       <c r="C26">
-        <v>200</v>
+        <v>261</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46156.26041666666</v>
+        <v>46162.26041666666</v>
       </c>
       <c r="B27">
-        <v>417.942</v>
+        <v>451.383</v>
       </c>
       <c r="C27">
-        <v>287</v>
+        <v>353</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46156.27083333334</v>
+        <v>46162.27083333334</v>
       </c>
       <c r="B28">
-        <v>540.324</v>
+        <v>572.9690000000001</v>
       </c>
       <c r="C28">
-        <v>374</v>
+        <v>452</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46156.28125</v>
+        <v>46162.28125</v>
       </c>
       <c r="B29">
-        <v>679.886</v>
+        <v>704.728</v>
       </c>
       <c r="C29">
-        <v>484</v>
+        <v>530</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46156.29166666666</v>
+        <v>46162.29166666666</v>
       </c>
       <c r="B30">
-        <v>994.159</v>
+        <v>1027.97</v>
       </c>
       <c r="C30">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46156.30208333334</v>
+        <v>46162.30208333334</v>
       </c>
       <c r="B31">
-        <v>1176.464</v>
+        <v>1182.308</v>
       </c>
       <c r="C31">
-        <v>746</v>
+        <v>675</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46156.3125</v>
+        <v>46162.3125</v>
       </c>
       <c r="B32">
-        <v>1354.459</v>
+        <v>1329.282</v>
       </c>
       <c r="C32">
-        <v>897</v>
+        <v>820</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46156.32291666666</v>
+        <v>46162.32291666666</v>
       </c>
       <c r="B33">
-        <v>1541.154</v>
+        <v>1480.263</v>
       </c>
       <c r="C33">
-        <v>1063</v>
+        <v>945</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46156.33333333334</v>
+        <v>46162.33333333334</v>
       </c>
       <c r="B34">
-        <v>1779.083</v>
+        <v>1721.168</v>
       </c>
       <c r="C34">
-        <v>1256</v>
+        <v>1115</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46156.34375</v>
+        <v>46162.34375</v>
       </c>
       <c r="B35">
-        <v>1950.896</v>
+        <v>1852</v>
       </c>
       <c r="C35">
-        <v>1430</v>
+        <v>1247</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46156.35416666666</v>
+        <v>46162.35416666666</v>
       </c>
       <c r="B36">
-        <v>2119.794</v>
+        <v>1982.661</v>
       </c>
       <c r="C36">
-        <v>1520</v>
+        <v>1343</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46156.36458333334</v>
+        <v>46162.36458333334</v>
       </c>
       <c r="B37">
-        <v>2287.632</v>
+        <v>2119.394</v>
       </c>
       <c r="C37">
-        <v>1607</v>
+        <v>1391</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46156.375</v>
+        <v>46162.375</v>
       </c>
       <c r="B38">
-        <v>2447.624</v>
+        <v>2268.964</v>
       </c>
       <c r="C38">
-        <v>1706</v>
+        <v>1404</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46156.38541666666</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="B39">
-        <v>2560.062</v>
+        <v>2401.353</v>
       </c>
       <c r="C39">
-        <v>1782</v>
+        <v>1524</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46156.39583333334</v>
+        <v>46162.39583333334</v>
       </c>
       <c r="B40">
-        <v>2659.149</v>
+        <v>2511.867</v>
       </c>
       <c r="C40">
-        <v>1848</v>
+        <v>1669</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46156.40625</v>
+        <v>46162.40625</v>
       </c>
       <c r="B41">
-        <v>2744.978</v>
+        <v>2608.656</v>
       </c>
       <c r="C41">
-        <v>1937</v>
+        <v>1749</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46156.41666666666</v>
+        <v>46162.41666666666</v>
       </c>
       <c r="B42">
-        <v>2793.637</v>
+        <v>2709.041</v>
       </c>
       <c r="C42">
-        <v>1946</v>
+        <v>1877</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46156.42708333334</v>
+        <v>46162.42708333334</v>
       </c>
       <c r="B43">
-        <v>2830.731</v>
+        <v>2763.136</v>
       </c>
       <c r="C43">
-        <v>2021</v>
+        <v>1963</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46156.4375</v>
+        <v>46162.4375</v>
       </c>
       <c r="B44">
-        <v>2855.859</v>
+        <v>2816.334</v>
       </c>
       <c r="C44">
-        <v>1997</v>
+        <v>2066</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46156.44791666666</v>
+        <v>46162.44791666666</v>
       </c>
       <c r="B45">
-        <v>2883.404</v>
+        <v>2860.102</v>
       </c>
       <c r="C45">
-        <v>2066</v>
+        <v>2091</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46156.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="B46">
-        <v>2912.033</v>
+        <v>2858.094</v>
       </c>
       <c r="C46">
-        <v>1992</v>
+        <v>2056</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46156.46875</v>
+        <v>46162.46875</v>
       </c>
       <c r="B47">
-        <v>2907.561</v>
+        <v>2865.917</v>
       </c>
       <c r="C47">
-        <v>1996</v>
+        <v>2050</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46156.47916666666</v>
+        <v>46162.47916666666</v>
       </c>
       <c r="B48">
-        <v>2890.374</v>
+        <v>2876.202</v>
       </c>
       <c r="C48">
-        <v>2031</v>
+        <v>2047</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46156.48958333334</v>
+        <v>46162.48958333334</v>
       </c>
       <c r="B49">
-        <v>2876.851</v>
+        <v>2884.636</v>
       </c>
       <c r="C49">
-        <v>1938</v>
+        <v>2001</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46156.5</v>
+        <v>46162.5</v>
       </c>
       <c r="B50">
-        <v>2864.175</v>
+        <v>2870.148</v>
       </c>
       <c r="C50">
-        <v>2005</v>
+        <v>1925</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46156.51041666666</v>
+        <v>46162.51041666666</v>
       </c>
       <c r="B51">
-        <v>2836.133</v>
+        <v>2867.674</v>
       </c>
       <c r="C51">
-        <v>2087</v>
+        <v>1897</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46156.52083333334</v>
+        <v>46162.52083333334</v>
       </c>
       <c r="B52">
-        <v>2807.157</v>
+        <v>2846.202</v>
       </c>
       <c r="C52">
-        <v>1996</v>
+        <v>1967</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46156.53125</v>
+        <v>46162.53125</v>
       </c>
       <c r="B53">
-        <v>2791.156</v>
+        <v>2817.799</v>
       </c>
       <c r="C53">
-        <v>1914</v>
+        <v>1905</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46156.54166666666</v>
+        <v>46162.54166666666</v>
       </c>
       <c r="B54">
-        <v>2748.554</v>
+        <v>2725.373</v>
       </c>
       <c r="C54">
-        <v>1960</v>
+        <v>1840</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46156.55208333334</v>
+        <v>46162.55208333334</v>
       </c>
       <c r="B55">
-        <v>2725.286</v>
+        <v>2706.153</v>
       </c>
       <c r="C55">
-        <v>1942</v>
+        <v>1702</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46156.5625</v>
+        <v>46162.5625</v>
       </c>
       <c r="B56">
-        <v>2682.541</v>
+        <v>2679.604</v>
       </c>
       <c r="C56">
-        <v>1802</v>
+        <v>1673</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46156.57291666666</v>
+        <v>46162.57291666666</v>
       </c>
       <c r="B57">
-        <v>2662.042</v>
+        <v>2623.256</v>
       </c>
       <c r="C57">
-        <v>1850</v>
+        <v>1667</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46156.58333333334</v>
+        <v>46162.58333333334</v>
       </c>
       <c r="B58">
-        <v>2597.353</v>
+        <v>2539.182</v>
       </c>
       <c r="C58">
-        <v>1842</v>
+        <v>1585</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46156.59375</v>
+        <v>46162.59375</v>
       </c>
       <c r="B59">
-        <v>2552.622</v>
+        <v>2468.46</v>
       </c>
       <c r="C59">
-        <v>1758</v>
+        <v>1512</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46156.60416666666</v>
+        <v>46162.60416666666</v>
       </c>
       <c r="B60">
-        <v>2505.776</v>
+        <v>2415.682</v>
       </c>
       <c r="C60">
-        <v>1714</v>
+        <v>1539</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46156.61458333334</v>
+        <v>46162.61458333334</v>
       </c>
       <c r="B61">
-        <v>2457.893</v>
+        <v>2354.948</v>
       </c>
       <c r="C61">
-        <v>1834</v>
+        <v>1487</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46156.625</v>
+        <v>46162.625</v>
       </c>
       <c r="B62">
-        <v>2352.909</v>
+        <v>2220.895</v>
       </c>
       <c r="C62">
-        <v>1715</v>
+        <v>1408</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46156.63541666666</v>
+        <v>46162.63541666666</v>
       </c>
       <c r="B63">
-        <v>2270.755</v>
+        <v>2109.698</v>
       </c>
       <c r="C63">
-        <v>1671</v>
+        <v>1301</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46156.64583333334</v>
+        <v>46162.64583333334</v>
       </c>
       <c r="B64">
-        <v>2177.285</v>
+        <v>2025.014</v>
       </c>
       <c r="C64">
-        <v>1565</v>
+        <v>1277</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46156.65625</v>
+        <v>46162.65625</v>
       </c>
       <c r="B65">
-        <v>2095.707</v>
+        <v>1928.577</v>
       </c>
       <c r="C65">
-        <v>1591</v>
+        <v>1253</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46156.66666666666</v>
+        <v>46162.66666666666</v>
       </c>
       <c r="B66">
-        <v>1937.55</v>
+        <v>1728.986</v>
       </c>
       <c r="C66">
-        <v>1538</v>
+        <v>1070</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46156.67708333334</v>
+        <v>46162.67708333334</v>
       </c>
       <c r="B67">
-        <v>1789.268</v>
+        <v>1590.746</v>
       </c>
       <c r="C67">
-        <v>1535</v>
+        <v>984</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46156.6875</v>
+        <v>46162.6875</v>
       </c>
       <c r="B68">
-        <v>1647.55</v>
+        <v>1442.143</v>
       </c>
       <c r="C68">
-        <v>1489</v>
+        <v>1015</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46156.69791666666</v>
+        <v>46162.69791666666</v>
       </c>
       <c r="B69">
-        <v>1494.335</v>
+        <v>1318.485</v>
       </c>
       <c r="C69">
-        <v>1339</v>
+        <v>961</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46156.70833333334</v>
+        <v>46162.70833333334</v>
       </c>
       <c r="B70">
-        <v>1259.164</v>
+        <v>1089.967</v>
       </c>
       <c r="C70">
-        <v>1142</v>
+        <v>810</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46156.71875</v>
+        <v>46162.71875</v>
       </c>
       <c r="B71">
-        <v>1104.201</v>
+        <v>974.558</v>
       </c>
       <c r="C71">
-        <v>980</v>
+        <v>681</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46156.72916666666</v>
+        <v>46162.72916666666</v>
       </c>
       <c r="B72">
-        <v>954.193</v>
+        <v>844.615</v>
       </c>
       <c r="C72">
-        <v>828</v>
+        <v>549</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46156.73958333334</v>
+        <v>46162.73958333334</v>
       </c>
       <c r="B73">
-        <v>800.663</v>
+        <v>728.063</v>
       </c>
       <c r="C73">
-        <v>685</v>
+        <v>462</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46156.75</v>
+        <v>46162.75</v>
       </c>
       <c r="B74">
-        <v>580.751</v>
+        <v>509.136</v>
       </c>
       <c r="C74">
-        <v>541</v>
+        <v>359</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46156.76041666666</v>
+        <v>46162.76041666666</v>
       </c>
       <c r="B75">
-        <v>449.897</v>
+        <v>417.174</v>
       </c>
       <c r="C75">
-        <v>378</v>
+        <v>274</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46156.77083333334</v>
+        <v>46162.77083333334</v>
       </c>
       <c r="B76">
-        <v>341.923</v>
+        <v>322.472</v>
       </c>
       <c r="C76">
-        <v>251</v>
+        <v>184</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46156.78125</v>
+        <v>46162.78125</v>
       </c>
       <c r="B77">
-        <v>253.339</v>
+        <v>245.915</v>
       </c>
       <c r="C77">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46156.79166666666</v>
+        <v>46162.79166666666</v>
       </c>
       <c r="B78">
-        <v>114.921</v>
+        <v>187.342</v>
       </c>
       <c r="C78">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46156.80208333334</v>
+        <v>46162.80208333334</v>
       </c>
       <c r="B79">
-        <v>78.324</v>
+        <v>151.123</v>
       </c>
       <c r="C79">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46156.8125</v>
+        <v>46162.8125</v>
       </c>
       <c r="B80">
-        <v>48.262</v>
+        <v>85.53</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46156.82291666666</v>
+        <v>46162.82291666666</v>
       </c>
       <c r="B81">
-        <v>34.226</v>
+        <v>31.925</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46156.83333333334</v>
+        <v>46162.83333333334</v>
       </c>
       <c r="B82">
-        <v>22.968</v>
+        <v>20.295</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46156.84375</v>
+        <v>46162.84375</v>
       </c>
       <c r="B83">
-        <v>20.243</v>
+        <v>17.016</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46156.85416666666</v>
+        <v>46162.85416666666</v>
       </c>
       <c r="B84">
-        <v>20.244</v>
+        <v>19.005</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46156.86458333334</v>
+        <v>46162.86458333334</v>
       </c>
       <c r="B85">
-        <v>19.694</v>
+        <v>15.97</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46156.875</v>
+        <v>46162.875</v>
       </c>
       <c r="B86">
-        <v>14.13</v>
+        <v>7.47</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46156.88541666666</v>
+        <v>46162.88541666666</v>
       </c>
       <c r="B87">
-        <v>13.73</v>
+        <v>4.87</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46156.89583333334</v>
+        <v>46162.89583333334</v>
       </c>
       <c r="B88">
-        <v>5.33</v>
+        <v>1.77</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46156.90625</v>
+        <v>46162.90625</v>
       </c>
       <c r="B89">
-        <v>4.93</v>
+        <v>1.37</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46156.91666666666</v>
+        <v>46162.91666666666</v>
       </c>
       <c r="B90">
-        <v>2.03</v>
+        <v>0.87</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46156.92708333334</v>
+        <v>46162.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46156.9375</v>
+        <v>46162.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46156.94791666666</v>
+        <v>46162.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46156.95833333334</v>
+        <v>46162.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46156.96875</v>
+        <v>46162.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46156.97916666666</v>
+        <v>46162.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46156.98958333334</v>
+        <v>46162.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>7.77</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>7.771</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B113">
-        <v>0.734</v>
+        <v>7.775</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B114">
-        <v>0.878</v>
+        <v>8.086</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B115">
-        <v>0.927</v>
+        <v>8.092000000000001</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B116">
-        <v>0.976</v>
+        <v>8.112</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B117">
-        <v>5.052</v>
+        <v>9.452</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B118">
-        <v>36.279</v>
+        <v>43.22</v>
       </c>
       <c r="C118">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B119">
-        <v>82.262</v>
+        <v>71.55800000000001</v>
       </c>
       <c r="C119">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B120">
-        <v>138.808</v>
+        <v>107.136</v>
       </c>
       <c r="C120">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B121">
-        <v>212.603</v>
+        <v>144.371</v>
       </c>
       <c r="C121">
-        <v>179</v>
+        <v>97</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B122">
-        <v>379.599</v>
+        <v>278.998</v>
       </c>
       <c r="C122">
-        <v>283</v>
+        <v>153</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B123">
-        <v>504.787</v>
+        <v>351.776</v>
       </c>
       <c r="C123">
-        <v>415</v>
+        <v>225</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B124">
-        <v>644.135</v>
+        <v>447.834</v>
       </c>
       <c r="C124">
-        <v>575</v>
+        <v>316</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B125">
-        <v>806.033</v>
+        <v>556.0359999999999</v>
       </c>
       <c r="C125">
-        <v>701</v>
+        <v>422</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B126">
-        <v>1109.797</v>
+        <v>763.179</v>
       </c>
       <c r="C126">
-        <v>818</v>
+        <v>530</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B127">
-        <v>1277.655</v>
+        <v>871.533</v>
       </c>
       <c r="C127">
-        <v>980</v>
+        <v>608</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B128">
-        <v>1468.783</v>
+        <v>984.004</v>
       </c>
       <c r="C128">
-        <v>1113</v>
+        <v>704</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B129">
-        <v>1653.145</v>
+        <v>1076.122</v>
       </c>
       <c r="C129">
-        <v>1269</v>
+        <v>801</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B130">
-        <v>1956.7</v>
+        <v>1230.85</v>
       </c>
       <c r="C130">
-        <v>1398</v>
+        <v>876</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B131">
-        <v>2145.474</v>
+        <v>1317.145</v>
       </c>
       <c r="C131">
-        <v>1487</v>
+        <v>979</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B132">
-        <v>2289.582</v>
+        <v>1406.763</v>
       </c>
       <c r="C132">
-        <v>1599</v>
+        <v>1094</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B133">
-        <v>2428.781</v>
+        <v>1498.898</v>
       </c>
       <c r="C133">
-        <v>1662</v>
+        <v>1179</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B134">
-        <v>2594.897</v>
+        <v>1609.988</v>
       </c>
       <c r="C134">
-        <v>1675</v>
+        <v>1231</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B135">
-        <v>2708.788</v>
+        <v>1654.627</v>
       </c>
       <c r="C135">
-        <v>1783</v>
+        <v>1308</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B136">
-        <v>2797.196</v>
+        <v>1716.049</v>
       </c>
       <c r="C136">
-        <v>1846</v>
+        <v>1367</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B137">
-        <v>2867.144</v>
+        <v>1764.772</v>
       </c>
       <c r="C137">
-        <v>1880</v>
+        <v>1369</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B138">
-        <v>2943.748</v>
+        <v>1850.678</v>
       </c>
       <c r="C138">
-        <v>1951</v>
+        <v>1346</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B139">
-        <v>2988.933</v>
+        <v>1874.983</v>
       </c>
       <c r="C139">
-        <v>2046</v>
+        <v>1379</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B140">
-        <v>3029.447</v>
+        <v>1916.207</v>
       </c>
       <c r="C140">
-        <v>2098</v>
+        <v>1374</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3351,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B141">
-        <v>3069.867</v>
+        <v>1924.118</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1406</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B142">
-        <v>3090.446</v>
+        <v>1958.013</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1379</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3385,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B143">
-        <v>3111.366</v>
+        <v>1961.945</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1361</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3402,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B144">
-        <v>3122.059</v>
+        <v>1951.232</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1308</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3419,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B145">
-        <v>3132.406</v>
+        <v>1942.379</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1264</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +3436,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B146">
-        <v>3142.348</v>
+        <v>1944.136</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1289</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +3453,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B147">
-        <v>3139.707</v>
+        <v>1919.049</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1333</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +3470,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B148">
-        <v>3128.819</v>
+        <v>1901.511</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1261</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B149">
-        <v>3109.836</v>
+        <v>1874.301</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B150">
-        <v>3088.24</v>
+        <v>1851.77</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B151">
-        <v>3066.478</v>
+        <v>1817.189</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B152">
-        <v>3043.64</v>
+        <v>1790.493</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B153">
-        <v>3004.512</v>
+        <v>1759.048</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B154">
-        <v>2912.009</v>
+        <v>1672.71</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B155">
-        <v>2853.481</v>
+        <v>1630.296</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B156">
-        <v>2787.17</v>
+        <v>1579.955</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B157">
-        <v>2717.089</v>
+        <v>1535.055</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B158">
-        <v>2551.421</v>
+        <v>1423.239</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B159">
-        <v>2439.653</v>
+        <v>1362.155</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B160">
-        <v>2324.575</v>
+        <v>1305.003</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B161">
-        <v>2205.711</v>
+        <v>1242.72</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B162">
-        <v>2004.104</v>
+        <v>1120.131</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B163">
-        <v>1834.878</v>
+        <v>1050.606</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B164">
-        <v>1633.28</v>
+        <v>957.379</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B165">
-        <v>1458.084</v>
+        <v>870.646</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B166">
-        <v>1197.831</v>
+        <v>705.761</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B167">
-        <v>1029.954</v>
+        <v>611.523</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B168">
-        <v>877.853</v>
+        <v>525.674</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B169">
-        <v>719.61</v>
+        <v>447.341</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B170">
-        <v>509.731</v>
+        <v>303.669</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B171">
-        <v>394.705</v>
+        <v>241.949</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B172">
-        <v>294.964</v>
+        <v>190.307</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B173">
-        <v>193.141</v>
+        <v>149.562</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B174">
-        <v>108.401</v>
+        <v>85.68899999999999</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B175">
-        <v>63.305</v>
+        <v>59.978</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B176">
-        <v>37.809</v>
+        <v>39.784</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B177">
-        <v>20.356</v>
+        <v>31.927</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B178">
-        <v>13.128</v>
+        <v>25.069</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B179">
-        <v>21.717</v>
+        <v>21.781</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B180">
-        <v>10.706</v>
+        <v>21.162</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B181">
-        <v>10.197</v>
+        <v>20.561</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B182">
-        <v>4.63</v>
+        <v>13.67</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B183">
-        <v>4.23</v>
+        <v>13.27</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B184">
-        <v>1.13</v>
+        <v>9.57</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B185">
-        <v>0.73</v>
+        <v>5.27</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>9.77</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.05.20261</t>
-  </si>
-  <si>
-    <t>20.05.20262</t>
-  </si>
-  <si>
-    <t>20.05.20263</t>
-  </si>
-  <si>
-    <t>20.05.20264</t>
-  </si>
-  <si>
-    <t>20.05.20265</t>
-  </si>
-  <si>
-    <t>20.05.20266</t>
-  </si>
-  <si>
-    <t>20.05.20267</t>
-  </si>
-  <si>
-    <t>20.05.20268</t>
-  </si>
-  <si>
-    <t>20.05.20269</t>
-  </si>
-  <si>
-    <t>20.05.202610</t>
-  </si>
-  <si>
-    <t>20.05.202611</t>
-  </si>
-  <si>
-    <t>20.05.202612</t>
-  </si>
-  <si>
-    <t>20.05.202613</t>
-  </si>
-  <si>
-    <t>20.05.202614</t>
-  </si>
-  <si>
-    <t>20.05.202615</t>
-  </si>
-  <si>
-    <t>20.05.202616</t>
-  </si>
-  <si>
-    <t>20.05.202617</t>
-  </si>
-  <si>
-    <t>20.05.202618</t>
-  </si>
-  <si>
-    <t>20.05.202619</t>
-  </si>
-  <si>
-    <t>20.05.202620</t>
-  </si>
-  <si>
-    <t>20.05.202621</t>
-  </si>
-  <si>
-    <t>20.05.202622</t>
-  </si>
-  <si>
-    <t>20.05.202623</t>
-  </si>
-  <si>
-    <t>20.05.202624</t>
-  </si>
-  <si>
-    <t>20.05.202625</t>
-  </si>
-  <si>
-    <t>20.05.202626</t>
-  </si>
-  <si>
-    <t>20.05.202627</t>
-  </si>
-  <si>
-    <t>20.05.202628</t>
-  </si>
-  <si>
-    <t>20.05.202629</t>
-  </si>
-  <si>
-    <t>20.05.202630</t>
-  </si>
-  <si>
-    <t>20.05.202631</t>
-  </si>
-  <si>
-    <t>20.05.202632</t>
-  </si>
-  <si>
-    <t>20.05.202633</t>
-  </si>
-  <si>
-    <t>20.05.202634</t>
-  </si>
-  <si>
-    <t>20.05.202635</t>
-  </si>
-  <si>
-    <t>20.05.202636</t>
-  </si>
-  <si>
-    <t>20.05.202637</t>
-  </si>
-  <si>
-    <t>20.05.202638</t>
-  </si>
-  <si>
-    <t>20.05.202639</t>
-  </si>
-  <si>
-    <t>20.05.202640</t>
-  </si>
-  <si>
-    <t>20.05.202641</t>
-  </si>
-  <si>
-    <t>20.05.202642</t>
-  </si>
-  <si>
-    <t>20.05.202643</t>
-  </si>
-  <si>
-    <t>20.05.202644</t>
-  </si>
-  <si>
-    <t>20.05.202645</t>
-  </si>
-  <si>
-    <t>20.05.202646</t>
-  </si>
-  <si>
-    <t>20.05.202647</t>
-  </si>
-  <si>
-    <t>20.05.202648</t>
-  </si>
-  <si>
-    <t>20.05.202649</t>
-  </si>
-  <si>
-    <t>20.05.202650</t>
-  </si>
-  <si>
-    <t>20.05.202651</t>
-  </si>
-  <si>
-    <t>20.05.202652</t>
-  </si>
-  <si>
-    <t>20.05.202653</t>
-  </si>
-  <si>
-    <t>20.05.202654</t>
-  </si>
-  <si>
-    <t>20.05.202655</t>
-  </si>
-  <si>
-    <t>20.05.202656</t>
-  </si>
-  <si>
-    <t>20.05.202657</t>
-  </si>
-  <si>
-    <t>20.05.202658</t>
-  </si>
-  <si>
-    <t>20.05.202659</t>
-  </si>
-  <si>
-    <t>20.05.202660</t>
-  </si>
-  <si>
-    <t>20.05.202661</t>
-  </si>
-  <si>
-    <t>20.05.202662</t>
-  </si>
-  <si>
-    <t>20.05.202663</t>
-  </si>
-  <si>
-    <t>20.05.202664</t>
-  </si>
-  <si>
-    <t>20.05.202665</t>
-  </si>
-  <si>
-    <t>20.05.202666</t>
-  </si>
-  <si>
-    <t>20.05.202667</t>
-  </si>
-  <si>
-    <t>20.05.202668</t>
-  </si>
-  <si>
-    <t>20.05.202669</t>
-  </si>
-  <si>
-    <t>20.05.202670</t>
-  </si>
-  <si>
-    <t>20.05.202671</t>
-  </si>
-  <si>
-    <t>20.05.202672</t>
-  </si>
-  <si>
-    <t>20.05.202673</t>
-  </si>
-  <si>
-    <t>20.05.202674</t>
-  </si>
-  <si>
-    <t>20.05.202675</t>
-  </si>
-  <si>
-    <t>20.05.202676</t>
-  </si>
-  <si>
-    <t>20.05.202677</t>
-  </si>
-  <si>
-    <t>20.05.202678</t>
-  </si>
-  <si>
-    <t>20.05.202679</t>
-  </si>
-  <si>
-    <t>20.05.202680</t>
-  </si>
-  <si>
-    <t>20.05.202681</t>
-  </si>
-  <si>
-    <t>20.05.202682</t>
-  </si>
-  <si>
-    <t>20.05.202683</t>
-  </si>
-  <si>
-    <t>20.05.202684</t>
-  </si>
-  <si>
-    <t>20.05.202685</t>
-  </si>
-  <si>
-    <t>20.05.202686</t>
-  </si>
-  <si>
-    <t>20.05.202687</t>
-  </si>
-  <si>
-    <t>20.05.202688</t>
-  </si>
-  <si>
-    <t>20.05.202689</t>
-  </si>
-  <si>
-    <t>20.05.202690</t>
-  </si>
-  <si>
-    <t>20.05.202691</t>
-  </si>
-  <si>
-    <t>20.05.202692</t>
-  </si>
-  <si>
-    <t>20.05.202693</t>
-  </si>
-  <si>
-    <t>20.05.202694</t>
-  </si>
-  <si>
-    <t>20.05.202695</t>
-  </si>
-  <si>
-    <t>20.05.202696</t>
-  </si>
-  <si>
     <t>21.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>21.05.202696</t>
+  </si>
+  <si>
+    <t>22.05.20261</t>
+  </si>
+  <si>
+    <t>22.05.20262</t>
+  </si>
+  <si>
+    <t>22.05.20263</t>
+  </si>
+  <si>
+    <t>22.05.20264</t>
+  </si>
+  <si>
+    <t>22.05.20265</t>
+  </si>
+  <si>
+    <t>22.05.20266</t>
+  </si>
+  <si>
+    <t>22.05.20267</t>
+  </si>
+  <si>
+    <t>22.05.20268</t>
+  </si>
+  <si>
+    <t>22.05.20269</t>
+  </si>
+  <si>
+    <t>22.05.202610</t>
+  </si>
+  <si>
+    <t>22.05.202611</t>
+  </si>
+  <si>
+    <t>22.05.202612</t>
+  </si>
+  <si>
+    <t>22.05.202613</t>
+  </si>
+  <si>
+    <t>22.05.202614</t>
+  </si>
+  <si>
+    <t>22.05.202615</t>
+  </si>
+  <si>
+    <t>22.05.202616</t>
+  </si>
+  <si>
+    <t>22.05.202617</t>
+  </si>
+  <si>
+    <t>22.05.202618</t>
+  </si>
+  <si>
+    <t>22.05.202619</t>
+  </si>
+  <si>
+    <t>22.05.202620</t>
+  </si>
+  <si>
+    <t>22.05.202621</t>
+  </si>
+  <si>
+    <t>22.05.202622</t>
+  </si>
+  <si>
+    <t>22.05.202623</t>
+  </si>
+  <si>
+    <t>22.05.202624</t>
+  </si>
+  <si>
+    <t>22.05.202625</t>
+  </si>
+  <si>
+    <t>22.05.202626</t>
+  </si>
+  <si>
+    <t>22.05.202627</t>
+  </si>
+  <si>
+    <t>22.05.202628</t>
+  </si>
+  <si>
+    <t>22.05.202629</t>
+  </si>
+  <si>
+    <t>22.05.202630</t>
+  </si>
+  <si>
+    <t>22.05.202631</t>
+  </si>
+  <si>
+    <t>22.05.202632</t>
+  </si>
+  <si>
+    <t>22.05.202633</t>
+  </si>
+  <si>
+    <t>22.05.202634</t>
+  </si>
+  <si>
+    <t>22.05.202635</t>
+  </si>
+  <si>
+    <t>22.05.202636</t>
+  </si>
+  <si>
+    <t>22.05.202637</t>
+  </si>
+  <si>
+    <t>22.05.202638</t>
+  </si>
+  <si>
+    <t>22.05.202639</t>
+  </si>
+  <si>
+    <t>22.05.202640</t>
+  </si>
+  <si>
+    <t>22.05.202641</t>
+  </si>
+  <si>
+    <t>22.05.202642</t>
+  </si>
+  <si>
+    <t>22.05.202643</t>
+  </si>
+  <si>
+    <t>22.05.202644</t>
+  </si>
+  <si>
+    <t>22.05.202645</t>
+  </si>
+  <si>
+    <t>22.05.202646</t>
+  </si>
+  <si>
+    <t>22.05.202647</t>
+  </si>
+  <si>
+    <t>22.05.202648</t>
+  </si>
+  <si>
+    <t>22.05.202649</t>
+  </si>
+  <si>
+    <t>22.05.202650</t>
+  </si>
+  <si>
+    <t>22.05.202651</t>
+  </si>
+  <si>
+    <t>22.05.202652</t>
+  </si>
+  <si>
+    <t>22.05.202653</t>
+  </si>
+  <si>
+    <t>22.05.202654</t>
+  </si>
+  <si>
+    <t>22.05.202655</t>
+  </si>
+  <si>
+    <t>22.05.202656</t>
+  </si>
+  <si>
+    <t>22.05.202657</t>
+  </si>
+  <si>
+    <t>22.05.202658</t>
+  </si>
+  <si>
+    <t>22.05.202659</t>
+  </si>
+  <si>
+    <t>22.05.202660</t>
+  </si>
+  <si>
+    <t>22.05.202661</t>
+  </si>
+  <si>
+    <t>22.05.202662</t>
+  </si>
+  <si>
+    <t>22.05.202663</t>
+  </si>
+  <si>
+    <t>22.05.202664</t>
+  </si>
+  <si>
+    <t>22.05.202665</t>
+  </si>
+  <si>
+    <t>22.05.202666</t>
+  </si>
+  <si>
+    <t>22.05.202667</t>
+  </si>
+  <si>
+    <t>22.05.202668</t>
+  </si>
+  <si>
+    <t>22.05.202669</t>
+  </si>
+  <si>
+    <t>22.05.202670</t>
+  </si>
+  <si>
+    <t>22.05.202671</t>
+  </si>
+  <si>
+    <t>22.05.202672</t>
+  </si>
+  <si>
+    <t>22.05.202673</t>
+  </si>
+  <si>
+    <t>22.05.202674</t>
+  </si>
+  <si>
+    <t>22.05.202675</t>
+  </si>
+  <si>
+    <t>22.05.202676</t>
+  </si>
+  <si>
+    <t>22.05.202677</t>
+  </si>
+  <si>
+    <t>22.05.202678</t>
+  </si>
+  <si>
+    <t>22.05.202679</t>
+  </si>
+  <si>
+    <t>22.05.202680</t>
+  </si>
+  <si>
+    <t>22.05.202681</t>
+  </si>
+  <si>
+    <t>22.05.202682</t>
+  </si>
+  <si>
+    <t>22.05.202683</t>
+  </si>
+  <si>
+    <t>22.05.202684</t>
+  </si>
+  <si>
+    <t>22.05.202685</t>
+  </si>
+  <si>
+    <t>22.05.202686</t>
+  </si>
+  <si>
+    <t>22.05.202687</t>
+  </si>
+  <si>
+    <t>22.05.202688</t>
+  </si>
+  <si>
+    <t>22.05.202689</t>
+  </si>
+  <si>
+    <t>22.05.202690</t>
+  </si>
+  <si>
+    <t>22.05.202691</t>
+  </si>
+  <si>
+    <t>22.05.202692</t>
+  </si>
+  <si>
+    <t>22.05.202693</t>
+  </si>
+  <si>
+    <t>22.05.202694</t>
+  </si>
+  <si>
+    <t>22.05.202695</t>
+  </si>
+  <si>
+    <t>22.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,10 +988,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B2">
-        <v>7.27</v>
+        <v>7.77</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46162.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46162.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46162.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46162.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46162.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46162.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46162.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46162.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46162.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46162.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46162.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46162.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46162.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46162.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.772</v>
+        <v>7.771</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46162.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B17">
-        <v>0.781</v>
+        <v>7.775</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46162.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.911</v>
+        <v>8.086</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46162.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.389</v>
+        <v>8.092000000000001</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46162.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B20">
-        <v>4.434</v>
+        <v>8.112</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46162.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B21">
-        <v>8.507999999999999</v>
+        <v>9.452</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46162.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B22">
-        <v>59.802</v>
+        <v>43.22</v>
       </c>
       <c r="C22">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46162.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B23">
-        <v>91.84099999999999</v>
+        <v>71.55800000000001</v>
       </c>
       <c r="C23">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46162.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B24">
-        <v>139.043</v>
+        <v>107.136</v>
       </c>
       <c r="C24">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46162.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B25">
-        <v>191.907</v>
+        <v>144.371</v>
       </c>
       <c r="C25">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46162.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B26">
-        <v>354.39</v>
+        <v>278.998</v>
       </c>
       <c r="C26">
-        <v>261</v>
+        <v>153</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46162.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B27">
-        <v>451.383</v>
+        <v>351.776</v>
       </c>
       <c r="C27">
-        <v>353</v>
+        <v>225</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46162.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B28">
-        <v>572.9690000000001</v>
+        <v>447.834</v>
       </c>
       <c r="C28">
-        <v>452</v>
+        <v>316</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46162.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B29">
-        <v>704.728</v>
+        <v>556.0359999999999</v>
       </c>
       <c r="C29">
-        <v>530</v>
+        <v>422</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46162.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B30">
-        <v>1027.97</v>
+        <v>763.179</v>
       </c>
       <c r="C30">
-        <v>606</v>
+        <v>530</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46162.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B31">
-        <v>1182.308</v>
+        <v>871.533</v>
       </c>
       <c r="C31">
-        <v>675</v>
+        <v>608</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46162.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B32">
-        <v>1329.282</v>
+        <v>984.004</v>
       </c>
       <c r="C32">
-        <v>820</v>
+        <v>704</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46162.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B33">
-        <v>1480.263</v>
+        <v>1076.122</v>
       </c>
       <c r="C33">
-        <v>945</v>
+        <v>801</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46162.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B34">
-        <v>1721.168</v>
+        <v>1230.85</v>
       </c>
       <c r="C34">
-        <v>1115</v>
+        <v>876</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46162.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B35">
-        <v>1852</v>
+        <v>1317.145</v>
       </c>
       <c r="C35">
-        <v>1247</v>
+        <v>979</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46162.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B36">
-        <v>1982.661</v>
+        <v>1406.763</v>
       </c>
       <c r="C36">
-        <v>1343</v>
+        <v>1094</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46162.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B37">
-        <v>2119.394</v>
+        <v>1498.898</v>
       </c>
       <c r="C37">
-        <v>1391</v>
+        <v>1179</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46162.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B38">
-        <v>2268.964</v>
+        <v>1609.988</v>
       </c>
       <c r="C38">
-        <v>1404</v>
+        <v>1231</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46162.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B39">
-        <v>2401.353</v>
+        <v>1654.627</v>
       </c>
       <c r="C39">
-        <v>1524</v>
+        <v>1308</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46162.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B40">
-        <v>2511.867</v>
+        <v>1716.049</v>
       </c>
       <c r="C40">
-        <v>1669</v>
+        <v>1367</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46162.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B41">
-        <v>2608.656</v>
+        <v>1764.772</v>
       </c>
       <c r="C41">
-        <v>1749</v>
+        <v>1369</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46162.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B42">
-        <v>2709.041</v>
+        <v>1850.678</v>
       </c>
       <c r="C42">
-        <v>1877</v>
+        <v>1346</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46162.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B43">
-        <v>2763.136</v>
+        <v>1874.983</v>
       </c>
       <c r="C43">
-        <v>1963</v>
+        <v>1379</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46162.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B44">
-        <v>2816.334</v>
+        <v>1916.207</v>
       </c>
       <c r="C44">
-        <v>2066</v>
+        <v>1374</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46162.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B45">
-        <v>2860.102</v>
+        <v>1924.118</v>
       </c>
       <c r="C45">
-        <v>2091</v>
+        <v>1406</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46162.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B46">
-        <v>2858.094</v>
+        <v>1958.013</v>
       </c>
       <c r="C46">
-        <v>2056</v>
+        <v>1379</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46162.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B47">
-        <v>2865.917</v>
+        <v>1961.945</v>
       </c>
       <c r="C47">
-        <v>2050</v>
+        <v>1361</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46162.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B48">
-        <v>2876.202</v>
+        <v>1951.232</v>
       </c>
       <c r="C48">
-        <v>2047</v>
+        <v>1308</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46162.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B49">
-        <v>2884.636</v>
+        <v>1942.379</v>
       </c>
       <c r="C49">
-        <v>2001</v>
+        <v>1264</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46162.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B50">
-        <v>2870.148</v>
+        <v>1944.136</v>
       </c>
       <c r="C50">
-        <v>1925</v>
+        <v>1289</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46162.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B51">
-        <v>2867.674</v>
+        <v>1919.049</v>
       </c>
       <c r="C51">
-        <v>1897</v>
+        <v>1333</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46162.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B52">
-        <v>2846.202</v>
+        <v>1901.511</v>
       </c>
       <c r="C52">
-        <v>1967</v>
+        <v>1261</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46162.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B53">
-        <v>2817.799</v>
+        <v>1874.301</v>
       </c>
       <c r="C53">
-        <v>1905</v>
+        <v>1283</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46162.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B54">
-        <v>2725.373</v>
+        <v>1851.77</v>
       </c>
       <c r="C54">
-        <v>1840</v>
+        <v>1258</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46162.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B55">
-        <v>2706.153</v>
+        <v>1817.189</v>
       </c>
       <c r="C55">
-        <v>1702</v>
+        <v>1220</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46162.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B56">
-        <v>2679.604</v>
+        <v>1790.493</v>
       </c>
       <c r="C56">
-        <v>1673</v>
+        <v>1174</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46162.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B57">
-        <v>2623.256</v>
+        <v>1759.048</v>
       </c>
       <c r="C57">
-        <v>1667</v>
+        <v>1145</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46162.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B58">
-        <v>2539.182</v>
+        <v>1672.71</v>
       </c>
       <c r="C58">
-        <v>1585</v>
+        <v>1037</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46162.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B59">
-        <v>2468.46</v>
+        <v>1630.296</v>
       </c>
       <c r="C59">
-        <v>1512</v>
+        <v>954</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46162.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B60">
-        <v>2415.682</v>
+        <v>1579.955</v>
       </c>
       <c r="C60">
-        <v>1539</v>
+        <v>991</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46162.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B61">
-        <v>2354.948</v>
+        <v>1535.055</v>
       </c>
       <c r="C61">
-        <v>1487</v>
+        <v>929</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46162.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B62">
-        <v>2220.895</v>
+        <v>1423.239</v>
       </c>
       <c r="C62">
-        <v>1408</v>
+        <v>855</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46162.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B63">
-        <v>2109.698</v>
+        <v>1362.155</v>
       </c>
       <c r="C63">
-        <v>1301</v>
+        <v>829</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46162.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B64">
-        <v>2025.014</v>
+        <v>1305.003</v>
       </c>
       <c r="C64">
-        <v>1277</v>
+        <v>797</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46162.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B65">
-        <v>1928.577</v>
+        <v>1242.72</v>
       </c>
       <c r="C65">
-        <v>1253</v>
+        <v>686</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46162.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B66">
-        <v>1728.986</v>
+        <v>1120.131</v>
       </c>
       <c r="C66">
-        <v>1070</v>
+        <v>637</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46162.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B67">
-        <v>1590.746</v>
+        <v>1050.606</v>
       </c>
       <c r="C67">
-        <v>984</v>
+        <v>598</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46162.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B68">
-        <v>1442.143</v>
+        <v>957.379</v>
       </c>
       <c r="C68">
-        <v>1015</v>
+        <v>527</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46162.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B69">
-        <v>1318.485</v>
+        <v>870.646</v>
       </c>
       <c r="C69">
-        <v>961</v>
+        <v>488</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46162.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B70">
-        <v>1089.967</v>
+        <v>705.761</v>
       </c>
       <c r="C70">
-        <v>810</v>
+        <v>452</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46162.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B71">
-        <v>974.558</v>
+        <v>611.523</v>
       </c>
       <c r="C71">
-        <v>681</v>
+        <v>439</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46162.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B72">
-        <v>844.615</v>
+        <v>525.674</v>
       </c>
       <c r="C72">
-        <v>549</v>
+        <v>402</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46162.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B73">
-        <v>728.063</v>
+        <v>447.341</v>
       </c>
       <c r="C73">
-        <v>462</v>
+        <v>344</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46162.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B74">
-        <v>509.136</v>
+        <v>303.669</v>
       </c>
       <c r="C74">
-        <v>359</v>
+        <v>263</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46162.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B75">
-        <v>417.174</v>
+        <v>241.949</v>
       </c>
       <c r="C75">
-        <v>274</v>
+        <v>206</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46162.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B76">
-        <v>322.472</v>
+        <v>190.307</v>
       </c>
       <c r="C76">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46162.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B77">
-        <v>245.915</v>
+        <v>149.562</v>
       </c>
       <c r="C77">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46162.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B78">
-        <v>187.342</v>
+        <v>85.68899999999999</v>
       </c>
       <c r="C78">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46162.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B79">
-        <v>151.123</v>
+        <v>59.978</v>
       </c>
       <c r="C79">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46162.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B80">
-        <v>85.53</v>
+        <v>39.784</v>
       </c>
       <c r="C80">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46162.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B81">
-        <v>31.925</v>
+        <v>31.927</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46162.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B82">
-        <v>20.295</v>
+        <v>25.069</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46162.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B83">
-        <v>17.016</v>
+        <v>21.781</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46162.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B84">
-        <v>19.005</v>
+        <v>21.162</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46162.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B85">
-        <v>15.97</v>
+        <v>20.561</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46162.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B86">
-        <v>7.47</v>
+        <v>13.67</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46162.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B87">
-        <v>4.87</v>
+        <v>13.27</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46162.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.77</v>
+        <v>9.57</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46162.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B89">
-        <v>1.37</v>
+        <v>5.27</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46162.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.87</v>
+        <v>9.77</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46162.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46162.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46162.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46162.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46162.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46162.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46162.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98">
         <v>7.77</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,10 +2807,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>7.771</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>7.775</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>7.776</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.771</v>
+        <v>7.779</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B113">
-        <v>7.775</v>
+        <v>7.786</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B114">
-        <v>8.086</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B115">
-        <v>8.092000000000001</v>
+        <v>8.132</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B116">
-        <v>8.112</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B117">
-        <v>9.452</v>
+        <v>10.679</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B118">
-        <v>43.22</v>
+        <v>35.465</v>
       </c>
       <c r="C118">
         <v>4</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B119">
-        <v>71.55800000000001</v>
+        <v>57.121</v>
       </c>
       <c r="C119">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B120">
-        <v>107.136</v>
+        <v>88.717</v>
       </c>
       <c r="C120">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B121">
-        <v>144.371</v>
+        <v>123.81</v>
       </c>
       <c r="C121">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B122">
-        <v>278.998</v>
+        <v>216.815</v>
       </c>
       <c r="C122">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B123">
-        <v>351.776</v>
+        <v>275.914</v>
       </c>
       <c r="C123">
-        <v>225</v>
+        <v>136</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B124">
-        <v>447.834</v>
+        <v>348.046</v>
       </c>
       <c r="C124">
-        <v>316</v>
+        <v>193</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B125">
-        <v>556.0359999999999</v>
+        <v>436.161</v>
       </c>
       <c r="C125">
-        <v>422</v>
+        <v>243</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B126">
-        <v>763.179</v>
+        <v>606.5069999999999</v>
       </c>
       <c r="C126">
-        <v>530</v>
+        <v>304</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B127">
-        <v>871.533</v>
+        <v>706.063</v>
       </c>
       <c r="C127">
-        <v>608</v>
+        <v>384</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B128">
-        <v>984.004</v>
+        <v>812.92</v>
       </c>
       <c r="C128">
-        <v>704</v>
+        <v>416</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B129">
-        <v>1076.122</v>
+        <v>914.894</v>
       </c>
       <c r="C129">
-        <v>801</v>
+        <v>519</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B130">
-        <v>1230.85</v>
+        <v>1081.478</v>
       </c>
       <c r="C130">
-        <v>876</v>
+        <v>641</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B131">
-        <v>1317.145</v>
+        <v>1178.237</v>
       </c>
       <c r="C131">
-        <v>979</v>
+        <v>648</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B132">
-        <v>1406.763</v>
+        <v>1278.566</v>
       </c>
       <c r="C132">
-        <v>1094</v>
+        <v>723</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B133">
-        <v>1498.898</v>
+        <v>1367.439</v>
       </c>
       <c r="C133">
-        <v>1179</v>
+        <v>852</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B134">
-        <v>1609.988</v>
+        <v>1530.796</v>
       </c>
       <c r="C134">
-        <v>1231</v>
+        <v>910</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B135">
-        <v>1654.627</v>
+        <v>1614.437</v>
       </c>
       <c r="C135">
-        <v>1308</v>
+        <v>1087</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B136">
-        <v>1716.049</v>
+        <v>1704.998</v>
       </c>
       <c r="C136">
-        <v>1367</v>
+        <v>1186</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B137">
-        <v>1764.772</v>
+        <v>1770.689</v>
       </c>
       <c r="C137">
-        <v>1369</v>
+        <v>1153</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B138">
-        <v>1850.678</v>
+        <v>1890.295</v>
       </c>
       <c r="C138">
-        <v>1346</v>
+        <v>1145</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B139">
-        <v>1874.983</v>
+        <v>1940.486</v>
       </c>
       <c r="C139">
-        <v>1379</v>
+        <v>1194</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B140">
-        <v>1916.207</v>
+        <v>2019.32</v>
       </c>
       <c r="C140">
-        <v>1374</v>
+        <v>1155</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3351,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B141">
-        <v>1924.118</v>
+        <v>2067.392</v>
       </c>
       <c r="C141">
-        <v>1406</v>
+        <v>1251</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B142">
-        <v>1958.013</v>
+        <v>2097.747</v>
       </c>
       <c r="C142">
-        <v>1379</v>
+        <v>1333</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3385,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B143">
-        <v>1961.945</v>
+        <v>2121.557</v>
       </c>
       <c r="C143">
-        <v>1361</v>
+        <v>1323</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3402,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B144">
-        <v>1951.232</v>
+        <v>2074.246</v>
       </c>
       <c r="C144">
-        <v>1308</v>
+        <v>1371</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3419,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B145">
-        <v>1942.379</v>
+        <v>2072.066</v>
       </c>
       <c r="C145">
-        <v>1264</v>
+        <v>1341</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +3436,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B146">
-        <v>1944.136</v>
+        <v>2054.691</v>
       </c>
       <c r="C146">
-        <v>1289</v>
+        <v>1236</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +3453,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B147">
-        <v>1919.049</v>
+        <v>2024.518</v>
       </c>
       <c r="C147">
-        <v>1333</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +3470,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B148">
-        <v>1901.511</v>
+        <v>1994.334</v>
       </c>
       <c r="C148">
-        <v>1261</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B149">
-        <v>1874.301</v>
+        <v>1985.185</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B150">
-        <v>1851.77</v>
+        <v>1973.287</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B151">
-        <v>1817.189</v>
+        <v>1952.66</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B152">
-        <v>1790.493</v>
+        <v>1918.352</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B153">
-        <v>1759.048</v>
+        <v>1873.258</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B154">
-        <v>1672.71</v>
+        <v>1836.85</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B155">
-        <v>1630.296</v>
+        <v>1800.968</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B156">
-        <v>1579.955</v>
+        <v>1774.211</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B157">
-        <v>1535.055</v>
+        <v>1746.392</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B158">
-        <v>1423.239</v>
+        <v>1601.071</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B159">
-        <v>1362.155</v>
+        <v>1511.024</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B160">
-        <v>1305.003</v>
+        <v>1438.069</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B161">
-        <v>1242.72</v>
+        <v>1371.658</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B162">
-        <v>1120.131</v>
+        <v>1243.272</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B163">
-        <v>1050.606</v>
+        <v>1160.547</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B164">
-        <v>957.379</v>
+        <v>1061.553</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B165">
-        <v>870.646</v>
+        <v>981.9109999999999</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B166">
-        <v>705.761</v>
+        <v>828.511</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B167">
-        <v>611.523</v>
+        <v>725.6130000000001</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B168">
-        <v>525.674</v>
+        <v>631.403</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B169">
-        <v>447.341</v>
+        <v>541.043</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B170">
-        <v>303.669</v>
+        <v>367.48</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B171">
-        <v>241.949</v>
+        <v>300.441</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B172">
-        <v>190.307</v>
+        <v>230.249</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B173">
-        <v>149.562</v>
+        <v>177.577</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B174">
-        <v>85.68899999999999</v>
+        <v>120.753</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B175">
-        <v>59.978</v>
+        <v>109.443</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B176">
-        <v>39.784</v>
+        <v>50.106</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B177">
-        <v>31.927</v>
+        <v>35.009</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B178">
-        <v>25.069</v>
+        <v>18.639</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B179">
-        <v>21.781</v>
+        <v>18.847</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B180">
-        <v>21.162</v>
+        <v>18.481</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B181">
-        <v>20.561</v>
+        <v>17.867</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B182">
-        <v>13.67</v>
+        <v>17.27</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B183">
-        <v>13.27</v>
+        <v>7.07</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B184">
-        <v>9.57</v>
+        <v>3.97</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B185">
-        <v>5.27</v>
+        <v>1.37</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B186">
-        <v>9.77</v>
+        <v>10.27</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B187">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B189">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.05.20261</t>
-  </si>
-  <si>
-    <t>21.05.20262</t>
-  </si>
-  <si>
-    <t>21.05.20263</t>
-  </si>
-  <si>
-    <t>21.05.20264</t>
-  </si>
-  <si>
-    <t>21.05.20265</t>
-  </si>
-  <si>
-    <t>21.05.20266</t>
-  </si>
-  <si>
-    <t>21.05.20267</t>
-  </si>
-  <si>
-    <t>21.05.20268</t>
-  </si>
-  <si>
-    <t>21.05.20269</t>
-  </si>
-  <si>
-    <t>21.05.202610</t>
-  </si>
-  <si>
-    <t>21.05.202611</t>
-  </si>
-  <si>
-    <t>21.05.202612</t>
-  </si>
-  <si>
-    <t>21.05.202613</t>
-  </si>
-  <si>
-    <t>21.05.202614</t>
-  </si>
-  <si>
-    <t>21.05.202615</t>
-  </si>
-  <si>
-    <t>21.05.202616</t>
-  </si>
-  <si>
-    <t>21.05.202617</t>
-  </si>
-  <si>
-    <t>21.05.202618</t>
-  </si>
-  <si>
-    <t>21.05.202619</t>
-  </si>
-  <si>
-    <t>21.05.202620</t>
-  </si>
-  <si>
-    <t>21.05.202621</t>
-  </si>
-  <si>
-    <t>21.05.202622</t>
-  </si>
-  <si>
-    <t>21.05.202623</t>
-  </si>
-  <si>
-    <t>21.05.202624</t>
-  </si>
-  <si>
-    <t>21.05.202625</t>
-  </si>
-  <si>
-    <t>21.05.202626</t>
-  </si>
-  <si>
-    <t>21.05.202627</t>
-  </si>
-  <si>
-    <t>21.05.202628</t>
-  </si>
-  <si>
-    <t>21.05.202629</t>
-  </si>
-  <si>
-    <t>21.05.202630</t>
-  </si>
-  <si>
-    <t>21.05.202631</t>
-  </si>
-  <si>
-    <t>21.05.202632</t>
-  </si>
-  <si>
-    <t>21.05.202633</t>
-  </si>
-  <si>
-    <t>21.05.202634</t>
-  </si>
-  <si>
-    <t>21.05.202635</t>
-  </si>
-  <si>
-    <t>21.05.202636</t>
-  </si>
-  <si>
-    <t>21.05.202637</t>
-  </si>
-  <si>
-    <t>21.05.202638</t>
-  </si>
-  <si>
-    <t>21.05.202639</t>
-  </si>
-  <si>
-    <t>21.05.202640</t>
-  </si>
-  <si>
-    <t>21.05.202641</t>
-  </si>
-  <si>
-    <t>21.05.202642</t>
-  </si>
-  <si>
-    <t>21.05.202643</t>
-  </si>
-  <si>
-    <t>21.05.202644</t>
-  </si>
-  <si>
-    <t>21.05.202645</t>
-  </si>
-  <si>
-    <t>21.05.202646</t>
-  </si>
-  <si>
-    <t>21.05.202647</t>
-  </si>
-  <si>
-    <t>21.05.202648</t>
-  </si>
-  <si>
-    <t>21.05.202649</t>
-  </si>
-  <si>
-    <t>21.05.202650</t>
-  </si>
-  <si>
-    <t>21.05.202651</t>
-  </si>
-  <si>
-    <t>21.05.202652</t>
-  </si>
-  <si>
-    <t>21.05.202653</t>
-  </si>
-  <si>
-    <t>21.05.202654</t>
-  </si>
-  <si>
-    <t>21.05.202655</t>
-  </si>
-  <si>
-    <t>21.05.202656</t>
-  </si>
-  <si>
-    <t>21.05.202657</t>
-  </si>
-  <si>
-    <t>21.05.202658</t>
-  </si>
-  <si>
-    <t>21.05.202659</t>
-  </si>
-  <si>
-    <t>21.05.202660</t>
-  </si>
-  <si>
-    <t>21.05.202661</t>
-  </si>
-  <si>
-    <t>21.05.202662</t>
-  </si>
-  <si>
-    <t>21.05.202663</t>
-  </si>
-  <si>
-    <t>21.05.202664</t>
-  </si>
-  <si>
-    <t>21.05.202665</t>
-  </si>
-  <si>
-    <t>21.05.202666</t>
-  </si>
-  <si>
-    <t>21.05.202667</t>
-  </si>
-  <si>
-    <t>21.05.202668</t>
-  </si>
-  <si>
-    <t>21.05.202669</t>
-  </si>
-  <si>
-    <t>21.05.202670</t>
-  </si>
-  <si>
-    <t>21.05.202671</t>
-  </si>
-  <si>
-    <t>21.05.202672</t>
-  </si>
-  <si>
-    <t>21.05.202673</t>
-  </si>
-  <si>
-    <t>21.05.202674</t>
-  </si>
-  <si>
-    <t>21.05.202675</t>
-  </si>
-  <si>
-    <t>21.05.202676</t>
-  </si>
-  <si>
-    <t>21.05.202677</t>
-  </si>
-  <si>
-    <t>21.05.202678</t>
-  </si>
-  <si>
-    <t>21.05.202679</t>
-  </si>
-  <si>
-    <t>21.05.202680</t>
-  </si>
-  <si>
-    <t>21.05.202681</t>
-  </si>
-  <si>
-    <t>21.05.202682</t>
-  </si>
-  <si>
-    <t>21.05.202683</t>
-  </si>
-  <si>
-    <t>21.05.202684</t>
-  </si>
-  <si>
-    <t>21.05.202685</t>
-  </si>
-  <si>
-    <t>21.05.202686</t>
-  </si>
-  <si>
-    <t>21.05.202687</t>
-  </si>
-  <si>
-    <t>21.05.202688</t>
-  </si>
-  <si>
-    <t>21.05.202689</t>
-  </si>
-  <si>
-    <t>21.05.202690</t>
-  </si>
-  <si>
-    <t>21.05.202691</t>
-  </si>
-  <si>
-    <t>21.05.202692</t>
-  </si>
-  <si>
-    <t>21.05.202693</t>
-  </si>
-  <si>
-    <t>21.05.202694</t>
-  </si>
-  <si>
-    <t>21.05.202695</t>
-  </si>
-  <si>
-    <t>21.05.202696</t>
-  </si>
-  <si>
     <t>22.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,870 @@
   </si>
   <si>
     <t>22.05.202696</t>
+  </si>
+  <si>
+    <t>23.05.20261</t>
+  </si>
+  <si>
+    <t>23.05.20262</t>
+  </si>
+  <si>
+    <t>23.05.20263</t>
+  </si>
+  <si>
+    <t>23.05.20264</t>
+  </si>
+  <si>
+    <t>23.05.20265</t>
+  </si>
+  <si>
+    <t>23.05.20266</t>
+  </si>
+  <si>
+    <t>23.05.20267</t>
+  </si>
+  <si>
+    <t>23.05.20268</t>
+  </si>
+  <si>
+    <t>23.05.20269</t>
+  </si>
+  <si>
+    <t>23.05.202610</t>
+  </si>
+  <si>
+    <t>23.05.202611</t>
+  </si>
+  <si>
+    <t>23.05.202612</t>
+  </si>
+  <si>
+    <t>23.05.202613</t>
+  </si>
+  <si>
+    <t>23.05.202614</t>
+  </si>
+  <si>
+    <t>23.05.202615</t>
+  </si>
+  <si>
+    <t>23.05.202616</t>
+  </si>
+  <si>
+    <t>23.05.202617</t>
+  </si>
+  <si>
+    <t>23.05.202618</t>
+  </si>
+  <si>
+    <t>23.05.202619</t>
+  </si>
+  <si>
+    <t>23.05.202620</t>
+  </si>
+  <si>
+    <t>23.05.202621</t>
+  </si>
+  <si>
+    <t>23.05.202622</t>
+  </si>
+  <si>
+    <t>23.05.202623</t>
+  </si>
+  <si>
+    <t>23.05.202624</t>
+  </si>
+  <si>
+    <t>23.05.202625</t>
+  </si>
+  <si>
+    <t>23.05.202626</t>
+  </si>
+  <si>
+    <t>23.05.202627</t>
+  </si>
+  <si>
+    <t>23.05.202628</t>
+  </si>
+  <si>
+    <t>23.05.202629</t>
+  </si>
+  <si>
+    <t>23.05.202630</t>
+  </si>
+  <si>
+    <t>23.05.202631</t>
+  </si>
+  <si>
+    <t>23.05.202632</t>
+  </si>
+  <si>
+    <t>23.05.202633</t>
+  </si>
+  <si>
+    <t>23.05.202634</t>
+  </si>
+  <si>
+    <t>23.05.202635</t>
+  </si>
+  <si>
+    <t>23.05.202636</t>
+  </si>
+  <si>
+    <t>23.05.202637</t>
+  </si>
+  <si>
+    <t>23.05.202638</t>
+  </si>
+  <si>
+    <t>23.05.202639</t>
+  </si>
+  <si>
+    <t>23.05.202640</t>
+  </si>
+  <si>
+    <t>23.05.202641</t>
+  </si>
+  <si>
+    <t>23.05.202642</t>
+  </si>
+  <si>
+    <t>23.05.202643</t>
+  </si>
+  <si>
+    <t>23.05.202644</t>
+  </si>
+  <si>
+    <t>23.05.202645</t>
+  </si>
+  <si>
+    <t>23.05.202646</t>
+  </si>
+  <si>
+    <t>23.05.202647</t>
+  </si>
+  <si>
+    <t>23.05.202648</t>
+  </si>
+  <si>
+    <t>23.05.202649</t>
+  </si>
+  <si>
+    <t>23.05.202650</t>
+  </si>
+  <si>
+    <t>23.05.202651</t>
+  </si>
+  <si>
+    <t>23.05.202652</t>
+  </si>
+  <si>
+    <t>23.05.202653</t>
+  </si>
+  <si>
+    <t>23.05.202654</t>
+  </si>
+  <si>
+    <t>23.05.202655</t>
+  </si>
+  <si>
+    <t>23.05.202656</t>
+  </si>
+  <si>
+    <t>23.05.202657</t>
+  </si>
+  <si>
+    <t>23.05.202658</t>
+  </si>
+  <si>
+    <t>23.05.202659</t>
+  </si>
+  <si>
+    <t>23.05.202660</t>
+  </si>
+  <si>
+    <t>23.05.202661</t>
+  </si>
+  <si>
+    <t>23.05.202662</t>
+  </si>
+  <si>
+    <t>23.05.202663</t>
+  </si>
+  <si>
+    <t>23.05.202664</t>
+  </si>
+  <si>
+    <t>23.05.202665</t>
+  </si>
+  <si>
+    <t>23.05.202666</t>
+  </si>
+  <si>
+    <t>23.05.202667</t>
+  </si>
+  <si>
+    <t>23.05.202668</t>
+  </si>
+  <si>
+    <t>23.05.202669</t>
+  </si>
+  <si>
+    <t>23.05.202670</t>
+  </si>
+  <si>
+    <t>23.05.202671</t>
+  </si>
+  <si>
+    <t>23.05.202672</t>
+  </si>
+  <si>
+    <t>23.05.202673</t>
+  </si>
+  <si>
+    <t>23.05.202674</t>
+  </si>
+  <si>
+    <t>23.05.202675</t>
+  </si>
+  <si>
+    <t>23.05.202676</t>
+  </si>
+  <si>
+    <t>23.05.202677</t>
+  </si>
+  <si>
+    <t>23.05.202678</t>
+  </si>
+  <si>
+    <t>23.05.202679</t>
+  </si>
+  <si>
+    <t>23.05.202680</t>
+  </si>
+  <si>
+    <t>23.05.202681</t>
+  </si>
+  <si>
+    <t>23.05.202682</t>
+  </si>
+  <si>
+    <t>23.05.202683</t>
+  </si>
+  <si>
+    <t>23.05.202684</t>
+  </si>
+  <si>
+    <t>23.05.202685</t>
+  </si>
+  <si>
+    <t>23.05.202686</t>
+  </si>
+  <si>
+    <t>23.05.202687</t>
+  </si>
+  <si>
+    <t>23.05.202688</t>
+  </si>
+  <si>
+    <t>23.05.202689</t>
+  </si>
+  <si>
+    <t>23.05.202690</t>
+  </si>
+  <si>
+    <t>23.05.202691</t>
+  </si>
+  <si>
+    <t>23.05.202692</t>
+  </si>
+  <si>
+    <t>23.05.202693</t>
+  </si>
+  <si>
+    <t>23.05.202694</t>
+  </si>
+  <si>
+    <t>23.05.202695</t>
+  </si>
+  <si>
+    <t>23.05.202696</t>
+  </si>
+  <si>
+    <t>24.05.20261</t>
+  </si>
+  <si>
+    <t>24.05.20262</t>
+  </si>
+  <si>
+    <t>24.05.20263</t>
+  </si>
+  <si>
+    <t>24.05.20264</t>
+  </si>
+  <si>
+    <t>24.05.20265</t>
+  </si>
+  <si>
+    <t>24.05.20266</t>
+  </si>
+  <si>
+    <t>24.05.20267</t>
+  </si>
+  <si>
+    <t>24.05.20268</t>
+  </si>
+  <si>
+    <t>24.05.20269</t>
+  </si>
+  <si>
+    <t>24.05.202610</t>
+  </si>
+  <si>
+    <t>24.05.202611</t>
+  </si>
+  <si>
+    <t>24.05.202612</t>
+  </si>
+  <si>
+    <t>24.05.202613</t>
+  </si>
+  <si>
+    <t>24.05.202614</t>
+  </si>
+  <si>
+    <t>24.05.202615</t>
+  </si>
+  <si>
+    <t>24.05.202616</t>
+  </si>
+  <si>
+    <t>24.05.202617</t>
+  </si>
+  <si>
+    <t>24.05.202618</t>
+  </si>
+  <si>
+    <t>24.05.202619</t>
+  </si>
+  <si>
+    <t>24.05.202620</t>
+  </si>
+  <si>
+    <t>24.05.202621</t>
+  </si>
+  <si>
+    <t>24.05.202622</t>
+  </si>
+  <si>
+    <t>24.05.202623</t>
+  </si>
+  <si>
+    <t>24.05.202624</t>
+  </si>
+  <si>
+    <t>24.05.202625</t>
+  </si>
+  <si>
+    <t>24.05.202626</t>
+  </si>
+  <si>
+    <t>24.05.202627</t>
+  </si>
+  <si>
+    <t>24.05.202628</t>
+  </si>
+  <si>
+    <t>24.05.202629</t>
+  </si>
+  <si>
+    <t>24.05.202630</t>
+  </si>
+  <si>
+    <t>24.05.202631</t>
+  </si>
+  <si>
+    <t>24.05.202632</t>
+  </si>
+  <si>
+    <t>24.05.202633</t>
+  </si>
+  <si>
+    <t>24.05.202634</t>
+  </si>
+  <si>
+    <t>24.05.202635</t>
+  </si>
+  <si>
+    <t>24.05.202636</t>
+  </si>
+  <si>
+    <t>24.05.202637</t>
+  </si>
+  <si>
+    <t>24.05.202638</t>
+  </si>
+  <si>
+    <t>24.05.202639</t>
+  </si>
+  <si>
+    <t>24.05.202640</t>
+  </si>
+  <si>
+    <t>24.05.202641</t>
+  </si>
+  <si>
+    <t>24.05.202642</t>
+  </si>
+  <si>
+    <t>24.05.202643</t>
+  </si>
+  <si>
+    <t>24.05.202644</t>
+  </si>
+  <si>
+    <t>24.05.202645</t>
+  </si>
+  <si>
+    <t>24.05.202646</t>
+  </si>
+  <si>
+    <t>24.05.202647</t>
+  </si>
+  <si>
+    <t>24.05.202648</t>
+  </si>
+  <si>
+    <t>24.05.202649</t>
+  </si>
+  <si>
+    <t>24.05.202650</t>
+  </si>
+  <si>
+    <t>24.05.202651</t>
+  </si>
+  <si>
+    <t>24.05.202652</t>
+  </si>
+  <si>
+    <t>24.05.202653</t>
+  </si>
+  <si>
+    <t>24.05.202654</t>
+  </si>
+  <si>
+    <t>24.05.202655</t>
+  </si>
+  <si>
+    <t>24.05.202656</t>
+  </si>
+  <si>
+    <t>24.05.202657</t>
+  </si>
+  <si>
+    <t>24.05.202658</t>
+  </si>
+  <si>
+    <t>24.05.202659</t>
+  </si>
+  <si>
+    <t>24.05.202660</t>
+  </si>
+  <si>
+    <t>24.05.202661</t>
+  </si>
+  <si>
+    <t>24.05.202662</t>
+  </si>
+  <si>
+    <t>24.05.202663</t>
+  </si>
+  <si>
+    <t>24.05.202664</t>
+  </si>
+  <si>
+    <t>24.05.202665</t>
+  </si>
+  <si>
+    <t>24.05.202666</t>
+  </si>
+  <si>
+    <t>24.05.202667</t>
+  </si>
+  <si>
+    <t>24.05.202668</t>
+  </si>
+  <si>
+    <t>24.05.202669</t>
+  </si>
+  <si>
+    <t>24.05.202670</t>
+  </si>
+  <si>
+    <t>24.05.202671</t>
+  </si>
+  <si>
+    <t>24.05.202672</t>
+  </si>
+  <si>
+    <t>24.05.202673</t>
+  </si>
+  <si>
+    <t>24.05.202674</t>
+  </si>
+  <si>
+    <t>24.05.202675</t>
+  </si>
+  <si>
+    <t>24.05.202676</t>
+  </si>
+  <si>
+    <t>24.05.202677</t>
+  </si>
+  <si>
+    <t>24.05.202678</t>
+  </si>
+  <si>
+    <t>24.05.202679</t>
+  </si>
+  <si>
+    <t>24.05.202680</t>
+  </si>
+  <si>
+    <t>24.05.202681</t>
+  </si>
+  <si>
+    <t>24.05.202682</t>
+  </si>
+  <si>
+    <t>24.05.202683</t>
+  </si>
+  <si>
+    <t>24.05.202684</t>
+  </si>
+  <si>
+    <t>24.05.202685</t>
+  </si>
+  <si>
+    <t>24.05.202686</t>
+  </si>
+  <si>
+    <t>24.05.202687</t>
+  </si>
+  <si>
+    <t>24.05.202688</t>
+  </si>
+  <si>
+    <t>24.05.202689</t>
+  </si>
+  <si>
+    <t>24.05.202690</t>
+  </si>
+  <si>
+    <t>24.05.202691</t>
+  </si>
+  <si>
+    <t>24.05.202692</t>
+  </si>
+  <si>
+    <t>24.05.202693</t>
+  </si>
+  <si>
+    <t>24.05.202694</t>
+  </si>
+  <si>
+    <t>24.05.202695</t>
+  </si>
+  <si>
+    <t>24.05.202696</t>
+  </si>
+  <si>
+    <t>25.05.20261</t>
+  </si>
+  <si>
+    <t>25.05.20262</t>
+  </si>
+  <si>
+    <t>25.05.20263</t>
+  </si>
+  <si>
+    <t>25.05.20264</t>
+  </si>
+  <si>
+    <t>25.05.20265</t>
+  </si>
+  <si>
+    <t>25.05.20266</t>
+  </si>
+  <si>
+    <t>25.05.20267</t>
+  </si>
+  <si>
+    <t>25.05.20268</t>
+  </si>
+  <si>
+    <t>25.05.20269</t>
+  </si>
+  <si>
+    <t>25.05.202610</t>
+  </si>
+  <si>
+    <t>25.05.202611</t>
+  </si>
+  <si>
+    <t>25.05.202612</t>
+  </si>
+  <si>
+    <t>25.05.202613</t>
+  </si>
+  <si>
+    <t>25.05.202614</t>
+  </si>
+  <si>
+    <t>25.05.202615</t>
+  </si>
+  <si>
+    <t>25.05.202616</t>
+  </si>
+  <si>
+    <t>25.05.202617</t>
+  </si>
+  <si>
+    <t>25.05.202618</t>
+  </si>
+  <si>
+    <t>25.05.202619</t>
+  </si>
+  <si>
+    <t>25.05.202620</t>
+  </si>
+  <si>
+    <t>25.05.202621</t>
+  </si>
+  <si>
+    <t>25.05.202622</t>
+  </si>
+  <si>
+    <t>25.05.202623</t>
+  </si>
+  <si>
+    <t>25.05.202624</t>
+  </si>
+  <si>
+    <t>25.05.202625</t>
+  </si>
+  <si>
+    <t>25.05.202626</t>
+  </si>
+  <si>
+    <t>25.05.202627</t>
+  </si>
+  <si>
+    <t>25.05.202628</t>
+  </si>
+  <si>
+    <t>25.05.202629</t>
+  </si>
+  <si>
+    <t>25.05.202630</t>
+  </si>
+  <si>
+    <t>25.05.202631</t>
+  </si>
+  <si>
+    <t>25.05.202632</t>
+  </si>
+  <si>
+    <t>25.05.202633</t>
+  </si>
+  <si>
+    <t>25.05.202634</t>
+  </si>
+  <si>
+    <t>25.05.202635</t>
+  </si>
+  <si>
+    <t>25.05.202636</t>
+  </si>
+  <si>
+    <t>25.05.202637</t>
+  </si>
+  <si>
+    <t>25.05.202638</t>
+  </si>
+  <si>
+    <t>25.05.202639</t>
+  </si>
+  <si>
+    <t>25.05.202640</t>
+  </si>
+  <si>
+    <t>25.05.202641</t>
+  </si>
+  <si>
+    <t>25.05.202642</t>
+  </si>
+  <si>
+    <t>25.05.202643</t>
+  </si>
+  <si>
+    <t>25.05.202644</t>
+  </si>
+  <si>
+    <t>25.05.202645</t>
+  </si>
+  <si>
+    <t>25.05.202646</t>
+  </si>
+  <si>
+    <t>25.05.202647</t>
+  </si>
+  <si>
+    <t>25.05.202648</t>
+  </si>
+  <si>
+    <t>25.05.202649</t>
+  </si>
+  <si>
+    <t>25.05.202650</t>
+  </si>
+  <si>
+    <t>25.05.202651</t>
+  </si>
+  <si>
+    <t>25.05.202652</t>
+  </si>
+  <si>
+    <t>25.05.202653</t>
+  </si>
+  <si>
+    <t>25.05.202654</t>
+  </si>
+  <si>
+    <t>25.05.202655</t>
+  </si>
+  <si>
+    <t>25.05.202656</t>
+  </si>
+  <si>
+    <t>25.05.202657</t>
+  </si>
+  <si>
+    <t>25.05.202658</t>
+  </si>
+  <si>
+    <t>25.05.202659</t>
+  </si>
+  <si>
+    <t>25.05.202660</t>
+  </si>
+  <si>
+    <t>25.05.202661</t>
+  </si>
+  <si>
+    <t>25.05.202662</t>
+  </si>
+  <si>
+    <t>25.05.202663</t>
+  </si>
+  <si>
+    <t>25.05.202664</t>
+  </si>
+  <si>
+    <t>25.05.202665</t>
+  </si>
+  <si>
+    <t>25.05.202666</t>
+  </si>
+  <si>
+    <t>25.05.202667</t>
+  </si>
+  <si>
+    <t>25.05.202668</t>
+  </si>
+  <si>
+    <t>25.05.202669</t>
+  </si>
+  <si>
+    <t>25.05.202670</t>
+  </si>
+  <si>
+    <t>25.05.202671</t>
+  </si>
+  <si>
+    <t>25.05.202672</t>
+  </si>
+  <si>
+    <t>25.05.202673</t>
+  </si>
+  <si>
+    <t>25.05.202674</t>
+  </si>
+  <si>
+    <t>25.05.202675</t>
+  </si>
+  <si>
+    <t>25.05.202676</t>
+  </si>
+  <si>
+    <t>25.05.202677</t>
+  </si>
+  <si>
+    <t>25.05.202678</t>
+  </si>
+  <si>
+    <t>25.05.202679</t>
+  </si>
+  <si>
+    <t>25.05.202680</t>
+  </si>
+  <si>
+    <t>25.05.202681</t>
+  </si>
+  <si>
+    <t>25.05.202682</t>
+  </si>
+  <si>
+    <t>25.05.202683</t>
+  </si>
+  <si>
+    <t>25.05.202684</t>
+  </si>
+  <si>
+    <t>25.05.202685</t>
+  </si>
+  <si>
+    <t>25.05.202686</t>
+  </si>
+  <si>
+    <t>25.05.202687</t>
+  </si>
+  <si>
+    <t>25.05.202688</t>
+  </si>
+  <si>
+    <t>25.05.202689</t>
+  </si>
+  <si>
+    <t>25.05.202690</t>
+  </si>
+  <si>
+    <t>25.05.202691</t>
+  </si>
+  <si>
+    <t>25.05.202692</t>
+  </si>
+  <si>
+    <t>25.05.202693</t>
+  </si>
+  <si>
+    <t>25.05.202694</t>
+  </si>
+  <si>
+    <t>25.05.202695</t>
+  </si>
+  <si>
+    <t>25.05.202696</t>
   </si>
 </sst>
 </file>
@@ -966,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -988,7 +1564,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2">
         <v>7.77</v>
@@ -1005,7 +1581,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1598,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1615,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1632,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1649,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1666,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1683,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1700,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1717,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1734,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,10 +1751,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>7.771</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1192,10 +1768,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>7.775</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,10 +1785,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>7.776</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1226,10 +1802,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.771</v>
+        <v>7.779</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1819,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B17">
-        <v>7.775</v>
+        <v>7.786</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1836,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B18">
-        <v>8.086</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1853,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B19">
-        <v>8.092000000000001</v>
+        <v>8.132</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1870,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B20">
-        <v>8.112</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,10 +1887,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B21">
-        <v>9.452</v>
+        <v>10.679</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1328,10 +1904,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B22">
-        <v>43.22</v>
+        <v>35.465</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -1345,13 +1921,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B23">
-        <v>71.55800000000001</v>
+        <v>57.121</v>
       </c>
       <c r="C23">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1938,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B24">
-        <v>107.136</v>
+        <v>88.717</v>
       </c>
       <c r="C24">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1955,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B25">
-        <v>144.371</v>
+        <v>123.81</v>
       </c>
       <c r="C25">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1972,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B26">
-        <v>278.998</v>
+        <v>216.815</v>
       </c>
       <c r="C26">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1989,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B27">
-        <v>351.776</v>
+        <v>275.914</v>
       </c>
       <c r="C27">
-        <v>225</v>
+        <v>136</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +2006,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B28">
-        <v>447.834</v>
+        <v>348.046</v>
       </c>
       <c r="C28">
-        <v>316</v>
+        <v>193</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +2023,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B29">
-        <v>556.0359999999999</v>
+        <v>436.161</v>
       </c>
       <c r="C29">
-        <v>422</v>
+        <v>243</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +2040,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B30">
-        <v>763.179</v>
+        <v>606.5069999999999</v>
       </c>
       <c r="C30">
-        <v>530</v>
+        <v>304</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +2057,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B31">
-        <v>871.533</v>
+        <v>706.063</v>
       </c>
       <c r="C31">
-        <v>608</v>
+        <v>384</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +2074,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B32">
-        <v>984.004</v>
+        <v>812.92</v>
       </c>
       <c r="C32">
-        <v>704</v>
+        <v>416</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +2091,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B33">
-        <v>1076.122</v>
+        <v>914.894</v>
       </c>
       <c r="C33">
-        <v>801</v>
+        <v>519</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +2108,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B34">
-        <v>1230.85</v>
+        <v>1081.478</v>
       </c>
       <c r="C34">
-        <v>876</v>
+        <v>641</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +2125,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B35">
-        <v>1317.145</v>
+        <v>1178.237</v>
       </c>
       <c r="C35">
-        <v>979</v>
+        <v>648</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +2142,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B36">
-        <v>1406.763</v>
+        <v>1278.566</v>
       </c>
       <c r="C36">
-        <v>1094</v>
+        <v>723</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +2159,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B37">
-        <v>1498.898</v>
+        <v>1367.439</v>
       </c>
       <c r="C37">
-        <v>1179</v>
+        <v>852</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +2176,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B38">
-        <v>1609.988</v>
+        <v>1530.796</v>
       </c>
       <c r="C38">
-        <v>1231</v>
+        <v>910</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +2193,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B39">
-        <v>1654.627</v>
+        <v>1614.437</v>
       </c>
       <c r="C39">
-        <v>1308</v>
+        <v>1087</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +2210,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B40">
-        <v>1716.049</v>
+        <v>1704.998</v>
       </c>
       <c r="C40">
-        <v>1367</v>
+        <v>1186</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +2227,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B41">
-        <v>1764.772</v>
+        <v>1770.689</v>
       </c>
       <c r="C41">
-        <v>1369</v>
+        <v>1153</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +2244,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B42">
-        <v>1850.678</v>
+        <v>1890.295</v>
       </c>
       <c r="C42">
-        <v>1346</v>
+        <v>1145</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +2261,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B43">
-        <v>1874.983</v>
+        <v>1940.486</v>
       </c>
       <c r="C43">
-        <v>1379</v>
+        <v>1194</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +2278,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B44">
-        <v>1916.207</v>
+        <v>2019.32</v>
       </c>
       <c r="C44">
-        <v>1374</v>
+        <v>1155</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +2295,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B45">
-        <v>1924.118</v>
+        <v>2067.392</v>
       </c>
       <c r="C45">
-        <v>1406</v>
+        <v>1251</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +2312,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B46">
-        <v>1958.013</v>
+        <v>2097.747</v>
       </c>
       <c r="C46">
-        <v>1379</v>
+        <v>1333</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +2329,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B47">
-        <v>1961.945</v>
+        <v>2121.557</v>
       </c>
       <c r="C47">
-        <v>1361</v>
+        <v>1323</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +2346,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B48">
-        <v>1951.232</v>
+        <v>2074.246</v>
       </c>
       <c r="C48">
-        <v>1308</v>
+        <v>1371</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +2363,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B49">
-        <v>1942.379</v>
+        <v>2072.066</v>
       </c>
       <c r="C49">
-        <v>1264</v>
+        <v>1341</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +2380,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B50">
-        <v>1944.136</v>
+        <v>2054.691</v>
       </c>
       <c r="C50">
-        <v>1289</v>
+        <v>1236</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +2397,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B51">
-        <v>1919.049</v>
+        <v>2024.518</v>
       </c>
       <c r="C51">
-        <v>1333</v>
+        <v>1302</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +2414,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B52">
-        <v>1901.511</v>
+        <v>1994.334</v>
       </c>
       <c r="C52">
-        <v>1261</v>
+        <v>1328</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +2431,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B53">
-        <v>1874.301</v>
+        <v>1985.185</v>
       </c>
       <c r="C53">
-        <v>1283</v>
+        <v>1329</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +2448,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B54">
-        <v>1851.77</v>
+        <v>1973.287</v>
       </c>
       <c r="C54">
-        <v>1258</v>
+        <v>1453</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +2465,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B55">
-        <v>1817.189</v>
+        <v>1952.66</v>
       </c>
       <c r="C55">
-        <v>1220</v>
+        <v>1459</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +2482,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B56">
-        <v>1790.493</v>
+        <v>1918.352</v>
       </c>
       <c r="C56">
-        <v>1174</v>
+        <v>1370</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +2499,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B57">
-        <v>1759.048</v>
+        <v>1873.258</v>
       </c>
       <c r="C57">
-        <v>1145</v>
+        <v>1385</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +2516,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B58">
-        <v>1672.71</v>
+        <v>1836.85</v>
       </c>
       <c r="C58">
-        <v>1037</v>
+        <v>1324</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +2533,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B59">
-        <v>1630.296</v>
+        <v>1800.968</v>
       </c>
       <c r="C59">
-        <v>954</v>
+        <v>1379</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +2550,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B60">
-        <v>1579.955</v>
+        <v>1774.211</v>
       </c>
       <c r="C60">
-        <v>991</v>
+        <v>1428</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +2567,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B61">
-        <v>1535.055</v>
+        <v>1746.392</v>
       </c>
       <c r="C61">
-        <v>929</v>
+        <v>1272</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2584,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B62">
-        <v>1423.239</v>
+        <v>1601.071</v>
       </c>
       <c r="C62">
-        <v>855</v>
+        <v>1390</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2601,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B63">
-        <v>1362.155</v>
+        <v>1511.024</v>
       </c>
       <c r="C63">
-        <v>829</v>
+        <v>1441</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2618,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B64">
-        <v>1305.003</v>
+        <v>1438.069</v>
       </c>
       <c r="C64">
-        <v>797</v>
+        <v>1341</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2635,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B65">
-        <v>1242.72</v>
+        <v>1371.658</v>
       </c>
       <c r="C65">
-        <v>686</v>
+        <v>1205</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2652,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B66">
-        <v>1120.131</v>
+        <v>1243.272</v>
       </c>
       <c r="C66">
-        <v>637</v>
+        <v>994</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2669,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B67">
-        <v>1050.606</v>
+        <v>1160.547</v>
       </c>
       <c r="C67">
-        <v>598</v>
+        <v>1028</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2686,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B68">
-        <v>957.379</v>
+        <v>1061.553</v>
       </c>
       <c r="C68">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2703,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B69">
-        <v>870.646</v>
+        <v>981.9109999999999</v>
       </c>
       <c r="C69">
-        <v>488</v>
+        <v>981</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2720,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B70">
-        <v>705.761</v>
+        <v>828.511</v>
       </c>
       <c r="C70">
-        <v>452</v>
+        <v>876</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2737,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B71">
-        <v>611.523</v>
+        <v>725.6130000000001</v>
       </c>
       <c r="C71">
-        <v>439</v>
+        <v>773</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2754,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B72">
-        <v>525.674</v>
+        <v>631.403</v>
       </c>
       <c r="C72">
-        <v>402</v>
+        <v>672</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2771,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B73">
-        <v>447.341</v>
+        <v>541.043</v>
       </c>
       <c r="C73">
-        <v>344</v>
+        <v>635</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2788,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B74">
-        <v>303.669</v>
+        <v>367.48</v>
       </c>
       <c r="C74">
-        <v>263</v>
+        <v>512</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2805,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B75">
-        <v>241.949</v>
+        <v>300.441</v>
       </c>
       <c r="C75">
-        <v>206</v>
+        <v>343</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2822,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B76">
-        <v>190.307</v>
+        <v>230.249</v>
       </c>
       <c r="C76">
-        <v>138</v>
+        <v>211</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2839,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B77">
-        <v>149.562</v>
+        <v>177.577</v>
       </c>
       <c r="C77">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2856,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B78">
-        <v>85.68899999999999</v>
+        <v>120.753</v>
       </c>
       <c r="C78">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2873,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B79">
-        <v>59.978</v>
+        <v>109.443</v>
       </c>
       <c r="C79">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2890,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B80">
-        <v>39.784</v>
+        <v>50.106</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,10 +2907,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B81">
-        <v>31.927</v>
+        <v>35.009</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2348,10 +2924,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B82">
-        <v>25.069</v>
+        <v>18.639</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2941,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B83">
-        <v>21.781</v>
+        <v>18.847</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2958,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B84">
-        <v>21.162</v>
+        <v>18.481</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2975,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B85">
-        <v>20.561</v>
+        <v>17.867</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2992,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B86">
-        <v>13.67</v>
+        <v>17.27</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +3009,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B87">
-        <v>13.27</v>
+        <v>7.07</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +3026,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B88">
-        <v>9.57</v>
+        <v>3.97</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +3043,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B89">
-        <v>5.27</v>
+        <v>1.37</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +3060,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B90">
-        <v>9.77</v>
+        <v>10.27</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +3077,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,10 +3094,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2535,10 +3111,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B93">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2552,10 +3128,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,7 +3145,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +3162,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +3179,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,10 +3196,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B98">
-        <v>7.77</v>
+        <v>7.87</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2637,7 +3213,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46164.01041666666</v>
+        <v>46165.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +3230,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46164.02083333334</v>
+        <v>46165.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +3247,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46164.03125</v>
+        <v>46165.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +3264,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46164.04166666666</v>
+        <v>46165.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +3281,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46164.05208333334</v>
+        <v>46165.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +3298,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46164.0625</v>
+        <v>46165.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +3315,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46164.07291666666</v>
+        <v>46165.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +3332,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46164.08333333334</v>
+        <v>46165.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +3349,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46164.09375</v>
+        <v>46165.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +3366,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46164.10416666666</v>
+        <v>46165.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,10 +3383,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46164.11458333334</v>
+        <v>46165.11458333334</v>
       </c>
       <c r="B109">
-        <v>7.771</v>
+        <v>0</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2824,10 +3400,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46164.125</v>
+        <v>46165.125</v>
       </c>
       <c r="B110">
-        <v>7.775</v>
+        <v>0</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,10 +3417,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46164.13541666666</v>
+        <v>46165.13541666666</v>
       </c>
       <c r="B111">
-        <v>7.776</v>
+        <v>0</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2858,10 +3434,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46164.14583333334</v>
+        <v>46165.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.779</v>
+        <v>0</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2875,10 +3451,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46164.15625</v>
+        <v>46165.15625</v>
       </c>
       <c r="B113">
-        <v>7.786</v>
+        <v>0</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +3468,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46164.16666666666</v>
+        <v>46165.16666666666</v>
       </c>
       <c r="B114">
-        <v>8.119999999999999</v>
+        <v>8.202</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +3485,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46164.17708333334</v>
+        <v>46165.17708333334</v>
       </c>
       <c r="B115">
-        <v>8.132</v>
+        <v>0</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +3502,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46164.1875</v>
+        <v>46165.1875</v>
       </c>
       <c r="B116">
-        <v>8.186999999999999</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +3519,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46164.19791666666</v>
+        <v>46165.19791666666</v>
       </c>
       <c r="B117">
-        <v>10.679</v>
+        <v>15.405</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,13 +3536,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46164.20833333334</v>
+        <v>46165.20833333334</v>
       </c>
       <c r="B118">
-        <v>35.465</v>
+        <v>44.194</v>
       </c>
       <c r="C118">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +3553,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46164.21875</v>
+        <v>46165.21875</v>
       </c>
       <c r="B119">
-        <v>57.121</v>
+        <v>75.233</v>
       </c>
       <c r="C119">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +3570,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46164.22916666666</v>
+        <v>46165.22916666666</v>
       </c>
       <c r="B120">
-        <v>88.717</v>
+        <v>115.25</v>
       </c>
       <c r="C120">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3587,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46164.23958333334</v>
+        <v>46165.23958333334</v>
       </c>
       <c r="B121">
-        <v>123.81</v>
+        <v>170.728</v>
       </c>
       <c r="C121">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3604,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46164.25</v>
+        <v>46165.25</v>
       </c>
       <c r="B122">
-        <v>216.815</v>
+        <v>284.722</v>
       </c>
       <c r="C122">
-        <v>95</v>
+        <v>165</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3621,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46164.26041666666</v>
+        <v>46165.26041666666</v>
       </c>
       <c r="B123">
-        <v>275.914</v>
+        <v>366.49</v>
       </c>
       <c r="C123">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3638,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46164.27083333334</v>
+        <v>46165.27083333334</v>
       </c>
       <c r="B124">
-        <v>348.046</v>
+        <v>461.093</v>
       </c>
       <c r="C124">
-        <v>193</v>
+        <v>297</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3655,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46164.28125</v>
+        <v>46165.28125</v>
       </c>
       <c r="B125">
-        <v>436.161</v>
+        <v>567.111</v>
       </c>
       <c r="C125">
-        <v>243</v>
+        <v>395</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3672,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46164.29166666666</v>
+        <v>46165.29166666666</v>
       </c>
       <c r="B126">
-        <v>606.5069999999999</v>
+        <v>745.524</v>
       </c>
       <c r="C126">
-        <v>304</v>
+        <v>469</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3689,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46164.30208333334</v>
+        <v>46165.30208333334</v>
       </c>
       <c r="B127">
-        <v>706.063</v>
+        <v>871.384</v>
       </c>
       <c r="C127">
-        <v>384</v>
+        <v>515</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3706,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46164.3125</v>
+        <v>46165.3125</v>
       </c>
       <c r="B128">
-        <v>812.92</v>
+        <v>991.596</v>
       </c>
       <c r="C128">
-        <v>416</v>
+        <v>616</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3723,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46164.32291666666</v>
+        <v>46165.32291666666</v>
       </c>
       <c r="B129">
-        <v>914.894</v>
+        <v>1102.342</v>
       </c>
       <c r="C129">
-        <v>519</v>
+        <v>715</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3740,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46164.33333333334</v>
+        <v>46165.33333333334</v>
       </c>
       <c r="B130">
-        <v>1081.478</v>
+        <v>1297.666</v>
       </c>
       <c r="C130">
-        <v>641</v>
+        <v>805</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3757,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46164.34375</v>
+        <v>46165.34375</v>
       </c>
       <c r="B131">
-        <v>1178.237</v>
+        <v>1403.947</v>
       </c>
       <c r="C131">
-        <v>648</v>
+        <v>947</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3774,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46164.35416666666</v>
+        <v>46165.35416666666</v>
       </c>
       <c r="B132">
-        <v>1278.566</v>
+        <v>1529.962</v>
       </c>
       <c r="C132">
-        <v>723</v>
+        <v>1006</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3791,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46164.36458333334</v>
+        <v>46165.36458333334</v>
       </c>
       <c r="B133">
-        <v>1367.439</v>
+        <v>1635.807</v>
       </c>
       <c r="C133">
-        <v>852</v>
+        <v>1032</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3808,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46164.375</v>
+        <v>46165.375</v>
       </c>
       <c r="B134">
-        <v>1530.796</v>
+        <v>1792.243</v>
       </c>
       <c r="C134">
-        <v>910</v>
+        <v>1093</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3825,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46164.38541666666</v>
+        <v>46165.38541666666</v>
       </c>
       <c r="B135">
-        <v>1614.437</v>
+        <v>1889.027</v>
       </c>
       <c r="C135">
-        <v>1087</v>
+        <v>1221</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3842,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46164.39583333334</v>
+        <v>46165.39583333334</v>
       </c>
       <c r="B136">
-        <v>1704.998</v>
+        <v>1861.31</v>
       </c>
       <c r="C136">
-        <v>1186</v>
+        <v>1195</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3859,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46164.40625</v>
+        <v>46165.40625</v>
       </c>
       <c r="B137">
-        <v>1770.689</v>
+        <v>1526.309</v>
       </c>
       <c r="C137">
-        <v>1153</v>
+        <v>937</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3876,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46164.41666666666</v>
+        <v>46165.41666666666</v>
       </c>
       <c r="B138">
-        <v>1890.295</v>
+        <v>1532.936</v>
       </c>
       <c r="C138">
-        <v>1145</v>
+        <v>874</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3893,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46164.42708333334</v>
+        <v>46165.42708333334</v>
       </c>
       <c r="B139">
-        <v>1940.486</v>
+        <v>1584.276</v>
       </c>
       <c r="C139">
-        <v>1194</v>
+        <v>893</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3910,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46164.4375</v>
+        <v>46165.4375</v>
       </c>
       <c r="B140">
-        <v>2019.32</v>
+        <v>1570.099</v>
       </c>
       <c r="C140">
-        <v>1155</v>
+        <v>915</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3927,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46164.44791666666</v>
+        <v>46165.44791666666</v>
       </c>
       <c r="B141">
-        <v>2067.392</v>
+        <v>1571.084</v>
       </c>
       <c r="C141">
-        <v>1251</v>
+        <v>891</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3944,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46164.45833333334</v>
+        <v>46165.45833333334</v>
       </c>
       <c r="B142">
-        <v>2097.747</v>
+        <v>2099.024</v>
       </c>
       <c r="C142">
-        <v>1333</v>
+        <v>1265</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3961,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46164.46875</v>
+        <v>46165.46875</v>
       </c>
       <c r="B143">
-        <v>2121.557</v>
+        <v>2141.512</v>
       </c>
       <c r="C143">
-        <v>1323</v>
+        <v>1371</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3978,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46164.47916666666</v>
+        <v>46165.47916666666</v>
       </c>
       <c r="B144">
-        <v>2074.246</v>
+        <v>2146.285</v>
       </c>
       <c r="C144">
-        <v>1371</v>
+        <v>1444</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3995,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46164.48958333334</v>
+        <v>46165.48958333334</v>
       </c>
       <c r="B145">
-        <v>2072.066</v>
+        <v>2160.371</v>
       </c>
       <c r="C145">
-        <v>1341</v>
+        <v>1447</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +4012,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46164.5</v>
+        <v>46165.5</v>
       </c>
       <c r="B146">
-        <v>2054.691</v>
+        <v>2249.504</v>
       </c>
       <c r="C146">
-        <v>1236</v>
+        <v>1439</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +4029,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46164.51041666666</v>
+        <v>46165.51041666666</v>
       </c>
       <c r="B147">
-        <v>2024.518</v>
+        <v>2276.89</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1559</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +4046,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46164.52083333334</v>
+        <v>46165.52083333334</v>
       </c>
       <c r="B148">
-        <v>1994.334</v>
+        <v>2251.969</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1684</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,13 +4063,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46164.53125</v>
+        <v>46165.53125</v>
       </c>
       <c r="B149">
-        <v>1985.185</v>
+        <v>2254.493</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1552</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3504,13 +4080,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46164.54166666666</v>
+        <v>46165.54166666666</v>
       </c>
       <c r="B150">
-        <v>1973.287</v>
+        <v>2206.225</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>1508</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3521,13 +4097,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46164.55208333334</v>
+        <v>46165.55208333334</v>
       </c>
       <c r="B151">
-        <v>1952.66</v>
+        <v>2187.746</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>1555</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3538,13 +4114,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46164.5625</v>
+        <v>46165.5625</v>
       </c>
       <c r="B152">
-        <v>1918.352</v>
+        <v>2141.382</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3555,13 +4131,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46164.57291666666</v>
+        <v>46165.57291666666</v>
       </c>
       <c r="B153">
-        <v>1873.258</v>
+        <v>2120.989</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>1505</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3572,13 +4148,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46164.58333333334</v>
+        <v>46165.58333333334</v>
       </c>
       <c r="B154">
-        <v>1836.85</v>
+        <v>1621.754</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>1129</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3589,13 +4165,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46164.59375</v>
+        <v>46165.59375</v>
       </c>
       <c r="B155">
-        <v>1800.968</v>
+        <v>1581.405</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3606,13 +4182,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46164.60416666666</v>
+        <v>46165.60416666666</v>
       </c>
       <c r="B156">
-        <v>1774.211</v>
+        <v>1525.372</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3623,13 +4199,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46164.61458333334</v>
+        <v>46165.61458333334</v>
       </c>
       <c r="B157">
-        <v>1746.392</v>
+        <v>1476.014</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3640,13 +4216,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46164.625</v>
+        <v>46165.625</v>
       </c>
       <c r="B158">
-        <v>1601.071</v>
+        <v>1220.333</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3657,13 +4233,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46164.63541666666</v>
+        <v>46165.63541666666</v>
       </c>
       <c r="B159">
-        <v>1511.024</v>
+        <v>1209.516</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3674,13 +4250,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46164.64583333334</v>
+        <v>46165.64583333334</v>
       </c>
       <c r="B160">
-        <v>1438.069</v>
+        <v>1147.922</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>697</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3691,13 +4267,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46164.65625</v>
+        <v>46165.65625</v>
       </c>
       <c r="B161">
-        <v>1371.658</v>
+        <v>1085.023</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3708,13 +4284,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46164.66666666666</v>
+        <v>46165.66666666666</v>
       </c>
       <c r="B162">
-        <v>1243.272</v>
+        <v>965.987</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3725,13 +4301,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46164.67708333334</v>
+        <v>46165.67708333334</v>
       </c>
       <c r="B163">
-        <v>1160.547</v>
+        <v>941.081</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3742,13 +4318,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46164.6875</v>
+        <v>46165.6875</v>
       </c>
       <c r="B164">
-        <v>1061.553</v>
+        <v>877.46</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>518</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3759,13 +4335,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46164.69791666666</v>
+        <v>46165.69791666666</v>
       </c>
       <c r="B165">
-        <v>981.9109999999999</v>
+        <v>1041.156</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3776,13 +4352,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46164.70833333334</v>
+        <v>46165.70833333334</v>
       </c>
       <c r="B166">
-        <v>828.511</v>
+        <v>901.9690000000001</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3793,13 +4369,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46164.71875</v>
+        <v>46165.71875</v>
       </c>
       <c r="B167">
-        <v>725.6130000000001</v>
+        <v>800.519</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>739</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3810,13 +4386,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46164.72916666666</v>
+        <v>46165.72916666666</v>
       </c>
       <c r="B168">
-        <v>631.403</v>
+        <v>679.519</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3827,13 +4403,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46164.73958333334</v>
+        <v>46165.73958333334</v>
       </c>
       <c r="B169">
-        <v>541.043</v>
+        <v>558.1660000000001</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>535</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3844,13 +4420,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46164.75</v>
+        <v>46165.75</v>
       </c>
       <c r="B170">
-        <v>367.48</v>
+        <v>386.986</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3861,13 +4437,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46164.76041666666</v>
+        <v>46165.76041666666</v>
       </c>
       <c r="B171">
-        <v>300.441</v>
+        <v>295.785</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3878,13 +4454,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46164.77083333334</v>
+        <v>46165.77083333334</v>
       </c>
       <c r="B172">
-        <v>230.249</v>
+        <v>215.113</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3895,13 +4471,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46164.78125</v>
+        <v>46165.78125</v>
       </c>
       <c r="B173">
-        <v>177.577</v>
+        <v>153.848</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3912,13 +4488,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46164.79166666666</v>
+        <v>46165.79166666666</v>
       </c>
       <c r="B174">
-        <v>120.753</v>
+        <v>83.73399999999999</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3929,13 +4505,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46164.80208333334</v>
+        <v>46165.80208333334</v>
       </c>
       <c r="B175">
-        <v>109.443</v>
+        <v>53.664</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3946,13 +4522,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46164.8125</v>
+        <v>46165.8125</v>
       </c>
       <c r="B176">
-        <v>50.106</v>
+        <v>33.216</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3963,13 +4539,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46164.82291666666</v>
+        <v>46165.82291666666</v>
       </c>
       <c r="B177">
-        <v>35.009</v>
+        <v>23.125</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3980,13 +4556,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46164.83333333334</v>
+        <v>46165.83333333334</v>
       </c>
       <c r="B178">
-        <v>18.639</v>
+        <v>17.479</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3997,10 +4573,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46164.84375</v>
+        <v>46165.84375</v>
       </c>
       <c r="B179">
-        <v>18.847</v>
+        <v>14.48</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4590,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46164.85416666666</v>
+        <v>46165.85416666666</v>
       </c>
       <c r="B180">
-        <v>18.481</v>
+        <v>11.76</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4607,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46164.86458333334</v>
+        <v>46165.86458333334</v>
       </c>
       <c r="B181">
-        <v>17.867</v>
+        <v>10.852</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4624,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46164.875</v>
+        <v>46165.875</v>
       </c>
       <c r="B182">
-        <v>17.27</v>
+        <v>6.37</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4641,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46164.88541666666</v>
+        <v>46165.88541666666</v>
       </c>
       <c r="B183">
-        <v>7.07</v>
+        <v>6.07</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4658,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46164.89583333334</v>
+        <v>46165.89583333334</v>
       </c>
       <c r="B184">
-        <v>3.97</v>
+        <v>2.37</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4675,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46164.90625</v>
+        <v>46165.90625</v>
       </c>
       <c r="B185">
-        <v>1.37</v>
+        <v>1.97</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4692,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46164.91666666666</v>
+        <v>46165.91666666666</v>
       </c>
       <c r="B186">
-        <v>10.27</v>
+        <v>2.27</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4709,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46164.92708333334</v>
+        <v>46165.92708333334</v>
       </c>
       <c r="B187">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4726,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46164.9375</v>
+        <v>46165.9375</v>
       </c>
       <c r="B188">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4743,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46164.94791666666</v>
+        <v>46165.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,10 +4760,10 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46164.95833333334</v>
+        <v>46165.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -4201,7 +4777,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46164.96875</v>
+        <v>46165.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4794,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46164.97916666666</v>
+        <v>46165.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4811,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46164.98958333334</v>
+        <v>46165.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4248,6 +4824,3270 @@
       </c>
       <c r="E193" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B194">
+        <v>7.87</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46166.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46166.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46166.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46166.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46166.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46166.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46166.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46166.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46166.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46166.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46166.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46166.125</v>
+      </c>
+      <c r="B206">
+        <v>8.031000000000001</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46166.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>8.015000000000001</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46166.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>8.007</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46166.15625</v>
+      </c>
+      <c r="B209">
+        <v>8.031000000000001</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46166.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>8.249000000000001</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46166.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>8.364000000000001</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46166.1875</v>
+      </c>
+      <c r="B212">
+        <v>10.457</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46166.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>25.377</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46166.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>71.831</v>
+      </c>
+      <c r="C214">
+        <v>15</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46166.21875</v>
+      </c>
+      <c r="B215">
+        <v>129.133</v>
+      </c>
+      <c r="C215">
+        <v>43</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46166.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>189.929</v>
+      </c>
+      <c r="C216">
+        <v>80</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46166.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>268.613</v>
+      </c>
+      <c r="C217">
+        <v>136</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46166.25</v>
+      </c>
+      <c r="B218">
+        <v>440.446</v>
+      </c>
+      <c r="C218">
+        <v>197</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46166.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>552.223</v>
+      </c>
+      <c r="C219">
+        <v>288</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46166.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>682.326</v>
+      </c>
+      <c r="C220">
+        <v>375</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46166.28125</v>
+      </c>
+      <c r="B221">
+        <v>826.947</v>
+      </c>
+      <c r="C221">
+        <v>474</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46166.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>1086.127</v>
+      </c>
+      <c r="C222">
+        <v>611</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46166.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>1232.938</v>
+      </c>
+      <c r="C223">
+        <v>710</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46166.3125</v>
+      </c>
+      <c r="B224">
+        <v>1387.864</v>
+      </c>
+      <c r="C224">
+        <v>799</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46166.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>1533.993</v>
+      </c>
+      <c r="C225">
+        <v>827</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46166.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1770.664</v>
+      </c>
+      <c r="C226">
+        <v>974</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46166.34375</v>
+      </c>
+      <c r="B227">
+        <v>1903.237</v>
+      </c>
+      <c r="C227">
+        <v>1130</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46166.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>1931.442</v>
+      </c>
+      <c r="C228">
+        <v>1264</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46166.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>1988.543</v>
+      </c>
+      <c r="C229">
+        <v>1252</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46166.375</v>
+      </c>
+      <c r="B230">
+        <v>2111.641</v>
+      </c>
+      <c r="C230">
+        <v>1297</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46166.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>1713.266</v>
+      </c>
+      <c r="C231">
+        <v>1052</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46166.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>1761.537</v>
+      </c>
+      <c r="C232">
+        <v>1032</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46166.40625</v>
+      </c>
+      <c r="B233">
+        <v>1821.039</v>
+      </c>
+      <c r="C233">
+        <v>1026</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46166.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>1915.576</v>
+      </c>
+      <c r="C234">
+        <v>1029</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46166.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>1875.031</v>
+      </c>
+      <c r="C235">
+        <v>1093</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46166.4375</v>
+      </c>
+      <c r="B236">
+        <v>1863.207</v>
+      </c>
+      <c r="C236">
+        <v>1061</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46166.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>1827.93</v>
+      </c>
+      <c r="C237">
+        <v>1018</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46166.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>1836.54</v>
+      </c>
+      <c r="C238">
+        <v>1079</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46166.46875</v>
+      </c>
+      <c r="B239">
+        <v>1844.138</v>
+      </c>
+      <c r="C239">
+        <v>1088</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46166.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>1853.033</v>
+      </c>
+      <c r="C240">
+        <v>1144</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46166.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>1854.867</v>
+      </c>
+      <c r="C241">
+        <v>1209</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46166.5</v>
+      </c>
+      <c r="B242">
+        <v>1853.398</v>
+      </c>
+      <c r="C242">
+        <v>1129</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46166.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>1850.597</v>
+      </c>
+      <c r="C243">
+        <v>1093</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46166.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>1856.221</v>
+      </c>
+      <c r="C244">
+        <v>1110</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46166.53125</v>
+      </c>
+      <c r="B245">
+        <v>1872.429</v>
+      </c>
+      <c r="C245">
+        <v>1058</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46166.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>1792.33</v>
+      </c>
+      <c r="C246">
+        <v>1042</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46166.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1829.258</v>
+      </c>
+      <c r="C247">
+        <v>973</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46166.5625</v>
+      </c>
+      <c r="B248">
+        <v>1802.623</v>
+      </c>
+      <c r="C248">
+        <v>947</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46166.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>1721.048</v>
+      </c>
+      <c r="C249">
+        <v>937</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46166.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1825.571</v>
+      </c>
+      <c r="C250">
+        <v>951</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46166.59375</v>
+      </c>
+      <c r="B251">
+        <v>1617.52</v>
+      </c>
+      <c r="C251">
+        <v>937</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46166.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>1627.589</v>
+      </c>
+      <c r="C252">
+        <v>881</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46166.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>1578.59</v>
+      </c>
+      <c r="C253">
+        <v>868</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46166.625</v>
+      </c>
+      <c r="B254">
+        <v>1408.628</v>
+      </c>
+      <c r="C254">
+        <v>827</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46166.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>1326.772</v>
+      </c>
+      <c r="C255">
+        <v>746</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46166.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1264.554</v>
+      </c>
+      <c r="C256">
+        <v>717</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46166.65625</v>
+      </c>
+      <c r="B257">
+        <v>1201.94</v>
+      </c>
+      <c r="C257">
+        <v>722</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46166.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1083.311</v>
+      </c>
+      <c r="C258">
+        <v>663</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46166.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>1054.96</v>
+      </c>
+      <c r="C259">
+        <v>652</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46166.6875</v>
+      </c>
+      <c r="B260">
+        <v>988.6079999999999</v>
+      </c>
+      <c r="C260">
+        <v>679</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46166.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>943.977</v>
+      </c>
+      <c r="C261">
+        <v>647</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46166.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>1010.149</v>
+      </c>
+      <c r="C262">
+        <v>739</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46166.71875</v>
+      </c>
+      <c r="B263">
+        <v>929.994</v>
+      </c>
+      <c r="C263">
+        <v>719</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46166.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>824.5890000000001</v>
+      </c>
+      <c r="C264">
+        <v>620</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46166.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>683.829</v>
+      </c>
+      <c r="C265">
+        <v>505</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46166.75</v>
+      </c>
+      <c r="B266">
+        <v>473.961</v>
+      </c>
+      <c r="C266">
+        <v>395</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46166.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>362.196</v>
+      </c>
+      <c r="C267">
+        <v>289</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46166.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>260.94</v>
+      </c>
+      <c r="C268">
+        <v>194</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46166.78125</v>
+      </c>
+      <c r="B269">
+        <v>189.442</v>
+      </c>
+      <c r="C269">
+        <v>120</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46166.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>113.205</v>
+      </c>
+      <c r="C270">
+        <v>68</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46166.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>73.937</v>
+      </c>
+      <c r="C271">
+        <v>40</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46166.8125</v>
+      </c>
+      <c r="B272">
+        <v>44.124</v>
+      </c>
+      <c r="C272">
+        <v>12</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46166.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>32.86</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46166.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>19.096</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46166.84375</v>
+      </c>
+      <c r="B275">
+        <v>18.352</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46166.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>14.854</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46166.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>12.317</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46166.875</v>
+      </c>
+      <c r="B278">
+        <v>5.302</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46166.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>4.89</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46166.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>1.77</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46166.90625</v>
+      </c>
+      <c r="B281">
+        <v>1.37</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46166.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46166.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>1.77</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46166.9375</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46166.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>1.37</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46166.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0.97</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46166.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46166.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46166.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B290">
+        <v>7.97</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46167.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46167.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46167.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46167.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46167.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46167.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46167.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46167.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46167.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46167.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46167.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46167.125</v>
+      </c>
+      <c r="B302">
+        <v>7.989</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46167.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46167.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>7.991</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46167.15625</v>
+      </c>
+      <c r="B305">
+        <v>7.996</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46167.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>8.4</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46167.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>8.484999999999999</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46167.1875</v>
+      </c>
+      <c r="B308">
+        <v>8.714</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46167.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>27.057</v>
+      </c>
+      <c r="C309">
+        <v>1</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46167.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>81.357</v>
+      </c>
+      <c r="C310">
+        <v>24</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46167.21875</v>
+      </c>
+      <c r="B311">
+        <v>146.757</v>
+      </c>
+      <c r="C311">
+        <v>74</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46167.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>209.892</v>
+      </c>
+      <c r="C312">
+        <v>147</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46167.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>297.016</v>
+      </c>
+      <c r="C313">
+        <v>227</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46167.25</v>
+      </c>
+      <c r="B314">
+        <v>481.292</v>
+      </c>
+      <c r="C314">
+        <v>345</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46167.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>615.706</v>
+      </c>
+      <c r="C315">
+        <v>491</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46167.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>750.925</v>
+      </c>
+      <c r="C316">
+        <v>595</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46167.28125</v>
+      </c>
+      <c r="B317">
+        <v>914.871</v>
+      </c>
+      <c r="C317">
+        <v>773</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46167.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>1230.68</v>
+      </c>
+      <c r="C318">
+        <v>972</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46167.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>1415.906</v>
+      </c>
+      <c r="C319">
+        <v>1160</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46167.3125</v>
+      </c>
+      <c r="B320">
+        <v>1615.361</v>
+      </c>
+      <c r="C320">
+        <v>1333</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46167.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>1778.252</v>
+      </c>
+      <c r="C321">
+        <v>1494</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46167.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>2131.836</v>
+      </c>
+      <c r="C322">
+        <v>1607</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46167.34375</v>
+      </c>
+      <c r="B323">
+        <v>2281.091</v>
+      </c>
+      <c r="C323">
+        <v>1740</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46167.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>2429.636</v>
+      </c>
+      <c r="C324">
+        <v>1869</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46167.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>2551.979</v>
+      </c>
+      <c r="C325">
+        <v>1991</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46167.375</v>
+      </c>
+      <c r="B326">
+        <v>2706.66</v>
+      </c>
+      <c r="C326">
+        <v>2075</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46167.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>2805.345</v>
+      </c>
+      <c r="C327">
+        <v>2125</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46167.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>2757.352</v>
+      </c>
+      <c r="C328">
+        <v>2009</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46167.40625</v>
+      </c>
+      <c r="B329">
+        <v>2715.633</v>
+      </c>
+      <c r="C329">
+        <v>1909</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46167.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>2871.262</v>
+      </c>
+      <c r="C330">
+        <v>2066</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46167.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>2947.675</v>
+      </c>
+      <c r="C331">
+        <v>2204</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46167.4375</v>
+      </c>
+      <c r="B332">
+        <v>3001.965</v>
+      </c>
+      <c r="C332">
+        <v>2220</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46167.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>3023.773</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46167.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>3183.57</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46167.46875</v>
+      </c>
+      <c r="B335">
+        <v>3186.279</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46167.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>3178.579</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46167.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>3183.472</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46167.5</v>
+      </c>
+      <c r="B338">
+        <v>3156.447</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46167.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>3141.34</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46167.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>3134.151</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46167.53125</v>
+      </c>
+      <c r="B341">
+        <v>3107.738</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46167.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>2927.537</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46167.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>2902.83</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46167.5625</v>
+      </c>
+      <c r="B344">
+        <v>2867.83</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46167.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>2933.707</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46167.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>2848.184</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46167.59375</v>
+      </c>
+      <c r="B347">
+        <v>2786.226</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46167.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>2706.109</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46167.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>2603.284</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46167.625</v>
+      </c>
+      <c r="B350">
+        <v>2432.361</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46167.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>2306.375</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46167.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>2192.969</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46167.65625</v>
+      </c>
+      <c r="B353">
+        <v>2074.904</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46167.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>1840.863</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46167.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>1671.148</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46167.6875</v>
+      </c>
+      <c r="B356">
+        <v>1500.546</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46167.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>1350.273</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46167.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>1079.014</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46167.71875</v>
+      </c>
+      <c r="B359">
+        <v>944.069</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46167.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>801.301</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46167.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>665.01</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46167.75</v>
+      </c>
+      <c r="B362">
+        <v>449.784</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46167.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>349.155</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46167.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>261.816</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46167.78125</v>
+      </c>
+      <c r="B365">
+        <v>195.335</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46167.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>105.112</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46167.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>64.839</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46167.8125</v>
+      </c>
+      <c r="B368">
+        <v>38.95</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46167.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>34.969</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46167.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>22.061</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46167.84375</v>
+      </c>
+      <c r="B371">
+        <v>20.108</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46167.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>20.779</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46167.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>20.265</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46167.875</v>
+      </c>
+      <c r="B374">
+        <v>19.672</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46167.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>11.772</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46167.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>6.272</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46167.90625</v>
+      </c>
+      <c r="B377">
+        <v>5.872</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46167.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>10.77</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46167.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>2.27</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46167.9375</v>
+      </c>
+      <c r="B380">
+        <v>1.87</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46167.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>1.57</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46167.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46167.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46167.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46167.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.05.20261</t>
-  </si>
-  <si>
-    <t>25.05.20262</t>
-  </si>
-  <si>
-    <t>25.05.20263</t>
-  </si>
-  <si>
-    <t>25.05.20264</t>
-  </si>
-  <si>
-    <t>25.05.20265</t>
-  </si>
-  <si>
-    <t>25.05.20266</t>
-  </si>
-  <si>
-    <t>25.05.20267</t>
-  </si>
-  <si>
-    <t>25.05.20268</t>
-  </si>
-  <si>
-    <t>25.05.20269</t>
-  </si>
-  <si>
-    <t>25.05.202610</t>
-  </si>
-  <si>
-    <t>25.05.202611</t>
-  </si>
-  <si>
-    <t>25.05.202612</t>
-  </si>
-  <si>
-    <t>25.05.202613</t>
-  </si>
-  <si>
-    <t>25.05.202614</t>
-  </si>
-  <si>
-    <t>25.05.202615</t>
-  </si>
-  <si>
-    <t>25.05.202616</t>
-  </si>
-  <si>
-    <t>25.05.202617</t>
-  </si>
-  <si>
-    <t>25.05.202618</t>
-  </si>
-  <si>
-    <t>25.05.202619</t>
-  </si>
-  <si>
-    <t>25.05.202620</t>
-  </si>
-  <si>
-    <t>25.05.202621</t>
-  </si>
-  <si>
-    <t>25.05.202622</t>
-  </si>
-  <si>
-    <t>25.05.202623</t>
-  </si>
-  <si>
-    <t>25.05.202624</t>
-  </si>
-  <si>
-    <t>25.05.202625</t>
-  </si>
-  <si>
-    <t>25.05.202626</t>
-  </si>
-  <si>
-    <t>25.05.202627</t>
-  </si>
-  <si>
-    <t>25.05.202628</t>
-  </si>
-  <si>
-    <t>25.05.202629</t>
-  </si>
-  <si>
-    <t>25.05.202630</t>
-  </si>
-  <si>
-    <t>25.05.202631</t>
-  </si>
-  <si>
-    <t>25.05.202632</t>
-  </si>
-  <si>
-    <t>25.05.202633</t>
-  </si>
-  <si>
-    <t>25.05.202634</t>
-  </si>
-  <si>
-    <t>25.05.202635</t>
-  </si>
-  <si>
-    <t>25.05.202636</t>
-  </si>
-  <si>
-    <t>25.05.202637</t>
-  </si>
-  <si>
-    <t>25.05.202638</t>
-  </si>
-  <si>
-    <t>25.05.202639</t>
-  </si>
-  <si>
-    <t>25.05.202640</t>
-  </si>
-  <si>
-    <t>25.05.202641</t>
-  </si>
-  <si>
-    <t>25.05.202642</t>
-  </si>
-  <si>
-    <t>25.05.202643</t>
-  </si>
-  <si>
-    <t>25.05.202644</t>
-  </si>
-  <si>
-    <t>25.05.202645</t>
-  </si>
-  <si>
-    <t>25.05.202646</t>
-  </si>
-  <si>
-    <t>25.05.202647</t>
-  </si>
-  <si>
-    <t>25.05.202648</t>
-  </si>
-  <si>
-    <t>25.05.202649</t>
-  </si>
-  <si>
-    <t>25.05.202650</t>
-  </si>
-  <si>
-    <t>25.05.202651</t>
-  </si>
-  <si>
-    <t>25.05.202652</t>
-  </si>
-  <si>
-    <t>25.05.202653</t>
-  </si>
-  <si>
-    <t>25.05.202654</t>
-  </si>
-  <si>
-    <t>25.05.202655</t>
-  </si>
-  <si>
-    <t>25.05.202656</t>
-  </si>
-  <si>
-    <t>25.05.202657</t>
-  </si>
-  <si>
-    <t>25.05.202658</t>
-  </si>
-  <si>
-    <t>25.05.202659</t>
-  </si>
-  <si>
-    <t>25.05.202660</t>
-  </si>
-  <si>
-    <t>25.05.202661</t>
-  </si>
-  <si>
-    <t>25.05.202662</t>
-  </si>
-  <si>
-    <t>25.05.202663</t>
-  </si>
-  <si>
-    <t>25.05.202664</t>
-  </si>
-  <si>
-    <t>25.05.202665</t>
-  </si>
-  <si>
-    <t>25.05.202666</t>
-  </si>
-  <si>
-    <t>25.05.202667</t>
-  </si>
-  <si>
-    <t>25.05.202668</t>
-  </si>
-  <si>
-    <t>25.05.202669</t>
-  </si>
-  <si>
-    <t>25.05.202670</t>
-  </si>
-  <si>
-    <t>25.05.202671</t>
-  </si>
-  <si>
-    <t>25.05.202672</t>
-  </si>
-  <si>
-    <t>25.05.202673</t>
-  </si>
-  <si>
-    <t>25.05.202674</t>
-  </si>
-  <si>
-    <t>25.05.202675</t>
-  </si>
-  <si>
-    <t>25.05.202676</t>
-  </si>
-  <si>
-    <t>25.05.202677</t>
-  </si>
-  <si>
-    <t>25.05.202678</t>
-  </si>
-  <si>
-    <t>25.05.202679</t>
-  </si>
-  <si>
-    <t>25.05.202680</t>
-  </si>
-  <si>
-    <t>25.05.202681</t>
-  </si>
-  <si>
-    <t>25.05.202682</t>
-  </si>
-  <si>
-    <t>25.05.202683</t>
-  </si>
-  <si>
-    <t>25.05.202684</t>
-  </si>
-  <si>
-    <t>25.05.202685</t>
-  </si>
-  <si>
-    <t>25.05.202686</t>
-  </si>
-  <si>
-    <t>25.05.202687</t>
-  </si>
-  <si>
-    <t>25.05.202688</t>
-  </si>
-  <si>
-    <t>25.05.202689</t>
-  </si>
-  <si>
-    <t>25.05.202690</t>
-  </si>
-  <si>
-    <t>25.05.202691</t>
-  </si>
-  <si>
-    <t>25.05.202692</t>
-  </si>
-  <si>
-    <t>25.05.202693</t>
-  </si>
-  <si>
-    <t>25.05.202694</t>
-  </si>
-  <si>
-    <t>25.05.202695</t>
-  </si>
-  <si>
-    <t>25.05.202696</t>
-  </si>
-  <si>
     <t>26.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>26.05.202696</t>
+  </si>
+  <si>
+    <t>27.05.20261</t>
+  </si>
+  <si>
+    <t>27.05.20262</t>
+  </si>
+  <si>
+    <t>27.05.20263</t>
+  </si>
+  <si>
+    <t>27.05.20264</t>
+  </si>
+  <si>
+    <t>27.05.20265</t>
+  </si>
+  <si>
+    <t>27.05.20266</t>
+  </si>
+  <si>
+    <t>27.05.20267</t>
+  </si>
+  <si>
+    <t>27.05.20268</t>
+  </si>
+  <si>
+    <t>27.05.20269</t>
+  </si>
+  <si>
+    <t>27.05.202610</t>
+  </si>
+  <si>
+    <t>27.05.202611</t>
+  </si>
+  <si>
+    <t>27.05.202612</t>
+  </si>
+  <si>
+    <t>27.05.202613</t>
+  </si>
+  <si>
+    <t>27.05.202614</t>
+  </si>
+  <si>
+    <t>27.05.202615</t>
+  </si>
+  <si>
+    <t>27.05.202616</t>
+  </si>
+  <si>
+    <t>27.05.202617</t>
+  </si>
+  <si>
+    <t>27.05.202618</t>
+  </si>
+  <si>
+    <t>27.05.202619</t>
+  </si>
+  <si>
+    <t>27.05.202620</t>
+  </si>
+  <si>
+    <t>27.05.202621</t>
+  </si>
+  <si>
+    <t>27.05.202622</t>
+  </si>
+  <si>
+    <t>27.05.202623</t>
+  </si>
+  <si>
+    <t>27.05.202624</t>
+  </si>
+  <si>
+    <t>27.05.202625</t>
+  </si>
+  <si>
+    <t>27.05.202626</t>
+  </si>
+  <si>
+    <t>27.05.202627</t>
+  </si>
+  <si>
+    <t>27.05.202628</t>
+  </si>
+  <si>
+    <t>27.05.202629</t>
+  </si>
+  <si>
+    <t>27.05.202630</t>
+  </si>
+  <si>
+    <t>27.05.202631</t>
+  </si>
+  <si>
+    <t>27.05.202632</t>
+  </si>
+  <si>
+    <t>27.05.202633</t>
+  </si>
+  <si>
+    <t>27.05.202634</t>
+  </si>
+  <si>
+    <t>27.05.202635</t>
+  </si>
+  <si>
+    <t>27.05.202636</t>
+  </si>
+  <si>
+    <t>27.05.202637</t>
+  </si>
+  <si>
+    <t>27.05.202638</t>
+  </si>
+  <si>
+    <t>27.05.202639</t>
+  </si>
+  <si>
+    <t>27.05.202640</t>
+  </si>
+  <si>
+    <t>27.05.202641</t>
+  </si>
+  <si>
+    <t>27.05.202642</t>
+  </si>
+  <si>
+    <t>27.05.202643</t>
+  </si>
+  <si>
+    <t>27.05.202644</t>
+  </si>
+  <si>
+    <t>27.05.202645</t>
+  </si>
+  <si>
+    <t>27.05.202646</t>
+  </si>
+  <si>
+    <t>27.05.202647</t>
+  </si>
+  <si>
+    <t>27.05.202648</t>
+  </si>
+  <si>
+    <t>27.05.202649</t>
+  </si>
+  <si>
+    <t>27.05.202650</t>
+  </si>
+  <si>
+    <t>27.05.202651</t>
+  </si>
+  <si>
+    <t>27.05.202652</t>
+  </si>
+  <si>
+    <t>27.05.202653</t>
+  </si>
+  <si>
+    <t>27.05.202654</t>
+  </si>
+  <si>
+    <t>27.05.202655</t>
+  </si>
+  <si>
+    <t>27.05.202656</t>
+  </si>
+  <si>
+    <t>27.05.202657</t>
+  </si>
+  <si>
+    <t>27.05.202658</t>
+  </si>
+  <si>
+    <t>27.05.202659</t>
+  </si>
+  <si>
+    <t>27.05.202660</t>
+  </si>
+  <si>
+    <t>27.05.202661</t>
+  </si>
+  <si>
+    <t>27.05.202662</t>
+  </si>
+  <si>
+    <t>27.05.202663</t>
+  </si>
+  <si>
+    <t>27.05.202664</t>
+  </si>
+  <si>
+    <t>27.05.202665</t>
+  </si>
+  <si>
+    <t>27.05.202666</t>
+  </si>
+  <si>
+    <t>27.05.202667</t>
+  </si>
+  <si>
+    <t>27.05.202668</t>
+  </si>
+  <si>
+    <t>27.05.202669</t>
+  </si>
+  <si>
+    <t>27.05.202670</t>
+  </si>
+  <si>
+    <t>27.05.202671</t>
+  </si>
+  <si>
+    <t>27.05.202672</t>
+  </si>
+  <si>
+    <t>27.05.202673</t>
+  </si>
+  <si>
+    <t>27.05.202674</t>
+  </si>
+  <si>
+    <t>27.05.202675</t>
+  </si>
+  <si>
+    <t>27.05.202676</t>
+  </si>
+  <si>
+    <t>27.05.202677</t>
+  </si>
+  <si>
+    <t>27.05.202678</t>
+  </si>
+  <si>
+    <t>27.05.202679</t>
+  </si>
+  <si>
+    <t>27.05.202680</t>
+  </si>
+  <si>
+    <t>27.05.202681</t>
+  </si>
+  <si>
+    <t>27.05.202682</t>
+  </si>
+  <si>
+    <t>27.05.202683</t>
+  </si>
+  <si>
+    <t>27.05.202684</t>
+  </si>
+  <si>
+    <t>27.05.202685</t>
+  </si>
+  <si>
+    <t>27.05.202686</t>
+  </si>
+  <si>
+    <t>27.05.202687</t>
+  </si>
+  <si>
+    <t>27.05.202688</t>
+  </si>
+  <si>
+    <t>27.05.202689</t>
+  </si>
+  <si>
+    <t>27.05.202690</t>
+  </si>
+  <si>
+    <t>27.05.202691</t>
+  </si>
+  <si>
+    <t>27.05.202692</t>
+  </si>
+  <si>
+    <t>27.05.202693</t>
+  </si>
+  <si>
+    <t>27.05.202694</t>
+  </si>
+  <si>
+    <t>27.05.202695</t>
+  </si>
+  <si>
+    <t>27.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,10 +988,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2">
-        <v>7.97</v>
+        <v>7.87</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
-        <v>7.989</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.991</v>
+        <v>7.952</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
-        <v>7.996</v>
+        <v>7.958</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
-        <v>8.4</v>
+        <v>8.786</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
-        <v>8.484999999999999</v>
+        <v>8.878</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
-        <v>8.714</v>
+        <v>9.065</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
-        <v>27.057</v>
+        <v>28.749</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
-        <v>81.357</v>
+        <v>89.514</v>
       </c>
       <c r="C22">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
-        <v>146.757</v>
+        <v>157.423</v>
       </c>
       <c r="C23">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
-        <v>209.892</v>
+        <v>239.452</v>
       </c>
       <c r="C24">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
-        <v>297.016</v>
+        <v>335.77</v>
       </c>
       <c r="C25">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
-        <v>481.292</v>
+        <v>522.255</v>
       </c>
       <c r="C26">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
-        <v>615.706</v>
+        <v>673.812</v>
       </c>
       <c r="C27">
-        <v>491</v>
+        <v>462</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
-        <v>750.925</v>
+        <v>841.54</v>
       </c>
       <c r="C28">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
-        <v>914.871</v>
+        <v>1023.07</v>
       </c>
       <c r="C29">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
-        <v>1230.68</v>
+        <v>1353.559</v>
       </c>
       <c r="C30">
-        <v>972</v>
+        <v>995</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
-        <v>1415.906</v>
+        <v>1580.965</v>
       </c>
       <c r="C31">
-        <v>1160</v>
+        <v>1198</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
-        <v>1615.361</v>
+        <v>1784.587</v>
       </c>
       <c r="C32">
-        <v>1333</v>
+        <v>1350</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
-        <v>1778.252</v>
+        <v>1987.175</v>
       </c>
       <c r="C33">
-        <v>1494</v>
+        <v>1507</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
-        <v>2131.836</v>
+        <v>2260.949</v>
       </c>
       <c r="C34">
-        <v>1607</v>
+        <v>1658</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
-        <v>2281.091</v>
+        <v>2420.112</v>
       </c>
       <c r="C35">
-        <v>1740</v>
+        <v>1787</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
-        <v>2429.636</v>
+        <v>2556.703</v>
       </c>
       <c r="C36">
-        <v>1869</v>
+        <v>1886</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
-        <v>2551.979</v>
+        <v>2718.243</v>
       </c>
       <c r="C37">
-        <v>1991</v>
+        <v>1979</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>2706.66</v>
+        <v>2875.139</v>
       </c>
       <c r="C38">
-        <v>2075</v>
+        <v>2068</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>2805.345</v>
+        <v>2973.236</v>
       </c>
       <c r="C39">
-        <v>2125</v>
+        <v>2148</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
-        <v>2757.352</v>
+        <v>3057.101</v>
       </c>
       <c r="C40">
-        <v>2009</v>
+        <v>2216</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
-        <v>2715.633</v>
+        <v>3115.047</v>
       </c>
       <c r="C41">
-        <v>1909</v>
+        <v>2286</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
-        <v>2871.262</v>
+        <v>3204.576</v>
       </c>
       <c r="C42">
-        <v>2066</v>
+        <v>2305</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
-        <v>2947.675</v>
+        <v>3243.867</v>
       </c>
       <c r="C43">
-        <v>2204</v>
+        <v>2255</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
-        <v>3001.965</v>
+        <v>3134.936</v>
       </c>
       <c r="C44">
-        <v>2220</v>
+        <v>2257</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
-        <v>3023.773</v>
+        <v>3158.683</v>
       </c>
       <c r="C45">
-        <v>2194</v>
+        <v>2287</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
-        <v>3183.57</v>
+        <v>3141.778</v>
       </c>
       <c r="C46">
-        <v>2165</v>
+        <v>2176</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
-        <v>3186.279</v>
+        <v>3135.428</v>
       </c>
       <c r="C47">
-        <v>2236</v>
+        <v>2173</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
-        <v>3178.579</v>
+        <v>3152.79</v>
       </c>
       <c r="C48">
-        <v>2273</v>
+        <v>2188</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
-        <v>3183.472</v>
+        <v>3160.546</v>
       </c>
       <c r="C49">
-        <v>2303</v>
+        <v>2149</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
-        <v>3156.447</v>
+        <v>3149.736</v>
       </c>
       <c r="C50">
-        <v>2170</v>
+        <v>2184</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
-        <v>3141.34</v>
+        <v>3132.293</v>
       </c>
       <c r="C51">
-        <v>2211</v>
+        <v>2174</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
-        <v>3134.151</v>
+        <v>3105.786</v>
       </c>
       <c r="C52">
-        <v>2256</v>
+        <v>2214</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
-        <v>3107.738</v>
+        <v>3089.85</v>
       </c>
       <c r="C53">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
-        <v>2927.537</v>
+        <v>3108.061</v>
       </c>
       <c r="C54">
-        <v>2026</v>
+        <v>2156</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
-        <v>2902.83</v>
+        <v>3081.405</v>
       </c>
       <c r="C55">
-        <v>1989</v>
+        <v>2184</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
-        <v>2867.83</v>
+        <v>3074.369</v>
       </c>
       <c r="C56">
-        <v>2143</v>
+        <v>2201</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
-        <v>2933.707</v>
+        <v>3037.281</v>
       </c>
       <c r="C57">
-        <v>2173</v>
+        <v>2236</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
-        <v>2848.184</v>
+        <v>2959.662</v>
       </c>
       <c r="C58">
-        <v>2094</v>
+        <v>2200</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
-        <v>2786.226</v>
+        <v>2953.03</v>
       </c>
       <c r="C59">
-        <v>2073</v>
+        <v>2161</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
-        <v>2706.109</v>
+        <v>2912.616</v>
       </c>
       <c r="C60">
-        <v>2046</v>
+        <v>2142</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
-        <v>2603.284</v>
+        <v>2804.396</v>
       </c>
       <c r="C61">
-        <v>1866</v>
+        <v>2113</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
-        <v>2432.361</v>
+        <v>2668.647</v>
       </c>
       <c r="C62">
-        <v>1704</v>
+        <v>2014</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
-        <v>2306.375</v>
+        <v>2569.178</v>
       </c>
       <c r="C63">
-        <v>1629</v>
+        <v>1959</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
-        <v>2192.969</v>
+        <v>2473.643</v>
       </c>
       <c r="C64">
-        <v>1689</v>
+        <v>1905</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
-        <v>2074.904</v>
+        <v>2395.685</v>
       </c>
       <c r="C65">
-        <v>1653</v>
+        <v>1858</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
-        <v>1840.863</v>
+        <v>2205.756</v>
       </c>
       <c r="C66">
-        <v>1525</v>
+        <v>1754</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
-        <v>1671.148</v>
+        <v>2161.985</v>
       </c>
       <c r="C67">
-        <v>1453</v>
+        <v>1740</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
-        <v>1500.546</v>
+        <v>2004.187</v>
       </c>
       <c r="C68">
-        <v>1356</v>
+        <v>1633</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
-        <v>1350.273</v>
+        <v>1820.157</v>
       </c>
       <c r="C69">
-        <v>1249</v>
+        <v>1499</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
-        <v>1079.014</v>
+        <v>1482.459</v>
       </c>
       <c r="C70">
-        <v>1081</v>
+        <v>1316</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
-        <v>944.069</v>
+        <v>1287.788</v>
       </c>
       <c r="C71">
-        <v>921</v>
+        <v>1131</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
-        <v>801.301</v>
+        <v>1069.479</v>
       </c>
       <c r="C72">
-        <v>770</v>
+        <v>942</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
-        <v>665.01</v>
+        <v>883.658</v>
       </c>
       <c r="C73">
-        <v>645</v>
+        <v>779</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
-        <v>449.784</v>
+        <v>622.0069999999999</v>
       </c>
       <c r="C74">
-        <v>512</v>
+        <v>603</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
-        <v>349.155</v>
+        <v>491.61</v>
       </c>
       <c r="C75">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
-        <v>261.816</v>
+        <v>359.652</v>
       </c>
       <c r="C76">
         <v>289</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
-        <v>195.335</v>
+        <v>260.047</v>
       </c>
       <c r="C77">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
-        <v>105.112</v>
+        <v>148.311</v>
       </c>
       <c r="C78">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
-        <v>64.839</v>
+        <v>91.15300000000001</v>
       </c>
       <c r="C79">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
-        <v>38.95</v>
+        <v>53.839</v>
       </c>
       <c r="C80">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
-        <v>34.969</v>
+        <v>40.692</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
-        <v>22.061</v>
+        <v>27.211</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
-        <v>20.108</v>
+        <v>25.434</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
-        <v>20.779</v>
+        <v>24.568</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
-        <v>20.265</v>
+        <v>23.349</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
-        <v>19.672</v>
+        <v>23.77</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
-        <v>11.772</v>
+        <v>16.87</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
-        <v>6.272</v>
+        <v>11.17</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
-        <v>5.872</v>
+        <v>3.57</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
         <v>10.77</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
-        <v>2.27</v>
+        <v>1.37</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.87</v>
+        <v>1.87</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B98">
-        <v>7.87</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>7.87</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B101">
-        <v>7.95</v>
+        <v>7.92</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.952</v>
+        <v>7.922</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B113">
-        <v>7.958</v>
+        <v>7.928</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B114">
-        <v>8.786</v>
+        <v>9.065</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B115">
-        <v>8.878</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B116">
-        <v>9.065</v>
+        <v>9.423999999999999</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B117">
-        <v>28.749</v>
+        <v>30.475</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B118">
-        <v>89.514</v>
+        <v>99.221</v>
       </c>
       <c r="C118">
         <v>29</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B119">
-        <v>157.423</v>
+        <v>171.97</v>
       </c>
       <c r="C119">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B120">
-        <v>239.452</v>
+        <v>254.944</v>
       </c>
       <c r="C120">
         <v>149</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B121">
-        <v>335.77</v>
+        <v>355.089</v>
       </c>
       <c r="C121">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B122">
-        <v>522.255</v>
+        <v>555.944</v>
       </c>
       <c r="C122">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B123">
-        <v>673.812</v>
+        <v>709.098</v>
       </c>
       <c r="C123">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B124">
-        <v>841.54</v>
+        <v>875.087</v>
       </c>
       <c r="C124">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B125">
-        <v>1023.07</v>
+        <v>1052.844</v>
       </c>
       <c r="C125">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B126">
-        <v>1353.559</v>
+        <v>1427.303</v>
       </c>
       <c r="C126">
-        <v>995</v>
+        <v>967</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B127">
-        <v>1580.965</v>
+        <v>1647.032</v>
       </c>
       <c r="C127">
-        <v>1198</v>
+        <v>1152</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B128">
-        <v>1784.587</v>
+        <v>1853.951</v>
       </c>
       <c r="C128">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B129">
-        <v>1987.175</v>
+        <v>2040.751</v>
       </c>
       <c r="C129">
-        <v>1507</v>
+        <v>1464</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B130">
-        <v>2260.949</v>
+        <v>2324.916</v>
       </c>
       <c r="C130">
-        <v>1658</v>
+        <v>1605</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B131">
-        <v>2420.112</v>
+        <v>2482.684</v>
       </c>
       <c r="C131">
-        <v>1787</v>
+        <v>1733</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B132">
-        <v>2556.703</v>
+        <v>2619.925</v>
       </c>
       <c r="C132">
-        <v>1886</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B133">
-        <v>2718.243</v>
+        <v>2803.273</v>
       </c>
       <c r="C133">
-        <v>1979</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B134">
-        <v>2875.139</v>
+        <v>2988.39</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B135">
-        <v>2973.236</v>
+        <v>3090.509</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B136">
-        <v>3057.101</v>
+        <v>3168.016</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B137">
-        <v>3115.047</v>
+        <v>3224.202</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B138">
-        <v>3204.576</v>
+        <v>3347.391</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B139">
-        <v>3243.867</v>
+        <v>3396.716</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B140">
-        <v>3134.936</v>
+        <v>3442.498</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B141">
-        <v>3158.683</v>
+        <v>3475.83</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B142">
-        <v>3141.778</v>
+        <v>3472.486</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B143">
-        <v>3135.428</v>
+        <v>3484.207</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B144">
-        <v>3152.79</v>
+        <v>3487.549</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B145">
-        <v>3160.546</v>
+        <v>3490.593</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B146">
-        <v>3149.736</v>
+        <v>3485.279</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B147">
-        <v>3132.293</v>
+        <v>3479.6</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B148">
-        <v>3105.786</v>
+        <v>3467.177</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B149">
-        <v>3089.85</v>
+        <v>3449.344</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B150">
-        <v>3108.061</v>
+        <v>3425.535</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B151">
-        <v>3081.405</v>
+        <v>3397.156</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B152">
-        <v>3074.369</v>
+        <v>3355.908</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B153">
-        <v>3037.281</v>
+        <v>3315.174</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B154">
-        <v>2959.662</v>
+        <v>3252.191</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B155">
-        <v>2953.03</v>
+        <v>3196.288</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B156">
-        <v>2912.616</v>
+        <v>3141.417</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B157">
-        <v>2804.396</v>
+        <v>3058.855</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B158">
-        <v>2668.647</v>
+        <v>2888.378</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B159">
-        <v>2569.178</v>
+        <v>2801.108</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B160">
-        <v>2473.643</v>
+        <v>2650.463</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B161">
-        <v>2395.685</v>
+        <v>2552.294</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B162">
-        <v>2205.756</v>
+        <v>2311.334</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B163">
-        <v>2161.985</v>
+        <v>2134.496</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B164">
-        <v>2004.187</v>
+        <v>1964.452</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B165">
-        <v>1820.157</v>
+        <v>1773.02</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B166">
-        <v>1482.459</v>
+        <v>1464.086</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B167">
-        <v>1287.788</v>
+        <v>1263.8</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B168">
-        <v>1069.479</v>
+        <v>1073.597</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B169">
-        <v>883.658</v>
+        <v>898.822</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B170">
-        <v>622.0069999999999</v>
+        <v>610.1660000000001</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B171">
-        <v>491.61</v>
+        <v>472.775</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B172">
-        <v>359.652</v>
+        <v>355.97</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B173">
-        <v>260.047</v>
+        <v>269.501</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B174">
-        <v>148.311</v>
+        <v>148.147</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B175">
-        <v>91.15300000000001</v>
+        <v>90.982</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B176">
-        <v>53.839</v>
+        <v>53.969</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B177">
-        <v>40.692</v>
+        <v>40.572</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B178">
-        <v>27.211</v>
+        <v>21.882</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B179">
-        <v>25.434</v>
+        <v>21.164</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B180">
-        <v>24.568</v>
+        <v>18.942</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B181">
-        <v>23.349</v>
+        <v>17.878</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B182">
-        <v>23.77</v>
+        <v>17.27</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B183">
         <v>16.87</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B184">
-        <v>11.17</v>
+        <v>13.77</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B185">
-        <v>3.57</v>
+        <v>8.27</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B186">
-        <v>10.77</v>
+        <v>13.37</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B187">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>26.05.20261</t>
-  </si>
-  <si>
-    <t>26.05.20262</t>
-  </si>
-  <si>
-    <t>26.05.20263</t>
-  </si>
-  <si>
-    <t>26.05.20264</t>
-  </si>
-  <si>
-    <t>26.05.20265</t>
-  </si>
-  <si>
-    <t>26.05.20266</t>
-  </si>
-  <si>
-    <t>26.05.20267</t>
-  </si>
-  <si>
-    <t>26.05.20268</t>
-  </si>
-  <si>
-    <t>26.05.20269</t>
-  </si>
-  <si>
-    <t>26.05.202610</t>
-  </si>
-  <si>
-    <t>26.05.202611</t>
-  </si>
-  <si>
-    <t>26.05.202612</t>
-  </si>
-  <si>
-    <t>26.05.202613</t>
-  </si>
-  <si>
-    <t>26.05.202614</t>
-  </si>
-  <si>
-    <t>26.05.202615</t>
-  </si>
-  <si>
-    <t>26.05.202616</t>
-  </si>
-  <si>
-    <t>26.05.202617</t>
-  </si>
-  <si>
-    <t>26.05.202618</t>
-  </si>
-  <si>
-    <t>26.05.202619</t>
-  </si>
-  <si>
-    <t>26.05.202620</t>
-  </si>
-  <si>
-    <t>26.05.202621</t>
-  </si>
-  <si>
-    <t>26.05.202622</t>
-  </si>
-  <si>
-    <t>26.05.202623</t>
-  </si>
-  <si>
-    <t>26.05.202624</t>
-  </si>
-  <si>
-    <t>26.05.202625</t>
-  </si>
-  <si>
-    <t>26.05.202626</t>
-  </si>
-  <si>
-    <t>26.05.202627</t>
-  </si>
-  <si>
-    <t>26.05.202628</t>
-  </si>
-  <si>
-    <t>26.05.202629</t>
-  </si>
-  <si>
-    <t>26.05.202630</t>
-  </si>
-  <si>
-    <t>26.05.202631</t>
-  </si>
-  <si>
-    <t>26.05.202632</t>
-  </si>
-  <si>
-    <t>26.05.202633</t>
-  </si>
-  <si>
-    <t>26.05.202634</t>
-  </si>
-  <si>
-    <t>26.05.202635</t>
-  </si>
-  <si>
-    <t>26.05.202636</t>
-  </si>
-  <si>
-    <t>26.05.202637</t>
-  </si>
-  <si>
-    <t>26.05.202638</t>
-  </si>
-  <si>
-    <t>26.05.202639</t>
-  </si>
-  <si>
-    <t>26.05.202640</t>
-  </si>
-  <si>
-    <t>26.05.202641</t>
-  </si>
-  <si>
-    <t>26.05.202642</t>
-  </si>
-  <si>
-    <t>26.05.202643</t>
-  </si>
-  <si>
-    <t>26.05.202644</t>
-  </si>
-  <si>
-    <t>26.05.202645</t>
-  </si>
-  <si>
-    <t>26.05.202646</t>
-  </si>
-  <si>
-    <t>26.05.202647</t>
-  </si>
-  <si>
-    <t>26.05.202648</t>
-  </si>
-  <si>
-    <t>26.05.202649</t>
-  </si>
-  <si>
-    <t>26.05.202650</t>
-  </si>
-  <si>
-    <t>26.05.202651</t>
-  </si>
-  <si>
-    <t>26.05.202652</t>
-  </si>
-  <si>
-    <t>26.05.202653</t>
-  </si>
-  <si>
-    <t>26.05.202654</t>
-  </si>
-  <si>
-    <t>26.05.202655</t>
-  </si>
-  <si>
-    <t>26.05.202656</t>
-  </si>
-  <si>
-    <t>26.05.202657</t>
-  </si>
-  <si>
-    <t>26.05.202658</t>
-  </si>
-  <si>
-    <t>26.05.202659</t>
-  </si>
-  <si>
-    <t>26.05.202660</t>
-  </si>
-  <si>
-    <t>26.05.202661</t>
-  </si>
-  <si>
-    <t>26.05.202662</t>
-  </si>
-  <si>
-    <t>26.05.202663</t>
-  </si>
-  <si>
-    <t>26.05.202664</t>
-  </si>
-  <si>
-    <t>26.05.202665</t>
-  </si>
-  <si>
-    <t>26.05.202666</t>
-  </si>
-  <si>
-    <t>26.05.202667</t>
-  </si>
-  <si>
-    <t>26.05.202668</t>
-  </si>
-  <si>
-    <t>26.05.202669</t>
-  </si>
-  <si>
-    <t>26.05.202670</t>
-  </si>
-  <si>
-    <t>26.05.202671</t>
-  </si>
-  <si>
-    <t>26.05.202672</t>
-  </si>
-  <si>
-    <t>26.05.202673</t>
-  </si>
-  <si>
-    <t>26.05.202674</t>
-  </si>
-  <si>
-    <t>26.05.202675</t>
-  </si>
-  <si>
-    <t>26.05.202676</t>
-  </si>
-  <si>
-    <t>26.05.202677</t>
-  </si>
-  <si>
-    <t>26.05.202678</t>
-  </si>
-  <si>
-    <t>26.05.202679</t>
-  </si>
-  <si>
-    <t>26.05.202680</t>
-  </si>
-  <si>
-    <t>26.05.202681</t>
-  </si>
-  <si>
-    <t>26.05.202682</t>
-  </si>
-  <si>
-    <t>26.05.202683</t>
-  </si>
-  <si>
-    <t>26.05.202684</t>
-  </si>
-  <si>
-    <t>26.05.202685</t>
-  </si>
-  <si>
-    <t>26.05.202686</t>
-  </si>
-  <si>
-    <t>26.05.202687</t>
-  </si>
-  <si>
-    <t>26.05.202688</t>
-  </si>
-  <si>
-    <t>26.05.202689</t>
-  </si>
-  <si>
-    <t>26.05.202690</t>
-  </si>
-  <si>
-    <t>26.05.202691</t>
-  </si>
-  <si>
-    <t>26.05.202692</t>
-  </si>
-  <si>
-    <t>26.05.202693</t>
-  </si>
-  <si>
-    <t>26.05.202694</t>
-  </si>
-  <si>
-    <t>26.05.202695</t>
-  </si>
-  <si>
-    <t>26.05.202696</t>
-  </si>
-  <si>
     <t>27.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>27.05.202696</t>
+  </si>
+  <si>
+    <t>28.05.20261</t>
+  </si>
+  <si>
+    <t>28.05.20262</t>
+  </si>
+  <si>
+    <t>28.05.20263</t>
+  </si>
+  <si>
+    <t>28.05.20264</t>
+  </si>
+  <si>
+    <t>28.05.20265</t>
+  </si>
+  <si>
+    <t>28.05.20266</t>
+  </si>
+  <si>
+    <t>28.05.20267</t>
+  </si>
+  <si>
+    <t>28.05.20268</t>
+  </si>
+  <si>
+    <t>28.05.20269</t>
+  </si>
+  <si>
+    <t>28.05.202610</t>
+  </si>
+  <si>
+    <t>28.05.202611</t>
+  </si>
+  <si>
+    <t>28.05.202612</t>
+  </si>
+  <si>
+    <t>28.05.202613</t>
+  </si>
+  <si>
+    <t>28.05.202614</t>
+  </si>
+  <si>
+    <t>28.05.202615</t>
+  </si>
+  <si>
+    <t>28.05.202616</t>
+  </si>
+  <si>
+    <t>28.05.202617</t>
+  </si>
+  <si>
+    <t>28.05.202618</t>
+  </si>
+  <si>
+    <t>28.05.202619</t>
+  </si>
+  <si>
+    <t>28.05.202620</t>
+  </si>
+  <si>
+    <t>28.05.202621</t>
+  </si>
+  <si>
+    <t>28.05.202622</t>
+  </si>
+  <si>
+    <t>28.05.202623</t>
+  </si>
+  <si>
+    <t>28.05.202624</t>
+  </si>
+  <si>
+    <t>28.05.202625</t>
+  </si>
+  <si>
+    <t>28.05.202626</t>
+  </si>
+  <si>
+    <t>28.05.202627</t>
+  </si>
+  <si>
+    <t>28.05.202628</t>
+  </si>
+  <si>
+    <t>28.05.202629</t>
+  </si>
+  <si>
+    <t>28.05.202630</t>
+  </si>
+  <si>
+    <t>28.05.202631</t>
+  </si>
+  <si>
+    <t>28.05.202632</t>
+  </si>
+  <si>
+    <t>28.05.202633</t>
+  </si>
+  <si>
+    <t>28.05.202634</t>
+  </si>
+  <si>
+    <t>28.05.202635</t>
+  </si>
+  <si>
+    <t>28.05.202636</t>
+  </si>
+  <si>
+    <t>28.05.202637</t>
+  </si>
+  <si>
+    <t>28.05.202638</t>
+  </si>
+  <si>
+    <t>28.05.202639</t>
+  </si>
+  <si>
+    <t>28.05.202640</t>
+  </si>
+  <si>
+    <t>28.05.202641</t>
+  </si>
+  <si>
+    <t>28.05.202642</t>
+  </si>
+  <si>
+    <t>28.05.202643</t>
+  </si>
+  <si>
+    <t>28.05.202644</t>
+  </si>
+  <si>
+    <t>28.05.202645</t>
+  </si>
+  <si>
+    <t>28.05.202646</t>
+  </si>
+  <si>
+    <t>28.05.202647</t>
+  </si>
+  <si>
+    <t>28.05.202648</t>
+  </si>
+  <si>
+    <t>28.05.202649</t>
+  </si>
+  <si>
+    <t>28.05.202650</t>
+  </si>
+  <si>
+    <t>28.05.202651</t>
+  </si>
+  <si>
+    <t>28.05.202652</t>
+  </si>
+  <si>
+    <t>28.05.202653</t>
+  </si>
+  <si>
+    <t>28.05.202654</t>
+  </si>
+  <si>
+    <t>28.05.202655</t>
+  </si>
+  <si>
+    <t>28.05.202656</t>
+  </si>
+  <si>
+    <t>28.05.202657</t>
+  </si>
+  <si>
+    <t>28.05.202658</t>
+  </si>
+  <si>
+    <t>28.05.202659</t>
+  </si>
+  <si>
+    <t>28.05.202660</t>
+  </si>
+  <si>
+    <t>28.05.202661</t>
+  </si>
+  <si>
+    <t>28.05.202662</t>
+  </si>
+  <si>
+    <t>28.05.202663</t>
+  </si>
+  <si>
+    <t>28.05.202664</t>
+  </si>
+  <si>
+    <t>28.05.202665</t>
+  </si>
+  <si>
+    <t>28.05.202666</t>
+  </si>
+  <si>
+    <t>28.05.202667</t>
+  </si>
+  <si>
+    <t>28.05.202668</t>
+  </si>
+  <si>
+    <t>28.05.202669</t>
+  </si>
+  <si>
+    <t>28.05.202670</t>
+  </si>
+  <si>
+    <t>28.05.202671</t>
+  </si>
+  <si>
+    <t>28.05.202672</t>
+  </si>
+  <si>
+    <t>28.05.202673</t>
+  </si>
+  <si>
+    <t>28.05.202674</t>
+  </si>
+  <si>
+    <t>28.05.202675</t>
+  </si>
+  <si>
+    <t>28.05.202676</t>
+  </si>
+  <si>
+    <t>28.05.202677</t>
+  </si>
+  <si>
+    <t>28.05.202678</t>
+  </si>
+  <si>
+    <t>28.05.202679</t>
+  </si>
+  <si>
+    <t>28.05.202680</t>
+  </si>
+  <si>
+    <t>28.05.202681</t>
+  </si>
+  <si>
+    <t>28.05.202682</t>
+  </si>
+  <si>
+    <t>28.05.202683</t>
+  </si>
+  <si>
+    <t>28.05.202684</t>
+  </si>
+  <si>
+    <t>28.05.202685</t>
+  </si>
+  <si>
+    <t>28.05.202686</t>
+  </si>
+  <si>
+    <t>28.05.202687</t>
+  </si>
+  <si>
+    <t>28.05.202688</t>
+  </si>
+  <si>
+    <t>28.05.202689</t>
+  </si>
+  <si>
+    <t>28.05.202690</t>
+  </si>
+  <si>
+    <t>28.05.202691</t>
+  </si>
+  <si>
+    <t>28.05.202692</t>
+  </si>
+  <si>
+    <t>28.05.202693</t>
+  </si>
+  <si>
+    <t>28.05.202694</t>
+  </si>
+  <si>
+    <t>28.05.202695</t>
+  </si>
+  <si>
+    <t>28.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,10 +988,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
-        <v>7.87</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>7.87</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
-        <v>7.95</v>
+        <v>7.92</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.952</v>
+        <v>7.922</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
-        <v>7.958</v>
+        <v>7.928</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
-        <v>8.786</v>
+        <v>9.065</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
-        <v>8.878</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
-        <v>9.065</v>
+        <v>9.423999999999999</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>28.749</v>
+        <v>30.475</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
-        <v>89.514</v>
+        <v>99.221</v>
       </c>
       <c r="C22">
         <v>29</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>157.423</v>
+        <v>171.97</v>
       </c>
       <c r="C23">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
-        <v>239.452</v>
+        <v>254.944</v>
       </c>
       <c r="C24">
         <v>149</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>335.77</v>
+        <v>355.089</v>
       </c>
       <c r="C25">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>522.255</v>
+        <v>555.944</v>
       </c>
       <c r="C26">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>673.812</v>
+        <v>709.098</v>
       </c>
       <c r="C27">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>841.54</v>
+        <v>875.087</v>
       </c>
       <c r="C28">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>1023.07</v>
+        <v>1052.844</v>
       </c>
       <c r="C29">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>1353.559</v>
+        <v>1427.303</v>
       </c>
       <c r="C30">
-        <v>995</v>
+        <v>967</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>1580.965</v>
+        <v>1647.032</v>
       </c>
       <c r="C31">
-        <v>1198</v>
+        <v>1152</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>1784.587</v>
+        <v>1853.951</v>
       </c>
       <c r="C32">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>1987.175</v>
+        <v>2040.751</v>
       </c>
       <c r="C33">
-        <v>1507</v>
+        <v>1464</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>2260.949</v>
+        <v>2324.916</v>
       </c>
       <c r="C34">
-        <v>1658</v>
+        <v>1605</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>2420.112</v>
+        <v>2482.684</v>
       </c>
       <c r="C35">
-        <v>1787</v>
+        <v>1733</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>2556.703</v>
+        <v>2619.925</v>
       </c>
       <c r="C36">
-        <v>1886</v>
+        <v>1844</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>2718.243</v>
+        <v>2803.273</v>
       </c>
       <c r="C37">
-        <v>1979</v>
+        <v>1933</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>2875.139</v>
+        <v>2988.39</v>
       </c>
       <c r="C38">
-        <v>2068</v>
+        <v>2014</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>2973.236</v>
+        <v>3090.509</v>
       </c>
       <c r="C39">
-        <v>2148</v>
+        <v>2100</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>3057.101</v>
+        <v>3168.016</v>
       </c>
       <c r="C40">
-        <v>2216</v>
+        <v>2174</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>3115.047</v>
+        <v>3224.202</v>
       </c>
       <c r="C41">
-        <v>2286</v>
+        <v>2209</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>3204.576</v>
+        <v>3347.391</v>
       </c>
       <c r="C42">
-        <v>2305</v>
+        <v>2256</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>3243.867</v>
+        <v>3396.716</v>
       </c>
       <c r="C43">
-        <v>2255</v>
+        <v>2300</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>3134.936</v>
+        <v>3442.498</v>
       </c>
       <c r="C44">
-        <v>2257</v>
+        <v>2303</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
-        <v>3158.683</v>
+        <v>3475.83</v>
       </c>
       <c r="C45">
-        <v>2287</v>
+        <v>2351</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
-        <v>3141.778</v>
+        <v>3472.486</v>
       </c>
       <c r="C46">
-        <v>2176</v>
+        <v>2371</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
-        <v>3135.428</v>
+        <v>3484.207</v>
       </c>
       <c r="C47">
-        <v>2173</v>
+        <v>2434</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>3152.79</v>
+        <v>3487.549</v>
       </c>
       <c r="C48">
-        <v>2188</v>
+        <v>2425</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>3160.546</v>
+        <v>3490.593</v>
       </c>
       <c r="C49">
-        <v>2149</v>
+        <v>2414</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>3149.736</v>
+        <v>3485.279</v>
       </c>
       <c r="C50">
-        <v>2184</v>
+        <v>2482</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
-        <v>3132.293</v>
+        <v>3479.6</v>
       </c>
       <c r="C51">
-        <v>2174</v>
+        <v>2492</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>3105.786</v>
+        <v>3467.177</v>
       </c>
       <c r="C52">
-        <v>2214</v>
+        <v>2479</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
-        <v>3089.85</v>
+        <v>3449.344</v>
       </c>
       <c r="C53">
-        <v>2212</v>
+        <v>2475</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>3108.061</v>
+        <v>3425.535</v>
       </c>
       <c r="C54">
-        <v>2156</v>
+        <v>2424</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>3081.405</v>
+        <v>3397.156</v>
       </c>
       <c r="C55">
-        <v>2184</v>
+        <v>2401</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>3074.369</v>
+        <v>3355.908</v>
       </c>
       <c r="C56">
-        <v>2201</v>
+        <v>2379</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>3037.281</v>
+        <v>3315.174</v>
       </c>
       <c r="C57">
-        <v>2236</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>2959.662</v>
+        <v>3252.191</v>
       </c>
       <c r="C58">
-        <v>2200</v>
+        <v>2398</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>2953.03</v>
+        <v>3196.288</v>
       </c>
       <c r="C59">
-        <v>2161</v>
+        <v>2371</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>2912.616</v>
+        <v>3141.417</v>
       </c>
       <c r="C60">
-        <v>2142</v>
+        <v>2328</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>2804.396</v>
+        <v>3058.855</v>
       </c>
       <c r="C61">
-        <v>2113</v>
+        <v>2302</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>2668.647</v>
+        <v>2888.378</v>
       </c>
       <c r="C62">
-        <v>2014</v>
+        <v>2199</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>2569.178</v>
+        <v>2801.108</v>
       </c>
       <c r="C63">
-        <v>1959</v>
+        <v>2115</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>2473.643</v>
+        <v>2650.463</v>
       </c>
       <c r="C64">
-        <v>1905</v>
+        <v>2031</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>2395.685</v>
+        <v>2552.294</v>
       </c>
       <c r="C65">
-        <v>1858</v>
+        <v>1959</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>2205.756</v>
+        <v>2311.334</v>
       </c>
       <c r="C66">
-        <v>1754</v>
+        <v>1824</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>2161.985</v>
+        <v>2134.496</v>
       </c>
       <c r="C67">
-        <v>1740</v>
+        <v>1692</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>2004.187</v>
+        <v>1964.452</v>
       </c>
       <c r="C68">
-        <v>1633</v>
+        <v>1549</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>1820.157</v>
+        <v>1773.02</v>
       </c>
       <c r="C69">
-        <v>1499</v>
+        <v>1409</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>1482.459</v>
+        <v>1464.086</v>
       </c>
       <c r="C70">
-        <v>1316</v>
+        <v>1244</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>1287.788</v>
+        <v>1263.8</v>
       </c>
       <c r="C71">
-        <v>1131</v>
+        <v>1077</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>1069.479</v>
+        <v>1073.597</v>
       </c>
       <c r="C72">
-        <v>942</v>
+        <v>863</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>883.658</v>
+        <v>898.822</v>
       </c>
       <c r="C73">
-        <v>779</v>
+        <v>702</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>622.0069999999999</v>
+        <v>610.1660000000001</v>
       </c>
       <c r="C74">
-        <v>603</v>
+        <v>533</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>491.61</v>
+        <v>472.775</v>
       </c>
       <c r="C75">
-        <v>440</v>
+        <v>398</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>359.652</v>
+        <v>355.97</v>
       </c>
       <c r="C76">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>260.047</v>
+        <v>269.501</v>
       </c>
       <c r="C77">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>148.311</v>
+        <v>148.147</v>
       </c>
       <c r="C78">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>91.15300000000001</v>
+        <v>90.982</v>
       </c>
       <c r="C79">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>53.839</v>
+        <v>53.969</v>
       </c>
       <c r="C80">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>40.692</v>
+        <v>40.572</v>
       </c>
       <c r="C81">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>27.211</v>
+        <v>21.882</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
-        <v>25.434</v>
+        <v>21.164</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
-        <v>24.568</v>
+        <v>18.942</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
-        <v>23.349</v>
+        <v>17.878</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
-        <v>23.77</v>
+        <v>17.27</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
         <v>16.87</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
-        <v>11.17</v>
+        <v>13.77</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
-        <v>3.57</v>
+        <v>8.27</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
-        <v>10.77</v>
+        <v>13.37</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.87</v>
+        <v>0.87</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
-        <v>8.869999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B99">
-        <v>7.87</v>
+        <v>0</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B101">
-        <v>7.92</v>
+        <v>0</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>7.67</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.922</v>
+        <v>7.672</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B113">
-        <v>7.928</v>
+        <v>7.678</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B114">
-        <v>9.065</v>
+        <v>8.295</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B115">
-        <v>9.148999999999999</v>
+        <v>9.587</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B116">
-        <v>9.423999999999999</v>
+        <v>9.722</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B117">
-        <v>30.475</v>
+        <v>24.965</v>
       </c>
       <c r="C117">
         <v>2</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B118">
-        <v>99.221</v>
+        <v>80.745</v>
       </c>
       <c r="C118">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B119">
-        <v>171.97</v>
+        <v>141.739</v>
       </c>
       <c r="C119">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B120">
-        <v>254.944</v>
+        <v>209.019</v>
       </c>
       <c r="C120">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B121">
-        <v>355.089</v>
+        <v>289.879</v>
       </c>
       <c r="C121">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B122">
-        <v>555.944</v>
+        <v>472.061</v>
       </c>
       <c r="C122">
-        <v>338</v>
+        <v>287</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B123">
-        <v>709.098</v>
+        <v>612.024</v>
       </c>
       <c r="C123">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B124">
-        <v>875.087</v>
+        <v>756.615</v>
       </c>
       <c r="C124">
-        <v>625</v>
+        <v>596</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B125">
-        <v>1052.844</v>
+        <v>926.422</v>
       </c>
       <c r="C125">
-        <v>794</v>
+        <v>750</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B126">
-        <v>1427.303</v>
+        <v>1235.928</v>
       </c>
       <c r="C126">
-        <v>967</v>
+        <v>917</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B127">
-        <v>1647.032</v>
+        <v>1410.091</v>
       </c>
       <c r="C127">
-        <v>1152</v>
+        <v>1075</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B128">
-        <v>1853.951</v>
+        <v>1575.173</v>
       </c>
       <c r="C128">
-        <v>1300</v>
+        <v>1172</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B129">
-        <v>2040.751</v>
+        <v>1743.182</v>
       </c>
       <c r="C129">
-        <v>1464</v>
+        <v>1289</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B130">
-        <v>2324.916</v>
+        <v>1971.031</v>
       </c>
       <c r="C130">
-        <v>1605</v>
+        <v>1431</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B131">
-        <v>2482.684</v>
+        <v>2113.921</v>
       </c>
       <c r="C131">
-        <v>1733</v>
+        <v>1552</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B132">
-        <v>2619.925</v>
+        <v>2232.892</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1678</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B133">
-        <v>2803.273</v>
+        <v>2362.386</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B134">
-        <v>2988.39</v>
+        <v>2552.391</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B135">
-        <v>3090.509</v>
+        <v>2637.633</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B136">
-        <v>3168.016</v>
+        <v>2703.518</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B137">
-        <v>3224.202</v>
+        <v>2762.636</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B138">
-        <v>3347.391</v>
+        <v>2845.166</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B139">
-        <v>3396.716</v>
+        <v>2889.952</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B140">
-        <v>3442.498</v>
+        <v>2929.939</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B141">
-        <v>3475.83</v>
+        <v>2948.98</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B142">
-        <v>3472.486</v>
+        <v>2933.221</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B143">
-        <v>3484.207</v>
+        <v>2946.715</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B144">
-        <v>3487.549</v>
+        <v>2812.622</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B145">
-        <v>3490.593</v>
+        <v>2785.666</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B146">
-        <v>3485.279</v>
+        <v>2863.063</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B147">
-        <v>3479.6</v>
+        <v>2818.961</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B148">
-        <v>3467.177</v>
+        <v>2805.208</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B149">
-        <v>3449.344</v>
+        <v>2793.022</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B150">
-        <v>3425.535</v>
+        <v>2772.229</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B151">
-        <v>3397.156</v>
+        <v>2742.144</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B152">
-        <v>3355.908</v>
+        <v>2668.429</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B153">
-        <v>3315.174</v>
+        <v>2644.701</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B154">
-        <v>3252.191</v>
+        <v>2588.451</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B155">
-        <v>3196.288</v>
+        <v>2551.748</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B156">
-        <v>3141.417</v>
+        <v>2510.113</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B157">
-        <v>3058.855</v>
+        <v>2481.585</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B158">
-        <v>2888.378</v>
+        <v>2327.175</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B159">
-        <v>2801.108</v>
+        <v>2251.329</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B160">
-        <v>2650.463</v>
+        <v>2253.8</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B161">
-        <v>2552.294</v>
+        <v>2164.79</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B162">
-        <v>2311.334</v>
+        <v>1955.871</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B163">
-        <v>2134.496</v>
+        <v>1844.956</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B164">
-        <v>1964.452</v>
+        <v>1699.818</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B165">
-        <v>1773.02</v>
+        <v>1557.991</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B166">
-        <v>1464.086</v>
+        <v>1295.946</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B167">
-        <v>1263.8</v>
+        <v>1141.974</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B168">
-        <v>1073.597</v>
+        <v>978.022</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B169">
-        <v>898.822</v>
+        <v>817.2670000000001</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B170">
-        <v>610.1660000000001</v>
+        <v>554.426</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B171">
-        <v>472.775</v>
+        <v>431.278</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B172">
-        <v>355.97</v>
+        <v>319.58</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B173">
-        <v>269.501</v>
+        <v>233.17</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B174">
-        <v>148.147</v>
+        <v>128.097</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B175">
-        <v>90.982</v>
+        <v>85.43300000000001</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B176">
-        <v>53.969</v>
+        <v>56.284</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B177">
-        <v>40.572</v>
+        <v>43.979</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B178">
-        <v>21.882</v>
+        <v>27.263</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B179">
-        <v>21.164</v>
+        <v>25.667</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B180">
-        <v>18.942</v>
+        <v>24.236</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B181">
-        <v>17.878</v>
+        <v>24.919</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B182">
-        <v>17.27</v>
+        <v>23.77</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B183">
-        <v>16.87</v>
+        <v>23.37</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B184">
         <v>13.77</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B185">
-        <v>8.27</v>
+        <v>10.77</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B186">
-        <v>13.37</v>
+        <v>19.37</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B187">
-        <v>1.87</v>
+        <v>0.87</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>27.05.20261</t>
-  </si>
-  <si>
-    <t>27.05.20262</t>
-  </si>
-  <si>
-    <t>27.05.20263</t>
-  </si>
-  <si>
-    <t>27.05.20264</t>
-  </si>
-  <si>
-    <t>27.05.20265</t>
-  </si>
-  <si>
-    <t>27.05.20266</t>
-  </si>
-  <si>
-    <t>27.05.20267</t>
-  </si>
-  <si>
-    <t>27.05.20268</t>
-  </si>
-  <si>
-    <t>27.05.20269</t>
-  </si>
-  <si>
-    <t>27.05.202610</t>
-  </si>
-  <si>
-    <t>27.05.202611</t>
-  </si>
-  <si>
-    <t>27.05.202612</t>
-  </si>
-  <si>
-    <t>27.05.202613</t>
-  </si>
-  <si>
-    <t>27.05.202614</t>
-  </si>
-  <si>
-    <t>27.05.202615</t>
-  </si>
-  <si>
-    <t>27.05.202616</t>
-  </si>
-  <si>
-    <t>27.05.202617</t>
-  </si>
-  <si>
-    <t>27.05.202618</t>
-  </si>
-  <si>
-    <t>27.05.202619</t>
-  </si>
-  <si>
-    <t>27.05.202620</t>
-  </si>
-  <si>
-    <t>27.05.202621</t>
-  </si>
-  <si>
-    <t>27.05.202622</t>
-  </si>
-  <si>
-    <t>27.05.202623</t>
-  </si>
-  <si>
-    <t>27.05.202624</t>
-  </si>
-  <si>
-    <t>27.05.202625</t>
-  </si>
-  <si>
-    <t>27.05.202626</t>
-  </si>
-  <si>
-    <t>27.05.202627</t>
-  </si>
-  <si>
-    <t>27.05.202628</t>
-  </si>
-  <si>
-    <t>27.05.202629</t>
-  </si>
-  <si>
-    <t>27.05.202630</t>
-  </si>
-  <si>
-    <t>27.05.202631</t>
-  </si>
-  <si>
-    <t>27.05.202632</t>
-  </si>
-  <si>
-    <t>27.05.202633</t>
-  </si>
-  <si>
-    <t>27.05.202634</t>
-  </si>
-  <si>
-    <t>27.05.202635</t>
-  </si>
-  <si>
-    <t>27.05.202636</t>
-  </si>
-  <si>
-    <t>27.05.202637</t>
-  </si>
-  <si>
-    <t>27.05.202638</t>
-  </si>
-  <si>
-    <t>27.05.202639</t>
-  </si>
-  <si>
-    <t>27.05.202640</t>
-  </si>
-  <si>
-    <t>27.05.202641</t>
-  </si>
-  <si>
-    <t>27.05.202642</t>
-  </si>
-  <si>
-    <t>27.05.202643</t>
-  </si>
-  <si>
-    <t>27.05.202644</t>
-  </si>
-  <si>
-    <t>27.05.202645</t>
-  </si>
-  <si>
-    <t>27.05.202646</t>
-  </si>
-  <si>
-    <t>27.05.202647</t>
-  </si>
-  <si>
-    <t>27.05.202648</t>
-  </si>
-  <si>
-    <t>27.05.202649</t>
-  </si>
-  <si>
-    <t>27.05.202650</t>
-  </si>
-  <si>
-    <t>27.05.202651</t>
-  </si>
-  <si>
-    <t>27.05.202652</t>
-  </si>
-  <si>
-    <t>27.05.202653</t>
-  </si>
-  <si>
-    <t>27.05.202654</t>
-  </si>
-  <si>
-    <t>27.05.202655</t>
-  </si>
-  <si>
-    <t>27.05.202656</t>
-  </si>
-  <si>
-    <t>27.05.202657</t>
-  </si>
-  <si>
-    <t>27.05.202658</t>
-  </si>
-  <si>
-    <t>27.05.202659</t>
-  </si>
-  <si>
-    <t>27.05.202660</t>
-  </si>
-  <si>
-    <t>27.05.202661</t>
-  </si>
-  <si>
-    <t>27.05.202662</t>
-  </si>
-  <si>
-    <t>27.05.202663</t>
-  </si>
-  <si>
-    <t>27.05.202664</t>
-  </si>
-  <si>
-    <t>27.05.202665</t>
-  </si>
-  <si>
-    <t>27.05.202666</t>
-  </si>
-  <si>
-    <t>27.05.202667</t>
-  </si>
-  <si>
-    <t>27.05.202668</t>
-  </si>
-  <si>
-    <t>27.05.202669</t>
-  </si>
-  <si>
-    <t>27.05.202670</t>
-  </si>
-  <si>
-    <t>27.05.202671</t>
-  </si>
-  <si>
-    <t>27.05.202672</t>
-  </si>
-  <si>
-    <t>27.05.202673</t>
-  </si>
-  <si>
-    <t>27.05.202674</t>
-  </si>
-  <si>
-    <t>27.05.202675</t>
-  </si>
-  <si>
-    <t>27.05.202676</t>
-  </si>
-  <si>
-    <t>27.05.202677</t>
-  </si>
-  <si>
-    <t>27.05.202678</t>
-  </si>
-  <si>
-    <t>27.05.202679</t>
-  </si>
-  <si>
-    <t>27.05.202680</t>
-  </si>
-  <si>
-    <t>27.05.202681</t>
-  </si>
-  <si>
-    <t>27.05.202682</t>
-  </si>
-  <si>
-    <t>27.05.202683</t>
-  </si>
-  <si>
-    <t>27.05.202684</t>
-  </si>
-  <si>
-    <t>27.05.202685</t>
-  </si>
-  <si>
-    <t>27.05.202686</t>
-  </si>
-  <si>
-    <t>27.05.202687</t>
-  </si>
-  <si>
-    <t>27.05.202688</t>
-  </si>
-  <si>
-    <t>27.05.202689</t>
-  </si>
-  <si>
-    <t>27.05.202690</t>
-  </si>
-  <si>
-    <t>27.05.202691</t>
-  </si>
-  <si>
-    <t>27.05.202692</t>
-  </si>
-  <si>
-    <t>27.05.202693</t>
-  </si>
-  <si>
-    <t>27.05.202694</t>
-  </si>
-  <si>
-    <t>27.05.202695</t>
-  </si>
-  <si>
-    <t>27.05.202696</t>
-  </si>
-  <si>
     <t>28.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>28.05.202696</t>
+  </si>
+  <si>
+    <t>29.05.20261</t>
+  </si>
+  <si>
+    <t>29.05.20262</t>
+  </si>
+  <si>
+    <t>29.05.20263</t>
+  </si>
+  <si>
+    <t>29.05.20264</t>
+  </si>
+  <si>
+    <t>29.05.20265</t>
+  </si>
+  <si>
+    <t>29.05.20266</t>
+  </si>
+  <si>
+    <t>29.05.20267</t>
+  </si>
+  <si>
+    <t>29.05.20268</t>
+  </si>
+  <si>
+    <t>29.05.20269</t>
+  </si>
+  <si>
+    <t>29.05.202610</t>
+  </si>
+  <si>
+    <t>29.05.202611</t>
+  </si>
+  <si>
+    <t>29.05.202612</t>
+  </si>
+  <si>
+    <t>29.05.202613</t>
+  </si>
+  <si>
+    <t>29.05.202614</t>
+  </si>
+  <si>
+    <t>29.05.202615</t>
+  </si>
+  <si>
+    <t>29.05.202616</t>
+  </si>
+  <si>
+    <t>29.05.202617</t>
+  </si>
+  <si>
+    <t>29.05.202618</t>
+  </si>
+  <si>
+    <t>29.05.202619</t>
+  </si>
+  <si>
+    <t>29.05.202620</t>
+  </si>
+  <si>
+    <t>29.05.202621</t>
+  </si>
+  <si>
+    <t>29.05.202622</t>
+  </si>
+  <si>
+    <t>29.05.202623</t>
+  </si>
+  <si>
+    <t>29.05.202624</t>
+  </si>
+  <si>
+    <t>29.05.202625</t>
+  </si>
+  <si>
+    <t>29.05.202626</t>
+  </si>
+  <si>
+    <t>29.05.202627</t>
+  </si>
+  <si>
+    <t>29.05.202628</t>
+  </si>
+  <si>
+    <t>29.05.202629</t>
+  </si>
+  <si>
+    <t>29.05.202630</t>
+  </si>
+  <si>
+    <t>29.05.202631</t>
+  </si>
+  <si>
+    <t>29.05.202632</t>
+  </si>
+  <si>
+    <t>29.05.202633</t>
+  </si>
+  <si>
+    <t>29.05.202634</t>
+  </si>
+  <si>
+    <t>29.05.202635</t>
+  </si>
+  <si>
+    <t>29.05.202636</t>
+  </si>
+  <si>
+    <t>29.05.202637</t>
+  </si>
+  <si>
+    <t>29.05.202638</t>
+  </si>
+  <si>
+    <t>29.05.202639</t>
+  </si>
+  <si>
+    <t>29.05.202640</t>
+  </si>
+  <si>
+    <t>29.05.202641</t>
+  </si>
+  <si>
+    <t>29.05.202642</t>
+  </si>
+  <si>
+    <t>29.05.202643</t>
+  </si>
+  <si>
+    <t>29.05.202644</t>
+  </si>
+  <si>
+    <t>29.05.202645</t>
+  </si>
+  <si>
+    <t>29.05.202646</t>
+  </si>
+  <si>
+    <t>29.05.202647</t>
+  </si>
+  <si>
+    <t>29.05.202648</t>
+  </si>
+  <si>
+    <t>29.05.202649</t>
+  </si>
+  <si>
+    <t>29.05.202650</t>
+  </si>
+  <si>
+    <t>29.05.202651</t>
+  </si>
+  <si>
+    <t>29.05.202652</t>
+  </si>
+  <si>
+    <t>29.05.202653</t>
+  </si>
+  <si>
+    <t>29.05.202654</t>
+  </si>
+  <si>
+    <t>29.05.202655</t>
+  </si>
+  <si>
+    <t>29.05.202656</t>
+  </si>
+  <si>
+    <t>29.05.202657</t>
+  </si>
+  <si>
+    <t>29.05.202658</t>
+  </si>
+  <si>
+    <t>29.05.202659</t>
+  </si>
+  <si>
+    <t>29.05.202660</t>
+  </si>
+  <si>
+    <t>29.05.202661</t>
+  </si>
+  <si>
+    <t>29.05.202662</t>
+  </si>
+  <si>
+    <t>29.05.202663</t>
+  </si>
+  <si>
+    <t>29.05.202664</t>
+  </si>
+  <si>
+    <t>29.05.202665</t>
+  </si>
+  <si>
+    <t>29.05.202666</t>
+  </si>
+  <si>
+    <t>29.05.202667</t>
+  </si>
+  <si>
+    <t>29.05.202668</t>
+  </si>
+  <si>
+    <t>29.05.202669</t>
+  </si>
+  <si>
+    <t>29.05.202670</t>
+  </si>
+  <si>
+    <t>29.05.202671</t>
+  </si>
+  <si>
+    <t>29.05.202672</t>
+  </si>
+  <si>
+    <t>29.05.202673</t>
+  </si>
+  <si>
+    <t>29.05.202674</t>
+  </si>
+  <si>
+    <t>29.05.202675</t>
+  </si>
+  <si>
+    <t>29.05.202676</t>
+  </si>
+  <si>
+    <t>29.05.202677</t>
+  </si>
+  <si>
+    <t>29.05.202678</t>
+  </si>
+  <si>
+    <t>29.05.202679</t>
+  </si>
+  <si>
+    <t>29.05.202680</t>
+  </si>
+  <si>
+    <t>29.05.202681</t>
+  </si>
+  <si>
+    <t>29.05.202682</t>
+  </si>
+  <si>
+    <t>29.05.202683</t>
+  </si>
+  <si>
+    <t>29.05.202684</t>
+  </si>
+  <si>
+    <t>29.05.202685</t>
+  </si>
+  <si>
+    <t>29.05.202686</t>
+  </si>
+  <si>
+    <t>29.05.202687</t>
+  </si>
+  <si>
+    <t>29.05.202688</t>
+  </si>
+  <si>
+    <t>29.05.202689</t>
+  </si>
+  <si>
+    <t>29.05.202690</t>
+  </si>
+  <si>
+    <t>29.05.202691</t>
+  </si>
+  <si>
+    <t>29.05.202692</t>
+  </si>
+  <si>
+    <t>29.05.202693</t>
+  </si>
+  <si>
+    <t>29.05.202694</t>
+  </si>
+  <si>
+    <t>29.05.202695</t>
+  </si>
+  <si>
+    <t>29.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,10 +988,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
-        <v>8.869999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
-        <v>7.87</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
-        <v>7.92</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>7.67</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.922</v>
+        <v>7.672</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
-        <v>7.928</v>
+        <v>7.678</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
-        <v>9.065</v>
+        <v>8.295</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
-        <v>9.148999999999999</v>
+        <v>9.587</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
-        <v>9.423999999999999</v>
+        <v>9.722</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
-        <v>30.475</v>
+        <v>24.965</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>99.221</v>
+        <v>80.745</v>
       </c>
       <c r="C22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>171.97</v>
+        <v>141.739</v>
       </c>
       <c r="C23">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>254.944</v>
+        <v>209.019</v>
       </c>
       <c r="C24">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>355.089</v>
+        <v>289.879</v>
       </c>
       <c r="C25">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>555.944</v>
+        <v>472.061</v>
       </c>
       <c r="C26">
-        <v>338</v>
+        <v>287</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>709.098</v>
+        <v>612.024</v>
       </c>
       <c r="C27">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>875.087</v>
+        <v>756.615</v>
       </c>
       <c r="C28">
-        <v>625</v>
+        <v>596</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>1052.844</v>
+        <v>926.422</v>
       </c>
       <c r="C29">
-        <v>794</v>
+        <v>750</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>1427.303</v>
+        <v>1235.928</v>
       </c>
       <c r="C30">
-        <v>967</v>
+        <v>917</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>1647.032</v>
+        <v>1410.091</v>
       </c>
       <c r="C31">
-        <v>1152</v>
+        <v>1075</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
-        <v>1853.951</v>
+        <v>1575.173</v>
       </c>
       <c r="C32">
-        <v>1300</v>
+        <v>1172</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
-        <v>2040.751</v>
+        <v>1743.182</v>
       </c>
       <c r="C33">
-        <v>1464</v>
+        <v>1289</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>2324.916</v>
+        <v>1971.031</v>
       </c>
       <c r="C34">
-        <v>1605</v>
+        <v>1431</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>2482.684</v>
+        <v>2113.921</v>
       </c>
       <c r="C35">
-        <v>1733</v>
+        <v>1552</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>2619.925</v>
+        <v>2232.892</v>
       </c>
       <c r="C36">
-        <v>1844</v>
+        <v>1678</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>2803.273</v>
+        <v>2362.386</v>
       </c>
       <c r="C37">
-        <v>1933</v>
+        <v>1753</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>2988.39</v>
+        <v>2552.391</v>
       </c>
       <c r="C38">
-        <v>2014</v>
+        <v>1875</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>3090.509</v>
+        <v>2637.633</v>
       </c>
       <c r="C39">
-        <v>2100</v>
+        <v>1967</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>3168.016</v>
+        <v>2703.518</v>
       </c>
       <c r="C40">
-        <v>2174</v>
+        <v>1929</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>3224.202</v>
+        <v>2762.636</v>
       </c>
       <c r="C41">
-        <v>2209</v>
+        <v>1995</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>3347.391</v>
+        <v>2845.166</v>
       </c>
       <c r="C42">
-        <v>2256</v>
+        <v>2031</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>3396.716</v>
+        <v>2889.952</v>
       </c>
       <c r="C43">
-        <v>2300</v>
+        <v>2119</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>3442.498</v>
+        <v>2929.939</v>
       </c>
       <c r="C44">
-        <v>2303</v>
+        <v>2115</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>3475.83</v>
+        <v>2948.98</v>
       </c>
       <c r="C45">
-        <v>2351</v>
+        <v>2066</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
-        <v>3472.486</v>
+        <v>2933.221</v>
       </c>
       <c r="C46">
-        <v>2371</v>
+        <v>2051</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
-        <v>3484.207</v>
+        <v>2946.715</v>
       </c>
       <c r="C47">
-        <v>2434</v>
+        <v>2072</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>3487.549</v>
+        <v>2812.622</v>
       </c>
       <c r="C48">
-        <v>2425</v>
+        <v>1899</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>3490.593</v>
+        <v>2785.666</v>
       </c>
       <c r="C49">
-        <v>2414</v>
+        <v>1920</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>3485.279</v>
+        <v>2863.063</v>
       </c>
       <c r="C50">
-        <v>2482</v>
+        <v>1963</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
-        <v>3479.6</v>
+        <v>2818.961</v>
       </c>
       <c r="C51">
-        <v>2492</v>
+        <v>1970</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>3467.177</v>
+        <v>2805.208</v>
       </c>
       <c r="C52">
-        <v>2479</v>
+        <v>1957</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>3449.344</v>
+        <v>2793.022</v>
       </c>
       <c r="C53">
-        <v>2475</v>
+        <v>2017</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>3425.535</v>
+        <v>2772.229</v>
       </c>
       <c r="C54">
-        <v>2424</v>
+        <v>2079</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>3397.156</v>
+        <v>2742.144</v>
       </c>
       <c r="C55">
-        <v>2401</v>
+        <v>1968</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>3355.908</v>
+        <v>2668.429</v>
       </c>
       <c r="C56">
-        <v>2379</v>
+        <v>1860</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>3315.174</v>
+        <v>2644.701</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1816</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>3252.191</v>
+        <v>2588.451</v>
       </c>
       <c r="C58">
-        <v>2398</v>
+        <v>1781</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>3196.288</v>
+        <v>2551.748</v>
       </c>
       <c r="C59">
-        <v>2371</v>
+        <v>1842</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>3141.417</v>
+        <v>2510.113</v>
       </c>
       <c r="C60">
-        <v>2328</v>
+        <v>1812</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>3058.855</v>
+        <v>2481.585</v>
       </c>
       <c r="C61">
-        <v>2302</v>
+        <v>1840</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>2888.378</v>
+        <v>2327.175</v>
       </c>
       <c r="C62">
-        <v>2199</v>
+        <v>1744</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>2801.108</v>
+        <v>2251.329</v>
       </c>
       <c r="C63">
-        <v>2115</v>
+        <v>1645</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>2650.463</v>
+        <v>2253.8</v>
       </c>
       <c r="C64">
-        <v>2031</v>
+        <v>1625</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>2552.294</v>
+        <v>2164.79</v>
       </c>
       <c r="C65">
-        <v>1959</v>
+        <v>1544</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>2311.334</v>
+        <v>1955.871</v>
       </c>
       <c r="C66">
-        <v>1824</v>
+        <v>1571</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>2134.496</v>
+        <v>1844.956</v>
       </c>
       <c r="C67">
-        <v>1692</v>
+        <v>1386</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>1964.452</v>
+        <v>1699.818</v>
       </c>
       <c r="C68">
-        <v>1549</v>
+        <v>1306</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>1773.02</v>
+        <v>1557.991</v>
       </c>
       <c r="C69">
-        <v>1409</v>
+        <v>1185</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>1464.086</v>
+        <v>1295.946</v>
       </c>
       <c r="C70">
-        <v>1244</v>
+        <v>1066</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
-        <v>1263.8</v>
+        <v>1141.974</v>
       </c>
       <c r="C71">
-        <v>1077</v>
+        <v>972</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>1073.597</v>
+        <v>978.022</v>
       </c>
       <c r="C72">
-        <v>863</v>
+        <v>784</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>898.822</v>
+        <v>817.2670000000001</v>
       </c>
       <c r="C73">
-        <v>702</v>
+        <v>642</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>610.1660000000001</v>
+        <v>554.426</v>
       </c>
       <c r="C74">
-        <v>533</v>
+        <v>488</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>472.775</v>
+        <v>431.278</v>
       </c>
       <c r="C75">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>355.97</v>
+        <v>319.58</v>
       </c>
       <c r="C76">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>269.501</v>
+        <v>233.17</v>
       </c>
       <c r="C77">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>148.147</v>
+        <v>128.097</v>
       </c>
       <c r="C78">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>90.982</v>
+        <v>85.43300000000001</v>
       </c>
       <c r="C79">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>53.969</v>
+        <v>56.284</v>
       </c>
       <c r="C80">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>40.572</v>
+        <v>43.979</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
-        <v>21.882</v>
+        <v>27.263</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
-        <v>21.164</v>
+        <v>25.667</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
-        <v>18.942</v>
+        <v>24.236</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
-        <v>17.878</v>
+        <v>24.919</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
-        <v>17.27</v>
+        <v>23.77</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
-        <v>16.87</v>
+        <v>23.37</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
         <v>13.77</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
-        <v>8.27</v>
+        <v>10.77</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
-        <v>13.37</v>
+        <v>19.37</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.87</v>
+        <v>0.87</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
         <v>7.87</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B110">
-        <v>7.67</v>
+        <v>0</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.672</v>
+        <v>7.872</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B113">
-        <v>7.678</v>
+        <v>7.884</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B114">
-        <v>8.295</v>
+        <v>8.441000000000001</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B115">
-        <v>9.587</v>
+        <v>9.323</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B116">
-        <v>9.722</v>
+        <v>8.715</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B117">
-        <v>24.965</v>
+        <v>30.872</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B118">
-        <v>80.745</v>
+        <v>98.02500000000001</v>
       </c>
       <c r="C118">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B119">
-        <v>141.739</v>
+        <v>167.58</v>
       </c>
       <c r="C119">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B120">
-        <v>209.019</v>
+        <v>252.107</v>
       </c>
       <c r="C120">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B121">
-        <v>289.879</v>
+        <v>348.665</v>
       </c>
       <c r="C121">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B122">
-        <v>472.061</v>
+        <v>560.468</v>
       </c>
       <c r="C122">
-        <v>287</v>
+        <v>355</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B123">
-        <v>612.024</v>
+        <v>712.129</v>
       </c>
       <c r="C123">
-        <v>463</v>
+        <v>503</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B124">
-        <v>756.615</v>
+        <v>877.288</v>
       </c>
       <c r="C124">
-        <v>596</v>
+        <v>650</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B125">
-        <v>926.422</v>
+        <v>1074.335</v>
       </c>
       <c r="C125">
-        <v>750</v>
+        <v>843</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B126">
-        <v>1235.928</v>
+        <v>1464.65</v>
       </c>
       <c r="C126">
-        <v>917</v>
+        <v>1058</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B127">
-        <v>1410.091</v>
+        <v>1675.445</v>
       </c>
       <c r="C127">
-        <v>1075</v>
+        <v>1243</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B128">
-        <v>1575.173</v>
+        <v>1851.95</v>
       </c>
       <c r="C128">
-        <v>1172</v>
+        <v>1425</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B129">
-        <v>1743.182</v>
+        <v>2022.012</v>
       </c>
       <c r="C129">
-        <v>1289</v>
+        <v>1626</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B130">
-        <v>1971.031</v>
+        <v>2278.719</v>
       </c>
       <c r="C130">
-        <v>1431</v>
+        <v>1784</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B131">
-        <v>2113.921</v>
+        <v>2443.52</v>
       </c>
       <c r="C131">
-        <v>1552</v>
+        <v>1915</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B132">
-        <v>2232.892</v>
+        <v>2569.092</v>
       </c>
       <c r="C132">
-        <v>1678</v>
+        <v>2021</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B133">
-        <v>2362.386</v>
+        <v>2712.564</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B134">
-        <v>2552.391</v>
+        <v>2869.217</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B135">
-        <v>2637.633</v>
+        <v>2964.169</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B136">
-        <v>2703.518</v>
+        <v>3029.208</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B137">
-        <v>2762.636</v>
+        <v>3077.166</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B138">
-        <v>2845.166</v>
+        <v>3156.369</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B139">
-        <v>2889.952</v>
+        <v>3193.695</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B140">
-        <v>2929.939</v>
+        <v>3227.613</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B141">
-        <v>2948.98</v>
+        <v>3243.356</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B142">
-        <v>2933.221</v>
+        <v>3266.336</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B143">
-        <v>2946.715</v>
+        <v>3120.032</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B144">
-        <v>2812.622</v>
+        <v>3131.368</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B145">
-        <v>2785.666</v>
+        <v>3128.079</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B146">
-        <v>2863.063</v>
+        <v>3102.341</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B147">
-        <v>2818.961</v>
+        <v>3090.205</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B148">
-        <v>2805.208</v>
+        <v>3073.937</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B149">
-        <v>2793.022</v>
+        <v>3037.664</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B150">
-        <v>2772.229</v>
+        <v>3032.051</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B151">
-        <v>2742.144</v>
+        <v>2973.833</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B152">
-        <v>2668.429</v>
+        <v>2931.071</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B153">
-        <v>2644.701</v>
+        <v>2862.335</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B154">
-        <v>2588.451</v>
+        <v>2832.541</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B155">
-        <v>2551.748</v>
+        <v>2815.781</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B156">
-        <v>2510.113</v>
+        <v>2754.785</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B157">
-        <v>2481.585</v>
+        <v>2683.565</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B158">
-        <v>2327.175</v>
+        <v>2656.57</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B159">
-        <v>2251.329</v>
+        <v>2536.319</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B160">
-        <v>2253.8</v>
+        <v>2449.103</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B161">
-        <v>2164.79</v>
+        <v>2331.57</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B162">
-        <v>1955.871</v>
+        <v>2111.713</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B163">
-        <v>1844.956</v>
+        <v>1954.97</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B164">
-        <v>1699.818</v>
+        <v>1809.45</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B165">
-        <v>1557.991</v>
+        <v>1631.89</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B166">
-        <v>1295.946</v>
+        <v>1333.972</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B167">
-        <v>1141.974</v>
+        <v>1163.42</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B168">
-        <v>978.022</v>
+        <v>990.5119999999999</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B169">
-        <v>817.2670000000001</v>
+        <v>826.472</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B170">
-        <v>554.426</v>
+        <v>559.629</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B171">
-        <v>431.278</v>
+        <v>437.712</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B172">
-        <v>319.58</v>
+        <v>320.004</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B173">
-        <v>233.17</v>
+        <v>241.659</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B174">
-        <v>128.097</v>
+        <v>135.902</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B175">
-        <v>85.43300000000001</v>
+        <v>83.26300000000001</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B176">
-        <v>56.284</v>
+        <v>51.228</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B177">
-        <v>43.979</v>
+        <v>34.889</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B178">
-        <v>27.263</v>
+        <v>18.562</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B179">
-        <v>25.667</v>
+        <v>20.014</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B180">
-        <v>24.236</v>
+        <v>22.948</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B181">
-        <v>24.919</v>
+        <v>18.876</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B182">
-        <v>23.77</v>
+        <v>12.47</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B183">
-        <v>23.37</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B184">
-        <v>13.77</v>
+        <v>1.77</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B185">
-        <v>10.77</v>
+        <v>1.37</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B186">
-        <v>19.37</v>
+        <v>0</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B187">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.06.20261</t>
-  </si>
-  <si>
-    <t>03.06.20262</t>
-  </si>
-  <si>
-    <t>03.06.20263</t>
-  </si>
-  <si>
-    <t>03.06.20264</t>
-  </si>
-  <si>
-    <t>03.06.20265</t>
-  </si>
-  <si>
-    <t>03.06.20266</t>
-  </si>
-  <si>
-    <t>03.06.20267</t>
-  </si>
-  <si>
-    <t>03.06.20268</t>
-  </si>
-  <si>
-    <t>03.06.20269</t>
-  </si>
-  <si>
-    <t>03.06.202610</t>
-  </si>
-  <si>
-    <t>03.06.202611</t>
-  </si>
-  <si>
-    <t>03.06.202612</t>
-  </si>
-  <si>
-    <t>03.06.202613</t>
-  </si>
-  <si>
-    <t>03.06.202614</t>
-  </si>
-  <si>
-    <t>03.06.202615</t>
-  </si>
-  <si>
-    <t>03.06.202616</t>
-  </si>
-  <si>
-    <t>03.06.202617</t>
-  </si>
-  <si>
-    <t>03.06.202618</t>
-  </si>
-  <si>
-    <t>03.06.202619</t>
-  </si>
-  <si>
-    <t>03.06.202620</t>
-  </si>
-  <si>
-    <t>03.06.202621</t>
-  </si>
-  <si>
-    <t>03.06.202622</t>
-  </si>
-  <si>
-    <t>03.06.202623</t>
-  </si>
-  <si>
-    <t>03.06.202624</t>
-  </si>
-  <si>
-    <t>03.06.202625</t>
-  </si>
-  <si>
-    <t>03.06.202626</t>
-  </si>
-  <si>
-    <t>03.06.202627</t>
-  </si>
-  <si>
-    <t>03.06.202628</t>
-  </si>
-  <si>
-    <t>03.06.202629</t>
-  </si>
-  <si>
-    <t>03.06.202630</t>
-  </si>
-  <si>
-    <t>03.06.202631</t>
-  </si>
-  <si>
-    <t>03.06.202632</t>
-  </si>
-  <si>
-    <t>03.06.202633</t>
-  </si>
-  <si>
-    <t>03.06.202634</t>
-  </si>
-  <si>
-    <t>03.06.202635</t>
-  </si>
-  <si>
-    <t>03.06.202636</t>
-  </si>
-  <si>
-    <t>03.06.202637</t>
-  </si>
-  <si>
-    <t>03.06.202638</t>
-  </si>
-  <si>
-    <t>03.06.202639</t>
-  </si>
-  <si>
-    <t>03.06.202640</t>
-  </si>
-  <si>
-    <t>03.06.202641</t>
-  </si>
-  <si>
-    <t>03.06.202642</t>
-  </si>
-  <si>
-    <t>03.06.202643</t>
-  </si>
-  <si>
-    <t>03.06.202644</t>
-  </si>
-  <si>
-    <t>03.06.202645</t>
-  </si>
-  <si>
-    <t>03.06.202646</t>
-  </si>
-  <si>
-    <t>03.06.202647</t>
-  </si>
-  <si>
-    <t>03.06.202648</t>
-  </si>
-  <si>
-    <t>03.06.202649</t>
-  </si>
-  <si>
-    <t>03.06.202650</t>
-  </si>
-  <si>
-    <t>03.06.202651</t>
-  </si>
-  <si>
-    <t>03.06.202652</t>
-  </si>
-  <si>
-    <t>03.06.202653</t>
-  </si>
-  <si>
-    <t>03.06.202654</t>
-  </si>
-  <si>
-    <t>03.06.202655</t>
-  </si>
-  <si>
-    <t>03.06.202656</t>
-  </si>
-  <si>
-    <t>03.06.202657</t>
-  </si>
-  <si>
-    <t>03.06.202658</t>
-  </si>
-  <si>
-    <t>03.06.202659</t>
-  </si>
-  <si>
-    <t>03.06.202660</t>
-  </si>
-  <si>
-    <t>03.06.202661</t>
-  </si>
-  <si>
-    <t>03.06.202662</t>
-  </si>
-  <si>
-    <t>03.06.202663</t>
-  </si>
-  <si>
-    <t>03.06.202664</t>
-  </si>
-  <si>
-    <t>03.06.202665</t>
-  </si>
-  <si>
-    <t>03.06.202666</t>
-  </si>
-  <si>
-    <t>03.06.202667</t>
-  </si>
-  <si>
-    <t>03.06.202668</t>
-  </si>
-  <si>
-    <t>03.06.202669</t>
-  </si>
-  <si>
-    <t>03.06.202670</t>
-  </si>
-  <si>
-    <t>03.06.202671</t>
-  </si>
-  <si>
-    <t>03.06.202672</t>
-  </si>
-  <si>
-    <t>03.06.202673</t>
-  </si>
-  <si>
-    <t>03.06.202674</t>
-  </si>
-  <si>
-    <t>03.06.202675</t>
-  </si>
-  <si>
-    <t>03.06.202676</t>
-  </si>
-  <si>
-    <t>03.06.202677</t>
-  </si>
-  <si>
-    <t>03.06.202678</t>
-  </si>
-  <si>
-    <t>03.06.202679</t>
-  </si>
-  <si>
-    <t>03.06.202680</t>
-  </si>
-  <si>
-    <t>03.06.202681</t>
-  </si>
-  <si>
-    <t>03.06.202682</t>
-  </si>
-  <si>
-    <t>03.06.202683</t>
-  </si>
-  <si>
-    <t>03.06.202684</t>
-  </si>
-  <si>
-    <t>03.06.202685</t>
-  </si>
-  <si>
-    <t>03.06.202686</t>
-  </si>
-  <si>
-    <t>03.06.202687</t>
-  </si>
-  <si>
-    <t>03.06.202688</t>
-  </si>
-  <si>
-    <t>03.06.202689</t>
-  </si>
-  <si>
-    <t>03.06.202690</t>
-  </si>
-  <si>
-    <t>03.06.202691</t>
-  </si>
-  <si>
-    <t>03.06.202692</t>
-  </si>
-  <si>
-    <t>03.06.202693</t>
-  </si>
-  <si>
-    <t>03.06.202694</t>
-  </si>
-  <si>
-    <t>03.06.202695</t>
-  </si>
-  <si>
-    <t>03.06.202696</t>
-  </si>
-  <si>
-    <t>04.06.20261</t>
-  </si>
-  <si>
-    <t>04.06.20262</t>
-  </si>
-  <si>
-    <t>04.06.20263</t>
-  </si>
-  <si>
-    <t>04.06.20264</t>
-  </si>
-  <si>
-    <t>04.06.20265</t>
-  </si>
-  <si>
-    <t>04.06.20266</t>
-  </si>
-  <si>
-    <t>04.06.20267</t>
-  </si>
-  <si>
-    <t>04.06.20268</t>
-  </si>
-  <si>
-    <t>04.06.20269</t>
-  </si>
-  <si>
-    <t>04.06.202610</t>
-  </si>
-  <si>
-    <t>04.06.202611</t>
-  </si>
-  <si>
-    <t>04.06.202612</t>
-  </si>
-  <si>
-    <t>04.06.202613</t>
-  </si>
-  <si>
-    <t>04.06.202614</t>
-  </si>
-  <si>
-    <t>04.06.202615</t>
-  </si>
-  <si>
-    <t>04.06.202616</t>
-  </si>
-  <si>
-    <t>04.06.202617</t>
-  </si>
-  <si>
-    <t>04.06.202618</t>
-  </si>
-  <si>
-    <t>04.06.202619</t>
-  </si>
-  <si>
-    <t>04.06.202620</t>
-  </si>
-  <si>
-    <t>04.06.202621</t>
-  </si>
-  <si>
-    <t>04.06.202622</t>
-  </si>
-  <si>
-    <t>04.06.202623</t>
-  </si>
-  <si>
-    <t>04.06.202624</t>
-  </si>
-  <si>
-    <t>04.06.202625</t>
-  </si>
-  <si>
-    <t>04.06.202626</t>
-  </si>
-  <si>
-    <t>04.06.202627</t>
-  </si>
-  <si>
-    <t>04.06.202628</t>
-  </si>
-  <si>
-    <t>04.06.202629</t>
-  </si>
-  <si>
-    <t>04.06.202630</t>
-  </si>
-  <si>
-    <t>04.06.202631</t>
-  </si>
-  <si>
-    <t>04.06.202632</t>
-  </si>
-  <si>
-    <t>04.06.202633</t>
-  </si>
-  <si>
-    <t>04.06.202634</t>
-  </si>
-  <si>
-    <t>04.06.202635</t>
-  </si>
-  <si>
-    <t>04.06.202636</t>
-  </si>
-  <si>
-    <t>04.06.202637</t>
-  </si>
-  <si>
-    <t>04.06.202638</t>
-  </si>
-  <si>
-    <t>04.06.202639</t>
-  </si>
-  <si>
-    <t>04.06.202640</t>
-  </si>
-  <si>
-    <t>04.06.202641</t>
-  </si>
-  <si>
-    <t>04.06.202642</t>
-  </si>
-  <si>
-    <t>04.06.202643</t>
-  </si>
-  <si>
-    <t>04.06.202644</t>
-  </si>
-  <si>
-    <t>04.06.202645</t>
-  </si>
-  <si>
-    <t>04.06.202646</t>
-  </si>
-  <si>
-    <t>04.06.202647</t>
-  </si>
-  <si>
-    <t>04.06.202648</t>
-  </si>
-  <si>
-    <t>04.06.202649</t>
-  </si>
-  <si>
-    <t>04.06.202650</t>
-  </si>
-  <si>
-    <t>04.06.202651</t>
-  </si>
-  <si>
-    <t>04.06.202652</t>
-  </si>
-  <si>
-    <t>04.06.202653</t>
-  </si>
-  <si>
-    <t>04.06.202654</t>
-  </si>
-  <si>
-    <t>04.06.202655</t>
-  </si>
-  <si>
-    <t>04.06.202656</t>
-  </si>
-  <si>
-    <t>04.06.202657</t>
-  </si>
-  <si>
-    <t>04.06.202658</t>
-  </si>
-  <si>
-    <t>04.06.202659</t>
-  </si>
-  <si>
-    <t>04.06.202660</t>
-  </si>
-  <si>
-    <t>04.06.202661</t>
-  </si>
-  <si>
-    <t>04.06.202662</t>
-  </si>
-  <si>
-    <t>04.06.202663</t>
-  </si>
-  <si>
-    <t>04.06.202664</t>
-  </si>
-  <si>
-    <t>04.06.202665</t>
-  </si>
-  <si>
-    <t>04.06.202666</t>
-  </si>
-  <si>
-    <t>04.06.202667</t>
-  </si>
-  <si>
-    <t>04.06.202668</t>
-  </si>
-  <si>
-    <t>04.06.202669</t>
-  </si>
-  <si>
-    <t>04.06.202670</t>
-  </si>
-  <si>
-    <t>04.06.202671</t>
-  </si>
-  <si>
-    <t>04.06.202672</t>
-  </si>
-  <si>
-    <t>04.06.202673</t>
-  </si>
-  <si>
-    <t>04.06.202674</t>
-  </si>
-  <si>
-    <t>04.06.202675</t>
-  </si>
-  <si>
-    <t>04.06.202676</t>
-  </si>
-  <si>
-    <t>04.06.202677</t>
-  </si>
-  <si>
-    <t>04.06.202678</t>
-  </si>
-  <si>
-    <t>04.06.202679</t>
-  </si>
-  <si>
-    <t>04.06.202680</t>
-  </si>
-  <si>
-    <t>04.06.202681</t>
-  </si>
-  <si>
-    <t>04.06.202682</t>
-  </si>
-  <si>
-    <t>04.06.202683</t>
-  </si>
-  <si>
-    <t>04.06.202684</t>
-  </si>
-  <si>
-    <t>04.06.202685</t>
-  </si>
-  <si>
-    <t>04.06.202686</t>
-  </si>
-  <si>
-    <t>04.06.202687</t>
-  </si>
-  <si>
-    <t>04.06.202688</t>
-  </si>
-  <si>
-    <t>04.06.202689</t>
-  </si>
-  <si>
-    <t>04.06.202690</t>
-  </si>
-  <si>
-    <t>04.06.202691</t>
-  </si>
-  <si>
-    <t>04.06.202692</t>
-  </si>
-  <si>
-    <t>04.06.202693</t>
-  </si>
-  <si>
-    <t>04.06.202694</t>
-  </si>
-  <si>
-    <t>04.06.202695</t>
-  </si>
-  <si>
-    <t>04.06.202696</t>
+    <t>11.06.20261</t>
+  </si>
+  <si>
+    <t>11.06.20262</t>
+  </si>
+  <si>
+    <t>11.06.20263</t>
+  </si>
+  <si>
+    <t>11.06.20264</t>
+  </si>
+  <si>
+    <t>11.06.20265</t>
+  </si>
+  <si>
+    <t>11.06.20266</t>
+  </si>
+  <si>
+    <t>11.06.20267</t>
+  </si>
+  <si>
+    <t>11.06.20268</t>
+  </si>
+  <si>
+    <t>11.06.20269</t>
+  </si>
+  <si>
+    <t>11.06.202610</t>
+  </si>
+  <si>
+    <t>11.06.202611</t>
+  </si>
+  <si>
+    <t>11.06.202612</t>
+  </si>
+  <si>
+    <t>11.06.202613</t>
+  </si>
+  <si>
+    <t>11.06.202614</t>
+  </si>
+  <si>
+    <t>11.06.202615</t>
+  </si>
+  <si>
+    <t>11.06.202616</t>
+  </si>
+  <si>
+    <t>11.06.202617</t>
+  </si>
+  <si>
+    <t>11.06.202618</t>
+  </si>
+  <si>
+    <t>11.06.202619</t>
+  </si>
+  <si>
+    <t>11.06.202620</t>
+  </si>
+  <si>
+    <t>11.06.202621</t>
+  </si>
+  <si>
+    <t>11.06.202622</t>
+  </si>
+  <si>
+    <t>11.06.202623</t>
+  </si>
+  <si>
+    <t>11.06.202624</t>
+  </si>
+  <si>
+    <t>11.06.202625</t>
+  </si>
+  <si>
+    <t>11.06.202626</t>
+  </si>
+  <si>
+    <t>11.06.202627</t>
+  </si>
+  <si>
+    <t>11.06.202628</t>
+  </si>
+  <si>
+    <t>11.06.202629</t>
+  </si>
+  <si>
+    <t>11.06.202630</t>
+  </si>
+  <si>
+    <t>11.06.202631</t>
+  </si>
+  <si>
+    <t>11.06.202632</t>
+  </si>
+  <si>
+    <t>11.06.202633</t>
+  </si>
+  <si>
+    <t>11.06.202634</t>
+  </si>
+  <si>
+    <t>11.06.202635</t>
+  </si>
+  <si>
+    <t>11.06.202636</t>
+  </si>
+  <si>
+    <t>11.06.202637</t>
+  </si>
+  <si>
+    <t>11.06.202638</t>
+  </si>
+  <si>
+    <t>11.06.202639</t>
+  </si>
+  <si>
+    <t>11.06.202640</t>
+  </si>
+  <si>
+    <t>11.06.202641</t>
+  </si>
+  <si>
+    <t>11.06.202642</t>
+  </si>
+  <si>
+    <t>11.06.202643</t>
+  </si>
+  <si>
+    <t>11.06.202644</t>
+  </si>
+  <si>
+    <t>11.06.202645</t>
+  </si>
+  <si>
+    <t>11.06.202646</t>
+  </si>
+  <si>
+    <t>11.06.202647</t>
+  </si>
+  <si>
+    <t>11.06.202648</t>
+  </si>
+  <si>
+    <t>11.06.202649</t>
+  </si>
+  <si>
+    <t>11.06.202650</t>
+  </si>
+  <si>
+    <t>11.06.202651</t>
+  </si>
+  <si>
+    <t>11.06.202652</t>
+  </si>
+  <si>
+    <t>11.06.202653</t>
+  </si>
+  <si>
+    <t>11.06.202654</t>
+  </si>
+  <si>
+    <t>11.06.202655</t>
+  </si>
+  <si>
+    <t>11.06.202656</t>
+  </si>
+  <si>
+    <t>11.06.202657</t>
+  </si>
+  <si>
+    <t>11.06.202658</t>
+  </si>
+  <si>
+    <t>11.06.202659</t>
+  </si>
+  <si>
+    <t>11.06.202660</t>
+  </si>
+  <si>
+    <t>11.06.202661</t>
+  </si>
+  <si>
+    <t>11.06.202662</t>
+  </si>
+  <si>
+    <t>11.06.202663</t>
+  </si>
+  <si>
+    <t>11.06.202664</t>
+  </si>
+  <si>
+    <t>11.06.202665</t>
+  </si>
+  <si>
+    <t>11.06.202666</t>
+  </si>
+  <si>
+    <t>11.06.202667</t>
+  </si>
+  <si>
+    <t>11.06.202668</t>
+  </si>
+  <si>
+    <t>11.06.202669</t>
+  </si>
+  <si>
+    <t>11.06.202670</t>
+  </si>
+  <si>
+    <t>11.06.202671</t>
+  </si>
+  <si>
+    <t>11.06.202672</t>
+  </si>
+  <si>
+    <t>11.06.202673</t>
+  </si>
+  <si>
+    <t>11.06.202674</t>
+  </si>
+  <si>
+    <t>11.06.202675</t>
+  </si>
+  <si>
+    <t>11.06.202676</t>
+  </si>
+  <si>
+    <t>11.06.202677</t>
+  </si>
+  <si>
+    <t>11.06.202678</t>
+  </si>
+  <si>
+    <t>11.06.202679</t>
+  </si>
+  <si>
+    <t>11.06.202680</t>
+  </si>
+  <si>
+    <t>11.06.202681</t>
+  </si>
+  <si>
+    <t>11.06.202682</t>
+  </si>
+  <si>
+    <t>11.06.202683</t>
+  </si>
+  <si>
+    <t>11.06.202684</t>
+  </si>
+  <si>
+    <t>11.06.202685</t>
+  </si>
+  <si>
+    <t>11.06.202686</t>
+  </si>
+  <si>
+    <t>11.06.202687</t>
+  </si>
+  <si>
+    <t>11.06.202688</t>
+  </si>
+  <si>
+    <t>11.06.202689</t>
+  </si>
+  <si>
+    <t>11.06.202690</t>
+  </si>
+  <si>
+    <t>11.06.202691</t>
+  </si>
+  <si>
+    <t>11.06.202692</t>
+  </si>
+  <si>
+    <t>11.06.202693</t>
+  </si>
+  <si>
+    <t>11.06.202694</t>
+  </si>
+  <si>
+    <t>11.06.202695</t>
+  </si>
+  <si>
+    <t>11.06.202696</t>
+  </si>
+  <si>
+    <t>12.06.20261</t>
+  </si>
+  <si>
+    <t>12.06.20262</t>
+  </si>
+  <si>
+    <t>12.06.20263</t>
+  </si>
+  <si>
+    <t>12.06.20264</t>
+  </si>
+  <si>
+    <t>12.06.20265</t>
+  </si>
+  <si>
+    <t>12.06.20266</t>
+  </si>
+  <si>
+    <t>12.06.20267</t>
+  </si>
+  <si>
+    <t>12.06.20268</t>
+  </si>
+  <si>
+    <t>12.06.20269</t>
+  </si>
+  <si>
+    <t>12.06.202610</t>
+  </si>
+  <si>
+    <t>12.06.202611</t>
+  </si>
+  <si>
+    <t>12.06.202612</t>
+  </si>
+  <si>
+    <t>12.06.202613</t>
+  </si>
+  <si>
+    <t>12.06.202614</t>
+  </si>
+  <si>
+    <t>12.06.202615</t>
+  </si>
+  <si>
+    <t>12.06.202616</t>
+  </si>
+  <si>
+    <t>12.06.202617</t>
+  </si>
+  <si>
+    <t>12.06.202618</t>
+  </si>
+  <si>
+    <t>12.06.202619</t>
+  </si>
+  <si>
+    <t>12.06.202620</t>
+  </si>
+  <si>
+    <t>12.06.202621</t>
+  </si>
+  <si>
+    <t>12.06.202622</t>
+  </si>
+  <si>
+    <t>12.06.202623</t>
+  </si>
+  <si>
+    <t>12.06.202624</t>
+  </si>
+  <si>
+    <t>12.06.202625</t>
+  </si>
+  <si>
+    <t>12.06.202626</t>
+  </si>
+  <si>
+    <t>12.06.202627</t>
+  </si>
+  <si>
+    <t>12.06.202628</t>
+  </si>
+  <si>
+    <t>12.06.202629</t>
+  </si>
+  <si>
+    <t>12.06.202630</t>
+  </si>
+  <si>
+    <t>12.06.202631</t>
+  </si>
+  <si>
+    <t>12.06.202632</t>
+  </si>
+  <si>
+    <t>12.06.202633</t>
+  </si>
+  <si>
+    <t>12.06.202634</t>
+  </si>
+  <si>
+    <t>12.06.202635</t>
+  </si>
+  <si>
+    <t>12.06.202636</t>
+  </si>
+  <si>
+    <t>12.06.202637</t>
+  </si>
+  <si>
+    <t>12.06.202638</t>
+  </si>
+  <si>
+    <t>12.06.202639</t>
+  </si>
+  <si>
+    <t>12.06.202640</t>
+  </si>
+  <si>
+    <t>12.06.202641</t>
+  </si>
+  <si>
+    <t>12.06.202642</t>
+  </si>
+  <si>
+    <t>12.06.202643</t>
+  </si>
+  <si>
+    <t>12.06.202644</t>
+  </si>
+  <si>
+    <t>12.06.202645</t>
+  </si>
+  <si>
+    <t>12.06.202646</t>
+  </si>
+  <si>
+    <t>12.06.202647</t>
+  </si>
+  <si>
+    <t>12.06.202648</t>
+  </si>
+  <si>
+    <t>12.06.202649</t>
+  </si>
+  <si>
+    <t>12.06.202650</t>
+  </si>
+  <si>
+    <t>12.06.202651</t>
+  </si>
+  <si>
+    <t>12.06.202652</t>
+  </si>
+  <si>
+    <t>12.06.202653</t>
+  </si>
+  <si>
+    <t>12.06.202654</t>
+  </si>
+  <si>
+    <t>12.06.202655</t>
+  </si>
+  <si>
+    <t>12.06.202656</t>
+  </si>
+  <si>
+    <t>12.06.202657</t>
+  </si>
+  <si>
+    <t>12.06.202658</t>
+  </si>
+  <si>
+    <t>12.06.202659</t>
+  </si>
+  <si>
+    <t>12.06.202660</t>
+  </si>
+  <si>
+    <t>12.06.202661</t>
+  </si>
+  <si>
+    <t>12.06.202662</t>
+  </si>
+  <si>
+    <t>12.06.202663</t>
+  </si>
+  <si>
+    <t>12.06.202664</t>
+  </si>
+  <si>
+    <t>12.06.202665</t>
+  </si>
+  <si>
+    <t>12.06.202666</t>
+  </si>
+  <si>
+    <t>12.06.202667</t>
+  </si>
+  <si>
+    <t>12.06.202668</t>
+  </si>
+  <si>
+    <t>12.06.202669</t>
+  </si>
+  <si>
+    <t>12.06.202670</t>
+  </si>
+  <si>
+    <t>12.06.202671</t>
+  </si>
+  <si>
+    <t>12.06.202672</t>
+  </si>
+  <si>
+    <t>12.06.202673</t>
+  </si>
+  <si>
+    <t>12.06.202674</t>
+  </si>
+  <si>
+    <t>12.06.202675</t>
+  </si>
+  <si>
+    <t>12.06.202676</t>
+  </si>
+  <si>
+    <t>12.06.202677</t>
+  </si>
+  <si>
+    <t>12.06.202678</t>
+  </si>
+  <si>
+    <t>12.06.202679</t>
+  </si>
+  <si>
+    <t>12.06.202680</t>
+  </si>
+  <si>
+    <t>12.06.202681</t>
+  </si>
+  <si>
+    <t>12.06.202682</t>
+  </si>
+  <si>
+    <t>12.06.202683</t>
+  </si>
+  <si>
+    <t>12.06.202684</t>
+  </si>
+  <si>
+    <t>12.06.202685</t>
+  </si>
+  <si>
+    <t>12.06.202686</t>
+  </si>
+  <si>
+    <t>12.06.202687</t>
+  </si>
+  <si>
+    <t>12.06.202688</t>
+  </si>
+  <si>
+    <t>12.06.202689</t>
+  </si>
+  <si>
+    <t>12.06.202690</t>
+  </si>
+  <si>
+    <t>12.06.202691</t>
+  </si>
+  <si>
+    <t>12.06.202692</t>
+  </si>
+  <si>
+    <t>12.06.202693</t>
+  </si>
+  <si>
+    <t>12.06.202694</t>
+  </si>
+  <si>
+    <t>12.06.202695</t>
+  </si>
+  <si>
+    <t>12.06.202696</t>
   </si>
 </sst>
 </file>
@@ -988,10 +988,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2">
-        <v>7.87</v>
+        <v>0.87</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46176.01041666666</v>
+        <v>46184.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46176.02083333334</v>
+        <v>46184.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46176.03125</v>
+        <v>46184.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46176.04166666666</v>
+        <v>46184.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46176.05208333334</v>
+        <v>46184.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46176.0625</v>
+        <v>46184.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46176.07291666666</v>
+        <v>46184.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46176.08333333334</v>
+        <v>46184.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46176.09375</v>
+        <v>46184.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46176.10416666666</v>
+        <v>46184.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46176.11458333334</v>
+        <v>46184.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46176.125</v>
+        <v>46184.125</v>
       </c>
       <c r="B14">
-        <v>7.906</v>
+        <v>2.97</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46176.13541666666</v>
+        <v>46184.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>3.071</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46176.14583333334</v>
+        <v>46184.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.91</v>
+        <v>2.975</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1243,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46176.15625</v>
+        <v>46184.15625</v>
       </c>
       <c r="B17">
-        <v>7.916</v>
+        <v>2.98</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46176.16666666666</v>
+        <v>46184.16666666666</v>
       </c>
       <c r="B18">
-        <v>8.582000000000001</v>
+        <v>3.773</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46176.17708333334</v>
+        <v>46184.17708333334</v>
       </c>
       <c r="B19">
-        <v>8.593</v>
+        <v>5.723</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46176.1875</v>
+        <v>46184.1875</v>
       </c>
       <c r="B20">
-        <v>9.085000000000001</v>
+        <v>14.896</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46176.19791666666</v>
+        <v>46184.19791666666</v>
       </c>
       <c r="B21">
-        <v>23.247</v>
+        <v>40.535</v>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46176.20833333334</v>
+        <v>46184.20833333334</v>
       </c>
       <c r="B22">
-        <v>71.167</v>
+        <v>107.824</v>
       </c>
       <c r="C22">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46176.21875</v>
+        <v>46184.21875</v>
       </c>
       <c r="B23">
-        <v>119.167</v>
+        <v>178.212</v>
       </c>
       <c r="C23">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46176.22916666666</v>
+        <v>46184.22916666666</v>
       </c>
       <c r="B24">
-        <v>180.447</v>
+        <v>250.8</v>
       </c>
       <c r="C24">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46176.23958333334</v>
+        <v>46184.23958333334</v>
       </c>
       <c r="B25">
-        <v>253.76</v>
+        <v>340.601</v>
       </c>
       <c r="C25">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46176.25</v>
+        <v>46184.25</v>
       </c>
       <c r="B26">
-        <v>420.616</v>
+        <v>569.215</v>
       </c>
       <c r="C26">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46176.26041666666</v>
+        <v>46184.26041666666</v>
       </c>
       <c r="B27">
-        <v>534.889</v>
+        <v>698.995</v>
       </c>
       <c r="C27">
-        <v>494</v>
+        <v>521</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46176.27083333334</v>
+        <v>46184.27083333334</v>
       </c>
       <c r="B28">
-        <v>661.447</v>
+        <v>839.131</v>
       </c>
       <c r="C28">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46176.28125</v>
+        <v>46184.28125</v>
       </c>
       <c r="B29">
-        <v>804.793</v>
+        <v>999.223</v>
       </c>
       <c r="C29">
-        <v>771</v>
+        <v>837</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46176.29166666666</v>
+        <v>46184.29166666666</v>
       </c>
       <c r="B30">
-        <v>1085.33</v>
+        <v>1319.871</v>
       </c>
       <c r="C30">
-        <v>948</v>
+        <v>988</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46176.30208333334</v>
+        <v>46184.30208333334</v>
       </c>
       <c r="B31">
-        <v>1274.64</v>
+        <v>1476.775</v>
       </c>
       <c r="C31">
-        <v>1093</v>
+        <v>1205</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46176.3125</v>
+        <v>46184.3125</v>
       </c>
       <c r="B32">
-        <v>1442.957</v>
+        <v>1638.833</v>
       </c>
       <c r="C32">
-        <v>1270</v>
+        <v>1323</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46176.32291666666</v>
+        <v>46184.32291666666</v>
       </c>
       <c r="B33">
-        <v>1618.75</v>
+        <v>1783.191</v>
       </c>
       <c r="C33">
-        <v>1432</v>
+        <v>1400</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46176.33333333334</v>
+        <v>46184.33333333334</v>
       </c>
       <c r="B34">
-        <v>1909.895</v>
+        <v>2025.088</v>
       </c>
       <c r="C34">
-        <v>1574</v>
+        <v>1496</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46176.34375</v>
+        <v>46184.34375</v>
       </c>
       <c r="B35">
-        <v>2046.332</v>
+        <v>2156.917</v>
       </c>
       <c r="C35">
-        <v>1661</v>
+        <v>1588</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46176.35416666666</v>
+        <v>46184.35416666666</v>
       </c>
       <c r="B36">
-        <v>2178.87</v>
+        <v>2266.495</v>
       </c>
       <c r="C36">
-        <v>1764</v>
+        <v>1672</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46176.36458333334</v>
+        <v>46184.36458333334</v>
       </c>
       <c r="B37">
-        <v>2315.831</v>
+        <v>2383.613</v>
       </c>
       <c r="C37">
-        <v>1868</v>
+        <v>1719</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46176.375</v>
+        <v>46184.375</v>
       </c>
       <c r="B38">
-        <v>2498.304</v>
+        <v>2560.415</v>
       </c>
       <c r="C38">
-        <v>1949</v>
+        <v>1689</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46176.38541666666</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="B39">
-        <v>2571.988</v>
+        <v>2610.028</v>
       </c>
       <c r="C39">
-        <v>2047</v>
+        <v>1802</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46176.39583333334</v>
+        <v>46184.39583333334</v>
       </c>
       <c r="B40">
-        <v>2664.676</v>
+        <v>2651.207</v>
       </c>
       <c r="C40">
-        <v>2138</v>
+        <v>1869</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46176.40625</v>
+        <v>46184.40625</v>
       </c>
       <c r="B41">
-        <v>2748.226</v>
+        <v>2564.83</v>
       </c>
       <c r="C41">
-        <v>2190</v>
+        <v>1892</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46176.41666666666</v>
+        <v>46184.41666666666</v>
       </c>
       <c r="B42">
-        <v>2836.032</v>
+        <v>2754.48</v>
       </c>
       <c r="C42">
-        <v>2272</v>
+        <v>1956</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46176.42708333334</v>
+        <v>46184.42708333334</v>
       </c>
       <c r="B43">
-        <v>2890.426</v>
+        <v>2783.673</v>
       </c>
       <c r="C43">
-        <v>2376</v>
+        <v>1990</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46176.4375</v>
+        <v>46184.4375</v>
       </c>
       <c r="B44">
-        <v>2939.383</v>
+        <v>2814.356</v>
       </c>
       <c r="C44">
-        <v>2403</v>
+        <v>2036</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46176.44791666666</v>
+        <v>46184.44791666666</v>
       </c>
       <c r="B45">
-        <v>2970.589</v>
+        <v>2840.081</v>
       </c>
       <c r="C45">
-        <v>2431</v>
+        <v>2079</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46176.45833333334</v>
+        <v>46184.45833333334</v>
       </c>
       <c r="B46">
-        <v>3008.015</v>
+        <v>2858.993</v>
       </c>
       <c r="C46">
-        <v>2374</v>
+        <v>2151</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46176.46875</v>
+        <v>46184.46875</v>
       </c>
       <c r="B47">
-        <v>3017.981</v>
+        <v>2878.859</v>
       </c>
       <c r="C47">
-        <v>2361</v>
+        <v>2141</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46176.47916666666</v>
+        <v>46184.47916666666</v>
       </c>
       <c r="B48">
-        <v>3032.899</v>
+        <v>2880.358</v>
       </c>
       <c r="C48">
-        <v>2371</v>
+        <v>2136</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46176.48958333334</v>
+        <v>46184.48958333334</v>
       </c>
       <c r="B49">
-        <v>3029.334</v>
+        <v>2875.162</v>
       </c>
       <c r="C49">
-        <v>2415</v>
+        <v>2158</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46176.5</v>
+        <v>46184.5</v>
       </c>
       <c r="B50">
-        <v>3022.12</v>
+        <v>2861.236</v>
       </c>
       <c r="C50">
-        <v>2407</v>
+        <v>2113</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46176.51041666666</v>
+        <v>46184.51041666666</v>
       </c>
       <c r="B51">
-        <v>3021.386</v>
+        <v>2801.252</v>
       </c>
       <c r="C51">
-        <v>2413</v>
+        <v>2133</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46176.52083333334</v>
+        <v>46184.52083333334</v>
       </c>
       <c r="B52">
-        <v>3007.524</v>
+        <v>2760.224</v>
       </c>
       <c r="C52">
-        <v>2398</v>
+        <v>2179</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46176.53125</v>
+        <v>46184.53125</v>
       </c>
       <c r="B53">
-        <v>3000.999</v>
+        <v>2733.279</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>2079</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46176.54166666666</v>
+        <v>46184.54166666666</v>
       </c>
       <c r="B54">
-        <v>2960.817</v>
+        <v>2662.72</v>
       </c>
       <c r="C54">
-        <v>2294</v>
+        <v>1967</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46176.55208333334</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="B55">
-        <v>2932.931</v>
+        <v>2624.47</v>
       </c>
       <c r="C55">
-        <v>2252</v>
+        <v>2041</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46176.5625</v>
+        <v>46184.5625</v>
       </c>
       <c r="B56">
-        <v>2884.234</v>
+        <v>2574.522</v>
       </c>
       <c r="C56">
-        <v>2222</v>
+        <v>2119</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46176.57291666666</v>
+        <v>46184.57291666666</v>
       </c>
       <c r="B57">
-        <v>2839.416</v>
+        <v>2510.656</v>
       </c>
       <c r="C57">
-        <v>2211</v>
+        <v>2129</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46176.58333333334</v>
+        <v>46184.58333333334</v>
       </c>
       <c r="B58">
-        <v>2736.148</v>
+        <v>2396.792</v>
       </c>
       <c r="C58">
-        <v>2139</v>
+        <v>2043</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46176.59375</v>
+        <v>46184.59375</v>
       </c>
       <c r="B59">
-        <v>2674.629</v>
+        <v>2324.135</v>
       </c>
       <c r="C59">
-        <v>2099</v>
+        <v>1917</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46176.60416666666</v>
+        <v>46184.60416666666</v>
       </c>
       <c r="B60">
-        <v>2613.667</v>
+        <v>2268.093</v>
       </c>
       <c r="C60">
-        <v>2053</v>
+        <v>1758</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46176.61458333334</v>
+        <v>46184.61458333334</v>
       </c>
       <c r="B61">
-        <v>2528.575</v>
+        <v>2195.349</v>
       </c>
       <c r="C61">
-        <v>1983</v>
+        <v>1698</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46176.625</v>
+        <v>46184.625</v>
       </c>
       <c r="B62">
-        <v>2364.684</v>
+        <v>1978.392</v>
       </c>
       <c r="C62">
-        <v>1932</v>
+        <v>1616</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46176.63541666666</v>
+        <v>46184.63541666666</v>
       </c>
       <c r="B63">
-        <v>2253.516</v>
+        <v>1878.66</v>
       </c>
       <c r="C63">
-        <v>1846</v>
+        <v>1433</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46176.64583333334</v>
+        <v>46184.64583333334</v>
       </c>
       <c r="B64">
-        <v>2151.525</v>
+        <v>1764.05</v>
       </c>
       <c r="C64">
-        <v>1790</v>
+        <v>1286</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46176.65625</v>
+        <v>46184.65625</v>
       </c>
       <c r="B65">
-        <v>2046.117</v>
+        <v>1674.744</v>
       </c>
       <c r="C65">
-        <v>1665</v>
+        <v>1187</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46176.66666666666</v>
+        <v>46184.66666666666</v>
       </c>
       <c r="B66">
-        <v>1849.02</v>
+        <v>1485.289</v>
       </c>
       <c r="C66">
-        <v>1601</v>
+        <v>1140</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46176.67708333334</v>
+        <v>46184.67708333334</v>
       </c>
       <c r="B67">
-        <v>1702.592</v>
+        <v>1356.883</v>
       </c>
       <c r="C67">
-        <v>1568</v>
+        <v>1102</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46176.6875</v>
+        <v>46184.6875</v>
       </c>
       <c r="B68">
-        <v>1562.662</v>
+        <v>1227.026</v>
       </c>
       <c r="C68">
-        <v>1518</v>
+        <v>1127</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46176.69791666666</v>
+        <v>46184.69791666666</v>
       </c>
       <c r="B69">
-        <v>1433.776</v>
+        <v>1119.473</v>
       </c>
       <c r="C69">
-        <v>1369</v>
+        <v>1086</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46176.70833333334</v>
+        <v>46184.70833333334</v>
       </c>
       <c r="B70">
-        <v>1218.126</v>
+        <v>917.361</v>
       </c>
       <c r="C70">
-        <v>1156</v>
+        <v>966</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46176.71875</v>
+        <v>46184.71875</v>
       </c>
       <c r="B71">
-        <v>1078.978</v>
+        <v>808.1319999999999</v>
       </c>
       <c r="C71">
-        <v>967</v>
+        <v>770</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46176.72916666666</v>
+        <v>46184.72916666666</v>
       </c>
       <c r="B72">
-        <v>947.155</v>
+        <v>697.765</v>
       </c>
       <c r="C72">
-        <v>843</v>
+        <v>718</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46176.73958333334</v>
+        <v>46184.73958333334</v>
       </c>
       <c r="B73">
-        <v>822.497</v>
+        <v>600.343</v>
       </c>
       <c r="C73">
-        <v>686</v>
+        <v>616</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46176.75</v>
+        <v>46184.75</v>
       </c>
       <c r="B74">
-        <v>517.783</v>
+        <v>413.819</v>
       </c>
       <c r="C74">
-        <v>556</v>
+        <v>437</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46176.76041666666</v>
+        <v>46184.76041666666</v>
       </c>
       <c r="B75">
-        <v>423.076</v>
+        <v>342.954</v>
       </c>
       <c r="C75">
-        <v>424</v>
+        <v>310</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46176.77083333334</v>
+        <v>46184.77083333334</v>
       </c>
       <c r="B76">
-        <v>319.493</v>
+        <v>277.143</v>
       </c>
       <c r="C76">
-        <v>320</v>
+        <v>232</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46176.78125</v>
+        <v>46184.78125</v>
       </c>
       <c r="B77">
-        <v>244.85</v>
+        <v>222.545</v>
       </c>
       <c r="C77">
-        <v>233</v>
+        <v>170</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46176.79166666666</v>
+        <v>46184.79166666666</v>
       </c>
       <c r="B78">
-        <v>181.198</v>
+        <v>129.789</v>
       </c>
       <c r="C78">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46176.80208333334</v>
+        <v>46184.80208333334</v>
       </c>
       <c r="B79">
-        <v>93.485</v>
+        <v>90.511</v>
       </c>
       <c r="C79">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46176.8125</v>
+        <v>46184.8125</v>
       </c>
       <c r="B80">
-        <v>60.765</v>
+        <v>51.691</v>
       </c>
       <c r="C80">
         <v>33</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46176.82291666666</v>
+        <v>46184.82291666666</v>
       </c>
       <c r="B81">
-        <v>45.595</v>
+        <v>43.937</v>
       </c>
       <c r="C81">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46176.83333333334</v>
+        <v>46184.83333333334</v>
       </c>
       <c r="B82">
-        <v>21.306</v>
+        <v>29.833</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46176.84375</v>
+        <v>46184.84375</v>
       </c>
       <c r="B83">
-        <v>20.123</v>
+        <v>25.971</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46176.85416666666</v>
+        <v>46184.85416666666</v>
       </c>
       <c r="B84">
-        <v>16.479</v>
+        <v>13.884</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46176.86458333334</v>
+        <v>46184.86458333334</v>
       </c>
       <c r="B85">
-        <v>15.972</v>
+        <v>11.589</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46176.875</v>
+        <v>46184.875</v>
       </c>
       <c r="B86">
-        <v>16.77</v>
+        <v>5.44</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46176.88541666666</v>
+        <v>46184.88541666666</v>
       </c>
       <c r="B87">
-        <v>9.369999999999999</v>
+        <v>5.14</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46176.89583333334</v>
+        <v>46184.89583333334</v>
       </c>
       <c r="B88">
-        <v>5.47</v>
+        <v>1.97</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46176.90625</v>
+        <v>46184.90625</v>
       </c>
       <c r="B89">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46176.91666666666</v>
+        <v>46184.91666666666</v>
       </c>
       <c r="B90">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46176.92708333334</v>
+        <v>46184.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46176.9375</v>
+        <v>46184.9375</v>
       </c>
       <c r="B92">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2535,7 +2535,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46176.94791666666</v>
+        <v>46184.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46176.95833333334</v>
+        <v>46184.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46176.96875</v>
+        <v>46184.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46176.97916666666</v>
+        <v>46184.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46176.98958333334</v>
+        <v>46184.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46177.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46177.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46177.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46177.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46177.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46177.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46177.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46177.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46177.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46177.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46177.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46177.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B110">
-        <v>0.923</v>
+        <v>0</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46177.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46177.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B112">
-        <v>0.925</v>
+        <v>0</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46177.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B113">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46177.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B114">
-        <v>3.178</v>
+        <v>3.293</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46177.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B115">
-        <v>5.278</v>
+        <v>5.392</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46177.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B116">
-        <v>8.891999999999999</v>
+        <v>9.302</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46177.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B117">
-        <v>36.685</v>
+        <v>17.863</v>
       </c>
       <c r="C117">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46177.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B118">
-        <v>86.614</v>
+        <v>42.815</v>
       </c>
       <c r="C118">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46177.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B119">
-        <v>132.334</v>
+        <v>64.71899999999999</v>
       </c>
       <c r="C119">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46177.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B120">
-        <v>187.038</v>
+        <v>82.98399999999999</v>
       </c>
       <c r="C120">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46177.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B121">
-        <v>246.152</v>
+        <v>113.024</v>
       </c>
       <c r="C121">
-        <v>217</v>
+        <v>51</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46177.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B122">
-        <v>364.607</v>
+        <v>219.664</v>
       </c>
       <c r="C122">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46177.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B123">
-        <v>442.84</v>
+        <v>261.166</v>
       </c>
       <c r="C123">
-        <v>376</v>
+        <v>117</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46177.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B124">
-        <v>537.058</v>
+        <v>309.121</v>
       </c>
       <c r="C124">
-        <v>473</v>
+        <v>162</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46177.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B125">
-        <v>637.4829999999999</v>
+        <v>359.079</v>
       </c>
       <c r="C125">
-        <v>553</v>
+        <v>217</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46177.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B126">
-        <v>835.261</v>
+        <v>489.931</v>
       </c>
       <c r="C126">
-        <v>680</v>
+        <v>274</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46177.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B127">
-        <v>938.8869999999999</v>
+        <v>546.272</v>
       </c>
       <c r="C127">
-        <v>705</v>
+        <v>340</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46177.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B128">
-        <v>1047.256</v>
+        <v>604.856</v>
       </c>
       <c r="C128">
-        <v>773</v>
+        <v>410</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46177.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B129">
-        <v>1160.5</v>
+        <v>661.397</v>
       </c>
       <c r="C129">
-        <v>823</v>
+        <v>458</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46177.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B130">
-        <v>1380.657</v>
+        <v>756.39</v>
       </c>
       <c r="C130">
-        <v>938</v>
+        <v>531</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46177.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B131">
-        <v>1467.426</v>
+        <v>830.153</v>
       </c>
       <c r="C131">
-        <v>948</v>
+        <v>593</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46177.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B132">
-        <v>1570.601</v>
+        <v>873.244</v>
       </c>
       <c r="C132">
-        <v>1049</v>
+        <v>708</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46177.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B133">
-        <v>1671.266</v>
+        <v>948.851</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46177.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B134">
-        <v>1732.942</v>
+        <v>1075.032</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46177.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B135">
-        <v>1822.522</v>
+        <v>1126.605</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>939</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46177.39583333334</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B136">
-        <v>1910.707</v>
+        <v>1189.231</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1053</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46177.40625</v>
+        <v>46185.40625</v>
       </c>
       <c r="B137">
-        <v>1978.593</v>
+        <v>1243.119</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46177.41666666666</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B138">
-        <v>2071.251</v>
+        <v>1322.465</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1077</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46177.42708333334</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B139">
-        <v>2124.384</v>
+        <v>1379.364</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1079</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46177.4375</v>
+        <v>46185.4375</v>
       </c>
       <c r="B140">
-        <v>2178.49</v>
+        <v>1427.311</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>1085</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3351,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46177.44791666666</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B141">
-        <v>2216.083</v>
+        <v>1469.814</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1181</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46177.45833333334</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B142">
-        <v>2227.837</v>
+        <v>1525.098</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1194</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3385,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46177.46875</v>
+        <v>46185.46875</v>
       </c>
       <c r="B143">
-        <v>2262.753</v>
+        <v>1557.01</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1334</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3402,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46177.47916666666</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B144">
-        <v>2293.698</v>
+        <v>1583.906</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3419,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46177.48958333334</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B145">
-        <v>2309.015</v>
+        <v>1601.778</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1351</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +3436,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46177.5</v>
+        <v>46185.5</v>
       </c>
       <c r="B146">
-        <v>2306.541</v>
+        <v>1661.671</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1391</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +3453,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46177.51041666666</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B147">
-        <v>2276.251</v>
+        <v>1671.377</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +3470,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46177.52083333334</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B148">
-        <v>2265.215</v>
+        <v>1665.194</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1491</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,13 +3487,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46177.53125</v>
+        <v>46185.53125</v>
       </c>
       <c r="B149">
-        <v>2246.226</v>
+        <v>1656.035</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1394</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46177.54166666666</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B150">
-        <v>2172.875</v>
+        <v>1649.553</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46177.55208333334</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B151">
-        <v>2124.795</v>
+        <v>1631.125</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46177.5625</v>
+        <v>46185.5625</v>
       </c>
       <c r="B152">
-        <v>2093.798</v>
+        <v>1607.809</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46177.57291666666</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B153">
-        <v>2059.32</v>
+        <v>1602.644</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46177.58333333334</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B154">
-        <v>1962.944</v>
+        <v>1557.81</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46177.59375</v>
+        <v>46185.59375</v>
       </c>
       <c r="B155">
-        <v>1864.926</v>
+        <v>1526.775</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46177.60416666666</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B156">
-        <v>1805.379</v>
+        <v>1482.471</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46177.61458333334</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B157">
-        <v>1735.78</v>
+        <v>1449.03</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46177.625</v>
+        <v>46185.625</v>
       </c>
       <c r="B158">
-        <v>1563.127</v>
+        <v>1377.612</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46177.63541666666</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B159">
-        <v>1528.098</v>
+        <v>1354.843</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46177.64583333334</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B160">
-        <v>1448.997</v>
+        <v>1311.978</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46177.65625</v>
+        <v>46185.65625</v>
       </c>
       <c r="B161">
-        <v>1375.085</v>
+        <v>1267.502</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46177.66666666666</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B162">
-        <v>1229.609</v>
+        <v>1168.767</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46177.67708333334</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B163">
-        <v>1114.591</v>
+        <v>1111.084</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46177.6875</v>
+        <v>46185.6875</v>
       </c>
       <c r="B164">
-        <v>1009.559</v>
+        <v>1046.37</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46177.69791666666</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B165">
-        <v>923.446</v>
+        <v>965.842</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46177.70833333334</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B166">
-        <v>760.633</v>
+        <v>822.88</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46177.71875</v>
+        <v>46185.71875</v>
       </c>
       <c r="B167">
-        <v>669.958</v>
+        <v>734.208</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46177.72916666666</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B168">
-        <v>580.429</v>
+        <v>628.231</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46177.73958333334</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B169">
-        <v>508.399</v>
+        <v>544.273</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46177.75</v>
+        <v>46185.75</v>
       </c>
       <c r="B170">
-        <v>360.224</v>
+        <v>394.39</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46177.76041666666</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B171">
-        <v>291.82</v>
+        <v>319.836</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46177.77083333334</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B172">
-        <v>224.98</v>
+        <v>246.552</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46177.78125</v>
+        <v>46185.78125</v>
       </c>
       <c r="B173">
-        <v>175.776</v>
+        <v>187.567</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46177.79166666666</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B174">
-        <v>106.536</v>
+        <v>110.819</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46177.80208333334</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B175">
-        <v>67.218</v>
+        <v>78.533</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46177.8125</v>
+        <v>46185.8125</v>
       </c>
       <c r="B176">
-        <v>41.759</v>
+        <v>52.988</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46177.82291666666</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B177">
-        <v>25.535</v>
+        <v>39.561</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46177.83333333334</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B178">
-        <v>15.18</v>
+        <v>14.654</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46177.84375</v>
+        <v>46185.84375</v>
       </c>
       <c r="B179">
-        <v>14.105</v>
+        <v>12.052</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46177.85416666666</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B180">
-        <v>12.219</v>
+        <v>11.471</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46177.86458333334</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B181">
-        <v>11.529</v>
+        <v>10.679</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46177.875</v>
+        <v>46185.875</v>
       </c>
       <c r="B182">
-        <v>9.970000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46177.88541666666</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B183">
-        <v>4.97</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46177.89583333334</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B184">
-        <v>3.37</v>
+        <v>1.47</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46177.90625</v>
+        <v>46185.90625</v>
       </c>
       <c r="B185">
-        <v>1.77</v>
+        <v>0.87</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46177.91666666666</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B186">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46177.92708333334</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46177.9375</v>
+        <v>46185.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46177.94791666666</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>0.874</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46177.95833333334</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46177.96875</v>
+        <v>46185.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46177.97916666666</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46177.98958333334</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,580 +31,562 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.06.20261</t>
-  </si>
-  <si>
-    <t>11.06.20262</t>
-  </si>
-  <si>
-    <t>11.06.20263</t>
-  </si>
-  <si>
-    <t>11.06.20264</t>
-  </si>
-  <si>
-    <t>11.06.20265</t>
-  </si>
-  <si>
-    <t>11.06.20266</t>
-  </si>
-  <si>
-    <t>11.06.20267</t>
-  </si>
-  <si>
-    <t>11.06.20268</t>
-  </si>
-  <si>
-    <t>11.06.20269</t>
-  </si>
-  <si>
-    <t>11.06.202610</t>
-  </si>
-  <si>
-    <t>11.06.202611</t>
-  </si>
-  <si>
-    <t>11.06.202612</t>
-  </si>
-  <si>
-    <t>11.06.202613</t>
-  </si>
-  <si>
-    <t>11.06.202614</t>
-  </si>
-  <si>
-    <t>11.06.202615</t>
-  </si>
-  <si>
-    <t>11.06.202616</t>
-  </si>
-  <si>
-    <t>11.06.202617</t>
-  </si>
-  <si>
-    <t>11.06.202618</t>
-  </si>
-  <si>
-    <t>11.06.202619</t>
-  </si>
-  <si>
-    <t>11.06.202620</t>
-  </si>
-  <si>
-    <t>11.06.202621</t>
-  </si>
-  <si>
-    <t>11.06.202622</t>
-  </si>
-  <si>
-    <t>11.06.202623</t>
-  </si>
-  <si>
-    <t>11.06.202624</t>
-  </si>
-  <si>
-    <t>11.06.202625</t>
-  </si>
-  <si>
-    <t>11.06.202626</t>
-  </si>
-  <si>
-    <t>11.06.202627</t>
-  </si>
-  <si>
-    <t>11.06.202628</t>
-  </si>
-  <si>
-    <t>11.06.202629</t>
-  </si>
-  <si>
-    <t>11.06.202630</t>
-  </si>
-  <si>
-    <t>11.06.202631</t>
-  </si>
-  <si>
-    <t>11.06.202632</t>
-  </si>
-  <si>
-    <t>11.06.202633</t>
-  </si>
-  <si>
-    <t>11.06.202634</t>
-  </si>
-  <si>
-    <t>11.06.202635</t>
-  </si>
-  <si>
-    <t>11.06.202636</t>
-  </si>
-  <si>
-    <t>11.06.202637</t>
-  </si>
-  <si>
-    <t>11.06.202638</t>
-  </si>
-  <si>
-    <t>11.06.202639</t>
-  </si>
-  <si>
-    <t>11.06.202640</t>
-  </si>
-  <si>
-    <t>11.06.202641</t>
-  </si>
-  <si>
-    <t>11.06.202642</t>
-  </si>
-  <si>
-    <t>11.06.202643</t>
-  </si>
-  <si>
-    <t>11.06.202644</t>
-  </si>
-  <si>
-    <t>11.06.202645</t>
-  </si>
-  <si>
-    <t>11.06.202646</t>
-  </si>
-  <si>
-    <t>11.06.202647</t>
-  </si>
-  <si>
-    <t>11.06.202648</t>
-  </si>
-  <si>
-    <t>11.06.202649</t>
-  </si>
-  <si>
-    <t>11.06.202650</t>
-  </si>
-  <si>
-    <t>11.06.202651</t>
-  </si>
-  <si>
-    <t>11.06.202652</t>
-  </si>
-  <si>
-    <t>11.06.202653</t>
-  </si>
-  <si>
-    <t>11.06.202654</t>
-  </si>
-  <si>
-    <t>11.06.202655</t>
-  </si>
-  <si>
-    <t>11.06.202656</t>
-  </si>
-  <si>
-    <t>11.06.202657</t>
-  </si>
-  <si>
-    <t>11.06.202658</t>
-  </si>
-  <si>
-    <t>11.06.202659</t>
-  </si>
-  <si>
-    <t>11.06.202660</t>
-  </si>
-  <si>
-    <t>11.06.202661</t>
-  </si>
-  <si>
-    <t>11.06.202662</t>
-  </si>
-  <si>
-    <t>11.06.202663</t>
-  </si>
-  <si>
-    <t>11.06.202664</t>
-  </si>
-  <si>
-    <t>11.06.202665</t>
-  </si>
-  <si>
-    <t>11.06.202666</t>
-  </si>
-  <si>
-    <t>11.06.202667</t>
-  </si>
-  <si>
-    <t>11.06.202668</t>
-  </si>
-  <si>
-    <t>11.06.202669</t>
-  </si>
-  <si>
-    <t>11.06.202670</t>
-  </si>
-  <si>
-    <t>11.06.202671</t>
-  </si>
-  <si>
-    <t>11.06.202672</t>
-  </si>
-  <si>
-    <t>11.06.202673</t>
-  </si>
-  <si>
-    <t>11.06.202674</t>
-  </si>
-  <si>
-    <t>11.06.202675</t>
-  </si>
-  <si>
-    <t>11.06.202676</t>
-  </si>
-  <si>
-    <t>11.06.202677</t>
-  </si>
-  <si>
-    <t>11.06.202678</t>
-  </si>
-  <si>
-    <t>11.06.202679</t>
-  </si>
-  <si>
-    <t>11.06.202680</t>
-  </si>
-  <si>
-    <t>11.06.202681</t>
-  </si>
-  <si>
-    <t>11.06.202682</t>
-  </si>
-  <si>
-    <t>11.06.202683</t>
-  </si>
-  <si>
-    <t>11.06.202684</t>
-  </si>
-  <si>
-    <t>11.06.202685</t>
-  </si>
-  <si>
-    <t>11.06.202686</t>
-  </si>
-  <si>
-    <t>11.06.202687</t>
-  </si>
-  <si>
-    <t>11.06.202688</t>
-  </si>
-  <si>
-    <t>11.06.202689</t>
-  </si>
-  <si>
-    <t>11.06.202690</t>
-  </si>
-  <si>
-    <t>11.06.202691</t>
-  </si>
-  <si>
-    <t>11.06.202692</t>
-  </si>
-  <si>
-    <t>11.06.202693</t>
-  </si>
-  <si>
-    <t>11.06.202694</t>
-  </si>
-  <si>
-    <t>11.06.202695</t>
-  </si>
-  <si>
-    <t>11.06.202696</t>
-  </si>
-  <si>
-    <t>12.06.20261</t>
-  </si>
-  <si>
-    <t>12.06.20262</t>
-  </si>
-  <si>
-    <t>12.06.20263</t>
-  </si>
-  <si>
-    <t>12.06.20264</t>
-  </si>
-  <si>
-    <t>12.06.20265</t>
-  </si>
-  <si>
-    <t>12.06.20266</t>
-  </si>
-  <si>
-    <t>12.06.20267</t>
-  </si>
-  <si>
-    <t>12.06.20268</t>
-  </si>
-  <si>
-    <t>12.06.20269</t>
-  </si>
-  <si>
-    <t>12.06.202610</t>
-  </si>
-  <si>
-    <t>12.06.202611</t>
-  </si>
-  <si>
-    <t>12.06.202612</t>
-  </si>
-  <si>
-    <t>12.06.202613</t>
-  </si>
-  <si>
-    <t>12.06.202614</t>
-  </si>
-  <si>
-    <t>12.06.202615</t>
-  </si>
-  <si>
-    <t>12.06.202616</t>
-  </si>
-  <si>
-    <t>12.06.202617</t>
-  </si>
-  <si>
-    <t>12.06.202618</t>
-  </si>
-  <si>
-    <t>12.06.202619</t>
-  </si>
-  <si>
-    <t>12.06.202620</t>
-  </si>
-  <si>
-    <t>12.06.202621</t>
-  </si>
-  <si>
-    <t>12.06.202622</t>
-  </si>
-  <si>
-    <t>12.06.202623</t>
-  </si>
-  <si>
-    <t>12.06.202624</t>
-  </si>
-  <si>
-    <t>12.06.202625</t>
-  </si>
-  <si>
-    <t>12.06.202626</t>
-  </si>
-  <si>
-    <t>12.06.202627</t>
-  </si>
-  <si>
-    <t>12.06.202628</t>
-  </si>
-  <si>
-    <t>12.06.202629</t>
-  </si>
-  <si>
-    <t>12.06.202630</t>
-  </si>
-  <si>
-    <t>12.06.202631</t>
-  </si>
-  <si>
-    <t>12.06.202632</t>
-  </si>
-  <si>
-    <t>12.06.202633</t>
-  </si>
-  <si>
-    <t>12.06.202634</t>
-  </si>
-  <si>
-    <t>12.06.202635</t>
-  </si>
-  <si>
-    <t>12.06.202636</t>
-  </si>
-  <si>
-    <t>12.06.202637</t>
-  </si>
-  <si>
-    <t>12.06.202638</t>
-  </si>
-  <si>
-    <t>12.06.202639</t>
-  </si>
-  <si>
-    <t>12.06.202640</t>
-  </si>
-  <si>
-    <t>12.06.202641</t>
-  </si>
-  <si>
-    <t>12.06.202642</t>
-  </si>
-  <si>
-    <t>12.06.202643</t>
-  </si>
-  <si>
-    <t>12.06.202644</t>
-  </si>
-  <si>
-    <t>12.06.202645</t>
-  </si>
-  <si>
-    <t>12.06.202646</t>
-  </si>
-  <si>
-    <t>12.06.202647</t>
-  </si>
-  <si>
-    <t>12.06.202648</t>
-  </si>
-  <si>
-    <t>12.06.202649</t>
-  </si>
-  <si>
-    <t>12.06.202650</t>
-  </si>
-  <si>
-    <t>12.06.202651</t>
-  </si>
-  <si>
-    <t>12.06.202652</t>
-  </si>
-  <si>
-    <t>12.06.202653</t>
-  </si>
-  <si>
-    <t>12.06.202654</t>
-  </si>
-  <si>
-    <t>12.06.202655</t>
-  </si>
-  <si>
-    <t>12.06.202656</t>
-  </si>
-  <si>
-    <t>12.06.202657</t>
-  </si>
-  <si>
-    <t>12.06.202658</t>
-  </si>
-  <si>
-    <t>12.06.202659</t>
-  </si>
-  <si>
-    <t>12.06.202660</t>
-  </si>
-  <si>
-    <t>12.06.202661</t>
-  </si>
-  <si>
-    <t>12.06.202662</t>
-  </si>
-  <si>
-    <t>12.06.202663</t>
-  </si>
-  <si>
-    <t>12.06.202664</t>
-  </si>
-  <si>
-    <t>12.06.202665</t>
-  </si>
-  <si>
-    <t>12.06.202666</t>
-  </si>
-  <si>
-    <t>12.06.202667</t>
-  </si>
-  <si>
-    <t>12.06.202668</t>
-  </si>
-  <si>
-    <t>12.06.202669</t>
-  </si>
-  <si>
-    <t>12.06.202670</t>
-  </si>
-  <si>
-    <t>12.06.202671</t>
-  </si>
-  <si>
-    <t>12.06.202672</t>
-  </si>
-  <si>
-    <t>12.06.202673</t>
-  </si>
-  <si>
-    <t>12.06.202674</t>
-  </si>
-  <si>
-    <t>12.06.202675</t>
-  </si>
-  <si>
-    <t>12.06.202676</t>
-  </si>
-  <si>
-    <t>12.06.202677</t>
-  </si>
-  <si>
-    <t>12.06.202678</t>
-  </si>
-  <si>
-    <t>12.06.202679</t>
-  </si>
-  <si>
-    <t>12.06.202680</t>
-  </si>
-  <si>
-    <t>12.06.202681</t>
-  </si>
-  <si>
-    <t>12.06.202682</t>
-  </si>
-  <si>
-    <t>12.06.202683</t>
-  </si>
-  <si>
-    <t>12.06.202684</t>
-  </si>
-  <si>
-    <t>12.06.202685</t>
-  </si>
-  <si>
-    <t>12.06.202686</t>
-  </si>
-  <si>
-    <t>12.06.202687</t>
-  </si>
-  <si>
-    <t>12.06.202688</t>
-  </si>
-  <si>
-    <t>12.06.202689</t>
-  </si>
-  <si>
-    <t>12.06.202690</t>
-  </si>
-  <si>
-    <t>12.06.202691</t>
-  </si>
-  <si>
-    <t>12.06.202692</t>
-  </si>
-  <si>
-    <t>12.06.202693</t>
-  </si>
-  <si>
-    <t>12.06.202694</t>
-  </si>
-  <si>
-    <t>12.06.202695</t>
-  </si>
-  <si>
-    <t>12.06.202696</t>
+    <t>09.07.20261</t>
+  </si>
+  <si>
+    <t>09.07.20262</t>
+  </si>
+  <si>
+    <t>09.07.20263</t>
+  </si>
+  <si>
+    <t>09.07.20264</t>
+  </si>
+  <si>
+    <t>09.07.20265</t>
+  </si>
+  <si>
+    <t>09.07.20266</t>
+  </si>
+  <si>
+    <t>09.07.20267</t>
+  </si>
+  <si>
+    <t>09.07.20268</t>
+  </si>
+  <si>
+    <t>09.07.20269</t>
+  </si>
+  <si>
+    <t>09.07.202610</t>
+  </si>
+  <si>
+    <t>09.07.202611</t>
+  </si>
+  <si>
+    <t>09.07.202612</t>
+  </si>
+  <si>
+    <t>09.07.202613</t>
+  </si>
+  <si>
+    <t>09.07.202614</t>
+  </si>
+  <si>
+    <t>09.07.202615</t>
+  </si>
+  <si>
+    <t>09.07.202616</t>
+  </si>
+  <si>
+    <t>09.07.202617</t>
+  </si>
+  <si>
+    <t>09.07.202618</t>
+  </si>
+  <si>
+    <t>09.07.202619</t>
+  </si>
+  <si>
+    <t>09.07.202620</t>
+  </si>
+  <si>
+    <t>09.07.202621</t>
+  </si>
+  <si>
+    <t>09.07.202622</t>
+  </si>
+  <si>
+    <t>09.07.202623</t>
+  </si>
+  <si>
+    <t>09.07.202624</t>
+  </si>
+  <si>
+    <t>09.07.202625</t>
+  </si>
+  <si>
+    <t>09.07.202626</t>
+  </si>
+  <si>
+    <t>09.07.202627</t>
+  </si>
+  <si>
+    <t>09.07.202628</t>
+  </si>
+  <si>
+    <t>09.07.202629</t>
+  </si>
+  <si>
+    <t>09.07.202630</t>
+  </si>
+  <si>
+    <t>09.07.202631</t>
+  </si>
+  <si>
+    <t>09.07.202632</t>
+  </si>
+  <si>
+    <t>09.07.202633</t>
+  </si>
+  <si>
+    <t>09.07.202634</t>
+  </si>
+  <si>
+    <t>09.07.202635</t>
+  </si>
+  <si>
+    <t>09.07.202636</t>
+  </si>
+  <si>
+    <t>09.07.202637</t>
+  </si>
+  <si>
+    <t>09.07.202638</t>
+  </si>
+  <si>
+    <t>09.07.202639</t>
+  </si>
+  <si>
+    <t>09.07.202640</t>
+  </si>
+  <si>
+    <t>09.07.202641</t>
+  </si>
+  <si>
+    <t>09.07.202642</t>
+  </si>
+  <si>
+    <t>09.07.202643</t>
+  </si>
+  <si>
+    <t>09.07.202644</t>
+  </si>
+  <si>
+    <t>09.07.202645</t>
+  </si>
+  <si>
+    <t>09.07.202646</t>
+  </si>
+  <si>
+    <t>09.07.202647</t>
+  </si>
+  <si>
+    <t>09.07.202648</t>
+  </si>
+  <si>
+    <t>09.07.202649</t>
+  </si>
+  <si>
+    <t>09.07.202650</t>
+  </si>
+  <si>
+    <t>09.07.202651</t>
+  </si>
+  <si>
+    <t>09.07.202652</t>
+  </si>
+  <si>
+    <t>09.07.202653</t>
+  </si>
+  <si>
+    <t>09.07.202654</t>
+  </si>
+  <si>
+    <t>09.07.202655</t>
+  </si>
+  <si>
+    <t>09.07.202656</t>
+  </si>
+  <si>
+    <t>09.07.202657</t>
+  </si>
+  <si>
+    <t>09.07.202658</t>
+  </si>
+  <si>
+    <t>09.07.202659</t>
+  </si>
+  <si>
+    <t>09.07.202660</t>
+  </si>
+  <si>
+    <t>09.07.202661</t>
+  </si>
+  <si>
+    <t>09.07.202662</t>
+  </si>
+  <si>
+    <t>09.07.202663</t>
+  </si>
+  <si>
+    <t>09.07.202664</t>
+  </si>
+  <si>
+    <t>09.07.202665</t>
+  </si>
+  <si>
+    <t>09.07.202666</t>
+  </si>
+  <si>
+    <t>09.07.202667</t>
+  </si>
+  <si>
+    <t>09.07.202668</t>
+  </si>
+  <si>
+    <t>09.07.202669</t>
+  </si>
+  <si>
+    <t>09.07.202670</t>
+  </si>
+  <si>
+    <t>09.07.202671</t>
+  </si>
+  <si>
+    <t>09.07.202672</t>
+  </si>
+  <si>
+    <t>09.07.202673</t>
+  </si>
+  <si>
+    <t>09.07.202674</t>
+  </si>
+  <si>
+    <t>09.07.202675</t>
+  </si>
+  <si>
+    <t>09.07.202676</t>
+  </si>
+  <si>
+    <t>09.07.202677</t>
+  </si>
+  <si>
+    <t>09.07.202678</t>
+  </si>
+  <si>
+    <t>09.07.202679</t>
+  </si>
+  <si>
+    <t>09.07.202680</t>
+  </si>
+  <si>
+    <t>09.07.202681</t>
+  </si>
+  <si>
+    <t>09.07.202682</t>
+  </si>
+  <si>
+    <t>09.07.202683</t>
+  </si>
+  <si>
+    <t>09.07.202684</t>
+  </si>
+  <si>
+    <t>09.07.202685</t>
+  </si>
+  <si>
+    <t>09.07.202686</t>
+  </si>
+  <si>
+    <t>09.07.202687</t>
+  </si>
+  <si>
+    <t>09.07.202688</t>
+  </si>
+  <si>
+    <t>09.07.202689</t>
+  </si>
+  <si>
+    <t>09.07.202690</t>
+  </si>
+  <si>
+    <t>09.07.202691</t>
+  </si>
+  <si>
+    <t>09.07.202692</t>
+  </si>
+  <si>
+    <t>09.07.202693</t>
+  </si>
+  <si>
+    <t>09.07.202694</t>
+  </si>
+  <si>
+    <t>09.07.202695</t>
+  </si>
+  <si>
+    <t>09.07.202696</t>
+  </si>
+  <si>
+    <t>10.07.20261</t>
+  </si>
+  <si>
+    <t>10.07.20262</t>
+  </si>
+  <si>
+    <t>10.07.20263</t>
+  </si>
+  <si>
+    <t>10.07.20264</t>
+  </si>
+  <si>
+    <t>10.07.20265</t>
+  </si>
+  <si>
+    <t>10.07.20266</t>
+  </si>
+  <si>
+    <t>10.07.20267</t>
+  </si>
+  <si>
+    <t>10.07.20268</t>
+  </si>
+  <si>
+    <t>10.07.20269</t>
+  </si>
+  <si>
+    <t>10.07.202610</t>
+  </si>
+  <si>
+    <t>10.07.202611</t>
+  </si>
+  <si>
+    <t>10.07.202612</t>
+  </si>
+  <si>
+    <t>10.07.202613</t>
+  </si>
+  <si>
+    <t>10.07.202614</t>
+  </si>
+  <si>
+    <t>10.07.202615</t>
+  </si>
+  <si>
+    <t>10.07.202616</t>
+  </si>
+  <si>
+    <t>10.07.202617</t>
+  </si>
+  <si>
+    <t>10.07.202618</t>
+  </si>
+  <si>
+    <t>10.07.202619</t>
+  </si>
+  <si>
+    <t>10.07.202620</t>
+  </si>
+  <si>
+    <t>10.07.202621</t>
+  </si>
+  <si>
+    <t>10.07.202622</t>
+  </si>
+  <si>
+    <t>10.07.202623</t>
+  </si>
+  <si>
+    <t>10.07.202624</t>
+  </si>
+  <si>
+    <t>10.07.202625</t>
+  </si>
+  <si>
+    <t>10.07.202626</t>
+  </si>
+  <si>
+    <t>10.07.202627</t>
+  </si>
+  <si>
+    <t>10.07.202628</t>
+  </si>
+  <si>
+    <t>10.07.202629</t>
+  </si>
+  <si>
+    <t>10.07.202630</t>
+  </si>
+  <si>
+    <t>10.07.202631</t>
+  </si>
+  <si>
+    <t>10.07.202632</t>
+  </si>
+  <si>
+    <t>10.07.202633</t>
+  </si>
+  <si>
+    <t>10.07.202634</t>
+  </si>
+  <si>
+    <t>10.07.202635</t>
+  </si>
+  <si>
+    <t>10.07.202636</t>
+  </si>
+  <si>
+    <t>10.07.202637</t>
+  </si>
+  <si>
+    <t>10.07.202638</t>
+  </si>
+  <si>
+    <t>10.07.202639</t>
+  </si>
+  <si>
+    <t>10.07.202640</t>
+  </si>
+  <si>
+    <t>10.07.202641</t>
+  </si>
+  <si>
+    <t>10.07.202642</t>
+  </si>
+  <si>
+    <t>10.07.202643</t>
+  </si>
+  <si>
+    <t>10.07.202644</t>
+  </si>
+  <si>
+    <t>10.07.202645</t>
+  </si>
+  <si>
+    <t>10.07.202646</t>
+  </si>
+  <si>
+    <t>10.07.202647</t>
+  </si>
+  <si>
+    <t>10.07.202648</t>
+  </si>
+  <si>
+    <t>10.07.202649</t>
+  </si>
+  <si>
+    <t>10.07.202650</t>
+  </si>
+  <si>
+    <t>10.07.202651</t>
+  </si>
+  <si>
+    <t>10.07.202652</t>
+  </si>
+  <si>
+    <t>10.07.202653</t>
+  </si>
+  <si>
+    <t>10.07.202654</t>
+  </si>
+  <si>
+    <t>10.07.202655</t>
+  </si>
+  <si>
+    <t>10.07.202656</t>
+  </si>
+  <si>
+    <t>10.07.202657</t>
+  </si>
+  <si>
+    <t>10.07.202658</t>
+  </si>
+  <si>
+    <t>10.07.202659</t>
+  </si>
+  <si>
+    <t>10.07.202660</t>
+  </si>
+  <si>
+    <t>10.07.202661</t>
+  </si>
+  <si>
+    <t>10.07.202662</t>
+  </si>
+  <si>
+    <t>10.07.202663</t>
+  </si>
+  <si>
+    <t>10.07.202664</t>
+  </si>
+  <si>
+    <t>10.07.202665</t>
+  </si>
+  <si>
+    <t>10.07.202666</t>
+  </si>
+  <si>
+    <t>10.07.202667</t>
+  </si>
+  <si>
+    <t>10.07.202668</t>
+  </si>
+  <si>
+    <t>10.07.202669</t>
+  </si>
+  <si>
+    <t>10.07.202670</t>
+  </si>
+  <si>
+    <t>10.07.202671</t>
+  </si>
+  <si>
+    <t>10.07.202672</t>
+  </si>
+  <si>
+    <t>10.07.202673</t>
+  </si>
+  <si>
+    <t>10.07.202674</t>
+  </si>
+  <si>
+    <t>10.07.202675</t>
+  </si>
+  <si>
+    <t>10.07.202676</t>
+  </si>
+  <si>
+    <t>10.07.202677</t>
+  </si>
+  <si>
+    <t>10.07.202678</t>
+  </si>
+  <si>
+    <t>10.07.202679</t>
+  </si>
+  <si>
+    <t>10.07.202680</t>
+  </si>
+  <si>
+    <t>10.07.202681</t>
+  </si>
+  <si>
+    <t>10.07.202682</t>
+  </si>
+  <si>
+    <t>10.07.202683</t>
+  </si>
+  <si>
+    <t>10.07.202684</t>
+  </si>
+  <si>
+    <t>10.07.202685</t>
+  </si>
+  <si>
+    <t>10.07.202686</t>
+  </si>
+  <si>
+    <t>10.07.202687</t>
+  </si>
+  <si>
+    <t>10.07.202688</t>
+  </si>
+  <si>
+    <t>10.07.202689</t>
+  </si>
+  <si>
+    <t>10.07.202690</t>
   </si>
 </sst>
 </file>
@@ -966,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -988,10 +970,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46184</v>
+        <v>46212</v>
       </c>
       <c r="B2">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1005,10 +987,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46184.01041666666</v>
+        <v>46212.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1022,10 +1004,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46184.02083333334</v>
+        <v>46212.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1039,10 +1021,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46184.03125</v>
+        <v>46212.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1056,10 +1038,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46184.04166666666</v>
+        <v>46212.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1073,10 +1055,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46184.05208333334</v>
+        <v>46212.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1090,10 +1072,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46184.0625</v>
+        <v>46212.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1107,10 +1089,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46184.07291666666</v>
+        <v>46212.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1124,10 +1106,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46184.08333333334</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1141,10 +1123,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46184.09375</v>
+        <v>46212.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1158,10 +1140,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46184.10416666666</v>
+        <v>46212.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1175,10 +1157,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46184.11458333334</v>
+        <v>46212.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1192,10 +1174,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46184.125</v>
+        <v>46212.125</v>
       </c>
       <c r="B14">
-        <v>2.97</v>
+        <v>1.15</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1209,10 +1191,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46184.13541666666</v>
+        <v>46212.13541666666</v>
       </c>
       <c r="B15">
-        <v>3.071</v>
+        <v>1.15</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1226,10 +1208,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46184.14583333334</v>
+        <v>46212.14583333334</v>
       </c>
       <c r="B16">
-        <v>2.975</v>
+        <v>1.152</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1243,10 +1225,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46184.15625</v>
+        <v>46212.15625</v>
       </c>
       <c r="B17">
-        <v>2.98</v>
+        <v>1.158</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1260,10 +1242,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46184.16666666666</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B18">
-        <v>3.773</v>
+        <v>1.666</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1277,10 +1259,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46184.17708333334</v>
+        <v>46212.17708333334</v>
       </c>
       <c r="B19">
-        <v>5.723</v>
+        <v>1.754</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1294,10 +1276,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46184.1875</v>
+        <v>46212.1875</v>
       </c>
       <c r="B20">
-        <v>14.896</v>
+        <v>2.918</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1311,13 +1293,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46184.19791666666</v>
+        <v>46212.19791666666</v>
       </c>
       <c r="B21">
-        <v>40.535</v>
+        <v>7.354</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1310,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46184.20833333334</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B22">
-        <v>107.824</v>
+        <v>65.023</v>
       </c>
       <c r="C22">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1327,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46184.21875</v>
+        <v>46212.21875</v>
       </c>
       <c r="B23">
-        <v>178.212</v>
+        <v>105.725</v>
       </c>
       <c r="C23">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1344,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46184.22916666666</v>
+        <v>46212.22916666666</v>
       </c>
       <c r="B24">
-        <v>250.8</v>
+        <v>164.476</v>
       </c>
       <c r="C24">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1361,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46184.23958333334</v>
+        <v>46212.23958333334</v>
       </c>
       <c r="B25">
-        <v>340.601</v>
+        <v>232.043</v>
       </c>
       <c r="C25">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1378,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46184.25</v>
+        <v>46212.25</v>
       </c>
       <c r="B26">
-        <v>569.215</v>
+        <v>435.255</v>
       </c>
       <c r="C26">
-        <v>395</v>
+        <v>306</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1395,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46184.26041666666</v>
+        <v>46212.26041666666</v>
       </c>
       <c r="B27">
-        <v>698.995</v>
+        <v>552.554</v>
       </c>
       <c r="C27">
-        <v>521</v>
+        <v>450</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1412,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46184.27083333334</v>
+        <v>46212.27083333334</v>
       </c>
       <c r="B28">
-        <v>839.131</v>
+        <v>681.519</v>
       </c>
       <c r="C28">
-        <v>666</v>
+        <v>575</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1429,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46184.28125</v>
+        <v>46212.28125</v>
       </c>
       <c r="B29">
-        <v>999.223</v>
+        <v>848.6609999999999</v>
       </c>
       <c r="C29">
-        <v>837</v>
+        <v>768</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1446,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46184.29166666666</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B30">
-        <v>1319.871</v>
+        <v>1202.732</v>
       </c>
       <c r="C30">
-        <v>988</v>
+        <v>912</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1463,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46184.30208333334</v>
+        <v>46212.30208333334</v>
       </c>
       <c r="B31">
-        <v>1476.775</v>
+        <v>1377.478</v>
       </c>
       <c r="C31">
-        <v>1205</v>
+        <v>1151</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1480,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46184.3125</v>
+        <v>46212.3125</v>
       </c>
       <c r="B32">
-        <v>1638.833</v>
+        <v>1574.717</v>
       </c>
       <c r="C32">
-        <v>1323</v>
+        <v>1252</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1497,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46184.32291666666</v>
+        <v>46212.32291666666</v>
       </c>
       <c r="B33">
-        <v>1783.191</v>
+        <v>1755.942</v>
       </c>
       <c r="C33">
-        <v>1400</v>
+        <v>1353</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1514,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46184.33333333334</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B34">
-        <v>2025.088</v>
+        <v>2047.13</v>
       </c>
       <c r="C34">
-        <v>1496</v>
+        <v>1545</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1531,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46184.34375</v>
+        <v>46212.34375</v>
       </c>
       <c r="B35">
-        <v>2156.917</v>
+        <v>2205.002</v>
       </c>
       <c r="C35">
-        <v>1588</v>
+        <v>1779</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1548,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46184.35416666666</v>
+        <v>46212.35416666666</v>
       </c>
       <c r="B36">
-        <v>2266.495</v>
+        <v>2334.464</v>
       </c>
       <c r="C36">
-        <v>1672</v>
+        <v>1963</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1565,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46184.36458333334</v>
+        <v>46212.36458333334</v>
       </c>
       <c r="B37">
-        <v>2383.613</v>
+        <v>2479.077</v>
       </c>
       <c r="C37">
-        <v>1719</v>
+        <v>2059</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1582,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46184.375</v>
+        <v>46212.375</v>
       </c>
       <c r="B38">
-        <v>2560.415</v>
+        <v>2638.104</v>
       </c>
       <c r="C38">
-        <v>1689</v>
+        <v>2111</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1599,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46184.38541666666</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="B39">
-        <v>2610.028</v>
+        <v>2758.822</v>
       </c>
       <c r="C39">
-        <v>1802</v>
+        <v>2276</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1616,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46184.39583333334</v>
+        <v>46212.39583333334</v>
       </c>
       <c r="B40">
-        <v>2651.207</v>
+        <v>2847.861</v>
       </c>
       <c r="C40">
-        <v>1869</v>
+        <v>2312</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1633,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46184.40625</v>
+        <v>46212.40625</v>
       </c>
       <c r="B41">
-        <v>2564.83</v>
+        <v>2917.485</v>
       </c>
       <c r="C41">
-        <v>1892</v>
+        <v>2347</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1650,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46184.41666666666</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B42">
-        <v>2754.48</v>
+        <v>2947.43</v>
       </c>
       <c r="C42">
-        <v>1956</v>
+        <v>2350</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1667,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46184.42708333334</v>
+        <v>46212.42708333334</v>
       </c>
       <c r="B43">
-        <v>2783.673</v>
+        <v>2995.426</v>
       </c>
       <c r="C43">
-        <v>1990</v>
+        <v>2359</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1684,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46184.4375</v>
+        <v>46212.4375</v>
       </c>
       <c r="B44">
-        <v>2814.356</v>
+        <v>3045.006</v>
       </c>
       <c r="C44">
-        <v>2036</v>
+        <v>2422</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1701,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46184.44791666666</v>
+        <v>46212.44791666666</v>
       </c>
       <c r="B45">
-        <v>2840.081</v>
+        <v>3085.457</v>
       </c>
       <c r="C45">
-        <v>2079</v>
+        <v>2508</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1718,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46184.45833333334</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B46">
-        <v>2858.993</v>
+        <v>3096.238</v>
       </c>
       <c r="C46">
-        <v>2151</v>
+        <v>2517</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1735,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46184.46875</v>
+        <v>46212.46875</v>
       </c>
       <c r="B47">
-        <v>2878.859</v>
+        <v>3111.244</v>
       </c>
       <c r="C47">
-        <v>2141</v>
+        <v>2457</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1752,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46184.47916666666</v>
+        <v>46212.47916666666</v>
       </c>
       <c r="B48">
-        <v>2880.358</v>
+        <v>3107.565</v>
       </c>
       <c r="C48">
-        <v>2136</v>
+        <v>2452</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1769,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46184.48958333334</v>
+        <v>46212.48958333334</v>
       </c>
       <c r="B49">
-        <v>2875.162</v>
+        <v>3107.661</v>
       </c>
       <c r="C49">
-        <v>2158</v>
+        <v>2381</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1786,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46184.5</v>
+        <v>46212.5</v>
       </c>
       <c r="B50">
-        <v>2861.236</v>
+        <v>3101.935</v>
       </c>
       <c r="C50">
-        <v>2113</v>
+        <v>2326</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1803,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46184.51041666666</v>
+        <v>46212.51041666666</v>
       </c>
       <c r="B51">
-        <v>2801.252</v>
+        <v>3082.053</v>
       </c>
       <c r="C51">
-        <v>2133</v>
+        <v>2235</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1820,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46184.52083333334</v>
+        <v>46212.52083333334</v>
       </c>
       <c r="B52">
-        <v>2760.224</v>
+        <v>3068.686</v>
       </c>
       <c r="C52">
-        <v>2179</v>
+        <v>2228</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1837,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46184.53125</v>
+        <v>46212.53125</v>
       </c>
       <c r="B53">
-        <v>2733.279</v>
+        <v>3047.848</v>
       </c>
       <c r="C53">
-        <v>2079</v>
+        <v>2219</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1854,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46184.54166666666</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B54">
-        <v>2662.72</v>
+        <v>2975.266</v>
       </c>
       <c r="C54">
-        <v>1967</v>
+        <v>2272</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1871,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46184.55208333334</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="B55">
-        <v>2624.47</v>
+        <v>2929.252</v>
       </c>
       <c r="C55">
-        <v>2041</v>
+        <v>2278</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1888,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46184.5625</v>
+        <v>46212.5625</v>
       </c>
       <c r="B56">
-        <v>2574.522</v>
+        <v>2881.657</v>
       </c>
       <c r="C56">
-        <v>2119</v>
+        <v>2109</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1905,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46184.57291666666</v>
+        <v>46212.57291666666</v>
       </c>
       <c r="B57">
-        <v>2510.656</v>
+        <v>2833.709</v>
       </c>
       <c r="C57">
-        <v>2129</v>
+        <v>1987</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1922,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46184.58333333334</v>
+        <v>46212.58333333334</v>
       </c>
       <c r="B58">
-        <v>2396.792</v>
+        <v>2731.492</v>
       </c>
       <c r="C58">
-        <v>2043</v>
+        <v>1950</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1939,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46184.59375</v>
+        <v>46212.59375</v>
       </c>
       <c r="B59">
-        <v>2324.135</v>
+        <v>2653.278</v>
       </c>
       <c r="C59">
-        <v>1917</v>
+        <v>1838</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1956,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46184.60416666666</v>
+        <v>46212.60416666666</v>
       </c>
       <c r="B60">
-        <v>2268.093</v>
+        <v>2551.632</v>
       </c>
       <c r="C60">
-        <v>1758</v>
+        <v>1817</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1973,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46184.61458333334</v>
+        <v>46212.61458333334</v>
       </c>
       <c r="B61">
-        <v>2195.349</v>
+        <v>2465.028</v>
       </c>
       <c r="C61">
-        <v>1698</v>
+        <v>1801</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +1990,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46184.625</v>
+        <v>46212.625</v>
       </c>
       <c r="B62">
-        <v>1978.392</v>
+        <v>2287.231</v>
       </c>
       <c r="C62">
-        <v>1616</v>
+        <v>1517</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2007,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46184.63541666666</v>
+        <v>46212.63541666666</v>
       </c>
       <c r="B63">
-        <v>1878.66</v>
+        <v>2147.844</v>
       </c>
       <c r="C63">
-        <v>1433</v>
+        <v>1519</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2024,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46184.64583333334</v>
+        <v>46212.64583333334</v>
       </c>
       <c r="B64">
-        <v>1764.05</v>
+        <v>2025.431</v>
       </c>
       <c r="C64">
-        <v>1286</v>
+        <v>1405</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2041,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46184.65625</v>
+        <v>46212.65625</v>
       </c>
       <c r="B65">
-        <v>1674.744</v>
+        <v>1901.31</v>
       </c>
       <c r="C65">
-        <v>1187</v>
+        <v>1322</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2058,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46184.66666666666</v>
+        <v>46212.66666666666</v>
       </c>
       <c r="B66">
-        <v>1485.289</v>
+        <v>1717.472</v>
       </c>
       <c r="C66">
-        <v>1140</v>
+        <v>1172</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2075,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46184.67708333334</v>
+        <v>46212.67708333334</v>
       </c>
       <c r="B67">
-        <v>1356.883</v>
+        <v>1550.758</v>
       </c>
       <c r="C67">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2092,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46184.6875</v>
+        <v>46212.6875</v>
       </c>
       <c r="B68">
-        <v>1227.026</v>
+        <v>1432.556</v>
       </c>
       <c r="C68">
-        <v>1127</v>
+        <v>1005</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2109,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46184.69791666666</v>
+        <v>46212.69791666666</v>
       </c>
       <c r="B69">
-        <v>1119.473</v>
+        <v>1309.632</v>
       </c>
       <c r="C69">
-        <v>1086</v>
+        <v>907</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2126,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46184.70833333334</v>
+        <v>46212.70833333334</v>
       </c>
       <c r="B70">
-        <v>917.361</v>
+        <v>1089.468</v>
       </c>
       <c r="C70">
-        <v>966</v>
+        <v>848</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2143,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46184.71875</v>
+        <v>46212.71875</v>
       </c>
       <c r="B71">
-        <v>808.1319999999999</v>
+        <v>977.509</v>
       </c>
       <c r="C71">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2160,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46184.72916666666</v>
+        <v>46212.72916666666</v>
       </c>
       <c r="B72">
-        <v>697.765</v>
+        <v>856.359</v>
       </c>
       <c r="C72">
-        <v>718</v>
+        <v>675</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2177,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46184.73958333334</v>
+        <v>46212.73958333334</v>
       </c>
       <c r="B73">
-        <v>600.343</v>
+        <v>749.4880000000001</v>
       </c>
       <c r="C73">
-        <v>616</v>
+        <v>570</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2194,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46184.75</v>
+        <v>46212.75</v>
       </c>
       <c r="B74">
-        <v>413.819</v>
+        <v>542.937</v>
       </c>
       <c r="C74">
-        <v>437</v>
+        <v>536</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2211,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46184.76041666666</v>
+        <v>46212.76041666666</v>
       </c>
       <c r="B75">
-        <v>342.954</v>
+        <v>445.39</v>
       </c>
       <c r="C75">
-        <v>310</v>
+        <v>466</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2228,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46184.77083333334</v>
+        <v>46212.77083333334</v>
       </c>
       <c r="B76">
-        <v>277.143</v>
+        <v>355.677</v>
       </c>
       <c r="C76">
-        <v>232</v>
+        <v>383</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2245,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46184.78125</v>
+        <v>46212.78125</v>
       </c>
       <c r="B77">
-        <v>222.545</v>
+        <v>282.304</v>
       </c>
       <c r="C77">
-        <v>170</v>
+        <v>294</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2262,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46184.79166666666</v>
+        <v>46212.79166666666</v>
       </c>
       <c r="B78">
-        <v>129.789</v>
+        <v>158.785</v>
       </c>
       <c r="C78">
-        <v>116</v>
+        <v>185</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2279,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46184.80208333334</v>
+        <v>46212.80208333334</v>
       </c>
       <c r="B79">
-        <v>90.511</v>
+        <v>110.374</v>
       </c>
       <c r="C79">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2296,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46184.8125</v>
+        <v>46212.8125</v>
       </c>
       <c r="B80">
-        <v>51.691</v>
+        <v>75.53400000000001</v>
       </c>
       <c r="C80">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2313,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46184.82291666666</v>
+        <v>46212.82291666666</v>
       </c>
       <c r="B81">
-        <v>43.937</v>
+        <v>48.029</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,10 +2330,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46184.83333333334</v>
+        <v>46212.83333333334</v>
       </c>
       <c r="B82">
-        <v>29.833</v>
+        <v>24.625</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2365,10 +2347,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46184.84375</v>
+        <v>46212.84375</v>
       </c>
       <c r="B83">
-        <v>25.971</v>
+        <v>22.449</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2382,10 +2364,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46184.85416666666</v>
+        <v>46212.85416666666</v>
       </c>
       <c r="B84">
-        <v>13.884</v>
+        <v>22.465</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2399,10 +2381,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46184.86458333334</v>
+        <v>46212.86458333334</v>
       </c>
       <c r="B85">
-        <v>11.589</v>
+        <v>19.753</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2416,10 +2398,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46184.875</v>
+        <v>46212.875</v>
       </c>
       <c r="B86">
-        <v>5.44</v>
+        <v>12.42</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2433,10 +2415,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46184.88541666666</v>
+        <v>46212.88541666666</v>
       </c>
       <c r="B87">
-        <v>5.14</v>
+        <v>12.22</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2432,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46184.89583333334</v>
+        <v>46212.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.97</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2449,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46184.90625</v>
+        <v>46212.90625</v>
       </c>
       <c r="B89">
-        <v>1.37</v>
+        <v>6.55</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2466,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46184.91666666666</v>
+        <v>46212.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2483,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46184.92708333334</v>
+        <v>46212.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,10 +2500,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46184.9375</v>
+        <v>46212.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2535,10 +2517,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46184.94791666666</v>
+        <v>46212.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2552,10 +2534,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46184.95833333334</v>
+        <v>46212.95833333334</v>
       </c>
       <c r="B94">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,10 +2551,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46184.96875</v>
+        <v>46212.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2586,10 +2568,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46184.97916666666</v>
+        <v>46212.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2603,10 +2585,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46184.98958333334</v>
+        <v>46212.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2620,10 +2602,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46185</v>
+        <v>46213</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2637,10 +2619,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46185.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2654,10 +2636,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2671,10 +2653,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46185.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2688,10 +2670,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2705,10 +2687,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2722,10 +2704,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46185.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2739,10 +2721,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -2756,10 +2738,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46185.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2773,10 +2755,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46185.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2790,10 +2772,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46185.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2807,10 +2789,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46185.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2824,10 +2806,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46185.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,10 +2823,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46185.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2858,10 +2840,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46185.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2875,10 +2857,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46185.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2874,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46185.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B114">
-        <v>3.293</v>
+        <v>14.954</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2891,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46185.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B115">
-        <v>5.392</v>
+        <v>15.692</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2908,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46185.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B116">
-        <v>9.302</v>
+        <v>17.438</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,13 +2925,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46185.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B117">
-        <v>17.863</v>
+        <v>23.994</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2942,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46185.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B118">
-        <v>42.815</v>
+        <v>122.738</v>
       </c>
       <c r="C118">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2959,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46185.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B119">
-        <v>64.71899999999999</v>
+        <v>168.983</v>
       </c>
       <c r="C119">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2976,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46185.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B120">
-        <v>82.98399999999999</v>
+        <v>237.35</v>
       </c>
       <c r="C120">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +2993,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46185.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B121">
-        <v>113.024</v>
+        <v>313.052</v>
       </c>
       <c r="C121">
-        <v>51</v>
+        <v>217</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3010,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46185.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B122">
-        <v>219.664</v>
+        <v>525.246</v>
       </c>
       <c r="C122">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3027,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46185.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B123">
-        <v>261.166</v>
+        <v>641.347</v>
       </c>
       <c r="C123">
-        <v>117</v>
+        <v>463</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3044,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46185.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B124">
-        <v>309.121</v>
+        <v>790.361</v>
       </c>
       <c r="C124">
-        <v>162</v>
+        <v>612</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3061,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46185.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B125">
-        <v>359.079</v>
+        <v>950.872</v>
       </c>
       <c r="C125">
-        <v>217</v>
+        <v>780</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3078,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46185.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B126">
-        <v>489.931</v>
+        <v>1289.762</v>
       </c>
       <c r="C126">
-        <v>274</v>
+        <v>967</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3095,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46185.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B127">
-        <v>546.272</v>
+        <v>1464.37</v>
       </c>
       <c r="C127">
-        <v>340</v>
+        <v>1231</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3112,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46185.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B128">
-        <v>604.856</v>
+        <v>1659.56</v>
       </c>
       <c r="C128">
-        <v>410</v>
+        <v>1495</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3129,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46185.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B129">
-        <v>661.397</v>
+        <v>1852.075</v>
       </c>
       <c r="C129">
-        <v>458</v>
+        <v>1613</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3146,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46185.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B130">
-        <v>756.39</v>
+        <v>2206.042</v>
       </c>
       <c r="C130">
-        <v>531</v>
+        <v>1749</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3163,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46185.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B131">
-        <v>830.153</v>
+        <v>2363.633</v>
       </c>
       <c r="C131">
-        <v>593</v>
+        <v>1883</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3180,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46185.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B132">
-        <v>873.244</v>
+        <v>2518.516</v>
       </c>
       <c r="C132">
-        <v>708</v>
+        <v>1870</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3197,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46185.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B133">
-        <v>948.851</v>
+        <v>2655.904</v>
       </c>
       <c r="C133">
-        <v>816</v>
+        <v>2024</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3214,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46185.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B134">
-        <v>1075.032</v>
+        <v>2827.961</v>
       </c>
       <c r="C134">
-        <v>901</v>
+        <v>2209</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3231,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46185.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B135">
-        <v>1126.605</v>
+        <v>2951.516</v>
       </c>
       <c r="C135">
-        <v>939</v>
+        <v>2369</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3248,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46185.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B136">
-        <v>1189.231</v>
+        <v>3040.449</v>
       </c>
       <c r="C136">
-        <v>1053</v>
+        <v>2340</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3265,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46185.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B137">
-        <v>1243.119</v>
+        <v>3115.045</v>
       </c>
       <c r="C137">
-        <v>1041</v>
+        <v>2420</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3282,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46185.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B138">
-        <v>1322.465</v>
+        <v>3204.687</v>
       </c>
       <c r="C138">
-        <v>1077</v>
+        <v>2475</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3299,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46185.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B139">
-        <v>1379.364</v>
+        <v>3253.648</v>
       </c>
       <c r="C139">
-        <v>1079</v>
+        <v>2589</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3316,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46185.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B140">
-        <v>1427.311</v>
+        <v>3289.358</v>
       </c>
       <c r="C140">
-        <v>1085</v>
+        <v>2589</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3333,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46185.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B141">
-        <v>1469.814</v>
+        <v>3309.379</v>
       </c>
       <c r="C141">
-        <v>1181</v>
+        <v>2576</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3350,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46185.45833333334</v>
+        <v>46213.45833333334</v>
       </c>
       <c r="B142">
-        <v>1525.098</v>
-      </c>
-      <c r="C142">
-        <v>1194</v>
+        <v>3294.918</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3364,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46185.46875</v>
+        <v>46213.46875</v>
       </c>
       <c r="B143">
-        <v>1557.01</v>
-      </c>
-      <c r="C143">
-        <v>1334</v>
+        <v>3302.598</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3378,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46185.47916666666</v>
+        <v>46213.47916666666</v>
       </c>
       <c r="B144">
-        <v>1583.906</v>
-      </c>
-      <c r="C144">
-        <v>1375</v>
+        <v>3308.605</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3392,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46185.48958333334</v>
+        <v>46213.48958333334</v>
       </c>
       <c r="B145">
-        <v>1601.778</v>
-      </c>
-      <c r="C145">
-        <v>1351</v>
+        <v>3304.786</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +3406,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46185.5</v>
+        <v>46213.5</v>
       </c>
       <c r="B146">
-        <v>1661.671</v>
-      </c>
-      <c r="C146">
-        <v>1391</v>
+        <v>3300.627</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +3420,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46185.51041666666</v>
+        <v>46213.51041666666</v>
       </c>
       <c r="B147">
-        <v>1671.377</v>
-      </c>
-      <c r="C147">
-        <v>1500</v>
+        <v>3269.841</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +3434,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46185.52083333334</v>
+        <v>46213.52083333334</v>
       </c>
       <c r="B148">
-        <v>1665.194</v>
-      </c>
-      <c r="C148">
-        <v>1491</v>
+        <v>3239.349</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,13 +3448,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46185.53125</v>
+        <v>46213.53125</v>
       </c>
       <c r="B149">
-        <v>1656.035</v>
-      </c>
-      <c r="C149">
-        <v>1394</v>
+        <v>3216.597</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3504,13 +3462,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46185.54166666666</v>
+        <v>46213.54166666666</v>
       </c>
       <c r="B150">
-        <v>1649.553</v>
-      </c>
-      <c r="C150">
-        <v>0</v>
+        <v>3148.549</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3521,13 +3476,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46185.55208333334</v>
+        <v>46213.55208333334</v>
       </c>
       <c r="B151">
-        <v>1631.125</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
+        <v>3110.498</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3538,13 +3490,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46185.5625</v>
+        <v>46213.5625</v>
       </c>
       <c r="B152">
-        <v>1607.809</v>
-      </c>
-      <c r="C152">
-        <v>0</v>
+        <v>3059.445</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3555,13 +3504,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46185.57291666666</v>
+        <v>46213.57291666666</v>
       </c>
       <c r="B153">
-        <v>1602.644</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
+        <v>3015.139</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3572,13 +3518,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46185.58333333334</v>
+        <v>46213.58333333334</v>
       </c>
       <c r="B154">
-        <v>1557.81</v>
-      </c>
-      <c r="C154">
-        <v>0</v>
+        <v>2915.779</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3589,13 +3532,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46185.59375</v>
+        <v>46213.59375</v>
       </c>
       <c r="B155">
-        <v>1526.775</v>
-      </c>
-      <c r="C155">
-        <v>0</v>
+        <v>2854.252</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3606,13 +3546,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46185.60416666666</v>
+        <v>46213.60416666666</v>
       </c>
       <c r="B156">
-        <v>1482.471</v>
-      </c>
-      <c r="C156">
-        <v>0</v>
+        <v>2783.745</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3623,13 +3560,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46185.61458333334</v>
+        <v>46213.61458333334</v>
       </c>
       <c r="B157">
-        <v>1449.03</v>
-      </c>
-      <c r="C157">
-        <v>0</v>
+        <v>2699.19</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3640,13 +3574,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46185.625</v>
+        <v>46213.625</v>
       </c>
       <c r="B158">
-        <v>1377.612</v>
-      </c>
-      <c r="C158">
-        <v>0</v>
+        <v>2523.506</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3657,13 +3588,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46185.63541666666</v>
+        <v>46213.63541666666</v>
       </c>
       <c r="B159">
-        <v>1354.843</v>
-      </c>
-      <c r="C159">
-        <v>0</v>
+        <v>2381.506</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3674,13 +3602,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46185.64583333334</v>
+        <v>46213.64583333334</v>
       </c>
       <c r="B160">
-        <v>1311.978</v>
-      </c>
-      <c r="C160">
-        <v>0</v>
+        <v>2282.423</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3691,13 +3616,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46185.65625</v>
+        <v>46213.65625</v>
       </c>
       <c r="B161">
-        <v>1267.502</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
+        <v>2180.824</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3708,13 +3630,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46185.66666666666</v>
+        <v>46213.66666666666</v>
       </c>
       <c r="B162">
-        <v>1168.767</v>
-      </c>
-      <c r="C162">
-        <v>0</v>
+        <v>2040.134</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3725,13 +3644,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46185.67708333334</v>
+        <v>46213.67708333334</v>
       </c>
       <c r="B163">
-        <v>1111.084</v>
-      </c>
-      <c r="C163">
-        <v>0</v>
+        <v>1876.203</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3742,13 +3658,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46185.6875</v>
+        <v>46213.6875</v>
       </c>
       <c r="B164">
-        <v>1046.37</v>
-      </c>
-      <c r="C164">
-        <v>0</v>
+        <v>1731.938</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3759,13 +3672,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46185.69791666666</v>
+        <v>46213.69791666666</v>
       </c>
       <c r="B165">
-        <v>965.842</v>
-      </c>
-      <c r="C165">
-        <v>0</v>
+        <v>1614.036</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3776,13 +3686,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46185.70833333334</v>
+        <v>46213.70833333334</v>
       </c>
       <c r="B166">
-        <v>822.88</v>
-      </c>
-      <c r="C166">
-        <v>0</v>
+        <v>1372.754</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3793,13 +3700,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46185.71875</v>
+        <v>46213.71875</v>
       </c>
       <c r="B167">
-        <v>734.208</v>
-      </c>
-      <c r="C167">
-        <v>0</v>
+        <v>1237.355</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3810,13 +3714,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46185.72916666666</v>
+        <v>46213.72916666666</v>
       </c>
       <c r="B168">
-        <v>628.231</v>
-      </c>
-      <c r="C168">
-        <v>0</v>
+        <v>1099.279</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3827,13 +3728,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46185.73958333334</v>
+        <v>46213.73958333334</v>
       </c>
       <c r="B169">
-        <v>544.273</v>
-      </c>
-      <c r="C169">
-        <v>0</v>
+        <v>972.4349999999999</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3844,13 +3742,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46185.75</v>
+        <v>46213.75</v>
       </c>
       <c r="B170">
-        <v>394.39</v>
-      </c>
-      <c r="C170">
-        <v>0</v>
+        <v>709.034</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3861,13 +3756,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46185.76041666666</v>
+        <v>46213.76041666666</v>
       </c>
       <c r="B171">
-        <v>319.836</v>
-      </c>
-      <c r="C171">
-        <v>0</v>
+        <v>588.048</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3878,13 +3770,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46185.77083333334</v>
+        <v>46213.77083333334</v>
       </c>
       <c r="B172">
-        <v>246.552</v>
-      </c>
-      <c r="C172">
-        <v>0</v>
+        <v>474.373</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3895,13 +3784,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46185.78125</v>
+        <v>46213.78125</v>
       </c>
       <c r="B173">
-        <v>187.567</v>
-      </c>
-      <c r="C173">
-        <v>0</v>
+        <v>381.859</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3912,13 +3798,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46185.79166666666</v>
+        <v>46213.79166666666</v>
       </c>
       <c r="B174">
-        <v>110.819</v>
-      </c>
-      <c r="C174">
-        <v>0</v>
+        <v>192.719</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3929,13 +3812,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46185.80208333334</v>
+        <v>46213.80208333334</v>
       </c>
       <c r="B175">
-        <v>78.533</v>
-      </c>
-      <c r="C175">
-        <v>0</v>
+        <v>131.654</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3946,13 +3826,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46185.8125</v>
+        <v>46213.8125</v>
       </c>
       <c r="B176">
-        <v>52.988</v>
-      </c>
-      <c r="C176">
-        <v>0</v>
+        <v>79.768</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3963,13 +3840,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46185.82291666666</v>
+        <v>46213.82291666666</v>
       </c>
       <c r="B177">
-        <v>39.561</v>
-      </c>
-      <c r="C177">
-        <v>0</v>
+        <v>53.479</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3980,13 +3854,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46185.83333333334</v>
+        <v>46213.83333333334</v>
       </c>
       <c r="B178">
-        <v>14.654</v>
-      </c>
-      <c r="C178">
-        <v>0</v>
+        <v>22.899</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3997,13 +3868,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46185.84375</v>
+        <v>46213.84375</v>
       </c>
       <c r="B179">
-        <v>12.052</v>
-      </c>
-      <c r="C179">
-        <v>0</v>
+        <v>24.187</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4014,13 +3882,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46185.85416666666</v>
+        <v>46213.85416666666</v>
       </c>
       <c r="B180">
-        <v>11.471</v>
-      </c>
-      <c r="C180">
-        <v>0</v>
+        <v>23.206</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4031,13 +3896,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46185.86458333334</v>
+        <v>46213.86458333334</v>
       </c>
       <c r="B181">
-        <v>10.679</v>
-      </c>
-      <c r="C181">
-        <v>0</v>
+        <v>20.755</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4048,13 +3910,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46185.875</v>
+        <v>46213.875</v>
       </c>
       <c r="B182">
-        <v>9.94</v>
-      </c>
-      <c r="C182">
-        <v>0</v>
+        <v>18.52</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4065,13 +3924,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46185.88541666666</v>
+        <v>46213.88541666666</v>
       </c>
       <c r="B183">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="C183">
-        <v>0</v>
+        <v>17.32</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4082,13 +3938,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46185.89583333334</v>
+        <v>46213.89583333334</v>
       </c>
       <c r="B184">
-        <v>1.47</v>
-      </c>
-      <c r="C184">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4099,13 +3952,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46185.90625</v>
+        <v>46213.90625</v>
       </c>
       <c r="B185">
-        <v>0.87</v>
-      </c>
-      <c r="C185">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4116,13 +3966,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46185.91666666666</v>
+        <v>46213.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
-      </c>
-      <c r="C186">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4133,121 +3980,16 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46185.92708333334</v>
+        <v>46213.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
-      </c>
-      <c r="C187">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="D187">
         <v>90</v>
       </c>
       <c r="E187" t="s">
         <v>190</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" s="2">
-        <v>46185.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-      <c r="C188">
-        <v>0</v>
-      </c>
-      <c r="D188">
-        <v>91</v>
-      </c>
-      <c r="E188" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" s="2">
-        <v>46185.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0.874</v>
-      </c>
-      <c r="C189">
-        <v>0</v>
-      </c>
-      <c r="D189">
-        <v>92</v>
-      </c>
-      <c r="E189" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" s="2">
-        <v>46185.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-      <c r="C190">
-        <v>0</v>
-      </c>
-      <c r="D190">
-        <v>93</v>
-      </c>
-      <c r="E190" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
-      <c r="A191" s="2">
-        <v>46185.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-      <c r="C191">
-        <v>0</v>
-      </c>
-      <c r="D191">
-        <v>94</v>
-      </c>
-      <c r="E191" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" s="2">
-        <v>46185.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-      <c r="C192">
-        <v>0</v>
-      </c>
-      <c r="D192">
-        <v>95</v>
-      </c>
-      <c r="E192" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
-      <c r="A193" s="2">
-        <v>46185.98958333334</v>
-      </c>
-      <c r="B193">
-        <v>0</v>
-      </c>
-      <c r="C193">
-        <v>0</v>
-      </c>
-      <c r="D193">
-        <v>96</v>
-      </c>
-      <c r="E193" t="s">
-        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Solar_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Solar_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="383">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.07.20261</t>
-  </si>
-  <si>
-    <t>09.07.20262</t>
-  </si>
-  <si>
-    <t>09.07.20263</t>
-  </si>
-  <si>
-    <t>09.07.20264</t>
-  </si>
-  <si>
-    <t>09.07.20265</t>
-  </si>
-  <si>
-    <t>09.07.20266</t>
-  </si>
-  <si>
-    <t>09.07.20267</t>
-  </si>
-  <si>
-    <t>09.07.20268</t>
-  </si>
-  <si>
-    <t>09.07.20269</t>
-  </si>
-  <si>
-    <t>09.07.202610</t>
-  </si>
-  <si>
-    <t>09.07.202611</t>
-  </si>
-  <si>
-    <t>09.07.202612</t>
-  </si>
-  <si>
-    <t>09.07.202613</t>
-  </si>
-  <si>
-    <t>09.07.202614</t>
-  </si>
-  <si>
-    <t>09.07.202615</t>
-  </si>
-  <si>
-    <t>09.07.202616</t>
-  </si>
-  <si>
-    <t>09.07.202617</t>
-  </si>
-  <si>
-    <t>09.07.202618</t>
-  </si>
-  <si>
-    <t>09.07.202619</t>
-  </si>
-  <si>
-    <t>09.07.202620</t>
-  </si>
-  <si>
-    <t>09.07.202621</t>
-  </si>
-  <si>
-    <t>09.07.202622</t>
-  </si>
-  <si>
-    <t>09.07.202623</t>
-  </si>
-  <si>
-    <t>09.07.202624</t>
-  </si>
-  <si>
-    <t>09.07.202625</t>
-  </si>
-  <si>
-    <t>09.07.202626</t>
-  </si>
-  <si>
-    <t>09.07.202627</t>
-  </si>
-  <si>
-    <t>09.07.202628</t>
-  </si>
-  <si>
-    <t>09.07.202629</t>
-  </si>
-  <si>
-    <t>09.07.202630</t>
-  </si>
-  <si>
-    <t>09.07.202631</t>
-  </si>
-  <si>
-    <t>09.07.202632</t>
-  </si>
-  <si>
-    <t>09.07.202633</t>
-  </si>
-  <si>
-    <t>09.07.202634</t>
-  </si>
-  <si>
-    <t>09.07.202635</t>
-  </si>
-  <si>
-    <t>09.07.202636</t>
-  </si>
-  <si>
-    <t>09.07.202637</t>
-  </si>
-  <si>
-    <t>09.07.202638</t>
-  </si>
-  <si>
-    <t>09.07.202639</t>
-  </si>
-  <si>
-    <t>09.07.202640</t>
-  </si>
-  <si>
-    <t>09.07.202641</t>
-  </si>
-  <si>
-    <t>09.07.202642</t>
-  </si>
-  <si>
-    <t>09.07.202643</t>
-  </si>
-  <si>
-    <t>09.07.202644</t>
-  </si>
-  <si>
-    <t>09.07.202645</t>
-  </si>
-  <si>
-    <t>09.07.202646</t>
-  </si>
-  <si>
-    <t>09.07.202647</t>
-  </si>
-  <si>
-    <t>09.07.202648</t>
-  </si>
-  <si>
-    <t>09.07.202649</t>
-  </si>
-  <si>
-    <t>09.07.202650</t>
-  </si>
-  <si>
-    <t>09.07.202651</t>
-  </si>
-  <si>
-    <t>09.07.202652</t>
-  </si>
-  <si>
-    <t>09.07.202653</t>
-  </si>
-  <si>
-    <t>09.07.202654</t>
-  </si>
-  <si>
-    <t>09.07.202655</t>
-  </si>
-  <si>
-    <t>09.07.202656</t>
-  </si>
-  <si>
-    <t>09.07.202657</t>
-  </si>
-  <si>
-    <t>09.07.202658</t>
-  </si>
-  <si>
-    <t>09.07.202659</t>
-  </si>
-  <si>
-    <t>09.07.202660</t>
-  </si>
-  <si>
-    <t>09.07.202661</t>
-  </si>
-  <si>
-    <t>09.07.202662</t>
-  </si>
-  <si>
-    <t>09.07.202663</t>
-  </si>
-  <si>
-    <t>09.07.202664</t>
-  </si>
-  <si>
-    <t>09.07.202665</t>
-  </si>
-  <si>
-    <t>09.07.202666</t>
-  </si>
-  <si>
-    <t>09.07.202667</t>
-  </si>
-  <si>
-    <t>09.07.202668</t>
-  </si>
-  <si>
-    <t>09.07.202669</t>
-  </si>
-  <si>
-    <t>09.07.202670</t>
-  </si>
-  <si>
-    <t>09.07.202671</t>
-  </si>
-  <si>
-    <t>09.07.202672</t>
-  </si>
-  <si>
-    <t>09.07.202673</t>
-  </si>
-  <si>
-    <t>09.07.202674</t>
-  </si>
-  <si>
-    <t>09.07.202675</t>
-  </si>
-  <si>
-    <t>09.07.202676</t>
-  </si>
-  <si>
-    <t>09.07.202677</t>
-  </si>
-  <si>
-    <t>09.07.202678</t>
-  </si>
-  <si>
-    <t>09.07.202679</t>
-  </si>
-  <si>
-    <t>09.07.202680</t>
-  </si>
-  <si>
-    <t>09.07.202681</t>
-  </si>
-  <si>
-    <t>09.07.202682</t>
-  </si>
-  <si>
-    <t>09.07.202683</t>
-  </si>
-  <si>
-    <t>09.07.202684</t>
-  </si>
-  <si>
-    <t>09.07.202685</t>
-  </si>
-  <si>
-    <t>09.07.202686</t>
-  </si>
-  <si>
-    <t>09.07.202687</t>
-  </si>
-  <si>
-    <t>09.07.202688</t>
-  </si>
-  <si>
-    <t>09.07.202689</t>
-  </si>
-  <si>
-    <t>09.07.202690</t>
-  </si>
-  <si>
-    <t>09.07.202691</t>
-  </si>
-  <si>
-    <t>09.07.202692</t>
-  </si>
-  <si>
-    <t>09.07.202693</t>
-  </si>
-  <si>
-    <t>09.07.202694</t>
-  </si>
-  <si>
-    <t>09.07.202695</t>
-  </si>
-  <si>
-    <t>09.07.202696</t>
-  </si>
-  <si>
     <t>10.07.20261</t>
   </si>
   <si>
@@ -587,6 +299,870 @@
   </si>
   <si>
     <t>10.07.202690</t>
+  </si>
+  <si>
+    <t>10.07.202691</t>
+  </si>
+  <si>
+    <t>10.07.202692</t>
+  </si>
+  <si>
+    <t>10.07.202693</t>
+  </si>
+  <si>
+    <t>10.07.202694</t>
+  </si>
+  <si>
+    <t>10.07.202695</t>
+  </si>
+  <si>
+    <t>10.07.202696</t>
+  </si>
+  <si>
+    <t>11.07.20261</t>
+  </si>
+  <si>
+    <t>11.07.20262</t>
+  </si>
+  <si>
+    <t>11.07.20263</t>
+  </si>
+  <si>
+    <t>11.07.20264</t>
+  </si>
+  <si>
+    <t>11.07.20265</t>
+  </si>
+  <si>
+    <t>11.07.20266</t>
+  </si>
+  <si>
+    <t>11.07.20267</t>
+  </si>
+  <si>
+    <t>11.07.20268</t>
+  </si>
+  <si>
+    <t>11.07.20269</t>
+  </si>
+  <si>
+    <t>11.07.202610</t>
+  </si>
+  <si>
+    <t>11.07.202611</t>
+  </si>
+  <si>
+    <t>11.07.202612</t>
+  </si>
+  <si>
+    <t>11.07.202613</t>
+  </si>
+  <si>
+    <t>11.07.202614</t>
+  </si>
+  <si>
+    <t>11.07.202615</t>
+  </si>
+  <si>
+    <t>11.07.202616</t>
+  </si>
+  <si>
+    <t>11.07.202617</t>
+  </si>
+  <si>
+    <t>11.07.202618</t>
+  </si>
+  <si>
+    <t>11.07.202619</t>
+  </si>
+  <si>
+    <t>11.07.202620</t>
+  </si>
+  <si>
+    <t>11.07.202621</t>
+  </si>
+  <si>
+    <t>11.07.202622</t>
+  </si>
+  <si>
+    <t>11.07.202623</t>
+  </si>
+  <si>
+    <t>11.07.202624</t>
+  </si>
+  <si>
+    <t>11.07.202625</t>
+  </si>
+  <si>
+    <t>11.07.202626</t>
+  </si>
+  <si>
+    <t>11.07.202627</t>
+  </si>
+  <si>
+    <t>11.07.202628</t>
+  </si>
+  <si>
+    <t>11.07.202629</t>
+  </si>
+  <si>
+    <t>11.07.202630</t>
+  </si>
+  <si>
+    <t>11.07.202631</t>
+  </si>
+  <si>
+    <t>11.07.202632</t>
+  </si>
+  <si>
+    <t>11.07.202633</t>
+  </si>
+  <si>
+    <t>11.07.202634</t>
+  </si>
+  <si>
+    <t>11.07.202635</t>
+  </si>
+  <si>
+    <t>11.07.202636</t>
+  </si>
+  <si>
+    <t>11.07.202637</t>
+  </si>
+  <si>
+    <t>11.07.202638</t>
+  </si>
+  <si>
+    <t>11.07.202639</t>
+  </si>
+  <si>
+    <t>11.07.202640</t>
+  </si>
+  <si>
+    <t>11.07.202641</t>
+  </si>
+  <si>
+    <t>11.07.202642</t>
+  </si>
+  <si>
+    <t>11.07.202643</t>
+  </si>
+  <si>
+    <t>11.07.202644</t>
+  </si>
+  <si>
+    <t>11.07.202645</t>
+  </si>
+  <si>
+    <t>11.07.202646</t>
+  </si>
+  <si>
+    <t>11.07.202647</t>
+  </si>
+  <si>
+    <t>11.07.202648</t>
+  </si>
+  <si>
+    <t>11.07.202649</t>
+  </si>
+  <si>
+    <t>11.07.202650</t>
+  </si>
+  <si>
+    <t>11.07.202651</t>
+  </si>
+  <si>
+    <t>11.07.202652</t>
+  </si>
+  <si>
+    <t>11.07.202653</t>
+  </si>
+  <si>
+    <t>11.07.202654</t>
+  </si>
+  <si>
+    <t>11.07.202655</t>
+  </si>
+  <si>
+    <t>11.07.202656</t>
+  </si>
+  <si>
+    <t>11.07.202657</t>
+  </si>
+  <si>
+    <t>11.07.202658</t>
+  </si>
+  <si>
+    <t>11.07.202659</t>
+  </si>
+  <si>
+    <t>11.07.202660</t>
+  </si>
+  <si>
+    <t>11.07.202661</t>
+  </si>
+  <si>
+    <t>11.07.202662</t>
+  </si>
+  <si>
+    <t>11.07.202663</t>
+  </si>
+  <si>
+    <t>11.07.202664</t>
+  </si>
+  <si>
+    <t>11.07.202665</t>
+  </si>
+  <si>
+    <t>11.07.202666</t>
+  </si>
+  <si>
+    <t>11.07.202667</t>
+  </si>
+  <si>
+    <t>11.07.202668</t>
+  </si>
+  <si>
+    <t>11.07.202669</t>
+  </si>
+  <si>
+    <t>11.07.202670</t>
+  </si>
+  <si>
+    <t>11.07.202671</t>
+  </si>
+  <si>
+    <t>11.07.202672</t>
+  </si>
+  <si>
+    <t>11.07.202673</t>
+  </si>
+  <si>
+    <t>11.07.202674</t>
+  </si>
+  <si>
+    <t>11.07.202675</t>
+  </si>
+  <si>
+    <t>11.07.202676</t>
+  </si>
+  <si>
+    <t>11.07.202677</t>
+  </si>
+  <si>
+    <t>11.07.202678</t>
+  </si>
+  <si>
+    <t>11.07.202679</t>
+  </si>
+  <si>
+    <t>11.07.202680</t>
+  </si>
+  <si>
+    <t>11.07.202681</t>
+  </si>
+  <si>
+    <t>11.07.202682</t>
+  </si>
+  <si>
+    <t>11.07.202683</t>
+  </si>
+  <si>
+    <t>11.07.202684</t>
+  </si>
+  <si>
+    <t>11.07.202685</t>
+  </si>
+  <si>
+    <t>11.07.202686</t>
+  </si>
+  <si>
+    <t>11.07.202687</t>
+  </si>
+  <si>
+    <t>11.07.202688</t>
+  </si>
+  <si>
+    <t>11.07.202689</t>
+  </si>
+  <si>
+    <t>11.07.202690</t>
+  </si>
+  <si>
+    <t>11.07.202691</t>
+  </si>
+  <si>
+    <t>11.07.202692</t>
+  </si>
+  <si>
+    <t>11.07.202693</t>
+  </si>
+  <si>
+    <t>11.07.202694</t>
+  </si>
+  <si>
+    <t>11.07.202695</t>
+  </si>
+  <si>
+    <t>11.07.202696</t>
+  </si>
+  <si>
+    <t>12.07.20261</t>
+  </si>
+  <si>
+    <t>12.07.20262</t>
+  </si>
+  <si>
+    <t>12.07.20263</t>
+  </si>
+  <si>
+    <t>12.07.20264</t>
+  </si>
+  <si>
+    <t>12.07.20265</t>
+  </si>
+  <si>
+    <t>12.07.20266</t>
+  </si>
+  <si>
+    <t>12.07.20267</t>
+  </si>
+  <si>
+    <t>12.07.20268</t>
+  </si>
+  <si>
+    <t>12.07.20269</t>
+  </si>
+  <si>
+    <t>12.07.202610</t>
+  </si>
+  <si>
+    <t>12.07.202611</t>
+  </si>
+  <si>
+    <t>12.07.202612</t>
+  </si>
+  <si>
+    <t>12.07.202613</t>
+  </si>
+  <si>
+    <t>12.07.202614</t>
+  </si>
+  <si>
+    <t>12.07.202615</t>
+  </si>
+  <si>
+    <t>12.07.202616</t>
+  </si>
+  <si>
+    <t>12.07.202617</t>
+  </si>
+  <si>
+    <t>12.07.202618</t>
+  </si>
+  <si>
+    <t>12.07.202619</t>
+  </si>
+  <si>
+    <t>12.07.202620</t>
+  </si>
+  <si>
+    <t>12.07.202621</t>
+  </si>
+  <si>
+    <t>12.07.202622</t>
+  </si>
+  <si>
+    <t>12.07.202623</t>
+  </si>
+  <si>
+    <t>12.07.202624</t>
+  </si>
+  <si>
+    <t>12.07.202625</t>
+  </si>
+  <si>
+    <t>12.07.202626</t>
+  </si>
+  <si>
+    <t>12.07.202627</t>
+  </si>
+  <si>
+    <t>12.07.202628</t>
+  </si>
+  <si>
+    <t>12.07.202629</t>
+  </si>
+  <si>
+    <t>12.07.202630</t>
+  </si>
+  <si>
+    <t>12.07.202631</t>
+  </si>
+  <si>
+    <t>12.07.202632</t>
+  </si>
+  <si>
+    <t>12.07.202633</t>
+  </si>
+  <si>
+    <t>12.07.202634</t>
+  </si>
+  <si>
+    <t>12.07.202635</t>
+  </si>
+  <si>
+    <t>12.07.202636</t>
+  </si>
+  <si>
+    <t>12.07.202637</t>
+  </si>
+  <si>
+    <t>12.07.202638</t>
+  </si>
+  <si>
+    <t>12.07.202639</t>
+  </si>
+  <si>
+    <t>12.07.202640</t>
+  </si>
+  <si>
+    <t>12.07.202641</t>
+  </si>
+  <si>
+    <t>12.07.202642</t>
+  </si>
+  <si>
+    <t>12.07.202643</t>
+  </si>
+  <si>
+    <t>12.07.202644</t>
+  </si>
+  <si>
+    <t>12.07.202645</t>
+  </si>
+  <si>
+    <t>12.07.202646</t>
+  </si>
+  <si>
+    <t>12.07.202647</t>
+  </si>
+  <si>
+    <t>12.07.202648</t>
+  </si>
+  <si>
+    <t>12.07.202649</t>
+  </si>
+  <si>
+    <t>12.07.202650</t>
+  </si>
+  <si>
+    <t>12.07.202651</t>
+  </si>
+  <si>
+    <t>12.07.202652</t>
+  </si>
+  <si>
+    <t>12.07.202653</t>
+  </si>
+  <si>
+    <t>12.07.202654</t>
+  </si>
+  <si>
+    <t>12.07.202655</t>
+  </si>
+  <si>
+    <t>12.07.202656</t>
+  </si>
+  <si>
+    <t>12.07.202657</t>
+  </si>
+  <si>
+    <t>12.07.202658</t>
+  </si>
+  <si>
+    <t>12.07.202659</t>
+  </si>
+  <si>
+    <t>12.07.202660</t>
+  </si>
+  <si>
+    <t>12.07.202661</t>
+  </si>
+  <si>
+    <t>12.07.202662</t>
+  </si>
+  <si>
+    <t>12.07.202663</t>
+  </si>
+  <si>
+    <t>12.07.202664</t>
+  </si>
+  <si>
+    <t>12.07.202665</t>
+  </si>
+  <si>
+    <t>12.07.202666</t>
+  </si>
+  <si>
+    <t>12.07.202667</t>
+  </si>
+  <si>
+    <t>12.07.202668</t>
+  </si>
+  <si>
+    <t>12.07.202669</t>
+  </si>
+  <si>
+    <t>12.07.202670</t>
+  </si>
+  <si>
+    <t>12.07.202671</t>
+  </si>
+  <si>
+    <t>12.07.202672</t>
+  </si>
+  <si>
+    <t>12.07.202673</t>
+  </si>
+  <si>
+    <t>12.07.202674</t>
+  </si>
+  <si>
+    <t>12.07.202675</t>
+  </si>
+  <si>
+    <t>12.07.202676</t>
+  </si>
+  <si>
+    <t>12.07.202677</t>
+  </si>
+  <si>
+    <t>12.07.202678</t>
+  </si>
+  <si>
+    <t>12.07.202679</t>
+  </si>
+  <si>
+    <t>12.07.202680</t>
+  </si>
+  <si>
+    <t>12.07.202681</t>
+  </si>
+  <si>
+    <t>12.07.202682</t>
+  </si>
+  <si>
+    <t>12.07.202683</t>
+  </si>
+  <si>
+    <t>12.07.202684</t>
+  </si>
+  <si>
+    <t>12.07.202685</t>
+  </si>
+  <si>
+    <t>12.07.202686</t>
+  </si>
+  <si>
+    <t>12.07.202687</t>
+  </si>
+  <si>
+    <t>12.07.202688</t>
+  </si>
+  <si>
+    <t>12.07.202689</t>
+  </si>
+  <si>
+    <t>12.07.202690</t>
+  </si>
+  <si>
+    <t>12.07.202691</t>
+  </si>
+  <si>
+    <t>12.07.202692</t>
+  </si>
+  <si>
+    <t>12.07.202693</t>
+  </si>
+  <si>
+    <t>12.07.202694</t>
+  </si>
+  <si>
+    <t>12.07.202695</t>
+  </si>
+  <si>
+    <t>12.07.202696</t>
+  </si>
+  <si>
+    <t>13.07.20261</t>
+  </si>
+  <si>
+    <t>13.07.20262</t>
+  </si>
+  <si>
+    <t>13.07.20263</t>
+  </si>
+  <si>
+    <t>13.07.20264</t>
+  </si>
+  <si>
+    <t>13.07.20265</t>
+  </si>
+  <si>
+    <t>13.07.20266</t>
+  </si>
+  <si>
+    <t>13.07.20267</t>
+  </si>
+  <si>
+    <t>13.07.20268</t>
+  </si>
+  <si>
+    <t>13.07.20269</t>
+  </si>
+  <si>
+    <t>13.07.202610</t>
+  </si>
+  <si>
+    <t>13.07.202611</t>
+  </si>
+  <si>
+    <t>13.07.202612</t>
+  </si>
+  <si>
+    <t>13.07.202613</t>
+  </si>
+  <si>
+    <t>13.07.202614</t>
+  </si>
+  <si>
+    <t>13.07.202615</t>
+  </si>
+  <si>
+    <t>13.07.202616</t>
+  </si>
+  <si>
+    <t>13.07.202617</t>
+  </si>
+  <si>
+    <t>13.07.202618</t>
+  </si>
+  <si>
+    <t>13.07.202619</t>
+  </si>
+  <si>
+    <t>13.07.202620</t>
+  </si>
+  <si>
+    <t>13.07.202621</t>
+  </si>
+  <si>
+    <t>13.07.202622</t>
+  </si>
+  <si>
+    <t>13.07.202623</t>
+  </si>
+  <si>
+    <t>13.07.202624</t>
+  </si>
+  <si>
+    <t>13.07.202625</t>
+  </si>
+  <si>
+    <t>13.07.202626</t>
+  </si>
+  <si>
+    <t>13.07.202627</t>
+  </si>
+  <si>
+    <t>13.07.202628</t>
+  </si>
+  <si>
+    <t>13.07.202629</t>
+  </si>
+  <si>
+    <t>13.07.202630</t>
+  </si>
+  <si>
+    <t>13.07.202631</t>
+  </si>
+  <si>
+    <t>13.07.202632</t>
+  </si>
+  <si>
+    <t>13.07.202633</t>
+  </si>
+  <si>
+    <t>13.07.202634</t>
+  </si>
+  <si>
+    <t>13.07.202635</t>
+  </si>
+  <si>
+    <t>13.07.202636</t>
+  </si>
+  <si>
+    <t>13.07.202637</t>
+  </si>
+  <si>
+    <t>13.07.202638</t>
+  </si>
+  <si>
+    <t>13.07.202639</t>
+  </si>
+  <si>
+    <t>13.07.202640</t>
+  </si>
+  <si>
+    <t>13.07.202641</t>
+  </si>
+  <si>
+    <t>13.07.202642</t>
+  </si>
+  <si>
+    <t>13.07.202643</t>
+  </si>
+  <si>
+    <t>13.07.202644</t>
+  </si>
+  <si>
+    <t>13.07.202645</t>
+  </si>
+  <si>
+    <t>13.07.202646</t>
+  </si>
+  <si>
+    <t>13.07.202647</t>
+  </si>
+  <si>
+    <t>13.07.202648</t>
+  </si>
+  <si>
+    <t>13.07.202649</t>
+  </si>
+  <si>
+    <t>13.07.202650</t>
+  </si>
+  <si>
+    <t>13.07.202651</t>
+  </si>
+  <si>
+    <t>13.07.202652</t>
+  </si>
+  <si>
+    <t>13.07.202653</t>
+  </si>
+  <si>
+    <t>13.07.202654</t>
+  </si>
+  <si>
+    <t>13.07.202655</t>
+  </si>
+  <si>
+    <t>13.07.202656</t>
+  </si>
+  <si>
+    <t>13.07.202657</t>
+  </si>
+  <si>
+    <t>13.07.202658</t>
+  </si>
+  <si>
+    <t>13.07.202659</t>
+  </si>
+  <si>
+    <t>13.07.202660</t>
+  </si>
+  <si>
+    <t>13.07.202661</t>
+  </si>
+  <si>
+    <t>13.07.202662</t>
+  </si>
+  <si>
+    <t>13.07.202663</t>
+  </si>
+  <si>
+    <t>13.07.202664</t>
+  </si>
+  <si>
+    <t>13.07.202665</t>
+  </si>
+  <si>
+    <t>13.07.202666</t>
+  </si>
+  <si>
+    <t>13.07.202667</t>
+  </si>
+  <si>
+    <t>13.07.202668</t>
+  </si>
+  <si>
+    <t>13.07.202669</t>
+  </si>
+  <si>
+    <t>13.07.202670</t>
+  </si>
+  <si>
+    <t>13.07.202671</t>
+  </si>
+  <si>
+    <t>13.07.202672</t>
+  </si>
+  <si>
+    <t>13.07.202673</t>
+  </si>
+  <si>
+    <t>13.07.202674</t>
+  </si>
+  <si>
+    <t>13.07.202675</t>
+  </si>
+  <si>
+    <t>13.07.202676</t>
+  </si>
+  <si>
+    <t>13.07.202677</t>
+  </si>
+  <si>
+    <t>13.07.202678</t>
+  </si>
+  <si>
+    <t>13.07.202679</t>
+  </si>
+  <si>
+    <t>13.07.202680</t>
+  </si>
+  <si>
+    <t>13.07.202681</t>
+  </si>
+  <si>
+    <t>13.07.202682</t>
+  </si>
+  <si>
+    <t>13.07.202683</t>
+  </si>
+  <si>
+    <t>13.07.202684</t>
+  </si>
+  <si>
+    <t>13.07.202685</t>
+  </si>
+  <si>
+    <t>13.07.202686</t>
+  </si>
+  <si>
+    <t>13.07.202687</t>
+  </si>
+  <si>
+    <t>13.07.202688</t>
+  </si>
+  <si>
+    <t>13.07.202689</t>
+  </si>
+  <si>
+    <t>13.07.202690</t>
   </si>
 </sst>
 </file>
@@ -948,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E379"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -970,7 +1546,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B2">
         <v>1.15</v>
@@ -987,7 +1563,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46212.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B3">
         <v>1.15</v>
@@ -1004,7 +1580,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46212.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B4">
         <v>1.15</v>
@@ -1021,7 +1597,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46212.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B5">
         <v>1.15</v>
@@ -1038,7 +1614,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46212.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B6">
         <v>1.15</v>
@@ -1055,7 +1631,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46212.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B7">
         <v>1.15</v>
@@ -1072,7 +1648,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46212.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B8">
         <v>1.15</v>
@@ -1089,10 +1665,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46212.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B9">
-        <v>2.15</v>
+        <v>1.15</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1106,7 +1682,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46212.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B10">
         <v>1.15</v>
@@ -1123,7 +1699,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46212.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B11">
         <v>1.15</v>
@@ -1140,7 +1716,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46212.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B12">
         <v>1.15</v>
@@ -1157,7 +1733,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46212.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B13">
         <v>1.15</v>
@@ -1174,7 +1750,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46212.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B14">
         <v>1.15</v>
@@ -1191,7 +1767,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46212.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B15">
         <v>1.15</v>
@@ -1208,10 +1784,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46212.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.152</v>
+        <v>1.15</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1225,10 +1801,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46212.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B17">
-        <v>1.158</v>
+        <v>1.15</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1242,10 +1818,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46212.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.666</v>
+        <v>14.954</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1259,10 +1835,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46212.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.754</v>
+        <v>15.692</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1276,10 +1852,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46212.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B20">
-        <v>2.918</v>
+        <v>17.438</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1293,10 +1869,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46212.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B21">
-        <v>7.354</v>
+        <v>23.994</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1310,13 +1886,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46212.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B22">
-        <v>65.023</v>
+        <v>122.738</v>
       </c>
       <c r="C22">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1327,13 +1903,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46212.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B23">
-        <v>105.725</v>
+        <v>168.983</v>
       </c>
       <c r="C23">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1344,13 +1920,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46212.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B24">
-        <v>164.476</v>
+        <v>237.35</v>
       </c>
       <c r="C24">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1361,13 +1937,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46212.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B25">
-        <v>232.043</v>
+        <v>313.052</v>
       </c>
       <c r="C25">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1378,13 +1954,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46212.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B26">
-        <v>435.255</v>
+        <v>525.246</v>
       </c>
       <c r="C26">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1395,13 +1971,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46212.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B27">
-        <v>552.554</v>
+        <v>641.347</v>
       </c>
       <c r="C27">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1412,13 +1988,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46212.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B28">
-        <v>681.519</v>
+        <v>790.361</v>
       </c>
       <c r="C28">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1429,13 +2005,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46212.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B29">
-        <v>848.6609999999999</v>
+        <v>950.872</v>
       </c>
       <c r="C29">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1446,13 +2022,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46212.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B30">
-        <v>1202.732</v>
+        <v>1289.762</v>
       </c>
       <c r="C30">
-        <v>912</v>
+        <v>967</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1463,13 +2039,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46212.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B31">
-        <v>1377.478</v>
+        <v>1464.37</v>
       </c>
       <c r="C31">
-        <v>1151</v>
+        <v>1231</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1480,13 +2056,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46212.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B32">
-        <v>1574.717</v>
+        <v>1659.56</v>
       </c>
       <c r="C32">
-        <v>1252</v>
+        <v>1495</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1497,13 +2073,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46212.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B33">
-        <v>1755.942</v>
+        <v>1852.075</v>
       </c>
       <c r="C33">
-        <v>1353</v>
+        <v>1613</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1514,13 +2090,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46212.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B34">
-        <v>2047.13</v>
+        <v>2206.042</v>
       </c>
       <c r="C34">
-        <v>1545</v>
+        <v>1749</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1531,13 +2107,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46212.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B35">
-        <v>2205.002</v>
+        <v>2363.633</v>
       </c>
       <c r="C35">
-        <v>1779</v>
+        <v>1883</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1548,13 +2124,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46212.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B36">
-        <v>2334.464</v>
+        <v>2518.516</v>
       </c>
       <c r="C36">
-        <v>1963</v>
+        <v>1870</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1565,13 +2141,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46212.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B37">
-        <v>2479.077</v>
+        <v>2655.904</v>
       </c>
       <c r="C37">
-        <v>2059</v>
+        <v>2024</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1582,13 +2158,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46212.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B38">
-        <v>2638.104</v>
+        <v>2827.961</v>
       </c>
       <c r="C38">
-        <v>2111</v>
+        <v>2209</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1599,13 +2175,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46212.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B39">
-        <v>2758.822</v>
+        <v>2951.516</v>
       </c>
       <c r="C39">
-        <v>2276</v>
+        <v>2369</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1616,13 +2192,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46212.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B40">
-        <v>2847.861</v>
+        <v>3040.449</v>
       </c>
       <c r="C40">
-        <v>2312</v>
+        <v>2340</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1633,13 +2209,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46212.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B41">
-        <v>2917.485</v>
+        <v>3115.045</v>
       </c>
       <c r="C41">
-        <v>2347</v>
+        <v>2420</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1650,13 +2226,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46212.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B42">
-        <v>2947.43</v>
+        <v>3204.687</v>
       </c>
       <c r="C42">
-        <v>2350</v>
+        <v>2475</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1667,13 +2243,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46212.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B43">
-        <v>2995.426</v>
+        <v>3253.648</v>
       </c>
       <c r="C43">
-        <v>2359</v>
+        <v>2589</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1684,13 +2260,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46212.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B44">
-        <v>3045.006</v>
+        <v>3289.358</v>
       </c>
       <c r="C44">
-        <v>2422</v>
+        <v>2589</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1701,13 +2277,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46212.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B45">
-        <v>3085.457</v>
+        <v>3309.379</v>
       </c>
       <c r="C45">
-        <v>2508</v>
+        <v>2576</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1718,13 +2294,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46212.45833333334</v>
+        <v>46213.45833333334</v>
       </c>
       <c r="B46">
-        <v>3096.238</v>
+        <v>3294.918</v>
       </c>
       <c r="C46">
-        <v>2517</v>
+        <v>2612</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1735,13 +2311,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46212.46875</v>
+        <v>46213.46875</v>
       </c>
       <c r="B47">
-        <v>3111.244</v>
+        <v>3302.598</v>
       </c>
       <c r="C47">
-        <v>2457</v>
+        <v>2621</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1752,13 +2328,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46212.47916666666</v>
+        <v>46213.47916666666</v>
       </c>
       <c r="B48">
-        <v>3107.565</v>
+        <v>3308.605</v>
       </c>
       <c r="C48">
-        <v>2452</v>
+        <v>2586</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1769,13 +2345,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46212.48958333334</v>
+        <v>46213.48958333334</v>
       </c>
       <c r="B49">
-        <v>3107.661</v>
+        <v>3304.786</v>
       </c>
       <c r="C49">
-        <v>2381</v>
+        <v>2448</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1786,13 +2362,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46212.5</v>
+        <v>46213.5</v>
       </c>
       <c r="B50">
-        <v>3101.935</v>
+        <v>3300.627</v>
       </c>
       <c r="C50">
-        <v>2326</v>
+        <v>2476</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1803,13 +2379,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46212.51041666666</v>
+        <v>46213.51041666666</v>
       </c>
       <c r="B51">
-        <v>3082.053</v>
+        <v>3269.841</v>
       </c>
       <c r="C51">
-        <v>2235</v>
+        <v>2350</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1820,13 +2396,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46212.52083333334</v>
+        <v>46213.52083333334</v>
       </c>
       <c r="B52">
-        <v>3068.686</v>
+        <v>3239.349</v>
       </c>
       <c r="C52">
-        <v>2228</v>
+        <v>2382</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1837,13 +2413,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46212.53125</v>
+        <v>46213.53125</v>
       </c>
       <c r="B53">
-        <v>3047.848</v>
+        <v>3216.597</v>
       </c>
       <c r="C53">
-        <v>2219</v>
+        <v>2387</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1854,13 +2430,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46212.5